--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -53824,6 +53824,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2325">
+      <c r="A2325" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2325" t="n">
+        <v>77694</v>
+      </c>
+      <c r="C2325" t="n">
+        <v>81.1999969482422</v>
+      </c>
+      <c r="D2325" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="E2325" t="n">
+        <v>81.0999984741211</v>
+      </c>
+      <c r="F2325" t="n">
+        <v>72.6999969482422</v>
+      </c>
+      <c r="G2325" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -53847,6 +53847,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2326">
+      <c r="A2326" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2326" t="n">
+        <v>25301</v>
+      </c>
+      <c r="C2326" t="n">
+        <v>76.6999969482422</v>
+      </c>
+      <c r="D2326" t="n">
+        <v>70.5999984741211</v>
+      </c>
+      <c r="E2326" t="n">
+        <v>72.3000030517578</v>
+      </c>
+      <c r="F2326" t="n">
+        <v>73.8000030517578</v>
+      </c>
+      <c r="G2326" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -53870,6 +53870,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2327">
+      <c r="A2327" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2327" t="n">
+        <v>24404</v>
+      </c>
+      <c r="C2327" t="n">
+        <v>77.5999984741211</v>
+      </c>
+      <c r="D2327" t="n">
+        <v>72</v>
+      </c>
+      <c r="E2327" t="n">
+        <v>73.3000030517578</v>
+      </c>
+      <c r="F2327" t="n">
+        <v>77.1999969482422</v>
+      </c>
+      <c r="G2327" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -53893,6 +53893,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2328">
+      <c r="A2328" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2328" t="n">
+        <v>65090</v>
+      </c>
+      <c r="C2328" t="n">
+        <v>77.3000030517578</v>
+      </c>
+      <c r="D2328" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E2328" t="n">
+        <v>77.3000030517578</v>
+      </c>
+      <c r="F2328" t="n">
+        <v>73.3000030517578</v>
+      </c>
+      <c r="G2328" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -53734,22 +53734,22 @@
     </row>
     <row r="2321">
       <c r="A2321" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2321" t="n">
-        <v>32091</v>
+        <v>5730</v>
       </c>
       <c r="C2321" t="n">
-        <v>83.4000015258789</v>
+        <v>83.1999969482422</v>
       </c>
       <c r="D2321" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E2321" t="n">
+        <v>82.9000015258789</v>
+      </c>
+      <c r="F2321" t="n">
         <v>83.0999984741211</v>
-      </c>
-      <c r="F2321" t="n">
-        <v>79.1999969482422</v>
       </c>
       <c r="G2321" t="s">
         <v>7</v>
@@ -53757,22 +53757,22 @@
     </row>
     <row r="2322">
       <c r="A2322" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2322" t="n">
-        <v>18365</v>
+        <v>32091</v>
       </c>
       <c r="C2322" t="n">
-        <v>81.5999984741211</v>
+        <v>83.4000015258789</v>
       </c>
       <c r="D2322" t="n">
-        <v>78.5</v>
+        <v>77</v>
       </c>
       <c r="E2322" t="n">
-        <v>79.6999969482422</v>
+        <v>83.0999984741211</v>
       </c>
       <c r="F2322" t="n">
-        <v>80.8000030517578</v>
+        <v>79.1999969482422</v>
       </c>
       <c r="G2322" t="s">
         <v>7</v>
@@ -53780,22 +53780,22 @@
     </row>
     <row r="2323">
       <c r="A2323" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2323" t="n">
-        <v>12028</v>
+        <v>18365</v>
       </c>
       <c r="C2323" t="n">
-        <v>82.6999969482422</v>
+        <v>81.5999984741211</v>
       </c>
       <c r="D2323" t="n">
-        <v>79.0999984741211</v>
+        <v>78.5</v>
       </c>
       <c r="E2323" t="n">
-        <v>81.9000015258789</v>
+        <v>79.6999969482422</v>
       </c>
       <c r="F2323" t="n">
-        <v>79.0999984741211</v>
+        <v>80.8000030517578</v>
       </c>
       <c r="G2323" t="s">
         <v>7</v>
@@ -53803,22 +53803,22 @@
     </row>
     <row r="2324">
       <c r="A2324" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2324" t="n">
-        <v>15805</v>
+        <v>12028</v>
       </c>
       <c r="C2324" t="n">
-        <v>79.6999969482422</v>
+        <v>82.6999969482422</v>
       </c>
       <c r="D2324" t="n">
-        <v>76.9000015258789</v>
+        <v>79.0999984741211</v>
       </c>
       <c r="E2324" t="n">
-        <v>79.4000015258789</v>
+        <v>81.9000015258789</v>
       </c>
       <c r="F2324" t="n">
-        <v>78.8000030517578</v>
+        <v>79.0999984741211</v>
       </c>
       <c r="G2324" t="s">
         <v>7</v>
@@ -53826,22 +53826,22 @@
     </row>
     <row r="2325">
       <c r="A2325" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2325" t="n">
-        <v>77694</v>
+        <v>15805</v>
       </c>
       <c r="C2325" t="n">
-        <v>81.1999969482422</v>
+        <v>79.6999969482422</v>
       </c>
       <c r="D2325" t="n">
-        <v>69.5</v>
+        <v>76.9000015258789</v>
       </c>
       <c r="E2325" t="n">
-        <v>81.0999984741211</v>
+        <v>79.4000015258789</v>
       </c>
       <c r="F2325" t="n">
-        <v>72.6999969482422</v>
+        <v>78.8000030517578</v>
       </c>
       <c r="G2325" t="s">
         <v>7</v>
@@ -53849,22 +53849,22 @@
     </row>
     <row r="2326">
       <c r="A2326" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2326" t="n">
-        <v>25301</v>
+        <v>77694</v>
       </c>
       <c r="C2326" t="n">
-        <v>76.6999969482422</v>
+        <v>81.1999969482422</v>
       </c>
       <c r="D2326" t="n">
-        <v>70.5999984741211</v>
+        <v>69.5</v>
       </c>
       <c r="E2326" t="n">
-        <v>72.3000030517578</v>
+        <v>81.0999984741211</v>
       </c>
       <c r="F2326" t="n">
-        <v>73.8000030517578</v>
+        <v>72.6999969482422</v>
       </c>
       <c r="G2326" t="s">
         <v>7</v>
@@ -53872,22 +53872,22 @@
     </row>
     <row r="2327">
       <c r="A2327" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2327" t="n">
-        <v>24404</v>
+        <v>25301</v>
       </c>
       <c r="C2327" t="n">
-        <v>77.5999984741211</v>
+        <v>76.6999969482422</v>
       </c>
       <c r="D2327" t="n">
-        <v>72</v>
+        <v>70.5999984741211</v>
       </c>
       <c r="E2327" t="n">
-        <v>73.3000030517578</v>
+        <v>72.3000030517578</v>
       </c>
       <c r="F2327" t="n">
-        <v>77.1999969482422</v>
+        <v>73.8000030517578</v>
       </c>
       <c r="G2327" t="s">
         <v>7</v>
@@ -53895,24 +53895,47 @@
     </row>
     <row r="2328">
       <c r="A2328" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2328" t="n">
-        <v>65090</v>
+        <v>24404</v>
       </c>
       <c r="C2328" t="n">
-        <v>77.3000030517578</v>
+        <v>77.5999984741211</v>
       </c>
       <c r="D2328" t="n">
-        <v>72.5</v>
+        <v>72</v>
       </c>
       <c r="E2328" t="n">
-        <v>77.3000030517578</v>
+        <v>73.3000030517578</v>
       </c>
       <c r="F2328" t="n">
+        <v>77.1999969482422</v>
+      </c>
+      <c r="G2328" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2329" t="n">
+        <v>31005</v>
+      </c>
+      <c r="C2329" t="n">
+        <v>74.8000030517578</v>
+      </c>
+      <c r="D2329" t="n">
+        <v>73.0999984741211</v>
+      </c>
+      <c r="E2329" t="n">
+        <v>73.4000015258789</v>
+      </c>
+      <c r="F2329" t="n">
         <v>73.3000030517578</v>
       </c>
-      <c r="G2328" t="s">
+      <c r="G2329" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -421,7 +421,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>11.8307571411133</v>
+        <v>11.8307580947876</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>11.712366104126</v>
+        <v>11.7123651504517</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G4" t="n">
-        <v>11.1795997619629</v>
+        <v>11.1796016693115</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G6" t="n">
-        <v>10.8920774459839</v>
+        <v>10.8920783996582</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1711444854736</v>
+        <v>11.1711454391479</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>11.2726240158081</v>
+        <v>11.2726230621338</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G12" t="n">
-        <v>11.1880569458008</v>
+        <v>11.1880559921265</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G17" t="n">
-        <v>11.2726240158081</v>
+        <v>11.2726230621338</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>11.0358381271362</v>
+        <v>11.0358390808105</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>11.2895364761353</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>11.1204051971436</v>
+        <v>11.1204042434692</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>10.9174461364746</v>
+        <v>10.9174470901489</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>10.9512720108032</v>
+        <v>10.9512729644775</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>10.9850997924805</v>
+        <v>10.9850988388062</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G32" t="n">
-        <v>10.8159675598145</v>
+        <v>10.8159685134888</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7652263641357</v>
+        <v>10.7652282714844</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G35" t="n">
-        <v>10.6468353271484</v>
+        <v>10.6468372344971</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>10.942816734314</v>
+        <v>10.9428157806396</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G39" t="n">
-        <v>10.9512720108032</v>
+        <v>10.9512729644775</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G42" t="n">
-        <v>11.2387971878052</v>
+        <v>11.2387962341309</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.6700839996338</v>
+        <v>11.6700820922852</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G44" t="n">
-        <v>11.6700839996338</v>
+        <v>11.6700820922852</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.6447124481201</v>
+        <v>11.6447134017944</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6447124481201</v>
+        <v>11.6447134017944</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5009498596191</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>11.5009498596191</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>11.5855178833008</v>
+        <v>11.5855169296265</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.5</v>
       </c>
       <c r="G53" t="n">
-        <v>11.4163837432861</v>
+        <v>11.4163856506348</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>11.2895364761353</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>11.2810792922974</v>
+        <v>11.2810821533203</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>13.25</v>
       </c>
       <c r="G57" t="n">
-        <v>11.2049703598022</v>
+        <v>11.2049694061279</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G58" t="n">
-        <v>11.1288614273071</v>
+        <v>11.1288604736328</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>11.1204051971436</v>
+        <v>11.1204042434692</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G64" t="n">
-        <v>11.1542310714722</v>
+        <v>11.1542301177979</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>10.942816734314</v>
+        <v>10.9428157806396</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>11.0020132064819</v>
+        <v>11.0020141601562</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667087554932</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G69" t="n">
-        <v>10.8582515716553</v>
+        <v>10.858250617981</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5538120269775</v>
+        <v>10.5538139343262</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.5</v>
       </c>
       <c r="G86" t="n">
-        <v>10.5707273483276</v>
+        <v>10.570725440979</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G87" t="n">
-        <v>10.6806631088257</v>
+        <v>10.6806640625</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G91" t="n">
-        <v>10.9850997924805</v>
+        <v>10.9850988388062</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.6383781433105</v>
+        <v>10.6383810043335</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G94" t="n">
-        <v>10.6383781433105</v>
+        <v>10.6383810043335</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G97" t="n">
-        <v>10.8159675598145</v>
+        <v>10.8159685134888</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G102" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667087554932</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>10.8159675598145</v>
+        <v>10.8159685134888</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G105" t="n">
-        <v>10.6806631088257</v>
+        <v>10.6806640625</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G106" t="n">
-        <v>10.8497953414917</v>
+        <v>10.8497943878174</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861602783203</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.5</v>
       </c>
       <c r="G120" t="n">
-        <v>10.5707273483276</v>
+        <v>10.570725440979</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.5</v>
       </c>
       <c r="G126" t="n">
-        <v>10.5707273483276</v>
+        <v>10.570725440979</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861602783203</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>10.4015951156616</v>
+        <v>10.4015960693359</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>12.25</v>
       </c>
       <c r="G139" t="n">
-        <v>10.3593120574951</v>
+        <v>10.3593130111694</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861602783203</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861602783203</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861602783203</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>10.1901798248291</v>
+        <v>10.1901817321777</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861602783203</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861602783203</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861602783203</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>10.9512720108032</v>
+        <v>10.9512729644775</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G155" t="n">
-        <v>10.9512720108032</v>
+        <v>10.9512729644775</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667087554932</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G163" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G165" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.5</v>
       </c>
       <c r="G167" t="n">
-        <v>10.5707273483276</v>
+        <v>10.570725440979</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.5</v>
       </c>
       <c r="G169" t="n">
-        <v>10.5707273483276</v>
+        <v>10.570725440979</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>10.5707273483276</v>
+        <v>10.570725440979</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667087554932</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>10.9512720108032</v>
+        <v>10.9512729644775</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G177" t="n">
-        <v>10.9512720108032</v>
+        <v>10.9512729644775</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667087554932</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>11.1626882553101</v>
+        <v>11.1626863479614</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>10.9512720108032</v>
+        <v>10.9512729644775</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G185" t="n">
-        <v>11.1626882553101</v>
+        <v>11.1626863479614</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>11.2895364761353</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>11.2895364761353</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2472543716431</v>
+        <v>11.2472534179688</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>11.0358381271362</v>
+        <v>11.0358390808105</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2895364761353</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2472543716431</v>
+        <v>11.2472534179688</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>11.3741016387939</v>
+        <v>11.3741025924683</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>11.5855178833008</v>
+        <v>11.5855169296265</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>13.5</v>
       </c>
       <c r="G200" t="n">
-        <v>11.4163837432861</v>
+        <v>11.4163856506348</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.54323387146</v>
+        <v>11.5432348251343</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>11.54323387146</v>
+        <v>11.5432348251343</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5009498596191</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7869577407837</v>
+        <v>11.786958694458</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>11.4402837753296</v>
+        <v>11.440281867981</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>11.4402837753296</v>
+        <v>11.440281867981</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>13.75</v>
       </c>
       <c r="G212" t="n">
-        <v>11.9169616699219</v>
+        <v>11.9169607162476</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>11.5269527435303</v>
+        <v>11.526951789856</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>11.8302927017212</v>
+        <v>11.8302917480469</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>11.8302927017212</v>
+        <v>11.8302917480469</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>11.9602956771851</v>
+        <v>11.9602966308594</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>13.75</v>
       </c>
       <c r="G228" t="n">
-        <v>11.9169616699219</v>
+        <v>11.9169607162476</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>12.0902976989746</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>13.75</v>
       </c>
       <c r="G230" t="n">
-        <v>11.9169616699219</v>
+        <v>11.9169607162476</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G231" t="n">
-        <v>11.8302927017212</v>
+        <v>11.8302917480469</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>13.75</v>
       </c>
       <c r="G233" t="n">
-        <v>11.9169616699219</v>
+        <v>11.9169607162476</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>11.7869577407837</v>
+        <v>11.786958694458</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.0902976989746</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>12.0036306381226</v>
+        <v>12.0036296844482</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>12.0902976989746</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>12.7403144836426</v>
+        <v>12.7403154373169</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G247" t="n">
-        <v>12.9136533737183</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>12.9136533737183</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8703174591064</v>
+        <v>12.8703184127808</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>13.0436553955078</v>
+        <v>13.0436563491821</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G256" t="n">
-        <v>12.9136533737183</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9136533737183</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>12.9569864273071</v>
+        <v>12.9569873809814</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>12.8269834518433</v>
+        <v>12.8269844055176</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>12.9136533737183</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>15.5</v>
       </c>
       <c r="G297" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G304" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>15.75</v>
       </c>
       <c r="G308" t="n">
-        <v>13.6503372192383</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G315" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G322" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>15.5</v>
       </c>
       <c r="G330" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>15.5</v>
       </c>
       <c r="G331" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>15.75</v>
       </c>
       <c r="G333" t="n">
-        <v>13.6503372192383</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>15.5</v>
       </c>
       <c r="G334" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G343" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.75</v>
       </c>
       <c r="G348" t="n">
-        <v>13.6503372192383</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>15.75</v>
       </c>
       <c r="G350" t="n">
-        <v>13.6503372192383</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>15.5</v>
       </c>
       <c r="G351" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G353" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G355" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G356" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>15.75</v>
       </c>
       <c r="G357" t="n">
-        <v>13.6503372192383</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>15.5</v>
       </c>
       <c r="G359" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G360" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G365" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>15.5</v>
       </c>
       <c r="G371" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>15.5</v>
       </c>
       <c r="G372" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>13.1736574172974</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>15.5</v>
       </c>
       <c r="G375" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>15.5</v>
       </c>
       <c r="G382" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>15.75</v>
       </c>
       <c r="G386" t="n">
-        <v>13.6503372192383</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>14.2136831283569</v>
+        <v>14.2136850357056</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G389" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736928939819</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>17.25</v>
       </c>
       <c r="G392" t="n">
-        <v>14.9503688812256</v>
+        <v>14.9503707885742</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>14.9070358276367</v>
+        <v>14.9070348739624</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>17</v>
       </c>
       <c r="G395" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736928939819</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>16.75</v>
       </c>
       <c r="G397" t="n">
-        <v>14.5170240402222</v>
+        <v>14.5170278549194</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>14.560359954834</v>
+        <v>14.5603580474854</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>17</v>
       </c>
       <c r="G400" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>14.3870220184326</v>
+        <v>14.3870239257812</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G403" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>14.560359954834</v>
+        <v>14.5603580474854</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>14.560359954834</v>
+        <v>14.5603580474854</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>17</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>17</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>16.75</v>
       </c>
       <c r="G417" t="n">
-        <v>14.5170240402222</v>
+        <v>14.5170278549194</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736928939819</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736928939819</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>16.5</v>
       </c>
       <c r="G420" t="n">
-        <v>14.3003540039062</v>
+        <v>14.3003520965576</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.5</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3003540039062</v>
+        <v>14.3003520965576</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>14.3436861038208</v>
+        <v>14.3436870574951</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>14.2570190429688</v>
+        <v>14.2570199966431</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>14.3870220184326</v>
+        <v>14.3870239257812</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>14.3870220184326</v>
+        <v>14.3870239257812</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>14.2570190429688</v>
+        <v>14.2570199966431</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>17</v>
       </c>
       <c r="G430" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736928939819</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>17</v>
       </c>
       <c r="G432" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>17</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>14.8203649520874</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>14.8203649520874</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>14.8203649520874</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>14.8203649520874</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G443" t="n">
-        <v>14.9070358276367</v>
+        <v>14.9070348739624</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G444" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>14.9937028884888</v>
+        <v>14.9937038421631</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G446" t="n">
-        <v>14.9070358276367</v>
+        <v>14.9070348739624</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>14.8203649520874</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>15.0370388031006</v>
+        <v>15.0370378494263</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803737640381</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803737640381</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>14.9937028884888</v>
+        <v>14.9937038421631</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803737640381</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>15.526535987854</v>
+        <v>15.5265369415283</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>15.526535987854</v>
+        <v>15.5265369415283</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>17.25</v>
       </c>
       <c r="G456" t="n">
-        <v>15.3926877975464</v>
+        <v>15.3926887512207</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>15.526535987854</v>
+        <v>15.5265369415283</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>17.25</v>
       </c>
       <c r="G458" t="n">
-        <v>15.3926877975464</v>
+        <v>15.3926887512207</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>17</v>
       </c>
       <c r="G459" t="n">
-        <v>15.1696071624756</v>
+        <v>15.1696062088013</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>15.0803728103638</v>
+        <v>15.0803718566895</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G463" t="n">
-        <v>15.1249914169312</v>
+        <v>15.1249885559082</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>15.4373035430908</v>
+        <v>15.4373064041138</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>15.4373035430908</v>
+        <v>15.4373064041138</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G469" t="n">
-        <v>15.7496204376221</v>
+        <v>15.7496194839478</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>15.8834705352783</v>
+        <v>15.883469581604</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>15.8834705352783</v>
+        <v>15.883469581604</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G477" t="n">
-        <v>17.1327323913574</v>
+        <v>17.1327304840088</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>19.5</v>
       </c>
       <c r="G478" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>19.5</v>
       </c>
       <c r="G480" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>19.5</v>
       </c>
       <c r="G481" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>17.4450435638428</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G486" t="n">
-        <v>17.3111953735352</v>
+        <v>17.3111972808838</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>17.4450435638428</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>19.5</v>
       </c>
       <c r="G489" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G504" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250587463379</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G505" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G508" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250587463379</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>17.4450435638428</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>17.4450435638428</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.6681270599365</v>
+        <v>17.6681289672852</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>17.6681270599365</v>
+        <v>17.6681289672852</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>17.3111953735352</v>
+        <v>17.3111972808838</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>17.2665786743164</v>
+        <v>17.266580581665</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>17.2665786743164</v>
+        <v>17.266580581665</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>19.5</v>
       </c>
       <c r="G524" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>19.5</v>
       </c>
       <c r="G525" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>17.3111953735352</v>
+        <v>17.3111972808838</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>19.5</v>
       </c>
       <c r="G527" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>19.5</v>
       </c>
       <c r="G528" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>17.4896621704102</v>
+        <v>17.4896640777588</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>17.4450435638428</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G532" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>17.7573623657227</v>
+        <v>17.757360458374</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>20</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>20</v>
       </c>
       <c r="G535" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250587463379</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>20</v>
       </c>
       <c r="G537" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>20</v>
       </c>
       <c r="G539" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G550" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250587463379</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G552" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250587463379</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>17.7127456665039</v>
+        <v>17.7127475738525</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>17.7127456665039</v>
+        <v>17.7127475738525</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G562" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250587463379</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>20</v>
       </c>
       <c r="G565" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>20</v>
       </c>
       <c r="G566" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>20</v>
       </c>
       <c r="G567" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>20</v>
       </c>
       <c r="G568" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>17.6681270599365</v>
+        <v>17.6681289672852</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>20</v>
       </c>
       <c r="G570" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>20</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>20</v>
       </c>
       <c r="G572" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250587463379</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>19.452787399292</v>
+        <v>19.4527893066406</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>19.452787399292</v>
+        <v>19.4527893066406</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>19.2743225097656</v>
+        <v>19.2743244171143</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>19.452787399292</v>
+        <v>19.4527893066406</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>19.7204895019531</v>
+        <v>19.7204856872559</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>19.809720993042</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>19.7204895019531</v>
+        <v>19.7204856872559</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>19.7204895019531</v>
+        <v>19.7204856872559</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>20.1666507720947</v>
+        <v>20.1666526794434</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>20.1666507720947</v>
+        <v>20.1666526794434</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>19.809720993042</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G608" t="n">
-        <v>19.452787399292</v>
+        <v>19.4527893066406</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>19.2743225097656</v>
+        <v>19.2743244171143</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>19.2743225097656</v>
+        <v>19.2743244171143</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G612" t="n">
-        <v>19.7204895019531</v>
+        <v>19.7204856872559</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>19.8989524841309</v>
+        <v>19.8989543914795</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>19.809720993042</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>20.7912826538086</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>20.7020511627197</v>
+        <v>20.7020530700684</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>20.7020511627197</v>
+        <v>20.7020530700684</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>21.5051460266113</v>
+        <v>21.5051498413086</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>21.5051460266113</v>
+        <v>21.5051498413086</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>24.5</v>
       </c>
       <c r="G627" t="n">
-        <v>21.8620796203613</v>
+        <v>21.8620777130127</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>24</v>
       </c>
       <c r="G631" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>21.6836128234863</v>
+        <v>21.6836109161377</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>21.6836128234863</v>
+        <v>21.6836109161377</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>21.2374496459961</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>24</v>
       </c>
       <c r="G637" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>23.5</v>
       </c>
       <c r="G640" t="n">
-        <v>20.969747543335</v>
+        <v>20.9697513580322</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>20.7912826538086</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>24</v>
       </c>
       <c r="G648" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>24</v>
       </c>
       <c r="G649" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>24</v>
       </c>
       <c r="G650" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>21.2374496459961</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>21.2374496459961</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>20.7020511627197</v>
+        <v>20.7020530700684</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>23.5</v>
       </c>
       <c r="G661" t="n">
-        <v>20.969747543335</v>
+        <v>20.9697513580322</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>19.7204895019531</v>
+        <v>19.7204856872559</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G671" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G672" t="n">
-        <v>16.4188671112061</v>
+        <v>16.4188652038574</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>17.4896621704102</v>
+        <v>17.4896640777588</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>16.1957855224609</v>
+        <v>16.1957836151123</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>15.035756111145</v>
+        <v>15.0357580184937</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>15.7496204376221</v>
+        <v>15.7496194839478</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250587463379</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>20.7912826538086</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>21.2374496459961</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G689" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>23.5</v>
       </c>
       <c r="G693" t="n">
-        <v>20.969747543335</v>
+        <v>20.9697513580322</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>21.6836128234863</v>
+        <v>21.6836109161377</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G696" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>24</v>
       </c>
       <c r="G699" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>24</v>
       </c>
       <c r="G704" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>24</v>
       </c>
       <c r="G706" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>24</v>
       </c>
       <c r="G707" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G709" t="n">
-        <v>21.6836128234863</v>
+        <v>21.6836109161377</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>22.0405464172363</v>
+        <v>22.0405445098877</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678779602051</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>22.4588069915771</v>
+        <v>22.4588050842285</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678779602051</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>22.5497303009033</v>
+        <v>22.5497341156006</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>22.095100402832</v>
+        <v>22.0950984954834</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>24</v>
       </c>
       <c r="G733" t="n">
-        <v>21.822322845459</v>
+        <v>21.8223190307617</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>23.5</v>
       </c>
       <c r="G734" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>21.6404705047607</v>
+        <v>21.6404685974121</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>21.4586162567139</v>
+        <v>21.4586143493652</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>23.5</v>
       </c>
       <c r="G740" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>23.5</v>
       </c>
       <c r="G741" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>23.5</v>
       </c>
       <c r="G742" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>21.2767601013184</v>
+        <v>21.276762008667</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>23.5</v>
       </c>
       <c r="G749" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>23.5</v>
       </c>
       <c r="G750" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>24</v>
       </c>
       <c r="G751" t="n">
-        <v>21.822322845459</v>
+        <v>21.8223190307617</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>24</v>
       </c>
       <c r="G752" t="n">
-        <v>21.822322845459</v>
+        <v>21.8223190307617</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>23.5</v>
       </c>
       <c r="G758" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>21.2767601013184</v>
+        <v>21.276762008667</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G761" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>23.5</v>
       </c>
       <c r="G763" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>23.5</v>
       </c>
       <c r="G765" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G768" t="n">
-        <v>21.4586162567139</v>
+        <v>21.4586143493652</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G769" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>21.0949115753174</v>
+        <v>21.094913482666</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>21.0949115753174</v>
+        <v>21.094913482666</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>21.0949115753174</v>
+        <v>21.094913482666</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>21.4586162567139</v>
+        <v>21.4586143493652</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G776" t="n">
-        <v>21.2767601013184</v>
+        <v>21.276762008667</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>21.2767601013184</v>
+        <v>21.276762008667</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>21.0949115753174</v>
+        <v>21.094913482666</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>21.2767601013184</v>
+        <v>21.276762008667</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>20.7312049865723</v>
+        <v>20.7312068939209</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>23.5</v>
       </c>
       <c r="G786" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>23.5</v>
       </c>
       <c r="G787" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G796" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>20.3675022125244</v>
+        <v>20.3674983978271</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G804" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678779602051</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>23.5499210357666</v>
+        <v>23.5499229431152</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>22.9134387969971</v>
+        <v>22.9134368896484</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.5501098632812</v>
+        <v>24.5501117706299</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>24.0045547485352</v>
+        <v>24.0045528411865</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>23.0952892303467</v>
+        <v>23.0952911376953</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>24.0045547485352</v>
+        <v>24.0045528411865</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>24.4591865539551</v>
+        <v>24.4591846466064</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>24.2773342132568</v>
+        <v>24.2773323059082</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7319641113281</v>
+        <v>24.7319660186768</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>28</v>
       </c>
       <c r="G820" t="n">
-        <v>25.4593734741211</v>
+        <v>25.4593753814697</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>25.2775230407715</v>
+        <v>25.2775211334229</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>25.186595916748</v>
+        <v>25.1865940093994</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>27</v>
       </c>
       <c r="G832" t="n">
-        <v>24.5501098632812</v>
+        <v>24.5501117706299</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G834" t="n">
-        <v>24.186408996582</v>
+        <v>24.1864070892334</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>24.2773342132568</v>
+        <v>24.2773323059082</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>25.7321529388428</v>
+        <v>25.7321510314941</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>28.5</v>
       </c>
       <c r="G839" t="n">
-        <v>25.9140071868896</v>
+        <v>25.9140090942383</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>25.8230800628662</v>
+        <v>25.8230781555176</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>28</v>
       </c>
       <c r="G842" t="n">
-        <v>25.4593734741211</v>
+        <v>25.4593753814697</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>28</v>
       </c>
       <c r="G843" t="n">
-        <v>25.4593734741211</v>
+        <v>25.4593753814697</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>26.1867847442627</v>
+        <v>26.1867828369141</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>28.5</v>
       </c>
       <c r="G848" t="n">
-        <v>25.9140071868896</v>
+        <v>25.9140090942383</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>28.5</v>
       </c>
       <c r="G849" t="n">
-        <v>25.9140071868896</v>
+        <v>25.9140090942383</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>28</v>
       </c>
       <c r="G851" t="n">
-        <v>25.4593734741211</v>
+        <v>25.4593753814697</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>26.1867847442627</v>
+        <v>26.1867828369141</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>25.8230800628662</v>
+        <v>25.8230781555176</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>28.5</v>
       </c>
       <c r="G856" t="n">
-        <v>25.9140071868896</v>
+        <v>25.9140090942383</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G857" t="n">
-        <v>26.7323417663574</v>
+        <v>26.7323455810547</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>28.0053119659424</v>
+        <v>28.0053100585938</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>29.0055046081543</v>
+        <v>29.005500793457</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>29.7329158782959</v>
+        <v>29.7329120635986</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G861" t="n">
-        <v>30.2784729003906</v>
+        <v>30.2784690856934</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>32.5</v>
       </c>
       <c r="G862" t="n">
-        <v>29.5510578155518</v>
+        <v>29.5510597229004</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G864" t="n">
-        <v>29.9147644042969</v>
+        <v>29.9147682189941</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>30.6421756744385</v>
+        <v>30.6421794891357</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>31.1877326965332</v>
+        <v>31.1877346038818</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>33.9155197143555</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>34.2792320251465</v>
+        <v>34.2792282104492</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>35.643123626709</v>
+        <v>35.6431274414062</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>40</v>
       </c>
       <c r="G873" t="n">
-        <v>36.3705406188965</v>
+        <v>36.3705368041992</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>35.5521965026855</v>
+        <v>35.5522003173828</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G877" t="n">
-        <v>34.9157180786133</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G878" t="n">
-        <v>34.9157180786133</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>34.7338600158691</v>
+        <v>34.7338638305664</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>34.3701591491699</v>
+        <v>34.3701515197754</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>37.5</v>
       </c>
       <c r="G883" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>34.8247871398926</v>
+        <v>34.8247909545898</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G885" t="n">
-        <v>34.7338600158691</v>
+        <v>34.7338638305664</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>34.8247871398926</v>
+        <v>34.8247909545898</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>34.9157180786133</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>37.5</v>
       </c>
       <c r="G893" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>37</v>
       </c>
       <c r="G894" t="n">
-        <v>33.6427459716797</v>
+        <v>33.642749786377</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G896" t="n">
-        <v>34.2792320251465</v>
+        <v>34.2792282104492</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.3701591491699</v>
+        <v>34.3701515197754</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>33.3699684143066</v>
+        <v>33.3699645996094</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G900" t="n">
-        <v>33.0971870422363</v>
+        <v>33.0971908569336</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G901" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244094848633</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>34.3701591491699</v>
+        <v>34.3701515197754</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>33.9155197143555</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>38.5</v>
       </c>
       <c r="G906" t="n">
-        <v>35.0066375732422</v>
+        <v>35.0066413879395</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G907" t="n">
-        <v>34.9157180786133</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>34.8247871398926</v>
+        <v>34.8247909545898</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>37.5</v>
       </c>
       <c r="G909" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>33.2790412902832</v>
+        <v>33.2790336608887</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>37</v>
       </c>
       <c r="G914" t="n">
-        <v>33.6427459716797</v>
+        <v>33.642749786377</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G915" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244094848633</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>32.9153327941895</v>
+        <v>32.9153366088867</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>37</v>
       </c>
       <c r="G917" t="n">
-        <v>33.6427459716797</v>
+        <v>33.642749786377</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>36.5</v>
       </c>
       <c r="G919" t="n">
-        <v>33.1881103515625</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G920" t="n">
-        <v>33.0062637329102</v>
+        <v>33.0062599182129</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G921" t="n">
-        <v>32.9153327941895</v>
+        <v>32.9153366088867</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>36.5</v>
       </c>
       <c r="G923" t="n">
-        <v>33.1881103515625</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>36.5</v>
       </c>
       <c r="G924" t="n">
-        <v>33.1881103515625</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G925" t="n">
-        <v>33.2790412902832</v>
+        <v>33.2790336608887</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>33.0062637329102</v>
+        <v>33.0062599182129</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.6425590515137</v>
+        <v>32.6425552368164</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>33.9155197143555</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>34.3701591491699</v>
+        <v>34.3701515197754</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>37.5</v>
       </c>
       <c r="G936" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>37.5</v>
       </c>
       <c r="G939" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>37</v>
       </c>
       <c r="G941" t="n">
-        <v>33.6427459716797</v>
+        <v>33.642749786377</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.9155197143555</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G943" t="n">
-        <v>34.0064506530762</v>
+        <v>34.0064544677734</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>37.5</v>
       </c>
       <c r="G944" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G945" t="n">
-        <v>34.3701591491699</v>
+        <v>34.3701515197754</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>33.9155197143555</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>37.5</v>
       </c>
       <c r="G947" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G948" t="n">
-        <v>33.9155197143555</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G949" t="n">
-        <v>33.3699684143066</v>
+        <v>33.3699645996094</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G950" t="n">
-        <v>33.3699684143066</v>
+        <v>33.3699645996094</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G951" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244094848633</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244094848633</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>33.4608917236328</v>
+        <v>33.4608879089355</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>33.4608917236328</v>
+        <v>33.4608879089355</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>34.5444602966309</v>
+        <v>34.5444641113281</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G965" t="n">
-        <v>34.5444602966309</v>
+        <v>34.5444641113281</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G966" t="n">
-        <v>34.1740074157715</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>34.1740074157715</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G968" t="n">
-        <v>33.8961715698242</v>
+        <v>33.8961639404297</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G971" t="n">
-        <v>34.1740074157715</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G973" t="n">
-        <v>34.0813941955566</v>
+        <v>34.0813903808594</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>33.5257225036621</v>
+        <v>33.5257263183594</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G984" t="n">
-        <v>33.5257225036621</v>
+        <v>33.5257263183594</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>39</v>
       </c>
       <c r="G986" t="n">
-        <v>36.1188774108887</v>
+        <v>36.1188735961914</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>46</v>
       </c>
       <c r="G989" t="n">
-        <v>42.601749420166</v>
+        <v>42.6017456054688</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>42.2312927246094</v>
+        <v>42.2312965393066</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>41.5830078125</v>
+        <v>41.5830116271973</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>44.3613815307617</v>
+        <v>44.361385345459</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>45.9357948303223</v>
+        <v>45.9357986450195</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>48.9000015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>45.2875137329102</v>
+        <v>45.2875099182129</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>49.5</v>
       </c>
       <c r="G998" t="n">
-        <v>45.8431854248047</v>
+        <v>45.8431816101074</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>45.472728729248</v>
+        <v>45.4727325439453</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1001" t="n">
-        <v>46.1210250854492</v>
+        <v>46.121021270752</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>45.5653495788574</v>
+        <v>45.5653457641602</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>49.5</v>
       </c>
       <c r="G1003" t="n">
-        <v>45.8431854248047</v>
+        <v>45.8431816101074</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G1004" t="n">
-        <v>45.1948890686035</v>
+        <v>45.194896697998</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>46.1210250854492</v>
+        <v>46.121021270752</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>50</v>
       </c>
       <c r="G1008" t="n">
-        <v>46.3062438964844</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>50</v>
       </c>
       <c r="G1010" t="n">
-        <v>46.3062438964844</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>50</v>
       </c>
       <c r="G1011" t="n">
-        <v>46.3062438964844</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>46.1210250854492</v>
+        <v>46.121021270752</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>46.8619194030762</v>
+        <v>46.8619232177734</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>50</v>
       </c>
       <c r="G1020" t="n">
-        <v>46.3062438964844</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>49.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>45.8431854248047</v>
+        <v>45.8431816101074</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>54</v>
       </c>
       <c r="G1023" t="n">
-        <v>50.0107460021973</v>
+        <v>50.0107421875</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G1025" t="n">
-        <v>50.3811950683594</v>
+        <v>50.3811988830566</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>53.5300216674805</v>
+        <v>53.5300178527832</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>58.1606407165527</v>
+        <v>58.1606369018555</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>55.0118217468262</v>
+        <v>55.0118255615234</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>56.3083953857422</v>
+        <v>56.3083992004395</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>56.8640747070312</v>
+        <v>56.864070892334</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>59.642448425293</v>
+        <v>59.6424522399902</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1044" t="n">
-        <v>60.0128936767578</v>
+        <v>60.0128974914551</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>60.7537879943848</v>
+        <v>60.753791809082</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>65.1992034912109</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1051" t="n">
-        <v>65.1992034912109</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>65.3844223022461</v>
+        <v>65.3844146728516</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>65.1992034912109</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>66</v>
       </c>
       <c r="G1056" t="n">
-        <v>61.1242370605469</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>61.6799125671387</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>61.6799125671387</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>69</v>
       </c>
       <c r="G1059" t="n">
-        <v>63.9026145935059</v>
+        <v>63.9026222229004</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1062" t="n">
-        <v>62.4208221435547</v>
+        <v>62.420825958252</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1064" t="n">
-        <v>61.6799125671387</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1066" t="n">
-        <v>58.1606407165527</v>
+        <v>58.1606369018555</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>58.5311012268066</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>63</v>
       </c>
       <c r="G1070" t="n">
-        <v>58.3458709716797</v>
+        <v>58.3458671569824</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>64</v>
       </c>
       <c r="G1071" t="n">
-        <v>59.2719955444336</v>
+        <v>59.2719917297363</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1072" t="n">
-        <v>57.9754219055176</v>
+        <v>57.9754180908203</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>57.6049690246582</v>
+        <v>57.6049728393555</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1075" t="n">
-        <v>56.8640747070312</v>
+        <v>56.864070892334</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>58.5311012268066</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1078" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469390869141</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1079" t="n">
-        <v>61.3094635009766</v>
+        <v>61.3094711303711</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1080" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469390869141</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1081" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469390869141</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>69</v>
       </c>
       <c r="G1082" t="n">
-        <v>63.9026145935059</v>
+        <v>63.9026222229004</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>68</v>
       </c>
       <c r="G1083" t="n">
-        <v>62.9764976501465</v>
+        <v>62.9765014648438</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>68</v>
       </c>
       <c r="G1087" t="n">
-        <v>62.9764976501465</v>
+        <v>62.9765014648438</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1088" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469390869141</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>68</v>
       </c>
       <c r="G1089" t="n">
-        <v>62.9764976501465</v>
+        <v>62.9765014648438</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>65.5696411132812</v>
+        <v>65.5696487426758</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G1097" t="n">
-        <v>65.9400863647461</v>
+        <v>65.9401016235352</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1098" t="n">
-        <v>65.1992034912109</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1099" t="n">
-        <v>65.5696411132812</v>
+        <v>65.5696487426758</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1100" t="n">
-        <v>65.3844223022461</v>
+        <v>65.3844146728516</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1101" t="n">
-        <v>65.3844223022461</v>
+        <v>65.3844146728516</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1102" t="n">
-        <v>65.3844223022461</v>
+        <v>65.3844146728516</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1105" t="n">
-        <v>67.7923431396484</v>
+        <v>67.7923278808594</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>74</v>
       </c>
       <c r="G1107" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1108" t="n">
-        <v>70.2002792358398</v>
+        <v>70.2002639770508</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>74</v>
       </c>
       <c r="G1109" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1112" t="n">
-        <v>68.1627883911133</v>
+        <v>68.1627807617188</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>74</v>
       </c>
       <c r="G1113" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>69.0889205932617</v>
+        <v>69.0889282226562</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1117" t="n">
-        <v>68.1627883911133</v>
+        <v>68.1627807617188</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1118" t="n">
-        <v>67.7923431396484</v>
+        <v>67.7923278808594</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>74</v>
       </c>
       <c r="G1125" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1126" t="n">
-        <v>68.1627883911133</v>
+        <v>68.1627807617188</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1129" t="n">
-        <v>68.1627883911133</v>
+        <v>68.1627807617188</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1131" t="n">
-        <v>69.0889205932617</v>
+        <v>69.0889282226562</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>75</v>
       </c>
       <c r="G1133" t="n">
-        <v>69.4593734741211</v>
+        <v>69.4593658447266</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1134" t="n">
-        <v>70.2002792358398</v>
+        <v>70.2002639770508</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>79</v>
       </c>
       <c r="G1135" t="n">
-        <v>73.1638641357422</v>
+        <v>73.1638717651367</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>71.8672866821289</v>
+        <v>71.8672943115234</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>78</v>
       </c>
       <c r="G1137" t="n">
-        <v>72.2377548217773</v>
+        <v>72.2377471923828</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>73.8000030517578</v>
       </c>
       <c r="G1138" t="n">
-        <v>68.348014831543</v>
+        <v>68.3480224609375</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>74</v>
       </c>
       <c r="G1139" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1144" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469390869141</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1145" t="n">
-        <v>64.6435317993164</v>
+        <v>64.6435165405273</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1146" t="n">
-        <v>65.1992034912109</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1147" t="n">
-        <v>62.4208221435547</v>
+        <v>62.420825958252</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1148" t="n">
-        <v>60.7537879943848</v>
+        <v>60.753791809082</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>66</v>
       </c>
       <c r="G1150" t="n">
-        <v>61.1242370605469</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1151" t="n">
-        <v>61.6799125671387</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1152" t="n">
-        <v>61.3094635009766</v>
+        <v>61.3094711303711</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>66</v>
       </c>
       <c r="G1153" t="n">
-        <v>61.1242370605469</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1154" t="n">
-        <v>60.7537879943848</v>
+        <v>60.753791809082</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>60.939022064209</v>
+        <v>60.9390258789062</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>66</v>
       </c>
       <c r="G1156" t="n">
-        <v>61.1242370605469</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1159" t="n">
-        <v>58.7163162231445</v>
+        <v>58.7163200378418</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>57.9754219055176</v>
+        <v>57.9754180908203</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>58.5311012268066</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1166" t="n">
-        <v>57.9754219055176</v>
+        <v>57.9754180908203</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>63</v>
       </c>
       <c r="G1168" t="n">
-        <v>58.3458709716797</v>
+        <v>58.3458671569824</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1170" t="n">
-        <v>56.3083953857422</v>
+        <v>56.3083992004395</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>58.1606407165527</v>
+        <v>58.1606369018555</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1176" t="n">
-        <v>55.1970405578613</v>
+        <v>55.1970443725586</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>53.5300216674805</v>
+        <v>53.5300178527832</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1180" t="n">
-        <v>53.3447952270508</v>
+        <v>53.3447914123535</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>52.2334480285645</v>
+        <v>52.2334518432617</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1182" t="n">
-        <v>55.1970405578613</v>
+        <v>55.1970443725586</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1189" t="n">
-        <v>61.3094635009766</v>
+        <v>61.3094711303711</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1190" t="n">
-        <v>60.939022064209</v>
+        <v>60.9390258789062</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>63</v>
       </c>
       <c r="G1196" t="n">
-        <v>58.3458709716797</v>
+        <v>58.3458671569824</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1198" t="n">
-        <v>58.5311012268066</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>63.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>58.8089332580566</v>
+        <v>58.8089370727539</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1201" t="n">
-        <v>60.0128936767578</v>
+        <v>60.0128974914551</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1202" t="n">
-        <v>61.8651466369629</v>
+        <v>61.8651504516602</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>65.6999969482422</v>
       </c>
       <c r="G1204" t="n">
-        <v>60.8464012145996</v>
+        <v>60.8464050292969</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>65.6999969482422</v>
       </c>
       <c r="G1205" t="n">
-        <v>60.8464012145996</v>
+        <v>60.8464050292969</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1211" t="n">
-        <v>59.920280456543</v>
+        <v>59.9202766418457</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>58.1606407165527</v>
+        <v>58.1606369018555</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>63</v>
       </c>
       <c r="G1214" t="n">
-        <v>58.3458709716797</v>
+        <v>58.3458671569824</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1215" t="n">
-        <v>60.1055068969727</v>
+        <v>60.1055107116699</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>63.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>59.4594116210938</v>
+        <v>59.459415435791</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>56.5</v>
       </c>
       <c r="G1221" t="n">
-        <v>52.9048309326172</v>
+        <v>52.9048271179199</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1222" t="n">
-        <v>54.1221122741699</v>
+        <v>54.1221084594727</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1224" t="n">
-        <v>53.6539268493652</v>
+        <v>53.6539306640625</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1226" t="n">
-        <v>56.5566711425781</v>
+        <v>56.5566673278809</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G1229" t="n">
-        <v>57.2121238708496</v>
+        <v>57.2121276855469</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1231" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>57.8675880432129</v>
+        <v>57.8675842285156</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>62.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>64</v>
       </c>
       <c r="G1236" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G1237" t="n">
-        <v>61.8939666748047</v>
+        <v>61.893970489502</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>60.3021469116211</v>
+        <v>60.3021507263184</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>63.5</v>
       </c>
       <c r="G1241" t="n">
-        <v>59.4594116210938</v>
+        <v>59.459415435791</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>62.5</v>
       </c>
       <c r="G1242" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1243" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>61.5</v>
       </c>
       <c r="G1244" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>59</v>
       </c>
       <c r="G1250" t="n">
-        <v>55.2457580566406</v>
+        <v>55.2457504272461</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1252" t="n">
-        <v>55.9012107849121</v>
+        <v>55.9012145996094</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1254" t="n">
-        <v>56.5566711425781</v>
+        <v>56.5566673278809</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1257" t="n">
-        <v>56.9312171936035</v>
+        <v>56.9312210083008</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>67</v>
       </c>
       <c r="G1265" t="n">
-        <v>62.7367057800293</v>
+        <v>62.7367095947266</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1266" t="n">
-        <v>61.6130599975586</v>
+        <v>61.6130676269531</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1268" t="n">
-        <v>60.7703285217285</v>
+        <v>60.7703323364258</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1272" t="n">
-        <v>60.3021469116211</v>
+        <v>60.3021507263184</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>59.7403182983398</v>
+        <v>59.7403221130371</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1274" t="n">
-        <v>60.1148681640625</v>
+        <v>60.1148643493652</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1277" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1279" t="n">
-        <v>62.4557876586914</v>
+        <v>62.4557914733887</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>68</v>
       </c>
       <c r="G1283" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1284" t="n">
-        <v>64.7967147827148</v>
+        <v>64.7967224121094</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>67</v>
       </c>
       <c r="G1285" t="n">
-        <v>62.7367057800293</v>
+        <v>62.7367095947266</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>68</v>
       </c>
       <c r="G1286" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>63.7667007446289</v>
+        <v>63.7667083740234</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>67.5999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>63.298526763916</v>
+        <v>63.2985191345215</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>67</v>
       </c>
       <c r="G1295" t="n">
-        <v>62.7367057800293</v>
+        <v>62.7367095947266</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1308" t="n">
-        <v>66.1076354980469</v>
+        <v>66.1076278686523</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>70.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>66.0139923095703</v>
+        <v>66.0139846801758</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>70.3000030517578</v>
       </c>
       <c r="G1315" t="n">
-        <v>65.8267288208008</v>
+        <v>65.8267211914062</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>68</v>
       </c>
       <c r="G1316" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1319" t="n">
-        <v>59.7403182983398</v>
+        <v>59.7403221130371</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G1321" t="n">
-        <v>60.2085113525391</v>
+        <v>60.2085075378418</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>64</v>
       </c>
       <c r="G1322" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>66.3000030517578</v>
       </c>
       <c r="G1324" t="n">
-        <v>62.0812454223633</v>
+        <v>62.0812530517578</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1325" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1328" t="n">
-        <v>60.7703285217285</v>
+        <v>60.7703323364258</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1329" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1330" t="n">
-        <v>60.7703285217285</v>
+        <v>60.7703323364258</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1331" t="n">
-        <v>60.3021469116211</v>
+        <v>60.3021507263184</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1333" t="n">
-        <v>60.4894142150879</v>
+        <v>60.4894180297852</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G1335" t="n">
-        <v>60.9576034545898</v>
+        <v>60.9575996398926</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>64</v>
       </c>
       <c r="G1336" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G1338" t="n">
-        <v>60.9576034545898</v>
+        <v>60.9575996398926</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1339" t="n">
-        <v>60.1148681640625</v>
+        <v>60.1148643493652</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1341" t="n">
-        <v>61.9876022338867</v>
+        <v>61.9876098632812</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1342" t="n">
-        <v>61.9876022338867</v>
+        <v>61.9876098632812</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1343" t="n">
-        <v>61.9876022338867</v>
+        <v>61.9876098632812</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>68</v>
       </c>
       <c r="G1344" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1345" t="n">
-        <v>63.4858055114746</v>
+        <v>63.4857978820801</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>66.9000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>62.64306640625</v>
+        <v>62.6430702209473</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1351" t="n">
-        <v>62.4557876586914</v>
+        <v>62.4557914733887</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1352" t="n">
-        <v>62.4557876586914</v>
+        <v>62.4557914733887</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>67</v>
       </c>
       <c r="G1354" t="n">
-        <v>62.7367057800293</v>
+        <v>62.7367095947266</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1356" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1357" t="n">
-        <v>60.4894142150879</v>
+        <v>60.4894180297852</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1360" t="n">
-        <v>60.5830459594727</v>
+        <v>60.5830497741699</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1362" t="n">
-        <v>60.4894142150879</v>
+        <v>60.4894180297852</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>60.3021469116211</v>
+        <v>60.3021507263184</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>57.6803131103516</v>
+        <v>57.6803092956543</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>58.242130279541</v>
+        <v>58.2421340942383</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>62.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>62.5</v>
       </c>
       <c r="G1385" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1391" t="n">
-        <v>60.1148681640625</v>
+        <v>60.1148643493652</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>64</v>
       </c>
       <c r="G1393" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>62.5</v>
       </c>
       <c r="G1400" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>61.5</v>
       </c>
       <c r="G1403" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>61.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1409" t="n">
-        <v>56.9312171936035</v>
+        <v>56.9312210083008</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>59</v>
       </c>
       <c r="G1411" t="n">
-        <v>55.2457580566406</v>
+        <v>55.2457504272461</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G1412" t="n">
-        <v>55.5266647338867</v>
+        <v>55.5266609191895</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1413" t="n">
-        <v>55.3393936157227</v>
+        <v>55.3393898010254</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1415" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1419" t="n">
-        <v>58.242130279541</v>
+        <v>58.2421340942383</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>61.5</v>
       </c>
       <c r="G1420" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>61.5</v>
       </c>
       <c r="G1427" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>57.2121238708496</v>
+        <v>57.2121276855469</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1429" t="n">
-        <v>56.5566711425781</v>
+        <v>56.5566673278809</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1431" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1432" t="n">
-        <v>56.9312171936035</v>
+        <v>56.9312210083008</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>57.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>53.8412017822266</v>
+        <v>53.8411979675293</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>52.7175598144531</v>
+        <v>52.7175559997559</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1442" t="n">
-        <v>53.6539268493652</v>
+        <v>53.6539306640625</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>56.2000007629395</v>
       </c>
       <c r="G1443" t="n">
-        <v>52.6239204406738</v>
+        <v>52.6239242553711</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G1447" t="n">
-        <v>52.9984703063965</v>
+        <v>52.998462677002</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1450" t="n">
-        <v>52.3430099487305</v>
+        <v>52.3430137634277</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>52.0620918273926</v>
+        <v>52.0620994567871</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1453" t="n">
-        <v>52.0620918273926</v>
+        <v>52.0620994567871</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>51.2193641662598</v>
+        <v>51.219367980957</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G1462" t="n">
-        <v>49.814811706543</v>
+        <v>49.8148155212402</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>52</v>
       </c>
       <c r="G1472" t="n">
-        <v>48.6911697387695</v>
+        <v>48.6911735534668</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>52</v>
       </c>
       <c r="G1474" t="n">
-        <v>48.6911697387695</v>
+        <v>48.6911735534668</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -60978,6 +60978,32 @@
         <v>74.1999969482422</v>
       </c>
       <c r="H2331" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2332" t="n">
+        <v>43603</v>
+      </c>
+      <c r="C2332" t="n">
+        <v>74.4000015258789</v>
+      </c>
+      <c r="D2332" t="n">
+        <v>71.6999969482422</v>
+      </c>
+      <c r="E2332" t="n">
+        <v>74.1999969482422</v>
+      </c>
+      <c r="F2332" t="n">
+        <v>72.5999984741211</v>
+      </c>
+      <c r="G2332" t="n">
+        <v>72.5999984741211</v>
+      </c>
+      <c r="H2332" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -447,7 +447,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>11.7123651504517</v>
+        <v>11.712366104126</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G6" t="n">
-        <v>10.8920783996582</v>
+        <v>10.8920764923096</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>10.9005336761475</v>
+        <v>10.9005327224731</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1711454391479</v>
+        <v>11.1711435317993</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G12" t="n">
-        <v>11.1880559921265</v>
+        <v>11.1880578994751</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G15" t="n">
-        <v>11.0781230926514</v>
+        <v>11.0781211853027</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0189247131348</v>
+        <v>11.0189256668091</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G18" t="n">
-        <v>11.1034927368164</v>
+        <v>11.1034917831421</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>11.0358390808105</v>
+        <v>11.0358381271362</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>11.1204042434692</v>
+        <v>11.1204051971436</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G25" t="n">
-        <v>11.1034927368164</v>
+        <v>11.1034917831421</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>11.0781230926514</v>
+        <v>11.0781211853027</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>10.9850988388062</v>
+        <v>10.9850997924805</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G32" t="n">
-        <v>10.8159685134888</v>
+        <v>10.8159675598145</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7652282714844</v>
+        <v>10.7652273178101</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G35" t="n">
-        <v>10.6468372344971</v>
+        <v>10.6468353271484</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0781230926514</v>
+        <v>11.0781211853027</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G45" t="n">
-        <v>11.8222999572754</v>
+        <v>11.8223009109497</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5009508132935</v>
+        <v>11.5009498596191</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>11.5009508132935</v>
+        <v>11.5009498596191</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>11.5855169296265</v>
+        <v>11.5855159759521</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G51" t="n">
-        <v>11.4671258926392</v>
+        <v>11.4671239852905</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.5</v>
       </c>
       <c r="G53" t="n">
-        <v>11.4163856506348</v>
+        <v>11.4163866043091</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>11.2810821533203</v>
+        <v>11.281081199646</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>13.25</v>
       </c>
       <c r="G57" t="n">
-        <v>11.2049694061279</v>
+        <v>11.2049703598022</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>13</v>
       </c>
       <c r="G59" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>11.1204042434692</v>
+        <v>11.1204051971436</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G63" t="n">
-        <v>11.0527515411377</v>
+        <v>11.052752494812</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>11.0020141601562</v>
+        <v>11.0020132064819</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>10.8667087554932</v>
+        <v>10.8667078018188</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G70" t="n">
-        <v>10.8328819274902</v>
+        <v>10.8328809738159</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G71" t="n">
-        <v>10.8328819274902</v>
+        <v>10.8328809738159</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8328819274902</v>
+        <v>10.8328809738159</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>10.9005336761475</v>
+        <v>10.9005327224731</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>10.9259033203125</v>
+        <v>10.9259042739868</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5538139343262</v>
+        <v>10.5538148880005</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.5</v>
       </c>
       <c r="G86" t="n">
-        <v>10.570725440979</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G87" t="n">
-        <v>10.6806640625</v>
+        <v>10.6806631088257</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G88" t="n">
-        <v>10.6637496948242</v>
+        <v>10.6637477874756</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>13</v>
       </c>
       <c r="G89" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>13</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G91" t="n">
-        <v>10.9850988388062</v>
+        <v>10.9850997924805</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.6383810043335</v>
+        <v>10.6383800506592</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G94" t="n">
-        <v>10.6383810043335</v>
+        <v>10.6383800506592</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G97" t="n">
-        <v>10.8159685134888</v>
+        <v>10.8159675598145</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>10.6130094528198</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G100" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G102" t="n">
-        <v>10.8667087554932</v>
+        <v>10.8667078018188</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>10.8159685134888</v>
+        <v>10.8159675598145</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G105" t="n">
-        <v>10.6806640625</v>
+        <v>10.6806631088257</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G106" t="n">
-        <v>10.8497943878174</v>
+        <v>10.8497953414917</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G108" t="n">
-        <v>10.8328819274902</v>
+        <v>10.8328809738159</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.706033706665</v>
+        <v>10.7060327529907</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G112" t="n">
-        <v>10.706033706665</v>
+        <v>10.7060327529907</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G113" t="n">
-        <v>10.706033706665</v>
+        <v>10.7060327529907</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G114" t="n">
-        <v>10.706033706665</v>
+        <v>10.7060327529907</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.5</v>
       </c>
       <c r="G120" t="n">
-        <v>10.570725440979</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>10.6130094528198</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>10.6130094528198</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655291557312</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.5</v>
       </c>
       <c r="G126" t="n">
-        <v>10.570725440979</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655291557312</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655291557312</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655291557312</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>10.4438781738281</v>
+        <v>10.4438791275024</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>10.4015960693359</v>
+        <v>10.4015941619873</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>10.4438781738281</v>
+        <v>10.4438791275024</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>10.2324647903442</v>
+        <v>10.2324657440186</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>10.1901817321777</v>
+        <v>10.1901807785034</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>13</v>
       </c>
       <c r="G153" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655291557312</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.8667087554932</v>
+        <v>10.8667078018188</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>10.9089889526367</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.6130094528198</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.5</v>
       </c>
       <c r="G167" t="n">
-        <v>10.570725440979</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.5</v>
       </c>
       <c r="G169" t="n">
-        <v>10.570725440979</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>10.570725440979</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>13</v>
       </c>
       <c r="G174" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>10.8667087554932</v>
+        <v>10.8667078018188</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>10.8667087554932</v>
+        <v>10.8667078018188</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>11.1626863479614</v>
+        <v>11.1626882553101</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>13</v>
       </c>
       <c r="G181" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>13</v>
       </c>
       <c r="G182" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>13</v>
       </c>
       <c r="G183" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G185" t="n">
-        <v>11.1626863479614</v>
+        <v>11.1626882553101</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>11.0358390808105</v>
+        <v>11.0358381271362</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>11.3741025924683</v>
+        <v>11.3741016387939</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>11.5855169296265</v>
+        <v>11.5855159759521</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>13.5</v>
       </c>
       <c r="G200" t="n">
-        <v>11.4163856506348</v>
+        <v>11.4163866043091</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.5432348251343</v>
+        <v>11.5432329177856</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>11.5432348251343</v>
+        <v>11.5432329177856</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5009508132935</v>
+        <v>11.5009498596191</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>11.786958694458</v>
+        <v>11.7869577407837</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>11.5702867507935</v>
+        <v>11.5702877044678</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>11.440281867981</v>
+        <v>11.4402837753296</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>11.5702867507935</v>
+        <v>11.5702877044678</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>11.440281867981</v>
+        <v>11.4402837753296</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>11.6569547653198</v>
+        <v>11.6569528579712</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>13.5</v>
       </c>
       <c r="G214" t="n">
-        <v>11.700288772583</v>
+        <v>11.7002906799316</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G217" t="n">
-        <v>11.8736267089844</v>
+        <v>11.8736257553101</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>11.526951789856</v>
+        <v>11.5269508361816</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>11.5702867507935</v>
+        <v>11.5702877044678</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.6569547653198</v>
+        <v>11.6569528579712</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>11.8736267089844</v>
+        <v>11.8736257553101</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>11.9602966308594</v>
+        <v>11.9602947235107</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902996063232</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0469646453857</v>
+        <v>12.0469655990601</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>11.786958694458</v>
+        <v>11.7869577407837</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902996063232</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>13.5</v>
       </c>
       <c r="G237" t="n">
-        <v>11.700288772583</v>
+        <v>11.7002906799316</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>12.0469646453857</v>
+        <v>12.0469655990601</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>12.0036296844482</v>
+        <v>12.0036306381226</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902996063232</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.0469646453857</v>
+        <v>12.0469655990601</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>12.4803075790405</v>
+        <v>12.4803066253662</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>12.6969795227051</v>
+        <v>12.6969804763794</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G247" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>15</v>
       </c>
       <c r="G248" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003213882446</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>13.1303243637085</v>
+        <v>13.1303224563599</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8703184127808</v>
+        <v>12.8703174591064</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G256" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>12.9569873809814</v>
+        <v>12.9569854736328</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="G261" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003213882446</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>15.25</v>
       </c>
       <c r="G265" t="n">
-        <v>13.2169942855835</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G266" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>15</v>
       </c>
       <c r="G268" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003213882446</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>13.1303243637085</v>
+        <v>13.1303224563599</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>15.25</v>
       </c>
       <c r="G284" t="n">
-        <v>13.2169942855835</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>15.25</v>
       </c>
       <c r="G285" t="n">
-        <v>13.2169942855835</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>15.25</v>
       </c>
       <c r="G288" t="n">
-        <v>13.2169942855835</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>15.25</v>
       </c>
       <c r="G290" t="n">
-        <v>13.2169942855835</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>13.1303243637085</v>
+        <v>13.1303224563599</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>15.25</v>
       </c>
       <c r="G303" t="n">
-        <v>13.2169942855835</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G304" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>15.75</v>
       </c>
       <c r="G308" t="n">
-        <v>13.650336265564</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>13.7370071411133</v>
+        <v>13.737006187439</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>13.7370071411133</v>
+        <v>13.737006187439</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G315" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G322" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>15.25</v>
       </c>
       <c r="G325" t="n">
-        <v>13.2169942855835</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>15</v>
       </c>
       <c r="G328" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003213882446</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>15</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003213882446</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>15.75</v>
       </c>
       <c r="G333" t="n">
-        <v>13.650336265564</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>13.7370071411133</v>
+        <v>13.737006187439</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G343" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.75</v>
       </c>
       <c r="G348" t="n">
-        <v>13.650336265564</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>15.75</v>
       </c>
       <c r="G350" t="n">
-        <v>13.650336265564</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G353" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>15.75</v>
       </c>
       <c r="G357" t="n">
-        <v>13.650336265564</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G365" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>13.0869903564453</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>13.1303243637085</v>
+        <v>13.1303224563599</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>15.75</v>
       </c>
       <c r="G386" t="n">
-        <v>13.650336265564</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1270160675049</v>
+        <v>14.1270151138306</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>14.2136850357056</v>
+        <v>14.2136831283569</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G389" t="n">
-        <v>14.4736928939819</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>17.25</v>
       </c>
       <c r="G392" t="n">
-        <v>14.9503707885742</v>
+        <v>14.9503688812256</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>14.9070348739624</v>
+        <v>14.907036781311</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>14.6903648376465</v>
+        <v>14.6903619766235</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>17</v>
       </c>
       <c r="G395" t="n">
-        <v>14.7336978912354</v>
+        <v>14.7336988449097</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>14.4736928939819</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>16.75</v>
       </c>
       <c r="G397" t="n">
-        <v>14.5170278549194</v>
+        <v>14.5170259475708</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>14.5603580474854</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>17</v>
       </c>
       <c r="G400" t="n">
-        <v>14.7336978912354</v>
+        <v>14.7336988449097</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>14.6036939620972</v>
+        <v>14.6036949157715</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G403" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>14.5603580474854</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>14.5603580474854</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>17</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7336978912354</v>
+        <v>14.7336988449097</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>14.6903648376465</v>
+        <v>14.6903619766235</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>14.6903648376465</v>
+        <v>14.6903619766235</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>17</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7336978912354</v>
+        <v>14.7336988449097</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G411" t="n">
-        <v>14.6903648376465</v>
+        <v>14.6903619766235</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G412" t="n">
-        <v>14.6903648376465</v>
+        <v>14.6903619766235</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6903648376465</v>
+        <v>14.6903619766235</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6036939620972</v>
+        <v>14.6036949157715</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>16.75</v>
       </c>
       <c r="G417" t="n">
-        <v>14.5170278549194</v>
+        <v>14.5170259475708</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4736928939819</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>14.4736928939819</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>16.5</v>
       </c>
       <c r="G420" t="n">
-        <v>14.3003520965576</v>
+        <v>14.3003540039062</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>14.4303579330444</v>
+        <v>14.4303550720215</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.5</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3003520965576</v>
+        <v>14.3003540039062</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>14.2570199966431</v>
+        <v>14.2570219039917</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>14.6036939620972</v>
+        <v>14.6036949157715</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>14.2570199966431</v>
+        <v>14.2570219039917</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>17</v>
       </c>
       <c r="G430" t="n">
-        <v>14.7336978912354</v>
+        <v>14.7336988449097</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>14.4736928939819</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>17</v>
       </c>
       <c r="G432" t="n">
-        <v>14.7336978912354</v>
+        <v>14.7336988449097</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>14.6036939620972</v>
+        <v>14.6036949157715</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>17</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7336978912354</v>
+        <v>14.7336988449097</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>14.6903648376465</v>
+        <v>14.6903619766235</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>14.6903648376465</v>
+        <v>14.6903619766235</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>14.8203659057617</v>
+        <v>14.820366859436</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>14.8203659057617</v>
+        <v>14.820366859436</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>14.8203659057617</v>
+        <v>14.820366859436</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>14.8203659057617</v>
+        <v>14.820366859436</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G443" t="n">
-        <v>14.9070348739624</v>
+        <v>14.907036781311</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G444" t="n">
-        <v>14.6036939620972</v>
+        <v>14.6036949157715</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>14.9937038421631</v>
+        <v>14.9937047958374</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G446" t="n">
-        <v>14.9070348739624</v>
+        <v>14.907036781311</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>14.8203659057617</v>
+        <v>14.820366859436</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>15.0370378494263</v>
+        <v>15.0370388031006</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>14.9937038421631</v>
+        <v>14.9937047958374</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>17.25</v>
       </c>
       <c r="G456" t="n">
-        <v>15.3926887512207</v>
+        <v>15.3926906585693</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>17.25</v>
       </c>
       <c r="G458" t="n">
-        <v>15.3926887512207</v>
+        <v>15.3926906585693</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>17</v>
       </c>
       <c r="G459" t="n">
-        <v>15.1696062088013</v>
+        <v>15.1696071624756</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>15.2142219543457</v>
+        <v>15.2142210006714</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>14.9911394119263</v>
+        <v>14.991138458252</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G463" t="n">
-        <v>15.1249885559082</v>
+        <v>15.1249914169312</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>15.3480730056763</v>
+        <v>15.3480749130249</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>15.3480730056763</v>
+        <v>15.3480749130249</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>15.3480730056763</v>
+        <v>15.3480749130249</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G469" t="n">
-        <v>15.7496194839478</v>
+        <v>15.7496204376221</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>15.883469581604</v>
+        <v>15.883472442627</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>15.883469581604</v>
+        <v>15.883472442627</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G472" t="n">
-        <v>16.7757987976074</v>
+        <v>16.7758007049561</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G473" t="n">
-        <v>17.5788974761963</v>
+        <v>17.5788993835449</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>16.9988822937012</v>
+        <v>16.9988842010498</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G477" t="n">
-        <v>17.1327304840088</v>
+        <v>17.1327342987061</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>17.2219638824463</v>
+        <v>17.2219657897949</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450454711914</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450454711914</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>20.5</v>
       </c>
       <c r="G493" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604591369629</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604591369629</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604591369629</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G501" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>20.5</v>
       </c>
       <c r="G502" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G504" t="n">
-        <v>18.0250587463379</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G505" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>20.5</v>
       </c>
       <c r="G507" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G508" t="n">
-        <v>18.0250587463379</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>20.5</v>
       </c>
       <c r="G509" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>20.5</v>
       </c>
       <c r="G510" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450454711914</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450454711914</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.6681289672852</v>
+        <v>17.6681270599365</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G517" t="n">
-        <v>17.5788974761963</v>
+        <v>17.5788993835449</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>17.6681289672852</v>
+        <v>17.6681270599365</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>17.2219638824463</v>
+        <v>17.2219657897949</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450454711914</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G532" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>18.0250587463379</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>20.5</v>
       </c>
       <c r="G549" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G550" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>18.0250587463379</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G552" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>20.5</v>
       </c>
       <c r="G554" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G555" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604591369629</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>18.0250587463379</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>17.7127475738525</v>
+        <v>17.7127437591553</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>17.7127475738525</v>
+        <v>17.7127437591553</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G562" t="n">
-        <v>18.0250587463379</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>20.5</v>
       </c>
       <c r="G564" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>17.6681289672852</v>
+        <v>17.6681270599365</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>18.0250587463379</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>20.5</v>
       </c>
       <c r="G579" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>19.0958576202393</v>
+        <v>19.0958595275879</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>21.5</v>
       </c>
       <c r="G589" t="n">
-        <v>19.1850891113281</v>
+        <v>19.1850910186768</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>21.5</v>
       </c>
       <c r="G592" t="n">
-        <v>19.1850891113281</v>
+        <v>19.1850910186768</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>19.8097229003906</v>
+        <v>19.809720993042</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>19.8097229003906</v>
+        <v>19.809720993042</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>19.8097229003906</v>
+        <v>19.809720993042</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>20.79128074646</v>
+        <v>20.7912826538086</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>20.7020530700684</v>
+        <v>20.7020492553711</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>20.7020530700684</v>
+        <v>20.7020492553711</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>21.1482181549072</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>20.8805141448975</v>
+        <v>20.8805160522461</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>21.5051498413086</v>
+        <v>21.50514793396</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>21.1482181549072</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>20.8805141448975</v>
+        <v>20.8805160522461</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>21.5051498413086</v>
+        <v>21.50514793396</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>24.5</v>
       </c>
       <c r="G627" t="n">
-        <v>21.8620777130127</v>
+        <v>21.8620796203613</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>24</v>
       </c>
       <c r="G631" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>21.2374477386475</v>
+        <v>21.2374439239502</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>24</v>
       </c>
       <c r="G637" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>23.5</v>
       </c>
       <c r="G640" t="n">
-        <v>20.9697513580322</v>
+        <v>20.9697494506836</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>21.1482181549072</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>20.79128074646</v>
+        <v>20.7912826538086</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>21.1482181549072</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>24</v>
       </c>
       <c r="G648" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>24</v>
       </c>
       <c r="G649" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>24</v>
       </c>
       <c r="G650" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>21.1482181549072</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>21.1482181549072</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>21.2374477386475</v>
+        <v>21.2374439239502</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>21.2374477386475</v>
+        <v>21.2374439239502</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>20.7020530700684</v>
+        <v>20.7020492553711</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>23.5</v>
       </c>
       <c r="G661" t="n">
-        <v>20.9697513580322</v>
+        <v>20.9697494506836</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>23</v>
       </c>
       <c r="G662" t="n">
-        <v>20.5235843658447</v>
+        <v>20.5235862731934</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>22.5</v>
       </c>
       <c r="G664" t="n">
-        <v>20.0774192810059</v>
+        <v>20.0774173736572</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>20.5</v>
       </c>
       <c r="G670" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G671" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>18</v>
       </c>
       <c r="G675" t="n">
-        <v>16.0619354248047</v>
+        <v>16.0619335174561</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>15.0357580184937</v>
+        <v>15.035756111145</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>15.7496194839478</v>
+        <v>15.7496204376221</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>16.9988822937012</v>
+        <v>16.9988842010498</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604591369629</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>18.0250587463379</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>20.79128074646</v>
+        <v>20.7912826538086</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>21.2374477386475</v>
+        <v>21.2374439239502</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G689" t="n">
-        <v>21.1482181549072</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>23</v>
       </c>
       <c r="G690" t="n">
-        <v>20.5235843658447</v>
+        <v>20.5235862731934</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>20.8805141448975</v>
+        <v>20.8805160522461</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>20.8805141448975</v>
+        <v>20.8805160522461</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>23.5</v>
       </c>
       <c r="G693" t="n">
-        <v>20.9697513580322</v>
+        <v>20.9697494506836</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>24</v>
       </c>
       <c r="G699" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>24</v>
       </c>
       <c r="G704" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>24</v>
       </c>
       <c r="G706" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>24</v>
       </c>
       <c r="G707" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>22.3678779602051</v>
+        <v>22.3678798675537</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>22.3678779602051</v>
+        <v>22.3678798675537</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>22.5497341156006</v>
+        <v>22.5497303009033</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>22.0950984954834</v>
+        <v>22.095100402832</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>21.7313938140869</v>
+        <v>21.7313919067383</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G732" t="n">
-        <v>21.7313938140869</v>
+        <v>21.7313919067383</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>23.5</v>
       </c>
       <c r="G734" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>21.6404685974121</v>
+        <v>21.6404666900635</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>21.4586143493652</v>
+        <v>21.4586162567139</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>23.5</v>
       </c>
       <c r="G740" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>23.5</v>
       </c>
       <c r="G741" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>23.5</v>
       </c>
       <c r="G742" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>23.5</v>
       </c>
       <c r="G749" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>23.5</v>
       </c>
       <c r="G750" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>21.7313938140869</v>
+        <v>21.7313919067383</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>21.7313938140869</v>
+        <v>21.7313919067383</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>23.5</v>
       </c>
       <c r="G758" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G761" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>23.5</v>
       </c>
       <c r="G763" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>23.5</v>
       </c>
       <c r="G765" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>23</v>
       </c>
       <c r="G766" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G768" t="n">
-        <v>21.4586143493652</v>
+        <v>21.4586162567139</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G769" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>21.094913482666</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>23</v>
       </c>
       <c r="G772" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>21.094913482666</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>21.094913482666</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>21.4586143493652</v>
+        <v>21.4586162567139</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>21.094913482666</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>23</v>
       </c>
       <c r="G784" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>20.7312068939209</v>
+        <v>20.7312049865723</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>23.5</v>
       </c>
       <c r="G786" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>23.5</v>
       </c>
       <c r="G787" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676929473877</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>23</v>
       </c>
       <c r="G790" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>23</v>
       </c>
       <c r="G791" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>23</v>
       </c>
       <c r="G792" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>20.6402797698975</v>
+        <v>20.6402778625488</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>20.6402797698975</v>
+        <v>20.6402778625488</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G796" t="n">
-        <v>20.6402797698975</v>
+        <v>20.6402778625488</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>23</v>
       </c>
       <c r="G797" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>20.3674983978271</v>
+        <v>20.3675003051758</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>20.6402797698975</v>
+        <v>20.6402778625488</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G804" t="n">
-        <v>22.3678779602051</v>
+        <v>22.3678798675537</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>23.5499229431152</v>
+        <v>23.5499210357666</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>22.9134368896484</v>
+        <v>22.9134387969971</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>23.0952911376953</v>
+        <v>23.0952892303467</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>23.3680686950684</v>
+        <v>23.368070602417</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>24.4591846466064</v>
+        <v>24.4591827392578</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>24.2773323059082</v>
+        <v>24.2773342132568</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>28</v>
       </c>
       <c r="G820" t="n">
-        <v>25.4593753814697</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>26.0049343109131</v>
+        <v>26.0049362182617</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>26.0958595275879</v>
+        <v>26.0958614349365</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>26.0958595275879</v>
+        <v>26.0958614349365</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>25.2775211334229</v>
+        <v>25.2775249481201</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G826" t="n">
-        <v>24.8228912353516</v>
+        <v>24.8228893280029</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>24.8228912353516</v>
+        <v>24.8228893280029</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>24.8228912353516</v>
+        <v>24.8228893280029</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>25.1865940093994</v>
+        <v>25.186595916748</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>24.2773323059082</v>
+        <v>24.2773342132568</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>25.7321510314941</v>
+        <v>25.7321529388428</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G838" t="n">
-        <v>26.0049343109131</v>
+        <v>26.0049362182617</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>25.8230781555176</v>
+        <v>25.8230800628662</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>28</v>
       </c>
       <c r="G842" t="n">
-        <v>25.4593753814697</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>28</v>
       </c>
       <c r="G843" t="n">
-        <v>25.4593753814697</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>26.1867828369141</v>
+        <v>26.1867847442627</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G847" t="n">
-        <v>26.0958595275879</v>
+        <v>26.0958614349365</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>28</v>
       </c>
       <c r="G851" t="n">
-        <v>25.4593753814697</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>26.1867828369141</v>
+        <v>26.1867847442627</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>25.8230781555176</v>
+        <v>25.8230800628662</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>26.0049343109131</v>
+        <v>26.0049362182617</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G857" t="n">
-        <v>26.7323455810547</v>
+        <v>26.7323417663574</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>28.0053100585938</v>
+        <v>28.0053119659424</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>29.005500793457</v>
+        <v>29.0055027008057</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G861" t="n">
-        <v>30.2784690856934</v>
+        <v>30.278470993042</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>32.5</v>
       </c>
       <c r="G862" t="n">
-        <v>29.5510597229004</v>
+        <v>29.5510578155518</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>29.6419868469238</v>
+        <v>29.6419849395752</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>30.6421794891357</v>
+        <v>30.6421775817871</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G866" t="n">
-        <v>31.7332954406738</v>
+        <v>31.7332916259766</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>31.1877346038818</v>
+        <v>31.1877326965332</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>31.7332954406738</v>
+        <v>31.7332916259766</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>32.0060729980469</v>
+        <v>32.0060691833496</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>35.6431274414062</v>
+        <v>35.643123626709</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>40</v>
       </c>
       <c r="G873" t="n">
-        <v>36.3705368041992</v>
+        <v>36.3705406188965</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>35.5522003173828</v>
+        <v>35.5521965026855</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G877" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G878" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>34.7338638305664</v>
+        <v>34.7338600158691</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>37.5</v>
       </c>
       <c r="G883" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>34.8247909545898</v>
+        <v>34.8247871398926</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G885" t="n">
-        <v>34.7338638305664</v>
+        <v>34.7338600158691</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>34.8247909545898</v>
+        <v>34.8247871398926</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>37.5</v>
       </c>
       <c r="G893" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>37</v>
       </c>
       <c r="G894" t="n">
-        <v>33.642749786377</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G898" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336692810059</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G900" t="n">
-        <v>33.0971908569336</v>
+        <v>33.0971870422363</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G901" t="n">
-        <v>32.8244094848633</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>38</v>
       </c>
       <c r="G903" t="n">
-        <v>34.5520095825195</v>
+        <v>34.5520057678223</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>38.5</v>
       </c>
       <c r="G906" t="n">
-        <v>35.0066413879395</v>
+        <v>35.0066375732422</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G907" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>34.8247909545898</v>
+        <v>34.8247871398926</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>37.5</v>
       </c>
       <c r="G909" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336692810059</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G911" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336692810059</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G912" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336692810059</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>33.2790336608887</v>
+        <v>33.2790374755859</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>37</v>
       </c>
       <c r="G914" t="n">
-        <v>33.642749786377</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G915" t="n">
-        <v>32.8244094848633</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>37</v>
       </c>
       <c r="G917" t="n">
-        <v>33.642749786377</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G920" t="n">
-        <v>33.0062599182129</v>
+        <v>33.0062561035156</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G925" t="n">
-        <v>33.2790336608887</v>
+        <v>33.2790374755859</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>33.0062599182129</v>
+        <v>33.0062561035156</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.6425552368164</v>
+        <v>32.6425590515137</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>36</v>
       </c>
       <c r="G929" t="n">
-        <v>32.7334823608398</v>
+        <v>32.7334861755371</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>39.5</v>
       </c>
       <c r="G931" t="n">
-        <v>35.9159049987793</v>
+        <v>35.9159088134766</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>35.2794189453125</v>
+        <v>35.2794227600098</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>37.5</v>
       </c>
       <c r="G936" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>37.5</v>
       </c>
       <c r="G939" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G940" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336692810059</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>37</v>
       </c>
       <c r="G941" t="n">
-        <v>33.642749786377</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G943" t="n">
-        <v>34.0064544677734</v>
+        <v>34.0064506530762</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>37.5</v>
       </c>
       <c r="G944" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G945" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>37.5</v>
       </c>
       <c r="G947" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G948" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G951" t="n">
-        <v>32.8244094848633</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>32.8244094848633</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>33.4608879089355</v>
+        <v>33.4608840942383</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G955" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336692810059</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336692810059</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>33.4608879089355</v>
+        <v>33.4608840942383</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>34.3592338562012</v>
+        <v>34.3592300415039</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>34.5444641113281</v>
+        <v>34.5444602966309</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G964" t="n">
-        <v>34.6370735168457</v>
+        <v>34.6370697021484</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G965" t="n">
-        <v>34.5444641113281</v>
+        <v>34.5444602966309</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G968" t="n">
-        <v>33.8961639404297</v>
+        <v>33.896167755127</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>36.5</v>
       </c>
       <c r="G969" t="n">
-        <v>33.8035621643066</v>
+        <v>33.8035583496094</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>36.5</v>
       </c>
       <c r="G974" t="n">
-        <v>33.8035621643066</v>
+        <v>33.8035583496094</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>36.5</v>
       </c>
       <c r="G975" t="n">
-        <v>33.8035621643066</v>
+        <v>33.8035583496094</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>33.5257263183594</v>
+        <v>33.5257225036621</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3404960632324</v>
+        <v>33.3404922485352</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>36</v>
       </c>
       <c r="G981" t="n">
-        <v>33.3404960632324</v>
+        <v>33.3404922485352</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>36.5</v>
       </c>
       <c r="G983" t="n">
-        <v>33.8035621643066</v>
+        <v>33.8035583496094</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G984" t="n">
-        <v>33.5257263183594</v>
+        <v>33.5257225036621</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>42.2312965393066</v>
+        <v>42.2312927246094</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>41.9534568786621</v>
+        <v>41.9534530639648</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>49.5</v>
       </c>
       <c r="G998" t="n">
-        <v>45.8431816101074</v>
+        <v>45.8431854248047</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>45.4727325439453</v>
+        <v>45.472728729248</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>49.5</v>
       </c>
       <c r="G1003" t="n">
-        <v>45.8431816101074</v>
+        <v>45.8431854248047</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>49.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>45.8431816101074</v>
+        <v>45.8431854248047</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>48.8993949890137</v>
+        <v>48.8993911743164</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>57.0492935180664</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1038" t="n">
-        <v>57.0492935180664</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276748657227</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>60.753791809082</v>
+        <v>60.7537956237793</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>61.494701385498</v>
+        <v>61.4947052001953</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>64</v>
       </c>
       <c r="G1071" t="n">
-        <v>59.2719917297363</v>
+        <v>59.2719955444336</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>57.6049728393555</v>
+        <v>57.6049690246582</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>57.2345199584961</v>
+        <v>57.2345161437988</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1078" t="n">
-        <v>63.3469390869141</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1080" t="n">
-        <v>63.3469390869141</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1081" t="n">
-        <v>63.3469390869141</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>68</v>
       </c>
       <c r="G1083" t="n">
-        <v>62.9765014648438</v>
+        <v>62.9764976501465</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>68</v>
       </c>
       <c r="G1087" t="n">
-        <v>62.9765014648438</v>
+        <v>62.9764976501465</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1088" t="n">
-        <v>63.3469390869141</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>68</v>
       </c>
       <c r="G1089" t="n">
-        <v>62.9765014648438</v>
+        <v>62.9764976501465</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>72</v>
       </c>
       <c r="G1091" t="n">
-        <v>66.6809921264648</v>
+        <v>66.6809844970703</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>65.5696487426758</v>
+        <v>65.5696411132812</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G1097" t="n">
-        <v>65.9401016235352</v>
+        <v>65.9400939941406</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1099" t="n">
-        <v>65.5696487426758</v>
+        <v>65.5696411132812</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1105" t="n">
-        <v>67.7923278808594</v>
+        <v>67.7923355102539</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>69.0889282226562</v>
+        <v>69.0889205932617</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1118" t="n">
-        <v>67.7923278808594</v>
+        <v>67.7923355102539</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>73</v>
       </c>
       <c r="G1119" t="n">
-        <v>67.6071243286133</v>
+        <v>67.6071166992188</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>73</v>
       </c>
       <c r="G1121" t="n">
-        <v>67.6071243286133</v>
+        <v>67.6071166992188</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>72</v>
       </c>
       <c r="G1123" t="n">
-        <v>66.6809921264648</v>
+        <v>66.6809844970703</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>73</v>
       </c>
       <c r="G1130" t="n">
-        <v>67.6071243286133</v>
+        <v>67.6071166992188</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1131" t="n">
-        <v>69.0889282226562</v>
+        <v>69.0889205932617</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>69.8298187255859</v>
+        <v>69.8298110961914</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1144" t="n">
-        <v>63.3469390869141</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1145" t="n">
-        <v>64.6435165405273</v>
+        <v>64.6435241699219</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1148" t="n">
-        <v>60.753791809082</v>
+        <v>60.7537956237793</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1154" t="n">
-        <v>60.753791809082</v>
+        <v>60.7537956237793</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>60.9390258789062</v>
+        <v>60.9390296936035</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1157" t="n">
-        <v>59.0867691040039</v>
+        <v>59.0867729187012</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1159" t="n">
-        <v>58.7163200378418</v>
+        <v>58.7163162231445</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276748657227</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>59.0867691040039</v>
+        <v>59.0867729187012</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1167" t="n">
-        <v>59.0867691040039</v>
+        <v>59.0867729187012</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>57.0492935180664</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>57.2345199584961</v>
+        <v>57.2345161437988</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1174" t="n">
-        <v>57.0492935180664</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1175" t="n">
-        <v>57.2345199584961</v>
+        <v>57.2345161437988</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1180" t="n">
-        <v>53.3447914123535</v>
+        <v>53.3447952270508</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>52.2334518432617</v>
+        <v>52.2334480285645</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>57.0492935180664</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1190" t="n">
-        <v>60.9390258789062</v>
+        <v>60.9390296936035</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1193" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276748657227</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1194" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276748657227</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1195" t="n">
-        <v>59.0867691040039</v>
+        <v>59.0867729187012</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1197" t="n">
-        <v>59.0867691040039</v>
+        <v>59.0867729187012</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>63.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>58.8089370727539</v>
+        <v>58.8089332580566</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>61.494701385498</v>
+        <v>61.4947052001953</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1211" t="n">
-        <v>59.9202766418457</v>
+        <v>59.920280456543</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>58.6237106323242</v>
+        <v>58.623706817627</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1215" t="n">
-        <v>60.1055107116699</v>
+        <v>60.1055145263672</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -61004,6 +61004,32 @@
         <v>72.5999984741211</v>
       </c>
       <c r="H2332" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2333" t="n">
+        <v>22742</v>
+      </c>
+      <c r="C2333" t="n">
+        <v>72.5999984741211</v>
+      </c>
+      <c r="D2333" t="n">
+        <v>70</v>
+      </c>
+      <c r="E2333" t="n">
+        <v>72.3000030517578</v>
+      </c>
+      <c r="F2333" t="n">
+        <v>71</v>
+      </c>
+      <c r="G2333" t="n">
+        <v>71</v>
+      </c>
+      <c r="H2333" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -447,7 +447,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>11.712366104126</v>
+        <v>11.7123651504517</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G5" t="n">
-        <v>11.0273818969727</v>
+        <v>11.027382850647</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G6" t="n">
-        <v>10.8920764923096</v>
+        <v>10.8920755386353</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>10.9005327224731</v>
+        <v>10.9005346298218</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1711435317993</v>
+        <v>11.1711444854736</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G14" t="n">
-        <v>11.0273818969727</v>
+        <v>11.027382850647</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G15" t="n">
-        <v>11.0781211853027</v>
+        <v>11.0781221389771</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0189256668091</v>
+        <v>11.0189247131348</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895364761353</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>11.1204051971436</v>
+        <v>11.1204042434692</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>11.0781211853027</v>
+        <v>11.0781221389771</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512748718262</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>10.9850997924805</v>
+        <v>10.9850988388062</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G32" t="n">
-        <v>10.8159675598145</v>
+        <v>10.8159694671631</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7652273178101</v>
+        <v>10.7652282714844</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G35" t="n">
-        <v>10.6468353271484</v>
+        <v>10.6468362808228</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0696659088135</v>
+        <v>11.0696649551392</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>10.9428157806396</v>
+        <v>10.9428148269653</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G38" t="n">
-        <v>10.9343605041504</v>
+        <v>10.9343595504761</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G39" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512748718262</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0781211853027</v>
+        <v>11.0781221389771</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G42" t="n">
-        <v>11.2387962341309</v>
+        <v>11.2387981414795</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.6700820922852</v>
+        <v>11.6700830459595</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G44" t="n">
-        <v>11.6700820922852</v>
+        <v>11.6700830459595</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G45" t="n">
-        <v>11.8223009109497</v>
+        <v>11.822301864624</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.6447134017944</v>
+        <v>11.6447124481201</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6447134017944</v>
+        <v>11.6447124481201</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5009498596191</v>
+        <v>11.5009489059448</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>11.5009498596191</v>
+        <v>11.5009489059448</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>11.5855159759521</v>
+        <v>11.5855169296265</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G51" t="n">
-        <v>11.4671239852905</v>
+        <v>11.4671249389648</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.5</v>
       </c>
       <c r="G53" t="n">
-        <v>11.4163866043091</v>
+        <v>11.4163856506348</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895364761353</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>11.281081199646</v>
+        <v>11.2810802459717</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>13</v>
       </c>
       <c r="G59" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>11.1204051971436</v>
+        <v>11.1204042434692</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G63" t="n">
-        <v>11.052752494812</v>
+        <v>11.0527515411377</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G64" t="n">
-        <v>11.1542301177979</v>
+        <v>11.1542291641235</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>10.9428157806396</v>
+        <v>10.9428148269653</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G70" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328800201416</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G71" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328800201416</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328800201416</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>10.9005327224731</v>
+        <v>10.9005346298218</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5538148880005</v>
+        <v>10.5538129806519</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.5</v>
       </c>
       <c r="G86" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G87" t="n">
-        <v>10.6806631088257</v>
+        <v>10.6806621551514</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>13</v>
       </c>
       <c r="G89" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>13</v>
       </c>
       <c r="G90" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G91" t="n">
-        <v>10.9850997924805</v>
+        <v>10.9850988388062</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.6383800506592</v>
+        <v>10.6383790969849</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G94" t="n">
-        <v>10.6383800506592</v>
+        <v>10.6383790969849</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G97" t="n">
-        <v>10.8159675598145</v>
+        <v>10.8159694671631</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G100" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.75</v>
       </c>
       <c r="G101" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>10.8159675598145</v>
+        <v>10.8159694671631</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G105" t="n">
-        <v>10.6806631088257</v>
+        <v>10.6806621551514</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G108" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328800201416</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G109" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>10.7990560531616</v>
+        <v>10.7990550994873</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.7060327529907</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G112" t="n">
-        <v>10.7060327529907</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G113" t="n">
-        <v>10.7060327529907</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G114" t="n">
-        <v>10.7060327529907</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>12.75</v>
       </c>
       <c r="G116" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.5</v>
       </c>
       <c r="G120" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>10.655291557312</v>
+        <v>10.6552934646606</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.5</v>
       </c>
       <c r="G126" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>10.655291557312</v>
+        <v>10.6552934646606</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>10.655291557312</v>
+        <v>10.6552934646606</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>10.655291557312</v>
+        <v>10.6552934646606</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>10.4015941619873</v>
+        <v>10.4015951156616</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>12.25</v>
       </c>
       <c r="G139" t="n">
-        <v>10.3593130111694</v>
+        <v>10.3593139648438</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>12.75</v>
       </c>
       <c r="G140" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>10.5284433364868</v>
+        <v>10.5284442901611</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>10.5284433364868</v>
+        <v>10.5284442901611</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>10.2324657440186</v>
+        <v>10.2324638366699</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>13</v>
       </c>
       <c r="G153" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512748718262</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G155" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512748718262</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.655291557312</v>
+        <v>10.6552934646606</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>10.9089908599854</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.5</v>
       </c>
       <c r="G167" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.5</v>
       </c>
       <c r="G169" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.75</v>
       </c>
       <c r="G170" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>12.75</v>
       </c>
       <c r="G171" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>10.5284433364868</v>
+        <v>10.5284442901611</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>13</v>
       </c>
       <c r="G174" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512748718262</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G177" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512748718262</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>13</v>
       </c>
       <c r="G181" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>13</v>
       </c>
       <c r="G182" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>13</v>
       </c>
       <c r="G183" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512748718262</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895364761353</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895364761353</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2472534179688</v>
+        <v>11.2472543716431</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895364761353</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2472534179688</v>
+        <v>11.2472543716431</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>11.5855159759521</v>
+        <v>11.5855169296265</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>13.5</v>
       </c>
       <c r="G200" t="n">
-        <v>11.4163866043091</v>
+        <v>11.4163856506348</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.5432329177856</v>
+        <v>11.54323387146</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>11.5432329177856</v>
+        <v>11.54323387146</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5009498596191</v>
+        <v>11.5009489059448</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>11.5702877044678</v>
+        <v>11.5702867507935</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>11.5702877044678</v>
+        <v>11.5702867507935</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>13.75</v>
       </c>
       <c r="G212" t="n">
-        <v>11.9169607162476</v>
+        <v>11.9169616699219</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>11.6569528579712</v>
+        <v>11.6569547653198</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>13.5</v>
       </c>
       <c r="G214" t="n">
-        <v>11.7002906799316</v>
+        <v>11.7002897262573</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G217" t="n">
-        <v>11.8736257553101</v>
+        <v>11.8736267089844</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>11.5269508361816</v>
+        <v>11.526951789856</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>11.5702877044678</v>
+        <v>11.5702867507935</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.6569528579712</v>
+        <v>11.6569547653198</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>11.8736257553101</v>
+        <v>11.8736267089844</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>11.9602947235107</v>
+        <v>11.9602956771851</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>13.75</v>
       </c>
       <c r="G228" t="n">
-        <v>11.9169607162476</v>
+        <v>11.9169616699219</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>12.0902996063232</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>13.75</v>
       </c>
       <c r="G230" t="n">
-        <v>11.9169607162476</v>
+        <v>11.9169616699219</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0469655990601</v>
+        <v>12.0469646453857</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>13.75</v>
       </c>
       <c r="G233" t="n">
-        <v>11.9169607162476</v>
+        <v>11.9169616699219</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.0902996063232</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>13.5</v>
       </c>
       <c r="G237" t="n">
-        <v>11.7002906799316</v>
+        <v>11.7002897262573</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>12.0469655990601</v>
+        <v>12.0469646453857</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>12.0036306381226</v>
+        <v>12.0036296844482</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>12.0902996063232</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.0469655990601</v>
+        <v>12.0469646453857</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>14.5</v>
       </c>
       <c r="G242" t="n">
-        <v>12.5669765472412</v>
+        <v>12.5669775009155</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>12.4803066253662</v>
+        <v>12.4803075790405</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>14.5</v>
       </c>
       <c r="G244" t="n">
-        <v>12.5669765472412</v>
+        <v>12.5669775009155</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>12.7403154373169</v>
+        <v>12.7403144836426</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>12.6969804763794</v>
+        <v>12.6969795227051</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G247" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>15</v>
       </c>
       <c r="G248" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>13.1303224563599</v>
+        <v>13.1303234100342</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8703174591064</v>
+        <v>12.8703184127808</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>13.0436563491821</v>
+        <v>13.0436553955078</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G256" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>12.9569854736328</v>
+        <v>12.9569864273071</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>12.8269844055176</v>
+        <v>12.8269834518433</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="G261" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>15</v>
       </c>
       <c r="G268" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>13.1303224563599</v>
+        <v>13.1303234100342</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203332901001</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>13.1303224563599</v>
+        <v>13.1303234100342</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G304" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203332901001</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203332901001</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>15.75</v>
       </c>
       <c r="G308" t="n">
-        <v>13.6503381729126</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636701583862</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>13.737006187439</v>
+        <v>13.7370052337646</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>13.737006187439</v>
+        <v>13.7370052337646</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636701583862</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203332901001</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203332901001</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203332901001</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636701583862</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>15</v>
       </c>
       <c r="G328" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>15</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636701583862</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>15.75</v>
       </c>
       <c r="G333" t="n">
-        <v>13.6503381729126</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>13.737006187439</v>
+        <v>13.7370052337646</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636701583862</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636701583862</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636701583862</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636701583862</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>15.75</v>
       </c>
       <c r="G348" t="n">
-        <v>13.6503381729126</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203332901001</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>15.75</v>
       </c>
       <c r="G350" t="n">
-        <v>13.6503381729126</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636701583862</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203332901001</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G355" t="n">
-        <v>13.3903303146362</v>
+        <v>13.3903312683105</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G356" t="n">
-        <v>13.3903303146362</v>
+        <v>13.3903312683105</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>15.75</v>
       </c>
       <c r="G357" t="n">
-        <v>13.6503381729126</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G360" t="n">
-        <v>13.3903303146362</v>
+        <v>13.3903312683105</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G365" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>13.1303224563599</v>
+        <v>13.1303234100342</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636701583862</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036613464355</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>13.3903303146362</v>
+        <v>13.3903312683105</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>13.3903303146362</v>
+        <v>13.3903312683105</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>13.3469972610474</v>
+        <v>13.346996307373</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>15.75</v>
       </c>
       <c r="G386" t="n">
-        <v>13.6503381729126</v>
+        <v>13.650336265564</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G389" t="n">
-        <v>14.4736909866333</v>
+        <v>14.4736938476562</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070358276367</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>14.6903619766235</v>
+        <v>14.6903638839722</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>14.4736909866333</v>
+        <v>14.4736938476562</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>14.5603590011597</v>
+        <v>14.5603580474854</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G403" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>14.5603590011597</v>
+        <v>14.5603580474854</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>14.5603590011597</v>
+        <v>14.5603580474854</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>14.6903619766235</v>
+        <v>14.6903638839722</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>14.6903619766235</v>
+        <v>14.6903638839722</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G411" t="n">
-        <v>14.6903619766235</v>
+        <v>14.6903638839722</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G412" t="n">
-        <v>14.6903619766235</v>
+        <v>14.6903638839722</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6903619766235</v>
+        <v>14.6903638839722</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G414" t="n">
-        <v>14.7770309448242</v>
+        <v>14.7770318984985</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4736909866333</v>
+        <v>14.4736938476562</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>14.4736909866333</v>
+        <v>14.4736938476562</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>16.5</v>
       </c>
       <c r="G420" t="n">
-        <v>14.3003540039062</v>
+        <v>14.3003530502319</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>14.4303550720215</v>
+        <v>14.4303541183472</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.5</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3003540039062</v>
+        <v>14.3003530502319</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>14.2570219039917</v>
+        <v>14.2570199966431</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>14.2570219039917</v>
+        <v>14.2570199966431</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>14.4736909866333</v>
+        <v>14.4736938476562</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>14.6903619766235</v>
+        <v>14.6903638839722</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>14.6903619766235</v>
+        <v>14.6903638839722</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>14.820366859436</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>14.820366859436</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>14.820366859436</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>14.820366859436</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G443" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070358276367</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>14.9937047958374</v>
+        <v>14.9937028884888</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G446" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070358276367</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>14.820366859436</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G448" t="n">
-        <v>14.7770309448242</v>
+        <v>14.7770318984985</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>15.0803737640381</v>
+        <v>15.0803747177124</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>15.0803737640381</v>
+        <v>15.0803747177124</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>14.9937047958374</v>
+        <v>14.9937028884888</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>15.0803737640381</v>
+        <v>15.0803747177124</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265398025513</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265398025513</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>17.25</v>
       </c>
       <c r="G456" t="n">
-        <v>15.3926906585693</v>
+        <v>15.3926887512207</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265398025513</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>17.25</v>
       </c>
       <c r="G458" t="n">
-        <v>15.3926906585693</v>
+        <v>15.3926887512207</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803728103638</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>14.991138458252</v>
+        <v>14.9911375045776</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G463" t="n">
-        <v>15.1249914169312</v>
+        <v>15.1249895095825</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>15.4373064041138</v>
+        <v>15.4373044967651</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>15.3480749130249</v>
+        <v>15.3480730056763</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>15.3480749130249</v>
+        <v>15.3480730056763</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>15.3480749130249</v>
+        <v>15.3480730056763</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>15.4373064041138</v>
+        <v>15.4373044967651</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G469" t="n">
-        <v>15.7496204376221</v>
+        <v>15.7496185302734</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>15.883472442627</v>
+        <v>15.8834667205811</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>15.883472442627</v>
+        <v>15.8834667205811</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G472" t="n">
-        <v>16.7758007049561</v>
+        <v>16.7757987976074</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G473" t="n">
-        <v>17.5788993835449</v>
+        <v>17.5788955688477</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>19.5</v>
       </c>
       <c r="G478" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>19.5</v>
       </c>
       <c r="G480" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>19.5</v>
       </c>
       <c r="G481" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>17.2219657897949</v>
+        <v>17.2219638824463</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>17.4450454711914</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>17.4450454711914</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>19.5</v>
       </c>
       <c r="G489" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G490" t="n">
-        <v>18.6496906280518</v>
+        <v>18.6496887207031</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>18.6496906280518</v>
+        <v>18.6496887207031</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>18.6496906280518</v>
+        <v>18.6496887207031</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>20.5</v>
       </c>
       <c r="G493" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>18.5604591369629</v>
+        <v>18.5604553222656</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>18.6496906280518</v>
+        <v>18.6496887207031</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>21</v>
       </c>
       <c r="G496" t="n">
-        <v>18.7389240264893</v>
+        <v>18.7389221191406</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>18.6496906280518</v>
+        <v>18.6496887207031</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>18.6496906280518</v>
+        <v>18.6496887207031</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>18.5604591369629</v>
+        <v>18.5604553222656</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>18.5604591369629</v>
+        <v>18.5604553222656</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G501" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>20.5</v>
       </c>
       <c r="G502" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>18.3819923400879</v>
+        <v>18.3819942474365</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G505" t="n">
-        <v>18.1142959594727</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>18.1142959594727</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>20.5</v>
       </c>
       <c r="G507" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>20.5</v>
       </c>
       <c r="G509" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>20.5</v>
       </c>
       <c r="G510" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>18.1142959594727</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>17.4450454711914</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>17.4450454711914</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.6681270599365</v>
+        <v>17.6681251525879</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G517" t="n">
-        <v>17.5788993835449</v>
+        <v>17.5788955688477</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>17.6681270599365</v>
+        <v>17.6681251525879</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>17.2219657897949</v>
+        <v>17.2219638824463</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>19.5</v>
       </c>
       <c r="G524" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>19.5</v>
       </c>
       <c r="G525" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>19.5</v>
       </c>
       <c r="G527" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>19.5</v>
       </c>
       <c r="G528" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>17.4896640777588</v>
+        <v>17.4896659851074</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>17.4450454711914</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>17.757360458374</v>
+        <v>17.7573585510254</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>20</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>20</v>
       </c>
       <c r="G535" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>20</v>
       </c>
       <c r="G537" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>18.1142959594727</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>20</v>
       </c>
       <c r="G539" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>18.1142959594727</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>18.3819923400879</v>
+        <v>18.3819942474365</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>18.6496906280518</v>
+        <v>18.6496887207031</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>20.5</v>
       </c>
       <c r="G549" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G552" t="n">
-        <v>18.1142959594727</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G553" t="n">
-        <v>18.3819923400879</v>
+        <v>18.3819942474365</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>20.5</v>
       </c>
       <c r="G554" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G555" t="n">
-        <v>18.5604591369629</v>
+        <v>18.5604553222656</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>17.7127437591553</v>
+        <v>17.7127456665039</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>17.7127437591553</v>
+        <v>17.7127456665039</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>18.1142959594727</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>20.5</v>
       </c>
       <c r="G564" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>20</v>
       </c>
       <c r="G565" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>20</v>
       </c>
       <c r="G566" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>20</v>
       </c>
       <c r="G567" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>20</v>
       </c>
       <c r="G568" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>17.6681270599365</v>
+        <v>17.6681251525879</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>20</v>
       </c>
       <c r="G570" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>20</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>20</v>
       </c>
       <c r="G572" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>18.1142959594727</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>20.5</v>
       </c>
       <c r="G579" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>18.1142959594727</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>21</v>
       </c>
       <c r="G585" t="n">
-        <v>18.7389240264893</v>
+        <v>18.7389221191406</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>19.4527893066406</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>19.4527893066406</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>19.3635559082031</v>
+        <v>19.3635578155518</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>19.4527893066406</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>19.809720993042</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>22</v>
       </c>
       <c r="G599" t="n">
-        <v>19.631254196167</v>
+        <v>19.6312522888184</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>19.809720993042</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>19.3635559082031</v>
+        <v>19.3635578155518</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G608" t="n">
-        <v>19.4527893066406</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>22</v>
       </c>
       <c r="G611" t="n">
-        <v>19.631254196167</v>
+        <v>19.6312522888184</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>19.8989543914795</v>
+        <v>19.8989524841309</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>19.809720993042</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>22</v>
       </c>
       <c r="G616" t="n">
-        <v>19.631254196167</v>
+        <v>19.6312522888184</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>20.7912826538086</v>
+        <v>20.7912845611572</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>20.8805160522461</v>
+        <v>20.8805179595947</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G623" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>20.8805160522461</v>
+        <v>20.8805179595947</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>21.7728462219238</v>
+        <v>21.7728481292725</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G629" t="n">
-        <v>21.9513111114502</v>
+        <v>21.9513130187988</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>21.6836109161377</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>21.6836109161377</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>21.2374439239502</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>21.0589809417725</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>21.0589809417725</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>20.7912826538086</v>
+        <v>20.7912845611572</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G645" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G654" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G655" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>21.2374439239502</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>21.2374439239502</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>23</v>
       </c>
       <c r="G662" t="n">
-        <v>20.5235862731934</v>
+        <v>20.5235824584961</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>19.3635559082031</v>
+        <v>19.3635578155518</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G669" t="n">
-        <v>18.6496906280518</v>
+        <v>18.6496887207031</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>20.5</v>
       </c>
       <c r="G670" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>17.4896640777588</v>
+        <v>17.4896659851074</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>18</v>
       </c>
       <c r="G675" t="n">
-        <v>16.0619335174561</v>
+        <v>16.0619354248047</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>17.5</v>
       </c>
       <c r="G676" t="n">
-        <v>15.6157703399658</v>
+        <v>15.6157732009888</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>14.9019079208374</v>
+        <v>14.9019088745117</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>15.035756111145</v>
+        <v>15.0357570648193</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>15.7496204376221</v>
+        <v>15.7496185302734</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>18.5604591369629</v>
+        <v>18.5604553222656</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>22</v>
       </c>
       <c r="G685" t="n">
-        <v>19.631254196167</v>
+        <v>19.6312522888184</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>20.7912826538086</v>
+        <v>20.7912845611572</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>21.2374439239502</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G689" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482181549072</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>23</v>
       </c>
       <c r="G690" t="n">
-        <v>20.5235862731934</v>
+        <v>20.5235824584961</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>20.8805160522461</v>
+        <v>20.8805179595947</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>20.8805160522461</v>
+        <v>20.8805179595947</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>21.6836109161377</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G696" t="n">
-        <v>21.0589809417725</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>21.0589809417725</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G709" t="n">
-        <v>21.6836109161377</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>22.0405445098877</v>
+        <v>22.0405464172363</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>25</v>
       </c>
       <c r="G711" t="n">
-        <v>22.7315845489502</v>
+        <v>22.7315826416016</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>22.6406593322754</v>
+        <v>22.640661239624</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678817749023</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>22.6406593322754</v>
+        <v>22.640661239624</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678817749023</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>22.6406593322754</v>
+        <v>22.640661239624</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>22.6406593322754</v>
+        <v>22.640661239624</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>22.0041751861572</v>
+        <v>22.0041770935059</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>21.7313919067383</v>
+        <v>21.7313957214355</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G732" t="n">
-        <v>21.7313919067383</v>
+        <v>21.7313957214355</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>24</v>
       </c>
       <c r="G733" t="n">
-        <v>21.8223190307617</v>
+        <v>21.8223209381104</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>23.5</v>
       </c>
       <c r="G734" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>23.5</v>
       </c>
       <c r="G740" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>23.5</v>
       </c>
       <c r="G741" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>23.5</v>
       </c>
       <c r="G742" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>20.549352645874</v>
+        <v>20.5493545532227</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>23.5</v>
       </c>
       <c r="G749" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>23.5</v>
       </c>
       <c r="G750" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>24</v>
       </c>
       <c r="G751" t="n">
-        <v>21.8223190307617</v>
+        <v>21.8223209381104</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>24</v>
       </c>
       <c r="G752" t="n">
-        <v>21.8223190307617</v>
+        <v>21.8223209381104</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>22.0041751861572</v>
+        <v>22.0041770935059</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>21.7313919067383</v>
+        <v>21.7313957214355</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>21.7313919067383</v>
+        <v>21.7313957214355</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>23.5</v>
       </c>
       <c r="G758" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G761" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>23.5</v>
       </c>
       <c r="G763" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>23.5</v>
       </c>
       <c r="G765" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>21.0949115753174</v>
+        <v>21.094913482666</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>21.0949115753174</v>
+        <v>21.094913482666</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>21.0949115753174</v>
+        <v>21.094913482666</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>21.0949115753174</v>
+        <v>21.094913482666</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>20.7312049865723</v>
+        <v>20.731201171875</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>23.5</v>
       </c>
       <c r="G786" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>23.5</v>
       </c>
       <c r="G787" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402816772461</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402816772461</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>20.549352645874</v>
+        <v>20.5493545532227</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G796" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402816772461</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402816772461</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G800" t="n">
-        <v>20.549352645874</v>
+        <v>20.5493545532227</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>22.0041751861572</v>
+        <v>22.0041770935059</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G804" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678817749023</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>23.5499210357666</v>
+        <v>23.5499229431152</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>22.9134387969971</v>
+        <v>22.9134407043457</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>23.0952892303467</v>
+        <v>23.095287322998</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>23.368070602417</v>
+        <v>23.3680667877197</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>24.4591827392578</v>
+        <v>24.4591846466064</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>26.5</v>
       </c>
       <c r="G813" t="n">
-        <v>24.0954780578613</v>
+        <v>24.09547996521</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>24.2773342132568</v>
+        <v>24.2773323059082</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>26.5</v>
       </c>
       <c r="G815" t="n">
-        <v>24.0954780578613</v>
+        <v>24.09547996521</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7319660186768</v>
+        <v>24.7319641113281</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>26.0049362182617</v>
+        <v>26.0049343109131</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>26.0958614349365</v>
+        <v>26.0958595275879</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>26.0958614349365</v>
+        <v>26.0958595275879</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>25.2775249481201</v>
+        <v>25.2775230407715</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>25.186595916748</v>
+        <v>25.1865940093994</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>26</v>
       </c>
       <c r="G833" t="n">
-        <v>23.64084815979</v>
+        <v>23.6408462524414</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G834" t="n">
-        <v>24.1864070892334</v>
+        <v>24.1864051818848</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>24.2773342132568</v>
+        <v>24.2773323059082</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G838" t="n">
-        <v>26.0049362182617</v>
+        <v>26.0049343109131</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>28.5</v>
       </c>
       <c r="G839" t="n">
-        <v>25.9140090942383</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5503044128418</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>25.8230800628662</v>
+        <v>25.8230819702148</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>26.1867847442627</v>
+        <v>26.1867828369141</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>26.2777118682861</v>
+        <v>26.2777137756348</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>26.2777118682861</v>
+        <v>26.2777137756348</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G847" t="n">
-        <v>26.0958614349365</v>
+        <v>26.0958595275879</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>28.5</v>
       </c>
       <c r="G848" t="n">
-        <v>25.9140090942383</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>28.5</v>
       </c>
       <c r="G849" t="n">
-        <v>25.9140090942383</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5503044128418</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5503044128418</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>26.1867847442627</v>
+        <v>26.1867828369141</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>25.8230800628662</v>
+        <v>25.8230819702148</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>26.0049362182617</v>
+        <v>26.0049343109131</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>28.5</v>
       </c>
       <c r="G856" t="n">
-        <v>25.9140090942383</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G857" t="n">
-        <v>26.7323417663574</v>
+        <v>26.7323455810547</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G861" t="n">
-        <v>30.278470993042</v>
+        <v>30.2784671783447</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>32.5</v>
       </c>
       <c r="G862" t="n">
-        <v>29.5510578155518</v>
+        <v>29.5510597229004</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G864" t="n">
-        <v>29.9147682189941</v>
+        <v>29.9147644042969</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>31.1877326965332</v>
+        <v>31.1877346038818</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>34.2792282104492</v>
+        <v>34.2792320251465</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>40</v>
       </c>
       <c r="G873" t="n">
-        <v>36.3705406188965</v>
+        <v>36.3705368041992</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>35.5521965026855</v>
+        <v>35.5522003173828</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>35.1884918212891</v>
+        <v>35.1884956359863</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G886" t="n">
-        <v>34.4610786437988</v>
+        <v>34.4610824584961</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G895" t="n">
-        <v>34.4610786437988</v>
+        <v>34.4610824584961</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G896" t="n">
-        <v>34.2792282104492</v>
+        <v>34.2792320251465</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>33.3699645996094</v>
+        <v>33.3699684143066</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G900" t="n">
-        <v>33.0971870422363</v>
+        <v>33.0971908569336</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>33.2790374755859</v>
+        <v>33.2790336608887</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G925" t="n">
-        <v>33.2790374755859</v>
+        <v>33.2790336608887</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>32.1879272460938</v>
+        <v>32.187931060791</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>39.5</v>
       </c>
       <c r="G931" t="n">
-        <v>35.9159088134766</v>
+        <v>35.915901184082</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G937" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G943" t="n">
-        <v>34.0064506530762</v>
+        <v>34.0064544677734</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G945" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G949" t="n">
-        <v>33.3699645996094</v>
+        <v>33.3699684143066</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G950" t="n">
-        <v>33.3699645996094</v>
+        <v>33.3699684143066</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G953" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>33.4608840942383</v>
+        <v>33.4608917236328</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G958" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>33.4608840942383</v>
+        <v>33.4608917236328</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G964" t="n">
-        <v>34.6370697021484</v>
+        <v>34.6370735168457</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G970" t="n">
-        <v>33.9887847900391</v>
+        <v>33.9887886047363</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G972" t="n">
-        <v>33.9887847900391</v>
+        <v>33.9887886047363</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G973" t="n">
-        <v>34.0813903808594</v>
+        <v>34.0813941955566</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3404922485352</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>36</v>
       </c>
       <c r="G981" t="n">
-        <v>33.3404922485352</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.7109489440918</v>
+        <v>33.7109527587891</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>39</v>
       </c>
       <c r="G986" t="n">
-        <v>36.1188735961914</v>
+        <v>36.1188697814941</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G987" t="n">
-        <v>38.6194114685059</v>
+        <v>38.6194152832031</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G988" t="n">
-        <v>39.1750831604004</v>
+        <v>39.1750793457031</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>46</v>
       </c>
       <c r="G989" t="n">
-        <v>42.6017456054688</v>
+        <v>42.601749420166</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>42.2312927246094</v>
+        <v>42.2312889099121</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>45.9357986450195</v>
+        <v>45.9357948303223</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1001" t="n">
-        <v>46.121021270752</v>
+        <v>46.1210250854492</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>45.5653457641602</v>
+        <v>45.5653495788574</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>46.121021270752</v>
+        <v>46.1210250854492</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>47.0471458435059</v>
+        <v>47.0471420288086</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>50</v>
       </c>
       <c r="G1008" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1009" t="n">
-        <v>47.0471458435059</v>
+        <v>47.0471420288086</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>50</v>
       </c>
       <c r="G1010" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>50</v>
       </c>
       <c r="G1011" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1013" t="n">
-        <v>47.0471458435059</v>
+        <v>47.0471420288086</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>46.121021270752</v>
+        <v>46.1210250854492</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1016" t="n">
-        <v>47.6028213500977</v>
+        <v>47.6028175354004</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>47.0471458435059</v>
+        <v>47.0471420288086</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>46.8619232177734</v>
+        <v>46.8619194030762</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>50</v>
       </c>
       <c r="G1020" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>52</v>
       </c>
       <c r="G1022" t="n">
-        <v>48.1584968566895</v>
+        <v>48.1584930419922</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>54</v>
       </c>
       <c r="G1023" t="n">
-        <v>50.0107421875</v>
+        <v>50.0107460021973</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>48.8993911743164</v>
+        <v>48.8993949890137</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G1025" t="n">
-        <v>50.3811988830566</v>
+        <v>50.3811950683594</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>53.5300178527832</v>
+        <v>53.5300216674805</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>58.1606369018555</v>
+        <v>58.1606407165527</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>62</v>
       </c>
       <c r="G1032" t="n">
-        <v>57.4197463989258</v>
+        <v>57.4197425842285</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>62</v>
       </c>
       <c r="G1034" t="n">
-        <v>57.4197463989258</v>
+        <v>57.4197425842285</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1038" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>55.0118255615234</v>
+        <v>55.0118217468262</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>56.864070892334</v>
+        <v>56.8640670776367</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>59.6424522399902</v>
+        <v>59.642448425293</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>59.8276748657227</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>60.7537956237793</v>
+        <v>60.753791809082</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>71</v>
       </c>
       <c r="G1048" t="n">
-        <v>65.7548675537109</v>
+        <v>65.7548751831055</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>71</v>
       </c>
       <c r="G1049" t="n">
-        <v>65.7548675537109</v>
+        <v>65.7548751831055</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>70</v>
       </c>
       <c r="G1054" t="n">
-        <v>64.828742980957</v>
+        <v>64.8287506103516</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799087524414</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799087524414</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1062" t="n">
-        <v>62.420825958252</v>
+        <v>62.4208221435547</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>61.4947052001953</v>
+        <v>61.494701385498</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1064" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799087524414</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1066" t="n">
-        <v>58.1606369018555</v>
+        <v>58.1606407165527</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>63</v>
       </c>
       <c r="G1070" t="n">
-        <v>58.3458671569824</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1072" t="n">
-        <v>57.9754180908203</v>
+        <v>57.9754219055176</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>62</v>
       </c>
       <c r="G1073" t="n">
-        <v>57.4197463989258</v>
+        <v>57.4197425842285</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>57.6049690246582</v>
+        <v>57.6049728393555</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1075" t="n">
-        <v>56.864070892334</v>
+        <v>56.8640670776367</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>57.2345161437988</v>
+        <v>57.2345199584961</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1079" t="n">
-        <v>61.3094711303711</v>
+        <v>61.3094673156738</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>68</v>
       </c>
       <c r="G1083" t="n">
-        <v>62.9764976501465</v>
+        <v>62.976505279541</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>68</v>
       </c>
       <c r="G1087" t="n">
-        <v>62.9764976501465</v>
+        <v>62.976505279541</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>68</v>
       </c>
       <c r="G1089" t="n">
-        <v>62.9764976501465</v>
+        <v>62.976505279541</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>72</v>
       </c>
       <c r="G1091" t="n">
-        <v>66.6809844970703</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>71</v>
       </c>
       <c r="G1092" t="n">
-        <v>65.7548675537109</v>
+        <v>65.7548751831055</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>65.5696411132812</v>
+        <v>65.5696487426758</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G1097" t="n">
-        <v>65.9400939941406</v>
+        <v>65.9400863647461</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1099" t="n">
-        <v>65.5696411132812</v>
+        <v>65.5696487426758</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1104" t="n">
-        <v>64.0878524780273</v>
+        <v>64.0878448486328</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>74</v>
       </c>
       <c r="G1107" t="n">
-        <v>68.5332489013672</v>
+        <v>68.5332412719727</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1108" t="n">
-        <v>70.2002639770508</v>
+        <v>70.2002716064453</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>74</v>
       </c>
       <c r="G1109" t="n">
-        <v>68.5332489013672</v>
+        <v>68.5332412719727</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>71</v>
       </c>
       <c r="G1111" t="n">
-        <v>65.7548675537109</v>
+        <v>65.7548751831055</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1112" t="n">
-        <v>68.1627807617188</v>
+        <v>68.1627883911133</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>74</v>
       </c>
       <c r="G1113" t="n">
-        <v>68.5332489013672</v>
+        <v>68.5332412719727</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1114" t="n">
-        <v>67.4218978881836</v>
+        <v>67.4219055175781</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1117" t="n">
-        <v>68.1627807617188</v>
+        <v>68.1627883911133</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>73.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>67.9775695800781</v>
+        <v>67.9775772094727</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>72</v>
       </c>
       <c r="G1123" t="n">
-        <v>66.6809844970703</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>74</v>
       </c>
       <c r="G1125" t="n">
-        <v>68.5332489013672</v>
+        <v>68.5332412719727</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1126" t="n">
-        <v>68.1627807617188</v>
+        <v>68.1627883911133</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1127" t="n">
-        <v>67.4218978881836</v>
+        <v>67.4219055175781</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>73.4000015258789</v>
       </c>
       <c r="G1128" t="n">
-        <v>67.9775695800781</v>
+        <v>67.9775772094727</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1129" t="n">
-        <v>68.1627807617188</v>
+        <v>68.1627883911133</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>69.8298110961914</v>
+        <v>69.8298187255859</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>75</v>
       </c>
       <c r="G1133" t="n">
-        <v>69.4593658447266</v>
+        <v>69.4593734741211</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1134" t="n">
-        <v>70.2002639770508</v>
+        <v>70.2002716064453</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>79</v>
       </c>
       <c r="G1135" t="n">
-        <v>73.1638717651367</v>
+        <v>73.1638641357422</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>78</v>
       </c>
       <c r="G1137" t="n">
-        <v>72.2377471923828</v>
+        <v>72.2377395629883</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>74</v>
       </c>
       <c r="G1139" t="n">
-        <v>68.5332489013672</v>
+        <v>68.5332412719727</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1140" t="n">
-        <v>67.4218978881836</v>
+        <v>67.4219055175781</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>70</v>
       </c>
       <c r="G1143" t="n">
-        <v>64.828742980957</v>
+        <v>64.8287506103516</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1147" t="n">
-        <v>62.420825958252</v>
+        <v>62.4208221435547</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1148" t="n">
-        <v>60.7537956237793</v>
+        <v>60.753791809082</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1151" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799087524414</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1152" t="n">
-        <v>61.3094711303711</v>
+        <v>61.3094673156738</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1154" t="n">
-        <v>60.7537956237793</v>
+        <v>60.753791809082</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>60.9390296936035</v>
+        <v>60.939022064209</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>59.8276748657227</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>57.9754180908203</v>
+        <v>57.9754219055176</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1166" t="n">
-        <v>57.9754180908203</v>
+        <v>57.9754219055176</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>63</v>
       </c>
       <c r="G1168" t="n">
-        <v>58.3458671569824</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>57.2345161437988</v>
+        <v>57.2345199584961</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>58.1606369018555</v>
+        <v>58.1606407165527</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1174" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1175" t="n">
-        <v>57.2345161437988</v>
+        <v>57.2345199584961</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1176" t="n">
-        <v>55.1970443725586</v>
+        <v>55.1970405578613</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>53.5300178527832</v>
+        <v>53.5300216674805</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1180" t="n">
-        <v>53.3447952270508</v>
+        <v>53.3447914123535</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>52.2334480285645</v>
+        <v>52.2334442138672</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1182" t="n">
-        <v>55.1970443725586</v>
+        <v>55.1970405578613</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1184" t="n">
-        <v>55.382266998291</v>
+        <v>55.3822708129883</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1189" t="n">
-        <v>61.3094711303711</v>
+        <v>61.3094673156738</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1190" t="n">
-        <v>60.9390296936035</v>
+        <v>60.939022064209</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1193" t="n">
-        <v>59.8276748657227</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1194" t="n">
-        <v>59.8276748657227</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>63</v>
       </c>
       <c r="G1196" t="n">
-        <v>58.3458671569824</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>63.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>58.8089332580566</v>
+        <v>58.8089370727539</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>61.4947052001953</v>
+        <v>61.494701385498</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>65.6999969482422</v>
       </c>
       <c r="G1204" t="n">
-        <v>60.8464050292969</v>
+        <v>60.8464012145996</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>65.6999969482422</v>
       </c>
       <c r="G1205" t="n">
-        <v>60.8464050292969</v>
+        <v>60.8464012145996</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1211" t="n">
-        <v>59.920280456543</v>
+        <v>59.9202766418457</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>58.1606369018555</v>
+        <v>58.1606407165527</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>63</v>
       </c>
       <c r="G1214" t="n">
-        <v>58.3458671569824</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1215" t="n">
-        <v>60.1055145263672</v>
+        <v>60.1055107116699</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1216" t="n">
-        <v>60.6766929626465</v>
+        <v>60.6766967773438</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1220" t="n">
-        <v>51.5939140319824</v>
+        <v>51.5939178466797</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1222" t="n">
-        <v>54.1221084594727</v>
+        <v>54.1221122741699</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1224" t="n">
-        <v>53.6539306640625</v>
+        <v>53.6539268493652</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G1229" t="n">
-        <v>57.2121276855469</v>
+        <v>57.2121238708496</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1231" t="n">
-        <v>58.8039474487305</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>57.8675842285156</v>
+        <v>57.8675880432129</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>62.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>58.5230407714844</v>
+        <v>58.5230445861816</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>64</v>
       </c>
       <c r="G1236" t="n">
-        <v>59.9275932312012</v>
+        <v>59.9275970458984</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G1237" t="n">
-        <v>61.893970489502</v>
+        <v>61.8939666748047</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>60.3021507263184</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>62.5</v>
       </c>
       <c r="G1242" t="n">
-        <v>58.5230407714844</v>
+        <v>58.5230445861816</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1243" t="n">
-        <v>58.8039474487305</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>61.5</v>
       </c>
       <c r="G1244" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>58.8039474487305</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>56.7439422607422</v>
+        <v>56.7439384460449</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>62</v>
       </c>
       <c r="G1248" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>59</v>
       </c>
       <c r="G1250" t="n">
-        <v>55.2457504272461</v>
+        <v>55.2457542419434</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1252" t="n">
-        <v>55.9012145996094</v>
+        <v>55.9012107849121</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1262" t="n">
-        <v>57.4930381774902</v>
+        <v>57.493034362793</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1264" t="n">
-        <v>60.6766929626465</v>
+        <v>60.6766967773438</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>67</v>
       </c>
       <c r="G1265" t="n">
-        <v>62.7367095947266</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1266" t="n">
-        <v>61.6130676269531</v>
+        <v>61.6130638122559</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1272" t="n">
-        <v>60.3021507263184</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1274" t="n">
-        <v>60.1148643493652</v>
+        <v>60.1148681640625</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1279" t="n">
-        <v>62.4557914733887</v>
+        <v>62.4557876586914</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>68.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>64.1412582397461</v>
+        <v>64.1412658691406</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1284" t="n">
-        <v>64.7967224121094</v>
+        <v>64.7967147827148</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>67</v>
       </c>
       <c r="G1285" t="n">
-        <v>62.7367095947266</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>68.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>64.1412582397461</v>
+        <v>64.1412658691406</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>68.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>64.1412582397461</v>
+        <v>64.1412658691406</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>68.5</v>
       </c>
       <c r="G1290" t="n">
-        <v>64.1412582397461</v>
+        <v>64.1412658691406</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>67</v>
       </c>
       <c r="G1295" t="n">
-        <v>62.7367095947266</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>68.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>64.1412582397461</v>
+        <v>64.1412658691406</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>68.5</v>
       </c>
       <c r="G1297" t="n">
-        <v>64.1412582397461</v>
+        <v>64.1412658691406</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>68.5</v>
       </c>
       <c r="G1300" t="n">
-        <v>64.1412582397461</v>
+        <v>64.1412658691406</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>68.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>64.1412582397461</v>
+        <v>64.1412658691406</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1309" t="n">
-        <v>65.3585357666016</v>
+        <v>65.358528137207</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>71.0999984741211</v>
       </c>
       <c r="G1310" t="n">
-        <v>66.5758056640625</v>
+        <v>66.575813293457</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>70.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>66.0139846801758</v>
+        <v>66.0139923095703</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1312" t="n">
-        <v>66.2949066162109</v>
+        <v>66.2949142456055</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G1321" t="n">
-        <v>60.2085075378418</v>
+        <v>60.2085113525391</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>64</v>
       </c>
       <c r="G1322" t="n">
-        <v>59.9275932312012</v>
+        <v>59.9275970458984</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>66.3000030517578</v>
       </c>
       <c r="G1324" t="n">
-        <v>62.0812530517578</v>
+        <v>62.0812454223633</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1331" t="n">
-        <v>60.3021507263184</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1333" t="n">
-        <v>60.4894180297852</v>
+        <v>60.4894142150879</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>64</v>
       </c>
       <c r="G1336" t="n">
-        <v>59.9275932312012</v>
+        <v>59.9275970458984</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1339" t="n">
-        <v>60.1148643493652</v>
+        <v>60.1148681640625</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1341" t="n">
-        <v>61.9876098632812</v>
+        <v>61.987606048584</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1342" t="n">
-        <v>61.9876098632812</v>
+        <v>61.987606048584</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1343" t="n">
-        <v>61.9876098632812</v>
+        <v>61.987606048584</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>66.9000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>62.6430702209473</v>
+        <v>62.64306640625</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1351" t="n">
-        <v>62.4557914733887</v>
+        <v>62.4557876586914</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1352" t="n">
-        <v>62.4557914733887</v>
+        <v>62.4557876586914</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>67</v>
       </c>
       <c r="G1354" t="n">
-        <v>62.7367095947266</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1357" t="n">
-        <v>60.4894180297852</v>
+        <v>60.4894142150879</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1359" t="n">
-        <v>60.6766929626465</v>
+        <v>60.6766967773438</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1360" t="n">
-        <v>60.5830497741699</v>
+        <v>60.5830459594727</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1362" t="n">
-        <v>60.4894180297852</v>
+        <v>60.4894142150879</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>60.3021507263184</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>62</v>
       </c>
       <c r="G1369" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>57.6803092956543</v>
+        <v>57.6803131103516</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>62</v>
       </c>
       <c r="G1379" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>62.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>58.5230407714844</v>
+        <v>58.5230445861816</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>62.5</v>
       </c>
       <c r="G1385" t="n">
-        <v>58.5230407714844</v>
+        <v>58.5230445861816</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>58.8039474487305</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>58.8039474487305</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1391" t="n">
-        <v>60.1148643493652</v>
+        <v>60.1148681640625</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>64</v>
       </c>
       <c r="G1393" t="n">
-        <v>59.9275932312012</v>
+        <v>59.9275970458984</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>58.8039474487305</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>62.5</v>
       </c>
       <c r="G1400" t="n">
-        <v>58.5230407714844</v>
+        <v>58.5230445861816</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>62</v>
       </c>
       <c r="G1401" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>61.5</v>
       </c>
       <c r="G1403" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>61.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1406" t="n">
-        <v>57.4930381774902</v>
+        <v>57.493034362793</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>59</v>
       </c>
       <c r="G1411" t="n">
-        <v>55.2457504272461</v>
+        <v>55.2457542419434</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1413" t="n">
-        <v>55.3393898010254</v>
+        <v>55.3393936157227</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1417" t="n">
-        <v>57.4930381774902</v>
+        <v>57.493034362793</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>62</v>
       </c>
       <c r="G1418" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>61.5</v>
       </c>
       <c r="G1420" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>62</v>
       </c>
       <c r="G1424" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>62</v>
       </c>
       <c r="G1426" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>61.5</v>
       </c>
       <c r="G1427" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G1428" t="n">
-        <v>57.2121276855469</v>
+        <v>57.2121238708496</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1435" t="n">
-        <v>56.7439422607422</v>
+        <v>56.7439384460449</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>57.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>53.8411979675293</v>
+        <v>53.8412017822266</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1442" t="n">
-        <v>53.6539306640625</v>
+        <v>53.6539268493652</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G1447" t="n">
-        <v>52.998462677002</v>
+        <v>52.9984664916992</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>52.0620994567871</v>
+        <v>52.0620956420898</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1453" t="n">
-        <v>52.0620994567871</v>
+        <v>52.0620956420898</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1457" t="n">
-        <v>51.5939140319824</v>
+        <v>51.5939178466797</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>51.219367980957</v>
+        <v>51.2193641662598</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G1462" t="n">
-        <v>49.8148155212402</v>
+        <v>49.814811706543</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>47.1929817199707</v>
+        <v>47.192985534668</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>52</v>
       </c>
       <c r="G1472" t="n">
-        <v>48.6911735534668</v>
+        <v>48.6911697387695</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>52</v>
       </c>
       <c r="G1474" t="n">
-        <v>48.6911735534668</v>
+        <v>48.6911697387695</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -61030,6 +61030,32 @@
         <v>71</v>
       </c>
       <c r="H2333" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2334" t="n">
+        <v>26083</v>
+      </c>
+      <c r="C2334" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="D2334" t="n">
+        <v>70.1999969482422</v>
+      </c>
+      <c r="E2334" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2334" t="n">
+        <v>70.9000015258789</v>
+      </c>
+      <c r="G2334" t="n">
+        <v>70.9000015258789</v>
+      </c>
+      <c r="H2334" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -421,7 +421,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>11.8307571411133</v>
+        <v>11.8307580947876</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>11.7123651504517</v>
+        <v>11.712366104126</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G4" t="n">
-        <v>11.1796007156372</v>
+        <v>11.1795997619629</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G5" t="n">
-        <v>11.0273818969727</v>
+        <v>11.027382850647</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8244256973267</v>
+        <v>10.824423789978</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1457738876343</v>
+        <v>11.1457757949829</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1711444854736</v>
+        <v>11.1711463928223</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>11.2726221084595</v>
+        <v>11.2726230621338</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G12" t="n">
-        <v>11.1880569458008</v>
+        <v>11.1880578994751</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G14" t="n">
-        <v>11.0273818969727</v>
+        <v>11.027382850647</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G15" t="n">
-        <v>11.0781240463257</v>
+        <v>11.0781211853027</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G17" t="n">
-        <v>11.2726221084595</v>
+        <v>11.2726230621338</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G18" t="n">
-        <v>11.1034917831421</v>
+        <v>11.1034908294678</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>11.0358400344849</v>
+        <v>11.0358390808105</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>11.1204051971436</v>
+        <v>11.1204042434692</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G25" t="n">
-        <v>11.1034917831421</v>
+        <v>11.1034908294678</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>11.0781240463257</v>
+        <v>11.0781211853027</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G32" t="n">
-        <v>10.8159666061401</v>
+        <v>10.8159685134888</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G35" t="n">
-        <v>10.6468372344971</v>
+        <v>10.6468353271484</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0696649551392</v>
+        <v>11.0696659088135</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>10.9428157806396</v>
+        <v>10.9428176879883</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G38" t="n">
-        <v>10.9343585968018</v>
+        <v>10.9343605041504</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0781240463257</v>
+        <v>11.0781211853027</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.6700830459595</v>
+        <v>11.6700820922852</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G44" t="n">
-        <v>11.6700830459595</v>
+        <v>11.6700820922852</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.6447124481201</v>
+        <v>11.6447134017944</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6447124481201</v>
+        <v>11.6447134017944</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>11.5855159759521</v>
+        <v>11.5855169296265</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G51" t="n">
-        <v>11.4671258926392</v>
+        <v>11.4671249389648</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.5</v>
       </c>
       <c r="G53" t="n">
-        <v>11.4163856506348</v>
+        <v>11.4163846969604</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>13.25</v>
       </c>
       <c r="G57" t="n">
-        <v>11.2049713134766</v>
+        <v>11.2049703598022</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G58" t="n">
-        <v>11.1288604736328</v>
+        <v>11.1288614273071</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>13</v>
       </c>
       <c r="G59" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G60" t="n">
-        <v>11.1457738876343</v>
+        <v>11.1457757949829</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>11.1204051971436</v>
+        <v>11.1204042434692</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G62" t="n">
-        <v>11.1457738876343</v>
+        <v>11.1457757949829</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G63" t="n">
-        <v>11.052752494812</v>
+        <v>11.0527505874634</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G64" t="n">
-        <v>11.1542310714722</v>
+        <v>11.1542320251465</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>10.9428157806396</v>
+        <v>10.9428176879883</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667068481445</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>10.8244256973267</v>
+        <v>10.824423789978</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G70" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328828811646</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G71" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328828811646</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328828811646</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>10.8244256973267</v>
+        <v>10.824423789978</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.5</v>
       </c>
       <c r="G86" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G88" t="n">
-        <v>10.6637496948242</v>
+        <v>10.6637487411499</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>13</v>
       </c>
       <c r="G89" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>13</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>10.8244256973267</v>
+        <v>10.824423789978</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G97" t="n">
-        <v>10.8159666061401</v>
+        <v>10.8159685134888</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>10.8244256973267</v>
+        <v>10.824423789978</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G100" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G102" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667068481445</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>10.8159666061401</v>
+        <v>10.8159685134888</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G106" t="n">
-        <v>10.8497943878174</v>
+        <v>10.8497934341431</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>10.8244256973267</v>
+        <v>10.824423789978</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G108" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328828811646</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G109" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>10.799054145813</v>
+        <v>10.7990550994873</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861621856689</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.5</v>
       </c>
       <c r="G120" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.5</v>
       </c>
       <c r="G126" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861621856689</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>10.4438781738281</v>
+        <v>10.4438791275024</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>10.5284452438354</v>
+        <v>10.5284442901611</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>10.5284452438354</v>
+        <v>10.5284442901611</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>10.4438781738281</v>
+        <v>10.4438791275024</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861621856689</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>10.2324657440186</v>
+        <v>10.2324647903442</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861621856689</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861621856689</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>10.1901817321777</v>
+        <v>10.1901807785034</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861621856689</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861621856689</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>10.4861612319946</v>
+        <v>10.4861621856689</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>13</v>
       </c>
       <c r="G153" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>10.8244256973267</v>
+        <v>10.824423789978</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667068481445</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G163" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G165" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.5</v>
       </c>
       <c r="G167" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.5</v>
       </c>
       <c r="G169" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>10.5284452438354</v>
+        <v>10.5284442901611</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>13</v>
       </c>
       <c r="G174" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667068481445</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>10.8244256973267</v>
+        <v>10.824423789978</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667068481445</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>13</v>
       </c>
       <c r="G181" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>13</v>
       </c>
       <c r="G182" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>13</v>
       </c>
       <c r="G183" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2472524642944</v>
+        <v>11.2472534179688</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>11.0358400344849</v>
+        <v>11.0358390808105</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2472524642944</v>
+        <v>11.2472534179688</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>11.3741016387939</v>
+        <v>11.3741035461426</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>11.5855159759521</v>
+        <v>11.5855169296265</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>13.5</v>
       </c>
       <c r="G200" t="n">
-        <v>11.4163856506348</v>
+        <v>11.4163846969604</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.5432329177856</v>
+        <v>11.5432348251343</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>11.5432329177856</v>
+        <v>11.5432348251343</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>11.5702867507935</v>
+        <v>11.5702877044678</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>11.440281867981</v>
+        <v>11.4402809143066</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>13.25</v>
       </c>
       <c r="G207" t="n">
-        <v>11.4836168289185</v>
+        <v>11.4836177825928</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>13.25</v>
       </c>
       <c r="G208" t="n">
-        <v>11.4836168289185</v>
+        <v>11.4836177825928</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>11.5702867507935</v>
+        <v>11.5702877044678</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>11.440281867981</v>
+        <v>11.4402809143066</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>11.6569557189941</v>
+        <v>11.6569538116455</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>13.5</v>
       </c>
       <c r="G214" t="n">
-        <v>11.700288772583</v>
+        <v>11.7002878189087</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>11.526951789856</v>
+        <v>11.5269527435303</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>11.5702867507935</v>
+        <v>11.5702877044678</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.6569557189941</v>
+        <v>11.6569538116455</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>11.8302927017212</v>
+        <v>11.8302917480469</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>11.8302927017212</v>
+        <v>11.8302917480469</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>11.9602966308594</v>
+        <v>11.9602947235107</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902996063232</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G231" t="n">
-        <v>11.8302927017212</v>
+        <v>11.8302917480469</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0469636917114</v>
+        <v>12.0469646453857</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902996063232</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>13.5</v>
       </c>
       <c r="G237" t="n">
-        <v>11.700288772583</v>
+        <v>11.7002878189087</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>12.0469636917114</v>
+        <v>12.0469646453857</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>12.0036287307739</v>
+        <v>12.0036296844482</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902996063232</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.0469636917114</v>
+        <v>12.0469646453857</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G247" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136533737183</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>15</v>
       </c>
       <c r="G248" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136533737183</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>13.1303243637085</v>
+        <v>13.1303215026855</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8703184127808</v>
+        <v>12.8703174591064</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G256" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136533737183</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136533737183</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>12.8269844055176</v>
+        <v>12.8269834518433</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136533737183</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="G261" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>15.25</v>
       </c>
       <c r="G265" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G266" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>15</v>
       </c>
       <c r="G268" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>13.1303243637085</v>
+        <v>13.1303215026855</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>15.25</v>
       </c>
       <c r="G284" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>15.25</v>
       </c>
       <c r="G285" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>15.25</v>
       </c>
       <c r="G288" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>15.25</v>
       </c>
       <c r="G290" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>13.1303243637085</v>
+        <v>13.1303215026855</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>15.25</v>
       </c>
       <c r="G303" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G304" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>13.7370071411133</v>
+        <v>13.737006187439</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>13.7370071411133</v>
+        <v>13.737006187439</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>15.25</v>
       </c>
       <c r="G325" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>15</v>
       </c>
       <c r="G328" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>15</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>13.7370071411133</v>
+        <v>13.737006187439</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G355" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903293609619</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G356" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903293609619</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G360" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903293609619</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G365" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>13.1303243637085</v>
+        <v>13.1303215026855</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>13.1736574172974</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903293609619</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903293609619</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770011901855</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1270170211792</v>
+        <v>14.1270151138306</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>14.2136840820312</v>
+        <v>14.2136831283569</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G389" t="n">
-        <v>14.4736909866333</v>
+        <v>14.4736928939819</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>14.6470289230347</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.6470289230347</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>17.25</v>
       </c>
       <c r="G392" t="n">
-        <v>14.9503707885742</v>
+        <v>14.9503688812256</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>17</v>
       </c>
       <c r="G395" t="n">
-        <v>14.7336959838867</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>14.4736909866333</v>
+        <v>14.4736928939819</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>16.75</v>
       </c>
       <c r="G397" t="n">
-        <v>14.5170249938965</v>
+        <v>14.5170269012451</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>14.5603609085083</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>14.6470289230347</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>17</v>
       </c>
       <c r="G400" t="n">
-        <v>14.7336959838867</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G403" t="n">
-        <v>14.6470289230347</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>14.5603609085083</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>14.5603609085083</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>17</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7336959838867</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>14.6470289230347</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>17</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7336959838867</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G411" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G412" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G414" t="n">
-        <v>14.7770309448242</v>
+        <v>14.7770328521729</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>14.6470289230347</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>16.75</v>
       </c>
       <c r="G417" t="n">
-        <v>14.5170249938965</v>
+        <v>14.5170269012451</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4736909866333</v>
+        <v>14.4736928939819</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>14.4736909866333</v>
+        <v>14.4736928939819</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>14.4303569793701</v>
+        <v>14.4303560256958</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>14.2570190429688</v>
+        <v>14.2570199966431</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>14.2570190429688</v>
+        <v>14.2570199966431</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>14.6470289230347</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>17</v>
       </c>
       <c r="G430" t="n">
-        <v>14.7336959838867</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>14.4736909866333</v>
+        <v>14.4736928939819</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>17</v>
       </c>
       <c r="G432" t="n">
-        <v>14.7336959838867</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>14.6470289230347</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>17</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7336959838867</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>14.6470289230347</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>14.820366859436</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>14.820366859436</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>14.820366859436</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>14.820366859436</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G444" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>14.9937028884888</v>
+        <v>14.9937047958374</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>14.820366859436</v>
+        <v>14.8203659057617</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G448" t="n">
-        <v>14.7770309448242</v>
+        <v>14.7770328521729</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>15.0370378494263</v>
+        <v>15.0370388031006</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803747177124</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803747177124</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>14.9937028884888</v>
+        <v>14.9937047958374</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803747177124</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265398025513</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265398025513</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>17.25</v>
       </c>
       <c r="G456" t="n">
-        <v>15.3926887512207</v>
+        <v>15.3926877975464</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265398025513</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>17.25</v>
       </c>
       <c r="G458" t="n">
-        <v>15.3926887512207</v>
+        <v>15.3926877975464</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>17</v>
       </c>
       <c r="G459" t="n">
-        <v>15.1696043014526</v>
+        <v>15.169605255127</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>15.0803728103638</v>
+        <v>15.0803709030151</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>15.2142219543457</v>
+        <v>15.21422290802</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>14.9911413192749</v>
+        <v>14.9911394119263</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>15.4373035430908</v>
+        <v>15.4373054504395</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>15.4373035430908</v>
+        <v>15.4373054504395</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G469" t="n">
-        <v>15.7496213912964</v>
+        <v>15.7496223449707</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>15.8834686279297</v>
+        <v>15.8834667205811</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>15.8834686279297</v>
+        <v>15.8834667205811</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G472" t="n">
-        <v>16.7757987976074</v>
+        <v>16.7758007049561</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G473" t="n">
-        <v>17.5788955688477</v>
+        <v>17.5788974761963</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>16.9988803863525</v>
+        <v>16.9988822937012</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>19.5</v>
       </c>
       <c r="G478" t="n">
-        <v>17.4004325866699</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>19.5</v>
       </c>
       <c r="G480" t="n">
-        <v>17.4004325866699</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>19.5</v>
       </c>
       <c r="G481" t="n">
-        <v>17.4004325866699</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450435638428</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450435638428</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>19.5</v>
       </c>
       <c r="G489" t="n">
-        <v>17.4004325866699</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>20.5</v>
       </c>
       <c r="G493" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>21</v>
       </c>
       <c r="G496" t="n">
-        <v>18.7389259338379</v>
+        <v>18.7389240264893</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G501" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>20.5</v>
       </c>
       <c r="G502" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G504" t="n">
-        <v>18.0250625610352</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>20.5</v>
       </c>
       <c r="G507" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G508" t="n">
-        <v>18.0250625610352</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>20.5</v>
       </c>
       <c r="G509" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>20.5</v>
       </c>
       <c r="G510" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450435638428</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450435638428</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>17.8019771575928</v>
+        <v>17.8019790649414</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.6681270599365</v>
+        <v>17.6681308746338</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G517" t="n">
-        <v>17.5788955688477</v>
+        <v>17.5788974761963</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>17.6681270599365</v>
+        <v>17.6681308746338</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>19.75</v>
       </c>
       <c r="G519" t="n">
-        <v>17.6235122680664</v>
+        <v>17.623514175415</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>17.266580581665</v>
+        <v>17.2665786743164</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>17.266580581665</v>
+        <v>17.2665786743164</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>19.5</v>
       </c>
       <c r="G524" t="n">
-        <v>17.4004325866699</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>19.5</v>
       </c>
       <c r="G525" t="n">
-        <v>17.4004325866699</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>19.5</v>
       </c>
       <c r="G527" t="n">
-        <v>17.4004325866699</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>19.5</v>
       </c>
       <c r="G528" t="n">
-        <v>17.4004325866699</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>17.4896659851074</v>
+        <v>17.4896640777588</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450435638428</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>17.757360458374</v>
+        <v>17.7573623657227</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>20</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>20</v>
       </c>
       <c r="G535" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>18.0250625610352</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>20</v>
       </c>
       <c r="G537" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>20</v>
       </c>
       <c r="G539" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>20.5</v>
       </c>
       <c r="G549" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G550" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>18.0250625610352</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>20.5</v>
       </c>
       <c r="G554" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>18.0250625610352</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>17.7127456665039</v>
+        <v>17.7127475738525</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>17.7127456665039</v>
+        <v>17.7127475738525</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G562" t="n">
-        <v>18.0250625610352</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>20.5</v>
       </c>
       <c r="G564" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>20</v>
       </c>
       <c r="G565" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>20</v>
       </c>
       <c r="G566" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>20</v>
       </c>
       <c r="G567" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>20</v>
       </c>
       <c r="G568" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>17.6681270599365</v>
+        <v>17.6681308746338</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>20</v>
       </c>
       <c r="G570" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>20</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>20</v>
       </c>
       <c r="G572" t="n">
-        <v>17.8465938568115</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>19.75</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6235122680664</v>
+        <v>17.623514175415</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>18.0250625610352</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>20.5</v>
       </c>
       <c r="G579" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>21</v>
       </c>
       <c r="G585" t="n">
-        <v>18.7389259338379</v>
+        <v>18.7389240264893</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>19.0958557128906</v>
+        <v>19.0958576202393</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>19.0066223144531</v>
+        <v>19.0066242218018</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>21.5</v>
       </c>
       <c r="G589" t="n">
-        <v>19.1850929260254</v>
+        <v>19.1850891113281</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>19.4527835845947</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>19.4527835845947</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>21.5</v>
       </c>
       <c r="G592" t="n">
-        <v>19.1850929260254</v>
+        <v>19.1850891113281</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>19.2743244171143</v>
+        <v>19.2743225097656</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>19.4527835845947</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>19.7204895019531</v>
+        <v>19.7204875946045</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G598" t="n">
-        <v>19.7204895019531</v>
+        <v>19.7204875946045</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>22</v>
       </c>
       <c r="G599" t="n">
-        <v>19.6312580108643</v>
+        <v>19.631254196167</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>19.7204895019531</v>
+        <v>19.7204875946045</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G608" t="n">
-        <v>19.4527835845947</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>19.2743244171143</v>
+        <v>19.2743225097656</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>19.2743244171143</v>
+        <v>19.2743225097656</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>22</v>
       </c>
       <c r="G611" t="n">
-        <v>19.6312580108643</v>
+        <v>19.631254196167</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G612" t="n">
-        <v>19.7204895019531</v>
+        <v>19.7204875946045</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>22</v>
       </c>
       <c r="G616" t="n">
-        <v>19.6312580108643</v>
+        <v>19.631254196167</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>20.7020511627197</v>
+        <v>20.7020492553711</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>20.7020511627197</v>
+        <v>20.7020492553711</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>21.50514793396</v>
+        <v>21.5051498413086</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G623" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>21.50514793396</v>
+        <v>21.5051498413086</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>24.5</v>
       </c>
       <c r="G627" t="n">
-        <v>21.8620777130127</v>
+        <v>21.8620796203613</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>21.7728443145752</v>
+        <v>21.7728462219238</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G629" t="n">
-        <v>21.9513130187988</v>
+        <v>21.9513092041016</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>24</v>
       </c>
       <c r="G631" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>24</v>
       </c>
       <c r="G637" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>23.5</v>
       </c>
       <c r="G640" t="n">
-        <v>20.9697513580322</v>
+        <v>20.9697494506836</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G645" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>24</v>
       </c>
       <c r="G648" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>24</v>
       </c>
       <c r="G649" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>24</v>
       </c>
       <c r="G650" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G654" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G655" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>20.7020511627197</v>
+        <v>20.7020492553711</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>23.5</v>
       </c>
       <c r="G661" t="n">
-        <v>20.9697513580322</v>
+        <v>20.9697494506836</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>19.7204895019531</v>
+        <v>19.7204875946045</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>22.5</v>
       </c>
       <c r="G664" t="n">
-        <v>20.0774211883545</v>
+        <v>20.0774173736572</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>19.0066223144531</v>
+        <v>19.0066242218018</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>20.5</v>
       </c>
       <c r="G670" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G672" t="n">
-        <v>16.4188671112061</v>
+        <v>16.4188652038574</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>17.4896659851074</v>
+        <v>17.4896640777588</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>16.1957855224609</v>
+        <v>16.1957836151123</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>17.5</v>
       </c>
       <c r="G676" t="n">
-        <v>15.6157693862915</v>
+        <v>15.6157722473145</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>14.9019069671631</v>
+        <v>14.9019088745117</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>15.0357570648193</v>
+        <v>15.035756111145</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>15.7496213912964</v>
+        <v>15.7496223449707</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>16.9988803863525</v>
+        <v>16.9988822937012</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>18.0250625610352</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>19.0066223144531</v>
+        <v>19.0066242218018</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>22</v>
       </c>
       <c r="G685" t="n">
-        <v>19.6312580108643</v>
+        <v>19.631254196167</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>23.5</v>
       </c>
       <c r="G693" t="n">
-        <v>20.9697513580322</v>
+        <v>20.9697494506836</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G696" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>24</v>
       </c>
       <c r="G699" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>24</v>
       </c>
       <c r="G704" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>24</v>
       </c>
       <c r="G706" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>24</v>
       </c>
       <c r="G707" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>22.0405464172363</v>
+        <v>22.0405445098877</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>25</v>
       </c>
       <c r="G711" t="n">
-        <v>22.7315845489502</v>
+        <v>22.7315826416016</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>22.4588069915771</v>
+        <v>22.4588050842285</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>22.5497303009033</v>
+        <v>22.549732208252</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>24</v>
       </c>
       <c r="G733" t="n">
-        <v>21.822322845459</v>
+        <v>21.8223190307617</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>20.5493545532227</v>
+        <v>20.549352645874</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>24</v>
       </c>
       <c r="G751" t="n">
-        <v>21.822322845459</v>
+        <v>21.8223190307617</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>24</v>
       </c>
       <c r="G752" t="n">
-        <v>21.822322845459</v>
+        <v>21.8223190307617</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G761" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>21.0949115753174</v>
+        <v>21.0949096679688</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>21.0949115753174</v>
+        <v>21.0949096679688</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>21.0949115753174</v>
+        <v>21.0949096679688</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>21.0949115753174</v>
+        <v>21.0949096679688</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>20.7312049865723</v>
+        <v>20.7312068939209</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>20.6402797698975</v>
+        <v>20.6402816772461</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>20.6402797698975</v>
+        <v>20.6402816772461</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>20.5493545532227</v>
+        <v>20.549352645874</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G796" t="n">
-        <v>20.6402797698975</v>
+        <v>20.6402816772461</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>20.6402797698975</v>
+        <v>20.6402816772461</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G800" t="n">
-        <v>20.5493545532227</v>
+        <v>20.549352645874</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>23.5499210357666</v>
+        <v>23.5499229431152</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>22.9134368896484</v>
+        <v>22.9134407043457</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>23.0952911376953</v>
+        <v>23.0952892303467</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>25.2775211334229</v>
+        <v>25.2775230407715</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G826" t="n">
-        <v>24.8228912353516</v>
+        <v>24.8228893280029</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>24.8228912353516</v>
+        <v>24.8228893280029</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>24.8228912353516</v>
+        <v>24.8228893280029</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>25.1865940093994</v>
+        <v>25.186595916748</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>26</v>
       </c>
       <c r="G833" t="n">
-        <v>23.6408462524414</v>
+        <v>23.6408500671387</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>25.7321548461914</v>
+        <v>25.7321529388428</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>28.5</v>
       </c>
       <c r="G839" t="n">
-        <v>25.9140071868896</v>
+        <v>25.9140090942383</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>26.1867847442627</v>
+        <v>26.1867828369141</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>28.5</v>
       </c>
       <c r="G848" t="n">
-        <v>25.9140071868896</v>
+        <v>25.9140090942383</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>28.5</v>
       </c>
       <c r="G849" t="n">
-        <v>25.9140071868896</v>
+        <v>25.9140090942383</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>26.1867847442627</v>
+        <v>26.1867828369141</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>28.5</v>
       </c>
       <c r="G856" t="n">
-        <v>25.9140071868896</v>
+        <v>25.9140090942383</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>29.005500793457</v>
+        <v>29.0055027008057</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>29.7329139709473</v>
+        <v>29.7329120635986</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G861" t="n">
-        <v>30.278470993042</v>
+        <v>30.2784690856934</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>29.6419887542725</v>
+        <v>29.6419868469238</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G864" t="n">
-        <v>29.9147644042969</v>
+        <v>29.9147682189941</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G866" t="n">
-        <v>31.7332954406738</v>
+        <v>31.7332916259766</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>31.1877346038818</v>
+        <v>31.1877384185791</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>31.7332954406738</v>
+        <v>31.7332916259766</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>32.0060691833496</v>
+        <v>32.0060653686523</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>34.2792320251465</v>
+        <v>34.2792282104492</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>40</v>
       </c>
       <c r="G873" t="n">
-        <v>36.370532989502</v>
+        <v>36.3705368041992</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G874" t="n">
-        <v>36.0068244934082</v>
+        <v>36.0068283081055</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>35.5522003173828</v>
+        <v>35.5521926879883</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>34.1883010864258</v>
+        <v>34.188304901123</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G877" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157104492188</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G878" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157104492188</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>35.1884918212891</v>
+        <v>35.1884956359863</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G882" t="n">
-        <v>34.1883010864258</v>
+        <v>34.188304901123</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>37.5</v>
       </c>
       <c r="G883" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>34.8247871398926</v>
+        <v>34.8247909545898</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G886" t="n">
-        <v>34.4610862731934</v>
+        <v>34.4610786437988</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>34.1883010864258</v>
+        <v>34.188304901123</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G888" t="n">
-        <v>34.6429328918457</v>
+        <v>34.642936706543</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>34.8247871398926</v>
+        <v>34.8247909545898</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>34.6429328918457</v>
+        <v>34.642936706543</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157104492188</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>37.5</v>
       </c>
       <c r="G893" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>37</v>
       </c>
       <c r="G894" t="n">
-        <v>33.6427459716797</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G895" t="n">
-        <v>34.4610862731934</v>
+        <v>34.4610786437988</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G896" t="n">
-        <v>34.2792320251465</v>
+        <v>34.2792282104492</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G900" t="n">
-        <v>33.0971870422363</v>
+        <v>33.0971908569336</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G901" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244018554688</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>38</v>
       </c>
       <c r="G903" t="n">
-        <v>34.5520133972168</v>
+        <v>34.5520095825195</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G907" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157104492188</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>34.8247871398926</v>
+        <v>34.8247909545898</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>37.5</v>
       </c>
       <c r="G909" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>33.2790412902832</v>
+        <v>33.2790374755859</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>37</v>
       </c>
       <c r="G914" t="n">
-        <v>33.6427459716797</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G915" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244018554688</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>37</v>
       </c>
       <c r="G917" t="n">
-        <v>33.6427459716797</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G920" t="n">
-        <v>33.0062637329102</v>
+        <v>33.0062599182129</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G925" t="n">
-        <v>33.2790412902832</v>
+        <v>33.2790374755859</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>33.0062637329102</v>
+        <v>33.0062599182129</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>32.1879272460938</v>
+        <v>32.1879234313965</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.6425590515137</v>
+        <v>32.6425552368164</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>36</v>
       </c>
       <c r="G929" t="n">
-        <v>32.7334823608398</v>
+        <v>32.7334861755371</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>35.2794151306152</v>
+        <v>35.2794189453125</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.1883010864258</v>
+        <v>34.188304901123</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>37.5</v>
       </c>
       <c r="G936" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G937" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>37.5</v>
       </c>
       <c r="G939" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>37</v>
       </c>
       <c r="G941" t="n">
-        <v>33.6427459716797</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>37.5</v>
       </c>
       <c r="G944" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G945" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>37.5</v>
       </c>
       <c r="G947" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G948" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G951" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244018554688</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244018554688</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G953" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>33.4608917236328</v>
+        <v>33.4608879089355</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G958" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>33.4608917236328</v>
+        <v>33.4608879089355</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>34.3592338562012</v>
+        <v>34.3592300415039</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>34.5444602966309</v>
+        <v>34.5444564819336</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>34.451847076416</v>
+        <v>34.4518508911133</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>34.451847076416</v>
+        <v>34.4518508911133</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G965" t="n">
-        <v>34.5444602966309</v>
+        <v>34.5444564819336</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G968" t="n">
-        <v>33.896167755127</v>
+        <v>33.8961715698242</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>36.5</v>
       </c>
       <c r="G969" t="n">
-        <v>33.8035621643066</v>
+        <v>33.8035583496094</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G970" t="n">
-        <v>33.9887809753418</v>
+        <v>33.9887847900391</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G972" t="n">
-        <v>33.9887809753418</v>
+        <v>33.9887847900391</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>36.5</v>
       </c>
       <c r="G974" t="n">
-        <v>33.8035621643066</v>
+        <v>33.8035583496094</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>36.5</v>
       </c>
       <c r="G975" t="n">
-        <v>33.8035621643066</v>
+        <v>33.8035583496094</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G977" t="n">
-        <v>33.4331092834473</v>
+        <v>33.4331130981445</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>33.6183319091797</v>
+        <v>33.618335723877</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>33.6183319091797</v>
+        <v>33.618335723877</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3404998779297</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>36</v>
       </c>
       <c r="G981" t="n">
-        <v>33.3404998779297</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G982" t="n">
-        <v>33.4331092834473</v>
+        <v>33.4331130981445</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>36.5</v>
       </c>
       <c r="G983" t="n">
-        <v>33.8035621643066</v>
+        <v>33.8035583496094</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.7109489440918</v>
+        <v>33.7109451293945</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>39</v>
       </c>
       <c r="G986" t="n">
-        <v>36.1188735961914</v>
+        <v>36.1188697814941</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G987" t="n">
-        <v>38.6194076538086</v>
+        <v>38.6194114685059</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>46</v>
       </c>
       <c r="G989" t="n">
-        <v>42.6017456054688</v>
+        <v>42.601749420166</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>46.5</v>
       </c>
       <c r="G990" t="n">
-        <v>43.064811706543</v>
+        <v>43.0648078918457</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>42.2312965393066</v>
+        <v>42.2312927246094</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>41.9534606933594</v>
+        <v>41.9534568786621</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>44.3613815307617</v>
+        <v>44.3613891601562</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>45.935791015625</v>
+        <v>45.9357948303223</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>49.5</v>
       </c>
       <c r="G998" t="n">
-        <v>45.843189239502</v>
+        <v>45.8431854248047</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>45.4727363586426</v>
+        <v>45.4727325439453</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>45.1022796630859</v>
+        <v>45.1022834777832</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1001" t="n">
-        <v>46.1210250854492</v>
+        <v>46.121021270752</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>49.5</v>
       </c>
       <c r="G1003" t="n">
-        <v>45.843189239502</v>
+        <v>45.8431854248047</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G1004" t="n">
-        <v>45.1948928833008</v>
+        <v>45.1949005126953</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>46.1210250854492</v>
+        <v>46.121021270752</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>51</v>
       </c>
       <c r="G1006" t="n">
-        <v>47.2323684692383</v>
+        <v>47.2323722839355</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>49</v>
       </c>
       <c r="G1012" t="n">
-        <v>45.3801193237305</v>
+        <v>45.3801231384277</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>46.1210250854492</v>
+        <v>46.121021270752</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G1015" t="n">
-        <v>45.1022796630859</v>
+        <v>45.1022834777832</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1016" t="n">
-        <v>47.6028213500977</v>
+        <v>47.6028251647949</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>49.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>45.843189239502</v>
+        <v>45.8431854248047</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>48.8993988037109</v>
+        <v>48.8993949890137</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G1025" t="n">
-        <v>50.3811988830566</v>
+        <v>50.3811950683594</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>53.5300216674805</v>
+        <v>53.5300178527832</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>62</v>
       </c>
       <c r="G1032" t="n">
-        <v>57.4197463989258</v>
+        <v>57.4197425842285</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>57.0492973327637</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>62</v>
       </c>
       <c r="G1034" t="n">
-        <v>57.4197463989258</v>
+        <v>57.4197425842285</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1038" t="n">
-        <v>57.0492973327637</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>56.8640747070312</v>
+        <v>56.864070892334</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276672363281</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>60.753791809082</v>
+        <v>60.7537956237793</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1047" t="n">
-        <v>62.7912750244141</v>
+        <v>62.7912712097168</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>71</v>
       </c>
       <c r="G1048" t="n">
-        <v>65.7548599243164</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>71</v>
       </c>
       <c r="G1049" t="n">
-        <v>65.7548599243164</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>65.3844223022461</v>
+        <v>65.3844146728516</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>68.5999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>63.532169342041</v>
+        <v>63.5321769714355</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>66</v>
       </c>
       <c r="G1056" t="n">
-        <v>61.1242408752441</v>
+        <v>61.1242446899414</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1061" t="n">
-        <v>62.2355880737305</v>
+        <v>62.2355918884277</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1062" t="n">
-        <v>62.420825958252</v>
+        <v>62.4208221435547</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>61.4946975708008</v>
+        <v>61.494701385498</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5311012268066</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1072" t="n">
-        <v>57.975414276123</v>
+        <v>57.9754180908203</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>62</v>
       </c>
       <c r="G1073" t="n">
-        <v>57.4197463989258</v>
+        <v>57.4197425842285</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1075" t="n">
-        <v>56.8640747070312</v>
+        <v>56.864070892334</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5311012268066</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>62.7912750244141</v>
+        <v>62.7912712097168</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1090" t="n">
-        <v>66.3105392456055</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>72</v>
       </c>
       <c r="G1091" t="n">
-        <v>66.6809997558594</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>71</v>
       </c>
       <c r="G1092" t="n">
-        <v>65.7548599243164</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1093" t="n">
-        <v>66.3105392456055</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1096" t="n">
-        <v>66.3105392456055</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G1097" t="n">
-        <v>65.9400939941406</v>
+        <v>65.9400863647461</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1100" t="n">
-        <v>65.3844223022461</v>
+        <v>65.3844146728516</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1101" t="n">
-        <v>65.3844223022461</v>
+        <v>65.3844146728516</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1102" t="n">
-        <v>65.3844223022461</v>
+        <v>65.3844146728516</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1105" t="n">
-        <v>67.7923355102539</v>
+        <v>67.7923431396484</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>74.4000015258789</v>
       </c>
       <c r="G1106" t="n">
-        <v>68.903694152832</v>
+        <v>68.9037017822266</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>74</v>
       </c>
       <c r="G1107" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1108" t="n">
-        <v>70.2002792358398</v>
+        <v>70.2002716064453</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>74</v>
       </c>
       <c r="G1109" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>71</v>
       </c>
       <c r="G1111" t="n">
-        <v>65.7548599243164</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>74</v>
       </c>
       <c r="G1113" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1114" t="n">
-        <v>67.4218978881836</v>
+        <v>67.4218902587891</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>74.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>68.903694152832</v>
+        <v>68.9037017822266</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>69.0889205932617</v>
+        <v>69.0889129638672</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1118" t="n">
-        <v>67.7923355102539</v>
+        <v>67.7923431396484</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>73</v>
       </c>
       <c r="G1119" t="n">
-        <v>67.6071243286133</v>
+        <v>67.6071166992188</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>73.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>67.9775619506836</v>
+        <v>67.9775695800781</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>73</v>
       </c>
       <c r="G1121" t="n">
-        <v>67.6071243286133</v>
+        <v>67.6071166992188</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G1122" t="n">
-        <v>66.8662185668945</v>
+        <v>66.8662261962891</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>72</v>
       </c>
       <c r="G1123" t="n">
-        <v>66.6809997558594</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1124" t="n">
-        <v>66.3105392456055</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>74</v>
       </c>
       <c r="G1125" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1127" t="n">
-        <v>67.4218978881836</v>
+        <v>67.4218902587891</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>73.4000015258789</v>
       </c>
       <c r="G1128" t="n">
-        <v>67.9775619506836</v>
+        <v>67.9775695800781</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>73</v>
       </c>
       <c r="G1130" t="n">
-        <v>67.6071243286133</v>
+        <v>67.6071166992188</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1131" t="n">
-        <v>69.0889205932617</v>
+        <v>69.0889129638672</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1134" t="n">
-        <v>70.2002792358398</v>
+        <v>70.2002716064453</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>79</v>
       </c>
       <c r="G1135" t="n">
-        <v>73.1638641357422</v>
+        <v>73.1638717651367</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>71.8672866821289</v>
+        <v>71.8672943115234</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>78</v>
       </c>
       <c r="G1137" t="n">
-        <v>72.2377471923828</v>
+        <v>72.2377395629883</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>74</v>
       </c>
       <c r="G1139" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1140" t="n">
-        <v>67.4218978881836</v>
+        <v>67.4218902587891</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G1141" t="n">
-        <v>66.8662185668945</v>
+        <v>66.8662261962891</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1142" t="n">
-        <v>66.3105392456055</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1147" t="n">
-        <v>62.420825958252</v>
+        <v>62.4208221435547</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1148" t="n">
-        <v>60.753791809082</v>
+        <v>60.7537956237793</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>66</v>
       </c>
       <c r="G1150" t="n">
-        <v>61.1242408752441</v>
+        <v>61.1242446899414</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>66</v>
       </c>
       <c r="G1153" t="n">
-        <v>61.1242408752441</v>
+        <v>61.1242446899414</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1154" t="n">
-        <v>60.753791809082</v>
+        <v>60.7537956237793</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>66</v>
       </c>
       <c r="G1156" t="n">
-        <v>61.1242408752441</v>
+        <v>61.1242446899414</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1159" t="n">
-        <v>58.7163162231445</v>
+        <v>58.7163238525391</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276672363281</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1162" t="n">
-        <v>59.4572143554688</v>
+        <v>59.457218170166</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>57.975414276123</v>
+        <v>57.9754180908203</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5311012268066</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1166" t="n">
-        <v>57.975414276123</v>
+        <v>57.9754180908203</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>57.0492973327637</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1174" t="n">
-        <v>57.0492973327637</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>53.5300216674805</v>
+        <v>53.5300178527832</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1179" t="n">
-        <v>51.307315826416</v>
+        <v>51.3073196411133</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>57.0492973327637</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1192" t="n">
-        <v>59.4572143554688</v>
+        <v>59.457218170166</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1193" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276672363281</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1194" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276672363281</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1198" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5311012268066</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>61.4946975708008</v>
+        <v>61.494701385498</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>65.6999969482422</v>
       </c>
       <c r="G1204" t="n">
-        <v>60.8464012145996</v>
+        <v>60.8464050292969</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>65.6999969482422</v>
       </c>
       <c r="G1205" t="n">
-        <v>60.8464012145996</v>
+        <v>60.8464050292969</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1211" t="n">
-        <v>59.9202766418457</v>
+        <v>59.9202728271484</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>58.6237106323242</v>
+        <v>58.623706817627</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1216" t="n">
-        <v>60.6766929626465</v>
+        <v>60.6766967773438</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>56.3694000244141</v>
+        <v>56.3693962097168</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>54.4966583251953</v>
+        <v>54.4966621398926</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1220" t="n">
-        <v>51.5939140319824</v>
+        <v>51.5939178466797</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>56.5</v>
       </c>
       <c r="G1221" t="n">
-        <v>52.9048309326172</v>
+        <v>52.9048271179199</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1233" t="n">
-        <v>59.3657760620117</v>
+        <v>59.3657722473145</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G1235" t="n">
-        <v>57.9612236022949</v>
+        <v>57.9612274169922</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G1237" t="n">
-        <v>61.893970489502</v>
+        <v>61.8939666748047</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>60.3021469116211</v>
+        <v>60.3021430969238</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>62</v>
       </c>
       <c r="G1248" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>56.3694000244141</v>
+        <v>56.3693962097168</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>59</v>
       </c>
       <c r="G1250" t="n">
-        <v>55.2457542419434</v>
+        <v>55.2457504272461</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>57.3057670593262</v>
+        <v>57.3057632446289</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1257" t="n">
-        <v>56.9312133789062</v>
+        <v>56.9312171936035</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>60.2999992370605</v>
       </c>
       <c r="G1259" t="n">
-        <v>56.4630279541016</v>
+        <v>56.4630317687988</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1264" t="n">
-        <v>60.6766929626465</v>
+        <v>60.6766967773438</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1266" t="n">
-        <v>61.6130599975586</v>
+        <v>61.6130638122559</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1268" t="n">
-        <v>60.7703247070312</v>
+        <v>60.7703285217285</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1272" t="n">
-        <v>60.3021469116211</v>
+        <v>60.3021430969238</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>59.7403221130371</v>
+        <v>59.7403259277344</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1278" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>68</v>
       </c>
       <c r="G1283" t="n">
-        <v>63.6730613708496</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>68</v>
       </c>
       <c r="G1286" t="n">
-        <v>63.6730613708496</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1294" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>70</v>
       </c>
       <c r="G1304" t="n">
-        <v>65.5458068847656</v>
+        <v>65.5458145141602</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1309" t="n">
-        <v>65.3585357666016</v>
+        <v>65.358528137207</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>71.0999984741211</v>
       </c>
       <c r="G1310" t="n">
-        <v>66.5758056640625</v>
+        <v>66.575813293457</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>70.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>66.0139999389648</v>
+        <v>66.0139923095703</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1312" t="n">
-        <v>66.2949066162109</v>
+        <v>66.2949142456055</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>70</v>
       </c>
       <c r="G1313" t="n">
-        <v>65.5458068847656</v>
+        <v>65.5458145141602</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>70.3000030517578</v>
       </c>
       <c r="G1315" t="n">
-        <v>65.8267211914062</v>
+        <v>65.8267135620117</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>68</v>
       </c>
       <c r="G1316" t="n">
-        <v>63.6730613708496</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>66.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>62.2685127258301</v>
+        <v>62.2685165405273</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1319" t="n">
-        <v>59.7403221130371</v>
+        <v>59.7403259277344</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>66.3000030517578</v>
       </c>
       <c r="G1324" t="n">
-        <v>62.0812492370605</v>
+        <v>62.0812454223633</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1328" t="n">
-        <v>60.7703247070312</v>
+        <v>60.7703285217285</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1330" t="n">
-        <v>60.7703247070312</v>
+        <v>60.7703285217285</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1331" t="n">
-        <v>60.3021469116211</v>
+        <v>60.3021430969238</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G1335" t="n">
-        <v>60.9576034545898</v>
+        <v>60.9575996398926</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G1338" t="n">
-        <v>60.9576034545898</v>
+        <v>60.9575996398926</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1341" t="n">
-        <v>61.9876022338867</v>
+        <v>61.987606048584</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1342" t="n">
-        <v>61.9876022338867</v>
+        <v>61.987606048584</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1343" t="n">
-        <v>61.9876022338867</v>
+        <v>61.987606048584</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>68</v>
       </c>
       <c r="G1344" t="n">
-        <v>63.6730613708496</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1345" t="n">
-        <v>63.4858055114746</v>
+        <v>63.4857978820801</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>66.5</v>
       </c>
       <c r="G1349" t="n">
-        <v>62.2685127258301</v>
+        <v>62.2685165405273</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1350" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1355" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1359" t="n">
-        <v>60.6766929626465</v>
+        <v>60.6766967773438</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1360" t="n">
-        <v>60.5830535888672</v>
+        <v>60.5830497741699</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>60.3021469116211</v>
+        <v>60.3021430969238</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G1365" t="n">
-        <v>57.9612236022949</v>
+        <v>57.9612274169922</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>58.4294090270996</v>
+        <v>58.4294052124023</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>62</v>
       </c>
       <c r="G1369" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>57.6803092956543</v>
+        <v>57.6803131103516</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1375" t="n">
-        <v>58.6166763305664</v>
+        <v>58.6166801452637</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G1378" t="n">
-        <v>59.0848655700684</v>
+        <v>59.0848617553711</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>62</v>
       </c>
       <c r="G1379" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1387" t="n">
-        <v>58.6166763305664</v>
+        <v>58.6166801452637</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1395" t="n">
-        <v>59.3657760620117</v>
+        <v>59.3657722473145</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>62</v>
       </c>
       <c r="G1401" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>57.3057670593262</v>
+        <v>57.3057632446289</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1409" t="n">
-        <v>56.9312133789062</v>
+        <v>56.9312171936035</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>59</v>
       </c>
       <c r="G1411" t="n">
-        <v>55.2457542419434</v>
+        <v>55.2457504272461</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1415" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>62</v>
       </c>
       <c r="G1418" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>60.2999992370605</v>
       </c>
       <c r="G1421" t="n">
-        <v>56.4630279541016</v>
+        <v>56.4630317687988</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>56.3694000244141</v>
+        <v>56.3693962097168</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>62</v>
       </c>
       <c r="G1424" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G1425" t="n">
-        <v>57.9612236022949</v>
+        <v>57.9612274169922</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>62</v>
       </c>
       <c r="G1426" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1431" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1432" t="n">
-        <v>56.9312133789062</v>
+        <v>56.9312171936035</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1438" t="n">
-        <v>53.4666481018066</v>
+        <v>53.4666519165039</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>56</v>
       </c>
       <c r="G1439" t="n">
-        <v>52.4366455078125</v>
+        <v>52.4366416931152</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>52.7175598144531</v>
+        <v>52.7175559997559</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>56</v>
       </c>
       <c r="G1441" t="n">
-        <v>52.4366455078125</v>
+        <v>52.4366416931152</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>56.2000007629395</v>
       </c>
       <c r="G1443" t="n">
-        <v>52.6239204406738</v>
+        <v>52.6239242553711</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>53.0921020507812</v>
+        <v>53.0921058654785</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>53.4666481018066</v>
+        <v>53.4666519165039</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G1447" t="n">
-        <v>52.9984703063965</v>
+        <v>52.9984664916992</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>56</v>
       </c>
       <c r="G1448" t="n">
-        <v>52.4366455078125</v>
+        <v>52.4366416931152</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G1449" t="n">
-        <v>52.5302810668945</v>
+        <v>52.5302848815918</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1450" t="n">
-        <v>52.3430099487305</v>
+        <v>52.3430137634277</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>56</v>
       </c>
       <c r="G1451" t="n">
-        <v>52.4366455078125</v>
+        <v>52.4366416931152</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>52.1557388305664</v>
+        <v>52.1557350158691</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1457" t="n">
-        <v>51.5939140319824</v>
+        <v>51.5939178466797</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>50.8448181152344</v>
+        <v>50.8448143005371</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>51.2193717956543</v>
+        <v>51.219367980957</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1466" t="n">
-        <v>50.0020942687988</v>
+        <v>50.0020904541016</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G1467" t="n">
-        <v>50.1893615722656</v>
+        <v>50.1893577575684</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>47.1929817199707</v>
+        <v>47.192985534668</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1479" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>54.4939079284668</v>
+        <v>54.4939117431641</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G1483" t="n">
-        <v>54.3988037109375</v>
+        <v>54.3988075256348</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1490" t="n">
-        <v>55.8253479003906</v>
+        <v>55.8253440856934</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1491" t="n">
-        <v>56.205753326416</v>
+        <v>56.2057571411133</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>55.8253479003906</v>
+        <v>55.8253440856934</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1495" t="n">
-        <v>56.205753326416</v>
+        <v>56.2057571411133</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1501" t="n">
-        <v>57.4420967102051</v>
+        <v>57.4420928955078</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1505" t="n">
-        <v>58.583324432373</v>
+        <v>58.5833282470703</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1511" t="n">
-        <v>57.4420967102051</v>
+        <v>57.4420928955078</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>59.5</v>
       </c>
       <c r="G1512" t="n">
-        <v>56.5861701965332</v>
+        <v>56.5861663818359</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>59.5</v>
       </c>
       <c r="G1513" t="n">
-        <v>56.5861701965332</v>
+        <v>56.5861663818359</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1519" t="n">
-        <v>56.205753326416</v>
+        <v>56.2057571411133</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1520" t="n">
-        <v>55.8253479003906</v>
+        <v>55.8253440856934</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1521" t="n">
-        <v>56.6812744140625</v>
+        <v>56.6812705993652</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>58.5</v>
       </c>
       <c r="G1524" t="n">
-        <v>55.6351432800293</v>
+        <v>55.635139465332</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>58.5</v>
       </c>
       <c r="G1527" t="n">
-        <v>55.6351432800293</v>
+        <v>55.635139465332</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>58.5</v>
       </c>
       <c r="G1528" t="n">
-        <v>55.6351432800293</v>
+        <v>55.635139465332</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1533" t="n">
-        <v>54.7792167663574</v>
+        <v>54.7792129516602</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>57.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>54.6841125488281</v>
+        <v>54.6841163635254</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1537" t="n">
-        <v>54.3037033081055</v>
+        <v>54.3036994934082</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1539" t="n">
-        <v>53.6379814147949</v>
+        <v>53.6379852294922</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1544" t="n">
-        <v>53.162467956543</v>
+        <v>53.1624717712402</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1546" t="n">
-        <v>53.6379814147949</v>
+        <v>53.6379852294922</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1547" t="n">
-        <v>53.5428810119629</v>
+        <v>53.5428771972656</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1548" t="n">
-        <v>52.8771591186523</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G1551" t="n">
-        <v>51.9261322021484</v>
+        <v>51.9261283874512</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1555" t="n">
-        <v>52.8771591186523</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>55</v>
       </c>
       <c r="G1558" t="n">
-        <v>52.3065414428711</v>
+        <v>52.3065452575684</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G1559" t="n">
-        <v>51.9261322021484</v>
+        <v>51.9261283874512</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>55</v>
       </c>
       <c r="G1565" t="n">
-        <v>52.3065414428711</v>
+        <v>52.3065452575684</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1567" t="n">
-        <v>50.7848968505859</v>
+        <v>50.7849006652832</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1568" t="n">
-        <v>50.7848968505859</v>
+        <v>50.7849006652832</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>53</v>
       </c>
       <c r="G1571" t="n">
-        <v>50.4044876098633</v>
+        <v>50.404483795166</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>49.643669128418</v>
+        <v>49.6436653137207</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1575" t="n">
-        <v>48.4073257446289</v>
+        <v>48.4073295593262</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>49</v>
       </c>
       <c r="G1579" t="n">
-        <v>46.6003723144531</v>
+        <v>46.6003761291504</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>48</v>
       </c>
       <c r="G1588" t="n">
-        <v>45.6493492126465</v>
+        <v>45.6493453979492</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>48.9500007629395</v>
       </c>
       <c r="G1590" t="n">
-        <v>46.5528221130371</v>
+        <v>46.5528259277344</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1591" t="n">
-        <v>48.7877388000488</v>
+        <v>48.7877349853516</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>49.2999992370605</v>
       </c>
       <c r="G1596" t="n">
-        <v>46.8856811523438</v>
+        <v>46.885684967041</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>49</v>
       </c>
       <c r="G1597" t="n">
-        <v>46.6003723144531</v>
+        <v>46.6003761291504</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G1600" t="n">
-        <v>46.1724128723145</v>
+        <v>46.1724090576172</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>48.25</v>
       </c>
       <c r="G1601" t="n">
-        <v>45.8871040344238</v>
+        <v>45.8871078491211</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1603" t="n">
-        <v>48.7877388000488</v>
+        <v>48.7877349853516</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>48.9000015258789</v>
       </c>
       <c r="G1607" t="n">
-        <v>46.5052757263184</v>
+        <v>46.5052719116211</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>46.9807891845703</v>
+        <v>46.980785369873</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G1609" t="n">
-        <v>47.4087448120117</v>
+        <v>47.408748626709</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G1620" t="n">
-        <v>47.4563026428223</v>
+        <v>47.4563064575195</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>51.5</v>
       </c>
       <c r="G1621" t="n">
-        <v>48.9779434204102</v>
+        <v>48.9779472351074</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>51.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>48.9779434204102</v>
+        <v>48.9779472351074</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1627" t="n">
-        <v>52.8771591186523</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1629" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1631" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1632" t="n">
-        <v>52.8771591186523</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1633" t="n">
-        <v>54.4939079284668</v>
+        <v>54.4939117431641</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>56</v>
       </c>
       <c r="G1636" t="n">
-        <v>53.2575759887695</v>
+        <v>53.2575721740723</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1639" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1642" t="n">
-        <v>53.6379814147949</v>
+        <v>53.6379852294922</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1644" t="n">
-        <v>53.5428810119629</v>
+        <v>53.5428771972656</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>56</v>
       </c>
       <c r="G1646" t="n">
-        <v>53.2575759887695</v>
+        <v>53.2575721740723</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1647" t="n">
-        <v>53.162467956543</v>
+        <v>53.1624717712402</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1650" t="n">
-        <v>53.6379814147949</v>
+        <v>53.6379852294922</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>56.7763748168945</v>
+        <v>56.7763786315918</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1653" t="n">
-        <v>56.205753326416</v>
+        <v>56.2057571411133</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1655" t="n">
-        <v>54.7792167663574</v>
+        <v>54.7792129516602</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>59.5</v>
       </c>
       <c r="G1656" t="n">
-        <v>56.5861701965332</v>
+        <v>56.5861663818359</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>60.5</v>
       </c>
       <c r="G1658" t="n">
-        <v>57.5371971130371</v>
+        <v>57.5372009277344</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1660" t="n">
-        <v>57.1567878723145</v>
+        <v>57.1567840576172</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1662" t="n">
-        <v>58.583324432373</v>
+        <v>58.5833282470703</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>62</v>
       </c>
       <c r="G1663" t="n">
-        <v>58.9637413024902</v>
+        <v>58.963737487793</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>59.1539459228516</v>
+        <v>59.1539497375488</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>62</v>
       </c>
       <c r="G1666" t="n">
-        <v>58.9637413024902</v>
+        <v>58.963737487793</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1667" t="n">
-        <v>57.4420967102051</v>
+        <v>57.4420928955078</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1668" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1669" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1670" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>60.5</v>
       </c>
       <c r="G1671" t="n">
-        <v>57.5371971130371</v>
+        <v>57.5372009277344</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1673" t="n">
-        <v>59.7245635986328</v>
+        <v>59.7245597839355</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1675" t="n">
-        <v>59.5343589782715</v>
+        <v>59.5343551635742</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1677" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1678" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1679" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1682" t="n">
-        <v>58.583324432373</v>
+        <v>58.5833282470703</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>60.5</v>
       </c>
       <c r="G1683" t="n">
-        <v>57.5371971130371</v>
+        <v>57.5372009277344</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1684" t="n">
-        <v>56.7763748168945</v>
+        <v>56.7763786315918</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1685" t="n">
-        <v>56.6812744140625</v>
+        <v>56.6812705993652</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1694" t="n">
-        <v>56.7763748168945</v>
+        <v>56.7763786315918</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1700" t="n">
-        <v>54.4939079284668</v>
+        <v>54.4939117431641</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1703" t="n">
-        <v>54.7792167663574</v>
+        <v>54.7792129516602</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1706" t="n">
-        <v>53.6379814147949</v>
+        <v>53.6379852294922</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>56</v>
       </c>
       <c r="G1708" t="n">
-        <v>53.2575759887695</v>
+        <v>53.2575721740723</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>54.7999992370605</v>
       </c>
       <c r="G1711" t="n">
-        <v>52.1163368225098</v>
+        <v>52.116340637207</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>55</v>
       </c>
       <c r="G1714" t="n">
-        <v>52.3065414428711</v>
+        <v>52.3065452575684</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1715" t="n">
-        <v>50.7848968505859</v>
+        <v>50.7849006652832</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1716" t="n">
-        <v>51.1653099060059</v>
+        <v>51.1653060913086</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1717" t="n">
-        <v>51.1653099060059</v>
+        <v>51.1653060913086</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>53</v>
       </c>
       <c r="G1718" t="n">
-        <v>50.4044876098633</v>
+        <v>50.404483795166</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1719" t="n">
-        <v>49.2632522583008</v>
+        <v>49.263256072998</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1722" t="n">
-        <v>50.4995880126953</v>
+        <v>50.4995918273926</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>54</v>
       </c>
       <c r="G1725" t="n">
-        <v>51.3555145263672</v>
+        <v>51.3555183410645</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1726" t="n">
-        <v>50.7848968505859</v>
+        <v>50.7849006652832</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1727" t="n">
-        <v>49.3583602905273</v>
+        <v>49.3583564758301</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -61134,6 +61134,32 @@
         <v>72</v>
       </c>
       <c r="H2337" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2338" t="n">
+        <v>23519</v>
+      </c>
+      <c r="C2338" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D2338" t="n">
+        <v>70.1999969482422</v>
+      </c>
+      <c r="E2338" t="n">
+        <v>70.1999969482422</v>
+      </c>
+      <c r="F2338" t="n">
+        <v>73.0999984741211</v>
+      </c>
+      <c r="G2338" t="n">
+        <v>73.0999984741211</v>
+      </c>
+      <c r="H2338" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -54208,8 +54208,31 @@
       <c r="E2341" t="n">
         <v>70.1999969482422</v>
       </c>
-      <c r="F2341"/>
+      <c r="F2341" t="n">
+        <v>71.4000015258789</v>
+      </c>
       <c r="G2341" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2342" t="n">
+        <v>17028</v>
+      </c>
+      <c r="C2342" t="n">
+        <v>73.0999984741211</v>
+      </c>
+      <c r="D2342" t="n">
+        <v>71.6999969482422</v>
+      </c>
+      <c r="E2342" t="n">
+        <v>71.9000015258789</v>
+      </c>
+      <c r="F2342"/>
+      <c r="G2342" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -54231,8 +54231,31 @@
       <c r="E2342" t="n">
         <v>71.9000015258789</v>
       </c>
-      <c r="F2342"/>
+      <c r="F2342" t="n">
+        <v>72.5</v>
+      </c>
       <c r="G2342" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2343" t="n">
+        <v>8711</v>
+      </c>
+      <c r="C2343" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="D2343" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E2343" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F2343"/>
+      <c r="G2343" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -54254,8 +54254,31 @@
       <c r="E2343" t="n">
         <v>72.5</v>
       </c>
-      <c r="F2343"/>
+      <c r="F2343" t="n">
+        <v>72.8000030517578</v>
+      </c>
       <c r="G2343" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2344" t="n">
+        <v>10617</v>
+      </c>
+      <c r="C2344" t="n">
+        <v>73.0999984741211</v>
+      </c>
+      <c r="D2344" t="n">
+        <v>70.4000015258789</v>
+      </c>
+      <c r="E2344" t="n">
+        <v>73.0999984741211</v>
+      </c>
+      <c r="F2344"/>
+      <c r="G2344" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -54277,8 +54277,31 @@
       <c r="E2344" t="n">
         <v>73.0999984741211</v>
       </c>
-      <c r="F2344"/>
+      <c r="F2344" t="n">
+        <v>70.4000015258789</v>
+      </c>
       <c r="G2344" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2345" t="n">
+        <v>7397</v>
+      </c>
+      <c r="C2345" t="n">
+        <v>72</v>
+      </c>
+      <c r="D2345" t="n">
+        <v>70.3000030517578</v>
+      </c>
+      <c r="E2345" t="n">
+        <v>70.3000030517578</v>
+      </c>
+      <c r="F2345"/>
+      <c r="G2345" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -54307,6 +54307,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2346">
+      <c r="A2346" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2346" t="n">
+        <v>10134</v>
+      </c>
+      <c r="C2346" t="n">
+        <v>72</v>
+      </c>
+      <c r="D2346" t="n">
+        <v>70.1999969482422</v>
+      </c>
+      <c r="E2346" t="n">
+        <v>70.1999969482422</v>
+      </c>
+      <c r="F2346" t="n">
+        <v>70.8000030517578</v>
+      </c>
+      <c r="G2346" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -421,7 +421,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>11.8307580947876</v>
+        <v>11.8307571411133</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>11.712366104126</v>
+        <v>11.7123670578003</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G4" t="n">
-        <v>11.1795997619629</v>
+        <v>11.1796016693115</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G5" t="n">
-        <v>11.027382850647</v>
+        <v>11.0273818969727</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G6" t="n">
-        <v>10.8920774459839</v>
+        <v>10.8920764923096</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>10.9005346298218</v>
+        <v>10.9005327224731</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1457757949829</v>
+        <v>11.1457748413086</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1711444854736</v>
+        <v>11.1711454391479</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>11.2726240158081</v>
+        <v>11.2726230621338</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G12" t="n">
-        <v>11.1880569458008</v>
+        <v>11.1880578994751</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G14" t="n">
-        <v>11.027382850647</v>
+        <v>11.0273818969727</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G15" t="n">
-        <v>11.0781221389771</v>
+        <v>11.0781230926514</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G17" t="n">
-        <v>11.2726240158081</v>
+        <v>11.2726230621338</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G18" t="n">
-        <v>11.1034898757935</v>
+        <v>11.1034917831421</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>11.0358400344849</v>
+        <v>11.0358390808105</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>11.2895383834839</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G25" t="n">
-        <v>11.1034898757935</v>
+        <v>11.1034917831421</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>11.0781221389771</v>
+        <v>11.0781230926514</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G35" t="n">
-        <v>10.6468372344971</v>
+        <v>10.6468362808228</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0696649551392</v>
+        <v>11.0696668624878</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>10.942816734314</v>
+        <v>10.9428157806396</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G38" t="n">
-        <v>10.9343614578247</v>
+        <v>10.9343605041504</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0781221389771</v>
+        <v>11.0781230926514</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G45" t="n">
-        <v>11.8223009109497</v>
+        <v>11.822301864624</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.6447143554688</v>
+        <v>11.6447134017944</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6447143554688</v>
+        <v>11.6447134017944</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>11.5855159759521</v>
+        <v>11.5855169296265</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.5</v>
       </c>
       <c r="G53" t="n">
-        <v>11.4163846969604</v>
+        <v>11.4163856506348</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>11.2895383834839</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>11.3318195343018</v>
+        <v>11.3318185806274</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>11.281081199646</v>
+        <v>11.2810802459717</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G58" t="n">
-        <v>11.1288614273071</v>
+        <v>11.1288604736328</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>13</v>
       </c>
       <c r="G59" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G60" t="n">
-        <v>11.1457757949829</v>
+        <v>11.1457748413086</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G62" t="n">
-        <v>11.1457757949829</v>
+        <v>11.1457748413086</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G63" t="n">
-        <v>11.0527515411377</v>
+        <v>11.052752494812</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G64" t="n">
-        <v>11.1542301177979</v>
+        <v>11.1542320251465</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>10.942816734314</v>
+        <v>10.9428157806396</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>11.0020141601562</v>
+        <v>11.0020132064819</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>10.9005346298218</v>
+        <v>10.9005327224731</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5538129806519</v>
+        <v>10.5538139343262</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.5</v>
       </c>
       <c r="G86" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G88" t="n">
-        <v>10.6637506484985</v>
+        <v>10.6637477874756</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>13</v>
       </c>
       <c r="G89" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>13</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.6383800506592</v>
+        <v>10.6383790969849</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G94" t="n">
-        <v>10.6383800506592</v>
+        <v>10.6383790969849</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G100" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G104" t="n">
-        <v>10.7144899368286</v>
+        <v>10.71448802948</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G106" t="n">
-        <v>10.8497934341431</v>
+        <v>10.8497953414917</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>10.7990550994873</v>
+        <v>10.799054145813</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.5</v>
       </c>
       <c r="G120" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.5</v>
       </c>
       <c r="G126" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>10.4438781738281</v>
+        <v>10.4438791275024</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>10.4015951156616</v>
+        <v>10.4015941619873</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>12.25</v>
       </c>
       <c r="G139" t="n">
-        <v>10.3593139648438</v>
+        <v>10.3593130111694</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>10.4438781738281</v>
+        <v>10.4438791275024</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>10.1901817321777</v>
+        <v>10.1901807785034</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>13</v>
       </c>
       <c r="G153" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089908599854</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G163" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G165" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.5</v>
       </c>
       <c r="G167" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.5</v>
       </c>
       <c r="G169" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>13</v>
       </c>
       <c r="G174" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>13</v>
       </c>
       <c r="G181" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>13</v>
       </c>
       <c r="G182" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>13</v>
       </c>
       <c r="G183" t="n">
-        <v>10.9935569763184</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>11.2895383834839</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>11.3318195343018</v>
+        <v>11.3318185806274</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>11.2895383834839</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2472524642944</v>
+        <v>11.2472534179688</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>11.0358400344849</v>
+        <v>11.0358390808105</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2895383834839</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>11.3318195343018</v>
+        <v>11.3318185806274</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2472524642944</v>
+        <v>11.2472534179688</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>11.3318195343018</v>
+        <v>11.3318185806274</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.3318195343018</v>
+        <v>11.3318185806274</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>11.5855159759521</v>
+        <v>11.5855169296265</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>13.5</v>
       </c>
       <c r="G200" t="n">
-        <v>11.4163846969604</v>
+        <v>11.4163856506348</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.54323387146</v>
+        <v>11.5432329177856</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>11.54323387146</v>
+        <v>11.5432329177856</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7869577407837</v>
+        <v>11.7869596481323</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>11.4402828216553</v>
+        <v>11.440281867981</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>11.613618850708</v>
+        <v>11.6136198043823</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>11.4402828216553</v>
+        <v>11.440281867981</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>11.6569547653198</v>
+        <v>11.6569528579712</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G217" t="n">
-        <v>11.8736276626587</v>
+        <v>11.8736257553101</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>11.5269527435303</v>
+        <v>11.5269508361816</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.6569547653198</v>
+        <v>11.6569528579712</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>11.8302927017212</v>
+        <v>11.8302907943726</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>11.8302927017212</v>
+        <v>11.8302907943726</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>11.8736276626587</v>
+        <v>11.8736257553101</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>12.0902976989746</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G231" t="n">
-        <v>11.8302927017212</v>
+        <v>11.8302907943726</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>11.7869577407837</v>
+        <v>11.7869596481323</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.0902976989746</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>12.0902976989746</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>14.5</v>
       </c>
       <c r="G242" t="n">
-        <v>12.5669765472412</v>
+        <v>12.5669775009155</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>12.4803075790405</v>
+        <v>12.4803085327148</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>14.5</v>
       </c>
       <c r="G244" t="n">
-        <v>12.5669765472412</v>
+        <v>12.5669775009155</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G247" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>15</v>
       </c>
       <c r="G248" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>13.0436563491821</v>
+        <v>13.0436553955078</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G256" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>12.9569873809814</v>
+        <v>12.9569864273071</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>12.8269853591919</v>
+        <v>12.8269844055176</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="G261" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>15.25</v>
       </c>
       <c r="G265" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G266" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>15</v>
       </c>
       <c r="G268" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>15.25</v>
       </c>
       <c r="G284" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>15.25</v>
       </c>
       <c r="G285" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>15.25</v>
       </c>
       <c r="G288" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>15.25</v>
       </c>
       <c r="G290" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>15.5</v>
       </c>
       <c r="G297" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>15.25</v>
       </c>
       <c r="G303" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G315" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070032119751</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>13.7803401947021</v>
+        <v>13.7803411483765</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070032119751</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G322" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070032119751</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>15.25</v>
       </c>
       <c r="G325" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>15</v>
       </c>
       <c r="G328" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>15</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>15.5</v>
       </c>
       <c r="G330" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>15.5</v>
       </c>
       <c r="G331" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>15.5</v>
       </c>
       <c r="G334" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>15.5</v>
       </c>
       <c r="G351" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G353" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070032119751</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G355" t="n">
-        <v>13.3903293609619</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G356" t="n">
-        <v>13.3903293609619</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070032119751</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>15.5</v>
       </c>
       <c r="G359" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G360" t="n">
-        <v>13.3903293609619</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G365" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070032119751</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869913101196</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>15.5</v>
       </c>
       <c r="G371" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>15.5</v>
       </c>
       <c r="G372" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>13.1736602783203</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>15.5</v>
       </c>
       <c r="G375" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>13.3903293609619</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>15.5</v>
       </c>
       <c r="G382" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>13.3903293609619</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>13.4770011901855</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1270160675049</v>
+        <v>14.1270151138306</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>14.2136831283569</v>
+        <v>14.2136850357056</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>17.25</v>
       </c>
       <c r="G392" t="n">
-        <v>14.9503698348999</v>
+        <v>14.9503688812256</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>14.9070348739624</v>
+        <v>14.907036781311</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>17</v>
       </c>
       <c r="G395" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>16.75</v>
       </c>
       <c r="G397" t="n">
-        <v>14.5170278549194</v>
+        <v>14.5170249938965</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>14.560359954834</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>17</v>
       </c>
       <c r="G400" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>14.6036930084229</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>14.3870220184326</v>
+        <v>14.3870229721069</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G403" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>14.560359954834</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>14.560359954834</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>17</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>17</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G414" t="n">
-        <v>14.7770328521729</v>
+        <v>14.7770299911499</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6036930084229</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>16.75</v>
       </c>
       <c r="G417" t="n">
-        <v>14.5170278549194</v>
+        <v>14.5170249938965</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>16.5</v>
       </c>
       <c r="G420" t="n">
-        <v>14.3003540039062</v>
+        <v>14.3003549575806</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>14.4303550720215</v>
+        <v>14.4303569793701</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.5</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3003540039062</v>
+        <v>14.3003549575806</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>14.3870220184326</v>
+        <v>14.3870229721069</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>14.6036930084229</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>14.3870220184326</v>
+        <v>14.3870229721069</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>17</v>
       </c>
       <c r="G430" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>17</v>
       </c>
       <c r="G432" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>14.6036930084229</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>17</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G443" t="n">
-        <v>14.9070348739624</v>
+        <v>14.907036781311</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G444" t="n">
-        <v>14.6036930084229</v>
+        <v>14.6036939620972</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>14.9937019348145</v>
+        <v>14.9937047958374</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G446" t="n">
-        <v>14.9070348739624</v>
+        <v>14.907036781311</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G448" t="n">
-        <v>14.7770328521729</v>
+        <v>14.7770299911499</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>15.0370388031006</v>
+        <v>15.0370378494263</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>15.0803737640381</v>
+        <v>15.0803728103638</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>15.0803737640381</v>
+        <v>15.0803728103638</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>14.9937019348145</v>
+        <v>14.9937047958374</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>15.0803737640381</v>
+        <v>15.0803728103638</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>15.5265378952026</v>
+        <v>15.5265369415283</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>15.5265378952026</v>
+        <v>15.5265369415283</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>17.25</v>
       </c>
       <c r="G456" t="n">
-        <v>15.3926887512207</v>
+        <v>15.3926868438721</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>15.5265378952026</v>
+        <v>15.5265369415283</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>17.25</v>
       </c>
       <c r="G458" t="n">
-        <v>15.3926887512207</v>
+        <v>15.3926868438721</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>17</v>
       </c>
       <c r="G459" t="n">
-        <v>15.1696062088013</v>
+        <v>15.169605255127</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803709030151</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>15.21422290802</v>
+        <v>15.2142200469971</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>14.9911413192749</v>
+        <v>14.991138458252</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G463" t="n">
-        <v>15.1249904632568</v>
+        <v>15.1249895095825</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>15.4373025894165</v>
+        <v>15.4373064041138</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>15.3480710983276</v>
+        <v>15.3480739593506</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>15.3480710983276</v>
+        <v>15.3480739593506</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>15.3480710983276</v>
+        <v>15.3480739593506</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>15.4373025894165</v>
+        <v>15.4373064041138</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G473" t="n">
-        <v>17.5788974761963</v>
+        <v>17.5788955688477</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>17.0434989929199</v>
+        <v>17.0434970855713</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>17.0434989929199</v>
+        <v>17.0434970855713</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>16.9988842010498</v>
+        <v>16.9988822937012</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G477" t="n">
-        <v>17.1327285766602</v>
+        <v>17.1327323913574</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>19.5</v>
       </c>
       <c r="G478" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>17.0434989929199</v>
+        <v>17.0434970855713</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>19.5</v>
       </c>
       <c r="G480" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>19.5</v>
       </c>
       <c r="G481" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>17.2219638824463</v>
+        <v>17.221960067749</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>19.25</v>
       </c>
       <c r="G484" t="n">
-        <v>17.1773490905762</v>
+        <v>17.1773471832275</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>19.25</v>
       </c>
       <c r="G485" t="n">
-        <v>17.1773490905762</v>
+        <v>17.1773471832275</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>19.5</v>
       </c>
       <c r="G489" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G501" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G504" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G508" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>17.8019790649414</v>
+        <v>17.80198097229</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G517" t="n">
-        <v>17.5788974761963</v>
+        <v>17.5788955688477</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>19.75</v>
       </c>
       <c r="G519" t="n">
-        <v>17.6235122680664</v>
+        <v>17.623514175415</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>17.2219638824463</v>
+        <v>17.221960067749</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>19.5</v>
       </c>
       <c r="G524" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>19.5</v>
       </c>
       <c r="G525" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>19.5</v>
       </c>
       <c r="G527" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>19.5</v>
       </c>
       <c r="G528" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>19.25</v>
       </c>
       <c r="G530" t="n">
-        <v>17.1773490905762</v>
+        <v>17.1773471832275</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G550" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>17.7127437591553</v>
+        <v>17.7127456665039</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>17.7127437591553</v>
+        <v>17.7127456665039</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G562" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>19.75</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6235122680664</v>
+        <v>17.623514175415</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>19.0958576202393</v>
+        <v>19.0958557128906</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>19.0066242218018</v>
+        <v>19.0066223144531</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>21.5</v>
       </c>
       <c r="G589" t="n">
-        <v>19.1850891113281</v>
+        <v>19.1850910186768</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>21.5</v>
       </c>
       <c r="G592" t="n">
-        <v>19.1850891113281</v>
+        <v>19.1850910186768</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>19.3635559082031</v>
+        <v>19.3635578155518</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>20.1666507720947</v>
+        <v>20.1666526794434</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>20.1666507720947</v>
+        <v>20.1666526794434</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>19.3635559082031</v>
+        <v>19.3635578155518</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>19.8989543914795</v>
+        <v>19.8989524841309</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>20.7912788391113</v>
+        <v>20.7912826538086</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>20.7020530700684</v>
+        <v>20.7020511627197</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>20.7020530700684</v>
+        <v>20.7020511627197</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>21.1482162475586</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>21.50514793396</v>
+        <v>21.5051498413086</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G623" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>21.1482162475586</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>21.50514793396</v>
+        <v>21.5051498413086</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>24.5</v>
       </c>
       <c r="G627" t="n">
-        <v>21.8620777130127</v>
+        <v>21.8620796203613</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G629" t="n">
-        <v>21.9513111114502</v>
+        <v>21.9513130187988</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>24</v>
       </c>
       <c r="G631" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>21.683614730835</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>21.683614730835</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G635" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>21.2374477386475</v>
+        <v>21.2374458312988</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>24</v>
       </c>
       <c r="G637" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>23.5</v>
       </c>
       <c r="G640" t="n">
-        <v>20.9697513580322</v>
+        <v>20.969747543335</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>21.1482162475586</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>20.7912788391113</v>
+        <v>20.7912826538086</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G645" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>21.1482162475586</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>24</v>
       </c>
       <c r="G648" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>24</v>
       </c>
       <c r="G649" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>24</v>
       </c>
       <c r="G650" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>21.1482162475586</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G654" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G655" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>21.1482162475586</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>21.2374477386475</v>
+        <v>21.2374458312988</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>21.2374477386475</v>
+        <v>21.2374458312988</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G659" t="n">
-        <v>20.2558879852295</v>
+        <v>20.2558860778809</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>20.7020530700684</v>
+        <v>20.7020511627197</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>23.5</v>
       </c>
       <c r="G661" t="n">
-        <v>20.9697513580322</v>
+        <v>20.969747543335</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>22.5</v>
       </c>
       <c r="G664" t="n">
-        <v>20.0774192810059</v>
+        <v>20.0774173736572</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>19.3635559082031</v>
+        <v>19.3635578155518</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>19.0066242218018</v>
+        <v>19.0066223144531</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>16.1957874298096</v>
+        <v>16.1957817077637</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>17.5</v>
       </c>
       <c r="G676" t="n">
-        <v>15.6157712936401</v>
+        <v>15.6157703399658</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>15.0357542037964</v>
+        <v>15.035756111145</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>16.9988842010498</v>
+        <v>16.9988822937012</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>18.0250644683838</v>
+        <v>18.0250606536865</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>19.0066242218018</v>
+        <v>19.0066223144531</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>20.2558879852295</v>
+        <v>20.2558860778809</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>20.7912788391113</v>
+        <v>20.7912826538086</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>21.2374477386475</v>
+        <v>21.2374458312988</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G689" t="n">
-        <v>21.1482162475586</v>
+        <v>21.14821434021</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>23.5</v>
       </c>
       <c r="G693" t="n">
-        <v>20.9697513580322</v>
+        <v>20.969747543335</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>21.683614730835</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>24</v>
       </c>
       <c r="G699" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>21.3266830444336</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>24</v>
       </c>
       <c r="G704" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>24</v>
       </c>
       <c r="G706" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>24</v>
       </c>
       <c r="G707" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G709" t="n">
-        <v>21.683614730835</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>22.0405464172363</v>
+        <v>22.040548324585</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>22.6406574249268</v>
+        <v>22.640661239624</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>24.5</v>
       </c>
       <c r="G717" t="n">
-        <v>22.2769508361816</v>
+        <v>22.2769527435303</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>24.5</v>
       </c>
       <c r="G719" t="n">
-        <v>22.2769508361816</v>
+        <v>22.2769527435303</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>22.4588069915771</v>
+        <v>22.4588088989258</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>24.5</v>
       </c>
       <c r="G721" t="n">
-        <v>22.2769508361816</v>
+        <v>22.2769527435303</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>22.6406574249268</v>
+        <v>22.640661239624</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>22.6406574249268</v>
+        <v>22.640661239624</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>24.5</v>
       </c>
       <c r="G725" t="n">
-        <v>22.2769508361816</v>
+        <v>22.2769527435303</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>22.6406574249268</v>
+        <v>22.640661239624</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>24.5</v>
       </c>
       <c r="G728" t="n">
-        <v>22.2769508361816</v>
+        <v>22.2769527435303</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>22.0041751861572</v>
+        <v>22.0041770935059</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>22.0951023101807</v>
+        <v>22.0950984954834</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>24</v>
       </c>
       <c r="G733" t="n">
-        <v>21.8223190307617</v>
+        <v>21.822322845459</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>21.4586181640625</v>
+        <v>21.4586162567139</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>24</v>
       </c>
       <c r="G751" t="n">
-        <v>21.8223190307617</v>
+        <v>21.822322845459</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>24</v>
       </c>
       <c r="G752" t="n">
-        <v>21.8223190307617</v>
+        <v>21.822322845459</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>22.0041751861572</v>
+        <v>22.0041770935059</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G761" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G768" t="n">
-        <v>21.4586181640625</v>
+        <v>21.4586162567139</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G769" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>21.094913482666</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>21.094913482666</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>21.094913482666</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>21.4586181640625</v>
+        <v>21.4586162567139</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>21.094913482666</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>21.1858348846436</v>
+        <v>21.1858367919922</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>20.6402816772461</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>20.6402816772461</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G796" t="n">
-        <v>20.6402816772461</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>20.3674983978271</v>
+        <v>20.3675003051758</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>20.6402816772461</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>22.0041751861572</v>
+        <v>22.0041770935059</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>23.5499210357666</v>
+        <v>23.5499229431152</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>22.9134368896484</v>
+        <v>22.9134407043457</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.5501117706299</v>
+        <v>24.5501098632812</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>24.0045547485352</v>
+        <v>24.0045509338379</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>23.0952892303467</v>
+        <v>23.0952911376953</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>24.0045547485352</v>
+        <v>24.0045509338379</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>24.4591865539551</v>
+        <v>24.4591846466064</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>26.5</v>
       </c>
       <c r="G813" t="n">
-        <v>24.0954780578613</v>
+        <v>24.09547996521</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>24.2773323059082</v>
+        <v>24.2773303985596</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>26.5</v>
       </c>
       <c r="G815" t="n">
-        <v>24.0954780578613</v>
+        <v>24.09547996521</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7319641113281</v>
+        <v>24.7319660186768</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.9138164520264</v>
+        <v>24.9138145446777</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.9138164520264</v>
+        <v>24.9138145446777</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>27.5</v>
       </c>
       <c r="G819" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047397613525</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>26.0049304962158</v>
+        <v>26.0049324035645</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>26.0958614349365</v>
+        <v>26.0958595275879</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>26.0958614349365</v>
+        <v>26.0958595275879</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>27.5</v>
       </c>
       <c r="G825" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047397613525</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>24.9138164520264</v>
+        <v>24.9138145446777</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>27.5</v>
       </c>
       <c r="G830" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047397613525</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>27</v>
       </c>
       <c r="G832" t="n">
-        <v>24.5501117706299</v>
+        <v>24.5501098632812</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>26</v>
       </c>
       <c r="G833" t="n">
-        <v>23.64084815979</v>
+        <v>23.6408462524414</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>24.2773323059082</v>
+        <v>24.2773303985596</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>27.5</v>
       </c>
       <c r="G836" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047397613525</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>25.7321529388428</v>
+        <v>25.7321548461914</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G838" t="n">
-        <v>26.0049304962158</v>
+        <v>26.0049324035645</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>28.5</v>
       </c>
       <c r="G839" t="n">
-        <v>25.9140090942383</v>
+        <v>25.9140071868896</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5503005981445</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G847" t="n">
-        <v>26.0958614349365</v>
+        <v>26.0958595275879</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>28.5</v>
       </c>
       <c r="G848" t="n">
-        <v>25.9140090942383</v>
+        <v>25.9140071868896</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>28.5</v>
       </c>
       <c r="G849" t="n">
-        <v>25.9140090942383</v>
+        <v>25.9140071868896</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5503005981445</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5503005981445</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>26.0049304962158</v>
+        <v>26.0049324035645</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>28.5</v>
       </c>
       <c r="G856" t="n">
-        <v>25.9140090942383</v>
+        <v>25.9140071868896</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>29.0055046081543</v>
+        <v>29.005500793457</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>29.7329139709473</v>
+        <v>29.7329158782959</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G861" t="n">
-        <v>30.2784690856934</v>
+        <v>30.2784729003906</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>29.6419868469238</v>
+        <v>29.6419849395752</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>30.6421737670898</v>
+        <v>30.6421756744385</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>31.1877346038818</v>
+        <v>31.1877365112305</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>32.0060653686523</v>
+        <v>32.0060729980469</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>35.6431274414062</v>
+        <v>35.643123626709</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G874" t="n">
-        <v>36.0068321228027</v>
+        <v>36.0068283081055</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>35.5521965026855</v>
+        <v>35.5522003173828</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>34.1883010864258</v>
+        <v>34.1882972717285</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G877" t="n">
-        <v>34.9157104492188</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G878" t="n">
-        <v>34.9157104492188</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>34.7338638305664</v>
+        <v>34.7338600158691</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701515197754</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G882" t="n">
-        <v>34.1883010864258</v>
+        <v>34.1882972717285</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>37.5</v>
       </c>
       <c r="G883" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G885" t="n">
-        <v>34.7338638305664</v>
+        <v>34.7338600158691</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>34.1883010864258</v>
+        <v>34.1882972717285</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G888" t="n">
-        <v>34.642936706543</v>
+        <v>34.6429328918457</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>34.642936706543</v>
+        <v>34.6429328918457</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>34.9157104492188</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>37.5</v>
       </c>
       <c r="G893" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>37</v>
       </c>
       <c r="G894" t="n">
-        <v>33.6427421569824</v>
+        <v>33.6427459716797</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701515197754</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G898" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G900" t="n">
-        <v>33.0971908569336</v>
+        <v>33.0971870422363</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G901" t="n">
-        <v>32.8244018554688</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701515197754</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G907" t="n">
-        <v>34.9157104492188</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>37.5</v>
       </c>
       <c r="G909" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G911" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G912" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>33.2790374755859</v>
+        <v>33.2790412902832</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>37</v>
       </c>
       <c r="G914" t="n">
-        <v>33.6427421569824</v>
+        <v>33.6427459716797</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G915" t="n">
-        <v>32.8244018554688</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>32.9153327941895</v>
+        <v>32.9153366088867</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>37</v>
       </c>
       <c r="G917" t="n">
-        <v>33.6427421569824</v>
+        <v>33.6427459716797</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>36.5</v>
       </c>
       <c r="G919" t="n">
-        <v>33.1881141662598</v>
+        <v>33.1881103515625</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G920" t="n">
-        <v>33.0062637329102</v>
+        <v>33.0062599182129</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G921" t="n">
-        <v>32.9153327941895</v>
+        <v>32.9153366088867</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>36.5</v>
       </c>
       <c r="G923" t="n">
-        <v>33.1881141662598</v>
+        <v>33.1881103515625</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>36.5</v>
       </c>
       <c r="G924" t="n">
-        <v>33.1881141662598</v>
+        <v>33.1881103515625</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G925" t="n">
-        <v>33.2790374755859</v>
+        <v>33.2790412902832</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>33.0062637329102</v>
+        <v>33.0062599182129</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.6425552368164</v>
+        <v>32.6425590515137</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>36</v>
       </c>
       <c r="G929" t="n">
-        <v>32.7334823608398</v>
+        <v>32.7334861755371</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>39.5</v>
       </c>
       <c r="G931" t="n">
-        <v>35.9159049987793</v>
+        <v>35.915901184082</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>35.2794189453125</v>
+        <v>35.2794151306152</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.1883010864258</v>
+        <v>34.1882972717285</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701515197754</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>37.5</v>
       </c>
       <c r="G936" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G937" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>37.5</v>
       </c>
       <c r="G939" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G940" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>37</v>
       </c>
       <c r="G941" t="n">
-        <v>33.6427421569824</v>
+        <v>33.6427459716797</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G943" t="n">
-        <v>34.0064468383789</v>
+        <v>34.0064506530762</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>37.5</v>
       </c>
       <c r="G944" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G945" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701515197754</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>37.5</v>
       </c>
       <c r="G947" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G948" t="n">
-        <v>33.91552734375</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G951" t="n">
-        <v>32.8244018554688</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>32.8244018554688</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G953" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>33.4608917236328</v>
+        <v>33.4608955383301</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G955" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G958" t="n">
-        <v>33.8246040344238</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>33.4608917236328</v>
+        <v>33.4608955383301</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>34.3592338562012</v>
+        <v>34.3592376708984</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>34.5444564819336</v>
+        <v>34.5444602966309</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>34.4518508911133</v>
+        <v>34.4518432617188</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>34.4518508911133</v>
+        <v>34.4518432617188</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G965" t="n">
-        <v>34.5444564819336</v>
+        <v>34.5444602966309</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>33.5257225036621</v>
+        <v>33.5257263183594</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>33.618335723877</v>
+        <v>33.6183319091797</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>33.618335723877</v>
+        <v>33.6183319091797</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3404960632324</v>
+        <v>33.3404998779297</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>36</v>
       </c>
       <c r="G981" t="n">
-        <v>33.3404960632324</v>
+        <v>33.3404998779297</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G984" t="n">
-        <v>33.5257225036621</v>
+        <v>33.5257263183594</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.7109451293945</v>
+        <v>33.7109489440918</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>39</v>
       </c>
       <c r="G986" t="n">
-        <v>36.1188697814941</v>
+        <v>36.1188735961914</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G987" t="n">
-        <v>38.6194114685059</v>
+        <v>38.6194076538086</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G988" t="n">
-        <v>39.1750831604004</v>
+        <v>39.1750869750977</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>46</v>
       </c>
       <c r="G989" t="n">
-        <v>42.601749420166</v>
+        <v>42.6017456054688</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>42.2312965393066</v>
+        <v>42.2312927246094</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>41.5830154418945</v>
+        <v>41.5830078125</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>41.9534568786621</v>
+        <v>41.9534606933594</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G994" t="n">
-        <v>42.4165153503418</v>
+        <v>42.4165191650391</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>44.3613891601562</v>
+        <v>44.361385345459</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>48.9000015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>45.2875061035156</v>
+        <v>45.2875137329102</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>49.5</v>
       </c>
       <c r="G998" t="n">
-        <v>45.8431854248047</v>
+        <v>45.8431816101074</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>45.4727363586426</v>
+        <v>45.4727325439453</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>45.1022872924805</v>
+        <v>45.1022834777832</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>49.5</v>
       </c>
       <c r="G1003" t="n">
-        <v>45.8431854248047</v>
+        <v>45.8431816101074</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G1004" t="n">
-        <v>45.194896697998</v>
+        <v>45.1948928833008</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>51</v>
       </c>
       <c r="G1006" t="n">
-        <v>47.2323684692383</v>
+        <v>47.2323722839355</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>47.0471420288086</v>
+        <v>47.0471458435059</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1009" t="n">
-        <v>47.0471420288086</v>
+        <v>47.0471458435059</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1013" t="n">
-        <v>47.0471420288086</v>
+        <v>47.0471458435059</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G1015" t="n">
-        <v>45.1022872924805</v>
+        <v>45.1022834777832</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>50.2000007629395</v>
       </c>
       <c r="G1017" t="n">
-        <v>46.4914741516113</v>
+        <v>46.4914703369141</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>47.0471420288086</v>
+        <v>47.0471458435059</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>46.8619194030762</v>
+        <v>46.8619232177734</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>49.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>45.8431854248047</v>
+        <v>45.8431816101074</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>54</v>
       </c>
       <c r="G1023" t="n">
-        <v>50.0107460021973</v>
+        <v>50.0107421875</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G1025" t="n">
-        <v>50.3811950683594</v>
+        <v>50.3811988830566</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>60</v>
       </c>
       <c r="G1028" t="n">
-        <v>55.567497253418</v>
+        <v>55.5674934387207</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>57.0492935180664</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1038" t="n">
-        <v>57.0492935180664</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>55.0118179321289</v>
+        <v>55.0118255615234</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>59.642448425293</v>
+        <v>59.6424446105957</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>65</v>
       </c>
       <c r="G1043" t="n">
-        <v>60.1981239318848</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1044" t="n">
-        <v>60.0128936767578</v>
+        <v>60.0128974914551</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1047" t="n">
-        <v>62.7912712097168</v>
+        <v>62.7912826538086</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>65.1991882324219</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1051" t="n">
-        <v>65.1991882324219</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>65.1991882324219</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>70</v>
       </c>
       <c r="G1054" t="n">
-        <v>64.828742980957</v>
+        <v>64.8287506103516</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>68.5999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>63.532169342041</v>
+        <v>63.5321769714355</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>66</v>
       </c>
       <c r="G1056" t="n">
-        <v>61.1242446899414</v>
+        <v>61.1242485046387</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>67</v>
       </c>
       <c r="G1060" t="n">
-        <v>62.0503730773926</v>
+        <v>62.0503692626953</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1061" t="n">
-        <v>62.2355995178223</v>
+        <v>62.2355918884277</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1062" t="n">
-        <v>62.4208145141602</v>
+        <v>62.420825958252</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>61.4946937561035</v>
+        <v>61.4946975708008</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1064" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>60.5685691833496</v>
+        <v>60.5685729980469</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5310935974121</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>63</v>
       </c>
       <c r="G1070" t="n">
-        <v>58.3458709716797</v>
+        <v>58.3458671569824</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>64</v>
       </c>
       <c r="G1071" t="n">
-        <v>59.2719917297363</v>
+        <v>59.2719955444336</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1072" t="n">
-        <v>57.9754180908203</v>
+        <v>57.9754219055176</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>57.6049690246582</v>
+        <v>57.6049728393555</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5310935974121</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1078" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469390869141</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1080" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469390869141</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1081" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469390869141</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>67</v>
       </c>
       <c r="G1084" t="n">
-        <v>62.0503730773926</v>
+        <v>62.0503692626953</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>67</v>
       </c>
       <c r="G1085" t="n">
-        <v>62.0503730773926</v>
+        <v>62.0503692626953</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>62.7912712097168</v>
+        <v>62.7912826538086</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1088" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469390869141</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1090" t="n">
-        <v>66.3105545043945</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>72</v>
       </c>
       <c r="G1091" t="n">
-        <v>66.6809921264648</v>
+        <v>66.6809997558594</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1093" t="n">
-        <v>66.3105545043945</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G1094" t="n">
-        <v>65.0139694213867</v>
+        <v>65.0139541625977</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1096" t="n">
-        <v>66.3105545043945</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G1097" t="n">
-        <v>65.9400863647461</v>
+        <v>65.9400939941406</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1098" t="n">
-        <v>65.1991882324219</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G1103" t="n">
-        <v>65.0139694213867</v>
+        <v>65.0139541625977</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1104" t="n">
-        <v>64.0878372192383</v>
+        <v>64.0878448486328</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>74.4000015258789</v>
       </c>
       <c r="G1106" t="n">
-        <v>68.9037017822266</v>
+        <v>68.9036865234375</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>74</v>
       </c>
       <c r="G1107" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332336425781</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1108" t="n">
-        <v>70.2002716064453</v>
+        <v>70.2002639770508</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>74</v>
       </c>
       <c r="G1109" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332336425781</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>75.1999969482422</v>
       </c>
       <c r="G1110" t="n">
-        <v>69.6445922851562</v>
+        <v>69.6445846557617</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>74</v>
       </c>
       <c r="G1113" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332336425781</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1114" t="n">
-        <v>67.4218902587891</v>
+        <v>67.4218978881836</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>74.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>68.9037017822266</v>
+        <v>68.9036865234375</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>69.0889129638672</v>
+        <v>69.0889205932617</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>72</v>
       </c>
       <c r="G1123" t="n">
-        <v>66.6809921264648</v>
+        <v>66.6809997558594</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1124" t="n">
-        <v>66.3105545043945</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>74</v>
       </c>
       <c r="G1125" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332336425781</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1127" t="n">
-        <v>67.4218902587891</v>
+        <v>67.4218978881836</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1131" t="n">
-        <v>69.0889129638672</v>
+        <v>69.0889205932617</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>75</v>
       </c>
       <c r="G1133" t="n">
-        <v>69.4593658447266</v>
+        <v>69.4593734741211</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1134" t="n">
-        <v>70.2002716064453</v>
+        <v>70.2002639770508</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>79</v>
       </c>
       <c r="G1135" t="n">
-        <v>73.1638717651367</v>
+        <v>73.1638641357422</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>78</v>
       </c>
       <c r="G1137" t="n">
-        <v>72.2377395629883</v>
+        <v>72.2377471923828</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>74</v>
       </c>
       <c r="G1139" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332336425781</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1140" t="n">
-        <v>67.4218902587891</v>
+        <v>67.4218978881836</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1142" t="n">
-        <v>66.3105545043945</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>70</v>
       </c>
       <c r="G1143" t="n">
-        <v>64.828742980957</v>
+        <v>64.8287506103516</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1144" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469390869141</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1145" t="n">
-        <v>64.6435317993164</v>
+        <v>64.6435165405273</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1146" t="n">
-        <v>65.1991882324219</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1147" t="n">
-        <v>62.4208145141602</v>
+        <v>62.420825958252</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>67</v>
       </c>
       <c r="G1149" t="n">
-        <v>62.0503730773926</v>
+        <v>62.0503692626953</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>66</v>
       </c>
       <c r="G1150" t="n">
-        <v>61.1242446899414</v>
+        <v>61.1242485046387</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1151" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>66</v>
       </c>
       <c r="G1153" t="n">
-        <v>61.1242446899414</v>
+        <v>61.1242485046387</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>60.939022064209</v>
+        <v>60.9390182495117</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>66</v>
       </c>
       <c r="G1156" t="n">
-        <v>61.1242446899414</v>
+        <v>61.1242485046387</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>65</v>
       </c>
       <c r="G1158" t="n">
-        <v>60.1981239318848</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1159" t="n">
-        <v>58.7163238525391</v>
+        <v>58.7163200378418</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>57.9754180908203</v>
+        <v>57.9754219055176</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5310935974121</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1166" t="n">
-        <v>57.9754180908203</v>
+        <v>57.9754219055176</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>63</v>
       </c>
       <c r="G1168" t="n">
-        <v>58.3458709716797</v>
+        <v>58.3458671569824</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>57.0492935180664</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>60</v>
       </c>
       <c r="G1171" t="n">
-        <v>55.567497253418</v>
+        <v>55.5674934387207</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1174" t="n">
-        <v>57.0492935180664</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1176" t="n">
-        <v>55.1970405578613</v>
+        <v>55.1970443725586</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1179" t="n">
-        <v>51.3073196411133</v>
+        <v>51.3073234558105</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1182" t="n">
-        <v>55.1970405578613</v>
+        <v>55.1970443725586</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>57.0492935180664</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>60</v>
       </c>
       <c r="G1187" t="n">
-        <v>55.567497253418</v>
+        <v>55.5674934387207</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>60.5685691833496</v>
+        <v>60.5685729980469</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1190" t="n">
-        <v>60.939022064209</v>
+        <v>60.9390182495117</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>65</v>
       </c>
       <c r="G1191" t="n">
-        <v>60.1981239318848</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>63</v>
       </c>
       <c r="G1196" t="n">
-        <v>58.3458709716797</v>
+        <v>58.3458671569824</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1198" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5310935974121</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>65</v>
       </c>
       <c r="G1199" t="n">
-        <v>60.1981239318848</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1201" t="n">
-        <v>60.0128936767578</v>
+        <v>60.0128974914551</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>61.4946937561035</v>
+        <v>61.4946975708008</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>67</v>
       </c>
       <c r="G1206" t="n">
-        <v>62.0503730773926</v>
+        <v>62.0503692626953</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>65</v>
       </c>
       <c r="G1207" t="n">
-        <v>60.1981239318848</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>65</v>
       </c>
       <c r="G1208" t="n">
-        <v>60.1981239318848</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>65</v>
       </c>
       <c r="G1209" t="n">
-        <v>60.1981239318848</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>65</v>
       </c>
       <c r="G1210" t="n">
-        <v>60.1981239318848</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1211" t="n">
-        <v>59.9202766418457</v>
+        <v>59.920280456543</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>58.6237030029297</v>
+        <v>58.6237106323242</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>63</v>
       </c>
       <c r="G1214" t="n">
-        <v>58.3458709716797</v>
+        <v>58.3458671569824</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1216" t="n">
-        <v>60.6766967773438</v>
+        <v>60.6766929626465</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>63.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>59.459415435791</v>
+        <v>59.4594116210938</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>56.3693962097168</v>
+        <v>56.3693923950195</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>54.4966621398926</v>
+        <v>54.4966583251953</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1220" t="n">
-        <v>51.5939178466797</v>
+        <v>51.5939140319824</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>56.5</v>
       </c>
       <c r="G1221" t="n">
-        <v>52.9048271179199</v>
+        <v>52.9048309326172</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1222" t="n">
-        <v>54.1221122741699</v>
+        <v>54.1221084594727</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>56.2757530212402</v>
+        <v>56.2757606506348</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G1225" t="n">
-        <v>56.8375778198242</v>
+        <v>56.8375816345215</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>57.0248565673828</v>
+        <v>57.0248527526855</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1228" t="n">
-        <v>56.0884895324707</v>
+        <v>56.0884857177734</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G1230" t="n">
-        <v>57.0248565673828</v>
+        <v>57.0248527526855</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>57.8675880432129</v>
+        <v>57.8675842285156</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1233" t="n">
-        <v>59.3657722473145</v>
+        <v>59.3657760620117</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G1237" t="n">
-        <v>61.8939666748047</v>
+        <v>61.893970489502</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1238" t="n">
-        <v>61.0512390136719</v>
+        <v>61.0512313842773</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>66</v>
       </c>
       <c r="G1239" t="n">
-        <v>61.8003311157227</v>
+        <v>61.8003387451172</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>63.5</v>
       </c>
       <c r="G1241" t="n">
-        <v>59.459415435791</v>
+        <v>59.4594116210938</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>61.5</v>
       </c>
       <c r="G1244" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>56.7439422607422</v>
+        <v>56.7439384460449</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>55.9948463439941</v>
+        <v>55.9948501586914</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>62</v>
       </c>
       <c r="G1248" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>56.3693962097168</v>
+        <v>56.3693923950195</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>59</v>
       </c>
       <c r="G1250" t="n">
-        <v>55.2457504272461</v>
+        <v>55.2457542419434</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>57.3057632446289</v>
+        <v>57.3057670593262</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1264" t="n">
-        <v>60.6766967773438</v>
+        <v>60.6766929626465</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>67</v>
       </c>
       <c r="G1265" t="n">
-        <v>62.7367057800293</v>
+        <v>62.736701965332</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1266" t="n">
-        <v>61.6130638122559</v>
+        <v>61.6130599975586</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1268" t="n">
-        <v>60.7703285217285</v>
+        <v>60.7703323364258</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>63</v>
       </c>
       <c r="G1269" t="n">
-        <v>58.9912300109863</v>
+        <v>58.9912261962891</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>59.7403259277344</v>
+        <v>59.7403221130371</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1277" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1279" t="n">
-        <v>62.4557876586914</v>
+        <v>62.4557914733887</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G1282" t="n">
-        <v>64.3285217285156</v>
+        <v>64.3285293579102</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>68</v>
       </c>
       <c r="G1283" t="n">
-        <v>63.6730766296387</v>
+        <v>63.6730690002441</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1284" t="n">
-        <v>64.7967071533203</v>
+        <v>64.7967147827148</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>67</v>
       </c>
       <c r="G1285" t="n">
-        <v>62.7367057800293</v>
+        <v>62.736701965332</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>68</v>
       </c>
       <c r="G1286" t="n">
-        <v>63.6730766296387</v>
+        <v>63.6730690002441</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>69</v>
       </c>
       <c r="G1288" t="n">
-        <v>64.6094436645508</v>
+        <v>64.6094360351562</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>68.1999969482422</v>
       </c>
       <c r="G1291" t="n">
-        <v>63.8603363037109</v>
+        <v>63.8603439331055</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>63.7667083740234</v>
+        <v>63.7667045593262</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>67.5999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>63.2985229492188</v>
+        <v>63.2985153198242</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>67</v>
       </c>
       <c r="G1295" t="n">
-        <v>62.7367057800293</v>
+        <v>62.736701965332</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>69</v>
       </c>
       <c r="G1298" t="n">
-        <v>64.6094436645508</v>
+        <v>64.6094360351562</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>69</v>
       </c>
       <c r="G1299" t="n">
-        <v>64.6094436645508</v>
+        <v>64.6094360351562</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1303" t="n">
-        <v>63.5794410705566</v>
+        <v>63.5794334411621</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G1305" t="n">
-        <v>64.8903503417969</v>
+        <v>64.8903579711914</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1309" t="n">
-        <v>65.358528137207</v>
+        <v>65.3585357666016</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1312" t="n">
-        <v>66.2949142456055</v>
+        <v>66.2949066162109</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>70.3000030517578</v>
       </c>
       <c r="G1315" t="n">
-        <v>65.8267135620117</v>
+        <v>65.8267211914062</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>68</v>
       </c>
       <c r="G1316" t="n">
-        <v>63.6730766296387</v>
+        <v>63.6730690002441</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>66.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>62.2685165405273</v>
+        <v>62.2685089111328</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1318" t="n">
-        <v>61.0512390136719</v>
+        <v>61.0512313842773</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1319" t="n">
-        <v>59.7403259277344</v>
+        <v>59.7403221130371</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1325" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>66</v>
       </c>
       <c r="G1326" t="n">
-        <v>61.8003311157227</v>
+        <v>61.8003387451172</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>66</v>
       </c>
       <c r="G1327" t="n">
-        <v>61.8003311157227</v>
+        <v>61.8003387451172</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1328" t="n">
-        <v>60.7703285217285</v>
+        <v>60.7703323364258</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1329" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1330" t="n">
-        <v>60.7703285217285</v>
+        <v>60.7703323364258</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1332" t="n">
-        <v>59.5530471801758</v>
+        <v>59.553050994873</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1333" t="n">
-        <v>60.4894180297852</v>
+        <v>60.4894142150879</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1337" t="n">
-        <v>61.0512390136719</v>
+        <v>61.0512313842773</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1340" t="n">
-        <v>61.0512390136719</v>
+        <v>61.0512313842773</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>68</v>
       </c>
       <c r="G1344" t="n">
-        <v>63.6730766296387</v>
+        <v>63.6730690002441</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1345" t="n">
-        <v>63.4857978820801</v>
+        <v>63.4858093261719</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G1347" t="n">
-        <v>63.0176162719727</v>
+        <v>63.0176200866699</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>66.9000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>62.64306640625</v>
+        <v>62.6430625915527</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>66.5</v>
       </c>
       <c r="G1349" t="n">
-        <v>62.2685165405273</v>
+        <v>62.2685089111328</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1351" t="n">
-        <v>62.4557876586914</v>
+        <v>62.4557914733887</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1352" t="n">
-        <v>62.4557876586914</v>
+        <v>62.4557914733887</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1353" t="n">
-        <v>63.5794410705566</v>
+        <v>63.5794334411621</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>67</v>
       </c>
       <c r="G1354" t="n">
-        <v>62.7367057800293</v>
+        <v>62.736701965332</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1356" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1357" t="n">
-        <v>60.4894180297852</v>
+        <v>60.4894142150879</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1359" t="n">
-        <v>60.6766967773438</v>
+        <v>60.6766929626465</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1360" t="n">
-        <v>60.5830497741699</v>
+        <v>60.5830535888672</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1362" t="n">
-        <v>60.4894180297852</v>
+        <v>60.4894142150879</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1366" t="n">
-        <v>59.5530471801758</v>
+        <v>59.553050994873</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>59.6466827392578</v>
+        <v>59.6466865539551</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>58.4294052124023</v>
+        <v>58.4294090270996</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>62</v>
       </c>
       <c r="G1369" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1370" t="n">
-        <v>58.897590637207</v>
+        <v>58.8975944519043</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>57.6803131103516</v>
+        <v>57.680305480957</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1375" t="n">
-        <v>58.6166801452637</v>
+        <v>58.6166839599609</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1376" t="n">
-        <v>59.5530471801758</v>
+        <v>59.553050994873</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1377" t="n">
-        <v>59.5530471801758</v>
+        <v>59.553050994873</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>62</v>
       </c>
       <c r="G1379" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>63</v>
       </c>
       <c r="G1381" t="n">
-        <v>58.9912300109863</v>
+        <v>58.9912261962891</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1382" t="n">
-        <v>58.897590637207</v>
+        <v>58.8975944519043</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1387" t="n">
-        <v>58.6166801452637</v>
+        <v>58.6166839599609</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G1388" t="n">
-        <v>58.3357696533203</v>
+        <v>58.335765838623</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G1392" t="n">
-        <v>59.8339576721191</v>
+        <v>59.8339614868164</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>59.5530471801758</v>
+        <v>59.553050994873</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1395" t="n">
-        <v>59.3657722473145</v>
+        <v>59.3657760620117</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1396" t="n">
-        <v>58.897590637207</v>
+        <v>58.8975944519043</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>58.3357696533203</v>
+        <v>58.335765838623</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>63</v>
       </c>
       <c r="G1398" t="n">
-        <v>58.9912300109863</v>
+        <v>58.9912261962891</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>62</v>
       </c>
       <c r="G1401" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>57.3057632446289</v>
+        <v>57.3057670593262</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>61.5</v>
       </c>
       <c r="G1403" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>61.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1407" t="n">
-        <v>55.9948463439941</v>
+        <v>55.9948501586914</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>59</v>
       </c>
       <c r="G1411" t="n">
-        <v>55.2457504272461</v>
+        <v>55.2457542419434</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1413" t="n">
-        <v>55.3393898010254</v>
+        <v>55.3393859863281</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1415" t="n">
-        <v>56.2757530212402</v>
+        <v>56.2757606506348</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>56.0884895324707</v>
+        <v>56.0884857177734</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>62</v>
       </c>
       <c r="G1418" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>61.5</v>
       </c>
       <c r="G1420" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>56.3693962097168</v>
+        <v>56.3693923950195</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1423" t="n">
-        <v>56.0884895324707</v>
+        <v>56.0884857177734</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>62</v>
       </c>
       <c r="G1424" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>62</v>
       </c>
       <c r="G1426" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>61.5</v>
       </c>
       <c r="G1427" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1431" t="n">
-        <v>56.2757530212402</v>
+        <v>56.2757606506348</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G1433" t="n">
-        <v>56.8375778198242</v>
+        <v>56.8375816345215</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1435" t="n">
-        <v>56.7439422607422</v>
+        <v>56.7439384460449</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>57.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>53.8412017822266</v>
+        <v>53.8411979675293</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>56</v>
       </c>
       <c r="G1439" t="n">
-        <v>52.4366416931152</v>
+        <v>52.4366493225098</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>52.7175559997559</v>
+        <v>52.7175598144531</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>56</v>
       </c>
       <c r="G1441" t="n">
-        <v>52.4366416931152</v>
+        <v>52.4366493225098</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>56.2000007629395</v>
       </c>
       <c r="G1443" t="n">
-        <v>52.6239242553711</v>
+        <v>52.6239204406738</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>56</v>
       </c>
       <c r="G1448" t="n">
-        <v>52.4366416931152</v>
+        <v>52.4366493225098</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G1449" t="n">
-        <v>52.5302848815918</v>
+        <v>52.5302810668945</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1450" t="n">
-        <v>52.3430137634277</v>
+        <v>52.3430099487305</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>56</v>
       </c>
       <c r="G1451" t="n">
-        <v>52.4366416931152</v>
+        <v>52.4366493225098</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>55</v>
       </c>
       <c r="G1456" t="n">
-        <v>51.5002784729004</v>
+        <v>51.5002746582031</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1457" t="n">
-        <v>51.5939178466797</v>
+        <v>51.5939140319824</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>51.219367980957</v>
+        <v>51.2193641662598</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>54</v>
       </c>
       <c r="G1461" t="n">
-        <v>50.5639114379883</v>
+        <v>50.563907623291</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G1462" t="n">
-        <v>49.8148155212402</v>
+        <v>49.814811706543</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1463" t="n">
-        <v>50.3766326904297</v>
+        <v>50.376636505127</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1466" t="n">
-        <v>50.0020904541016</v>
+        <v>50.0020866394043</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>50</v>
       </c>
       <c r="G1469" t="n">
-        <v>46.818431854248</v>
+        <v>46.8184356689453</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1473" t="n">
-        <v>48.5975341796875</v>
+        <v>48.5975379943848</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1475" t="n">
-        <v>48.5975341796875</v>
+        <v>48.5975379943848</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1479" t="n">
-        <v>52.686954498291</v>
+        <v>52.6869583129883</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>54.4939117431641</v>
+        <v>54.4939079284668</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G1483" t="n">
-        <v>54.3988075256348</v>
+        <v>54.3988037109375</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1490" t="n">
-        <v>55.8253440856934</v>
+        <v>55.8253479003906</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1491" t="n">
-        <v>56.2057571411133</v>
+        <v>56.205753326416</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>55.8253440856934</v>
+        <v>55.8253479003906</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1495" t="n">
-        <v>56.2057571411133</v>
+        <v>56.205753326416</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1501" t="n">
-        <v>57.4420928955078</v>
+        <v>57.4420967102051</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1505" t="n">
-        <v>58.5833282470703</v>
+        <v>58.583324432373</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1511" t="n">
-        <v>57.4420928955078</v>
+        <v>57.4420967102051</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>59.5</v>
       </c>
       <c r="G1512" t="n">
-        <v>56.5861663818359</v>
+        <v>56.5861701965332</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>59.5</v>
       </c>
       <c r="G1513" t="n">
-        <v>56.5861663818359</v>
+        <v>56.5861701965332</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1519" t="n">
-        <v>56.2057571411133</v>
+        <v>56.205753326416</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1520" t="n">
-        <v>55.8253440856934</v>
+        <v>55.8253479003906</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1521" t="n">
-        <v>56.6812705993652</v>
+        <v>56.6812744140625</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>58.5</v>
       </c>
       <c r="G1524" t="n">
-        <v>55.635139465332</v>
+        <v>55.6351432800293</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>58.5</v>
       </c>
       <c r="G1527" t="n">
-        <v>55.635139465332</v>
+        <v>55.6351432800293</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>58.5</v>
       </c>
       <c r="G1528" t="n">
-        <v>55.635139465332</v>
+        <v>55.6351432800293</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1533" t="n">
-        <v>54.7792129516602</v>
+        <v>54.7792167663574</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>57.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>54.6841163635254</v>
+        <v>54.6841125488281</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1537" t="n">
-        <v>54.3036994934082</v>
+        <v>54.3037033081055</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1539" t="n">
-        <v>53.6379852294922</v>
+        <v>53.6379814147949</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1544" t="n">
-        <v>53.1624717712402</v>
+        <v>53.162467956543</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1546" t="n">
-        <v>53.6379852294922</v>
+        <v>53.6379814147949</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1547" t="n">
-        <v>53.5428771972656</v>
+        <v>53.5428810119629</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1548" t="n">
-        <v>52.8771629333496</v>
+        <v>52.8771591186523</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G1551" t="n">
-        <v>51.9261283874512</v>
+        <v>51.9261322021484</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1555" t="n">
-        <v>52.8771629333496</v>
+        <v>52.8771591186523</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>55</v>
       </c>
       <c r="G1558" t="n">
-        <v>52.3065452575684</v>
+        <v>52.3065414428711</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G1559" t="n">
-        <v>51.9261283874512</v>
+        <v>51.9261322021484</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>55</v>
       </c>
       <c r="G1565" t="n">
-        <v>52.3065452575684</v>
+        <v>52.3065414428711</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1567" t="n">
-        <v>50.7849006652832</v>
+        <v>50.7848968505859</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1568" t="n">
-        <v>50.7849006652832</v>
+        <v>50.7848968505859</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>53</v>
       </c>
       <c r="G1571" t="n">
-        <v>50.404483795166</v>
+        <v>50.4044876098633</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>49.6436653137207</v>
+        <v>49.643669128418</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G1575" t="n">
-        <v>48.4073295593262</v>
+        <v>48.4073257446289</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>49</v>
       </c>
       <c r="G1579" t="n">
-        <v>46.6003761291504</v>
+        <v>46.6003723144531</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>48</v>
       </c>
       <c r="G1588" t="n">
-        <v>45.6493453979492</v>
+        <v>45.6493492126465</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>48.9500007629395</v>
       </c>
       <c r="G1590" t="n">
-        <v>46.5528259277344</v>
+        <v>46.5528221130371</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1591" t="n">
-        <v>48.7877349853516</v>
+        <v>48.7877388000488</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>49.2999992370605</v>
       </c>
       <c r="G1596" t="n">
-        <v>46.885684967041</v>
+        <v>46.8856811523438</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>49</v>
       </c>
       <c r="G1597" t="n">
-        <v>46.6003761291504</v>
+        <v>46.6003723144531</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G1600" t="n">
-        <v>46.1724090576172</v>
+        <v>46.1724128723145</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>48.25</v>
       </c>
       <c r="G1601" t="n">
-        <v>45.8871078491211</v>
+        <v>45.8871040344238</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1603" t="n">
-        <v>48.7877349853516</v>
+        <v>48.7877388000488</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>48.9000015258789</v>
       </c>
       <c r="G1607" t="n">
-        <v>46.5052719116211</v>
+        <v>46.5052757263184</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>46.980785369873</v>
+        <v>46.9807891845703</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G1609" t="n">
-        <v>47.408748626709</v>
+        <v>47.4087448120117</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G1620" t="n">
-        <v>47.4563064575195</v>
+        <v>47.4563026428223</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>51.5</v>
       </c>
       <c r="G1621" t="n">
-        <v>48.9779472351074</v>
+        <v>48.9779434204102</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>51.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>48.9779472351074</v>
+        <v>48.9779434204102</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1627" t="n">
-        <v>52.8771629333496</v>
+        <v>52.8771591186523</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1629" t="n">
-        <v>52.686954498291</v>
+        <v>52.6869583129883</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1631" t="n">
-        <v>52.686954498291</v>
+        <v>52.6869583129883</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1632" t="n">
-        <v>52.8771629333496</v>
+        <v>52.8771591186523</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1633" t="n">
-        <v>54.4939117431641</v>
+        <v>54.4939079284668</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>56</v>
       </c>
       <c r="G1636" t="n">
-        <v>53.2575721740723</v>
+        <v>53.2575759887695</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1639" t="n">
-        <v>52.686954498291</v>
+        <v>52.6869583129883</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1642" t="n">
-        <v>53.6379852294922</v>
+        <v>53.6379814147949</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1644" t="n">
-        <v>53.5428771972656</v>
+        <v>53.5428810119629</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>56</v>
       </c>
       <c r="G1646" t="n">
-        <v>53.2575721740723</v>
+        <v>53.2575759887695</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1647" t="n">
-        <v>53.1624717712402</v>
+        <v>53.162467956543</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1650" t="n">
-        <v>53.6379852294922</v>
+        <v>53.6379814147949</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>56.7763786315918</v>
+        <v>56.7763748168945</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1653" t="n">
-        <v>56.2057571411133</v>
+        <v>56.205753326416</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1655" t="n">
-        <v>54.7792129516602</v>
+        <v>54.7792167663574</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>59.5</v>
       </c>
       <c r="G1656" t="n">
-        <v>56.5861663818359</v>
+        <v>56.5861701965332</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>60.5</v>
       </c>
       <c r="G1658" t="n">
-        <v>57.5372009277344</v>
+        <v>57.5371971130371</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1660" t="n">
-        <v>57.1567840576172</v>
+        <v>57.1567878723145</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1662" t="n">
-        <v>58.5833282470703</v>
+        <v>58.583324432373</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>62</v>
       </c>
       <c r="G1663" t="n">
-        <v>58.963737487793</v>
+        <v>58.9637413024902</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>59.1539497375488</v>
+        <v>59.1539459228516</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>62</v>
       </c>
       <c r="G1666" t="n">
-        <v>58.963737487793</v>
+        <v>58.9637413024902</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1667" t="n">
-        <v>57.4420928955078</v>
+        <v>57.4420967102051</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1668" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1669" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1670" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>60.5</v>
       </c>
       <c r="G1671" t="n">
-        <v>57.5372009277344</v>
+        <v>57.5371971130371</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1673" t="n">
-        <v>59.7245597839355</v>
+        <v>59.7245635986328</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1675" t="n">
-        <v>59.5343551635742</v>
+        <v>59.5343589782715</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1677" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1678" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1679" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1682" t="n">
-        <v>58.5833282470703</v>
+        <v>58.583324432373</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>60.5</v>
       </c>
       <c r="G1683" t="n">
-        <v>57.5372009277344</v>
+        <v>57.5371971130371</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1684" t="n">
-        <v>56.7763786315918</v>
+        <v>56.7763748168945</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1685" t="n">
-        <v>56.6812705993652</v>
+        <v>56.6812744140625</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1694" t="n">
-        <v>56.7763786315918</v>
+        <v>56.7763748168945</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1700" t="n">
-        <v>54.4939117431641</v>
+        <v>54.4939079284668</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1703" t="n">
-        <v>54.7792129516602</v>
+        <v>54.7792167663574</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1706" t="n">
-        <v>53.6379852294922</v>
+        <v>53.6379814147949</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>56</v>
       </c>
       <c r="G1708" t="n">
-        <v>53.2575721740723</v>
+        <v>53.2575759887695</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>54.7999992370605</v>
       </c>
       <c r="G1711" t="n">
-        <v>52.116340637207</v>
+        <v>52.1163368225098</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>55</v>
       </c>
       <c r="G1714" t="n">
-        <v>52.3065452575684</v>
+        <v>52.3065414428711</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1715" t="n">
-        <v>50.7849006652832</v>
+        <v>50.7848968505859</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1716" t="n">
-        <v>51.1653060913086</v>
+        <v>51.1653099060059</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1717" t="n">
-        <v>51.1653060913086</v>
+        <v>51.1653099060059</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>53</v>
       </c>
       <c r="G1718" t="n">
-        <v>50.404483795166</v>
+        <v>50.4044876098633</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1719" t="n">
-        <v>49.263256072998</v>
+        <v>49.2632522583008</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1722" t="n">
-        <v>50.4995918273926</v>
+        <v>50.4995880126953</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>54</v>
       </c>
       <c r="G1725" t="n">
-        <v>51.3555183410645</v>
+        <v>51.3555145263672</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1726" t="n">
-        <v>50.7849006652832</v>
+        <v>50.7848968505859</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1727" t="n">
-        <v>49.3583564758301</v>
+        <v>49.3583602905273</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -61420,6 +61420,32 @@
         <v>72.1999969482422</v>
       </c>
       <c r="H2348" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2349" t="n">
+        <v>8953</v>
+      </c>
+      <c r="C2349" t="n">
+        <v>73.8000030517578</v>
+      </c>
+      <c r="D2349" t="n">
+        <v>71.4000015258789</v>
+      </c>
+      <c r="E2349" t="n">
+        <v>72.3000030517578</v>
+      </c>
+      <c r="F2349" t="n">
+        <v>72.9000015258789</v>
+      </c>
+      <c r="G2349" t="n">
+        <v>72.9000015258789</v>
+      </c>
+      <c r="H2349" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -421,7 +421,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>11.8307571411133</v>
+        <v>11.8307580947876</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>11.7123670578003</v>
+        <v>11.7123651504517</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G5" t="n">
-        <v>11.0273818969727</v>
+        <v>11.027382850647</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>10.9005327224731</v>
+        <v>10.9005346298218</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1711454391479</v>
+        <v>11.1711444854736</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G12" t="n">
-        <v>11.1880578994751</v>
+        <v>11.1880569458008</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G14" t="n">
-        <v>11.0273818969727</v>
+        <v>11.027382850647</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0189266204834</v>
+        <v>11.0189256668091</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G18" t="n">
-        <v>11.1034917831421</v>
+        <v>11.1034927368164</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>11.0358390808105</v>
+        <v>11.0358400344849</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>11.1204042434692</v>
+        <v>11.1204051971436</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>10.9174461364746</v>
+        <v>10.9174480438232</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G25" t="n">
-        <v>11.1034917831421</v>
+        <v>11.1034927368164</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>10.739857673645</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>10.739857673645</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7652282714844</v>
+        <v>10.7652292251587</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0696668624878</v>
+        <v>11.0696649551392</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>10.9428157806396</v>
+        <v>10.942816734314</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G38" t="n">
-        <v>10.9343605041504</v>
+        <v>10.9343595504761</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G39" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G42" t="n">
-        <v>11.2387971878052</v>
+        <v>11.2387962341309</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.6700820922852</v>
+        <v>11.6700830459595</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G44" t="n">
-        <v>11.6700820922852</v>
+        <v>11.6700830459595</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G45" t="n">
-        <v>11.822301864624</v>
+        <v>11.8222999572754</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>11.5855169296265</v>
+        <v>11.5855178833008</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.4586668014526</v>
+        <v>11.4586687088013</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.5</v>
       </c>
       <c r="G53" t="n">
-        <v>11.4163856506348</v>
+        <v>11.4163837432861</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318176269531</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>11.2810802459717</v>
+        <v>11.2810792922974</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G58" t="n">
-        <v>11.1288604736328</v>
+        <v>11.1288614273071</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>11.1204042434692</v>
+        <v>11.1204051971436</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G63" t="n">
-        <v>11.052752494812</v>
+        <v>11.0527505874634</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G64" t="n">
-        <v>11.1542320251465</v>
+        <v>11.1542301177979</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>10.9428157806396</v>
+        <v>10.942816734314</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667068481445</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G70" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328828811646</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G71" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328828811646</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328828811646</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>10.9005327224731</v>
+        <v>10.9005346298218</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5538139343262</v>
+        <v>10.5538120269775</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.5</v>
       </c>
       <c r="G86" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G87" t="n">
-        <v>10.6806621551514</v>
+        <v>10.6806631088257</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G88" t="n">
-        <v>10.6637477874756</v>
+        <v>10.6637487411499</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.6383790969849</v>
+        <v>10.6383800506592</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G94" t="n">
-        <v>10.6383790969849</v>
+        <v>10.6383800506592</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G100" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.75</v>
       </c>
       <c r="G101" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G102" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667068481445</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G104" t="n">
-        <v>10.71448802948</v>
+        <v>10.7144908905029</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G105" t="n">
-        <v>10.6806621551514</v>
+        <v>10.6806631088257</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G108" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328828811646</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>10.799054145813</v>
+        <v>10.7990550994873</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>12.75</v>
       </c>
       <c r="G116" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>10.739857673645</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>10.739857673645</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.5</v>
       </c>
       <c r="G120" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655294418335</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>12.5</v>
       </c>
       <c r="G126" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655294418335</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655294418335</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655294418335</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>10.4438791275024</v>
+        <v>10.4438781738281</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>10.4015941619873</v>
+        <v>10.4015960693359</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>12.25</v>
       </c>
       <c r="G139" t="n">
-        <v>10.3593130111694</v>
+        <v>10.3593120574951</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>12.75</v>
       </c>
       <c r="G140" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>10.4438791275024</v>
+        <v>10.4438781738281</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>10.2324638366699</v>
+        <v>10.2324647903442</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>10.1901807785034</v>
+        <v>10.1901817321777</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G155" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655294418335</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667068481445</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>10.9089908599854</v>
+        <v>10.908989906311</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>10.739857673645</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>10.739857673645</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G163" t="n">
-        <v>10.739857673645</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>10.739857673645</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G165" t="n">
-        <v>10.739857673645</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.6130104064941</v>
+        <v>10.6130094528198</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.5</v>
       </c>
       <c r="G167" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>10.739857673645</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.5</v>
       </c>
       <c r="G169" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.75</v>
       </c>
       <c r="G170" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>12.75</v>
       </c>
       <c r="G171" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667068481445</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G177" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G179" t="n">
-        <v>10.8667078018188</v>
+        <v>10.8667068481445</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>11.1626873016357</v>
+        <v>11.1626882553101</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G185" t="n">
-        <v>11.1626873016357</v>
+        <v>11.1626882553101</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318176269531</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>11.0358390808105</v>
+        <v>11.0358400344849</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318176269531</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318176269531</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>11.4586668014526</v>
+        <v>11.4586687088013</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>11.4586668014526</v>
+        <v>11.4586687088013</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.3318185806274</v>
+        <v>11.3318176269531</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>11.5855169296265</v>
+        <v>11.5855178833008</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>13.5</v>
       </c>
       <c r="G200" t="n">
-        <v>11.4163856506348</v>
+        <v>11.4163837432861</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7869596481323</v>
+        <v>11.7869577407837</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>11.5702857971191</v>
+        <v>11.5702867507935</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>11.440281867981</v>
+        <v>11.4402828216553</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>11.5702857971191</v>
+        <v>11.5702867507935</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>11.6136198043823</v>
+        <v>11.613618850708</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>11.440281867981</v>
+        <v>11.4402828216553</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>11.6569528579712</v>
+        <v>11.6569547653198</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>13.5</v>
       </c>
       <c r="G214" t="n">
-        <v>11.700288772583</v>
+        <v>11.7002878189087</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G217" t="n">
-        <v>11.8736257553101</v>
+        <v>11.8736276626587</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>11.5269508361816</v>
+        <v>11.526951789856</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>11.5702857971191</v>
+        <v>11.5702867507935</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.6569528579712</v>
+        <v>11.6569547653198</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>11.8302907943726</v>
+        <v>11.8302917480469</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>11.8302907943726</v>
+        <v>11.8302917480469</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>11.8736257553101</v>
+        <v>11.8736276626587</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>11.9602947235107</v>
+        <v>11.9602956771851</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902976989746</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G231" t="n">
-        <v>11.8302907943726</v>
+        <v>11.8302917480469</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>11.7869596481323</v>
+        <v>11.7869577407837</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902976989746</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>13.5</v>
       </c>
       <c r="G237" t="n">
-        <v>11.700288772583</v>
+        <v>11.7002878189087</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>12.0036306381226</v>
+        <v>12.0036296844482</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902976989746</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>14.5</v>
       </c>
       <c r="G242" t="n">
-        <v>12.5669775009155</v>
+        <v>12.5669765472412</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>14.5</v>
       </c>
       <c r="G244" t="n">
-        <v>12.5669775009155</v>
+        <v>12.5669765472412</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>12.7403144836426</v>
+        <v>12.7403154373169</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>12.6969795227051</v>
+        <v>12.6969804763794</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G247" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>15</v>
       </c>
       <c r="G248" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003213882446</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8703184127808</v>
+        <v>12.8703193664551</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>13.0436553955078</v>
+        <v>13.0436563491821</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G256" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>12.9569864273071</v>
+        <v>12.9569873809814</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>12.8269844055176</v>
+        <v>12.8269834518433</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="G261" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003213882446</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>15.25</v>
       </c>
       <c r="G265" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>15</v>
       </c>
       <c r="G268" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003213882446</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>15.25</v>
       </c>
       <c r="G284" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>15.25</v>
       </c>
       <c r="G285" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>15.25</v>
       </c>
       <c r="G288" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>15.25</v>
       </c>
       <c r="G290" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>15.5</v>
       </c>
       <c r="G297" t="n">
-        <v>13.4336652755737</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>15.25</v>
       </c>
       <c r="G303" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G315" t="n">
-        <v>13.6070032119751</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>13.7803411483765</v>
+        <v>13.7803401947021</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>13.6070032119751</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G322" t="n">
-        <v>13.6070032119751</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>15.25</v>
       </c>
       <c r="G325" t="n">
-        <v>13.2169933319092</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>15</v>
       </c>
       <c r="G328" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003213882446</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>15</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0003204345703</v>
+        <v>13.0003213882446</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>15.5</v>
       </c>
       <c r="G330" t="n">
-        <v>13.4336652755737</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>15.5</v>
       </c>
       <c r="G331" t="n">
-        <v>13.4336652755737</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>15.5</v>
       </c>
       <c r="G334" t="n">
-        <v>13.4336652755737</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>15.5</v>
       </c>
       <c r="G351" t="n">
-        <v>13.4336652755737</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G353" t="n">
-        <v>13.6070032119751</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>13.6070032119751</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>15.5</v>
       </c>
       <c r="G359" t="n">
-        <v>13.4336652755737</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>13.6070032119751</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>15.5</v>
       </c>
       <c r="G371" t="n">
-        <v>13.4336652755737</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>15.5</v>
       </c>
       <c r="G372" t="n">
-        <v>13.4336652755737</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>15.5</v>
       </c>
       <c r="G375" t="n">
-        <v>13.4336652755737</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>15.5</v>
       </c>
       <c r="G382" t="n">
-        <v>13.4336652755737</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1270151138306</v>
+        <v>14.1270160675049</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>14.2136850357056</v>
+        <v>14.2136831283569</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G389" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070358276367</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>17</v>
       </c>
       <c r="G395" t="n">
-        <v>14.733696937561</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>16.75</v>
       </c>
       <c r="G397" t="n">
-        <v>14.5170249938965</v>
+        <v>14.5170259475708</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>17</v>
       </c>
       <c r="G400" t="n">
-        <v>14.733696937561</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>14.6036939620972</v>
+        <v>14.6036949157715</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G403" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>17</v>
       </c>
       <c r="G406" t="n">
-        <v>14.733696937561</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>17</v>
       </c>
       <c r="G410" t="n">
-        <v>14.733696937561</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G414" t="n">
-        <v>14.7770299911499</v>
+        <v>14.7770328521729</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6036939620972</v>
+        <v>14.6036949157715</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>16.75</v>
       </c>
       <c r="G417" t="n">
-        <v>14.5170249938965</v>
+        <v>14.5170259475708</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>16.5</v>
       </c>
       <c r="G420" t="n">
-        <v>14.3003549575806</v>
+        <v>14.3003540039062</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.5</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3003549575806</v>
+        <v>14.3003540039062</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>14.3436870574951</v>
+        <v>14.3436861038208</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>14.6036939620972</v>
+        <v>14.6036949157715</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>17</v>
       </c>
       <c r="G430" t="n">
-        <v>14.733696937561</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>17</v>
       </c>
       <c r="G432" t="n">
-        <v>14.733696937561</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>14.6036939620972</v>
+        <v>14.6036949157715</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>17</v>
       </c>
       <c r="G435" t="n">
-        <v>14.733696937561</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>14.6470260620117</v>
+        <v>14.647027015686</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G443" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070358276367</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G444" t="n">
-        <v>14.6036939620972</v>
+        <v>14.6036949157715</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>14.9937047958374</v>
+        <v>14.9937028884888</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G446" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070358276367</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G448" t="n">
-        <v>14.7770299911499</v>
+        <v>14.7770328521729</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>14.9937047958374</v>
+        <v>14.9937028884888</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265378952026</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265378952026</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>17.25</v>
       </c>
       <c r="G456" t="n">
-        <v>15.3926868438721</v>
+        <v>15.3926877975464</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265378952026</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>17.25</v>
       </c>
       <c r="G458" t="n">
-        <v>15.3926868438721</v>
+        <v>15.3926877975464</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>17</v>
       </c>
       <c r="G459" t="n">
-        <v>15.169605255127</v>
+        <v>15.1696062088013</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>15.2142200469971</v>
+        <v>15.21422290802</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G463" t="n">
-        <v>15.1249895095825</v>
+        <v>15.1249904632568</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>15.4373064041138</v>
+        <v>15.4373035430908</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>15.3480739593506</v>
+        <v>15.348072052002</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>15.3480739593506</v>
+        <v>15.348072052002</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>15.3480739593506</v>
+        <v>15.348072052002</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>15.4373064041138</v>
+        <v>15.4373035430908</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G469" t="n">
-        <v>15.7496194839478</v>
+        <v>15.7496185302734</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>15.8834686279297</v>
+        <v>15.8834705352783</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>15.8834686279297</v>
+        <v>15.8834705352783</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>17.0434970855713</v>
+        <v>17.0434989929199</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>17.0434970855713</v>
+        <v>17.0434989929199</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>19.5</v>
       </c>
       <c r="G478" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>17.0434970855713</v>
+        <v>17.0434989929199</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>19.5</v>
       </c>
       <c r="G480" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>19.5</v>
       </c>
       <c r="G481" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>17.221960067749</v>
+        <v>17.2219638824463</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>19.5</v>
       </c>
       <c r="G489" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G490" t="n">
-        <v>18.6496925354004</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>18.6496925354004</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>18.6496925354004</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604591369629</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>18.6496925354004</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>21</v>
       </c>
       <c r="G496" t="n">
-        <v>18.7389240264893</v>
+        <v>18.7389259338379</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>18.6496925354004</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>18.6496925354004</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604591369629</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604591369629</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G501" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>18.3819923400879</v>
+        <v>18.3819961547852</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G504" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G505" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G508" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>17.80198097229</v>
+        <v>17.8019790649414</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.6681308746338</v>
+        <v>17.6681289672852</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>17.6681308746338</v>
+        <v>17.6681289672852</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>19.75</v>
       </c>
       <c r="G519" t="n">
-        <v>17.623514175415</v>
+        <v>17.6235122680664</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>17.221960067749</v>
+        <v>17.2219638824463</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>19.5</v>
       </c>
       <c r="G524" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>19.5</v>
       </c>
       <c r="G525" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>19.5</v>
       </c>
       <c r="G527" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>19.5</v>
       </c>
       <c r="G528" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>17.4896640777588</v>
+        <v>17.4896659851074</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>20</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>20</v>
       </c>
       <c r="G535" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>20</v>
       </c>
       <c r="G537" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>20</v>
       </c>
       <c r="G539" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>18.3819923400879</v>
+        <v>18.3819961547852</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>18.6496925354004</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G550" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G552" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G553" t="n">
-        <v>18.3819923400879</v>
+        <v>18.3819961547852</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G555" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604591369629</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G562" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>20</v>
       </c>
       <c r="G565" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>20</v>
       </c>
       <c r="G566" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>20</v>
       </c>
       <c r="G567" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>20</v>
       </c>
       <c r="G568" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>17.6681308746338</v>
+        <v>17.6681289672852</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>20</v>
       </c>
       <c r="G570" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>20</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>20</v>
       </c>
       <c r="G572" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>19.75</v>
       </c>
       <c r="G574" t="n">
-        <v>17.623514175415</v>
+        <v>17.6235122680664</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>18.2035255432129</v>
+        <v>18.2035274505615</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>21</v>
       </c>
       <c r="G585" t="n">
-        <v>18.7389240264893</v>
+        <v>18.7389259338379</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>19.0958557128906</v>
+        <v>19.0958576202393</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G587" t="n">
-        <v>18.8281593322754</v>
+        <v>18.8281574249268</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>21.5</v>
       </c>
       <c r="G589" t="n">
-        <v>19.1850910186768</v>
+        <v>19.1850891113281</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>21.5</v>
       </c>
       <c r="G592" t="n">
-        <v>19.1850910186768</v>
+        <v>19.1850891113281</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>19.3635578155518</v>
+        <v>19.3635559082031</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>19.2743225097656</v>
+        <v>19.2743244171143</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>19.809720993042</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420188903809</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>20.1666526794434</v>
+        <v>20.166654586792</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>20.1666526794434</v>
+        <v>20.166654586792</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>19.809720993042</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>19.3635578155518</v>
+        <v>19.3635559082031</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420188903809</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420188903809</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>19.2743225097656</v>
+        <v>19.2743244171143</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>19.2743225097656</v>
+        <v>19.2743244171143</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420188903809</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>19.809720993042</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>20.7912826538086</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>21.5051498413086</v>
+        <v>21.50514793396</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G623" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>21.5051498413086</v>
+        <v>21.50514793396</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>24.5</v>
       </c>
       <c r="G627" t="n">
-        <v>21.8620796203613</v>
+        <v>21.8620777130127</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>21.7728443145752</v>
+        <v>21.7728462219238</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>21.5943813323975</v>
+        <v>21.5943832397461</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>24</v>
       </c>
       <c r="G631" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>21.5943813323975</v>
+        <v>21.5943832397461</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>21.6836128234863</v>
+        <v>21.6836109161377</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>21.6836128234863</v>
+        <v>21.6836109161377</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G635" t="n">
-        <v>21.5943813323975</v>
+        <v>21.5943832397461</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>24</v>
       </c>
       <c r="G637" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>21.5943813323975</v>
+        <v>21.5943832397461</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>21.0589847564697</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>23.5</v>
       </c>
       <c r="G640" t="n">
-        <v>20.969747543335</v>
+        <v>20.9697513580322</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>21.0589847564697</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>20.7912826538086</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>21.5943813323975</v>
+        <v>21.5943832397461</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G645" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>24</v>
       </c>
       <c r="G648" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>24</v>
       </c>
       <c r="G649" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>24</v>
       </c>
       <c r="G650" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G654" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G655" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>23.5</v>
       </c>
       <c r="G661" t="n">
-        <v>20.969747543335</v>
+        <v>20.9697513580322</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>23</v>
       </c>
       <c r="G662" t="n">
-        <v>20.5235862731934</v>
+        <v>20.5235843658447</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>22.5</v>
       </c>
       <c r="G664" t="n">
-        <v>20.0774173736572</v>
+        <v>20.0774192810059</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420188903809</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>19.3635578155518</v>
+        <v>19.3635559082031</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420188903809</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G669" t="n">
-        <v>18.6496925354004</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>17.4896640777588</v>
+        <v>17.4896659851074</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>16.1957817077637</v>
+        <v>16.1957836151123</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>18</v>
       </c>
       <c r="G675" t="n">
-        <v>16.0619354248047</v>
+        <v>16.0619373321533</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>17.5</v>
       </c>
       <c r="G676" t="n">
-        <v>15.6157703399658</v>
+        <v>15.6157722473145</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>14.9019088745117</v>
+        <v>14.9019069671631</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>15.035756111145</v>
+        <v>15.0357570648193</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>15.7496194839478</v>
+        <v>15.7496185302734</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604591369629</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250625610352</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>20.7912826538086</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G689" t="n">
-        <v>21.14821434021</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>23</v>
       </c>
       <c r="G690" t="n">
-        <v>20.5235862731934</v>
+        <v>20.5235843658447</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>23.5</v>
       </c>
       <c r="G693" t="n">
-        <v>20.969747543335</v>
+        <v>20.9697513580322</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>21.6836128234863</v>
+        <v>21.6836109161377</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>21.5943813323975</v>
+        <v>21.5943832397461</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G696" t="n">
-        <v>21.0589847564697</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>21.5943813323975</v>
+        <v>21.5943832397461</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>24</v>
       </c>
       <c r="G699" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>21.0589847564697</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>24</v>
       </c>
       <c r="G704" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>21.5943813323975</v>
+        <v>21.5943832397461</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>24</v>
       </c>
       <c r="G706" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>24</v>
       </c>
       <c r="G707" t="n">
-        <v>21.4159145355225</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>21.5943813323975</v>
+        <v>21.5943832397461</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G709" t="n">
-        <v>21.6836128234863</v>
+        <v>21.6836109161377</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>22.040548324585</v>
+        <v>22.0405445098877</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678817749023</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860237121582</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860237121582</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860237121582</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>24.5</v>
       </c>
       <c r="G717" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769508361816</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860237121582</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>24.5</v>
       </c>
       <c r="G719" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769508361816</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>22.4588088989258</v>
+        <v>22.4588050842285</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>24.5</v>
       </c>
       <c r="G721" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769508361816</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678817749023</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>24.5</v>
       </c>
       <c r="G725" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769508361816</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>24.5</v>
       </c>
       <c r="G728" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769508361816</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>22.0041770935059</v>
+        <v>22.0041751861572</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>22.0950984954834</v>
+        <v>22.095100402832</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>21.7313957214355</v>
+        <v>21.7313938140869</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G732" t="n">
-        <v>21.7313957214355</v>
+        <v>21.7313938140869</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>24</v>
       </c>
       <c r="G733" t="n">
-        <v>21.822322845459</v>
+        <v>21.8223209381104</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>23.5</v>
       </c>
       <c r="G734" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>23.5</v>
       </c>
       <c r="G740" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>23.5</v>
       </c>
       <c r="G741" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>23.5</v>
       </c>
       <c r="G742" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>20.5493507385254</v>
+        <v>20.549352645874</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767639160156</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>23.5</v>
       </c>
       <c r="G749" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>23.5</v>
       </c>
       <c r="G750" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>24</v>
       </c>
       <c r="G751" t="n">
-        <v>21.822322845459</v>
+        <v>21.8223209381104</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>24</v>
       </c>
       <c r="G752" t="n">
-        <v>21.822322845459</v>
+        <v>21.8223209381104</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>22.0041770935059</v>
+        <v>22.0041751861572</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>21.7313957214355</v>
+        <v>21.7313938140869</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>21.7313957214355</v>
+        <v>21.7313938140869</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>23.5</v>
       </c>
       <c r="G758" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767639160156</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>23.5</v>
       </c>
       <c r="G763" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>23.5</v>
       </c>
       <c r="G765" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G769" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G776" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767639160156</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767639160156</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767639160156</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>23.5</v>
       </c>
       <c r="G786" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>23.5</v>
       </c>
       <c r="G787" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676891326904</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858348846436</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>20.5493507385254</v>
+        <v>20.549352645874</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>20.3675003051758</v>
+        <v>20.3674983978271</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G800" t="n">
-        <v>20.5493507385254</v>
+        <v>20.549352645874</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039825439453</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>22.0041770935059</v>
+        <v>22.0041751861572</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860237121582</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G804" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678817749023</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>23.5499229431152</v>
+        <v>23.5499210357666</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>22.9134407043457</v>
+        <v>22.9134368896484</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.5501098632812</v>
+        <v>24.5501136779785</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>24.0045509338379</v>
+        <v>24.0045528411865</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>23.368070602417</v>
+        <v>23.3680686950684</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>24.0045509338379</v>
+        <v>24.0045528411865</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>26.5</v>
       </c>
       <c r="G813" t="n">
-        <v>24.09547996521</v>
+        <v>24.0954780578613</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>24.2773303985596</v>
+        <v>24.2773323059082</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>26.5</v>
       </c>
       <c r="G815" t="n">
-        <v>24.09547996521</v>
+        <v>24.0954780578613</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7319660186768</v>
+        <v>24.7319641113281</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.9138145446777</v>
+        <v>24.9138164520264</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.9138145446777</v>
+        <v>24.9138164520264</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>27.5</v>
       </c>
       <c r="G819" t="n">
-        <v>25.0047397613525</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>28</v>
       </c>
       <c r="G820" t="n">
-        <v>25.4593772888184</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>26.0958595275879</v>
+        <v>26.0958576202393</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>26.0958595275879</v>
+        <v>26.0958576202393</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>27.5</v>
       </c>
       <c r="G825" t="n">
-        <v>25.0047397613525</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>24.9138145446777</v>
+        <v>24.9138164520264</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>27.5</v>
       </c>
       <c r="G830" t="n">
-        <v>25.0047397613525</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>27</v>
       </c>
       <c r="G832" t="n">
-        <v>24.5501098632812</v>
+        <v>24.5501136779785</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>24.2773303985596</v>
+        <v>24.2773323059082</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>27.5</v>
       </c>
       <c r="G836" t="n">
-        <v>25.0047397613525</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>25.7321548461914</v>
+        <v>25.7321529388428</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>28.5</v>
       </c>
       <c r="G839" t="n">
-        <v>25.9140071868896</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>25.8230781555176</v>
+        <v>25.8230800628662</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>28</v>
       </c>
       <c r="G842" t="n">
-        <v>25.4593772888184</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>28</v>
       </c>
       <c r="G843" t="n">
-        <v>25.4593772888184</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G847" t="n">
-        <v>26.0958595275879</v>
+        <v>26.0958576202393</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>28.5</v>
       </c>
       <c r="G848" t="n">
-        <v>25.9140071868896</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>28.5</v>
       </c>
       <c r="G849" t="n">
-        <v>25.9140071868896</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>28</v>
       </c>
       <c r="G851" t="n">
-        <v>25.4593772888184</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>25.8230781555176</v>
+        <v>25.8230800628662</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>28.5</v>
       </c>
       <c r="G856" t="n">
-        <v>25.9140071868896</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>29.005500793457</v>
+        <v>29.0054988861084</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>29.7329158782959</v>
+        <v>29.7329120635986</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G861" t="n">
-        <v>30.2784729003906</v>
+        <v>30.278470993042</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>32.5</v>
       </c>
       <c r="G862" t="n">
-        <v>29.5510597229004</v>
+        <v>29.5510578155518</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>29.6419849395752</v>
+        <v>29.6419868469238</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>30.6421756744385</v>
+        <v>30.6421813964844</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G866" t="n">
-        <v>31.7332954406738</v>
+        <v>31.7332916259766</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>31.1877365112305</v>
+        <v>31.1877326965332</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>31.7332954406738</v>
+        <v>31.7332916259766</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>34.2792320251465</v>
+        <v>34.2792358398438</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>35.643123626709</v>
+        <v>35.6431312561035</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G874" t="n">
-        <v>36.0068283081055</v>
+        <v>36.0068244934082</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>34.1882972717285</v>
+        <v>34.1883010864258</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>35.1884956359863</v>
+        <v>35.1884918212891</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G882" t="n">
-        <v>34.1882972717285</v>
+        <v>34.1883010864258</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>34.8247871398926</v>
+        <v>34.8247833251953</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>34.1882972717285</v>
+        <v>34.1883010864258</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G888" t="n">
-        <v>34.6429328918457</v>
+        <v>34.642936706543</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>34.8247871398926</v>
+        <v>34.8247833251953</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>34.6429328918457</v>
+        <v>34.642936706543</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G896" t="n">
-        <v>34.2792320251465</v>
+        <v>34.2792358398438</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G898" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336654663086</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>38</v>
       </c>
       <c r="G903" t="n">
-        <v>34.5520133972168</v>
+        <v>34.5520095825195</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>34.8247871398926</v>
+        <v>34.8247833251953</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336654663086</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G911" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336654663086</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G912" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336654663086</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>32.9153366088867</v>
+        <v>32.9153327941895</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>36.5</v>
       </c>
       <c r="G919" t="n">
-        <v>33.1881103515625</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G921" t="n">
-        <v>32.9153366088867</v>
+        <v>32.9153327941895</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>36.5</v>
       </c>
       <c r="G923" t="n">
-        <v>33.1881103515625</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>36.5</v>
       </c>
       <c r="G924" t="n">
-        <v>33.1881103515625</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>32.1879234313965</v>
+        <v>32.1879196166992</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>36</v>
       </c>
       <c r="G929" t="n">
-        <v>32.7334861755371</v>
+        <v>32.7334823608398</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.5518226623535</v>
+        <v>33.5518188476562</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>35.2794151306152</v>
+        <v>35.2794189453125</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.1882972717285</v>
+        <v>34.1883010864258</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G940" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336654663086</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G945" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G948" t="n">
-        <v>33.9155235290527</v>
+        <v>33.91552734375</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>33.4608955383301</v>
+        <v>33.4608917236328</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G955" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336654663086</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7336730957031</v>
+        <v>33.7336654663086</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>33.4608955383301</v>
+        <v>33.4608917236328</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>34.3592376708984</v>
+        <v>34.3592300415039</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>34.5444602966309</v>
+        <v>34.5444564819336</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G965" t="n">
-        <v>34.5444602966309</v>
+        <v>34.5444564819336</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G966" t="n">
-        <v>34.1740112304688</v>
+        <v>34.1740074157715</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>34.1740112304688</v>
+        <v>34.1740074157715</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>36.5</v>
       </c>
       <c r="G969" t="n">
-        <v>33.8035583496094</v>
+        <v>33.8035621643066</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G971" t="n">
-        <v>34.1740112304688</v>
+        <v>34.1740074157715</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>36.5</v>
       </c>
       <c r="G974" t="n">
-        <v>33.8035583496094</v>
+        <v>33.8035621643066</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>36.5</v>
       </c>
       <c r="G975" t="n">
-        <v>33.8035583496094</v>
+        <v>33.8035621643066</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>33.5257263183594</v>
+        <v>33.5257225036621</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>33.6183319091797</v>
+        <v>33.618335723877</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>33.6183319091797</v>
+        <v>33.618335723877</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3404998779297</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>36</v>
       </c>
       <c r="G981" t="n">
-        <v>33.3404998779297</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>36.5</v>
       </c>
       <c r="G983" t="n">
-        <v>33.8035583496094</v>
+        <v>33.8035621643066</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G984" t="n">
-        <v>33.5257263183594</v>
+        <v>33.5257225036621</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G988" t="n">
-        <v>39.1750869750977</v>
+        <v>39.1750831604004</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>46.5</v>
       </c>
       <c r="G990" t="n">
-        <v>43.0648078918457</v>
+        <v>43.064811706543</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>42.2312927246094</v>
+        <v>42.2313003540039</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>41.5830078125</v>
+        <v>41.5830116271973</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G994" t="n">
-        <v>42.4165191650391</v>
+        <v>42.4165229797363</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>44.361385345459</v>
+        <v>44.3613891601562</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>45.9357948303223</v>
+        <v>45.935791015625</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>48.9000015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>45.2875137329102</v>
+        <v>45.2875061035156</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>49.5</v>
       </c>
       <c r="G998" t="n">
-        <v>45.8431816101074</v>
+        <v>45.8431854248047</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>45.4727325439453</v>
+        <v>45.4727363586426</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>45.1022834777832</v>
+        <v>45.1022796630859</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1001" t="n">
-        <v>46.121021270752</v>
+        <v>46.1210250854492</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>45.5653457641602</v>
+        <v>45.5653495788574</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>49.5</v>
       </c>
       <c r="G1003" t="n">
-        <v>45.8431816101074</v>
+        <v>45.8431854248047</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G1004" t="n">
-        <v>45.1948928833008</v>
+        <v>45.194896697998</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>46.121021270752</v>
+        <v>46.1210250854492</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>50</v>
       </c>
       <c r="G1008" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>50</v>
       </c>
       <c r="G1010" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>50</v>
       </c>
       <c r="G1011" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>46.121021270752</v>
+        <v>46.1210250854492</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G1015" t="n">
-        <v>45.1022834777832</v>
+        <v>45.1022796630859</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>46.8619232177734</v>
+        <v>46.8619155883789</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>50</v>
       </c>
       <c r="G1020" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>49.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>45.8431816101074</v>
+        <v>45.8431854248047</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>54</v>
       </c>
       <c r="G1023" t="n">
-        <v>50.0107421875</v>
+        <v>50.0107460021973</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>48.8993949890137</v>
+        <v>48.8993911743164</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>56</v>
       </c>
       <c r="G1026" t="n">
-        <v>51.8629989624023</v>
+        <v>51.8629951477051</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>53.5300178527832</v>
+        <v>53.5300216674805</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>60</v>
       </c>
       <c r="G1028" t="n">
-        <v>55.5674934387207</v>
+        <v>55.567497253418</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>58.16064453125</v>
+        <v>58.1606483459473</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1038" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>55.0118255615234</v>
+        <v>55.0118179321289</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>56.3083953857422</v>
+        <v>56.3083915710449</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>59.6424446105957</v>
+        <v>59.6424522399902</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>65</v>
       </c>
       <c r="G1043" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>59.8276672363281</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1047" t="n">
-        <v>62.7912826538086</v>
+        <v>62.7912750244141</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>70</v>
       </c>
       <c r="G1054" t="n">
-        <v>64.8287506103516</v>
+        <v>64.828742980957</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>68.5999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>63.5321769714355</v>
+        <v>63.5321617126465</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>66</v>
       </c>
       <c r="G1056" t="n">
-        <v>61.1242485046387</v>
+        <v>61.1242446899414</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>61.6799201965332</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>61.6799201965332</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>69</v>
       </c>
       <c r="G1059" t="n">
-        <v>63.9026145935059</v>
+        <v>63.9026222229004</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>67</v>
       </c>
       <c r="G1060" t="n">
-        <v>62.0503692626953</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1061" t="n">
-        <v>62.2355918884277</v>
+        <v>62.235595703125</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1064" t="n">
-        <v>61.6799201965332</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>60.5685729980469</v>
+        <v>60.5685691833496</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1066" t="n">
-        <v>58.16064453125</v>
+        <v>58.1606483459473</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>63</v>
       </c>
       <c r="G1070" t="n">
-        <v>58.3458671569824</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>64</v>
       </c>
       <c r="G1071" t="n">
-        <v>59.2719955444336</v>
+        <v>59.2719917297363</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1072" t="n">
-        <v>57.9754219055176</v>
+        <v>57.975414276123</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1078" t="n">
-        <v>63.3469390869141</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1079" t="n">
-        <v>61.3094673156738</v>
+        <v>61.3094635009766</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1080" t="n">
-        <v>63.3469390869141</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1081" t="n">
-        <v>63.3469390869141</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>69</v>
       </c>
       <c r="G1082" t="n">
-        <v>63.9026145935059</v>
+        <v>63.9026222229004</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>68</v>
       </c>
       <c r="G1083" t="n">
-        <v>62.9764938354492</v>
+        <v>62.9764862060547</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>67</v>
       </c>
       <c r="G1084" t="n">
-        <v>62.0503692626953</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>67</v>
       </c>
       <c r="G1085" t="n">
-        <v>62.0503692626953</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>62.7912826538086</v>
+        <v>62.7912750244141</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>68</v>
       </c>
       <c r="G1087" t="n">
-        <v>62.9764938354492</v>
+        <v>62.9764862060547</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1088" t="n">
-        <v>63.3469390869141</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>68</v>
       </c>
       <c r="G1089" t="n">
-        <v>62.9764938354492</v>
+        <v>62.9764862060547</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>72</v>
       </c>
       <c r="G1091" t="n">
-        <v>66.6809997558594</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G1094" t="n">
-        <v>65.0139541625977</v>
+        <v>65.0139694213867</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G1097" t="n">
-        <v>65.9400939941406</v>
+        <v>65.9400863647461</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G1103" t="n">
-        <v>65.0139541625977</v>
+        <v>65.0139694213867</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1104" t="n">
-        <v>64.0878448486328</v>
+        <v>64.0878372192383</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>74</v>
       </c>
       <c r="G1107" t="n">
-        <v>68.5332336425781</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1108" t="n">
-        <v>70.2002639770508</v>
+        <v>70.2002792358398</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>74</v>
       </c>
       <c r="G1109" t="n">
-        <v>68.5332336425781</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>75.1999969482422</v>
       </c>
       <c r="G1110" t="n">
-        <v>69.6445846557617</v>
+        <v>69.6445922851562</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>74</v>
       </c>
       <c r="G1113" t="n">
-        <v>68.5332336425781</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>69.0889205932617</v>
+        <v>69.0889129638672</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>73</v>
       </c>
       <c r="G1119" t="n">
-        <v>67.6071166992188</v>
+        <v>67.6071243286133</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>73</v>
       </c>
       <c r="G1121" t="n">
-        <v>67.6071166992188</v>
+        <v>67.6071243286133</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>72</v>
       </c>
       <c r="G1123" t="n">
-        <v>66.6809997558594</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>74</v>
       </c>
       <c r="G1125" t="n">
-        <v>68.5332336425781</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>73</v>
       </c>
       <c r="G1130" t="n">
-        <v>67.6071166992188</v>
+        <v>67.6071243286133</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1131" t="n">
-        <v>69.0889205932617</v>
+        <v>69.0889129638672</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1134" t="n">
-        <v>70.2002639770508</v>
+        <v>70.2002792358398</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>73.8000030517578</v>
       </c>
       <c r="G1138" t="n">
-        <v>68.3480224609375</v>
+        <v>68.348014831543</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>74</v>
       </c>
       <c r="G1139" t="n">
-        <v>68.5332336425781</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>70</v>
       </c>
       <c r="G1143" t="n">
-        <v>64.8287506103516</v>
+        <v>64.828742980957</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1144" t="n">
-        <v>63.3469390869141</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1145" t="n">
-        <v>64.6435165405273</v>
+        <v>64.6435241699219</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>67</v>
       </c>
       <c r="G1149" t="n">
-        <v>62.0503692626953</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>66</v>
       </c>
       <c r="G1150" t="n">
-        <v>61.1242485046387</v>
+        <v>61.1242446899414</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1151" t="n">
-        <v>61.6799201965332</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1152" t="n">
-        <v>61.3094673156738</v>
+        <v>61.3094635009766</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>66</v>
       </c>
       <c r="G1153" t="n">
-        <v>61.1242485046387</v>
+        <v>61.1242446899414</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>60.9390182495117</v>
+        <v>60.939022064209</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>66</v>
       </c>
       <c r="G1156" t="n">
-        <v>61.1242485046387</v>
+        <v>61.1242446899414</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>65</v>
       </c>
       <c r="G1158" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>59.8276672363281</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>57.9754219055176</v>
+        <v>57.975414276123</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1166" t="n">
-        <v>57.9754219055176</v>
+        <v>57.975414276123</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>63</v>
       </c>
       <c r="G1168" t="n">
-        <v>58.3458671569824</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1170" t="n">
-        <v>56.3083953857422</v>
+        <v>56.3083915710449</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>60</v>
       </c>
       <c r="G1171" t="n">
-        <v>55.5674934387207</v>
+        <v>55.567497253418</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>58.16064453125</v>
+        <v>58.1606483459473</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1174" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>53.5300178527832</v>
+        <v>53.5300216674805</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>56</v>
       </c>
       <c r="G1178" t="n">
-        <v>51.8629989624023</v>
+        <v>51.8629951477051</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1179" t="n">
-        <v>51.3073234558105</v>
+        <v>51.307315826416</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>52.2334442138672</v>
+        <v>52.2334480285645</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1184" t="n">
-        <v>55.3822708129883</v>
+        <v>55.382266998291</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>60</v>
       </c>
       <c r="G1187" t="n">
-        <v>55.5674934387207</v>
+        <v>55.567497253418</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>60.5685729980469</v>
+        <v>60.5685691833496</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1189" t="n">
-        <v>61.3094673156738</v>
+        <v>61.3094635009766</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1190" t="n">
-        <v>60.9390182495117</v>
+        <v>60.939022064209</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>65</v>
       </c>
       <c r="G1191" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1193" t="n">
-        <v>59.8276672363281</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1194" t="n">
-        <v>59.8276672363281</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>63</v>
       </c>
       <c r="G1196" t="n">
-        <v>58.3458671569824</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1198" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>65</v>
       </c>
       <c r="G1199" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>63.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>58.8089332580566</v>
+        <v>58.8089370727539</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1202" t="n">
-        <v>61.8651504516602</v>
+        <v>61.8651466369629</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>67</v>
       </c>
       <c r="G1206" t="n">
-        <v>62.0503692626953</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>65</v>
       </c>
       <c r="G1207" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>65</v>
       </c>
       <c r="G1208" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>65</v>
       </c>
       <c r="G1209" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>65</v>
       </c>
       <c r="G1210" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1211" t="n">
-        <v>59.920280456543</v>
+        <v>59.9202766418457</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>58.6237106323242</v>
+        <v>58.623706817627</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>58.16064453125</v>
+        <v>58.1606483459473</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>63</v>
       </c>
       <c r="G1214" t="n">
-        <v>58.3458671569824</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1215" t="n">
-        <v>60.1055107116699</v>
+        <v>60.1055068969727</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>63.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>59.4594116210938</v>
+        <v>59.459415435791</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>56.3693923950195</v>
+        <v>56.3694000244141</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1222" t="n">
-        <v>54.1221084594727</v>
+        <v>54.1221122741699</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>56.2757606506348</v>
+        <v>56.2757568359375</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G1225" t="n">
-        <v>56.8375816345215</v>
+        <v>56.8375778198242</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>57.0248527526855</v>
+        <v>57.0248565673828</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1228" t="n">
-        <v>56.0884857177734</v>
+        <v>56.0884895324707</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G1230" t="n">
-        <v>57.0248527526855</v>
+        <v>57.0248565673828</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>57.8675842285156</v>
+        <v>57.8675880432129</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G1235" t="n">
-        <v>57.9612274169922</v>
+        <v>57.9612236022949</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1238" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>66</v>
       </c>
       <c r="G1239" t="n">
-        <v>61.8003387451172</v>
+        <v>61.8003311157227</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>63.5</v>
       </c>
       <c r="G1241" t="n">
-        <v>59.4594116210938</v>
+        <v>59.459415435791</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>61.5</v>
       </c>
       <c r="G1244" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>56.7439384460449</v>
+        <v>56.7439422607422</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>55.9948501586914</v>
+        <v>55.9948463439941</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>56.3693923950195</v>
+        <v>56.3694000244141</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1257" t="n">
-        <v>56.9312171936035</v>
+        <v>56.9312133789062</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>60.2999992370605</v>
       </c>
       <c r="G1259" t="n">
-        <v>56.4630317687988</v>
+        <v>56.4630279541016</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>67</v>
       </c>
       <c r="G1265" t="n">
-        <v>62.736701965332</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1268" t="n">
-        <v>60.7703323364258</v>
+        <v>60.7703247070312</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>63</v>
       </c>
       <c r="G1269" t="n">
-        <v>58.9912261962891</v>
+        <v>58.9912300109863</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1272" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1277" t="n">
-        <v>61.4257850646973</v>
+        <v>61.42578125</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1278" t="n">
-        <v>62.5494346618652</v>
+        <v>62.549430847168</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1279" t="n">
-        <v>62.4557914733887</v>
+        <v>62.4557876586914</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G1282" t="n">
-        <v>64.3285293579102</v>
+        <v>64.3285217285156</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>68</v>
       </c>
       <c r="G1283" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730613708496</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1284" t="n">
-        <v>64.7967147827148</v>
+        <v>64.7967071533203</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>67</v>
       </c>
       <c r="G1285" t="n">
-        <v>62.736701965332</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>68</v>
       </c>
       <c r="G1286" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730613708496</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>69</v>
       </c>
       <c r="G1288" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>68.1999969482422</v>
       </c>
       <c r="G1291" t="n">
-        <v>63.8603439331055</v>
+        <v>63.8603363037109</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>63.7667045593262</v>
+        <v>63.7667083740234</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>67.5999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>63.2985153198242</v>
+        <v>63.2985229492188</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1294" t="n">
-        <v>62.5494346618652</v>
+        <v>62.549430847168</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>67</v>
       </c>
       <c r="G1295" t="n">
-        <v>62.736701965332</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>69</v>
       </c>
       <c r="G1298" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>69</v>
       </c>
       <c r="G1299" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1303" t="n">
-        <v>63.5794334411621</v>
+        <v>63.5794410705566</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>70</v>
       </c>
       <c r="G1304" t="n">
-        <v>65.5458145141602</v>
+        <v>65.5458068847656</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G1305" t="n">
-        <v>64.8903579711914</v>
+        <v>64.8903503417969</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>71.0999984741211</v>
       </c>
       <c r="G1310" t="n">
-        <v>66.575813293457</v>
+        <v>66.5758056640625</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>70.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>66.0139923095703</v>
+        <v>66.0139999389648</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>70</v>
       </c>
       <c r="G1313" t="n">
-        <v>65.5458145141602</v>
+        <v>65.5458068847656</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>68</v>
       </c>
       <c r="G1316" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730613708496</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>66.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>62.2685089111328</v>
+        <v>62.2685127258301</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1318" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>66.3000030517578</v>
       </c>
       <c r="G1324" t="n">
-        <v>62.0812454223633</v>
+        <v>62.0812492370605</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1325" t="n">
-        <v>61.4257850646973</v>
+        <v>61.42578125</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>66</v>
       </c>
       <c r="G1326" t="n">
-        <v>61.8003387451172</v>
+        <v>61.8003311157227</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>66</v>
       </c>
       <c r="G1327" t="n">
-        <v>61.8003387451172</v>
+        <v>61.8003311157227</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1328" t="n">
-        <v>60.7703323364258</v>
+        <v>60.7703247070312</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1329" t="n">
-        <v>61.4257850646973</v>
+        <v>61.42578125</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1330" t="n">
-        <v>60.7703323364258</v>
+        <v>60.7703247070312</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1331" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1332" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1333" t="n">
-        <v>60.4894142150879</v>
+        <v>60.4894180297852</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G1335" t="n">
-        <v>60.9575996398926</v>
+        <v>60.9576034545898</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1337" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G1338" t="n">
-        <v>60.9575996398926</v>
+        <v>60.9576034545898</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1340" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1341" t="n">
-        <v>61.987606048584</v>
+        <v>61.9876022338867</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1342" t="n">
-        <v>61.987606048584</v>
+        <v>61.9876022338867</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1343" t="n">
-        <v>61.987606048584</v>
+        <v>61.9876022338867</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>68</v>
       </c>
       <c r="G1344" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730613708496</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1345" t="n">
-        <v>63.4858093261719</v>
+        <v>63.4858055114746</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G1347" t="n">
-        <v>63.0176200866699</v>
+        <v>63.0176162719727</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>66.9000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>62.6430625915527</v>
+        <v>62.64306640625</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>66.5</v>
       </c>
       <c r="G1349" t="n">
-        <v>62.2685089111328</v>
+        <v>62.2685127258301</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1350" t="n">
-        <v>62.5494346618652</v>
+        <v>62.549430847168</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1351" t="n">
-        <v>62.4557914733887</v>
+        <v>62.4557876586914</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1352" t="n">
-        <v>62.4557914733887</v>
+        <v>62.4557876586914</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1353" t="n">
-        <v>63.5794334411621</v>
+        <v>63.5794410705566</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>67</v>
       </c>
       <c r="G1354" t="n">
-        <v>62.736701965332</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1355" t="n">
-        <v>62.5494346618652</v>
+        <v>62.549430847168</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1356" t="n">
-        <v>61.4257850646973</v>
+        <v>61.42578125</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1357" t="n">
-        <v>60.4894142150879</v>
+        <v>60.4894180297852</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1362" t="n">
-        <v>60.4894142150879</v>
+        <v>60.4894180297852</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G1365" t="n">
-        <v>57.9612274169922</v>
+        <v>57.9612236022949</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1366" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>59.6466865539551</v>
+        <v>59.6466827392578</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1370" t="n">
-        <v>58.8975944519043</v>
+        <v>58.897590637207</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>57.680305480957</v>
+        <v>57.6803092956543</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1375" t="n">
-        <v>58.6166839599609</v>
+        <v>58.6166763305664</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1376" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1377" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G1378" t="n">
-        <v>59.0848617553711</v>
+        <v>59.0848655700684</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>63</v>
       </c>
       <c r="G1381" t="n">
-        <v>58.9912261962891</v>
+        <v>58.9912300109863</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1382" t="n">
-        <v>58.8975944519043</v>
+        <v>58.897590637207</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1387" t="n">
-        <v>58.6166839599609</v>
+        <v>58.6166763305664</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G1388" t="n">
-        <v>58.335765838623</v>
+        <v>58.3357696533203</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G1392" t="n">
-        <v>59.8339614868164</v>
+        <v>59.8339576721191</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1396" t="n">
-        <v>58.8975944519043</v>
+        <v>58.897590637207</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>58.335765838623</v>
+        <v>58.3357696533203</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>63</v>
       </c>
       <c r="G1398" t="n">
-        <v>58.9912261962891</v>
+        <v>58.9912300109863</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>61.5</v>
       </c>
       <c r="G1403" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>61.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1407" t="n">
-        <v>55.9948501586914</v>
+        <v>55.9948463439941</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1409" t="n">
-        <v>56.9312171936035</v>
+        <v>56.9312133789062</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1413" t="n">
-        <v>55.3393859863281</v>
+        <v>55.3393898010254</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1415" t="n">
-        <v>56.2757606506348</v>
+        <v>56.2757568359375</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>56.0884857177734</v>
+        <v>56.0884895324707</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>61.5</v>
       </c>
       <c r="G1420" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>60.2999992370605</v>
       </c>
       <c r="G1421" t="n">
-        <v>56.4630317687988</v>
+        <v>56.4630279541016</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>56.3693923950195</v>
+        <v>56.3694000244141</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1423" t="n">
-        <v>56.0884857177734</v>
+        <v>56.0884895324707</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G1425" t="n">
-        <v>57.9612274169922</v>
+        <v>57.9612236022949</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>61.5</v>
       </c>
       <c r="G1427" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1431" t="n">
-        <v>56.2757606506348</v>
+        <v>56.2757568359375</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1432" t="n">
-        <v>56.9312171936035</v>
+        <v>56.9312133789062</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G1433" t="n">
-        <v>56.8375816345215</v>
+        <v>56.8375778198242</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1435" t="n">
-        <v>56.7439384460449</v>
+        <v>56.7439422607422</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>57.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>53.8411979675293</v>
+        <v>53.8412017822266</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1438" t="n">
-        <v>53.4666519165039</v>
+        <v>53.4666481018066</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>56</v>
       </c>
       <c r="G1439" t="n">
-        <v>52.4366493225098</v>
+        <v>52.4366455078125</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>56</v>
       </c>
       <c r="G1441" t="n">
-        <v>52.4366493225098</v>
+        <v>52.4366455078125</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>53.0921058654785</v>
+        <v>53.0921020507812</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>53.4666519165039</v>
+        <v>53.4666481018066</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G1447" t="n">
-        <v>52.9984664916992</v>
+        <v>52.9984703063965</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>56</v>
       </c>
       <c r="G1448" t="n">
-        <v>52.4366493225098</v>
+        <v>52.4366455078125</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>56</v>
       </c>
       <c r="G1451" t="n">
-        <v>52.4366493225098</v>
+        <v>52.4366455078125</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>52.1557350158691</v>
+        <v>52.1557388305664</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>55</v>
       </c>
       <c r="G1456" t="n">
-        <v>51.5002746582031</v>
+        <v>51.5002784729004</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>50.8448143005371</v>
+        <v>50.8448181152344</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>51.2193641662598</v>
+        <v>51.2193717956543</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>54</v>
       </c>
       <c r="G1461" t="n">
-        <v>50.563907623291</v>
+        <v>50.5639114379883</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G1462" t="n">
-        <v>49.814811706543</v>
+        <v>49.8148155212402</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1463" t="n">
-        <v>50.376636505127</v>
+        <v>50.3766326904297</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1466" t="n">
-        <v>50.0020866394043</v>
+        <v>50.0020942687988</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G1467" t="n">
-        <v>50.1893577575684</v>
+        <v>50.1893615722656</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>50</v>
       </c>
       <c r="G1469" t="n">
-        <v>46.8184356689453</v>
+        <v>46.818431854248</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>47.192985534668</v>
+        <v>47.1929817199707</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1473" t="n">
-        <v>48.5975379943848</v>
+        <v>48.5975341796875</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1475" t="n">
-        <v>48.5975379943848</v>
+        <v>48.5975341796875</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -61446,6 +61446,32 @@
         <v>72.9000015258789</v>
       </c>
       <c r="H2349" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2350" t="n">
+        <v>4668</v>
+      </c>
+      <c r="C2350" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="D2350" t="n">
+        <v>72.6999969482422</v>
+      </c>
+      <c r="E2350" t="n">
+        <v>73.0999984741211</v>
+      </c>
+      <c r="F2350" t="n">
+        <v>72.8000030517578</v>
+      </c>
+      <c r="G2350" t="n">
+        <v>72.8000030517578</v>
+      </c>
+      <c r="H2350" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -456,7 +456,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>11.7123670578003</v>
+        <v>11.712366104126</v>
       </c>
       <c r="H3" t="n">
         <v>99700</v>
@@ -485,7 +485,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G4" t="n">
-        <v>11.1796026229858</v>
+        <v>11.1796007156372</v>
       </c>
       <c r="H4" t="n">
         <v>83600</v>
@@ -514,7 +514,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G5" t="n">
-        <v>11.027382850647</v>
+        <v>11.0273818969727</v>
       </c>
       <c r="H5" t="n">
         <v>5500</v>
@@ -543,7 +543,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G6" t="n">
-        <v>10.8920774459839</v>
+        <v>10.8920764923096</v>
       </c>
       <c r="H6" t="n">
         <v>7500</v>
@@ -601,7 +601,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>10.9005327224731</v>
+        <v>10.9005336761475</v>
       </c>
       <c r="H8" t="n">
         <v>13200</v>
@@ -630,7 +630,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1457738876343</v>
+        <v>11.1457748413086</v>
       </c>
       <c r="H9" t="n">
         <v>12000</v>
@@ -688,7 +688,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>11.2726240158081</v>
+        <v>11.2726230621338</v>
       </c>
       <c r="H11" t="n">
         <v>2400</v>
@@ -717,7 +717,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G12" t="n">
-        <v>11.1880578994751</v>
+        <v>11.1880569458008</v>
       </c>
       <c r="H12" t="n">
         <v>2200</v>
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H13" t="n">
         <v>7400</v>
@@ -775,7 +775,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G14" t="n">
-        <v>11.027382850647</v>
+        <v>11.0273818969727</v>
       </c>
       <c r="H14" t="n">
         <v>1700</v>
@@ -804,7 +804,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G15" t="n">
-        <v>11.0781221389771</v>
+        <v>11.0781230926514</v>
       </c>
       <c r="H15" t="n">
         <v>2900</v>
@@ -833,7 +833,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0189247131348</v>
+        <v>11.0189237594604</v>
       </c>
       <c r="H16" t="n">
         <v>3800</v>
@@ -862,7 +862,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G17" t="n">
-        <v>11.2726240158081</v>
+        <v>11.2726230621338</v>
       </c>
       <c r="H17" t="n">
         <v>2700</v>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H20" t="n">
         <v>2800</v>
@@ -978,7 +978,7 @@
         <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H21" t="n">
         <v>6300</v>
@@ -1007,7 +1007,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895383834839</v>
       </c>
       <c r="H22" t="n">
         <v>6300</v>
@@ -1036,7 +1036,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>11.1204051971436</v>
+        <v>11.1204042434692</v>
       </c>
       <c r="H23" t="n">
         <v>1700</v>
@@ -1065,7 +1065,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>10.9174461364746</v>
+        <v>10.9174470901489</v>
       </c>
       <c r="H24" t="n">
         <v>4500</v>
@@ -1123,7 +1123,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>11.0781221389771</v>
+        <v>11.0781230926514</v>
       </c>
       <c r="H26" t="n">
         <v>2000</v>
@@ -1152,7 +1152,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H27" t="n">
         <v>1300</v>
@@ -1181,7 +1181,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H28" t="n">
         <v>1500</v>
@@ -1239,7 +1239,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H30" t="n">
         <v>1300</v>
@@ -1297,7 +1297,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G32" t="n">
-        <v>10.8159685134888</v>
+        <v>10.8159675598145</v>
       </c>
       <c r="H32" t="n">
         <v>200</v>
@@ -1355,7 +1355,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7652273178101</v>
+        <v>10.7652282714844</v>
       </c>
       <c r="H34" t="n">
         <v>4500</v>
@@ -1384,7 +1384,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G35" t="n">
-        <v>10.6468362808228</v>
+        <v>10.6468372344971</v>
       </c>
       <c r="H35" t="n">
         <v>10800</v>
@@ -1442,7 +1442,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>10.9428157806396</v>
+        <v>10.942816734314</v>
       </c>
       <c r="H37" t="n">
         <v>2100</v>
@@ -1471,7 +1471,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G38" t="n">
-        <v>10.9343614578247</v>
+        <v>10.9343595504761</v>
       </c>
       <c r="H38" t="n">
         <v>1700</v>
@@ -1500,7 +1500,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G39" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H39" t="n">
         <v>3800</v>
@@ -1529,7 +1529,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H40" t="n">
         <v>2900</v>
@@ -1558,7 +1558,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0781221389771</v>
+        <v>11.0781230926514</v>
       </c>
       <c r="H41" t="n">
         <v>3100</v>
@@ -1587,7 +1587,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G42" t="n">
-        <v>11.2387981414795</v>
+        <v>11.2387971878052</v>
       </c>
       <c r="H42" t="n">
         <v>13400</v>
@@ -1674,7 +1674,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G45" t="n">
-        <v>11.8223009109497</v>
+        <v>11.822301864624</v>
       </c>
       <c r="H45" t="n">
         <v>38700</v>
@@ -1761,7 +1761,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H48" t="n">
         <v>5200</v>
@@ -1790,7 +1790,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H49" t="n">
         <v>1800</v>
@@ -1819,7 +1819,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>11.5855169296265</v>
+        <v>11.5855159759521</v>
       </c>
       <c r="H50" t="n">
         <v>2000</v>
@@ -1935,7 +1935,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895383834839</v>
       </c>
       <c r="H54" t="n">
         <v>1300</v>
@@ -1993,7 +1993,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>11.2810802459717</v>
+        <v>11.2810792922974</v>
       </c>
       <c r="H56" t="n">
         <v>7600</v>
@@ -2022,7 +2022,7 @@
         <v>13.25</v>
       </c>
       <c r="G57" t="n">
-        <v>11.2049713134766</v>
+        <v>11.2049703598022</v>
       </c>
       <c r="H57" t="n">
         <v>2500</v>
@@ -2051,7 +2051,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G58" t="n">
-        <v>11.1288604736328</v>
+        <v>11.1288614273071</v>
       </c>
       <c r="H58" t="n">
         <v>1500</v>
@@ -2080,7 +2080,7 @@
         <v>13</v>
       </c>
       <c r="G59" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H59" t="n">
         <v>9700</v>
@@ -2109,7 +2109,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G60" t="n">
-        <v>11.1457738876343</v>
+        <v>11.1457748413086</v>
       </c>
       <c r="H60" t="n">
         <v>1200</v>
@@ -2138,7 +2138,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>11.1204051971436</v>
+        <v>11.1204042434692</v>
       </c>
       <c r="H61" t="n">
         <v>6300</v>
@@ -2167,7 +2167,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G62" t="n">
-        <v>11.1457738876343</v>
+        <v>11.1457748413086</v>
       </c>
       <c r="H62" t="n">
         <v>2100</v>
@@ -2196,7 +2196,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G63" t="n">
-        <v>11.0527534484863</v>
+        <v>11.0527515411377</v>
       </c>
       <c r="H63" t="n">
         <v>13700</v>
@@ -2254,7 +2254,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>10.9428157806396</v>
+        <v>10.942816734314</v>
       </c>
       <c r="H65" t="n">
         <v>1100</v>
@@ -2283,7 +2283,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>11.0020132064819</v>
+        <v>11.0020122528076</v>
       </c>
       <c r="H66" t="n">
         <v>3400</v>
@@ -2457,7 +2457,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H72" t="n">
         <v>900</v>
@@ -2486,7 +2486,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H73" t="n">
         <v>1500</v>
@@ -2515,7 +2515,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H74" t="n">
         <v>3300</v>
@@ -2544,7 +2544,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H75" t="n">
         <v>500</v>
@@ -2602,7 +2602,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H77" t="n">
         <v>400</v>
@@ -2631,7 +2631,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H78" t="n">
         <v>1400</v>
@@ -2660,7 +2660,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H79" t="n">
         <v>2500</v>
@@ -2689,7 +2689,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>10.9005327224731</v>
+        <v>10.9005336761475</v>
       </c>
       <c r="H80" t="n">
         <v>1200</v>
@@ -2718,7 +2718,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>10.9259023666382</v>
+        <v>10.9259033203125</v>
       </c>
       <c r="H81" t="n">
         <v>1600</v>
@@ -2747,7 +2747,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G82" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H82" t="n">
         <v>3600</v>
@@ -2776,7 +2776,7 @@
         <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H83" t="n">
         <v>6800</v>
@@ -2950,7 +2950,7 @@
         <v>13</v>
       </c>
       <c r="G89" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H89" t="n">
         <v>43500</v>
@@ -2979,7 +2979,7 @@
         <v>13</v>
       </c>
       <c r="G90" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H90" t="n">
         <v>300</v>
@@ -3066,7 +3066,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.6383790969849</v>
+        <v>10.6383800506592</v>
       </c>
       <c r="H93" t="n">
         <v>3300</v>
@@ -3095,7 +3095,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G94" t="n">
-        <v>10.6383790969849</v>
+        <v>10.6383800506592</v>
       </c>
       <c r="H94" t="n">
         <v>200</v>
@@ -3124,7 +3124,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H95" t="n">
         <v>1700</v>
@@ -3153,7 +3153,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G97" t="n">
-        <v>10.8159685134888</v>
+        <v>10.8159675598145</v>
       </c>
       <c r="H97" t="n">
         <v>1100</v>
@@ -3211,7 +3211,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>10.6130084991455</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H98" t="n">
         <v>3200</v>
@@ -3269,7 +3269,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G100" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H100" t="n">
         <v>3100</v>
@@ -3298,7 +3298,7 @@
         <v>12.75</v>
       </c>
       <c r="G101" t="n">
-        <v>10.7821435928345</v>
+        <v>10.7821426391602</v>
       </c>
       <c r="H101" t="n">
         <v>7700</v>
@@ -3356,7 +3356,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>10.8159685134888</v>
+        <v>10.8159675598145</v>
       </c>
       <c r="H103" t="n">
         <v>600</v>
@@ -3385,7 +3385,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G104" t="n">
-        <v>10.7144889831543</v>
+        <v>10.7144899368286</v>
       </c>
       <c r="H104" t="n">
         <v>300</v>
@@ -3443,7 +3443,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G106" t="n">
-        <v>10.8497934341431</v>
+        <v>10.8497943878174</v>
       </c>
       <c r="H106" t="n">
         <v>500</v>
@@ -3530,7 +3530,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G109" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H109" t="n">
         <v>600</v>
@@ -3559,7 +3559,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>10.7990550994873</v>
+        <v>10.7990560531616</v>
       </c>
       <c r="H110" t="n">
         <v>700</v>
@@ -3588,7 +3588,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.7060327529907</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H111" t="n">
         <v>7100</v>
@@ -3617,7 +3617,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G112" t="n">
-        <v>10.7060327529907</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G113" t="n">
-        <v>10.7060327529907</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G114" t="n">
-        <v>10.7060327529907</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H115" t="n">
         <v>600</v>
@@ -3733,7 +3733,7 @@
         <v>12.75</v>
       </c>
       <c r="G116" t="n">
-        <v>10.7821435928345</v>
+        <v>10.7821426391602</v>
       </c>
       <c r="H116" t="n">
         <v>1500</v>
@@ -3820,7 +3820,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H119" t="n">
         <v>1200</v>
@@ -3878,7 +3878,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>10.6130084991455</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H121" t="n">
         <v>1300</v>
@@ -3907,7 +3907,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>10.6130084991455</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H124" t="n">
         <v>1000</v>
@@ -3994,7 +3994,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H125" t="n">
         <v>1300</v>
@@ -4052,7 +4052,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H127" t="n">
         <v>200</v>
@@ -4081,7 +4081,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H128" t="n">
         <v>800</v>
@@ -4110,7 +4110,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H131" t="n">
         <v>1200</v>
@@ -4197,7 +4197,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H136" t="n">
         <v>1500</v>
@@ -4342,7 +4342,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>10.4438791275024</v>
+        <v>10.4438781738281</v>
       </c>
       <c r="H137" t="n">
         <v>4600</v>
@@ -4371,7 +4371,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>10.4015941619873</v>
+        <v>10.4015951156616</v>
       </c>
       <c r="H138" t="n">
         <v>6500</v>
@@ -4429,7 +4429,7 @@
         <v>12.75</v>
       </c>
       <c r="G140" t="n">
-        <v>10.7821435928345</v>
+        <v>10.7821426391602</v>
       </c>
       <c r="H140" t="n">
         <v>21700</v>
@@ -4458,7 +4458,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>10.6975746154785</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H141" t="n">
         <v>3500</v>
@@ -4487,7 +4487,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H142" t="n">
         <v>800</v>
@@ -4516,7 +4516,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H143" t="n">
         <v>1800</v>
@@ -4545,7 +4545,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>10.4438791275024</v>
+        <v>10.4438781738281</v>
       </c>
       <c r="H144" t="n">
         <v>400</v>
@@ -4574,7 +4574,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H145" t="n">
         <v>8600</v>
@@ -4603,7 +4603,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>10.2324638366699</v>
+        <v>10.2324647903442</v>
       </c>
       <c r="H146" t="n">
         <v>600</v>
@@ -4632,7 +4632,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H147" t="n">
         <v>500</v>
@@ -4661,7 +4661,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H148" t="n">
         <v>4000</v>
@@ -4719,7 +4719,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H150" t="n">
         <v>2300</v>
@@ -4748,7 +4748,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H151" t="n">
         <v>1600</v>
@@ -4777,7 +4777,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H152" t="n">
         <v>800</v>
@@ -4806,7 +4806,7 @@
         <v>13</v>
       </c>
       <c r="G153" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H153" t="n">
         <v>6700</v>
@@ -4835,7 +4835,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H154" t="n">
         <v>13200</v>
@@ -4864,7 +4864,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G155" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H155" t="n">
         <v>3400</v>
@@ -4922,7 +4922,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H157" t="n">
         <v>39900</v>
@@ -5009,7 +5009,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>10.908989906311</v>
+        <v>10.9089889526367</v>
       </c>
       <c r="H160" t="n">
         <v>11800</v>
@@ -5183,7 +5183,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.6130084991455</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H166" t="n">
         <v>2600</v>
@@ -5299,7 +5299,7 @@
         <v>12.75</v>
       </c>
       <c r="G170" t="n">
-        <v>10.7821435928345</v>
+        <v>10.7821426391602</v>
       </c>
       <c r="H170" t="n">
         <v>8800</v>
@@ -5328,7 +5328,7 @@
         <v>12.75</v>
       </c>
       <c r="G171" t="n">
-        <v>10.7821435928345</v>
+        <v>10.7821426391602</v>
       </c>
       <c r="H171" t="n">
         <v>400</v>
@@ -5386,7 +5386,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H173" t="n">
         <v>4300</v>
@@ -5415,7 +5415,7 @@
         <v>13</v>
       </c>
       <c r="G174" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H174" t="n">
         <v>41300</v>
@@ -5473,7 +5473,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H176" t="n">
         <v>2600</v>
@@ -5502,7 +5502,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G177" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H177" t="n">
         <v>400</v>
@@ -5589,7 +5589,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>11.1626892089844</v>
+        <v>11.1626882553101</v>
       </c>
       <c r="H180" t="n">
         <v>1400</v>
@@ -5618,7 +5618,7 @@
         <v>13</v>
       </c>
       <c r="G181" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H181" t="n">
         <v>900</v>
@@ -5647,7 +5647,7 @@
         <v>13</v>
       </c>
       <c r="G182" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H182" t="n">
         <v>1300</v>
@@ -5676,7 +5676,7 @@
         <v>13</v>
       </c>
       <c r="G183" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H183" t="n">
         <v>4000</v>
@@ -5705,7 +5705,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512720108032</v>
       </c>
       <c r="H184" t="n">
         <v>9200</v>
@@ -5734,7 +5734,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G185" t="n">
-        <v>11.1626892089844</v>
+        <v>11.1626882553101</v>
       </c>
       <c r="H185" t="n">
         <v>10300</v>
@@ -5763,7 +5763,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895383834839</v>
       </c>
       <c r="H186" t="n">
         <v>11400</v>
@@ -5821,7 +5821,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895383834839</v>
       </c>
       <c r="H188" t="n">
         <v>2000</v>
@@ -5908,7 +5908,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895383834839</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -6140,7 +6140,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>11.5855169296265</v>
+        <v>11.5855159759521</v>
       </c>
       <c r="H199" t="n">
         <v>1900</v>
@@ -6198,7 +6198,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.54323387146</v>
+        <v>11.5432348251343</v>
       </c>
       <c r="H201" t="n">
         <v>7000</v>
@@ -6227,7 +6227,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>11.54323387146</v>
+        <v>11.5432348251343</v>
       </c>
       <c r="H202" t="n">
         <v>4600</v>
@@ -6256,7 +6256,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H203" t="n">
         <v>5800</v>
@@ -6285,7 +6285,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>11.786958694458</v>
+        <v>11.7869577407837</v>
       </c>
       <c r="H204" t="n">
         <v>8400</v>
@@ -6314,7 +6314,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>11.5702867507935</v>
+        <v>11.5702877044678</v>
       </c>
       <c r="H205" t="n">
         <v>12700</v>
@@ -6343,7 +6343,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>11.4402837753296</v>
+        <v>11.4402828216553</v>
       </c>
       <c r="H206" t="n">
         <v>6500</v>
@@ -6372,7 +6372,7 @@
         <v>13.25</v>
       </c>
       <c r="G207" t="n">
-        <v>11.4836177825928</v>
+        <v>11.4836168289185</v>
       </c>
       <c r="H207" t="n">
         <v>7400</v>
@@ -6401,7 +6401,7 @@
         <v>13.25</v>
       </c>
       <c r="G208" t="n">
-        <v>11.4836177825928</v>
+        <v>11.4836168289185</v>
       </c>
       <c r="H208" t="n">
         <v>400</v>
@@ -6430,7 +6430,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>11.5702867507935</v>
+        <v>11.5702877044678</v>
       </c>
       <c r="H209" t="n">
         <v>2800</v>
@@ -6488,7 +6488,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>11.4402837753296</v>
+        <v>11.4402828216553</v>
       </c>
       <c r="H211" t="n">
         <v>2300</v>
@@ -6517,7 +6517,7 @@
         <v>13.75</v>
       </c>
       <c r="G212" t="n">
-        <v>11.9169616699219</v>
+        <v>11.9169626235962</v>
       </c>
       <c r="H212" t="n">
         <v>5600</v>
@@ -6546,7 +6546,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>11.6569528579712</v>
+        <v>11.6569538116455</v>
       </c>
       <c r="H213" t="n">
         <v>4500</v>
@@ -6604,7 +6604,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H215" t="n">
         <v>700</v>
@@ -6633,7 +6633,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H216" t="n">
         <v>1800</v>
@@ -6662,7 +6662,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G217" t="n">
-        <v>11.8736267089844</v>
+        <v>11.8736257553101</v>
       </c>
       <c r="H217" t="n">
         <v>2900</v>
@@ -6691,7 +6691,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6749,7 +6749,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>11.5702867507935</v>
+        <v>11.5702877044678</v>
       </c>
       <c r="H220" t="n">
         <v>1500</v>
@@ -6778,7 +6778,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H221" t="n">
         <v>1500</v>
@@ -6807,7 +6807,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.6569528579712</v>
+        <v>11.6569538116455</v>
       </c>
       <c r="H222" t="n">
         <v>1900</v>
@@ -6836,7 +6836,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H223" t="n">
         <v>41700</v>
@@ -6865,7 +6865,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>11.8302917480469</v>
+        <v>11.8302936553955</v>
       </c>
       <c r="H224" t="n">
         <v>4800</v>
@@ -6894,7 +6894,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>11.8302917480469</v>
+        <v>11.8302936553955</v>
       </c>
       <c r="H225" t="n">
         <v>40300</v>
@@ -6923,7 +6923,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>11.8736267089844</v>
+        <v>11.8736257553101</v>
       </c>
       <c r="H226" t="n">
         <v>3400</v>
@@ -6952,7 +6952,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>11.9602966308594</v>
+        <v>11.9602956771851</v>
       </c>
       <c r="H227" t="n">
         <v>5400</v>
@@ -6981,7 +6981,7 @@
         <v>13.75</v>
       </c>
       <c r="G228" t="n">
-        <v>11.9169616699219</v>
+        <v>11.9169626235962</v>
       </c>
       <c r="H228" t="n">
         <v>2700</v>
@@ -7010,7 +7010,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902976989746</v>
       </c>
       <c r="H229" t="n">
         <v>1300</v>
@@ -7039,7 +7039,7 @@
         <v>13.75</v>
       </c>
       <c r="G230" t="n">
-        <v>11.9169616699219</v>
+        <v>11.9169626235962</v>
       </c>
       <c r="H230" t="n">
         <v>2100</v>
@@ -7068,7 +7068,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G231" t="n">
-        <v>11.8302917480469</v>
+        <v>11.8302936553955</v>
       </c>
       <c r="H231" t="n">
         <v>1500</v>
@@ -7126,7 +7126,7 @@
         <v>13.75</v>
       </c>
       <c r="G233" t="n">
-        <v>11.9169616699219</v>
+        <v>11.9169626235962</v>
       </c>
       <c r="H233" t="n">
         <v>2200</v>
@@ -7155,7 +7155,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>11.786958694458</v>
+        <v>11.7869577407837</v>
       </c>
       <c r="H234" t="n">
         <v>700</v>
@@ -7184,7 +7184,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H235" t="n">
         <v>2900</v>
@@ -7213,7 +7213,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902976989746</v>
       </c>
       <c r="H236" t="n">
         <v>2000</v>
@@ -7329,7 +7329,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902976989746</v>
       </c>
       <c r="H240" t="n">
         <v>900</v>
@@ -7416,7 +7416,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>12.4803085327148</v>
+        <v>12.4803094863892</v>
       </c>
       <c r="H243" t="n">
         <v>3700</v>
@@ -7561,7 +7561,7 @@
         <v>15</v>
       </c>
       <c r="G248" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H248" t="n">
         <v>2600</v>
@@ -7619,7 +7619,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>13.1303234100342</v>
+        <v>13.1303243637085</v>
       </c>
       <c r="H250" t="n">
         <v>4600</v>
@@ -7648,7 +7648,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H251" t="n">
         <v>12100</v>
@@ -7735,7 +7735,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8703174591064</v>
+        <v>12.8703193664551</v>
       </c>
       <c r="H254" t="n">
         <v>1600</v>
@@ -7764,7 +7764,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>13.0436553955078</v>
+        <v>13.0436544418335</v>
       </c>
       <c r="H255" t="n">
         <v>12700</v>
@@ -7880,7 +7880,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>12.8269844055176</v>
+        <v>12.8269834518433</v>
       </c>
       <c r="H259" t="n">
         <v>1300</v>
@@ -7938,7 +7938,7 @@
         <v>15</v>
       </c>
       <c r="G261" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H261" t="n">
         <v>1800</v>
@@ -7996,7 +7996,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H263" t="n">
         <v>2900</v>
@@ -8025,7 +8025,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H264" t="n">
         <v>2000</v>
@@ -8054,7 +8054,7 @@
         <v>15.25</v>
       </c>
       <c r="G265" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H265" t="n">
         <v>4200</v>
@@ -8112,7 +8112,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H267" t="n">
         <v>2500</v>
@@ -8141,7 +8141,7 @@
         <v>15</v>
       </c>
       <c r="G268" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H268" t="n">
         <v>3000</v>
@@ -8170,7 +8170,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H269" t="n">
         <v>2200</v>
@@ -8199,7 +8199,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H270" t="n">
         <v>300</v>
@@ -8228,7 +8228,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>13.1303234100342</v>
+        <v>13.1303243637085</v>
       </c>
       <c r="H271" t="n">
         <v>1100</v>
@@ -8286,7 +8286,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H273" t="n">
         <v>1600</v>
@@ -8315,7 +8315,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H274" t="n">
         <v>1100</v>
@@ -8431,7 +8431,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H278" t="n">
         <v>1700</v>
@@ -8460,7 +8460,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H280" t="n">
         <v>200</v>
@@ -8518,7 +8518,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H281" t="n">
         <v>1000</v>
@@ -8547,7 +8547,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>13.520336151123</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8576,7 +8576,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H283" t="n">
         <v>4000</v>
@@ -8605,7 +8605,7 @@
         <v>15.25</v>
       </c>
       <c r="G284" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H284" t="n">
         <v>100</v>
@@ -8634,7 +8634,7 @@
         <v>15.25</v>
       </c>
       <c r="G285" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H285" t="n">
         <v>800</v>
@@ -8663,7 +8663,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H286" t="n">
         <v>25700</v>
@@ -8692,7 +8692,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H287" t="n">
         <v>400</v>
@@ -8721,7 +8721,7 @@
         <v>15.25</v>
       </c>
       <c r="G288" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H288" t="n">
         <v>1900</v>
@@ -8750,7 +8750,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H289" t="n">
         <v>2500</v>
@@ -8779,7 +8779,7 @@
         <v>15.25</v>
       </c>
       <c r="G290" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H290" t="n">
         <v>700</v>
@@ -8808,7 +8808,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H291" t="n">
         <v>2500</v>
@@ -8837,7 +8837,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H292" t="n">
         <v>1100</v>
@@ -8866,7 +8866,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H293" t="n">
         <v>800</v>
@@ -8895,7 +8895,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H294" t="n">
         <v>1800</v>
@@ -8924,7 +8924,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H295" t="n">
         <v>800</v>
@@ -8953,7 +8953,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H296" t="n">
         <v>25700</v>
@@ -9011,7 +9011,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H298" t="n">
         <v>6800</v>
@@ -9040,7 +9040,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>13.1303234100342</v>
+        <v>13.1303243637085</v>
       </c>
       <c r="H299" t="n">
         <v>1700</v>
@@ -9069,7 +9069,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H300" t="n">
         <v>3000</v>
@@ -9098,7 +9098,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H301" t="n">
         <v>2000</v>
@@ -9127,7 +9127,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H302" t="n">
         <v>1200</v>
@@ -9156,7 +9156,7 @@
         <v>15.25</v>
       </c>
       <c r="G303" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H303" t="n">
         <v>600</v>
@@ -9185,7 +9185,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G304" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H304" t="n">
         <v>900</v>
@@ -9214,7 +9214,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>13.520336151123</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H305" t="n">
         <v>12300</v>
@@ -9243,7 +9243,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>13.520336151123</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H306" t="n">
         <v>1200</v>
@@ -9272,7 +9272,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H307" t="n">
         <v>6600</v>
@@ -9330,7 +9330,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>13.5636672973633</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H309" t="n">
         <v>2700</v>
@@ -9359,7 +9359,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>13.737006187439</v>
+        <v>13.7370071411133</v>
       </c>
       <c r="H310" t="n">
         <v>2000</v>
@@ -9388,7 +9388,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>13.737006187439</v>
+        <v>13.7370071411133</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>13.5636672973633</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H312" t="n">
         <v>11300</v>
@@ -9446,7 +9446,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H313" t="n">
         <v>9400</v>
@@ -9475,7 +9475,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>13.520336151123</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H314" t="n">
         <v>3300</v>
@@ -9504,7 +9504,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G315" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H315" t="n">
         <v>2100</v>
@@ -9533,7 +9533,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>13.7803401947021</v>
+        <v>13.7803411483765</v>
       </c>
       <c r="H316" t="n">
         <v>3200</v>
@@ -9562,7 +9562,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>13.520336151123</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H317" t="n">
         <v>1900</v>
@@ -9591,7 +9591,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>13.520336151123</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H318" t="n">
         <v>1500</v>
@@ -9620,7 +9620,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H319" t="n">
         <v>200</v>
@@ -9649,7 +9649,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H320" t="n">
         <v>1400</v>
@@ -9678,7 +9678,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>13.5636672973633</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H321" t="n">
         <v>2200</v>
@@ -9707,7 +9707,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G322" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H322" t="n">
         <v>300</v>
@@ -9736,7 +9736,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H323" t="n">
         <v>1900</v>
@@ -9765,7 +9765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H324" t="n">
         <v>2600</v>
@@ -9794,7 +9794,7 @@
         <v>15.25</v>
       </c>
       <c r="G325" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169942855835</v>
       </c>
       <c r="H325" t="n">
         <v>2200</v>
@@ -9823,7 +9823,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H326" t="n">
         <v>2300</v>
@@ -9881,7 +9881,7 @@
         <v>15</v>
       </c>
       <c r="G328" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H328" t="n">
         <v>11200</v>
@@ -9910,7 +9910,7 @@
         <v>15</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5636672973633</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H332" t="n">
         <v>30500</v>
@@ -10084,7 +10084,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>13.737006187439</v>
+        <v>13.7370071411133</v>
       </c>
       <c r="H337" t="n">
         <v>3100</v>
@@ -10171,7 +10171,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>13.5636672973633</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H338" t="n">
         <v>1000</v>
@@ -10200,7 +10200,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>13.5636672973633</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H339" t="n">
         <v>1000</v>
@@ -10229,7 +10229,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>13.5636672973633</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>13.5636672973633</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H341" t="n">
         <v>200</v>
@@ -10287,7 +10287,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H342" t="n">
         <v>1100</v>
@@ -10316,7 +10316,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G343" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H343" t="n">
         <v>500</v>
@@ -10432,7 +10432,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H347" t="n">
         <v>600</v>
@@ -10490,7 +10490,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>13.520336151123</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H349" t="n">
         <v>3400</v>
@@ -10577,7 +10577,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>13.5636672973633</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H352" t="n">
         <v>4000</v>
@@ -10606,7 +10606,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G353" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H353" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>13.520336151123</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H354" t="n">
         <v>3600</v>
@@ -10664,7 +10664,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G355" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H355" t="n">
         <v>400</v>
@@ -10693,7 +10693,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G356" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H358" t="n">
         <v>3400</v>
@@ -10809,7 +10809,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G360" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H360" t="n">
         <v>800</v>
@@ -10838,7 +10838,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H361" t="n">
         <v>900</v>
@@ -10867,7 +10867,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H363" t="n">
         <v>1300</v>
@@ -10925,7 +10925,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H364" t="n">
         <v>200</v>
@@ -10954,7 +10954,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G365" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H365" t="n">
         <v>1300</v>
@@ -10983,7 +10983,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>13.6070022583008</v>
+        <v>13.6070013046265</v>
       </c>
       <c r="H366" t="n">
         <v>4500</v>
@@ -11012,7 +11012,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11099,7 +11099,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H370" t="n">
         <v>1000</v>
@@ -11186,7 +11186,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>13.1303234100342</v>
+        <v>13.1303243637085</v>
       </c>
       <c r="H373" t="n">
         <v>700</v>
@@ -11215,7 +11215,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H374" t="n">
         <v>100</v>
@@ -11273,7 +11273,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>13.5636672973633</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H376" t="n">
         <v>2300</v>
@@ -11302,7 +11302,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H377" t="n">
         <v>900</v>
@@ -11331,7 +11331,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>13.3036632537842</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H378" t="n">
         <v>100</v>
@@ -11360,7 +11360,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H379" t="n">
         <v>6400</v>
@@ -11389,7 +11389,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H380" t="n">
         <v>900</v>
@@ -11418,7 +11418,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H381" t="n">
         <v>800</v>
@@ -11476,7 +11476,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G383" t="n">
-        <v>13.3903312683105</v>
+        <v>13.3903303146362</v>
       </c>
       <c r="H383" t="n">
         <v>1000</v>
@@ -11505,7 +11505,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H384" t="n">
         <v>300</v>
@@ -11534,7 +11534,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H385" t="n">
         <v>200</v>
@@ -11592,7 +11592,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1270141601562</v>
+        <v>14.1270151138306</v>
       </c>
       <c r="H387" t="n">
         <v>5300</v>
@@ -11621,7 +11621,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>14.2136840820312</v>
+        <v>14.2136850357056</v>
       </c>
       <c r="H388" t="n">
         <v>3100</v>
@@ -11679,7 +11679,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H390" t="n">
         <v>10000</v>
@@ -11708,7 +11708,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H391" t="n">
         <v>7500</v>
@@ -11737,7 +11737,7 @@
         <v>17.25</v>
       </c>
       <c r="G392" t="n">
-        <v>14.9503679275513</v>
+        <v>14.9503698348999</v>
       </c>
       <c r="H392" t="n">
         <v>5500</v>
@@ -11766,7 +11766,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070348739624</v>
       </c>
       <c r="H393" t="n">
         <v>3100</v>
@@ -11824,7 +11824,7 @@
         <v>17</v>
       </c>
       <c r="G395" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H395" t="n">
         <v>3200</v>
@@ -11882,7 +11882,7 @@
         <v>16.75</v>
       </c>
       <c r="G397" t="n">
-        <v>14.5170249938965</v>
+        <v>14.5170240402222</v>
       </c>
       <c r="H397" t="n">
         <v>4600</v>
@@ -11911,7 +11911,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>14.5603590011597</v>
+        <v>14.560359954834</v>
       </c>
       <c r="H398" t="n">
         <v>300</v>
@@ -11940,7 +11940,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H399" t="n">
         <v>1200</v>
@@ -11969,7 +11969,7 @@
         <v>17</v>
       </c>
       <c r="G400" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H400" t="n">
         <v>3000</v>
@@ -12027,7 +12027,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>14.3870229721069</v>
+        <v>14.3870220184326</v>
       </c>
       <c r="H402" t="n">
         <v>1500</v>
@@ -12056,7 +12056,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G403" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H403" t="n">
         <v>900</v>
@@ -12085,7 +12085,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>14.5603590011597</v>
+        <v>14.560359954834</v>
       </c>
       <c r="H404" t="n">
         <v>2900</v>
@@ -12114,7 +12114,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>14.5603590011597</v>
+        <v>14.560359954834</v>
       </c>
       <c r="H405" t="n">
         <v>2000</v>
@@ -12143,7 +12143,7 @@
         <v>17</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H406" t="n">
         <v>3400</v>
@@ -12172,7 +12172,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H407" t="n">
         <v>5600</v>
@@ -12259,7 +12259,7 @@
         <v>17</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H410" t="n">
         <v>6700</v>
@@ -12375,7 +12375,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G414" t="n">
-        <v>14.7770309448242</v>
+        <v>14.7770328521729</v>
       </c>
       <c r="H414" t="n">
         <v>900</v>
@@ -12433,7 +12433,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H416" t="n">
         <v>2000</v>
@@ -12462,7 +12462,7 @@
         <v>16.75</v>
       </c>
       <c r="G417" t="n">
-        <v>14.5170249938965</v>
+        <v>14.5170240402222</v>
       </c>
       <c r="H417" t="n">
         <v>15600</v>
@@ -12549,7 +12549,7 @@
         <v>16.5</v>
       </c>
       <c r="G420" t="n">
-        <v>14.3003530502319</v>
+        <v>14.3003549575806</v>
       </c>
       <c r="H420" t="n">
         <v>25000</v>
@@ -12607,7 +12607,7 @@
         <v>16.5</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3003530502319</v>
+        <v>14.3003549575806</v>
       </c>
       <c r="H422" t="n">
         <v>4000</v>
@@ -12694,7 +12694,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>14.3870229721069</v>
+        <v>14.3870220184326</v>
       </c>
       <c r="H425" t="n">
         <v>4300</v>
@@ -12752,7 +12752,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>14.3870229721069</v>
+        <v>14.3870220184326</v>
       </c>
       <c r="H427" t="n">
         <v>600</v>
@@ -12810,7 +12810,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H429" t="n">
         <v>11700</v>
@@ -12839,7 +12839,7 @@
         <v>17</v>
       </c>
       <c r="G430" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H430" t="n">
         <v>8300</v>
@@ -12897,7 +12897,7 @@
         <v>17</v>
       </c>
       <c r="G432" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H432" t="n">
         <v>4100</v>
@@ -12955,7 +12955,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H434" t="n">
         <v>700</v>
@@ -12984,7 +12984,7 @@
         <v>17</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H435" t="n">
         <v>3600</v>
@@ -13042,7 +13042,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H437" t="n">
         <v>2300</v>
@@ -13216,7 +13216,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G443" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070348739624</v>
       </c>
       <c r="H443" t="n">
         <v>14843</v>
@@ -13274,7 +13274,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>14.9937038421631</v>
+        <v>14.9937047958374</v>
       </c>
       <c r="H445" t="n">
         <v>4294</v>
@@ -13303,7 +13303,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G446" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070348739624</v>
       </c>
       <c r="H446" t="n">
         <v>3301</v>
@@ -13361,7 +13361,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G448" t="n">
-        <v>14.7770309448242</v>
+        <v>14.7770328521729</v>
       </c>
       <c r="H448" t="n">
         <v>885</v>
@@ -13419,7 +13419,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>15.0803737640381</v>
+        <v>15.0803728103638</v>
       </c>
       <c r="H450" t="n">
         <v>6177</v>
@@ -13448,7 +13448,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>15.0803737640381</v>
+        <v>15.0803728103638</v>
       </c>
       <c r="H451" t="n">
         <v>14450</v>
@@ -13477,7 +13477,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>14.9937038421631</v>
+        <v>14.9937047958374</v>
       </c>
       <c r="H452" t="n">
         <v>4325</v>
@@ -13506,7 +13506,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>15.0803737640381</v>
+        <v>15.0803728103638</v>
       </c>
       <c r="H453" t="n">
         <v>24934</v>
@@ -13535,7 +13535,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265378952026</v>
       </c>
       <c r="H454" t="n">
         <v>4000</v>
@@ -13564,7 +13564,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265378952026</v>
       </c>
       <c r="H455" t="n">
         <v>10462</v>
@@ -13622,7 +13622,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>15.5265369415283</v>
+        <v>15.5265378952026</v>
       </c>
       <c r="H457" t="n">
         <v>880</v>
@@ -13680,7 +13680,7 @@
         <v>17</v>
       </c>
       <c r="G459" t="n">
-        <v>15.1696071624756</v>
+        <v>15.1696062088013</v>
       </c>
       <c r="H459" t="n">
         <v>20546</v>
@@ -13738,7 +13738,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>15.2142200469971</v>
+        <v>15.21422290802</v>
       </c>
       <c r="H461" t="n">
         <v>4400</v>
@@ -13767,7 +13767,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>14.9911394119263</v>
+        <v>14.9911403656006</v>
       </c>
       <c r="H462" t="n">
         <v>599</v>
@@ -13796,7 +13796,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G463" t="n">
-        <v>15.1249923706055</v>
+        <v>15.1249895095825</v>
       </c>
       <c r="H463" t="n">
         <v>771</v>
@@ -13825,7 +13825,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>15.4373044967651</v>
+        <v>15.4373054504395</v>
       </c>
       <c r="H464" t="n">
         <v>1237</v>
@@ -13854,7 +13854,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>15.3480749130249</v>
+        <v>15.348072052002</v>
       </c>
       <c r="H465" t="n">
         <v>9270</v>
@@ -13883,7 +13883,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>15.3480749130249</v>
+        <v>15.348072052002</v>
       </c>
       <c r="H466" t="n">
         <v>3452</v>
@@ -13912,7 +13912,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>15.3480749130249</v>
+        <v>15.348072052002</v>
       </c>
       <c r="H467" t="n">
         <v>30811</v>
@@ -13941,7 +13941,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>15.4373044967651</v>
+        <v>15.4373054504395</v>
       </c>
       <c r="H468" t="n">
         <v>1311</v>
@@ -13970,7 +13970,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G469" t="n">
-        <v>15.7496194839478</v>
+        <v>15.7496175765991</v>
       </c>
       <c r="H469" t="n">
         <v>6229</v>
@@ -14173,7 +14173,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>16.9988822937012</v>
+        <v>16.9988803863525</v>
       </c>
       <c r="H476" t="n">
         <v>6745</v>
@@ -14202,7 +14202,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G477" t="n">
-        <v>17.1327323913574</v>
+        <v>17.1327342987061</v>
       </c>
       <c r="H477" t="n">
         <v>16785</v>
@@ -14347,7 +14347,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>17.2219638824463</v>
+        <v>17.2219619750977</v>
       </c>
       <c r="H482" t="n">
         <v>2971</v>
@@ -14492,7 +14492,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342807769775</v>
       </c>
       <c r="H487" t="n">
         <v>5816</v>
@@ -14666,7 +14666,7 @@
         <v>20.5</v>
       </c>
       <c r="G493" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H493" t="n">
         <v>2753</v>
@@ -14753,7 +14753,7 @@
         <v>21</v>
       </c>
       <c r="G496" t="n">
-        <v>18.7389240264893</v>
+        <v>18.7389259338379</v>
       </c>
       <c r="H496" t="n">
         <v>12906</v>
@@ -14898,7 +14898,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G501" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H501" t="n">
         <v>3610</v>
@@ -14927,7 +14927,7 @@
         <v>20.5</v>
       </c>
       <c r="G502" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H502" t="n">
         <v>6475</v>
@@ -14956,7 +14956,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>18.3819942474365</v>
+        <v>18.3819923400879</v>
       </c>
       <c r="H503" t="n">
         <v>4027</v>
@@ -14985,7 +14985,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G504" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250644683838</v>
       </c>
       <c r="H504" t="n">
         <v>2132</v>
@@ -15014,7 +15014,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G505" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H505" t="n">
         <v>2052</v>
@@ -15043,7 +15043,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H506" t="n">
         <v>8048</v>
@@ -15072,7 +15072,7 @@
         <v>20.5</v>
       </c>
       <c r="G507" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H507" t="n">
         <v>3880</v>
@@ -15101,7 +15101,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G508" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250644683838</v>
       </c>
       <c r="H508" t="n">
         <v>3833</v>
@@ -15130,7 +15130,7 @@
         <v>20.5</v>
       </c>
       <c r="G509" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H509" t="n">
         <v>3508</v>
@@ -15159,7 +15159,7 @@
         <v>20.5</v>
       </c>
       <c r="G510" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H510" t="n">
         <v>1314</v>
@@ -15188,7 +15188,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H511" t="n">
         <v>2701</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H512" t="n">
         <v>3189</v>
@@ -15304,7 +15304,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>17.80198097229</v>
+        <v>17.8019790649414</v>
       </c>
       <c r="H515" t="n">
         <v>5505</v>
@@ -15333,7 +15333,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.6681289672852</v>
+        <v>17.6681270599365</v>
       </c>
       <c r="H516" t="n">
         <v>14791</v>
@@ -15391,7 +15391,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>17.6681289672852</v>
+        <v>17.6681270599365</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15449,7 +15449,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>17.2219638824463</v>
+        <v>17.2219619750977</v>
       </c>
       <c r="H520" t="n">
         <v>1635</v>
@@ -15507,7 +15507,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>17.2665824890137</v>
+        <v>17.266580581665</v>
       </c>
       <c r="H522" t="n">
         <v>1999</v>
@@ -15536,7 +15536,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>17.2665824890137</v>
+        <v>17.266580581665</v>
       </c>
       <c r="H523" t="n">
         <v>5001</v>
@@ -15710,7 +15710,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>17.4896659851074</v>
+        <v>17.4896621704102</v>
       </c>
       <c r="H529" t="n">
         <v>1050</v>
@@ -15797,7 +15797,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G532" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342807769775</v>
       </c>
       <c r="H532" t="n">
         <v>1402</v>
@@ -15855,7 +15855,7 @@
         <v>20</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H534" t="n">
         <v>2224</v>
@@ -15884,7 +15884,7 @@
         <v>20</v>
       </c>
       <c r="G535" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H535" t="n">
         <v>4616</v>
@@ -15913,7 +15913,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G536" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250644683838</v>
       </c>
       <c r="H536" t="n">
         <v>13894</v>
@@ -15942,7 +15942,7 @@
         <v>20</v>
       </c>
       <c r="G537" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H537" t="n">
         <v>2250</v>
@@ -15971,7 +15971,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H538" t="n">
         <v>10406</v>
@@ -16000,7 +16000,7 @@
         <v>20</v>
       </c>
       <c r="G539" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H539" t="n">
         <v>1256</v>
@@ -16029,7 +16029,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H540" t="n">
         <v>5116</v>
@@ -16058,7 +16058,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>18.3819942474365</v>
+        <v>18.3819923400879</v>
       </c>
       <c r="H541" t="n">
         <v>2182</v>
@@ -16116,7 +16116,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H543" t="n">
         <v>2090</v>
@@ -16145,7 +16145,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H544" t="n">
         <v>2060</v>
@@ -16174,7 +16174,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H545" t="n">
         <v>2697</v>
@@ -16232,7 +16232,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H547" t="n">
         <v>603</v>
@@ -16290,7 +16290,7 @@
         <v>20.5</v>
       </c>
       <c r="G549" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H549" t="n">
         <v>7326</v>
@@ -16348,7 +16348,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250644683838</v>
       </c>
       <c r="H551" t="n">
         <v>20579</v>
@@ -16377,7 +16377,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G552" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H552" t="n">
         <v>5016</v>
@@ -16406,7 +16406,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G553" t="n">
-        <v>18.3819942474365</v>
+        <v>18.3819923400879</v>
       </c>
       <c r="H553" t="n">
         <v>3343</v>
@@ -16435,7 +16435,7 @@
         <v>20.5</v>
       </c>
       <c r="G554" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H554" t="n">
         <v>1796</v>
@@ -16551,7 +16551,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250644683838</v>
       </c>
       <c r="H558" t="n">
         <v>7770</v>
@@ -16667,7 +16667,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G562" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250644683838</v>
       </c>
       <c r="H562" t="n">
         <v>1395</v>
@@ -16696,7 +16696,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H563" t="n">
         <v>2101</v>
@@ -16725,7 +16725,7 @@
         <v>20.5</v>
       </c>
       <c r="G564" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H564" t="n">
         <v>3218</v>
@@ -16754,7 +16754,7 @@
         <v>20</v>
       </c>
       <c r="G565" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H565" t="n">
         <v>2880</v>
@@ -16783,7 +16783,7 @@
         <v>20</v>
       </c>
       <c r="G566" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H566" t="n">
         <v>2491</v>
@@ -16812,7 +16812,7 @@
         <v>20</v>
       </c>
       <c r="G567" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H567" t="n">
         <v>2423</v>
@@ -16841,7 +16841,7 @@
         <v>20</v>
       </c>
       <c r="G568" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H568" t="n">
         <v>5106</v>
@@ -16870,7 +16870,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>17.6681289672852</v>
+        <v>17.6681270599365</v>
       </c>
       <c r="H569" t="n">
         <v>610</v>
@@ -16899,7 +16899,7 @@
         <v>20</v>
       </c>
       <c r="G570" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H570" t="n">
         <v>534</v>
@@ -16928,7 +16928,7 @@
         <v>20</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H571" t="n">
         <v>1494</v>
@@ -16957,7 +16957,7 @@
         <v>20</v>
       </c>
       <c r="G572" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H572" t="n">
         <v>126</v>
@@ -16986,7 +16986,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342807769775</v>
       </c>
       <c r="H573" t="n">
         <v>1276</v>
@@ -17044,7 +17044,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H575" t="n">
         <v>12920</v>
@@ -17073,7 +17073,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342807769775</v>
       </c>
       <c r="H576" t="n">
         <v>6126</v>
@@ -17102,7 +17102,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342807769775</v>
       </c>
       <c r="H577" t="n">
         <v>3426</v>
@@ -17131,7 +17131,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250644683838</v>
       </c>
       <c r="H578" t="n">
         <v>5848</v>
@@ -17160,7 +17160,7 @@
         <v>20.5</v>
       </c>
       <c r="G579" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H579" t="n">
         <v>6769</v>
@@ -17218,7 +17218,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H581" t="n">
         <v>1397</v>
@@ -17334,7 +17334,7 @@
         <v>21</v>
       </c>
       <c r="G585" t="n">
-        <v>18.7389240264893</v>
+        <v>18.7389259338379</v>
       </c>
       <c r="H585" t="n">
         <v>62155</v>
@@ -17392,7 +17392,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G587" t="n">
-        <v>18.828161239624</v>
+        <v>18.8281593322754</v>
       </c>
       <c r="H587" t="n">
         <v>10010</v>
@@ -17566,7 +17566,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>19.3635578155518</v>
+        <v>19.3635559082031</v>
       </c>
       <c r="H593" t="n">
         <v>5818</v>
@@ -17595,7 +17595,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>19.2743225097656</v>
+        <v>19.274320602417</v>
       </c>
       <c r="H594" t="n">
         <v>3162</v>
@@ -17682,7 +17682,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>19.8097190856934</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H597" t="n">
         <v>6848</v>
@@ -17798,7 +17798,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H601" t="n">
         <v>2527</v>
@@ -17827,7 +17827,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>20.1666526794434</v>
+        <v>20.1666507720947</v>
       </c>
       <c r="H602" t="n">
         <v>19155</v>
@@ -17856,7 +17856,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>20.1666526794434</v>
+        <v>20.1666507720947</v>
       </c>
       <c r="H603" t="n">
         <v>3830</v>
@@ -17885,7 +17885,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>19.8097190856934</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H604" t="n">
         <v>6581</v>
@@ -17914,7 +17914,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>19.3635578155518</v>
+        <v>19.3635559082031</v>
       </c>
       <c r="H605" t="n">
         <v>5376</v>
@@ -17943,7 +17943,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H606" t="n">
         <v>2280</v>
@@ -17972,7 +17972,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H607" t="n">
         <v>3152</v>
@@ -18030,7 +18030,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>19.2743225097656</v>
+        <v>19.274320602417</v>
       </c>
       <c r="H609" t="n">
         <v>1522</v>
@@ -18059,7 +18059,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>19.2743225097656</v>
+        <v>19.274320602417</v>
       </c>
       <c r="H610" t="n">
         <v>5108</v>
@@ -18146,7 +18146,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>19.8989524841309</v>
+        <v>19.8989505767822</v>
       </c>
       <c r="H613" t="n">
         <v>3145</v>
@@ -18175,7 +18175,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H614" t="n">
         <v>2737</v>
@@ -18204,7 +18204,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>19.8097190856934</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H615" t="n">
         <v>420</v>
@@ -18262,7 +18262,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>20.7912826538086</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H617" t="n">
         <v>12485</v>
@@ -18291,7 +18291,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>20.7020492553711</v>
+        <v>20.7020511627197</v>
       </c>
       <c r="H618" t="n">
         <v>17175</v>
@@ -18320,7 +18320,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>20.7020492553711</v>
+        <v>20.7020511627197</v>
       </c>
       <c r="H619" t="n">
         <v>10967</v>
@@ -18407,7 +18407,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>21.5051460266113</v>
+        <v>21.50514793396</v>
       </c>
       <c r="H622" t="n">
         <v>3553</v>
@@ -18523,7 +18523,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>21.5051460266113</v>
+        <v>21.50514793396</v>
       </c>
       <c r="H626" t="n">
         <v>5729</v>
@@ -18552,7 +18552,7 @@
         <v>24.5</v>
       </c>
       <c r="G627" t="n">
-        <v>21.8620796203613</v>
+        <v>21.86208152771</v>
       </c>
       <c r="H627" t="n">
         <v>11972</v>
@@ -18581,7 +18581,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>21.7728443145752</v>
+        <v>21.7728462219238</v>
       </c>
       <c r="H628" t="n">
         <v>3942</v>
@@ -18610,7 +18610,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G629" t="n">
-        <v>21.9513092041016</v>
+        <v>21.9513111114502</v>
       </c>
       <c r="H629" t="n">
         <v>6820</v>
@@ -18668,7 +18668,7 @@
         <v>24</v>
       </c>
       <c r="G631" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H631" t="n">
         <v>16893</v>
@@ -18726,7 +18726,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>21.683614730835</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H633" t="n">
         <v>16822</v>
@@ -18755,7 +18755,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>21.683614730835</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H634" t="n">
         <v>12327</v>
@@ -18842,7 +18842,7 @@
         <v>24</v>
       </c>
       <c r="G637" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H637" t="n">
         <v>11025</v>
@@ -18929,7 +18929,7 @@
         <v>23.5</v>
       </c>
       <c r="G640" t="n">
-        <v>20.969747543335</v>
+        <v>20.9697494506836</v>
       </c>
       <c r="H640" t="n">
         <v>4685</v>
@@ -19016,7 +19016,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>20.7912826538086</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H643" t="n">
         <v>2095</v>
@@ -19161,7 +19161,7 @@
         <v>24</v>
       </c>
       <c r="G648" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H648" t="n">
         <v>6636</v>
@@ -19190,7 +19190,7 @@
         <v>24</v>
       </c>
       <c r="G649" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H649" t="n">
         <v>10221</v>
@@ -19219,7 +19219,7 @@
         <v>24</v>
       </c>
       <c r="G650" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H650" t="n">
         <v>3081</v>
@@ -19480,7 +19480,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G659" t="n">
-        <v>20.2558841705322</v>
+        <v>20.2558860778809</v>
       </c>
       <c r="H659" t="n">
         <v>9014</v>
@@ -19509,7 +19509,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>20.7020492553711</v>
+        <v>20.7020511627197</v>
       </c>
       <c r="H660" t="n">
         <v>2179</v>
@@ -19538,7 +19538,7 @@
         <v>23.5</v>
       </c>
       <c r="G661" t="n">
-        <v>20.969747543335</v>
+        <v>20.9697494506836</v>
       </c>
       <c r="H661" t="n">
         <v>6201</v>
@@ -19567,7 +19567,7 @@
         <v>23</v>
       </c>
       <c r="G662" t="n">
-        <v>20.5235862731934</v>
+        <v>20.5235843658447</v>
       </c>
       <c r="H662" t="n">
         <v>3585</v>
@@ -19625,7 +19625,7 @@
         <v>22.5</v>
       </c>
       <c r="G664" t="n">
-        <v>20.0774192810059</v>
+        <v>20.0774211883545</v>
       </c>
       <c r="H664" t="n">
         <v>8734</v>
@@ -19654,7 +19654,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H665" t="n">
         <v>8640</v>
@@ -19683,7 +19683,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>19.3635578155518</v>
+        <v>19.3635559082031</v>
       </c>
       <c r="H666" t="n">
         <v>4583</v>
@@ -19712,7 +19712,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H667" t="n">
         <v>10615</v>
@@ -19799,7 +19799,7 @@
         <v>20.5</v>
       </c>
       <c r="G670" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H670" t="n">
         <v>9957</v>
@@ -19828,7 +19828,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G671" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342807769775</v>
       </c>
       <c r="H671" t="n">
         <v>4618</v>
@@ -19857,7 +19857,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G672" t="n">
-        <v>16.4188671112061</v>
+        <v>16.4188652038574</v>
       </c>
       <c r="H672" t="n">
         <v>11168</v>
@@ -19886,7 +19886,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>17.4896659851074</v>
+        <v>17.4896621704102</v>
       </c>
       <c r="H673" t="n">
         <v>2591</v>
@@ -19915,7 +19915,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>16.1957855224609</v>
+        <v>16.1957836151123</v>
       </c>
       <c r="H674" t="n">
         <v>4844</v>
@@ -19944,7 +19944,7 @@
         <v>18</v>
       </c>
       <c r="G675" t="n">
-        <v>16.0619335174561</v>
+        <v>16.0619373321533</v>
       </c>
       <c r="H675" t="n">
         <v>22529</v>
@@ -19973,7 +19973,7 @@
         <v>17.5</v>
       </c>
       <c r="G676" t="n">
-        <v>15.6157703399658</v>
+        <v>15.6157665252686</v>
       </c>
       <c r="H676" t="n">
         <v>12149</v>
@@ -20002,7 +20002,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>14.9019088745117</v>
+        <v>14.9019079208374</v>
       </c>
       <c r="H677" t="n">
         <v>5955</v>
@@ -20031,7 +20031,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>15.035756111145</v>
+        <v>15.0357570648193</v>
       </c>
       <c r="H678" t="n">
         <v>6939</v>
@@ -20060,7 +20060,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>15.7496194839478</v>
+        <v>15.7496175765991</v>
       </c>
       <c r="H679" t="n">
         <v>1490</v>
@@ -20089,7 +20089,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>16.9988822937012</v>
+        <v>16.9988803863525</v>
       </c>
       <c r="H680" t="n">
         <v>12506</v>
@@ -20118,7 +20118,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H681" t="n">
         <v>24241</v>
@@ -20176,7 +20176,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>18.0250606536865</v>
+        <v>18.0250644683838</v>
       </c>
       <c r="H683" t="n">
         <v>1437</v>
@@ -20263,7 +20263,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>20.2558841705322</v>
+        <v>20.2558860778809</v>
       </c>
       <c r="H686" t="n">
         <v>17625</v>
@@ -20292,7 +20292,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>20.7912826538086</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H687" t="n">
         <v>33277</v>
@@ -20379,7 +20379,7 @@
         <v>23</v>
       </c>
       <c r="G690" t="n">
-        <v>20.5235862731934</v>
+        <v>20.5235843658447</v>
       </c>
       <c r="H690" t="n">
         <v>13295</v>
@@ -20466,7 +20466,7 @@
         <v>23.5</v>
       </c>
       <c r="G693" t="n">
-        <v>20.969747543335</v>
+        <v>20.9697494506836</v>
       </c>
       <c r="H693" t="n">
         <v>3825</v>
@@ -20495,7 +20495,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>21.683614730835</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H694" t="n">
         <v>38058</v>
@@ -20640,7 +20640,7 @@
         <v>24</v>
       </c>
       <c r="G699" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H699" t="n">
         <v>4272</v>
@@ -20785,7 +20785,7 @@
         <v>24</v>
       </c>
       <c r="G704" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H704" t="n">
         <v>20313</v>
@@ -20843,7 +20843,7 @@
         <v>24</v>
       </c>
       <c r="G706" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H706" t="n">
         <v>2368</v>
@@ -20872,7 +20872,7 @@
         <v>24</v>
       </c>
       <c r="G707" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H707" t="n">
         <v>10495</v>
@@ -20930,7 +20930,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G709" t="n">
-        <v>21.683614730835</v>
+        <v>21.6836128234863</v>
       </c>
       <c r="H709" t="n">
         <v>3978</v>
@@ -20988,7 +20988,7 @@
         <v>25</v>
       </c>
       <c r="G711" t="n">
-        <v>22.7315864562988</v>
+        <v>22.7315845489502</v>
       </c>
       <c r="H711" t="n">
         <v>5201</v>
@@ -21017,7 +21017,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H712" t="n">
         <v>5833</v>
@@ -21075,7 +21075,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H714" t="n">
         <v>3575</v>
@@ -21104,7 +21104,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H715" t="n">
         <v>1991</v>
@@ -21133,7 +21133,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H716" t="n">
         <v>3812</v>
@@ -21162,7 +21162,7 @@
         <v>24.5</v>
       </c>
       <c r="G717" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769546508789</v>
       </c>
       <c r="H717" t="n">
         <v>2681</v>
@@ -21191,7 +21191,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H718" t="n">
         <v>1554</v>
@@ -21220,7 +21220,7 @@
         <v>24.5</v>
       </c>
       <c r="G719" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769546508789</v>
       </c>
       <c r="H719" t="n">
         <v>565</v>
@@ -21249,7 +21249,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>22.4588069915771</v>
+        <v>22.4588050842285</v>
       </c>
       <c r="H720" t="n">
         <v>2726</v>
@@ -21278,7 +21278,7 @@
         <v>24.5</v>
       </c>
       <c r="G721" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769546508789</v>
       </c>
       <c r="H721" t="n">
         <v>484</v>
@@ -21307,7 +21307,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H722" t="n">
         <v>17150</v>
@@ -21365,7 +21365,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H724" t="n">
         <v>722</v>
@@ -21394,7 +21394,7 @@
         <v>24.5</v>
       </c>
       <c r="G725" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769546508789</v>
       </c>
       <c r="H725" t="n">
         <v>1685</v>
@@ -21452,7 +21452,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>22.640661239624</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H727" t="n">
         <v>412</v>
@@ -21481,7 +21481,7 @@
         <v>24.5</v>
       </c>
       <c r="G728" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769546508789</v>
       </c>
       <c r="H728" t="n">
         <v>11066</v>
@@ -21510,7 +21510,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>22.0041770935059</v>
+        <v>22.0041751861572</v>
       </c>
       <c r="H729" t="n">
         <v>4125</v>
@@ -21539,7 +21539,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>22.095100402832</v>
+        <v>22.0950984954834</v>
       </c>
       <c r="H730" t="n">
         <v>2200</v>
@@ -21655,7 +21655,7 @@
         <v>23.5</v>
       </c>
       <c r="G734" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H734" t="n">
         <v>416</v>
@@ -21684,7 +21684,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H735" t="n">
         <v>5515</v>
@@ -21742,7 +21742,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>21.6404705047607</v>
+        <v>21.6404685974121</v>
       </c>
       <c r="H737" t="n">
         <v>3131</v>
@@ -21800,7 +21800,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H739" t="n">
         <v>7641</v>
@@ -21829,7 +21829,7 @@
         <v>23.5</v>
       </c>
       <c r="G740" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H740" t="n">
         <v>3450</v>
@@ -21858,7 +21858,7 @@
         <v>23.5</v>
       </c>
       <c r="G741" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H741" t="n">
         <v>767</v>
@@ -21887,7 +21887,7 @@
         <v>23.5</v>
       </c>
       <c r="G742" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H742" t="n">
         <v>1047</v>
@@ -21916,7 +21916,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>20.5493507385254</v>
+        <v>20.5493488311768</v>
       </c>
       <c r="H743" t="n">
         <v>3875</v>
@@ -21974,7 +21974,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767639160156</v>
       </c>
       <c r="H745" t="n">
         <v>1335</v>
@@ -22061,7 +22061,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H748" t="n">
         <v>1173</v>
@@ -22090,7 +22090,7 @@
         <v>23.5</v>
       </c>
       <c r="G749" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H749" t="n">
         <v>979</v>
@@ -22119,7 +22119,7 @@
         <v>23.5</v>
       </c>
       <c r="G750" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H750" t="n">
         <v>3667</v>
@@ -22206,7 +22206,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>22.0041770935059</v>
+        <v>22.0041751861572</v>
       </c>
       <c r="H753" t="n">
         <v>2888</v>
@@ -22322,7 +22322,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H757" t="n">
         <v>722</v>
@@ -22351,7 +22351,7 @@
         <v>23.5</v>
       </c>
       <c r="G758" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H758" t="n">
         <v>6240</v>
@@ -22380,7 +22380,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H759" t="n">
         <v>1830</v>
@@ -22409,7 +22409,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767639160156</v>
       </c>
       <c r="H760" t="n">
         <v>2070</v>
@@ -22438,7 +22438,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G761" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H761" t="n">
         <v>2011</v>
@@ -22467,7 +22467,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H762" t="n">
         <v>383</v>
@@ -22496,7 +22496,7 @@
         <v>23.5</v>
       </c>
       <c r="G763" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H763" t="n">
         <v>728</v>
@@ -22554,7 +22554,7 @@
         <v>23.5</v>
       </c>
       <c r="G765" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H765" t="n">
         <v>1731</v>
@@ -22583,7 +22583,7 @@
         <v>23</v>
       </c>
       <c r="G766" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H766" t="n">
         <v>1718</v>
@@ -22612,7 +22612,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H767" t="n">
         <v>305</v>
@@ -22699,7 +22699,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>21.0949096679688</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H770" t="n">
         <v>305</v>
@@ -22728,7 +22728,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H771" t="n">
         <v>779</v>
@@ -22757,7 +22757,7 @@
         <v>23</v>
       </c>
       <c r="G772" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H772" t="n">
         <v>843</v>
@@ -22786,7 +22786,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>21.0949096679688</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H773" t="n">
         <v>688</v>
@@ -22815,7 +22815,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>21.0949096679688</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H774" t="n">
         <v>881</v>
@@ -22873,7 +22873,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G776" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767639160156</v>
       </c>
       <c r="H776" t="n">
         <v>3</v>
@@ -22902,7 +22902,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767639160156</v>
       </c>
       <c r="H777" t="n">
         <v>3189</v>
@@ -22960,7 +22960,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>21.5495433807373</v>
+        <v>21.5495414733887</v>
       </c>
       <c r="H779" t="n">
         <v>4210</v>
@@ -23018,7 +23018,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H781" t="n">
         <v>278</v>
@@ -23047,7 +23047,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>21.0949096679688</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H782" t="n">
         <v>424</v>
@@ -23076,7 +23076,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767639160156</v>
       </c>
       <c r="H783" t="n">
         <v>505</v>
@@ -23105,7 +23105,7 @@
         <v>23</v>
       </c>
       <c r="G784" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H784" t="n">
         <v>1187</v>
@@ -23134,7 +23134,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>20.7312068939209</v>
+        <v>20.7312030792236</v>
       </c>
       <c r="H785" t="n">
         <v>294</v>
@@ -23163,7 +23163,7 @@
         <v>23.5</v>
       </c>
       <c r="G786" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H786" t="n">
         <v>19431</v>
@@ -23192,7 +23192,7 @@
         <v>23.5</v>
       </c>
       <c r="G787" t="n">
-        <v>21.3676929473877</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H787" t="n">
         <v>8270</v>
@@ -23279,7 +23279,7 @@
         <v>23</v>
       </c>
       <c r="G790" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H790" t="n">
         <v>1960</v>
@@ -23308,7 +23308,7 @@
         <v>23</v>
       </c>
       <c r="G791" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H791" t="n">
         <v>417</v>
@@ -23337,7 +23337,7 @@
         <v>23</v>
       </c>
       <c r="G792" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H792" t="n">
         <v>14773</v>
@@ -23366,7 +23366,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H793" t="n">
         <v>1759</v>
@@ -23395,7 +23395,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H794" t="n">
         <v>1332</v>
@@ -23424,7 +23424,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>20.5493507385254</v>
+        <v>20.5493488311768</v>
       </c>
       <c r="H795" t="n">
         <v>869</v>
@@ -23453,7 +23453,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G796" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H796" t="n">
         <v>628</v>
@@ -23482,7 +23482,7 @@
         <v>23</v>
       </c>
       <c r="G797" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H797" t="n">
         <v>710</v>
@@ -23511,7 +23511,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>20.3675003051758</v>
+        <v>20.3675022125244</v>
       </c>
       <c r="H798" t="n">
         <v>4392</v>
@@ -23540,7 +23540,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H799" t="n">
         <v>1250</v>
@@ -23569,7 +23569,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G800" t="n">
-        <v>20.5493507385254</v>
+        <v>20.5493488311768</v>
       </c>
       <c r="H800" t="n">
         <v>7793</v>
@@ -23598,7 +23598,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H801" t="n">
         <v>1969</v>
@@ -23627,7 +23627,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>22.0041770935059</v>
+        <v>22.0041751861572</v>
       </c>
       <c r="H802" t="n">
         <v>30806</v>
@@ -23656,7 +23656,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H803" t="n">
         <v>3814</v>
@@ -23714,7 +23714,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>23.5499229431152</v>
+        <v>23.5499210357666</v>
       </c>
       <c r="H805" t="n">
         <v>15078</v>
@@ -23801,7 +23801,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>24.0045528411865</v>
+        <v>24.0045547485352</v>
       </c>
       <c r="H808" t="n">
         <v>10233</v>
@@ -23830,7 +23830,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>23.0952892303467</v>
+        <v>23.0952911376953</v>
       </c>
       <c r="H809" t="n">
         <v>248720</v>
@@ -23888,7 +23888,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>24.0045528411865</v>
+        <v>24.0045547485352</v>
       </c>
       <c r="H811" t="n">
         <v>3875</v>
@@ -23975,7 +23975,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>24.2773323059082</v>
+        <v>24.2773342132568</v>
       </c>
       <c r="H814" t="n">
         <v>1094</v>
@@ -24033,7 +24033,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7319660186768</v>
+        <v>24.7319641113281</v>
       </c>
       <c r="H816" t="n">
         <v>19373</v>
@@ -24062,7 +24062,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.9138164520264</v>
+        <v>24.9138145446777</v>
       </c>
       <c r="H817" t="n">
         <v>5600</v>
@@ -24091,7 +24091,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.9138164520264</v>
+        <v>24.9138145446777</v>
       </c>
       <c r="H818" t="n">
         <v>1123</v>
@@ -24120,7 +24120,7 @@
         <v>27.5</v>
       </c>
       <c r="G819" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047454833984</v>
       </c>
       <c r="H819" t="n">
         <v>12457</v>
@@ -24265,7 +24265,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>25.2775211334229</v>
+        <v>25.2775230407715</v>
       </c>
       <c r="H824" t="n">
         <v>9201</v>
@@ -24294,7 +24294,7 @@
         <v>27.5</v>
       </c>
       <c r="G825" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047454833984</v>
       </c>
       <c r="H825" t="n">
         <v>7361</v>
@@ -24323,7 +24323,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G826" t="n">
-        <v>24.8228912353516</v>
+        <v>24.8228931427002</v>
       </c>
       <c r="H826" t="n">
         <v>3821</v>
@@ -24352,7 +24352,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>24.8228912353516</v>
+        <v>24.8228931427002</v>
       </c>
       <c r="H827" t="n">
         <v>2515</v>
@@ -24381,7 +24381,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>24.8228912353516</v>
+        <v>24.8228931427002</v>
       </c>
       <c r="H828" t="n">
         <v>2875</v>
@@ -24410,7 +24410,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>24.9138164520264</v>
+        <v>24.9138145446777</v>
       </c>
       <c r="H829" t="n">
         <v>1504</v>
@@ -24439,7 +24439,7 @@
         <v>27.5</v>
       </c>
       <c r="G830" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047454833984</v>
       </c>
       <c r="H830" t="n">
         <v>3462</v>
@@ -24555,7 +24555,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G834" t="n">
-        <v>24.1864070892334</v>
+        <v>24.186408996582</v>
       </c>
       <c r="H834" t="n">
         <v>2244</v>
@@ -24584,7 +24584,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>24.2773323059082</v>
+        <v>24.2773342132568</v>
       </c>
       <c r="H835" t="n">
         <v>942</v>
@@ -24613,7 +24613,7 @@
         <v>27.5</v>
       </c>
       <c r="G836" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047454833984</v>
       </c>
       <c r="H836" t="n">
         <v>3180</v>
@@ -24642,7 +24642,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>25.7321529388428</v>
+        <v>25.7321548461914</v>
       </c>
       <c r="H837" t="n">
         <v>6802</v>
@@ -24729,7 +24729,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5502986907959</v>
       </c>
       <c r="H840" t="n">
         <v>1023</v>
@@ -24758,7 +24758,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>25.8230800628662</v>
+        <v>25.8230781555176</v>
       </c>
       <c r="H841" t="n">
         <v>6920</v>
@@ -24845,7 +24845,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>26.1867828369141</v>
+        <v>26.1867866516113</v>
       </c>
       <c r="H844" t="n">
         <v>4971</v>
@@ -24874,7 +24874,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>26.2777099609375</v>
+        <v>26.2777118682861</v>
       </c>
       <c r="H845" t="n">
         <v>4924</v>
@@ -24903,7 +24903,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>26.2777099609375</v>
+        <v>26.2777118682861</v>
       </c>
       <c r="H846" t="n">
         <v>2260</v>
@@ -25019,7 +25019,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5502986907959</v>
       </c>
       <c r="H850" t="n">
         <v>4390</v>
@@ -25077,7 +25077,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5502986907959</v>
       </c>
       <c r="H852" t="n">
         <v>2971</v>
@@ -25106,7 +25106,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>26.1867828369141</v>
+        <v>26.1867866516113</v>
       </c>
       <c r="H853" t="n">
         <v>2676</v>
@@ -25135,7 +25135,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>25.8230800628662</v>
+        <v>25.8230781555176</v>
       </c>
       <c r="H854" t="n">
         <v>6517</v>
@@ -25251,7 +25251,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>28.0053100585938</v>
+        <v>28.005313873291</v>
       </c>
       <c r="H858" t="n">
         <v>16337</v>
@@ -25280,7 +25280,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>29.005500793457</v>
+        <v>29.0055027008057</v>
       </c>
       <c r="H859" t="n">
         <v>9815</v>
@@ -25309,7 +25309,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>29.7329139709473</v>
+        <v>29.7329158782959</v>
       </c>
       <c r="H860" t="n">
         <v>11282</v>
@@ -25338,7 +25338,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G861" t="n">
-        <v>30.278470993042</v>
+        <v>30.2784690856934</v>
       </c>
       <c r="H861" t="n">
         <v>13365</v>
@@ -25367,7 +25367,7 @@
         <v>32.5</v>
       </c>
       <c r="G862" t="n">
-        <v>29.5510578155518</v>
+        <v>29.5510597229004</v>
       </c>
       <c r="H862" t="n">
         <v>8073</v>
@@ -25425,7 +25425,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G864" t="n">
-        <v>29.9147682189941</v>
+        <v>29.9147663116455</v>
       </c>
       <c r="H864" t="n">
         <v>1831</v>
@@ -25599,7 +25599,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H870" t="n">
         <v>18083</v>
@@ -25686,7 +25686,7 @@
         <v>40</v>
       </c>
       <c r="G873" t="n">
-        <v>36.3705406188965</v>
+        <v>36.3705368041992</v>
       </c>
       <c r="H873" t="n">
         <v>15350</v>
@@ -25773,7 +25773,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>34.1883010864258</v>
+        <v>34.1882972717285</v>
       </c>
       <c r="H876" t="n">
         <v>14351</v>
@@ -25802,7 +25802,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G877" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H877" t="n">
         <v>17056</v>
@@ -25831,7 +25831,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G878" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H878" t="n">
         <v>9962</v>
@@ -25860,7 +25860,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>35.1884956359863</v>
+        <v>35.1884918212891</v>
       </c>
       <c r="H879" t="n">
         <v>1363</v>
@@ -25947,7 +25947,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G882" t="n">
-        <v>34.1883010864258</v>
+        <v>34.1882972717285</v>
       </c>
       <c r="H882" t="n">
         <v>2774</v>
@@ -25976,7 +25976,7 @@
         <v>37.5</v>
       </c>
       <c r="G883" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H883" t="n">
         <v>3077</v>
@@ -26005,7 +26005,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>34.8247909545898</v>
+        <v>34.8247871398926</v>
       </c>
       <c r="H884" t="n">
         <v>7646</v>
@@ -26063,7 +26063,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G886" t="n">
-        <v>34.4610824584961</v>
+        <v>34.4610786437988</v>
       </c>
       <c r="H886" t="n">
         <v>5736</v>
@@ -26092,7 +26092,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>34.1883010864258</v>
+        <v>34.1882972717285</v>
       </c>
       <c r="H887" t="n">
         <v>3978</v>
@@ -26150,7 +26150,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>34.8247909545898</v>
+        <v>34.8247871398926</v>
       </c>
       <c r="H889" t="n">
         <v>3085</v>
@@ -26208,7 +26208,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H891" t="n">
         <v>8405</v>
@@ -26237,7 +26237,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H892" t="n">
         <v>6935</v>
@@ -26266,7 +26266,7 @@
         <v>37.5</v>
       </c>
       <c r="G893" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H893" t="n">
         <v>3082</v>
@@ -26295,7 +26295,7 @@
         <v>37</v>
       </c>
       <c r="G894" t="n">
-        <v>33.6427421569824</v>
+        <v>33.6427459716797</v>
       </c>
       <c r="H894" t="n">
         <v>6046</v>
@@ -26324,7 +26324,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G895" t="n">
-        <v>34.4610824584961</v>
+        <v>34.4610786437988</v>
       </c>
       <c r="H895" t="n">
         <v>8776</v>
@@ -26411,7 +26411,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G898" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336769104004</v>
       </c>
       <c r="H898" t="n">
         <v>5138</v>
@@ -26527,7 +26527,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H902" t="n">
         <v>30124</v>
@@ -26556,7 +26556,7 @@
         <v>38</v>
       </c>
       <c r="G903" t="n">
-        <v>34.5520095825195</v>
+        <v>34.5520133972168</v>
       </c>
       <c r="H903" t="n">
         <v>12607</v>
@@ -26614,7 +26614,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H905" t="n">
         <v>8882</v>
@@ -26672,7 +26672,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G907" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H907" t="n">
         <v>10279</v>
@@ -26701,7 +26701,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>34.8247909545898</v>
+        <v>34.8247871398926</v>
       </c>
       <c r="H908" t="n">
         <v>5104</v>
@@ -26730,7 +26730,7 @@
         <v>37.5</v>
       </c>
       <c r="G909" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H909" t="n">
         <v>1722</v>
@@ -26759,7 +26759,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336769104004</v>
       </c>
       <c r="H910" t="n">
         <v>2409</v>
@@ -26788,7 +26788,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G911" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336769104004</v>
       </c>
       <c r="H911" t="n">
         <v>2922</v>
@@ -26817,7 +26817,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G912" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336769104004</v>
       </c>
       <c r="H912" t="n">
         <v>13822</v>
@@ -26846,7 +26846,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>33.2790374755859</v>
+        <v>33.2790412902832</v>
       </c>
       <c r="H913" t="n">
         <v>3210</v>
@@ -26875,7 +26875,7 @@
         <v>37</v>
       </c>
       <c r="G914" t="n">
-        <v>33.6427421569824</v>
+        <v>33.6427459716797</v>
       </c>
       <c r="H914" t="n">
         <v>4087</v>
@@ -26933,7 +26933,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>32.9153366088867</v>
+        <v>32.9153327941895</v>
       </c>
       <c r="H916" t="n">
         <v>5400</v>
@@ -26962,7 +26962,7 @@
         <v>37</v>
       </c>
       <c r="G917" t="n">
-        <v>33.6427421569824</v>
+        <v>33.6427459716797</v>
       </c>
       <c r="H917" t="n">
         <v>3855</v>
@@ -26991,7 +26991,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H918" t="n">
         <v>1642</v>
@@ -27049,7 +27049,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G920" t="n">
-        <v>33.0062637329102</v>
+        <v>33.0062599182129</v>
       </c>
       <c r="H920" t="n">
         <v>1008</v>
@@ -27078,7 +27078,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G921" t="n">
-        <v>32.9153366088867</v>
+        <v>32.9153327941895</v>
       </c>
       <c r="H921" t="n">
         <v>160</v>
@@ -27107,7 +27107,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H922" t="n">
         <v>3813</v>
@@ -27194,7 +27194,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G925" t="n">
-        <v>33.2790374755859</v>
+        <v>33.2790412902832</v>
       </c>
       <c r="H925" t="n">
         <v>1376</v>
@@ -27223,7 +27223,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>33.0062637329102</v>
+        <v>33.0062599182129</v>
       </c>
       <c r="H926" t="n">
         <v>3948</v>
@@ -27281,7 +27281,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.6425590515137</v>
+        <v>32.6425514221191</v>
       </c>
       <c r="H928" t="n">
         <v>5913</v>
@@ -27339,7 +27339,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.5518188476562</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H930" t="n">
         <v>13794</v>
@@ -27368,7 +27368,7 @@
         <v>39.5</v>
       </c>
       <c r="G931" t="n">
-        <v>35.915901184082</v>
+        <v>35.9159049987793</v>
       </c>
       <c r="H931" t="n">
         <v>14219</v>
@@ -27426,7 +27426,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.1883010864258</v>
+        <v>34.1882972717285</v>
       </c>
       <c r="H933" t="n">
         <v>13379</v>
@@ -27455,7 +27455,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H934" t="n">
         <v>5593</v>
@@ -27513,7 +27513,7 @@
         <v>37.5</v>
       </c>
       <c r="G936" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H936" t="n">
         <v>3891</v>
@@ -27542,7 +27542,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G937" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H937" t="n">
         <v>43211</v>
@@ -27571,7 +27571,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H938" t="n">
         <v>1429</v>
@@ -27600,7 +27600,7 @@
         <v>37.5</v>
       </c>
       <c r="G939" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H939" t="n">
         <v>1372</v>
@@ -27629,7 +27629,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G940" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336769104004</v>
       </c>
       <c r="H940" t="n">
         <v>3638</v>
@@ -27658,7 +27658,7 @@
         <v>37</v>
       </c>
       <c r="G941" t="n">
-        <v>33.6427421569824</v>
+        <v>33.6427459716797</v>
       </c>
       <c r="H941" t="n">
         <v>2299</v>
@@ -27687,7 +27687,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H942" t="n">
         <v>7615</v>
@@ -27716,7 +27716,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G943" t="n">
-        <v>34.0064506530762</v>
+        <v>34.0064582824707</v>
       </c>
       <c r="H943" t="n">
         <v>5713</v>
@@ -27745,7 +27745,7 @@
         <v>37.5</v>
       </c>
       <c r="G944" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H944" t="n">
         <v>3069</v>
@@ -27803,7 +27803,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H946" t="n">
         <v>1543</v>
@@ -27832,7 +27832,7 @@
         <v>37.5</v>
       </c>
       <c r="G947" t="n">
-        <v>34.0973739624023</v>
+        <v>34.0973777770996</v>
       </c>
       <c r="H947" t="n">
         <v>2150</v>
@@ -27861,7 +27861,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G948" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H948" t="n">
         <v>1091</v>
@@ -28006,7 +28006,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G953" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H953" t="n">
         <v>3746</v>
@@ -28064,7 +28064,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G955" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336769104004</v>
       </c>
       <c r="H955" t="n">
         <v>782</v>
@@ -28093,7 +28093,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336769104004</v>
       </c>
       <c r="H956" t="n">
         <v>2318</v>
@@ -28122,7 +28122,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H957" t="n">
         <v>3272</v>
@@ -28151,7 +28151,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G958" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H958" t="n">
         <v>2088</v>
@@ -28238,7 +28238,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>34.5444602966309</v>
+        <v>34.5444641113281</v>
       </c>
       <c r="H961" t="n">
         <v>2709</v>
@@ -28354,7 +28354,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G965" t="n">
-        <v>34.5444602966309</v>
+        <v>34.5444641113281</v>
       </c>
       <c r="H965" t="n">
         <v>6827</v>
@@ -28383,7 +28383,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G966" t="n">
-        <v>34.1740074157715</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H966" t="n">
         <v>4232</v>
@@ -28412,7 +28412,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>34.1740074157715</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H967" t="n">
         <v>5406</v>
@@ -28441,7 +28441,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G968" t="n">
-        <v>33.896167755127</v>
+        <v>33.8961639404297</v>
       </c>
       <c r="H968" t="n">
         <v>11032</v>
@@ -28470,7 +28470,7 @@
         <v>36.5</v>
       </c>
       <c r="G969" t="n">
-        <v>33.8035545349121</v>
+        <v>33.8035621643066</v>
       </c>
       <c r="H969" t="n">
         <v>1933</v>
@@ -28528,7 +28528,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G971" t="n">
-        <v>34.1740074157715</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H971" t="n">
         <v>1501</v>
@@ -28586,7 +28586,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G973" t="n">
-        <v>34.0813980102539</v>
+        <v>34.0813903808594</v>
       </c>
       <c r="H973" t="n">
         <v>5784</v>
@@ -28615,7 +28615,7 @@
         <v>36.5</v>
       </c>
       <c r="G974" t="n">
-        <v>33.8035545349121</v>
+        <v>33.8035621643066</v>
       </c>
       <c r="H974" t="n">
         <v>1613</v>
@@ -28644,7 +28644,7 @@
         <v>36.5</v>
       </c>
       <c r="G975" t="n">
-        <v>33.8035545349121</v>
+        <v>33.8035621643066</v>
       </c>
       <c r="H975" t="n">
         <v>3105</v>
@@ -28731,7 +28731,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>33.618335723877</v>
+        <v>33.6183319091797</v>
       </c>
       <c r="H978" t="n">
         <v>4498</v>
@@ -28760,7 +28760,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G979" t="n">
-        <v>33.618335723877</v>
+        <v>33.6183319091797</v>
       </c>
       <c r="H979" t="n">
         <v>4569</v>
@@ -28789,7 +28789,7 @@
         <v>36</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3404998779297</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H980" t="n">
         <v>3550</v>
@@ -28818,7 +28818,7 @@
         <v>36</v>
       </c>
       <c r="G981" t="n">
-        <v>33.3404998779297</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H981" t="n">
         <v>8066</v>
@@ -28876,7 +28876,7 @@
         <v>36.5</v>
       </c>
       <c r="G983" t="n">
-        <v>33.8035545349121</v>
+        <v>33.8035621643066</v>
       </c>
       <c r="H983" t="n">
         <v>27322</v>
@@ -28963,7 +28963,7 @@
         <v>39</v>
       </c>
       <c r="G986" t="n">
-        <v>36.1188697814941</v>
+        <v>36.1188735961914</v>
       </c>
       <c r="H986" t="n">
         <v>41483</v>
@@ -28992,7 +28992,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G987" t="n">
-        <v>38.6194076538086</v>
+        <v>38.6194114685059</v>
       </c>
       <c r="H987" t="n">
         <v>51406</v>
@@ -29108,7 +29108,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>42.2312927246094</v>
+        <v>42.2312965393066</v>
       </c>
       <c r="H991" t="n">
         <v>8761</v>
@@ -29195,7 +29195,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G994" t="n">
-        <v>42.4165191650391</v>
+        <v>42.4165229797363</v>
       </c>
       <c r="H994" t="n">
         <v>28173</v>
@@ -29253,7 +29253,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>45.9357948303223</v>
+        <v>45.9357986450195</v>
       </c>
       <c r="H996" t="n">
         <v>42057</v>
@@ -29601,7 +29601,7 @@
         <v>50</v>
       </c>
       <c r="G1008" t="n">
-        <v>46.3062515258789</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1008" t="n">
         <v>9494</v>
@@ -29659,7 +29659,7 @@
         <v>50</v>
       </c>
       <c r="G1010" t="n">
-        <v>46.3062515258789</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1010" t="n">
         <v>4334</v>
@@ -29688,7 +29688,7 @@
         <v>50</v>
       </c>
       <c r="G1011" t="n">
-        <v>46.3062515258789</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1011" t="n">
         <v>9263</v>
@@ -29717,7 +29717,7 @@
         <v>49</v>
       </c>
       <c r="G1012" t="n">
-        <v>45.3801231384277</v>
+        <v>45.3801193237305</v>
       </c>
       <c r="H1012" t="n">
         <v>9197</v>
@@ -29920,7 +29920,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1019" t="n">
-        <v>46.8619194030762</v>
+        <v>46.8619232177734</v>
       </c>
       <c r="H1019" t="n">
         <v>3286</v>
@@ -29949,7 +29949,7 @@
         <v>50</v>
       </c>
       <c r="G1020" t="n">
-        <v>46.3062515258789</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1020" t="n">
         <v>4229</v>
@@ -30181,7 +30181,7 @@
         <v>60</v>
       </c>
       <c r="G1028" t="n">
-        <v>55.5674896240234</v>
+        <v>55.567497253418</v>
       </c>
       <c r="H1028" t="n">
         <v>48705</v>
@@ -30268,7 +30268,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>58.1606407165527</v>
+        <v>58.1606369018555</v>
       </c>
       <c r="H1031" t="n">
         <v>5992</v>
@@ -30413,7 +30413,7 @@
         <v>61</v>
       </c>
       <c r="G1036" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1036" t="n">
         <v>5963</v>
@@ -30500,7 +30500,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>55.0118217468262</v>
+        <v>55.0118255615234</v>
       </c>
       <c r="H1039" t="n">
         <v>13841</v>
@@ -30587,7 +30587,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>59.6424446105957</v>
+        <v>59.6424522399902</v>
       </c>
       <c r="H1042" t="n">
         <v>52827</v>
@@ -30616,7 +30616,7 @@
         <v>65</v>
       </c>
       <c r="G1043" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1043" t="n">
         <v>9419</v>
@@ -30732,7 +30732,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1047" t="n">
-        <v>62.7912826538086</v>
+        <v>62.7912712097168</v>
       </c>
       <c r="H1047" t="n">
         <v>20312</v>
@@ -30761,7 +30761,7 @@
         <v>71</v>
       </c>
       <c r="G1048" t="n">
-        <v>65.7548599243164</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1048" t="n">
         <v>33718</v>
@@ -30790,7 +30790,7 @@
         <v>71</v>
       </c>
       <c r="G1049" t="n">
-        <v>65.7548599243164</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1049" t="n">
         <v>27056</v>
@@ -30819,7 +30819,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>65.1992034912109</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1050" t="n">
         <v>20635</v>
@@ -30848,7 +30848,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1051" t="n">
-        <v>65.1992034912109</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1051" t="n">
         <v>16230</v>
@@ -30906,7 +30906,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>65.1992034912109</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1053" t="n">
         <v>9328</v>
@@ -30935,7 +30935,7 @@
         <v>70</v>
       </c>
       <c r="G1054" t="n">
-        <v>64.8287506103516</v>
+        <v>64.828742980957</v>
       </c>
       <c r="H1054" t="n">
         <v>12488</v>
@@ -31080,7 +31080,7 @@
         <v>69</v>
       </c>
       <c r="G1059" t="n">
-        <v>63.9026145935059</v>
+        <v>63.9026222229004</v>
       </c>
       <c r="H1059" t="n">
         <v>24805</v>
@@ -31109,7 +31109,7 @@
         <v>67</v>
       </c>
       <c r="G1060" t="n">
-        <v>62.0503692626953</v>
+        <v>62.0503768920898</v>
       </c>
       <c r="H1060" t="n">
         <v>10940</v>
@@ -31196,7 +31196,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>61.4946937561035</v>
+        <v>61.494701385498</v>
       </c>
       <c r="H1063" t="n">
         <v>4540</v>
@@ -31254,7 +31254,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>60.5685691833496</v>
+        <v>60.5685653686523</v>
       </c>
       <c r="H1065" t="n">
         <v>10994</v>
@@ -31283,7 +31283,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1066" t="n">
-        <v>58.1606407165527</v>
+        <v>58.1606369018555</v>
       </c>
       <c r="H1066" t="n">
         <v>16555</v>
@@ -31370,7 +31370,7 @@
         <v>61</v>
       </c>
       <c r="G1069" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1069" t="n">
         <v>6987</v>
@@ -31428,7 +31428,7 @@
         <v>64</v>
       </c>
       <c r="G1071" t="n">
-        <v>59.2719955444336</v>
+        <v>59.2719917297363</v>
       </c>
       <c r="H1071" t="n">
         <v>19842</v>
@@ -31515,7 +31515,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>57.6049766540527</v>
+        <v>57.6049728393555</v>
       </c>
       <c r="H1074" t="n">
         <v>9173</v>
@@ -31573,7 +31573,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>57.2345237731934</v>
+        <v>57.2345199584961</v>
       </c>
       <c r="H1076" t="n">
         <v>7020</v>
@@ -31660,7 +31660,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1079" t="n">
-        <v>61.3094596862793</v>
+        <v>61.3094711303711</v>
       </c>
       <c r="H1079" t="n">
         <v>18499</v>
@@ -31747,7 +31747,7 @@
         <v>69</v>
       </c>
       <c r="G1082" t="n">
-        <v>63.9026145935059</v>
+        <v>63.9026222229004</v>
       </c>
       <c r="H1082" t="n">
         <v>5155</v>
@@ -31776,7 +31776,7 @@
         <v>68</v>
       </c>
       <c r="G1083" t="n">
-        <v>62.9764938354492</v>
+        <v>62.9765014648438</v>
       </c>
       <c r="H1083" t="n">
         <v>14757</v>
@@ -31805,7 +31805,7 @@
         <v>67</v>
       </c>
       <c r="G1084" t="n">
-        <v>62.0503692626953</v>
+        <v>62.0503768920898</v>
       </c>
       <c r="H1084" t="n">
         <v>14476</v>
@@ -31834,7 +31834,7 @@
         <v>67</v>
       </c>
       <c r="G1085" t="n">
-        <v>62.0503692626953</v>
+        <v>62.0503768920898</v>
       </c>
       <c r="H1085" t="n">
         <v>9085</v>
@@ -31863,7 +31863,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>62.7912826538086</v>
+        <v>62.7912712097168</v>
       </c>
       <c r="H1086" t="n">
         <v>23354</v>
@@ -31892,7 +31892,7 @@
         <v>68</v>
       </c>
       <c r="G1087" t="n">
-        <v>62.9764938354492</v>
+        <v>62.9765014648438</v>
       </c>
       <c r="H1087" t="n">
         <v>9103</v>
@@ -31950,7 +31950,7 @@
         <v>68</v>
       </c>
       <c r="G1089" t="n">
-        <v>62.9764938354492</v>
+        <v>62.9765014648438</v>
       </c>
       <c r="H1089" t="n">
         <v>7549</v>
@@ -32008,7 +32008,7 @@
         <v>72</v>
       </c>
       <c r="G1091" t="n">
-        <v>66.6809997558594</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1091" t="n">
         <v>20242</v>
@@ -32037,7 +32037,7 @@
         <v>71</v>
       </c>
       <c r="G1092" t="n">
-        <v>65.7548599243164</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1092" t="n">
         <v>9074</v>
@@ -32124,7 +32124,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>65.5696563720703</v>
+        <v>65.5696487426758</v>
       </c>
       <c r="H1095" t="n">
         <v>9719</v>
@@ -32182,7 +32182,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G1097" t="n">
-        <v>65.9400939941406</v>
+        <v>65.9401016235352</v>
       </c>
       <c r="H1097" t="n">
         <v>9269</v>
@@ -32211,7 +32211,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1098" t="n">
-        <v>65.1992034912109</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1098" t="n">
         <v>5246</v>
@@ -32240,7 +32240,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1099" t="n">
-        <v>65.5696563720703</v>
+        <v>65.5696487426758</v>
       </c>
       <c r="H1099" t="n">
         <v>22010</v>
@@ -32385,7 +32385,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1104" t="n">
-        <v>64.0878372192383</v>
+        <v>64.0878524780273</v>
       </c>
       <c r="H1104" t="n">
         <v>8003</v>
@@ -32414,7 +32414,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1105" t="n">
-        <v>67.7923355102539</v>
+        <v>67.7923278808594</v>
       </c>
       <c r="H1105" t="n">
         <v>43163</v>
@@ -32472,7 +32472,7 @@
         <v>74</v>
       </c>
       <c r="G1107" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1107" t="n">
         <v>25256</v>
@@ -32501,7 +32501,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1108" t="n">
-        <v>70.2002563476562</v>
+        <v>70.2002639770508</v>
       </c>
       <c r="H1108" t="n">
         <v>15408</v>
@@ -32530,7 +32530,7 @@
         <v>74</v>
       </c>
       <c r="G1109" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1109" t="n">
         <v>24390</v>
@@ -32588,7 +32588,7 @@
         <v>71</v>
       </c>
       <c r="G1111" t="n">
-        <v>65.7548599243164</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1111" t="n">
         <v>110589</v>
@@ -32617,7 +32617,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1112" t="n">
-        <v>68.1627960205078</v>
+        <v>68.1627807617188</v>
       </c>
       <c r="H1112" t="n">
         <v>9255</v>
@@ -32646,7 +32646,7 @@
         <v>74</v>
       </c>
       <c r="G1113" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1113" t="n">
         <v>10107</v>
@@ -32733,7 +32733,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>69.0889205932617</v>
+        <v>69.0889282226562</v>
       </c>
       <c r="H1116" t="n">
         <v>7602</v>
@@ -32762,7 +32762,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1117" t="n">
-        <v>68.1627960205078</v>
+        <v>68.1627807617188</v>
       </c>
       <c r="H1117" t="n">
         <v>5033</v>
@@ -32791,7 +32791,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1118" t="n">
-        <v>67.7923355102539</v>
+        <v>67.7923278808594</v>
       </c>
       <c r="H1118" t="n">
         <v>10546</v>
@@ -32820,7 +32820,7 @@
         <v>73</v>
       </c>
       <c r="G1119" t="n">
-        <v>67.6071090698242</v>
+        <v>67.6071243286133</v>
       </c>
       <c r="H1119" t="n">
         <v>2532</v>
@@ -32878,7 +32878,7 @@
         <v>73</v>
       </c>
       <c r="G1121" t="n">
-        <v>67.6071090698242</v>
+        <v>67.6071243286133</v>
       </c>
       <c r="H1121" t="n">
         <v>7639</v>
@@ -32936,7 +32936,7 @@
         <v>72</v>
       </c>
       <c r="G1123" t="n">
-        <v>66.6809997558594</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1123" t="n">
         <v>3823</v>
@@ -32994,7 +32994,7 @@
         <v>74</v>
       </c>
       <c r="G1125" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1125" t="n">
         <v>8495</v>
@@ -33023,7 +33023,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1126" t="n">
-        <v>68.1627960205078</v>
+        <v>68.1627807617188</v>
       </c>
       <c r="H1126" t="n">
         <v>5608</v>
@@ -33110,7 +33110,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1129" t="n">
-        <v>68.1627960205078</v>
+        <v>68.1627807617188</v>
       </c>
       <c r="H1129" t="n">
         <v>3417</v>
@@ -33139,7 +33139,7 @@
         <v>73</v>
       </c>
       <c r="G1130" t="n">
-        <v>67.6071090698242</v>
+        <v>67.6071243286133</v>
       </c>
       <c r="H1130" t="n">
         <v>3689</v>
@@ -33168,7 +33168,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1131" t="n">
-        <v>69.0889205932617</v>
+        <v>69.0889282226562</v>
       </c>
       <c r="H1131" t="n">
         <v>6699</v>
@@ -33197,7 +33197,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>69.8298263549805</v>
+        <v>69.8298187255859</v>
       </c>
       <c r="H1132" t="n">
         <v>10422</v>
@@ -33226,7 +33226,7 @@
         <v>75</v>
       </c>
       <c r="G1133" t="n">
-        <v>69.4593734741211</v>
+        <v>69.4593658447266</v>
       </c>
       <c r="H1133" t="n">
         <v>3252</v>
@@ -33255,7 +33255,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1134" t="n">
-        <v>70.2002563476562</v>
+        <v>70.2002639770508</v>
       </c>
       <c r="H1134" t="n">
         <v>7874</v>
@@ -33313,7 +33313,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>71.867301940918</v>
+        <v>71.8672943115234</v>
       </c>
       <c r="H1136" t="n">
         <v>9339</v>
@@ -33342,7 +33342,7 @@
         <v>78</v>
       </c>
       <c r="G1137" t="n">
-        <v>72.2377395629883</v>
+        <v>72.2377471923828</v>
       </c>
       <c r="H1137" t="n">
         <v>8145</v>
@@ -33371,7 +33371,7 @@
         <v>73.8000030517578</v>
       </c>
       <c r="G1138" t="n">
-        <v>68.348014831543</v>
+        <v>68.3480224609375</v>
       </c>
       <c r="H1138" t="n">
         <v>13068</v>
@@ -33400,7 +33400,7 @@
         <v>74</v>
       </c>
       <c r="G1139" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1139" t="n">
         <v>10084</v>
@@ -33516,7 +33516,7 @@
         <v>70</v>
       </c>
       <c r="G1143" t="n">
-        <v>64.8287506103516</v>
+        <v>64.828742980957</v>
       </c>
       <c r="H1143" t="n">
         <v>22451</v>
@@ -33574,7 +33574,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1145" t="n">
-        <v>64.6435241699219</v>
+        <v>64.6435165405273</v>
       </c>
       <c r="H1145" t="n">
         <v>10235</v>
@@ -33603,7 +33603,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1146" t="n">
-        <v>65.1992034912109</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1146" t="n">
         <v>9298</v>
@@ -33690,7 +33690,7 @@
         <v>67</v>
       </c>
       <c r="G1149" t="n">
-        <v>62.0503692626953</v>
+        <v>62.0503768920898</v>
       </c>
       <c r="H1149" t="n">
         <v>9187</v>
@@ -33777,7 +33777,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1152" t="n">
-        <v>61.3094596862793</v>
+        <v>61.3094711303711</v>
       </c>
       <c r="H1152" t="n">
         <v>5804</v>
@@ -33864,7 +33864,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>60.939022064209</v>
+        <v>60.9390258789062</v>
       </c>
       <c r="H1155" t="n">
         <v>10916</v>
@@ -33922,7 +33922,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1157" t="n">
-        <v>59.0867652893066</v>
+        <v>59.0867691040039</v>
       </c>
       <c r="H1157" t="n">
         <v>8194</v>
@@ -33951,7 +33951,7 @@
         <v>65</v>
       </c>
       <c r="G1158" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1158" t="n">
         <v>10093</v>
@@ -34038,7 +34038,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>59.0867652893066</v>
+        <v>59.0867691040039</v>
       </c>
       <c r="H1161" t="n">
         <v>5556</v>
@@ -34067,7 +34067,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1162" t="n">
-        <v>59.457218170166</v>
+        <v>59.4572143554688</v>
       </c>
       <c r="H1162" t="n">
         <v>7471</v>
@@ -34212,7 +34212,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1167" t="n">
-        <v>59.0867652893066</v>
+        <v>59.0867691040039</v>
       </c>
       <c r="H1167" t="n">
         <v>9054</v>
@@ -34328,7 +34328,7 @@
         <v>60</v>
       </c>
       <c r="G1171" t="n">
-        <v>55.5674896240234</v>
+        <v>55.567497253418</v>
       </c>
       <c r="H1171" t="n">
         <v>20455</v>
@@ -34357,7 +34357,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>57.2345237731934</v>
+        <v>57.2345199584961</v>
       </c>
       <c r="H1172" t="n">
         <v>9422</v>
@@ -34386,7 +34386,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>58.1606407165527</v>
+        <v>58.1606369018555</v>
       </c>
       <c r="H1173" t="n">
         <v>12736</v>
@@ -34444,7 +34444,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1175" t="n">
-        <v>57.2345237731934</v>
+        <v>57.2345199584961</v>
       </c>
       <c r="H1175" t="n">
         <v>8716</v>
@@ -34473,7 +34473,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1176" t="n">
-        <v>55.1970405578613</v>
+        <v>55.1970443725586</v>
       </c>
       <c r="H1176" t="n">
         <v>12029</v>
@@ -34560,7 +34560,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1179" t="n">
-        <v>51.3073234558105</v>
+        <v>51.3073196411133</v>
       </c>
       <c r="H1179" t="n">
         <v>7235</v>
@@ -34618,7 +34618,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>52.2334480285645</v>
+        <v>52.2334518432617</v>
       </c>
       <c r="H1181" t="n">
         <v>3643</v>
@@ -34647,7 +34647,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1182" t="n">
-        <v>55.1970405578613</v>
+        <v>55.1970443725586</v>
       </c>
       <c r="H1182" t="n">
         <v>3171</v>
@@ -34705,7 +34705,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1184" t="n">
-        <v>55.3822708129883</v>
+        <v>55.382266998291</v>
       </c>
       <c r="H1184" t="n">
         <v>5635</v>
@@ -34734,7 +34734,7 @@
         <v>61</v>
       </c>
       <c r="G1185" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1185" t="n">
         <v>8219</v>
@@ -34763,7 +34763,7 @@
         <v>61</v>
       </c>
       <c r="G1186" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1186" t="n">
         <v>3492</v>
@@ -34792,7 +34792,7 @@
         <v>60</v>
       </c>
       <c r="G1187" t="n">
-        <v>55.5674896240234</v>
+        <v>55.567497253418</v>
       </c>
       <c r="H1187" t="n">
         <v>5045</v>
@@ -34821,7 +34821,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>60.5685691833496</v>
+        <v>60.5685653686523</v>
       </c>
       <c r="H1188" t="n">
         <v>18854</v>
@@ -34850,7 +34850,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1189" t="n">
-        <v>61.3094596862793</v>
+        <v>61.3094711303711</v>
       </c>
       <c r="H1189" t="n">
         <v>10432</v>
@@ -34879,7 +34879,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1190" t="n">
-        <v>60.939022064209</v>
+        <v>60.9390258789062</v>
       </c>
       <c r="H1190" t="n">
         <v>5931</v>
@@ -34908,7 +34908,7 @@
         <v>65</v>
       </c>
       <c r="G1191" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1191" t="n">
         <v>8658</v>
@@ -34937,7 +34937,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1192" t="n">
-        <v>59.457218170166</v>
+        <v>59.4572143554688</v>
       </c>
       <c r="H1192" t="n">
         <v>4435</v>
@@ -35024,7 +35024,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1195" t="n">
-        <v>59.0867652893066</v>
+        <v>59.0867691040039</v>
       </c>
       <c r="H1195" t="n">
         <v>6314</v>
@@ -35082,7 +35082,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1197" t="n">
-        <v>59.0867652893066</v>
+        <v>59.0867691040039</v>
       </c>
       <c r="H1197" t="n">
         <v>5073</v>
@@ -35140,7 +35140,7 @@
         <v>65</v>
       </c>
       <c r="G1199" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1199" t="n">
         <v>32409</v>
@@ -35169,7 +35169,7 @@
         <v>63.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>58.8089332580566</v>
+        <v>58.8089370727539</v>
       </c>
       <c r="H1200" t="n">
         <v>4442</v>
@@ -35227,7 +35227,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1202" t="n">
-        <v>61.8651466369629</v>
+        <v>61.8651504516602</v>
       </c>
       <c r="H1202" t="n">
         <v>7305</v>
@@ -35256,7 +35256,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>61.4946937561035</v>
+        <v>61.494701385498</v>
       </c>
       <c r="H1203" t="n">
         <v>5708</v>
@@ -35343,7 +35343,7 @@
         <v>67</v>
       </c>
       <c r="G1206" t="n">
-        <v>62.0503692626953</v>
+        <v>62.0503768920898</v>
       </c>
       <c r="H1206" t="n">
         <v>7404</v>
@@ -35372,7 +35372,7 @@
         <v>65</v>
       </c>
       <c r="G1207" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1207" t="n">
         <v>3155</v>
@@ -35401,7 +35401,7 @@
         <v>65</v>
       </c>
       <c r="G1208" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1208" t="n">
         <v>4312</v>
@@ -35430,7 +35430,7 @@
         <v>65</v>
       </c>
       <c r="G1209" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1209" t="n">
         <v>3029</v>
@@ -35459,7 +35459,7 @@
         <v>65</v>
       </c>
       <c r="G1210" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1210" t="n">
         <v>3326</v>
@@ -35488,7 +35488,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1211" t="n">
-        <v>59.9202842712402</v>
+        <v>59.9202766418457</v>
       </c>
       <c r="H1211" t="n">
         <v>3950</v>
@@ -35517,7 +35517,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>58.623706817627</v>
+        <v>58.6237106323242</v>
       </c>
       <c r="H1212" t="n">
         <v>5794</v>
@@ -35546,7 +35546,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>58.1606407165527</v>
+        <v>58.1606369018555</v>
       </c>
       <c r="H1213" t="n">
         <v>4220</v>
@@ -35662,7 +35662,7 @@
         <v>63.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>59.4594116210938</v>
+        <v>59.459415435791</v>
       </c>
       <c r="H1217" t="n">
         <v>7287</v>
@@ -35691,7 +35691,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>56.3693923950195</v>
+        <v>56.3693962097168</v>
       </c>
       <c r="H1218" t="n">
         <v>13625</v>
@@ -35720,7 +35720,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>54.4966583251953</v>
+        <v>54.4966621398926</v>
       </c>
       <c r="H1219" t="n">
         <v>6610</v>
@@ -35749,7 +35749,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1220" t="n">
-        <v>51.5939102172852</v>
+        <v>51.5939140319824</v>
       </c>
       <c r="H1220" t="n">
         <v>9662</v>
@@ -35836,7 +35836,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1223" t="n">
         <v>8299</v>
@@ -35923,7 +35923,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1226" t="n">
-        <v>56.5566711425781</v>
+        <v>56.5566673278809</v>
       </c>
       <c r="H1226" t="n">
         <v>5095</v>
@@ -35952,7 +35952,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>57.0248527526855</v>
+        <v>57.0248565673828</v>
       </c>
       <c r="H1227" t="n">
         <v>4148</v>
@@ -35981,7 +35981,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1228" t="n">
-        <v>56.0884857177734</v>
+        <v>56.0884895324707</v>
       </c>
       <c r="H1228" t="n">
         <v>2058</v>
@@ -36039,7 +36039,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G1230" t="n">
-        <v>57.0248527526855</v>
+        <v>57.0248565673828</v>
       </c>
       <c r="H1230" t="n">
         <v>6303</v>
@@ -36068,7 +36068,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1231" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1231" t="n">
         <v>3054</v>
@@ -36097,7 +36097,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>57.8675880432129</v>
+        <v>57.8675842285156</v>
       </c>
       <c r="H1232" t="n">
         <v>2813</v>
@@ -36213,7 +36213,7 @@
         <v>64</v>
       </c>
       <c r="G1236" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1236" t="n">
         <v>3476</v>
@@ -36242,7 +36242,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G1237" t="n">
-        <v>61.8939743041992</v>
+        <v>61.893970489502</v>
       </c>
       <c r="H1237" t="n">
         <v>15476</v>
@@ -36271,7 +36271,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1238" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1238" t="n">
         <v>8167</v>
@@ -36329,7 +36329,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021507263184</v>
       </c>
       <c r="H1240" t="n">
         <v>1183</v>
@@ -36358,7 +36358,7 @@
         <v>63.5</v>
       </c>
       <c r="G1241" t="n">
-        <v>59.4594116210938</v>
+        <v>59.459415435791</v>
       </c>
       <c r="H1241" t="n">
         <v>1588</v>
@@ -36416,7 +36416,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1243" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1243" t="n">
         <v>927</v>
@@ -36474,7 +36474,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1245" t="n">
         <v>4530</v>
@@ -36532,7 +36532,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>55.9948501586914</v>
+        <v>55.9948463439941</v>
       </c>
       <c r="H1247" t="n">
         <v>5448</v>
@@ -36590,7 +36590,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>56.3693923950195</v>
+        <v>56.3693962097168</v>
       </c>
       <c r="H1249" t="n">
         <v>5915</v>
@@ -36735,7 +36735,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1254" t="n">
-        <v>56.5566711425781</v>
+        <v>56.5566673278809</v>
       </c>
       <c r="H1254" t="n">
         <v>2202</v>
@@ -36764,7 +36764,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>57.3057708740234</v>
+        <v>57.3057632446289</v>
       </c>
       <c r="H1255" t="n">
         <v>1840</v>
@@ -36793,7 +36793,7 @@
         <v>61</v>
       </c>
       <c r="G1256" t="n">
-        <v>57.1184921264648</v>
+        <v>57.1184883117676</v>
       </c>
       <c r="H1256" t="n">
         <v>4305</v>
@@ -36851,7 +36851,7 @@
         <v>61</v>
       </c>
       <c r="G1258" t="n">
-        <v>57.1184921264648</v>
+        <v>57.1184883117676</v>
       </c>
       <c r="H1258" t="n">
         <v>2266</v>
@@ -36909,7 +36909,7 @@
         <v>60</v>
       </c>
       <c r="G1260" t="n">
-        <v>56.1821174621582</v>
+        <v>56.1821250915527</v>
       </c>
       <c r="H1260" t="n">
         <v>873</v>
@@ -37054,7 +37054,7 @@
         <v>67</v>
       </c>
       <c r="G1265" t="n">
-        <v>62.736701965332</v>
+        <v>62.7367095947266</v>
       </c>
       <c r="H1265" t="n">
         <v>20893</v>
@@ -37083,7 +37083,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1266" t="n">
-        <v>61.6130638122559</v>
+        <v>61.6130676269531</v>
       </c>
       <c r="H1266" t="n">
         <v>8319</v>
@@ -37112,7 +37112,7 @@
         <v>65</v>
       </c>
       <c r="G1267" t="n">
-        <v>60.8639602661133</v>
+        <v>60.8639640808105</v>
       </c>
       <c r="H1267" t="n">
         <v>2808</v>
@@ -37228,7 +37228,7 @@
         <v>65</v>
       </c>
       <c r="G1271" t="n">
-        <v>60.8639602661133</v>
+        <v>60.8639640808105</v>
       </c>
       <c r="H1271" t="n">
         <v>2931</v>
@@ -37257,7 +37257,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1272" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021507263184</v>
       </c>
       <c r="H1272" t="n">
         <v>836</v>
@@ -37286,7 +37286,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>59.7403182983398</v>
+        <v>59.7403221130371</v>
       </c>
       <c r="H1273" t="n">
         <v>3377</v>
@@ -37315,7 +37315,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1274" t="n">
-        <v>60.1148681640625</v>
+        <v>60.1148643493652</v>
       </c>
       <c r="H1274" t="n">
         <v>3377</v>
@@ -37344,7 +37344,7 @@
         <v>65</v>
       </c>
       <c r="G1275" t="n">
-        <v>60.8639602661133</v>
+        <v>60.8639640808105</v>
       </c>
       <c r="H1275" t="n">
         <v>2458</v>
@@ -37431,7 +37431,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1278" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1278" t="n">
         <v>7535</v>
@@ -37547,7 +37547,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G1282" t="n">
-        <v>64.3285293579102</v>
+        <v>64.3285217285156</v>
       </c>
       <c r="H1282" t="n">
         <v>2456</v>
@@ -37576,7 +37576,7 @@
         <v>68</v>
       </c>
       <c r="G1283" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1283" t="n">
         <v>3127</v>
@@ -37605,7 +37605,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1284" t="n">
-        <v>64.7967071533203</v>
+        <v>64.7967224121094</v>
       </c>
       <c r="H1284" t="n">
         <v>54452</v>
@@ -37634,7 +37634,7 @@
         <v>67</v>
       </c>
       <c r="G1285" t="n">
-        <v>62.736701965332</v>
+        <v>62.7367095947266</v>
       </c>
       <c r="H1285" t="n">
         <v>3334</v>
@@ -37663,7 +37663,7 @@
         <v>68</v>
       </c>
       <c r="G1286" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1286" t="n">
         <v>4639</v>
@@ -37721,7 +37721,7 @@
         <v>69</v>
       </c>
       <c r="G1288" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1288" t="n">
         <v>4841</v>
@@ -37837,7 +37837,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>63.7667121887207</v>
+        <v>63.7667083740234</v>
       </c>
       <c r="H1292" t="n">
         <v>2952</v>
@@ -37866,7 +37866,7 @@
         <v>67.5999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>63.2985229492188</v>
+        <v>63.2985191345215</v>
       </c>
       <c r="H1293" t="n">
         <v>6297</v>
@@ -37895,7 +37895,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1294" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1294" t="n">
         <v>1691</v>
@@ -37924,7 +37924,7 @@
         <v>67</v>
       </c>
       <c r="G1295" t="n">
-        <v>62.736701965332</v>
+        <v>62.7367095947266</v>
       </c>
       <c r="H1295" t="n">
         <v>3848</v>
@@ -38011,7 +38011,7 @@
         <v>69</v>
       </c>
       <c r="G1298" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1298" t="n">
         <v>3290</v>
@@ -38040,7 +38040,7 @@
         <v>69</v>
       </c>
       <c r="G1299" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1299" t="n">
         <v>4702</v>
@@ -38156,7 +38156,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1303" t="n">
-        <v>63.5794334411621</v>
+        <v>63.5794372558594</v>
       </c>
       <c r="H1303" t="n">
         <v>7397</v>
@@ -38185,7 +38185,7 @@
         <v>70</v>
       </c>
       <c r="G1304" t="n">
-        <v>65.5458145141602</v>
+        <v>65.5458068847656</v>
       </c>
       <c r="H1304" t="n">
         <v>9973</v>
@@ -38214,7 +38214,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G1305" t="n">
-        <v>64.8903579711914</v>
+        <v>64.8903503417969</v>
       </c>
       <c r="H1305" t="n">
         <v>9202</v>
@@ -38243,7 +38243,7 @@
         <v>71</v>
       </c>
       <c r="G1306" t="n">
-        <v>66.4821701049805</v>
+        <v>66.482177734375</v>
       </c>
       <c r="H1306" t="n">
         <v>11441</v>
@@ -38272,7 +38272,7 @@
         <v>71</v>
       </c>
       <c r="G1307" t="n">
-        <v>66.4821701049805</v>
+        <v>66.482177734375</v>
       </c>
       <c r="H1307" t="n">
         <v>11320</v>
@@ -38330,7 +38330,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1309" t="n">
-        <v>65.3585433959961</v>
+        <v>65.3585357666016</v>
       </c>
       <c r="H1309" t="n">
         <v>5793</v>
@@ -38359,7 +38359,7 @@
         <v>71.0999984741211</v>
       </c>
       <c r="G1310" t="n">
-        <v>66.575813293457</v>
+        <v>66.5758056640625</v>
       </c>
       <c r="H1310" t="n">
         <v>23508</v>
@@ -38388,7 +38388,7 @@
         <v>70.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>66.0139923095703</v>
+        <v>66.0139846801758</v>
       </c>
       <c r="H1311" t="n">
         <v>9821</v>
@@ -38417,7 +38417,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1312" t="n">
-        <v>66.2949142456055</v>
+        <v>66.2949066162109</v>
       </c>
       <c r="H1312" t="n">
         <v>3551</v>
@@ -38446,7 +38446,7 @@
         <v>70</v>
       </c>
       <c r="G1313" t="n">
-        <v>65.5458145141602</v>
+        <v>65.5458068847656</v>
       </c>
       <c r="H1313" t="n">
         <v>6557</v>
@@ -38475,7 +38475,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G1314" t="n">
-        <v>66.8567276000977</v>
+        <v>66.8567199707031</v>
       </c>
       <c r="H1314" t="n">
         <v>11466</v>
@@ -38533,7 +38533,7 @@
         <v>68</v>
       </c>
       <c r="G1316" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1316" t="n">
         <v>16446</v>
@@ -38591,7 +38591,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1318" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1318" t="n">
         <v>6967</v>
@@ -38620,7 +38620,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1319" t="n">
-        <v>59.7403182983398</v>
+        <v>59.7403221130371</v>
       </c>
       <c r="H1319" t="n">
         <v>9758</v>
@@ -38649,7 +38649,7 @@
         <v>65</v>
       </c>
       <c r="G1320" t="n">
-        <v>60.8639602661133</v>
+        <v>60.8639640808105</v>
       </c>
       <c r="H1320" t="n">
         <v>7998</v>
@@ -38678,7 +38678,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G1321" t="n">
-        <v>60.2085113525391</v>
+        <v>60.2085075378418</v>
       </c>
       <c r="H1321" t="n">
         <v>1816</v>
@@ -38707,7 +38707,7 @@
         <v>64</v>
       </c>
       <c r="G1322" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1322" t="n">
         <v>13481</v>
@@ -38736,7 +38736,7 @@
         <v>65</v>
       </c>
       <c r="G1323" t="n">
-        <v>60.8639602661133</v>
+        <v>60.8639640808105</v>
       </c>
       <c r="H1323" t="n">
         <v>6789</v>
@@ -38968,7 +38968,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1331" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021507263184</v>
       </c>
       <c r="H1331" t="n">
         <v>1785</v>
@@ -38997,7 +38997,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1332" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1332" t="n">
         <v>3100</v>
@@ -39055,7 +39055,7 @@
         <v>65</v>
       </c>
       <c r="G1334" t="n">
-        <v>60.8639602661133</v>
+        <v>60.8639640808105</v>
       </c>
       <c r="H1334" t="n">
         <v>5303</v>
@@ -39113,7 +39113,7 @@
         <v>64</v>
       </c>
       <c r="G1336" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1336" t="n">
         <v>3411</v>
@@ -39142,7 +39142,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1337" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1337" t="n">
         <v>889</v>
@@ -39200,7 +39200,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1339" t="n">
-        <v>60.1148681640625</v>
+        <v>60.1148643493652</v>
       </c>
       <c r="H1339" t="n">
         <v>1136</v>
@@ -39229,7 +39229,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1340" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1340" t="n">
         <v>2138</v>
@@ -39258,7 +39258,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1341" t="n">
-        <v>61.9875984191895</v>
+        <v>61.9876098632812</v>
       </c>
       <c r="H1341" t="n">
         <v>1813</v>
@@ -39287,7 +39287,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1342" t="n">
-        <v>61.9875984191895</v>
+        <v>61.9876098632812</v>
       </c>
       <c r="H1342" t="n">
         <v>1533</v>
@@ -39316,7 +39316,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1343" t="n">
-        <v>61.9875984191895</v>
+        <v>61.9876098632812</v>
       </c>
       <c r="H1343" t="n">
         <v>2190</v>
@@ -39345,7 +39345,7 @@
         <v>68</v>
       </c>
       <c r="G1344" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1344" t="n">
         <v>1117</v>
@@ -39374,7 +39374,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1345" t="n">
-        <v>63.4858093261719</v>
+        <v>63.4857978820801</v>
       </c>
       <c r="H1345" t="n">
         <v>2489</v>
@@ -39432,7 +39432,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G1347" t="n">
-        <v>63.0176200866699</v>
+        <v>63.0176162719727</v>
       </c>
       <c r="H1347" t="n">
         <v>1993</v>
@@ -39461,7 +39461,7 @@
         <v>66.9000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>62.6430625915527</v>
+        <v>62.6430702209473</v>
       </c>
       <c r="H1348" t="n">
         <v>1938</v>
@@ -39519,7 +39519,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1350" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1350" t="n">
         <v>899</v>
@@ -39606,7 +39606,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1353" t="n">
-        <v>63.5794334411621</v>
+        <v>63.5794372558594</v>
       </c>
       <c r="H1353" t="n">
         <v>2513</v>
@@ -39635,7 +39635,7 @@
         <v>67</v>
       </c>
       <c r="G1354" t="n">
-        <v>62.736701965332</v>
+        <v>62.7367095947266</v>
       </c>
       <c r="H1354" t="n">
         <v>1811</v>
@@ -39664,7 +39664,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1355" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1355" t="n">
         <v>1776</v>
@@ -39809,7 +39809,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1360" t="n">
-        <v>60.5830574035645</v>
+        <v>60.5830497741699</v>
       </c>
       <c r="H1360" t="n">
         <v>366</v>
@@ -39838,7 +39838,7 @@
         <v>65</v>
       </c>
       <c r="G1361" t="n">
-        <v>60.8639602661133</v>
+        <v>60.8639640808105</v>
       </c>
       <c r="H1361" t="n">
         <v>2406</v>
@@ -39896,7 +39896,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021507263184</v>
       </c>
       <c r="H1363" t="n">
         <v>5150</v>
@@ -39925,7 +39925,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>59.2721366882324</v>
+        <v>59.2721405029297</v>
       </c>
       <c r="H1364" t="n">
         <v>5559</v>
@@ -39983,7 +39983,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1366" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1366" t="n">
         <v>9059</v>
@@ -40012,7 +40012,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>59.6466865539551</v>
+        <v>59.6466827392578</v>
       </c>
       <c r="H1367" t="n">
         <v>3869</v>
@@ -40186,7 +40186,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>58.2421379089355</v>
+        <v>58.2421340942383</v>
       </c>
       <c r="H1373" t="n">
         <v>4034</v>
@@ -40215,7 +40215,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1374" t="n">
-        <v>59.2721366882324</v>
+        <v>59.2721405029297</v>
       </c>
       <c r="H1374" t="n">
         <v>4750</v>
@@ -40273,7 +40273,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1376" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1376" t="n">
         <v>7123</v>
@@ -40302,7 +40302,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1377" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1377" t="n">
         <v>4730</v>
@@ -40389,7 +40389,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1380" t="n">
-        <v>58.7103157043457</v>
+        <v>58.710319519043</v>
       </c>
       <c r="H1380" t="n">
         <v>796</v>
@@ -40505,7 +40505,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1384" t="n">
-        <v>58.7103157043457</v>
+        <v>58.710319519043</v>
       </c>
       <c r="H1384" t="n">
         <v>1033</v>
@@ -40563,7 +40563,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1386" t="n">
         <v>617</v>
@@ -40621,7 +40621,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G1388" t="n">
-        <v>58.335765838623</v>
+        <v>58.3357696533203</v>
       </c>
       <c r="H1388" t="n">
         <v>1486</v>
@@ -40650,7 +40650,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1389" t="n">
         <v>649</v>
@@ -40679,7 +40679,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1390" t="n">
-        <v>58.7103157043457</v>
+        <v>58.710319519043</v>
       </c>
       <c r="H1390" t="n">
         <v>5705</v>
@@ -40708,7 +40708,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1391" t="n">
-        <v>60.1148681640625</v>
+        <v>60.1148643493652</v>
       </c>
       <c r="H1391" t="n">
         <v>3887</v>
@@ -40737,7 +40737,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G1392" t="n">
-        <v>59.8339614868164</v>
+        <v>59.8339576721191</v>
       </c>
       <c r="H1392" t="n">
         <v>1331</v>
@@ -40766,7 +40766,7 @@
         <v>64</v>
       </c>
       <c r="G1393" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1393" t="n">
         <v>402</v>
@@ -40795,7 +40795,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1394" t="n">
         <v>6905</v>
@@ -40882,7 +40882,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>58.335765838623</v>
+        <v>58.3357696533203</v>
       </c>
       <c r="H1397" t="n">
         <v>1555</v>
@@ -40940,7 +40940,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>58.8039512634277</v>
+        <v>58.8039474487305</v>
       </c>
       <c r="H1399" t="n">
         <v>963</v>
@@ -41027,7 +41027,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>57.3057708740234</v>
+        <v>57.3057632446289</v>
       </c>
       <c r="H1402" t="n">
         <v>5152</v>
@@ -41114,7 +41114,7 @@
         <v>61</v>
       </c>
       <c r="G1405" t="n">
-        <v>57.1184921264648</v>
+        <v>57.1184883117676</v>
       </c>
       <c r="H1405" t="n">
         <v>5988</v>
@@ -41172,7 +41172,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1407" t="n">
-        <v>55.9948501586914</v>
+        <v>55.9948463439941</v>
       </c>
       <c r="H1407" t="n">
         <v>4172</v>
@@ -41201,7 +41201,7 @@
         <v>60</v>
       </c>
       <c r="G1408" t="n">
-        <v>56.1821174621582</v>
+        <v>56.1821250915527</v>
       </c>
       <c r="H1408" t="n">
         <v>4832</v>
@@ -41259,7 +41259,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G1410" t="n">
-        <v>55.0584754943848</v>
+        <v>55.058479309082</v>
       </c>
       <c r="H1410" t="n">
         <v>7309</v>
@@ -41317,7 +41317,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G1412" t="n">
-        <v>55.5266647338867</v>
+        <v>55.5266609191895</v>
       </c>
       <c r="H1412" t="n">
         <v>4335</v>
@@ -41404,7 +41404,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1415" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1415" t="n">
         <v>1544</v>
@@ -41433,7 +41433,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>56.0884857177734</v>
+        <v>56.0884895324707</v>
       </c>
       <c r="H1416" t="n">
         <v>13800</v>
@@ -41520,7 +41520,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1419" t="n">
-        <v>58.2421379089355</v>
+        <v>58.2421340942383</v>
       </c>
       <c r="H1419" t="n">
         <v>10103</v>
@@ -41607,7 +41607,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>56.3693923950195</v>
+        <v>56.3693962097168</v>
       </c>
       <c r="H1422" t="n">
         <v>3120</v>
@@ -41636,7 +41636,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1423" t="n">
-        <v>56.0884857177734</v>
+        <v>56.0884895324707</v>
       </c>
       <c r="H1423" t="n">
         <v>9382</v>
@@ -41810,7 +41810,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1429" t="n">
-        <v>56.5566711425781</v>
+        <v>56.5566673278809</v>
       </c>
       <c r="H1429" t="n">
         <v>3742</v>
@@ -41839,7 +41839,7 @@
         <v>60</v>
       </c>
       <c r="G1430" t="n">
-        <v>56.1821174621582</v>
+        <v>56.1821250915527</v>
       </c>
       <c r="H1430" t="n">
         <v>27633</v>
@@ -41868,7 +41868,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1431" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1431" t="n">
         <v>5393</v>
@@ -42042,7 +42042,7 @@
         <v>57.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>53.8412017822266</v>
+        <v>53.8411979675293</v>
       </c>
       <c r="H1437" t="n">
         <v>9231</v>
@@ -42071,7 +42071,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1438" t="n">
-        <v>53.4666481018066</v>
+        <v>53.4666519165039</v>
       </c>
       <c r="H1438" t="n">
         <v>4813</v>
@@ -42245,7 +42245,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>53.0921020507812</v>
+        <v>53.0921058654785</v>
       </c>
       <c r="H1444" t="n">
         <v>6522</v>
@@ -42274,7 +42274,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>53.4666481018066</v>
+        <v>53.4666519165039</v>
       </c>
       <c r="H1445" t="n">
         <v>5885</v>
@@ -42332,7 +42332,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G1447" t="n">
-        <v>52.9984664916992</v>
+        <v>52.998462677002</v>
       </c>
       <c r="H1447" t="n">
         <v>4076</v>
@@ -42390,7 +42390,7 @@
         <v>56.0999984741211</v>
       </c>
       <c r="G1449" t="n">
-        <v>52.5302810668945</v>
+        <v>52.5302848815918</v>
       </c>
       <c r="H1449" t="n">
         <v>2059</v>
@@ -42564,7 +42564,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1455" t="n">
-        <v>51.4066467285156</v>
+        <v>51.4066429138184</v>
       </c>
       <c r="H1455" t="n">
         <v>3335</v>
@@ -42622,7 +42622,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1457" t="n">
-        <v>51.5939102172852</v>
+        <v>51.5939140319824</v>
       </c>
       <c r="H1457" t="n">
         <v>1898</v>
@@ -42651,7 +42651,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1458" t="n">
-        <v>51.4066467285156</v>
+        <v>51.4066429138184</v>
       </c>
       <c r="H1458" t="n">
         <v>4585</v>
@@ -42767,7 +42767,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G1462" t="n">
-        <v>49.814811706543</v>
+        <v>49.8148155212402</v>
       </c>
       <c r="H1462" t="n">
         <v>5486</v>
@@ -42825,7 +42825,7 @@
         <v>53</v>
       </c>
       <c r="G1464" t="n">
-        <v>49.6275405883789</v>
+        <v>49.6275367736816</v>
       </c>
       <c r="H1464" t="n">
         <v>6098</v>
@@ -42912,7 +42912,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G1467" t="n">
-        <v>50.1893577575684</v>
+        <v>50.1893615722656</v>
       </c>
       <c r="H1467" t="n">
         <v>3607</v>
@@ -42970,7 +42970,7 @@
         <v>50</v>
       </c>
       <c r="G1469" t="n">
-        <v>46.8184394836426</v>
+        <v>46.8184356689453</v>
       </c>
       <c r="H1469" t="n">
         <v>23042</v>
@@ -43028,7 +43028,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>47.192985534668</v>
+        <v>47.1929817199707</v>
       </c>
       <c r="H1471" t="n">
         <v>4172</v>
@@ -43260,7 +43260,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1479" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1479" t="n">
         <v>8380</v>
@@ -43405,7 +43405,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1484" t="n">
-        <v>54.5890159606934</v>
+        <v>54.5890121459961</v>
       </c>
       <c r="H1484" t="n">
         <v>7920</v>
@@ -43550,7 +43550,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1489" t="n">
-        <v>55.2547302246094</v>
+        <v>55.2547340393066</v>
       </c>
       <c r="H1489" t="n">
         <v>4867</v>
@@ -43579,7 +43579,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1490" t="n">
-        <v>55.8253517150879</v>
+        <v>55.8253479003906</v>
       </c>
       <c r="H1490" t="n">
         <v>5008</v>
@@ -43666,7 +43666,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>55.8253517150879</v>
+        <v>55.8253479003906</v>
       </c>
       <c r="H1493" t="n">
         <v>20583</v>
@@ -43840,7 +43840,7 @@
         <v>60</v>
       </c>
       <c r="G1499" t="n">
-        <v>57.0616798400879</v>
+        <v>57.0616836547852</v>
       </c>
       <c r="H1499" t="n">
         <v>10694</v>
@@ -43956,7 +43956,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>58.2029228210449</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1503" t="n">
         <v>3852</v>
@@ -44391,7 +44391,7 @@
         <v>60</v>
       </c>
       <c r="G1518" t="n">
-        <v>57.0616798400879</v>
+        <v>57.0616836547852</v>
       </c>
       <c r="H1518" t="n">
         <v>2950</v>
@@ -44449,7 +44449,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1520" t="n">
-        <v>55.8253517150879</v>
+        <v>55.8253479003906</v>
       </c>
       <c r="H1520" t="n">
         <v>1640</v>
@@ -44739,7 +44739,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1530" t="n">
-        <v>54.5890159606934</v>
+        <v>54.5890121459961</v>
       </c>
       <c r="H1530" t="n">
         <v>4324</v>
@@ -44768,7 +44768,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1531" t="n">
-        <v>55.2547302246094</v>
+        <v>55.2547340393066</v>
       </c>
       <c r="H1531" t="n">
         <v>2078</v>
@@ -44884,7 +44884,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1535" t="n">
-        <v>55.2547302246094</v>
+        <v>55.2547340393066</v>
       </c>
       <c r="H1535" t="n">
         <v>2556</v>
@@ -44913,7 +44913,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1536" t="n">
-        <v>55.2547302246094</v>
+        <v>55.2547340393066</v>
       </c>
       <c r="H1536" t="n">
         <v>2855</v>
@@ -45261,7 +45261,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1548" t="n">
-        <v>52.8771591186523</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1548" t="n">
         <v>1297</v>
@@ -45290,7 +45290,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1549" t="n">
-        <v>52.4016418457031</v>
+        <v>52.4016456604004</v>
       </c>
       <c r="H1549" t="n">
         <v>2099</v>
@@ -45406,7 +45406,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1553" t="n">
-        <v>52.4016418457031</v>
+        <v>52.4016456604004</v>
       </c>
       <c r="H1553" t="n">
         <v>2543</v>
@@ -45435,7 +45435,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1554" t="n">
-        <v>52.4016418457031</v>
+        <v>52.4016456604004</v>
       </c>
       <c r="H1554" t="n">
         <v>3661</v>
@@ -45464,7 +45464,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1555" t="n">
-        <v>52.8771591186523</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1555" t="n">
         <v>362</v>
@@ -45609,7 +45609,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1560" t="n">
-        <v>52.2114448547363</v>
+        <v>52.2114410400391</v>
       </c>
       <c r="H1560" t="n">
         <v>1277</v>
@@ -45638,7 +45638,7 @@
         <v>54.5</v>
       </c>
       <c r="G1561" t="n">
-        <v>51.8310279846191</v>
+        <v>51.8310317993164</v>
       </c>
       <c r="H1561" t="n">
         <v>8729</v>
@@ -45696,7 +45696,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1563" t="n">
-        <v>51.6408233642578</v>
+        <v>51.6408195495605</v>
       </c>
       <c r="H1563" t="n">
         <v>1591</v>
@@ -45725,7 +45725,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>51.6408233642578</v>
+        <v>51.6408195495605</v>
       </c>
       <c r="H1564" t="n">
         <v>849</v>
@@ -45783,7 +45783,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>51.6408233642578</v>
+        <v>51.6408195495605</v>
       </c>
       <c r="H1566" t="n">
         <v>9648</v>
@@ -45928,7 +45928,7 @@
         <v>53</v>
       </c>
       <c r="G1571" t="n">
-        <v>50.4044876098633</v>
+        <v>50.404483795166</v>
       </c>
       <c r="H1571" t="n">
         <v>1778</v>
@@ -46102,7 +46102,7 @@
         <v>50</v>
       </c>
       <c r="G1577" t="n">
-        <v>47.5514068603516</v>
+        <v>47.5514030456543</v>
       </c>
       <c r="H1577" t="n">
         <v>2915</v>
@@ -46218,7 +46218,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>45.2689361572266</v>
+        <v>45.2689323425293</v>
       </c>
       <c r="H1581" t="n">
         <v>9437</v>
@@ -46247,7 +46247,7 @@
         <v>46.6500015258789</v>
       </c>
       <c r="G1582" t="n">
-        <v>44.3654632568359</v>
+        <v>44.3654594421387</v>
       </c>
       <c r="H1582" t="n">
         <v>3910</v>
@@ -46305,7 +46305,7 @@
         <v>47.4500007629395</v>
       </c>
       <c r="G1584" t="n">
-        <v>45.1262817382812</v>
+        <v>45.1262855529785</v>
       </c>
       <c r="H1584" t="n">
         <v>11053</v>
@@ -46421,7 +46421,7 @@
         <v>48</v>
       </c>
       <c r="G1588" t="n">
-        <v>45.6493492126465</v>
+        <v>45.6493453979492</v>
       </c>
       <c r="H1588" t="n">
         <v>5840</v>
@@ -46508,7 +46508,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1591" t="n">
-        <v>48.7877426147461</v>
+        <v>48.7877388000488</v>
       </c>
       <c r="H1591" t="n">
         <v>16510</v>
@@ -46537,7 +46537,7 @@
         <v>50</v>
       </c>
       <c r="G1592" t="n">
-        <v>47.5514068603516</v>
+        <v>47.5514030456543</v>
       </c>
       <c r="H1592" t="n">
         <v>12132</v>
@@ -46595,7 +46595,7 @@
         <v>49.25</v>
       </c>
       <c r="G1594" t="n">
-        <v>46.838134765625</v>
+        <v>46.8381309509277</v>
       </c>
       <c r="H1594" t="n">
         <v>3122</v>
@@ -46624,7 +46624,7 @@
         <v>49.1500015258789</v>
       </c>
       <c r="G1595" t="n">
-        <v>46.7430305480957</v>
+        <v>46.7430267333984</v>
       </c>
       <c r="H1595" t="n">
         <v>1381</v>
@@ -46798,7 +46798,7 @@
         <v>48.25</v>
       </c>
       <c r="G1601" t="n">
-        <v>45.8871040344238</v>
+        <v>45.8871078491211</v>
       </c>
       <c r="H1601" t="n">
         <v>13370</v>
@@ -46827,7 +46827,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G1602" t="n">
-        <v>46.933235168457</v>
+        <v>46.9332389831543</v>
       </c>
       <c r="H1602" t="n">
         <v>5561</v>
@@ -46856,7 +46856,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1603" t="n">
-        <v>48.7877426147461</v>
+        <v>48.7877388000488</v>
       </c>
       <c r="H1603" t="n">
         <v>4600</v>
@@ -47030,7 +47030,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G1609" t="n">
-        <v>47.4087448120117</v>
+        <v>47.408748626709</v>
       </c>
       <c r="H1609" t="n">
         <v>1214</v>
@@ -47088,7 +47088,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>48.1220169067383</v>
+        <v>48.1220207214355</v>
       </c>
       <c r="H1611" t="n">
         <v>1004</v>
@@ -47146,7 +47146,7 @@
         <v>52.5</v>
       </c>
       <c r="G1613" t="n">
-        <v>49.9289779663086</v>
+        <v>49.9289741516113</v>
       </c>
       <c r="H1613" t="n">
         <v>4226</v>
@@ -47175,7 +47175,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1614" t="n">
-        <v>49.8338737487793</v>
+        <v>49.833869934082</v>
       </c>
       <c r="H1614" t="n">
         <v>2347</v>
@@ -47494,7 +47494,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1625" t="n">
-        <v>48.1220169067383</v>
+        <v>48.1220207214355</v>
       </c>
       <c r="H1625" t="n">
         <v>2499</v>
@@ -47552,7 +47552,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1627" t="n">
-        <v>52.8771591186523</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1627" t="n">
         <v>11544</v>
@@ -47610,7 +47610,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1629" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1629" t="n">
         <v>6837</v>
@@ -47668,7 +47668,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1631" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1631" t="n">
         <v>1580</v>
@@ -47697,7 +47697,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1632" t="n">
-        <v>52.8771591186523</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1632" t="n">
         <v>4324</v>
@@ -47900,7 +47900,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1639" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1639" t="n">
         <v>1545</v>
@@ -47929,7 +47929,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1640" t="n">
-        <v>54.5890159606934</v>
+        <v>54.5890121459961</v>
       </c>
       <c r="H1640" t="n">
         <v>4794</v>
@@ -47958,7 +47958,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1641" t="n">
-        <v>54.0183944702148</v>
+        <v>54.0183906555176</v>
       </c>
       <c r="H1641" t="n">
         <v>5651</v>
@@ -48016,7 +48016,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1643" t="n">
-        <v>54.0183944702148</v>
+        <v>54.0183906555176</v>
       </c>
       <c r="H1643" t="n">
         <v>2019</v>
@@ -48161,7 +48161,7 @@
         <v>57</v>
       </c>
       <c r="G1648" t="n">
-        <v>54.2085990905762</v>
+        <v>54.2086029052734</v>
       </c>
       <c r="H1648" t="n">
         <v>5732</v>
@@ -48190,7 +48190,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1649" t="n">
-        <v>54.0183944702148</v>
+        <v>54.0183906555176</v>
       </c>
       <c r="H1649" t="n">
         <v>5414</v>
@@ -48654,7 +48654,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>58.2029228210449</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1665" t="n">
         <v>6024</v>
@@ -48741,7 +48741,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1668" t="n">
-        <v>58.2029228210449</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1668" t="n">
         <v>4693</v>
@@ -48770,7 +48770,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1669" t="n">
-        <v>58.2029228210449</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1669" t="n">
         <v>3555</v>
@@ -48799,7 +48799,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1670" t="n">
-        <v>58.2029228210449</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1670" t="n">
         <v>4025</v>
@@ -49002,7 +49002,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1677" t="n">
-        <v>58.2029228210449</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1677" t="n">
         <v>2547</v>
@@ -49031,7 +49031,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1678" t="n">
-        <v>58.2029228210449</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1678" t="n">
         <v>4489</v>
@@ -49060,7 +49060,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1679" t="n">
-        <v>58.2029228210449</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1679" t="n">
         <v>3557</v>
@@ -49350,7 +49350,7 @@
         <v>60</v>
       </c>
       <c r="G1689" t="n">
-        <v>57.0616798400879</v>
+        <v>57.0616836547852</v>
       </c>
       <c r="H1689" t="n">
         <v>4473</v>
@@ -49379,7 +49379,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1690" t="n">
-        <v>56.8714790344238</v>
+        <v>56.8714752197266</v>
       </c>
       <c r="H1690" t="n">
         <v>1679</v>
@@ -49408,7 +49408,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1691" t="n">
-        <v>56.8714790344238</v>
+        <v>56.8714752197266</v>
       </c>
       <c r="H1691" t="n">
         <v>3409</v>
@@ -49437,7 +49437,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1692" t="n">
-        <v>56.8714790344238</v>
+        <v>56.8714752197266</v>
       </c>
       <c r="H1692" t="n">
         <v>2453</v>
@@ -49524,7 +49524,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G1695" t="n">
-        <v>56.3959655761719</v>
+        <v>56.3959617614746</v>
       </c>
       <c r="H1695" t="n">
         <v>2243</v>
@@ -49611,7 +49611,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1698" t="n">
-        <v>54.5890159606934</v>
+        <v>54.5890121459961</v>
       </c>
       <c r="H1698" t="n">
         <v>7893</v>
@@ -49640,7 +49640,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1699" t="n">
-        <v>54.5890159606934</v>
+        <v>54.5890121459961</v>
       </c>
       <c r="H1699" t="n">
         <v>7702</v>
@@ -49698,7 +49698,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1701" t="n">
-        <v>55.2547302246094</v>
+        <v>55.2547340393066</v>
       </c>
       <c r="H1701" t="n">
         <v>5255</v>
@@ -49785,7 +49785,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1704" t="n">
-        <v>54.5890159606934</v>
+        <v>54.5890121459961</v>
       </c>
       <c r="H1704" t="n">
         <v>6158</v>
@@ -49814,7 +49814,7 @@
         <v>57</v>
       </c>
       <c r="G1705" t="n">
-        <v>54.2085990905762</v>
+        <v>54.2086029052734</v>
       </c>
       <c r="H1705" t="n">
         <v>6565</v>
@@ -49872,7 +49872,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1707" t="n">
-        <v>54.0183944702148</v>
+        <v>54.0183906555176</v>
       </c>
       <c r="H1707" t="n">
         <v>5729</v>
@@ -49930,7 +49930,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1709" t="n">
-        <v>52.4016418457031</v>
+        <v>52.4016456604004</v>
       </c>
       <c r="H1709" t="n">
         <v>3401</v>
@@ -49959,7 +49959,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1710" t="n">
-        <v>52.4016418457031</v>
+        <v>52.4016456604004</v>
       </c>
       <c r="H1710" t="n">
         <v>1428</v>
@@ -50191,7 +50191,7 @@
         <v>53</v>
       </c>
       <c r="G1718" t="n">
-        <v>50.4044876098633</v>
+        <v>50.404483795166</v>
       </c>
       <c r="H1718" t="n">
         <v>3597</v>
@@ -50307,7 +50307,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1722" t="n">
-        <v>50.4995880126953</v>
+        <v>50.4995918273926</v>
       </c>
       <c r="H1722" t="n">
         <v>3955</v>
@@ -50481,7 +50481,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1728" t="n">
-        <v>49.5485610961914</v>
+        <v>49.5485649108887</v>
       </c>
       <c r="H1728" t="n">
         <v>7217</v>
@@ -50655,7 +50655,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G1734" t="n">
-        <v>49.0168228149414</v>
+        <v>49.0168266296387</v>
       </c>
       <c r="H1734" t="n">
         <v>4123</v>
@@ -50742,7 +50742,7 @@
         <v>48.25</v>
       </c>
       <c r="G1737" t="n">
-        <v>46.6481590270996</v>
+        <v>46.6481628417969</v>
       </c>
       <c r="H1737" t="n">
         <v>12798</v>
@@ -50771,7 +50771,7 @@
         <v>48</v>
       </c>
       <c r="G1738" t="n">
-        <v>46.4064598083496</v>
+        <v>46.4064559936523</v>
       </c>
       <c r="H1738" t="n">
         <v>8909</v>
@@ -50800,7 +50800,7 @@
         <v>48.25</v>
       </c>
       <c r="G1739" t="n">
-        <v>46.6481590270996</v>
+        <v>46.6481628417969</v>
       </c>
       <c r="H1739" t="n">
         <v>7440</v>
@@ -50829,7 +50829,7 @@
         <v>48.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>46.6481590270996</v>
+        <v>46.6481628417969</v>
       </c>
       <c r="H1740" t="n">
         <v>4589</v>
@@ -50974,7 +50974,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>47.4699401855469</v>
+        <v>47.4699363708496</v>
       </c>
       <c r="H1745" t="n">
         <v>5196</v>
@@ -51032,7 +51032,7 @@
         <v>48.4500007629395</v>
       </c>
       <c r="G1747" t="n">
-        <v>46.8415184020996</v>
+        <v>46.8415222167969</v>
       </c>
       <c r="H1747" t="n">
         <v>6424</v>
@@ -51061,7 +51061,7 @@
         <v>49.25</v>
       </c>
       <c r="G1748" t="n">
-        <v>47.6149635314941</v>
+        <v>47.6149597167969</v>
       </c>
       <c r="H1748" t="n">
         <v>13987</v>
@@ -51177,7 +51177,7 @@
         <v>48</v>
       </c>
       <c r="G1752" t="n">
-        <v>46.4064598083496</v>
+        <v>46.4064559936523</v>
       </c>
       <c r="H1752" t="n">
         <v>7366</v>
@@ -51351,7 +51351,7 @@
         <v>46.0499992370605</v>
       </c>
       <c r="G1758" t="n">
-        <v>44.5211944580078</v>
+        <v>44.5211982727051</v>
       </c>
       <c r="H1758" t="n">
         <v>22829</v>
@@ -51467,7 +51467,7 @@
         <v>47.4500007629395</v>
       </c>
       <c r="G1762" t="n">
-        <v>45.8747177124023</v>
+        <v>45.8747215270996</v>
       </c>
       <c r="H1762" t="n">
         <v>16906</v>
@@ -51525,7 +51525,7 @@
         <v>47.5</v>
       </c>
       <c r="G1764" t="n">
-        <v>45.9230613708496</v>
+        <v>45.9230575561523</v>
       </c>
       <c r="H1764" t="n">
         <v>3409</v>
@@ -51844,7 +51844,7 @@
         <v>48</v>
       </c>
       <c r="G1775" t="n">
-        <v>46.4064598083496</v>
+        <v>46.4064559936523</v>
       </c>
       <c r="H1775" t="n">
         <v>2868</v>
@@ -51931,7 +51931,7 @@
         <v>48.25</v>
       </c>
       <c r="G1778" t="n">
-        <v>46.6481590270996</v>
+        <v>46.6481628417969</v>
       </c>
       <c r="H1778" t="n">
         <v>2304</v>
@@ -52018,7 +52018,7 @@
         <v>48.2000007629395</v>
       </c>
       <c r="G1781" t="n">
-        <v>46.5998191833496</v>
+        <v>46.5998229980469</v>
       </c>
       <c r="H1781" t="n">
         <v>2415</v>
@@ -52134,7 +52134,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G1785" t="n">
-        <v>45.5846786499023</v>
+        <v>45.5846824645996</v>
       </c>
       <c r="H1785" t="n">
         <v>2631</v>
@@ -52163,7 +52163,7 @@
         <v>47.75</v>
       </c>
       <c r="G1786" t="n">
-        <v>46.1647605895996</v>
+        <v>46.1647567749023</v>
       </c>
       <c r="H1786" t="n">
         <v>1985</v>
@@ -52279,7 +52279,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G1790" t="n">
-        <v>46.2614402770996</v>
+        <v>46.2614364624023</v>
       </c>
       <c r="H1790" t="n">
         <v>1116</v>
@@ -52453,7 +52453,7 @@
         <v>47.4500007629395</v>
       </c>
       <c r="G1796" t="n">
-        <v>45.8747177124023</v>
+        <v>45.8747215270996</v>
       </c>
       <c r="H1796" t="n">
         <v>1134</v>
@@ -52656,7 +52656,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G1803" t="n">
-        <v>47.7116394042969</v>
+        <v>47.7116432189941</v>
       </c>
       <c r="H1803" t="n">
         <v>1192</v>
@@ -52859,7 +52859,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1810" t="n">
-        <v>49.5969047546387</v>
+        <v>49.5969009399414</v>
       </c>
       <c r="H1810" t="n">
         <v>4232</v>
@@ -53381,7 +53381,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1828" t="n">
-        <v>55.4943962097168</v>
+        <v>55.4943923950195</v>
       </c>
       <c r="H1828" t="n">
         <v>1941</v>
@@ -53410,7 +53410,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1829" t="n">
-        <v>56.1711502075195</v>
+        <v>56.1711540222168</v>
       </c>
       <c r="H1829" t="n">
         <v>2077</v>
@@ -53555,7 +53555,7 @@
         <v>57</v>
       </c>
       <c r="G1834" t="n">
-        <v>55.1076698303223</v>
+        <v>55.1076736450195</v>
       </c>
       <c r="H1834" t="n">
         <v>4201</v>
@@ -53613,7 +53613,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1836" t="n">
-        <v>53.2707443237305</v>
+        <v>53.2707481384277</v>
       </c>
       <c r="H1836" t="n">
         <v>3803</v>
@@ -53642,7 +53642,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1837" t="n">
-        <v>53.077392578125</v>
+        <v>53.0773887634277</v>
       </c>
       <c r="H1837" t="n">
         <v>5249</v>
@@ -53729,7 +53729,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1840" t="n">
-        <v>53.560791015625</v>
+        <v>53.5607872009277</v>
       </c>
       <c r="H1840" t="n">
         <v>11120</v>
@@ -53816,7 +53816,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1843" t="n">
-        <v>55.4943962097168</v>
+        <v>55.4943923950195</v>
       </c>
       <c r="H1843" t="n">
         <v>3819</v>
@@ -53903,7 +53903,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1846" t="n">
-        <v>56.1711502075195</v>
+        <v>56.1711540222168</v>
       </c>
       <c r="H1846" t="n">
         <v>6678</v>
@@ -54048,7 +54048,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1851" t="n">
-        <v>53.7541465759277</v>
+        <v>53.754150390625</v>
       </c>
       <c r="H1851" t="n">
         <v>1761</v>
@@ -54106,7 +54106,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1853" t="n">
-        <v>55.4943962097168</v>
+        <v>55.4943923950195</v>
       </c>
       <c r="H1853" t="n">
         <v>1538</v>
@@ -54135,7 +54135,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1854" t="n">
-        <v>54.9143104553223</v>
+        <v>54.914306640625</v>
       </c>
       <c r="H1854" t="n">
         <v>2669</v>
@@ -54164,7 +54164,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1855" t="n">
-        <v>53.7541465759277</v>
+        <v>53.754150390625</v>
       </c>
       <c r="H1855" t="n">
         <v>2839</v>
@@ -54280,7 +54280,7 @@
         <v>53</v>
       </c>
       <c r="G1859" t="n">
-        <v>51.2404670715332</v>
+        <v>51.2404632568359</v>
       </c>
       <c r="H1859" t="n">
         <v>17183</v>
@@ -54309,7 +54309,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1860" t="n">
-        <v>50.8537406921387</v>
+        <v>50.8537445068359</v>
       </c>
       <c r="H1860" t="n">
         <v>9585</v>
@@ -54454,7 +54454,7 @@
         <v>57</v>
       </c>
       <c r="G1865" t="n">
-        <v>55.1076698303223</v>
+        <v>55.1076736450195</v>
       </c>
       <c r="H1865" t="n">
         <v>5904</v>
@@ -54686,7 +54686,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1873" t="n">
-        <v>53.077392578125</v>
+        <v>53.0773887634277</v>
       </c>
       <c r="H1873" t="n">
         <v>3146</v>
@@ -54744,7 +54744,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1875" t="n">
-        <v>53.560791015625</v>
+        <v>53.5607872009277</v>
       </c>
       <c r="H1875" t="n">
         <v>1086</v>
@@ -54889,7 +54889,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1880" t="n">
-        <v>53.077392578125</v>
+        <v>53.0773887634277</v>
       </c>
       <c r="H1880" t="n">
         <v>2906</v>
@@ -54918,7 +54918,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1881" t="n">
-        <v>53.2707443237305</v>
+        <v>53.2707481384277</v>
       </c>
       <c r="H1881" t="n">
         <v>1253</v>
@@ -55092,7 +55092,7 @@
         <v>54.5</v>
       </c>
       <c r="G1887" t="n">
-        <v>52.6906661987305</v>
+        <v>52.6906700134277</v>
       </c>
       <c r="H1887" t="n">
         <v>28310</v>
@@ -55150,7 +55150,7 @@
         <v>54</v>
       </c>
       <c r="G1889" t="n">
-        <v>52.2072639465332</v>
+        <v>52.2072677612305</v>
       </c>
       <c r="H1889" t="n">
         <v>2997</v>
@@ -55266,7 +55266,7 @@
         <v>54</v>
       </c>
       <c r="G1893" t="n">
-        <v>52.2072639465332</v>
+        <v>52.2072677612305</v>
       </c>
       <c r="H1893" t="n">
         <v>870</v>
@@ -55440,7 +55440,7 @@
         <v>53</v>
       </c>
       <c r="G1899" t="n">
-        <v>51.2404670715332</v>
+        <v>51.2404632568359</v>
       </c>
       <c r="H1899" t="n">
         <v>4188</v>
@@ -55498,7 +55498,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1901" t="n">
-        <v>50.8537406921387</v>
+        <v>50.8537445068359</v>
       </c>
       <c r="H1901" t="n">
         <v>5689</v>
@@ -55614,7 +55614,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1905" t="n">
-        <v>50.6603889465332</v>
+        <v>50.6603851318359</v>
       </c>
       <c r="H1905" t="n">
         <v>2333</v>
@@ -55730,7 +55730,7 @@
         <v>52.5</v>
       </c>
       <c r="G1909" t="n">
-        <v>50.7570686340332</v>
+        <v>50.7570648193359</v>
       </c>
       <c r="H1909" t="n">
         <v>2398</v>
@@ -55759,7 +55759,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1910" t="n">
-        <v>50.6603889465332</v>
+        <v>50.6603851318359</v>
       </c>
       <c r="H1910" t="n">
         <v>2425</v>
@@ -55875,7 +55875,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G1914" t="n">
-        <v>49.0168228149414</v>
+        <v>49.0168266296387</v>
       </c>
       <c r="H1914" t="n">
         <v>8427</v>
@@ -55904,7 +55904,7 @@
         <v>50.5</v>
       </c>
       <c r="G1915" t="n">
-        <v>48.8234634399414</v>
+        <v>48.8234596252441</v>
       </c>
       <c r="H1915" t="n">
         <v>4977</v>
@@ -56020,7 +56020,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1919" t="n">
-        <v>50.6603889465332</v>
+        <v>50.6603851318359</v>
       </c>
       <c r="H1919" t="n">
         <v>3266</v>
@@ -56078,7 +56078,7 @@
         <v>52.5</v>
       </c>
       <c r="G1921" t="n">
-        <v>50.7570686340332</v>
+        <v>50.7570648193359</v>
       </c>
       <c r="H1921" t="n">
         <v>3895</v>
@@ -56339,7 +56339,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1930" t="n">
-        <v>52.4973068237305</v>
+        <v>52.4973030090332</v>
       </c>
       <c r="H1930" t="n">
         <v>7946</v>
@@ -56368,7 +56368,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1931" t="n">
-        <v>53.2707443237305</v>
+        <v>53.2707481384277</v>
       </c>
       <c r="H1931" t="n">
         <v>7341</v>
@@ -56774,7 +56774,7 @@
         <v>54</v>
       </c>
       <c r="G1945" t="n">
-        <v>52.2072639465332</v>
+        <v>52.2072677612305</v>
       </c>
       <c r="H1945" t="n">
         <v>14594</v>
@@ -56977,7 +56977,7 @@
         <v>49.25</v>
       </c>
       <c r="G1952" t="n">
-        <v>47.6149635314941</v>
+        <v>47.6149597167969</v>
       </c>
       <c r="H1952" t="n">
         <v>24970</v>
@@ -57064,7 +57064,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1955" t="n">
-        <v>47.2282409667969</v>
+        <v>47.2282371520996</v>
       </c>
       <c r="H1955" t="n">
         <v>7459</v>
@@ -57122,7 +57122,7 @@
         <v>49.25</v>
       </c>
       <c r="G1957" t="n">
-        <v>47.6149635314941</v>
+        <v>47.6149597167969</v>
       </c>
       <c r="H1957" t="n">
         <v>4605</v>
@@ -57267,7 +57267,7 @@
         <v>48.25</v>
       </c>
       <c r="G1962" t="n">
-        <v>46.6481590270996</v>
+        <v>46.6481628417969</v>
       </c>
       <c r="H1962" t="n">
         <v>12015</v>
@@ -57296,7 +57296,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G1963" t="n">
-        <v>45.5846786499023</v>
+        <v>45.5846824645996</v>
       </c>
       <c r="H1963" t="n">
         <v>10367</v>
@@ -57499,7 +57499,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1970" t="n">
-        <v>49.5969047546387</v>
+        <v>49.5969009399414</v>
       </c>
       <c r="H1970" t="n">
         <v>6798</v>
@@ -57557,7 +57557,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G1972" t="n">
-        <v>49.0168228149414</v>
+        <v>49.0168266296387</v>
       </c>
       <c r="H1972" t="n">
         <v>3589</v>
@@ -57586,7 +57586,7 @@
         <v>50.5</v>
       </c>
       <c r="G1973" t="n">
-        <v>48.8234634399414</v>
+        <v>48.8234596252441</v>
       </c>
       <c r="H1973" t="n">
         <v>2070</v>
@@ -57615,7 +57615,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1974" t="n">
-        <v>49.5969047546387</v>
+        <v>49.5969009399414</v>
       </c>
       <c r="H1974" t="n">
         <v>3776</v>
@@ -68525,6 +68525,64 @@
         <v>4668</v>
       </c>
       <c r="I2350" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2351" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2351" t="n">
+        <v>73.1999969482422</v>
+      </c>
+      <c r="D2351" t="n">
+        <v>73.1999969482422</v>
+      </c>
+      <c r="E2351" t="n">
+        <v>71.4000015258789</v>
+      </c>
+      <c r="F2351" t="n">
+        <v>71.6999969482422</v>
+      </c>
+      <c r="G2351" t="n">
+        <v>71.6999969482422</v>
+      </c>
+      <c r="H2351" t="n">
+        <v>6091</v>
+      </c>
+      <c r="I2351" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2352" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2352" t="n">
+        <v>71</v>
+      </c>
+      <c r="D2352" t="n">
+        <v>71.5999984741211</v>
+      </c>
+      <c r="E2352" t="n">
+        <v>70.4000015258789</v>
+      </c>
+      <c r="F2352" t="n">
+        <v>70.9000015258789</v>
+      </c>
+      <c r="G2352" t="n">
+        <v>70.9000015258789</v>
+      </c>
+      <c r="H2352" t="n">
+        <v>7392</v>
+      </c>
+      <c r="I2352" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -543,7 +543,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G6" t="n">
-        <v>10.8920764923096</v>
+        <v>10.8920774459839</v>
       </c>
       <c r="H6" t="n">
         <v>7500</v>
@@ -572,7 +572,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H7" t="n">
         <v>5100</v>
@@ -601,7 +601,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>10.9005336761475</v>
+        <v>10.9005355834961</v>
       </c>
       <c r="H8" t="n">
         <v>13200</v>
@@ -659,7 +659,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1711435317993</v>
+        <v>11.1711454391479</v>
       </c>
       <c r="H10" t="n">
         <v>5500</v>
@@ -688,7 +688,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>11.2726221084595</v>
+        <v>11.2726240158081</v>
       </c>
       <c r="H11" t="n">
         <v>2400</v>
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H13" t="n">
         <v>7400</v>
@@ -862,7 +862,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G17" t="n">
-        <v>11.2726221084595</v>
+        <v>11.2726240158081</v>
       </c>
       <c r="H17" t="n">
         <v>2700</v>
@@ -920,7 +920,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>11.0358400344849</v>
+        <v>11.0358381271362</v>
       </c>
       <c r="H19" t="n">
         <v>1100</v>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H20" t="n">
         <v>2800</v>
@@ -978,7 +978,7 @@
         <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H21" t="n">
         <v>6300</v>
@@ -1007,7 +1007,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>11.2895364761353</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H22" t="n">
         <v>6300</v>
@@ -1065,7 +1065,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>10.9174480438232</v>
+        <v>10.9174470901489</v>
       </c>
       <c r="H24" t="n">
         <v>4500</v>
@@ -1210,7 +1210,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>10.9850997924805</v>
+        <v>10.9850988388062</v>
       </c>
       <c r="H29" t="n">
         <v>3800</v>
@@ -1268,7 +1268,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>10.7398586273193</v>
+        <v>10.7398595809937</v>
       </c>
       <c r="H31" t="n">
         <v>4100</v>
@@ -1297,7 +1297,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G32" t="n">
-        <v>10.8159666061401</v>
+        <v>10.8159675598145</v>
       </c>
       <c r="H32" t="n">
         <v>200</v>
@@ -1326,7 +1326,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7398586273193</v>
+        <v>10.7398595809937</v>
       </c>
       <c r="H33" t="n">
         <v>4700</v>
@@ -1384,7 +1384,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G35" t="n">
-        <v>10.6468372344971</v>
+        <v>10.6468353271484</v>
       </c>
       <c r="H35" t="n">
         <v>10800</v>
@@ -1413,7 +1413,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0696649551392</v>
+        <v>11.0696659088135</v>
       </c>
       <c r="H36" t="n">
         <v>11400</v>
@@ -1442,7 +1442,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>10.9428148269653</v>
+        <v>10.942816734314</v>
       </c>
       <c r="H37" t="n">
         <v>2100</v>
@@ -1471,7 +1471,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G38" t="n">
-        <v>10.9343595504761</v>
+        <v>10.9343585968018</v>
       </c>
       <c r="H38" t="n">
         <v>1700</v>
@@ -1587,7 +1587,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G42" t="n">
-        <v>11.2387952804565</v>
+        <v>11.2387981414795</v>
       </c>
       <c r="H42" t="n">
         <v>13400</v>
@@ -1616,7 +1616,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.6700839996338</v>
+        <v>11.6700820922852</v>
       </c>
       <c r="H43" t="n">
         <v>18500</v>
@@ -1645,7 +1645,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G44" t="n">
-        <v>11.6700839996338</v>
+        <v>11.6700820922852</v>
       </c>
       <c r="H44" t="n">
         <v>27300</v>
@@ -1703,7 +1703,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.6447134017944</v>
+        <v>11.6447143554688</v>
       </c>
       <c r="H46" t="n">
         <v>24300</v>
@@ -1732,7 +1732,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6447134017944</v>
+        <v>11.6447143554688</v>
       </c>
       <c r="H47" t="n">
         <v>9700</v>
@@ -1761,7 +1761,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5009508132935</v>
+        <v>11.5009517669678</v>
       </c>
       <c r="H48" t="n">
         <v>5200</v>
@@ -1790,7 +1790,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>11.5009508132935</v>
+        <v>11.5009517669678</v>
       </c>
       <c r="H49" t="n">
         <v>1800</v>
@@ -1877,7 +1877,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.4586696624756</v>
+        <v>11.458667755127</v>
       </c>
       <c r="H52" t="n">
         <v>1500</v>
@@ -1906,7 +1906,7 @@
         <v>13.5</v>
       </c>
       <c r="G53" t="n">
-        <v>11.4163846969604</v>
+        <v>11.4163866043091</v>
       </c>
       <c r="H53" t="n">
         <v>1200</v>
@@ -1935,7 +1935,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>11.2895364761353</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H54" t="n">
         <v>1300</v>
@@ -1993,7 +1993,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>11.2810802459717</v>
+        <v>11.281081199646</v>
       </c>
       <c r="H56" t="n">
         <v>7600</v>
@@ -2022,7 +2022,7 @@
         <v>13.25</v>
       </c>
       <c r="G57" t="n">
-        <v>11.2049713134766</v>
+        <v>11.2049694061279</v>
       </c>
       <c r="H57" t="n">
         <v>2500</v>
@@ -2080,7 +2080,7 @@
         <v>13</v>
       </c>
       <c r="G59" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H59" t="n">
         <v>9700</v>
@@ -2196,7 +2196,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G63" t="n">
-        <v>11.052752494812</v>
+        <v>11.0527515411377</v>
       </c>
       <c r="H63" t="n">
         <v>13700</v>
@@ -2225,7 +2225,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G64" t="n">
-        <v>11.1542310714722</v>
+        <v>11.1542301177979</v>
       </c>
       <c r="H64" t="n">
         <v>1500</v>
@@ -2254,7 +2254,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>10.9428148269653</v>
+        <v>10.942816734314</v>
       </c>
       <c r="H65" t="n">
         <v>1100</v>
@@ -2283,7 +2283,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>11.0020122528076</v>
+        <v>11.0020141601562</v>
       </c>
       <c r="H66" t="n">
         <v>3400</v>
@@ -2341,7 +2341,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H68" t="n">
         <v>1800</v>
@@ -2370,7 +2370,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G69" t="n">
-        <v>10.8582515716553</v>
+        <v>10.858250617981</v>
       </c>
       <c r="H69" t="n">
         <v>3700</v>
@@ -2399,7 +2399,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G70" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328800201416</v>
       </c>
       <c r="H70" t="n">
         <v>3300</v>
@@ -2428,7 +2428,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G71" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328800201416</v>
       </c>
       <c r="H71" t="n">
         <v>900</v>
@@ -2573,7 +2573,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328800201416</v>
       </c>
       <c r="H76" t="n">
         <v>1600</v>
@@ -2689,7 +2689,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>10.9005336761475</v>
+        <v>10.9005355834961</v>
       </c>
       <c r="H80" t="n">
         <v>1200</v>
@@ -2718,7 +2718,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>10.9259042739868</v>
+        <v>10.9259033203125</v>
       </c>
       <c r="H81" t="n">
         <v>1600</v>
@@ -2776,7 +2776,7 @@
         <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H83" t="n">
         <v>6800</v>
@@ -2805,7 +2805,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5538129806519</v>
+        <v>10.5538139343262</v>
       </c>
       <c r="H84" t="n">
         <v>2200</v>
@@ -2834,7 +2834,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H85" t="n">
         <v>9800</v>
@@ -2863,7 +2863,7 @@
         <v>12.5</v>
       </c>
       <c r="G86" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H86" t="n">
         <v>1600</v>
@@ -2892,7 +2892,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G87" t="n">
-        <v>10.6806640625</v>
+        <v>10.6806631088257</v>
       </c>
       <c r="H87" t="n">
         <v>800</v>
@@ -2921,7 +2921,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G88" t="n">
-        <v>10.6637496948242</v>
+        <v>10.6637477874756</v>
       </c>
       <c r="H88" t="n">
         <v>20600</v>
@@ -2950,7 +2950,7 @@
         <v>13</v>
       </c>
       <c r="G89" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H89" t="n">
         <v>43500</v>
@@ -2979,7 +2979,7 @@
         <v>13</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H90" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G91" t="n">
-        <v>10.9850997924805</v>
+        <v>10.9850988388062</v>
       </c>
       <c r="H91" t="n">
         <v>3900</v>
@@ -3037,7 +3037,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H92" t="n">
         <v>900</v>
@@ -3124,7 +3124,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H95" t="n">
         <v>1700</v>
@@ -3153,7 +3153,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G97" t="n">
-        <v>10.8159666061401</v>
+        <v>10.8159675598145</v>
       </c>
       <c r="H97" t="n">
         <v>1100</v>
@@ -3240,7 +3240,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H99" t="n">
         <v>1500</v>
@@ -3298,7 +3298,7 @@
         <v>12.75</v>
       </c>
       <c r="G101" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821426391602</v>
       </c>
       <c r="H101" t="n">
         <v>7700</v>
@@ -3356,7 +3356,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G103" t="n">
-        <v>10.8159666061401</v>
+        <v>10.8159675598145</v>
       </c>
       <c r="H103" t="n">
         <v>600</v>
@@ -3414,7 +3414,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G105" t="n">
-        <v>10.6806640625</v>
+        <v>10.6806631088257</v>
       </c>
       <c r="H105" t="n">
         <v>100</v>
@@ -3472,7 +3472,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H107" t="n">
         <v>1900</v>
@@ -3501,7 +3501,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G108" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328800201416</v>
       </c>
       <c r="H108" t="n">
         <v>5200</v>
@@ -3530,7 +3530,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G109" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H109" t="n">
         <v>600</v>
@@ -3588,7 +3588,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.7060317993164</v>
+        <v>10.7060327529907</v>
       </c>
       <c r="H111" t="n">
         <v>7100</v>
@@ -3617,7 +3617,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G112" t="n">
-        <v>10.7060317993164</v>
+        <v>10.7060327529907</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G113" t="n">
-        <v>10.7060317993164</v>
+        <v>10.7060327529907</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G114" t="n">
-        <v>10.7060317993164</v>
+        <v>10.7060327529907</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H115" t="n">
         <v>600</v>
@@ -3733,7 +3733,7 @@
         <v>12.75</v>
       </c>
       <c r="G116" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821426391602</v>
       </c>
       <c r="H116" t="n">
         <v>1500</v>
@@ -3762,7 +3762,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>10.7398586273193</v>
+        <v>10.7398595809937</v>
       </c>
       <c r="H117" t="n">
         <v>3300</v>
@@ -3791,7 +3791,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>10.7398586273193</v>
+        <v>10.7398595809937</v>
       </c>
       <c r="H118" t="n">
         <v>1000</v>
@@ -3820,7 +3820,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861631393433</v>
       </c>
       <c r="H119" t="n">
         <v>1200</v>
@@ -3849,7 +3849,7 @@
         <v>12.5</v>
       </c>
       <c r="G120" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H120" t="n">
         <v>1800</v>
@@ -3936,7 +3936,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>10.6552925109863</v>
+        <v>10.6552934646606</v>
       </c>
       <c r="H123" t="n">
         <v>1800</v>
@@ -3965,7 +3965,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H124" t="n">
         <v>1000</v>
@@ -3994,7 +3994,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H125" t="n">
         <v>1300</v>
@@ -4023,7 +4023,7 @@
         <v>12.5</v>
       </c>
       <c r="G126" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H126" t="n">
         <v>1100</v>
@@ -4052,7 +4052,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H127" t="n">
         <v>200</v>
@@ -4081,7 +4081,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H128" t="n">
         <v>800</v>
@@ -4110,7 +4110,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H131" t="n">
         <v>1200</v>
@@ -4197,7 +4197,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>10.6552925109863</v>
+        <v>10.6552934646606</v>
       </c>
       <c r="H133" t="n">
         <v>2100</v>
@@ -4255,7 +4255,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>10.6552925109863</v>
+        <v>10.6552934646606</v>
       </c>
       <c r="H134" t="n">
         <v>500</v>
@@ -4284,7 +4284,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>10.6552925109863</v>
+        <v>10.6552934646606</v>
       </c>
       <c r="H135" t="n">
         <v>900</v>
@@ -4313,7 +4313,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861631393433</v>
       </c>
       <c r="H136" t="n">
         <v>1500</v>
@@ -4342,7 +4342,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>10.4438791275024</v>
+        <v>10.4438781738281</v>
       </c>
       <c r="H137" t="n">
         <v>4600</v>
@@ -4400,7 +4400,7 @@
         <v>12.25</v>
       </c>
       <c r="G139" t="n">
-        <v>10.3593120574951</v>
+        <v>10.3593139648438</v>
       </c>
       <c r="H139" t="n">
         <v>18900</v>
@@ -4429,7 +4429,7 @@
         <v>12.75</v>
       </c>
       <c r="G140" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821426391602</v>
       </c>
       <c r="H140" t="n">
         <v>21700</v>
@@ -4458,7 +4458,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975765228271</v>
       </c>
       <c r="H141" t="n">
         <v>3500</v>
@@ -4487,7 +4487,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>10.5284433364868</v>
+        <v>10.5284452438354</v>
       </c>
       <c r="H142" t="n">
         <v>800</v>
@@ -4516,7 +4516,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>10.5284433364868</v>
+        <v>10.5284452438354</v>
       </c>
       <c r="H143" t="n">
         <v>1800</v>
@@ -4545,7 +4545,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>10.4438791275024</v>
+        <v>10.4438781738281</v>
       </c>
       <c r="H144" t="n">
         <v>400</v>
@@ -4574,7 +4574,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861631393433</v>
       </c>
       <c r="H145" t="n">
         <v>8600</v>
@@ -4603,7 +4603,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>10.2324628829956</v>
+        <v>10.2324638366699</v>
       </c>
       <c r="H146" t="n">
         <v>600</v>
@@ -4632,7 +4632,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861631393433</v>
       </c>
       <c r="H147" t="n">
         <v>500</v>
@@ -4661,7 +4661,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861631393433</v>
       </c>
       <c r="H148" t="n">
         <v>4000</v>
@@ -4719,7 +4719,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861631393433</v>
       </c>
       <c r="H150" t="n">
         <v>2300</v>
@@ -4748,7 +4748,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861631393433</v>
       </c>
       <c r="H151" t="n">
         <v>1600</v>
@@ -4777,7 +4777,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>10.4861602783203</v>
+        <v>10.4861631393433</v>
       </c>
       <c r="H152" t="n">
         <v>800</v>
@@ -4806,7 +4806,7 @@
         <v>13</v>
       </c>
       <c r="G153" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H153" t="n">
         <v>6700</v>
@@ -4893,7 +4893,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H156" t="n">
         <v>2800</v>
@@ -4951,7 +4951,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.6552925109863</v>
+        <v>10.6552934646606</v>
       </c>
       <c r="H158" t="n">
         <v>300</v>
@@ -5038,7 +5038,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>10.7398586273193</v>
+        <v>10.7398595809937</v>
       </c>
       <c r="H161" t="n">
         <v>2200</v>
@@ -5067,7 +5067,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>10.7398586273193</v>
+        <v>10.7398595809937</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G163" t="n">
-        <v>10.7398586273193</v>
+        <v>10.7398595809937</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>10.7398586273193</v>
+        <v>10.7398595809937</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G165" t="n">
-        <v>10.7398586273193</v>
+        <v>10.7398595809937</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>12.5</v>
       </c>
       <c r="G167" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H167" t="n">
         <v>3800</v>
@@ -5241,7 +5241,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>10.7398586273193</v>
+        <v>10.7398595809937</v>
       </c>
       <c r="H168" t="n">
         <v>12000</v>
@@ -5270,7 +5270,7 @@
         <v>12.5</v>
       </c>
       <c r="G169" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H169" t="n">
         <v>500</v>
@@ -5299,7 +5299,7 @@
         <v>12.75</v>
       </c>
       <c r="G170" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821426391602</v>
       </c>
       <c r="H170" t="n">
         <v>8800</v>
@@ -5328,7 +5328,7 @@
         <v>12.75</v>
       </c>
       <c r="G171" t="n">
-        <v>10.7821416854858</v>
+        <v>10.7821426391602</v>
       </c>
       <c r="H171" t="n">
         <v>400</v>
@@ -5357,7 +5357,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>10.5707273483276</v>
+        <v>10.5707263946533</v>
       </c>
       <c r="H172" t="n">
         <v>800</v>
@@ -5386,7 +5386,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>10.5284433364868</v>
+        <v>10.5284452438354</v>
       </c>
       <c r="H173" t="n">
         <v>4300</v>
@@ -5415,7 +5415,7 @@
         <v>13</v>
       </c>
       <c r="G174" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H174" t="n">
         <v>41300</v>
@@ -5531,7 +5531,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>10.824423789978</v>
+        <v>10.8244247436523</v>
       </c>
       <c r="H178" t="n">
         <v>700</v>
@@ -5589,7 +5589,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>11.1626882553101</v>
+        <v>11.1626873016357</v>
       </c>
       <c r="H180" t="n">
         <v>1400</v>
@@ -5618,7 +5618,7 @@
         <v>13</v>
       </c>
       <c r="G181" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H181" t="n">
         <v>900</v>
@@ -5647,7 +5647,7 @@
         <v>13</v>
       </c>
       <c r="G182" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H182" t="n">
         <v>1300</v>
@@ -5676,7 +5676,7 @@
         <v>13</v>
       </c>
       <c r="G183" t="n">
-        <v>10.9935569763184</v>
+        <v>10.9935550689697</v>
       </c>
       <c r="H183" t="n">
         <v>4000</v>
@@ -5734,7 +5734,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G185" t="n">
-        <v>11.1626882553101</v>
+        <v>11.1626873016357</v>
       </c>
       <c r="H185" t="n">
         <v>10300</v>
@@ -5763,7 +5763,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>11.2895364761353</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H186" t="n">
         <v>11400</v>
@@ -5821,7 +5821,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>11.2895364761353</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H188" t="n">
         <v>2000</v>
@@ -5850,7 +5850,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2472543716431</v>
+        <v>11.2472515106201</v>
       </c>
       <c r="H189" t="n">
         <v>100</v>
@@ -5879,7 +5879,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>11.0358400344849</v>
+        <v>11.0358381271362</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5908,7 +5908,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2895364761353</v>
+        <v>11.2895374298096</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -5966,7 +5966,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2472543716431</v>
+        <v>11.2472515106201</v>
       </c>
       <c r="H193" t="n">
         <v>1600</v>
@@ -6024,7 +6024,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>11.3741035461426</v>
+        <v>11.3741016387939</v>
       </c>
       <c r="H195" t="n">
         <v>2100</v>
@@ -6053,7 +6053,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>11.4586696624756</v>
+        <v>11.458667755127</v>
       </c>
       <c r="H196" t="n">
         <v>2000</v>
@@ -6082,7 +6082,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>11.4586696624756</v>
+        <v>11.458667755127</v>
       </c>
       <c r="H197" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>13.5</v>
       </c>
       <c r="G200" t="n">
-        <v>11.4163846969604</v>
+        <v>11.4163866043091</v>
       </c>
       <c r="H200" t="n">
         <v>2800</v>
@@ -6256,7 +6256,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5009508132935</v>
+        <v>11.5009517669678</v>
       </c>
       <c r="H203" t="n">
         <v>5800</v>
@@ -6285,7 +6285,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>11.7869577407837</v>
+        <v>11.786958694458</v>
       </c>
       <c r="H204" t="n">
         <v>8400</v>
@@ -6343,7 +6343,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>11.4402828216553</v>
+        <v>11.440281867981</v>
       </c>
       <c r="H206" t="n">
         <v>6500</v>
@@ -6372,7 +6372,7 @@
         <v>13.25</v>
       </c>
       <c r="G207" t="n">
-        <v>11.4836168289185</v>
+        <v>11.4836158752441</v>
       </c>
       <c r="H207" t="n">
         <v>7400</v>
@@ -6401,7 +6401,7 @@
         <v>13.25</v>
       </c>
       <c r="G208" t="n">
-        <v>11.4836168289185</v>
+        <v>11.4836158752441</v>
       </c>
       <c r="H208" t="n">
         <v>400</v>
@@ -6488,7 +6488,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>11.4402828216553</v>
+        <v>11.440281867981</v>
       </c>
       <c r="H211" t="n">
         <v>2300</v>
@@ -6546,7 +6546,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>11.6569557189941</v>
+        <v>11.6569538116455</v>
       </c>
       <c r="H213" t="n">
         <v>4500</v>
@@ -6575,7 +6575,7 @@
         <v>13.5</v>
       </c>
       <c r="G214" t="n">
-        <v>11.7002878189087</v>
+        <v>11.7002897262573</v>
       </c>
       <c r="H214" t="n">
         <v>1700</v>
@@ -6604,7 +6604,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H215" t="n">
         <v>700</v>
@@ -6633,7 +6633,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H216" t="n">
         <v>1800</v>
@@ -6662,7 +6662,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G217" t="n">
-        <v>11.8736267089844</v>
+        <v>11.8736276626587</v>
       </c>
       <c r="H217" t="n">
         <v>2900</v>
@@ -6691,7 +6691,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>11.526951789856</v>
+        <v>11.5269508361816</v>
       </c>
       <c r="H219" t="n">
         <v>3200</v>
@@ -6778,7 +6778,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H221" t="n">
         <v>1500</v>
@@ -6807,7 +6807,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.6569557189941</v>
+        <v>11.6569538116455</v>
       </c>
       <c r="H222" t="n">
         <v>1900</v>
@@ -6836,7 +6836,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H223" t="n">
         <v>41700</v>
@@ -6923,7 +6923,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>11.8736267089844</v>
+        <v>11.8736276626587</v>
       </c>
       <c r="H226" t="n">
         <v>3400</v>
@@ -7010,7 +7010,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>12.0902996063232</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H229" t="n">
         <v>1300</v>
@@ -7155,7 +7155,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>11.7869577407837</v>
+        <v>11.786958694458</v>
       </c>
       <c r="H234" t="n">
         <v>700</v>
@@ -7184,7 +7184,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436237335205</v>
       </c>
       <c r="H235" t="n">
         <v>2900</v>
@@ -7213,7 +7213,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.0902996063232</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H236" t="n">
         <v>2000</v>
@@ -7242,7 +7242,7 @@
         <v>13.5</v>
       </c>
       <c r="G237" t="n">
-        <v>11.7002878189087</v>
+        <v>11.7002897262573</v>
       </c>
       <c r="H237" t="n">
         <v>1100</v>
@@ -7329,7 +7329,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>12.0902996063232</v>
+        <v>12.0902986526489</v>
       </c>
       <c r="H240" t="n">
         <v>900</v>
@@ -7416,7 +7416,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>12.4803075790405</v>
+        <v>12.4803085327148</v>
       </c>
       <c r="H243" t="n">
         <v>3700</v>
@@ -7503,7 +7503,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>12.6969814300537</v>
+        <v>12.6969804763794</v>
       </c>
       <c r="H246" t="n">
         <v>4900</v>
@@ -7532,7 +7532,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G247" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H247" t="n">
         <v>10900</v>
@@ -7590,7 +7590,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H249" t="n">
         <v>8300</v>
@@ -7619,7 +7619,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>13.1303253173828</v>
+        <v>13.1303243637085</v>
       </c>
       <c r="H250" t="n">
         <v>4600</v>
@@ -7648,7 +7648,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H251" t="n">
         <v>12100</v>
@@ -7735,7 +7735,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8703174591064</v>
+        <v>12.8703184127808</v>
       </c>
       <c r="H254" t="n">
         <v>1600</v>
@@ -7793,7 +7793,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G256" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H256" t="n">
         <v>600</v>
@@ -7822,7 +7822,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H257" t="n">
         <v>900</v>
@@ -7851,7 +7851,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>12.9569883346558</v>
+        <v>12.9569864273071</v>
       </c>
       <c r="H258" t="n">
         <v>100</v>
@@ -7880,7 +7880,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>12.8269853591919</v>
+        <v>12.8269834518433</v>
       </c>
       <c r="H259" t="n">
         <v>1300</v>
@@ -7909,7 +7909,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>12.9136514663696</v>
+        <v>12.9136524200439</v>
       </c>
       <c r="H260" t="n">
         <v>1000</v>
@@ -7996,7 +7996,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H263" t="n">
         <v>2900</v>
@@ -8025,7 +8025,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>13.260329246521</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H264" t="n">
         <v>2000</v>
@@ -8112,7 +8112,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H267" t="n">
         <v>2500</v>
@@ -8170,7 +8170,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H269" t="n">
         <v>2200</v>
@@ -8199,7 +8199,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H270" t="n">
         <v>300</v>
@@ -8228,7 +8228,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>13.1303253173828</v>
+        <v>13.1303243637085</v>
       </c>
       <c r="H271" t="n">
         <v>1100</v>
@@ -8286,7 +8286,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H273" t="n">
         <v>1600</v>
@@ -8315,7 +8315,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H274" t="n">
         <v>1100</v>
@@ -8431,7 +8431,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H278" t="n">
         <v>1700</v>
@@ -8460,7 +8460,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H280" t="n">
         <v>200</v>
@@ -8518,7 +8518,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H281" t="n">
         <v>1000</v>
@@ -8547,7 +8547,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8576,7 +8576,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H283" t="n">
         <v>4000</v>
@@ -8663,7 +8663,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>13.260329246521</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H286" t="n">
         <v>25700</v>
@@ -8692,7 +8692,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>13.260329246521</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H287" t="n">
         <v>400</v>
@@ -8750,7 +8750,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H289" t="n">
         <v>2500</v>
@@ -8808,7 +8808,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>13.260329246521</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H291" t="n">
         <v>2500</v>
@@ -8837,7 +8837,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H292" t="n">
         <v>1100</v>
@@ -8866,7 +8866,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>13.260329246521</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H293" t="n">
         <v>800</v>
@@ -8895,7 +8895,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H294" t="n">
         <v>1800</v>
@@ -8924,7 +8924,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H295" t="n">
         <v>800</v>
@@ -8953,7 +8953,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H296" t="n">
         <v>25700</v>
@@ -8982,7 +8982,7 @@
         <v>15.5</v>
       </c>
       <c r="G297" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H297" t="n">
         <v>13600</v>
@@ -9011,7 +9011,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H298" t="n">
         <v>6800</v>
@@ -9040,7 +9040,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>13.1303253173828</v>
+        <v>13.1303243637085</v>
       </c>
       <c r="H299" t="n">
         <v>1700</v>
@@ -9069,7 +9069,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H300" t="n">
         <v>3000</v>
@@ -9098,7 +9098,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>13.260329246521</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H301" t="n">
         <v>2000</v>
@@ -9127,7 +9127,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H302" t="n">
         <v>1200</v>
@@ -9185,7 +9185,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G304" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H304" t="n">
         <v>900</v>
@@ -9214,7 +9214,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H305" t="n">
         <v>12300</v>
@@ -9243,7 +9243,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H306" t="n">
         <v>1200</v>
@@ -9272,7 +9272,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H307" t="n">
         <v>6600</v>
@@ -9301,7 +9301,7 @@
         <v>15.75</v>
       </c>
       <c r="G308" t="n">
-        <v>13.6503372192383</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H308" t="n">
         <v>15600</v>
@@ -9330,7 +9330,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H309" t="n">
         <v>2700</v>
@@ -9417,7 +9417,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H312" t="n">
         <v>11300</v>
@@ -9446,7 +9446,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H313" t="n">
         <v>9400</v>
@@ -9475,7 +9475,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H314" t="n">
         <v>3300</v>
@@ -9504,7 +9504,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G315" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H315" t="n">
         <v>2100</v>
@@ -9562,7 +9562,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H317" t="n">
         <v>1900</v>
@@ -9591,7 +9591,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H318" t="n">
         <v>1500</v>
@@ -9620,7 +9620,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G319" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H319" t="n">
         <v>200</v>
@@ -9649,7 +9649,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H320" t="n">
         <v>1400</v>
@@ -9678,7 +9678,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H321" t="n">
         <v>2200</v>
@@ -9707,7 +9707,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G322" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H322" t="n">
         <v>300</v>
@@ -9736,7 +9736,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H323" t="n">
         <v>1900</v>
@@ -9765,7 +9765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H324" t="n">
         <v>2600</v>
@@ -9823,7 +9823,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>13.260329246521</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H326" t="n">
         <v>2300</v>
@@ -9939,7 +9939,7 @@
         <v>15.5</v>
       </c>
       <c r="G330" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H330" t="n">
         <v>800</v>
@@ -9968,7 +9968,7 @@
         <v>15.5</v>
       </c>
       <c r="G331" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H332" t="n">
         <v>30500</v>
@@ -10026,7 +10026,7 @@
         <v>15.75</v>
       </c>
       <c r="G333" t="n">
-        <v>13.6503372192383</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H333" t="n">
         <v>1000</v>
@@ -10055,7 +10055,7 @@
         <v>15.5</v>
       </c>
       <c r="G334" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H334" t="n">
         <v>7500</v>
@@ -10084,7 +10084,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H338" t="n">
         <v>1000</v>
@@ -10200,7 +10200,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H339" t="n">
         <v>1000</v>
@@ -10229,7 +10229,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H341" t="n">
         <v>200</v>
@@ -10287,7 +10287,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H342" t="n">
         <v>1100</v>
@@ -10316,7 +10316,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G343" t="n">
-        <v>13.260329246521</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H343" t="n">
         <v>500</v>
@@ -10432,7 +10432,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>13.260329246521</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H347" t="n">
         <v>600</v>
@@ -10461,7 +10461,7 @@
         <v>15.75</v>
       </c>
       <c r="G348" t="n">
-        <v>13.6503372192383</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H348" t="n">
         <v>1900</v>
@@ -10490,7 +10490,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H349" t="n">
         <v>3400</v>
@@ -10519,7 +10519,7 @@
         <v>15.75</v>
       </c>
       <c r="G350" t="n">
-        <v>13.6503372192383</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H350" t="n">
         <v>500</v>
@@ -10548,7 +10548,7 @@
         <v>15.5</v>
       </c>
       <c r="G351" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H351" t="n">
         <v>1400</v>
@@ -10577,7 +10577,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H352" t="n">
         <v>4000</v>
@@ -10606,7 +10606,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G353" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H353" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>13.5203342437744</v>
+        <v>13.5203351974487</v>
       </c>
       <c r="H354" t="n">
         <v>3600</v>
@@ -10722,7 +10722,7 @@
         <v>15.75</v>
       </c>
       <c r="G357" t="n">
-        <v>13.6503372192383</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H357" t="n">
         <v>4100</v>
@@ -10751,7 +10751,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H358" t="n">
         <v>3400</v>
@@ -10780,7 +10780,7 @@
         <v>15.5</v>
       </c>
       <c r="G359" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H359" t="n">
         <v>200</v>
@@ -10838,7 +10838,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H361" t="n">
         <v>900</v>
@@ -10867,7 +10867,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H363" t="n">
         <v>1300</v>
@@ -10925,7 +10925,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H364" t="n">
         <v>200</v>
@@ -10954,7 +10954,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G365" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H365" t="n">
         <v>1300</v>
@@ -10983,7 +10983,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>13.6070013046265</v>
+        <v>13.6070022583008</v>
       </c>
       <c r="H366" t="n">
         <v>4500</v>
@@ -11012,7 +11012,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11099,7 +11099,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H370" t="n">
         <v>1000</v>
@@ -11128,7 +11128,7 @@
         <v>15.5</v>
       </c>
       <c r="G371" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H371" t="n">
         <v>400</v>
@@ -11157,7 +11157,7 @@
         <v>15.5</v>
       </c>
       <c r="G372" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H372" t="n">
         <v>1000</v>
@@ -11186,7 +11186,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>13.1303253173828</v>
+        <v>13.1303243637085</v>
       </c>
       <c r="H373" t="n">
         <v>700</v>
@@ -11215,7 +11215,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>13.173659324646</v>
+        <v>13.1736583709717</v>
       </c>
       <c r="H374" t="n">
         <v>100</v>
@@ -11244,7 +11244,7 @@
         <v>15.5</v>
       </c>
       <c r="G375" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H375" t="n">
         <v>1000</v>
@@ -11273,7 +11273,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H376" t="n">
         <v>2300</v>
@@ -11302,7 +11302,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H377" t="n">
         <v>900</v>
@@ -11331,7 +11331,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>13.3036613464355</v>
+        <v>13.3036623001099</v>
       </c>
       <c r="H378" t="n">
         <v>100</v>
@@ -11360,7 +11360,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H379" t="n">
         <v>6400</v>
@@ -11418,7 +11418,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H381" t="n">
         <v>800</v>
@@ -11447,7 +11447,7 @@
         <v>15.5</v>
       </c>
       <c r="G382" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336652755737</v>
       </c>
       <c r="H382" t="n">
         <v>300</v>
@@ -11505,7 +11505,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>13.346996307373</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H384" t="n">
         <v>300</v>
@@ -11534,7 +11534,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H385" t="n">
         <v>200</v>
@@ -11563,7 +11563,7 @@
         <v>15.75</v>
       </c>
       <c r="G386" t="n">
-        <v>13.6503372192383</v>
+        <v>13.6503381729126</v>
       </c>
       <c r="H386" t="n">
         <v>8100</v>
@@ -11621,7 +11621,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>14.2136821746826</v>
+        <v>14.2136840820312</v>
       </c>
       <c r="H388" t="n">
         <v>3100</v>
@@ -11679,7 +11679,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H390" t="n">
         <v>10000</v>
@@ -11708,7 +11708,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H391" t="n">
         <v>7500</v>
@@ -11766,7 +11766,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>14.9070358276367</v>
+        <v>14.907036781311</v>
       </c>
       <c r="H393" t="n">
         <v>3100</v>
@@ -11795,7 +11795,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H394" t="n">
         <v>3700</v>
@@ -11824,7 +11824,7 @@
         <v>17</v>
       </c>
       <c r="G395" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H395" t="n">
         <v>3200</v>
@@ -11882,7 +11882,7 @@
         <v>16.75</v>
       </c>
       <c r="G397" t="n">
-        <v>14.5170259475708</v>
+        <v>14.5170278549194</v>
       </c>
       <c r="H397" t="n">
         <v>4600</v>
@@ -11911,7 +11911,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>14.5603590011597</v>
+        <v>14.5603580474854</v>
       </c>
       <c r="H398" t="n">
         <v>300</v>
@@ -11940,7 +11940,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H399" t="n">
         <v>1200</v>
@@ -11969,7 +11969,7 @@
         <v>17</v>
       </c>
       <c r="G400" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H400" t="n">
         <v>3000</v>
@@ -12027,7 +12027,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>14.3870239257812</v>
+        <v>14.3870229721069</v>
       </c>
       <c r="H402" t="n">
         <v>1500</v>
@@ -12056,7 +12056,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G403" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H403" t="n">
         <v>900</v>
@@ -12085,7 +12085,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>14.5603590011597</v>
+        <v>14.5603580474854</v>
       </c>
       <c r="H404" t="n">
         <v>2900</v>
@@ -12114,7 +12114,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>14.5603590011597</v>
+        <v>14.5603580474854</v>
       </c>
       <c r="H405" t="n">
         <v>2000</v>
@@ -12143,7 +12143,7 @@
         <v>17</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H406" t="n">
         <v>3400</v>
@@ -12172,7 +12172,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H407" t="n">
         <v>5600</v>
@@ -12201,7 +12201,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H409" t="n">
         <v>2600</v>
@@ -12259,7 +12259,7 @@
         <v>17</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H410" t="n">
         <v>6700</v>
@@ -12288,7 +12288,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G411" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H411" t="n">
         <v>9500</v>
@@ -12317,7 +12317,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G412" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H412" t="n">
         <v>3600</v>
@@ -12346,7 +12346,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H413" t="n">
         <v>2000</v>
@@ -12375,7 +12375,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G414" t="n">
-        <v>14.7770318984985</v>
+        <v>14.7770299911499</v>
       </c>
       <c r="H414" t="n">
         <v>900</v>
@@ -12433,7 +12433,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H416" t="n">
         <v>2000</v>
@@ -12462,7 +12462,7 @@
         <v>16.75</v>
       </c>
       <c r="G417" t="n">
-        <v>14.5170259475708</v>
+        <v>14.5170278549194</v>
       </c>
       <c r="H417" t="n">
         <v>15600</v>
@@ -12636,7 +12636,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>14.3436880111694</v>
+        <v>14.3436870574951</v>
       </c>
       <c r="H423" t="n">
         <v>6600</v>
@@ -12665,7 +12665,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>14.2570199966431</v>
+        <v>14.2570209503174</v>
       </c>
       <c r="H424" t="n">
         <v>3100</v>
@@ -12694,7 +12694,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>14.3870239257812</v>
+        <v>14.3870229721069</v>
       </c>
       <c r="H425" t="n">
         <v>4300</v>
@@ -12752,7 +12752,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>14.3870239257812</v>
+        <v>14.3870229721069</v>
       </c>
       <c r="H427" t="n">
         <v>600</v>
@@ -12781,7 +12781,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>14.2570199966431</v>
+        <v>14.2570209503174</v>
       </c>
       <c r="H428" t="n">
         <v>9500</v>
@@ -12810,7 +12810,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H429" t="n">
         <v>11700</v>
@@ -12839,7 +12839,7 @@
         <v>17</v>
       </c>
       <c r="G430" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H430" t="n">
         <v>8300</v>
@@ -12897,7 +12897,7 @@
         <v>17</v>
       </c>
       <c r="G432" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H432" t="n">
         <v>4100</v>
@@ -12955,7 +12955,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H434" t="n">
         <v>700</v>
@@ -12984,7 +12984,7 @@
         <v>17</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7336988449097</v>
+        <v>14.7336978912354</v>
       </c>
       <c r="H435" t="n">
         <v>3600</v>
@@ -13013,7 +13013,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H436" t="n">
         <v>2900</v>
@@ -13042,7 +13042,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>14.647027015686</v>
+        <v>14.6470289230347</v>
       </c>
       <c r="H437" t="n">
         <v>2300</v>
@@ -13071,7 +13071,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>14.6903638839722</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H438" t="n">
         <v>3800</v>
@@ -13100,7 +13100,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>14.8203659057617</v>
+        <v>14.8203678131104</v>
       </c>
       <c r="H439" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>14.8203659057617</v>
+        <v>14.8203678131104</v>
       </c>
       <c r="H440" t="n">
         <v>3000</v>
@@ -13158,7 +13158,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>14.8203659057617</v>
+        <v>14.8203678131104</v>
       </c>
       <c r="H441" t="n">
         <v>600</v>
@@ -13187,7 +13187,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>14.8203659057617</v>
+        <v>14.8203678131104</v>
       </c>
       <c r="H442" t="n">
         <v>3700</v>
@@ -13216,7 +13216,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G443" t="n">
-        <v>14.9070358276367</v>
+        <v>14.907036781311</v>
       </c>
       <c r="H443" t="n">
         <v>14843</v>
@@ -13274,7 +13274,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>14.9937057495117</v>
+        <v>14.9937038421631</v>
       </c>
       <c r="H445" t="n">
         <v>4294</v>
@@ -13303,7 +13303,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G446" t="n">
-        <v>14.9070358276367</v>
+        <v>14.907036781311</v>
       </c>
       <c r="H446" t="n">
         <v>3301</v>
@@ -13332,7 +13332,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>14.8203659057617</v>
+        <v>14.8203678131104</v>
       </c>
       <c r="H447" t="n">
         <v>37419</v>
@@ -13361,7 +13361,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G448" t="n">
-        <v>14.7770318984985</v>
+        <v>14.7770299911499</v>
       </c>
       <c r="H448" t="n">
         <v>885</v>
@@ -13390,7 +13390,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>15.0370407104492</v>
+        <v>15.0370388031006</v>
       </c>
       <c r="H449" t="n">
         <v>3162</v>
@@ -13477,7 +13477,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>14.9937057495117</v>
+        <v>14.9937038421631</v>
       </c>
       <c r="H452" t="n">
         <v>4325</v>
@@ -13593,7 +13593,7 @@
         <v>17.25</v>
       </c>
       <c r="G456" t="n">
-        <v>15.3926887512207</v>
+        <v>15.3926877975464</v>
       </c>
       <c r="H456" t="n">
         <v>5156</v>
@@ -13651,7 +13651,7 @@
         <v>17.25</v>
       </c>
       <c r="G458" t="n">
-        <v>15.3926887512207</v>
+        <v>15.3926877975464</v>
       </c>
       <c r="H458" t="n">
         <v>6310</v>
@@ -13680,7 +13680,7 @@
         <v>17</v>
       </c>
       <c r="G459" t="n">
-        <v>15.1696071624756</v>
+        <v>15.1696062088013</v>
       </c>
       <c r="H459" t="n">
         <v>20546</v>
@@ -13709,7 +13709,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803728103638</v>
       </c>
       <c r="H460" t="n">
         <v>2407</v>
@@ -13738,7 +13738,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>15.21422290802</v>
+        <v>15.2142210006714</v>
       </c>
       <c r="H461" t="n">
         <v>4400</v>
@@ -13767,7 +13767,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>14.9911394119263</v>
+        <v>14.991138458252</v>
       </c>
       <c r="H462" t="n">
         <v>599</v>
@@ -13796,7 +13796,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G463" t="n">
-        <v>15.1249904632568</v>
+        <v>15.1249895095825</v>
       </c>
       <c r="H463" t="n">
         <v>771</v>
@@ -13825,7 +13825,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>15.4373064041138</v>
+        <v>15.4373054504395</v>
       </c>
       <c r="H464" t="n">
         <v>1237</v>
@@ -13854,7 +13854,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>15.348072052002</v>
+        <v>15.3480730056763</v>
       </c>
       <c r="H465" t="n">
         <v>9270</v>
@@ -13883,7 +13883,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>15.348072052002</v>
+        <v>15.3480730056763</v>
       </c>
       <c r="H466" t="n">
         <v>3452</v>
@@ -13912,7 +13912,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>15.348072052002</v>
+        <v>15.3480730056763</v>
       </c>
       <c r="H467" t="n">
         <v>30811</v>
@@ -13941,7 +13941,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>15.4373064041138</v>
+        <v>15.4373054504395</v>
       </c>
       <c r="H468" t="n">
         <v>1311</v>
@@ -13999,7 +13999,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>15.8834676742554</v>
+        <v>15.8834686279297</v>
       </c>
       <c r="H470" t="n">
         <v>9513</v>
@@ -14028,7 +14028,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>15.8834676742554</v>
+        <v>15.8834686279297</v>
       </c>
       <c r="H471" t="n">
         <v>3677</v>
@@ -14115,7 +14115,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>17.0434989929199</v>
+        <v>17.0434970855713</v>
       </c>
       <c r="H474" t="n">
         <v>23112</v>
@@ -14144,7 +14144,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>17.0434989929199</v>
+        <v>17.0434970855713</v>
       </c>
       <c r="H475" t="n">
         <v>20082</v>
@@ -14173,7 +14173,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>16.9988822937012</v>
+        <v>16.9988803863525</v>
       </c>
       <c r="H476" t="n">
         <v>6745</v>
@@ -14202,7 +14202,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G477" t="n">
-        <v>17.1327323913574</v>
+        <v>17.1327342987061</v>
       </c>
       <c r="H477" t="n">
         <v>16785</v>
@@ -14231,7 +14231,7 @@
         <v>19.5</v>
       </c>
       <c r="G478" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H478" t="n">
         <v>16646</v>
@@ -14260,7 +14260,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>17.0434989929199</v>
+        <v>17.0434970855713</v>
       </c>
       <c r="H479" t="n">
         <v>8480</v>
@@ -14289,7 +14289,7 @@
         <v>19.5</v>
       </c>
       <c r="G480" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H480" t="n">
         <v>6935</v>
@@ -14318,7 +14318,7 @@
         <v>19.5</v>
       </c>
       <c r="G481" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H481" t="n">
         <v>8270</v>
@@ -14376,7 +14376,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450454711914</v>
       </c>
       <c r="H483" t="n">
         <v>4149</v>
@@ -14521,7 +14521,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450454711914</v>
       </c>
       <c r="H488" t="n">
         <v>2521</v>
@@ -14550,7 +14550,7 @@
         <v>19.5</v>
       </c>
       <c r="G489" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H489" t="n">
         <v>2164</v>
@@ -14579,7 +14579,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G490" t="n">
-        <v>18.6496925354004</v>
+        <v>18.649694442749</v>
       </c>
       <c r="H490" t="n">
         <v>46374</v>
@@ -14608,7 +14608,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>18.6496925354004</v>
+        <v>18.649694442749</v>
       </c>
       <c r="H491" t="n">
         <v>14670</v>
@@ -14637,7 +14637,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>18.6496925354004</v>
+        <v>18.649694442749</v>
       </c>
       <c r="H492" t="n">
         <v>6388</v>
@@ -14666,7 +14666,7 @@
         <v>20.5</v>
       </c>
       <c r="G493" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H493" t="n">
         <v>2753</v>
@@ -14695,7 +14695,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604610443115</v>
       </c>
       <c r="H494" t="n">
         <v>3493</v>
@@ -14724,7 +14724,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>18.6496925354004</v>
+        <v>18.649694442749</v>
       </c>
       <c r="H495" t="n">
         <v>6097</v>
@@ -14782,7 +14782,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>18.6496925354004</v>
+        <v>18.649694442749</v>
       </c>
       <c r="H497" t="n">
         <v>6035</v>
@@ -14811,7 +14811,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>18.6496925354004</v>
+        <v>18.649694442749</v>
       </c>
       <c r="H498" t="n">
         <v>7892</v>
@@ -14840,7 +14840,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604610443115</v>
       </c>
       <c r="H499" t="n">
         <v>5362</v>
@@ -14869,7 +14869,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604610443115</v>
       </c>
       <c r="H500" t="n">
         <v>4065</v>
@@ -14898,7 +14898,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G501" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H501" t="n">
         <v>3610</v>
@@ -14927,7 +14927,7 @@
         <v>20.5</v>
       </c>
       <c r="G502" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H502" t="n">
         <v>6475</v>
@@ -15014,7 +15014,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G505" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142921447754</v>
       </c>
       <c r="H505" t="n">
         <v>2052</v>
@@ -15043,7 +15043,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142921447754</v>
       </c>
       <c r="H506" t="n">
         <v>8048</v>
@@ -15072,7 +15072,7 @@
         <v>20.5</v>
       </c>
       <c r="G507" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H507" t="n">
         <v>3880</v>
@@ -15130,7 +15130,7 @@
         <v>20.5</v>
       </c>
       <c r="G509" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H509" t="n">
         <v>3508</v>
@@ -15159,7 +15159,7 @@
         <v>20.5</v>
       </c>
       <c r="G510" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H510" t="n">
         <v>1314</v>
@@ -15188,7 +15188,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142921447754</v>
       </c>
       <c r="H511" t="n">
         <v>2701</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H512" t="n">
         <v>3189</v>
@@ -15246,7 +15246,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450454711914</v>
       </c>
       <c r="H513" t="n">
         <v>3700</v>
@@ -15275,7 +15275,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450454711914</v>
       </c>
       <c r="H514" t="n">
         <v>5110</v>
@@ -15304,7 +15304,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G515" t="n">
-        <v>17.80198097229</v>
+        <v>17.8019790649414</v>
       </c>
       <c r="H515" t="n">
         <v>5505</v>
@@ -15333,7 +15333,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.6681308746338</v>
+        <v>17.6681289672852</v>
       </c>
       <c r="H516" t="n">
         <v>14791</v>
@@ -15391,7 +15391,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>17.6681308746338</v>
+        <v>17.6681289672852</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>19.75</v>
       </c>
       <c r="G519" t="n">
-        <v>17.6235122680664</v>
+        <v>17.6235103607178</v>
       </c>
       <c r="H519" t="n">
         <v>3789</v>
@@ -15565,7 +15565,7 @@
         <v>19.5</v>
       </c>
       <c r="G524" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H524" t="n">
         <v>2311</v>
@@ -15594,7 +15594,7 @@
         <v>19.5</v>
       </c>
       <c r="G525" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H525" t="n">
         <v>4044</v>
@@ -15652,7 +15652,7 @@
         <v>19.5</v>
       </c>
       <c r="G527" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H527" t="n">
         <v>1461</v>
@@ -15681,7 +15681,7 @@
         <v>19.5</v>
       </c>
       <c r="G528" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>17.4896640777588</v>
+        <v>17.4896659851074</v>
       </c>
       <c r="H529" t="n">
         <v>1050</v>
@@ -15768,7 +15768,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>17.44504737854</v>
+        <v>17.4450454711914</v>
       </c>
       <c r="H531" t="n">
         <v>1036</v>
@@ -15826,7 +15826,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>17.757360458374</v>
+        <v>17.7573585510254</v>
       </c>
       <c r="H533" t="n">
         <v>1112</v>
@@ -15855,7 +15855,7 @@
         <v>20</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H534" t="n">
         <v>2224</v>
@@ -15884,7 +15884,7 @@
         <v>20</v>
       </c>
       <c r="G535" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H535" t="n">
         <v>4616</v>
@@ -15942,7 +15942,7 @@
         <v>20</v>
       </c>
       <c r="G537" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H537" t="n">
         <v>2250</v>
@@ -15971,7 +15971,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142921447754</v>
       </c>
       <c r="H538" t="n">
         <v>10406</v>
@@ -16000,7 +16000,7 @@
         <v>20</v>
       </c>
       <c r="G539" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H539" t="n">
         <v>1256</v>
@@ -16029,7 +16029,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142921447754</v>
       </c>
       <c r="H540" t="n">
         <v>5116</v>
@@ -16087,7 +16087,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>18.6496925354004</v>
+        <v>18.649694442749</v>
       </c>
       <c r="H542" t="n">
         <v>7090</v>
@@ -16116,7 +16116,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H543" t="n">
         <v>2090</v>
@@ -16145,7 +16145,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H544" t="n">
         <v>2060</v>
@@ -16174,7 +16174,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H545" t="n">
         <v>2697</v>
@@ -16232,7 +16232,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H547" t="n">
         <v>603</v>
@@ -16290,7 +16290,7 @@
         <v>20.5</v>
       </c>
       <c r="G549" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H549" t="n">
         <v>7326</v>
@@ -16377,7 +16377,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G552" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142921447754</v>
       </c>
       <c r="H552" t="n">
         <v>5016</v>
@@ -16435,7 +16435,7 @@
         <v>20.5</v>
       </c>
       <c r="G554" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H554" t="n">
         <v>1796</v>
@@ -16464,7 +16464,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G555" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604610443115</v>
       </c>
       <c r="H555" t="n">
         <v>7200</v>
@@ -16580,7 +16580,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>17.7127456665039</v>
+        <v>17.7127475738525</v>
       </c>
       <c r="H559" t="n">
         <v>1400</v>
@@ -16638,7 +16638,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>17.7127456665039</v>
+        <v>17.7127475738525</v>
       </c>
       <c r="H561" t="n">
         <v>5664</v>
@@ -16696,7 +16696,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142921447754</v>
       </c>
       <c r="H563" t="n">
         <v>2101</v>
@@ -16725,7 +16725,7 @@
         <v>20.5</v>
       </c>
       <c r="G564" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H564" t="n">
         <v>3218</v>
@@ -16754,7 +16754,7 @@
         <v>20</v>
       </c>
       <c r="G565" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H565" t="n">
         <v>2880</v>
@@ -16783,7 +16783,7 @@
         <v>20</v>
       </c>
       <c r="G566" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H566" t="n">
         <v>2491</v>
@@ -16812,7 +16812,7 @@
         <v>20</v>
       </c>
       <c r="G567" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H567" t="n">
         <v>2423</v>
@@ -16841,7 +16841,7 @@
         <v>20</v>
       </c>
       <c r="G568" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H568" t="n">
         <v>5106</v>
@@ -16870,7 +16870,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>17.6681308746338</v>
+        <v>17.6681289672852</v>
       </c>
       <c r="H569" t="n">
         <v>610</v>
@@ -16899,7 +16899,7 @@
         <v>20</v>
       </c>
       <c r="G570" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H570" t="n">
         <v>534</v>
@@ -16928,7 +16928,7 @@
         <v>20</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H571" t="n">
         <v>1494</v>
@@ -16957,7 +16957,7 @@
         <v>20</v>
       </c>
       <c r="G572" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465976715088</v>
       </c>
       <c r="H572" t="n">
         <v>126</v>
@@ -17015,7 +17015,7 @@
         <v>19.75</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6235122680664</v>
+        <v>17.6235103607178</v>
       </c>
       <c r="H574" t="n">
         <v>1476</v>
@@ -17044,7 +17044,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142921447754</v>
       </c>
       <c r="H575" t="n">
         <v>12920</v>
@@ -17160,7 +17160,7 @@
         <v>20.5</v>
       </c>
       <c r="G579" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H579" t="n">
         <v>6769</v>
@@ -17218,7 +17218,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142921447754</v>
       </c>
       <c r="H581" t="n">
         <v>1397</v>
@@ -17392,7 +17392,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G587" t="n">
-        <v>18.8281555175781</v>
+        <v>18.8281574249268</v>
       </c>
       <c r="H587" t="n">
         <v>10010</v>
@@ -17421,7 +17421,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>19.0066223144531</v>
+        <v>19.0066242218018</v>
       </c>
       <c r="H588" t="n">
         <v>3033</v>
@@ -17450,7 +17450,7 @@
         <v>21.5</v>
       </c>
       <c r="G589" t="n">
-        <v>19.1850891113281</v>
+        <v>19.1850910186768</v>
       </c>
       <c r="H589" t="n">
         <v>3910</v>
@@ -17479,7 +17479,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>19.4527854919434</v>
+        <v>19.4527893066406</v>
       </c>
       <c r="H590" t="n">
         <v>27442</v>
@@ -17508,7 +17508,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>19.4527854919434</v>
+        <v>19.4527893066406</v>
       </c>
       <c r="H591" t="n">
         <v>2820</v>
@@ -17537,7 +17537,7 @@
         <v>21.5</v>
       </c>
       <c r="G592" t="n">
-        <v>19.1850891113281</v>
+        <v>19.1850910186768</v>
       </c>
       <c r="H592" t="n">
         <v>14908</v>
@@ -17566,7 +17566,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>19.3635540008545</v>
+        <v>19.3635559082031</v>
       </c>
       <c r="H593" t="n">
         <v>5818</v>
@@ -17595,7 +17595,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>19.2743244171143</v>
+        <v>19.2743225097656</v>
       </c>
       <c r="H594" t="n">
         <v>3162</v>
@@ -17624,7 +17624,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>19.4527854919434</v>
+        <v>19.4527893066406</v>
       </c>
       <c r="H595" t="n">
         <v>7478</v>
@@ -17682,7 +17682,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>19.8097190856934</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H597" t="n">
         <v>6848</v>
@@ -17740,7 +17740,7 @@
         <v>22</v>
       </c>
       <c r="G599" t="n">
-        <v>19.6312561035156</v>
+        <v>19.631254196167</v>
       </c>
       <c r="H599" t="n">
         <v>6801</v>
@@ -17798,7 +17798,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H601" t="n">
         <v>2527</v>
@@ -17827,7 +17827,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>20.166654586792</v>
+        <v>20.1666526794434</v>
       </c>
       <c r="H602" t="n">
         <v>19155</v>
@@ -17856,7 +17856,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>20.166654586792</v>
+        <v>20.1666526794434</v>
       </c>
       <c r="H603" t="n">
         <v>3830</v>
@@ -17885,7 +17885,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>19.8097190856934</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H604" t="n">
         <v>6581</v>
@@ -17914,7 +17914,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>19.3635540008545</v>
+        <v>19.3635559082031</v>
       </c>
       <c r="H605" t="n">
         <v>5376</v>
@@ -17943,7 +17943,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H606" t="n">
         <v>2280</v>
@@ -17972,7 +17972,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H607" t="n">
         <v>3152</v>
@@ -18001,7 +18001,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G608" t="n">
-        <v>19.4527854919434</v>
+        <v>19.4527893066406</v>
       </c>
       <c r="H608" t="n">
         <v>8174</v>
@@ -18030,7 +18030,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>19.2743244171143</v>
+        <v>19.2743225097656</v>
       </c>
       <c r="H609" t="n">
         <v>1522</v>
@@ -18059,7 +18059,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>19.2743244171143</v>
+        <v>19.2743225097656</v>
       </c>
       <c r="H610" t="n">
         <v>5108</v>
@@ -18088,7 +18088,7 @@
         <v>22</v>
       </c>
       <c r="G611" t="n">
-        <v>19.6312561035156</v>
+        <v>19.631254196167</v>
       </c>
       <c r="H611" t="n">
         <v>2653</v>
@@ -18146,7 +18146,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>19.8989543914795</v>
+        <v>19.8989505767822</v>
       </c>
       <c r="H613" t="n">
         <v>3145</v>
@@ -18175,7 +18175,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H614" t="n">
         <v>2737</v>
@@ -18204,7 +18204,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>19.8097190856934</v>
+        <v>19.8097229003906</v>
       </c>
       <c r="H615" t="n">
         <v>420</v>
@@ -18233,7 +18233,7 @@
         <v>22</v>
       </c>
       <c r="G616" t="n">
-        <v>19.6312561035156</v>
+        <v>19.631254196167</v>
       </c>
       <c r="H616" t="n">
         <v>6076</v>
@@ -18262,7 +18262,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>20.79128074646</v>
+        <v>20.7912845611572</v>
       </c>
       <c r="H617" t="n">
         <v>12485</v>
@@ -18291,7 +18291,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>20.7020511627197</v>
+        <v>20.7020492553711</v>
       </c>
       <c r="H618" t="n">
         <v>17175</v>
@@ -18320,7 +18320,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>20.7020511627197</v>
+        <v>20.7020492553711</v>
       </c>
       <c r="H619" t="n">
         <v>10967</v>
@@ -18552,7 +18552,7 @@
         <v>24.5</v>
       </c>
       <c r="G627" t="n">
-        <v>21.8620758056641</v>
+        <v>21.86208152771</v>
       </c>
       <c r="H627" t="n">
         <v>11972</v>
@@ -18581,7 +18581,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>21.7728481292725</v>
+        <v>21.7728424072266</v>
       </c>
       <c r="H628" t="n">
         <v>3942</v>
@@ -18610,7 +18610,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G629" t="n">
-        <v>21.9513130187988</v>
+        <v>21.9513111114502</v>
       </c>
       <c r="H629" t="n">
         <v>6820</v>
@@ -18639,7 +18639,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H630" t="n">
         <v>8914</v>
@@ -18668,7 +18668,7 @@
         <v>24</v>
       </c>
       <c r="G631" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H631" t="n">
         <v>16893</v>
@@ -18697,7 +18697,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H632" t="n">
         <v>6876</v>
@@ -18784,7 +18784,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G635" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H635" t="n">
         <v>2316</v>
@@ -18813,7 +18813,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>21.2374458312988</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H636" t="n">
         <v>5007</v>
@@ -18842,7 +18842,7 @@
         <v>24</v>
       </c>
       <c r="G637" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H637" t="n">
         <v>11025</v>
@@ -18871,7 +18871,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H638" t="n">
         <v>1059</v>
@@ -19016,7 +19016,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>20.79128074646</v>
+        <v>20.7912845611572</v>
       </c>
       <c r="H643" t="n">
         <v>2095</v>
@@ -19045,7 +19045,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H644" t="n">
         <v>6935</v>
@@ -19161,7 +19161,7 @@
         <v>24</v>
       </c>
       <c r="G648" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H648" t="n">
         <v>6636</v>
@@ -19190,7 +19190,7 @@
         <v>24</v>
       </c>
       <c r="G649" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H649" t="n">
         <v>10221</v>
@@ -19219,7 +19219,7 @@
         <v>24</v>
       </c>
       <c r="G650" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H650" t="n">
         <v>3081</v>
@@ -19422,7 +19422,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>21.2374458312988</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H657" t="n">
         <v>2286</v>
@@ -19451,7 +19451,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>21.2374458312988</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H658" t="n">
         <v>5978</v>
@@ -19480,7 +19480,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G659" t="n">
-        <v>20.2558860778809</v>
+        <v>20.2558841705322</v>
       </c>
       <c r="H659" t="n">
         <v>9014</v>
@@ -19509,7 +19509,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>20.7020511627197</v>
+        <v>20.7020492553711</v>
       </c>
       <c r="H660" t="n">
         <v>2179</v>
@@ -19654,7 +19654,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H665" t="n">
         <v>8640</v>
@@ -19683,7 +19683,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>19.3635540008545</v>
+        <v>19.3635559082031</v>
       </c>
       <c r="H666" t="n">
         <v>4583</v>
@@ -19712,7 +19712,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H667" t="n">
         <v>10615</v>
@@ -19741,7 +19741,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>19.0066223144531</v>
+        <v>19.0066242218018</v>
       </c>
       <c r="H668" t="n">
         <v>4049</v>
@@ -19770,7 +19770,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G669" t="n">
-        <v>18.6496925354004</v>
+        <v>18.649694442749</v>
       </c>
       <c r="H669" t="n">
         <v>8327</v>
@@ -19799,7 +19799,7 @@
         <v>20.5</v>
       </c>
       <c r="G670" t="n">
-        <v>18.292760848999</v>
+        <v>18.2927589416504</v>
       </c>
       <c r="H670" t="n">
         <v>9957</v>
@@ -19886,7 +19886,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>17.4896640777588</v>
+        <v>17.4896659851074</v>
       </c>
       <c r="H673" t="n">
         <v>2591</v>
@@ -19915,7 +19915,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>16.1957836151123</v>
+        <v>16.1957855224609</v>
       </c>
       <c r="H674" t="n">
         <v>4844</v>
@@ -19944,7 +19944,7 @@
         <v>18</v>
       </c>
       <c r="G675" t="n">
-        <v>16.0619373321533</v>
+        <v>16.0619354248047</v>
       </c>
       <c r="H675" t="n">
         <v>22529</v>
@@ -19973,7 +19973,7 @@
         <v>17.5</v>
       </c>
       <c r="G676" t="n">
-        <v>15.6157703399658</v>
+        <v>15.6157732009888</v>
       </c>
       <c r="H676" t="n">
         <v>12149</v>
@@ -20002,7 +20002,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>14.9019069671631</v>
+        <v>14.9019088745117</v>
       </c>
       <c r="H677" t="n">
         <v>5955</v>
@@ -20089,7 +20089,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>16.9988822937012</v>
+        <v>16.9988803863525</v>
       </c>
       <c r="H680" t="n">
         <v>12506</v>
@@ -20118,7 +20118,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>18.471227645874</v>
+        <v>18.4712238311768</v>
       </c>
       <c r="H681" t="n">
         <v>24241</v>
@@ -20147,7 +20147,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604610443115</v>
       </c>
       <c r="H682" t="n">
         <v>3394</v>
@@ -20205,7 +20205,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>19.0066223144531</v>
+        <v>19.0066242218018</v>
       </c>
       <c r="H684" t="n">
         <v>1114</v>
@@ -20234,7 +20234,7 @@
         <v>22</v>
       </c>
       <c r="G685" t="n">
-        <v>19.6312561035156</v>
+        <v>19.631254196167</v>
       </c>
       <c r="H685" t="n">
         <v>14359</v>
@@ -20263,7 +20263,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>20.2558860778809</v>
+        <v>20.2558841705322</v>
       </c>
       <c r="H686" t="n">
         <v>17625</v>
@@ -20292,7 +20292,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>20.79128074646</v>
+        <v>20.7912845611572</v>
       </c>
       <c r="H687" t="n">
         <v>33277</v>
@@ -20321,7 +20321,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>21.2374458312988</v>
+        <v>21.2374477386475</v>
       </c>
       <c r="H688" t="n">
         <v>26401</v>
@@ -20524,7 +20524,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H695" t="n">
         <v>8663</v>
@@ -20582,7 +20582,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H697" t="n">
         <v>7919</v>
@@ -20640,7 +20640,7 @@
         <v>24</v>
       </c>
       <c r="G699" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H699" t="n">
         <v>4272</v>
@@ -20785,7 +20785,7 @@
         <v>24</v>
       </c>
       <c r="G704" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H704" t="n">
         <v>20313</v>
@@ -20814,7 +20814,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H705" t="n">
         <v>3836</v>
@@ -20843,7 +20843,7 @@
         <v>24</v>
       </c>
       <c r="G706" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H706" t="n">
         <v>2368</v>
@@ -20872,7 +20872,7 @@
         <v>24</v>
       </c>
       <c r="G707" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159107208252</v>
       </c>
       <c r="H707" t="n">
         <v>10495</v>
@@ -20901,7 +20901,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G708" t="n">
-        <v>21.5943794250488</v>
+        <v>21.5943813323975</v>
       </c>
       <c r="H708" t="n">
         <v>1747</v>
@@ -20959,7 +20959,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>22.0405464172363</v>
+        <v>22.0405426025391</v>
       </c>
       <c r="H710" t="n">
         <v>9060</v>
@@ -20988,7 +20988,7 @@
         <v>25</v>
       </c>
       <c r="G711" t="n">
-        <v>22.7315845489502</v>
+        <v>22.7315826416016</v>
       </c>
       <c r="H711" t="n">
         <v>5201</v>
@@ -21046,7 +21046,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>22.3678817749023</v>
+        <v>22.3678798675537</v>
       </c>
       <c r="H713" t="n">
         <v>4418</v>
@@ -21075,7 +21075,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>22.1860275268555</v>
+        <v>22.1860256195068</v>
       </c>
       <c r="H714" t="n">
         <v>3575</v>
@@ -21104,7 +21104,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>22.1860275268555</v>
+        <v>22.1860256195068</v>
       </c>
       <c r="H715" t="n">
         <v>1991</v>
@@ -21133,7 +21133,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>22.1860275268555</v>
+        <v>22.1860256195068</v>
       </c>
       <c r="H716" t="n">
         <v>3812</v>
@@ -21191,7 +21191,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>22.1860275268555</v>
+        <v>22.1860256195068</v>
       </c>
       <c r="H718" t="n">
         <v>1554</v>
@@ -21336,7 +21336,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>22.3678817749023</v>
+        <v>22.3678798675537</v>
       </c>
       <c r="H723" t="n">
         <v>6214</v>
@@ -21510,7 +21510,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>22.0041770935059</v>
+        <v>22.0041751861572</v>
       </c>
       <c r="H729" t="n">
         <v>4125</v>
@@ -21568,7 +21568,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>21.7313957214355</v>
+        <v>21.7313919067383</v>
       </c>
       <c r="H731" t="n">
         <v>1834</v>
@@ -21597,7 +21597,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G732" t="n">
-        <v>21.7313957214355</v>
+        <v>21.7313919067383</v>
       </c>
       <c r="H732" t="n">
         <v>4585</v>
@@ -21626,7 +21626,7 @@
         <v>24</v>
       </c>
       <c r="G733" t="n">
-        <v>21.8223209381104</v>
+        <v>21.8223190307617</v>
       </c>
       <c r="H733" t="n">
         <v>698</v>
@@ -21684,7 +21684,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H735" t="n">
         <v>5515</v>
@@ -21800,7 +21800,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H739" t="n">
         <v>7641</v>
@@ -21916,7 +21916,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>20.5493507385254</v>
+        <v>20.549352645874</v>
       </c>
       <c r="H743" t="n">
         <v>3875</v>
@@ -22148,7 +22148,7 @@
         <v>24</v>
       </c>
       <c r="G751" t="n">
-        <v>21.8223209381104</v>
+        <v>21.8223190307617</v>
       </c>
       <c r="H751" t="n">
         <v>3728</v>
@@ -22177,7 +22177,7 @@
         <v>24</v>
       </c>
       <c r="G752" t="n">
-        <v>21.8223209381104</v>
+        <v>21.8223190307617</v>
       </c>
       <c r="H752" t="n">
         <v>3094</v>
@@ -22206,7 +22206,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>22.0041770935059</v>
+        <v>22.0041751861572</v>
       </c>
       <c r="H753" t="n">
         <v>2888</v>
@@ -22235,7 +22235,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>21.7313957214355</v>
+        <v>21.7313919067383</v>
       </c>
       <c r="H754" t="n">
         <v>1943</v>
@@ -22264,7 +22264,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>21.7313957214355</v>
+        <v>21.7313919067383</v>
       </c>
       <c r="H755" t="n">
         <v>912</v>
@@ -22380,7 +22380,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H759" t="n">
         <v>1830</v>
@@ -22438,7 +22438,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G761" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H761" t="n">
         <v>2011</v>
@@ -22467,7 +22467,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H762" t="n">
         <v>383</v>
@@ -22583,7 +22583,7 @@
         <v>23</v>
       </c>
       <c r="G766" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H766" t="n">
         <v>1718</v>
@@ -22699,7 +22699,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>21.0949115753174</v>
+        <v>21.0949096679688</v>
       </c>
       <c r="H770" t="n">
         <v>305</v>
@@ -22757,7 +22757,7 @@
         <v>23</v>
       </c>
       <c r="G772" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H772" t="n">
         <v>843</v>
@@ -22786,7 +22786,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>21.0949115753174</v>
+        <v>21.0949096679688</v>
       </c>
       <c r="H773" t="n">
         <v>688</v>
@@ -22815,7 +22815,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>21.0949115753174</v>
+        <v>21.0949096679688</v>
       </c>
       <c r="H774" t="n">
         <v>881</v>
@@ -22960,7 +22960,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>21.5495414733887</v>
+        <v>21.5495452880859</v>
       </c>
       <c r="H779" t="n">
         <v>4210</v>
@@ -23047,7 +23047,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>21.0949115753174</v>
+        <v>21.0949096679688</v>
       </c>
       <c r="H782" t="n">
         <v>424</v>
@@ -23105,7 +23105,7 @@
         <v>23</v>
       </c>
       <c r="G784" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H784" t="n">
         <v>1187</v>
@@ -23134,7 +23134,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>20.7312068939209</v>
+        <v>20.7312030792236</v>
       </c>
       <c r="H785" t="n">
         <v>294</v>
@@ -23279,7 +23279,7 @@
         <v>23</v>
       </c>
       <c r="G790" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H790" t="n">
         <v>1960</v>
@@ -23308,7 +23308,7 @@
         <v>23</v>
       </c>
       <c r="G791" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H791" t="n">
         <v>417</v>
@@ -23337,7 +23337,7 @@
         <v>23</v>
       </c>
       <c r="G792" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H792" t="n">
         <v>14773</v>
@@ -23366,7 +23366,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H793" t="n">
         <v>1759</v>
@@ -23395,7 +23395,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H794" t="n">
         <v>1332</v>
@@ -23424,7 +23424,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>20.5493507385254</v>
+        <v>20.549352645874</v>
       </c>
       <c r="H795" t="n">
         <v>869</v>
@@ -23453,7 +23453,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G796" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H796" t="n">
         <v>628</v>
@@ -23482,7 +23482,7 @@
         <v>23</v>
       </c>
       <c r="G797" t="n">
-        <v>20.9130573272705</v>
+        <v>20.9130592346191</v>
       </c>
       <c r="H797" t="n">
         <v>710</v>
@@ -23540,7 +23540,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>20.6402778625488</v>
+        <v>20.6402797698975</v>
       </c>
       <c r="H799" t="n">
         <v>1250</v>
@@ -23569,7 +23569,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G800" t="n">
-        <v>20.5493507385254</v>
+        <v>20.549352645874</v>
       </c>
       <c r="H800" t="n">
         <v>7793</v>
@@ -23627,7 +23627,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>22.0041770935059</v>
+        <v>22.0041751861572</v>
       </c>
       <c r="H802" t="n">
         <v>30806</v>
@@ -23656,7 +23656,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>22.1860275268555</v>
+        <v>22.1860256195068</v>
       </c>
       <c r="H803" t="n">
         <v>3814</v>
@@ -23685,7 +23685,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G804" t="n">
-        <v>22.3678817749023</v>
+        <v>22.3678798675537</v>
       </c>
       <c r="H804" t="n">
         <v>9325</v>
@@ -23714,7 +23714,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>23.5499210357666</v>
+        <v>23.5499248504639</v>
       </c>
       <c r="H805" t="n">
         <v>15078</v>
@@ -23743,7 +23743,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>22.9134407043457</v>
+        <v>22.9134387969971</v>
       </c>
       <c r="H806" t="n">
         <v>5503</v>
@@ -23772,7 +23772,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.5501098632812</v>
+        <v>24.5501136779785</v>
       </c>
       <c r="H807" t="n">
         <v>16372</v>
@@ -23801,7 +23801,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>24.0045509338379</v>
+        <v>24.0045528411865</v>
       </c>
       <c r="H808" t="n">
         <v>10233</v>
@@ -23830,7 +23830,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>23.095287322998</v>
+        <v>23.0952911376953</v>
       </c>
       <c r="H809" t="n">
         <v>248720</v>
@@ -23859,7 +23859,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>23.368070602417</v>
+        <v>23.3680686950684</v>
       </c>
       <c r="H810" t="n">
         <v>2600</v>
@@ -23888,7 +23888,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>24.0045509338379</v>
+        <v>24.0045528411865</v>
       </c>
       <c r="H811" t="n">
         <v>3875</v>
@@ -23917,7 +23917,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>24.4591865539551</v>
+        <v>24.4591827392578</v>
       </c>
       <c r="H812" t="n">
         <v>2196</v>
@@ -23946,7 +23946,7 @@
         <v>26.5</v>
       </c>
       <c r="G813" t="n">
-        <v>24.09547996521</v>
+        <v>24.0954780578613</v>
       </c>
       <c r="H813" t="n">
         <v>742</v>
@@ -23975,7 +23975,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>24.2773323059082</v>
+        <v>24.2773342132568</v>
       </c>
       <c r="H814" t="n">
         <v>1094</v>
@@ -24004,7 +24004,7 @@
         <v>26.5</v>
       </c>
       <c r="G815" t="n">
-        <v>24.09547996521</v>
+        <v>24.0954780578613</v>
       </c>
       <c r="H815" t="n">
         <v>1378</v>
@@ -24033,7 +24033,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7319660186768</v>
+        <v>24.7319641113281</v>
       </c>
       <c r="H816" t="n">
         <v>19373</v>
@@ -24062,7 +24062,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.9138164520264</v>
+        <v>24.913818359375</v>
       </c>
       <c r="H817" t="n">
         <v>5600</v>
@@ -24091,7 +24091,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.9138164520264</v>
+        <v>24.913818359375</v>
       </c>
       <c r="H818" t="n">
         <v>1123</v>
@@ -24120,7 +24120,7 @@
         <v>27.5</v>
       </c>
       <c r="G819" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H819" t="n">
         <v>12457</v>
@@ -24149,7 +24149,7 @@
         <v>28</v>
       </c>
       <c r="G820" t="n">
-        <v>25.4593753814697</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H820" t="n">
         <v>21274</v>
@@ -24178,7 +24178,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>26.0049343109131</v>
+        <v>26.0049324035645</v>
       </c>
       <c r="H821" t="n">
         <v>17472</v>
@@ -24207,7 +24207,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>26.0958576202393</v>
+        <v>26.0958595275879</v>
       </c>
       <c r="H822" t="n">
         <v>12698</v>
@@ -24236,7 +24236,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>26.0958576202393</v>
+        <v>26.0958595275879</v>
       </c>
       <c r="H823" t="n">
         <v>9499</v>
@@ -24265,7 +24265,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>25.2775211334229</v>
+        <v>25.2775230407715</v>
       </c>
       <c r="H824" t="n">
         <v>9201</v>
@@ -24294,7 +24294,7 @@
         <v>27.5</v>
       </c>
       <c r="G825" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H825" t="n">
         <v>7361</v>
@@ -24323,7 +24323,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G826" t="n">
-        <v>24.8228893280029</v>
+        <v>24.8228874206543</v>
       </c>
       <c r="H826" t="n">
         <v>3821</v>
@@ -24352,7 +24352,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>24.8228893280029</v>
+        <v>24.8228874206543</v>
       </c>
       <c r="H827" t="n">
         <v>2515</v>
@@ -24381,7 +24381,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>24.8228893280029</v>
+        <v>24.8228874206543</v>
       </c>
       <c r="H828" t="n">
         <v>2875</v>
@@ -24410,7 +24410,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>24.9138164520264</v>
+        <v>24.913818359375</v>
       </c>
       <c r="H829" t="n">
         <v>1504</v>
@@ -24439,7 +24439,7 @@
         <v>27.5</v>
       </c>
       <c r="G830" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H830" t="n">
         <v>3462</v>
@@ -24497,7 +24497,7 @@
         <v>27</v>
       </c>
       <c r="G832" t="n">
-        <v>24.5501098632812</v>
+        <v>24.5501136779785</v>
       </c>
       <c r="H832" t="n">
         <v>462</v>
@@ -24526,7 +24526,7 @@
         <v>26</v>
       </c>
       <c r="G833" t="n">
-        <v>23.6408462524414</v>
+        <v>23.64084815979</v>
       </c>
       <c r="H833" t="n">
         <v>7174</v>
@@ -24584,7 +24584,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>24.2773323059082</v>
+        <v>24.2773342132568</v>
       </c>
       <c r="H835" t="n">
         <v>942</v>
@@ -24613,7 +24613,7 @@
         <v>27.5</v>
       </c>
       <c r="G836" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H836" t="n">
         <v>3180</v>
@@ -24671,7 +24671,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G838" t="n">
-        <v>26.0049343109131</v>
+        <v>26.0049324035645</v>
       </c>
       <c r="H838" t="n">
         <v>8817</v>
@@ -24729,7 +24729,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5503005981445</v>
       </c>
       <c r="H840" t="n">
         <v>1023</v>
@@ -24787,7 +24787,7 @@
         <v>28</v>
       </c>
       <c r="G842" t="n">
-        <v>25.4593753814697</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H842" t="n">
         <v>1789</v>
@@ -24816,7 +24816,7 @@
         <v>28</v>
       </c>
       <c r="G843" t="n">
-        <v>25.4593753814697</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H843" t="n">
         <v>5435</v>
@@ -24845,7 +24845,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>26.1867847442627</v>
+        <v>26.1867828369141</v>
       </c>
       <c r="H844" t="n">
         <v>4971</v>
@@ -24874,7 +24874,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>26.2777099609375</v>
+        <v>26.2777137756348</v>
       </c>
       <c r="H845" t="n">
         <v>4924</v>
@@ -24903,7 +24903,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>26.2777099609375</v>
+        <v>26.2777137756348</v>
       </c>
       <c r="H846" t="n">
         <v>2260</v>
@@ -24932,7 +24932,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G847" t="n">
-        <v>26.0958576202393</v>
+        <v>26.0958595275879</v>
       </c>
       <c r="H847" t="n">
         <v>1305</v>
@@ -25019,7 +25019,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5503005981445</v>
       </c>
       <c r="H850" t="n">
         <v>4390</v>
@@ -25048,7 +25048,7 @@
         <v>28</v>
       </c>
       <c r="G851" t="n">
-        <v>25.4593753814697</v>
+        <v>25.4593734741211</v>
       </c>
       <c r="H851" t="n">
         <v>3647</v>
@@ -25077,7 +25077,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>25.5503025054932</v>
+        <v>25.5503005981445</v>
       </c>
       <c r="H852" t="n">
         <v>2971</v>
@@ -25106,7 +25106,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>26.1867847442627</v>
+        <v>26.1867828369141</v>
       </c>
       <c r="H853" t="n">
         <v>2676</v>
@@ -25164,7 +25164,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>26.0049343109131</v>
+        <v>26.0049324035645</v>
       </c>
       <c r="H855" t="n">
         <v>2338</v>
@@ -25251,7 +25251,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>28.0053100585938</v>
+        <v>28.0053119659424</v>
       </c>
       <c r="H858" t="n">
         <v>16337</v>
@@ -25338,7 +25338,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G861" t="n">
-        <v>30.2784690856934</v>
+        <v>30.278470993042</v>
       </c>
       <c r="H861" t="n">
         <v>13365</v>
@@ -25396,7 +25396,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>29.6419830322266</v>
+        <v>29.6419849395752</v>
       </c>
       <c r="H863" t="n">
         <v>5110</v>
@@ -25425,7 +25425,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G864" t="n">
-        <v>29.9147663116455</v>
+        <v>29.9147682189941</v>
       </c>
       <c r="H864" t="n">
         <v>1831</v>
@@ -25454,7 +25454,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>30.6421794891357</v>
+        <v>30.6421775817871</v>
       </c>
       <c r="H865" t="n">
         <v>13129</v>
@@ -25483,7 +25483,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G866" t="n">
-        <v>31.7332992553711</v>
+        <v>31.7332878112793</v>
       </c>
       <c r="H866" t="n">
         <v>25815</v>
@@ -25512,7 +25512,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>31.1877307891846</v>
+        <v>31.1877403259277</v>
       </c>
       <c r="H867" t="n">
         <v>9130</v>
@@ -25541,7 +25541,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>31.7332992553711</v>
+        <v>31.7332878112793</v>
       </c>
       <c r="H868" t="n">
         <v>10584</v>
@@ -25570,7 +25570,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>32.0060729980469</v>
+        <v>32.0060691833496</v>
       </c>
       <c r="H869" t="n">
         <v>47310</v>
@@ -25599,7 +25599,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>33.9155197143555</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H870" t="n">
         <v>18083</v>
@@ -25657,7 +25657,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>35.643123626709</v>
+        <v>35.6431312561035</v>
       </c>
       <c r="H872" t="n">
         <v>23146</v>
@@ -25686,7 +25686,7 @@
         <v>40</v>
       </c>
       <c r="G873" t="n">
-        <v>36.3705368041992</v>
+        <v>36.3705406188965</v>
       </c>
       <c r="H873" t="n">
         <v>15350</v>
@@ -25715,7 +25715,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G874" t="n">
-        <v>36.0068321228027</v>
+        <v>36.0068244934082</v>
       </c>
       <c r="H874" t="n">
         <v>13085</v>
@@ -25744,7 +25744,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>35.5521926879883</v>
+        <v>35.5521965026855</v>
       </c>
       <c r="H875" t="n">
         <v>8378</v>
@@ -25802,7 +25802,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G877" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H877" t="n">
         <v>17056</v>
@@ -25831,7 +25831,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G878" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H878" t="n">
         <v>9962</v>
@@ -25860,7 +25860,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>35.1884956359863</v>
+        <v>35.1884918212891</v>
       </c>
       <c r="H879" t="n">
         <v>1363</v>
@@ -25889,7 +25889,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>34.7338600158691</v>
+        <v>34.7338638305664</v>
       </c>
       <c r="H880" t="n">
         <v>5049</v>
@@ -25918,7 +25918,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H881" t="n">
         <v>3852</v>
@@ -26005,7 +26005,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>34.8247833251953</v>
+        <v>34.8247909545898</v>
       </c>
       <c r="H884" t="n">
         <v>7646</v>
@@ -26034,7 +26034,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G885" t="n">
-        <v>34.7338600158691</v>
+        <v>34.7338638305664</v>
       </c>
       <c r="H885" t="n">
         <v>3396</v>
@@ -26150,7 +26150,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>34.8247833251953</v>
+        <v>34.8247909545898</v>
       </c>
       <c r="H889" t="n">
         <v>3085</v>
@@ -26208,7 +26208,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H891" t="n">
         <v>8405</v>
@@ -26237,7 +26237,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>33.5518264770508</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H892" t="n">
         <v>6935</v>
@@ -26295,7 +26295,7 @@
         <v>37</v>
       </c>
       <c r="G894" t="n">
-        <v>33.6427459716797</v>
+        <v>33.642749786377</v>
       </c>
       <c r="H894" t="n">
         <v>6046</v>
@@ -26382,7 +26382,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H897" t="n">
         <v>2274</v>
@@ -26469,7 +26469,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G900" t="n">
-        <v>33.0971870422363</v>
+        <v>33.0971832275391</v>
       </c>
       <c r="H900" t="n">
         <v>10732</v>
@@ -26498,7 +26498,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G901" t="n">
-        <v>32.8244094848633</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H901" t="n">
         <v>8762</v>
@@ -26527,7 +26527,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>33.8245964050293</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H902" t="n">
         <v>30124</v>
@@ -26585,7 +26585,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H904" t="n">
         <v>11103</v>
@@ -26614,7 +26614,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>33.9155197143555</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H905" t="n">
         <v>8882</v>
@@ -26672,7 +26672,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G907" t="n">
-        <v>34.915714263916</v>
+        <v>34.9157180786133</v>
       </c>
       <c r="H907" t="n">
         <v>10279</v>
@@ -26701,7 +26701,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>34.8247833251953</v>
+        <v>34.8247909545898</v>
       </c>
       <c r="H908" t="n">
         <v>5104</v>
@@ -26875,7 +26875,7 @@
         <v>37</v>
       </c>
       <c r="G914" t="n">
-        <v>33.6427459716797</v>
+        <v>33.642749786377</v>
       </c>
       <c r="H914" t="n">
         <v>4087</v>
@@ -26904,7 +26904,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G915" t="n">
-        <v>32.8244094848633</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H915" t="n">
         <v>5242</v>
@@ -26933,7 +26933,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>32.9153366088867</v>
+        <v>32.9153327941895</v>
       </c>
       <c r="H916" t="n">
         <v>5400</v>
@@ -26962,7 +26962,7 @@
         <v>37</v>
       </c>
       <c r="G917" t="n">
-        <v>33.6427459716797</v>
+        <v>33.642749786377</v>
       </c>
       <c r="H917" t="n">
         <v>3855</v>
@@ -26991,7 +26991,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.5518264770508</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H918" t="n">
         <v>1642</v>
@@ -27020,7 +27020,7 @@
         <v>36.5</v>
       </c>
       <c r="G919" t="n">
-        <v>33.188117980957</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H919" t="n">
         <v>1912</v>
@@ -27049,7 +27049,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G920" t="n">
-        <v>33.0062599182129</v>
+        <v>33.0062561035156</v>
       </c>
       <c r="H920" t="n">
         <v>1008</v>
@@ -27078,7 +27078,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G921" t="n">
-        <v>32.9153366088867</v>
+        <v>32.9153327941895</v>
       </c>
       <c r="H921" t="n">
         <v>160</v>
@@ -27107,7 +27107,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>33.5518264770508</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H922" t="n">
         <v>3813</v>
@@ -27136,7 +27136,7 @@
         <v>36.5</v>
       </c>
       <c r="G923" t="n">
-        <v>33.188117980957</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H923" t="n">
         <v>1171</v>
@@ -27165,7 +27165,7 @@
         <v>36.5</v>
       </c>
       <c r="G924" t="n">
-        <v>33.188117980957</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H924" t="n">
         <v>233</v>
@@ -27223,7 +27223,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>33.0062599182129</v>
+        <v>33.0062561035156</v>
       </c>
       <c r="H926" t="n">
         <v>3948</v>
@@ -27310,7 +27310,7 @@
         <v>36</v>
       </c>
       <c r="G929" t="n">
-        <v>32.7334861755371</v>
+        <v>32.7334823608398</v>
       </c>
       <c r="H929" t="n">
         <v>4169</v>
@@ -27339,7 +27339,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.5518264770508</v>
+        <v>33.5518226623535</v>
       </c>
       <c r="H930" t="n">
         <v>13794</v>
@@ -27397,7 +27397,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>35.2794189453125</v>
+        <v>35.2794151306152</v>
       </c>
       <c r="H932" t="n">
         <v>8467</v>
@@ -27455,7 +27455,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>33.9155197143555</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H934" t="n">
         <v>5593</v>
@@ -27484,7 +27484,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H935" t="n">
         <v>3269</v>
@@ -27542,7 +27542,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G937" t="n">
-        <v>33.8245964050293</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H937" t="n">
         <v>43211</v>
@@ -27571,7 +27571,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>33.8245964050293</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H938" t="n">
         <v>1429</v>
@@ -27658,7 +27658,7 @@
         <v>37</v>
       </c>
       <c r="G941" t="n">
-        <v>33.6427459716797</v>
+        <v>33.642749786377</v>
       </c>
       <c r="H941" t="n">
         <v>2299</v>
@@ -27687,7 +27687,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.9155197143555</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H942" t="n">
         <v>7615</v>
@@ -27716,7 +27716,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G943" t="n">
-        <v>34.0064506530762</v>
+        <v>34.0064468383789</v>
       </c>
       <c r="H943" t="n">
         <v>5713</v>
@@ -27774,7 +27774,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G945" t="n">
-        <v>34.3701515197754</v>
+        <v>34.3701553344727</v>
       </c>
       <c r="H945" t="n">
         <v>3459</v>
@@ -27803,7 +27803,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>33.9155197143555</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H946" t="n">
         <v>1543</v>
@@ -27861,7 +27861,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G948" t="n">
-        <v>33.9155197143555</v>
+        <v>33.9155235290527</v>
       </c>
       <c r="H948" t="n">
         <v>1091</v>
@@ -27948,7 +27948,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G951" t="n">
-        <v>32.8244094848633</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H951" t="n">
         <v>6258</v>
@@ -27977,7 +27977,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>32.8244094848633</v>
+        <v>32.824405670166</v>
       </c>
       <c r="H952" t="n">
         <v>2522</v>
@@ -28006,7 +28006,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G953" t="n">
-        <v>33.8245964050293</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H953" t="n">
         <v>3746</v>
@@ -28122,7 +28122,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>33.8245964050293</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H957" t="n">
         <v>3272</v>
@@ -28151,7 +28151,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G958" t="n">
-        <v>33.8245964050293</v>
+        <v>33.8246002197266</v>
       </c>
       <c r="H958" t="n">
         <v>2088</v>
@@ -28325,7 +28325,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G964" t="n">
-        <v>34.6370735168457</v>
+        <v>34.6370697021484</v>
       </c>
       <c r="H964" t="n">
         <v>18984</v>
@@ -28383,7 +28383,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G966" t="n">
-        <v>34.174015045166</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H966" t="n">
         <v>4232</v>
@@ -28412,7 +28412,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>34.174015045166</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H967" t="n">
         <v>5406</v>
@@ -28441,7 +28441,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G968" t="n">
-        <v>33.896167755127</v>
+        <v>33.8961715698242</v>
       </c>
       <c r="H968" t="n">
         <v>11032</v>
@@ -28499,7 +28499,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G970" t="n">
-        <v>33.9887847900391</v>
+        <v>33.9887886047363</v>
       </c>
       <c r="H970" t="n">
         <v>2687</v>
@@ -28528,7 +28528,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G971" t="n">
-        <v>34.174015045166</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H971" t="n">
         <v>1501</v>
@@ -28557,7 +28557,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G972" t="n">
-        <v>33.9887847900391</v>
+        <v>33.9887886047363</v>
       </c>
       <c r="H972" t="n">
         <v>778</v>
@@ -28789,7 +28789,7 @@
         <v>36</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3404998779297</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H980" t="n">
         <v>3550</v>
@@ -28818,7 +28818,7 @@
         <v>36</v>
       </c>
       <c r="G981" t="n">
-        <v>33.3404998779297</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H981" t="n">
         <v>8066</v>
@@ -28963,7 +28963,7 @@
         <v>39</v>
       </c>
       <c r="G986" t="n">
-        <v>36.1188735961914</v>
+        <v>36.1188697814941</v>
       </c>
       <c r="H986" t="n">
         <v>41483</v>
@@ -29021,7 +29021,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G988" t="n">
-        <v>39.1750869750977</v>
+        <v>39.1750831604004</v>
       </c>
       <c r="H988" t="n">
         <v>28013</v>
@@ -29079,7 +29079,7 @@
         <v>46.5</v>
       </c>
       <c r="G990" t="n">
-        <v>43.0648078918457</v>
+        <v>43.064811706543</v>
       </c>
       <c r="H990" t="n">
         <v>36955</v>
@@ -29108,7 +29108,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>42.2313003540039</v>
+        <v>42.2312927246094</v>
       </c>
       <c r="H991" t="n">
         <v>8761</v>
@@ -29137,7 +29137,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>41.5830078125</v>
+        <v>41.5830154418945</v>
       </c>
       <c r="H992" t="n">
         <v>7185</v>
@@ -29166,7 +29166,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>41.9534606933594</v>
+        <v>41.9534568786621</v>
       </c>
       <c r="H993" t="n">
         <v>15219</v>
@@ -29195,7 +29195,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G994" t="n">
-        <v>42.4165191650391</v>
+        <v>42.4165229797363</v>
       </c>
       <c r="H994" t="n">
         <v>28173</v>
@@ -29224,7 +29224,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>44.3613815307617</v>
+        <v>44.361385345459</v>
       </c>
       <c r="H995" t="n">
         <v>45209</v>
@@ -29282,7 +29282,7 @@
         <v>48.9000015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>45.2875061035156</v>
+        <v>45.2875022888184</v>
       </c>
       <c r="H997" t="n">
         <v>23201</v>
@@ -29398,7 +29398,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1001" t="n">
-        <v>46.121021270752</v>
+        <v>46.1210250854492</v>
       </c>
       <c r="H1001" t="n">
         <v>19411</v>
@@ -29485,7 +29485,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G1004" t="n">
-        <v>45.194896697998</v>
+        <v>45.1948928833008</v>
       </c>
       <c r="H1004" t="n">
         <v>7319</v>
@@ -29514,7 +29514,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>46.121021270752</v>
+        <v>46.1210250854492</v>
       </c>
       <c r="H1005" t="n">
         <v>7713</v>
@@ -29543,7 +29543,7 @@
         <v>51</v>
       </c>
       <c r="G1006" t="n">
-        <v>47.2323722839355</v>
+        <v>47.2323684692383</v>
       </c>
       <c r="H1006" t="n">
         <v>15076</v>
@@ -29601,7 +29601,7 @@
         <v>50</v>
       </c>
       <c r="G1008" t="n">
-        <v>46.3062438964844</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1008" t="n">
         <v>9494</v>
@@ -29659,7 +29659,7 @@
         <v>50</v>
       </c>
       <c r="G1010" t="n">
-        <v>46.3062438964844</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1010" t="n">
         <v>4334</v>
@@ -29688,7 +29688,7 @@
         <v>50</v>
       </c>
       <c r="G1011" t="n">
-        <v>46.3062438964844</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1011" t="n">
         <v>9263</v>
@@ -29717,7 +29717,7 @@
         <v>49</v>
       </c>
       <c r="G1012" t="n">
-        <v>45.3801193237305</v>
+        <v>45.3801231384277</v>
       </c>
       <c r="H1012" t="n">
         <v>9197</v>
@@ -29775,7 +29775,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>46.121021270752</v>
+        <v>46.1210250854492</v>
       </c>
       <c r="H1014" t="n">
         <v>2874</v>
@@ -29949,7 +29949,7 @@
         <v>50</v>
       </c>
       <c r="G1020" t="n">
-        <v>46.3062438964844</v>
+        <v>46.3062477111816</v>
       </c>
       <c r="H1020" t="n">
         <v>4229</v>
@@ -30007,7 +30007,7 @@
         <v>52</v>
       </c>
       <c r="G1022" t="n">
-        <v>48.1584930419922</v>
+        <v>48.1584968566895</v>
       </c>
       <c r="H1022" t="n">
         <v>9300</v>
@@ -30036,7 +30036,7 @@
         <v>54</v>
       </c>
       <c r="G1023" t="n">
-        <v>50.0107421875</v>
+        <v>50.0107460021973</v>
       </c>
       <c r="H1023" t="n">
         <v>11513</v>
@@ -30065,7 +30065,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>48.8993911743164</v>
+        <v>48.8993949890137</v>
       </c>
       <c r="H1024" t="n">
         <v>7243</v>
@@ -30268,7 +30268,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>58.1606407165527</v>
+        <v>58.16064453125</v>
       </c>
       <c r="H1031" t="n">
         <v>5992</v>
@@ -30297,7 +30297,7 @@
         <v>62</v>
       </c>
       <c r="G1032" t="n">
-        <v>57.419750213623</v>
+        <v>57.4197425842285</v>
       </c>
       <c r="H1032" t="n">
         <v>5899</v>
@@ -30326,7 +30326,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492973327637</v>
       </c>
       <c r="H1033" t="n">
         <v>6666</v>
@@ -30355,7 +30355,7 @@
         <v>62</v>
       </c>
       <c r="G1034" t="n">
-        <v>57.419750213623</v>
+        <v>57.4197425842285</v>
       </c>
       <c r="H1034" t="n">
         <v>2445</v>
@@ -30413,7 +30413,7 @@
         <v>61</v>
       </c>
       <c r="G1036" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1036" t="n">
         <v>5963</v>
@@ -30471,7 +30471,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1038" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492973327637</v>
       </c>
       <c r="H1038" t="n">
         <v>7252</v>
@@ -30500,7 +30500,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>55.0118179321289</v>
+        <v>55.0118217468262</v>
       </c>
       <c r="H1039" t="n">
         <v>13841</v>
@@ -30529,7 +30529,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>56.3083915710449</v>
+        <v>56.3083953857422</v>
       </c>
       <c r="H1040" t="n">
         <v>5631</v>
@@ -30558,7 +30558,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1041" t="n">
-        <v>56.8640747070312</v>
+        <v>56.864070892334</v>
       </c>
       <c r="H1041" t="n">
         <v>4396</v>
@@ -30587,7 +30587,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>59.6424446105957</v>
+        <v>59.642448425293</v>
       </c>
       <c r="H1042" t="n">
         <v>52827</v>
@@ -30616,7 +30616,7 @@
         <v>65</v>
       </c>
       <c r="G1043" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1043" t="n">
         <v>9419</v>
@@ -30645,7 +30645,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1044" t="n">
-        <v>60.0129013061523</v>
+        <v>60.0128974914551</v>
       </c>
       <c r="H1044" t="n">
         <v>8170</v>
@@ -30674,7 +30674,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>59.8276672363281</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1045" t="n">
         <v>7081</v>
@@ -30703,7 +30703,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>60.753791809082</v>
+        <v>60.7537956237793</v>
       </c>
       <c r="H1046" t="n">
         <v>21992</v>
@@ -30732,7 +30732,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1047" t="n">
-        <v>62.7912788391113</v>
+        <v>62.7912712097168</v>
       </c>
       <c r="H1047" t="n">
         <v>20312</v>
@@ -30761,7 +30761,7 @@
         <v>71</v>
       </c>
       <c r="G1048" t="n">
-        <v>65.7548751831055</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1048" t="n">
         <v>33718</v>
@@ -30790,7 +30790,7 @@
         <v>71</v>
       </c>
       <c r="G1049" t="n">
-        <v>65.7548751831055</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1049" t="n">
         <v>27056</v>
@@ -30819,7 +30819,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>65.1991958618164</v>
+        <v>65.1991882324219</v>
       </c>
       <c r="H1050" t="n">
         <v>20635</v>
@@ -30848,7 +30848,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1051" t="n">
-        <v>65.1991958618164</v>
+        <v>65.1991882324219</v>
       </c>
       <c r="H1051" t="n">
         <v>16230</v>
@@ -30906,7 +30906,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>65.1991958618164</v>
+        <v>65.1991882324219</v>
       </c>
       <c r="H1053" t="n">
         <v>9328</v>
@@ -30964,7 +30964,7 @@
         <v>68.5999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>63.5321617126465</v>
+        <v>63.5321769714355</v>
       </c>
       <c r="H1055" t="n">
         <v>12535</v>
@@ -30993,7 +30993,7 @@
         <v>66</v>
       </c>
       <c r="G1056" t="n">
-        <v>61.1242523193359</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1056" t="n">
         <v>24459</v>
@@ -31022,7 +31022,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1057" t="n">
         <v>8167</v>
@@ -31051,7 +31051,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1058" t="n">
         <v>7589</v>
@@ -31080,7 +31080,7 @@
         <v>69</v>
       </c>
       <c r="G1059" t="n">
-        <v>63.9026107788086</v>
+        <v>63.9026222229004</v>
       </c>
       <c r="H1059" t="n">
         <v>24805</v>
@@ -31109,7 +31109,7 @@
         <v>67</v>
       </c>
       <c r="G1060" t="n">
-        <v>62.0503616333008</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1060" t="n">
         <v>10940</v>
@@ -31196,7 +31196,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>61.4946899414062</v>
+        <v>61.4946937561035</v>
       </c>
       <c r="H1063" t="n">
         <v>4540</v>
@@ -31225,7 +31225,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1064" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1064" t="n">
         <v>7255</v>
@@ -31254,7 +31254,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>60.5685729980469</v>
+        <v>60.5685691833496</v>
       </c>
       <c r="H1065" t="n">
         <v>10994</v>
@@ -31283,7 +31283,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1066" t="n">
-        <v>58.1606407165527</v>
+        <v>58.16064453125</v>
       </c>
       <c r="H1066" t="n">
         <v>16555</v>
@@ -31312,7 +31312,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1067" t="n">
         <v>5930</v>
@@ -31370,7 +31370,7 @@
         <v>61</v>
       </c>
       <c r="G1069" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1069" t="n">
         <v>6987</v>
@@ -31399,7 +31399,7 @@
         <v>63</v>
       </c>
       <c r="G1070" t="n">
-        <v>58.3458709716797</v>
+        <v>58.345874786377</v>
       </c>
       <c r="H1070" t="n">
         <v>25088</v>
@@ -31428,7 +31428,7 @@
         <v>64</v>
       </c>
       <c r="G1071" t="n">
-        <v>59.2719955444336</v>
+        <v>59.2719917297363</v>
       </c>
       <c r="H1071" t="n">
         <v>19842</v>
@@ -31457,7 +31457,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1072" t="n">
-        <v>57.9754219055176</v>
+        <v>57.975414276123</v>
       </c>
       <c r="H1072" t="n">
         <v>11411</v>
@@ -31486,7 +31486,7 @@
         <v>62</v>
       </c>
       <c r="G1073" t="n">
-        <v>57.419750213623</v>
+        <v>57.4197425842285</v>
       </c>
       <c r="H1073" t="n">
         <v>5082</v>
@@ -31515,7 +31515,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>57.6049690246582</v>
+        <v>57.6049728393555</v>
       </c>
       <c r="H1074" t="n">
         <v>9173</v>
@@ -31544,7 +31544,7 @@
         <v>61.4000015258789</v>
       </c>
       <c r="G1075" t="n">
-        <v>56.8640747070312</v>
+        <v>56.864070892334</v>
       </c>
       <c r="H1075" t="n">
         <v>5753</v>
@@ -31602,7 +31602,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1077" t="n">
         <v>16965</v>
@@ -31631,7 +31631,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1078" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469505310059</v>
       </c>
       <c r="H1078" t="n">
         <v>26812</v>
@@ -31689,7 +31689,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1080" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469505310059</v>
       </c>
       <c r="H1080" t="n">
         <v>15561</v>
@@ -31718,7 +31718,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1081" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469505310059</v>
       </c>
       <c r="H1081" t="n">
         <v>12734</v>
@@ -31747,7 +31747,7 @@
         <v>69</v>
       </c>
       <c r="G1082" t="n">
-        <v>63.9026107788086</v>
+        <v>63.9026222229004</v>
       </c>
       <c r="H1082" t="n">
         <v>5155</v>
@@ -31805,7 +31805,7 @@
         <v>67</v>
       </c>
       <c r="G1084" t="n">
-        <v>62.0503616333008</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1084" t="n">
         <v>14476</v>
@@ -31834,7 +31834,7 @@
         <v>67</v>
       </c>
       <c r="G1085" t="n">
-        <v>62.0503616333008</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1085" t="n">
         <v>9085</v>
@@ -31863,7 +31863,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>62.7912788391113</v>
+        <v>62.7912712097168</v>
       </c>
       <c r="H1086" t="n">
         <v>23354</v>
@@ -31921,7 +31921,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1088" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469505310059</v>
       </c>
       <c r="H1088" t="n">
         <v>8142</v>
@@ -32008,7 +32008,7 @@
         <v>72</v>
       </c>
       <c r="G1091" t="n">
-        <v>66.6809997558594</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1091" t="n">
         <v>20242</v>
@@ -32037,7 +32037,7 @@
         <v>71</v>
       </c>
       <c r="G1092" t="n">
-        <v>65.7548751831055</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1092" t="n">
         <v>9074</v>
@@ -32095,7 +32095,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G1094" t="n">
-        <v>65.0139617919922</v>
+        <v>65.0139694213867</v>
       </c>
       <c r="H1094" t="n">
         <v>10097</v>
@@ -32124,7 +32124,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>65.5696487426758</v>
+        <v>65.5696563720703</v>
       </c>
       <c r="H1095" t="n">
         <v>9719</v>
@@ -32211,7 +32211,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1098" t="n">
-        <v>65.1991958618164</v>
+        <v>65.1991882324219</v>
       </c>
       <c r="H1098" t="n">
         <v>5246</v>
@@ -32240,7 +32240,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1099" t="n">
-        <v>65.5696487426758</v>
+        <v>65.5696563720703</v>
       </c>
       <c r="H1099" t="n">
         <v>22010</v>
@@ -32356,7 +32356,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G1103" t="n">
-        <v>65.0139617919922</v>
+        <v>65.0139694213867</v>
       </c>
       <c r="H1103" t="n">
         <v>9902</v>
@@ -32414,7 +32414,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1105" t="n">
-        <v>67.7923355102539</v>
+        <v>67.7923431396484</v>
       </c>
       <c r="H1105" t="n">
         <v>43163</v>
@@ -32472,7 +32472,7 @@
         <v>74</v>
       </c>
       <c r="G1107" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1107" t="n">
         <v>25256</v>
@@ -32530,7 +32530,7 @@
         <v>74</v>
       </c>
       <c r="G1109" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1109" t="n">
         <v>24390</v>
@@ -32588,7 +32588,7 @@
         <v>71</v>
       </c>
       <c r="G1111" t="n">
-        <v>65.7548751831055</v>
+        <v>65.7548675537109</v>
       </c>
       <c r="H1111" t="n">
         <v>110589</v>
@@ -32646,7 +32646,7 @@
         <v>74</v>
       </c>
       <c r="G1113" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1113" t="n">
         <v>10107</v>
@@ -32791,7 +32791,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1118" t="n">
-        <v>67.7923355102539</v>
+        <v>67.7923431396484</v>
       </c>
       <c r="H1118" t="n">
         <v>10546</v>
@@ -32849,7 +32849,7 @@
         <v>73.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>67.9775695800781</v>
+        <v>67.9775772094727</v>
       </c>
       <c r="H1120" t="n">
         <v>5221</v>
@@ -32936,7 +32936,7 @@
         <v>72</v>
       </c>
       <c r="G1123" t="n">
-        <v>66.6809997558594</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1123" t="n">
         <v>3823</v>
@@ -32994,7 +32994,7 @@
         <v>74</v>
       </c>
       <c r="G1125" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1125" t="n">
         <v>8495</v>
@@ -33081,7 +33081,7 @@
         <v>73.4000015258789</v>
       </c>
       <c r="G1128" t="n">
-        <v>67.9775695800781</v>
+        <v>67.9775772094727</v>
       </c>
       <c r="H1128" t="n">
         <v>1694</v>
@@ -33313,7 +33313,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>71.8672943115234</v>
+        <v>71.8672866821289</v>
       </c>
       <c r="H1136" t="n">
         <v>9339</v>
@@ -33342,7 +33342,7 @@
         <v>78</v>
       </c>
       <c r="G1137" t="n">
-        <v>72.2377471923828</v>
+        <v>72.2377395629883</v>
       </c>
       <c r="H1137" t="n">
         <v>8145</v>
@@ -33371,7 +33371,7 @@
         <v>73.8000030517578</v>
       </c>
       <c r="G1138" t="n">
-        <v>68.348030090332</v>
+        <v>68.3480224609375</v>
       </c>
       <c r="H1138" t="n">
         <v>13068</v>
@@ -33400,7 +33400,7 @@
         <v>74</v>
       </c>
       <c r="G1139" t="n">
-        <v>68.5332412719727</v>
+        <v>68.5332489013672</v>
       </c>
       <c r="H1139" t="n">
         <v>10084</v>
@@ -33545,7 +33545,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1144" t="n">
-        <v>63.3469429016113</v>
+        <v>63.3469505310059</v>
       </c>
       <c r="H1144" t="n">
         <v>8038</v>
@@ -33574,7 +33574,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1145" t="n">
-        <v>64.6435317993164</v>
+        <v>64.6435165405273</v>
       </c>
       <c r="H1145" t="n">
         <v>10235</v>
@@ -33603,7 +33603,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1146" t="n">
-        <v>65.1991958618164</v>
+        <v>65.1991882324219</v>
       </c>
       <c r="H1146" t="n">
         <v>9298</v>
@@ -33661,7 +33661,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1148" t="n">
-        <v>60.753791809082</v>
+        <v>60.7537956237793</v>
       </c>
       <c r="H1148" t="n">
         <v>15342</v>
@@ -33690,7 +33690,7 @@
         <v>67</v>
       </c>
       <c r="G1149" t="n">
-        <v>62.0503616333008</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1149" t="n">
         <v>9187</v>
@@ -33719,7 +33719,7 @@
         <v>66</v>
       </c>
       <c r="G1150" t="n">
-        <v>61.1242523193359</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1150" t="n">
         <v>10090</v>
@@ -33748,7 +33748,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1151" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1151" t="n">
         <v>3890</v>
@@ -33806,7 +33806,7 @@
         <v>66</v>
       </c>
       <c r="G1153" t="n">
-        <v>61.1242523193359</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1153" t="n">
         <v>7908</v>
@@ -33835,7 +33835,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1154" t="n">
-        <v>60.753791809082</v>
+        <v>60.7537956237793</v>
       </c>
       <c r="H1154" t="n">
         <v>13511</v>
@@ -33864,7 +33864,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>60.939022064209</v>
+        <v>60.9390258789062</v>
       </c>
       <c r="H1155" t="n">
         <v>10916</v>
@@ -33893,7 +33893,7 @@
         <v>66</v>
       </c>
       <c r="G1156" t="n">
-        <v>61.1242523193359</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1156" t="n">
         <v>6716</v>
@@ -33951,7 +33951,7 @@
         <v>65</v>
       </c>
       <c r="G1158" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1158" t="n">
         <v>10093</v>
@@ -34009,7 +34009,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>59.8276672363281</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1160" t="n">
         <v>5490</v>
@@ -34067,7 +34067,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1162" t="n">
-        <v>59.4572143554688</v>
+        <v>59.457218170166</v>
       </c>
       <c r="H1162" t="n">
         <v>7471</v>
@@ -34096,7 +34096,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>57.9754219055176</v>
+        <v>57.975414276123</v>
       </c>
       <c r="H1163" t="n">
         <v>9156</v>
@@ -34154,7 +34154,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1165" t="n">
         <v>6544</v>
@@ -34183,7 +34183,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1166" t="n">
-        <v>57.9754219055176</v>
+        <v>57.975414276123</v>
       </c>
       <c r="H1166" t="n">
         <v>11260</v>
@@ -34241,7 +34241,7 @@
         <v>63</v>
       </c>
       <c r="G1168" t="n">
-        <v>58.3458709716797</v>
+        <v>58.345874786377</v>
       </c>
       <c r="H1168" t="n">
         <v>7543</v>
@@ -34270,7 +34270,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492973327637</v>
       </c>
       <c r="H1169" t="n">
         <v>12328</v>
@@ -34299,7 +34299,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1170" t="n">
-        <v>56.3083915710449</v>
+        <v>56.3083953857422</v>
       </c>
       <c r="H1170" t="n">
         <v>7643</v>
@@ -34386,7 +34386,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>58.1606407165527</v>
+        <v>58.16064453125</v>
       </c>
       <c r="H1173" t="n">
         <v>12736</v>
@@ -34415,7 +34415,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1174" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492973327637</v>
       </c>
       <c r="H1174" t="n">
         <v>8061</v>
@@ -34560,7 +34560,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1179" t="n">
-        <v>51.3073196411133</v>
+        <v>51.307315826416</v>
       </c>
       <c r="H1179" t="n">
         <v>7235</v>
@@ -34589,7 +34589,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1180" t="n">
-        <v>53.3447952270508</v>
+        <v>53.3447914123535</v>
       </c>
       <c r="H1180" t="n">
         <v>8463</v>
@@ -34676,7 +34676,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492973327637</v>
       </c>
       <c r="H1183" t="n">
         <v>4645</v>
@@ -34705,7 +34705,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1184" t="n">
-        <v>55.3822708129883</v>
+        <v>55.382266998291</v>
       </c>
       <c r="H1184" t="n">
         <v>5635</v>
@@ -34734,7 +34734,7 @@
         <v>61</v>
       </c>
       <c r="G1185" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1185" t="n">
         <v>8219</v>
@@ -34763,7 +34763,7 @@
         <v>61</v>
       </c>
       <c r="G1186" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1186" t="n">
         <v>3492</v>
@@ -34821,7 +34821,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>60.5685729980469</v>
+        <v>60.5685691833496</v>
       </c>
       <c r="H1188" t="n">
         <v>18854</v>
@@ -34879,7 +34879,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1190" t="n">
-        <v>60.939022064209</v>
+        <v>60.9390258789062</v>
       </c>
       <c r="H1190" t="n">
         <v>5931</v>
@@ -34908,7 +34908,7 @@
         <v>65</v>
       </c>
       <c r="G1191" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1191" t="n">
         <v>8658</v>
@@ -34937,7 +34937,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1192" t="n">
-        <v>59.4572143554688</v>
+        <v>59.457218170166</v>
       </c>
       <c r="H1192" t="n">
         <v>4435</v>
@@ -34966,7 +34966,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1193" t="n">
-        <v>59.8276672363281</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1193" t="n">
         <v>2596</v>
@@ -34995,7 +34995,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1194" t="n">
-        <v>59.8276672363281</v>
+        <v>59.8276710510254</v>
       </c>
       <c r="H1194" t="n">
         <v>7145</v>
@@ -35053,7 +35053,7 @@
         <v>63</v>
       </c>
       <c r="G1196" t="n">
-        <v>58.3458709716797</v>
+        <v>58.345874786377</v>
       </c>
       <c r="H1196" t="n">
         <v>5314</v>
@@ -35111,7 +35111,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1198" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1198" t="n">
         <v>4906</v>
@@ -35140,7 +35140,7 @@
         <v>65</v>
       </c>
       <c r="G1199" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1199" t="n">
         <v>32409</v>
@@ -35169,7 +35169,7 @@
         <v>63.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>58.8089294433594</v>
+        <v>58.8089332580566</v>
       </c>
       <c r="H1200" t="n">
         <v>4442</v>
@@ -35198,7 +35198,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1201" t="n">
-        <v>60.0129013061523</v>
+        <v>60.0128974914551</v>
       </c>
       <c r="H1201" t="n">
         <v>8130</v>
@@ -35256,7 +35256,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>61.4946899414062</v>
+        <v>61.4946937561035</v>
       </c>
       <c r="H1203" t="n">
         <v>5708</v>
@@ -35343,7 +35343,7 @@
         <v>67</v>
       </c>
       <c r="G1206" t="n">
-        <v>62.0503616333008</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1206" t="n">
         <v>7404</v>
@@ -35372,7 +35372,7 @@
         <v>65</v>
       </c>
       <c r="G1207" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1207" t="n">
         <v>3155</v>
@@ -35401,7 +35401,7 @@
         <v>65</v>
       </c>
       <c r="G1208" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1208" t="n">
         <v>4312</v>
@@ -35430,7 +35430,7 @@
         <v>65</v>
       </c>
       <c r="G1209" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1209" t="n">
         <v>3029</v>
@@ -35459,7 +35459,7 @@
         <v>65</v>
       </c>
       <c r="G1210" t="n">
-        <v>60.1981163024902</v>
+        <v>60.1981201171875</v>
       </c>
       <c r="H1210" t="n">
         <v>3326</v>
@@ -35488,7 +35488,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1211" t="n">
-        <v>59.920280456543</v>
+        <v>59.9202766418457</v>
       </c>
       <c r="H1211" t="n">
         <v>3950</v>
@@ -35517,7 +35517,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>58.6237106323242</v>
+        <v>58.623706817627</v>
       </c>
       <c r="H1212" t="n">
         <v>5794</v>
@@ -35546,7 +35546,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>58.1606407165527</v>
+        <v>58.16064453125</v>
       </c>
       <c r="H1213" t="n">
         <v>4220</v>
@@ -35575,7 +35575,7 @@
         <v>63</v>
       </c>
       <c r="G1214" t="n">
-        <v>58.3458709716797</v>
+        <v>58.345874786377</v>
       </c>
       <c r="H1214" t="n">
         <v>4413</v>
@@ -35604,7 +35604,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1215" t="n">
-        <v>60.1055068969727</v>
+        <v>60.1055107116699</v>
       </c>
       <c r="H1215" t="n">
         <v>3849</v>
@@ -35633,7 +35633,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1216" t="n">
-        <v>60.6766967773438</v>
+        <v>60.6766929626465</v>
       </c>
       <c r="H1216" t="n">
         <v>4647</v>
@@ -35720,7 +35720,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>54.4966583251953</v>
+        <v>54.4966621398926</v>
       </c>
       <c r="H1219" t="n">
         <v>6610</v>
@@ -35749,7 +35749,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1220" t="n">
-        <v>51.5939140319824</v>
+        <v>51.5939178466797</v>
       </c>
       <c r="H1220" t="n">
         <v>9662</v>
@@ -35836,7 +35836,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1223" t="n">
         <v>8299</v>
@@ -35865,7 +35865,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1224" t="n">
-        <v>53.6539268493652</v>
+        <v>53.6539306640625</v>
       </c>
       <c r="H1224" t="n">
         <v>2530</v>
@@ -35923,7 +35923,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1226" t="n">
-        <v>56.5566749572754</v>
+        <v>56.5566711425781</v>
       </c>
       <c r="H1226" t="n">
         <v>5095</v>
@@ -36068,7 +36068,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1231" t="n">
-        <v>58.803955078125</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1231" t="n">
         <v>3054</v>
@@ -36097,7 +36097,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>57.8675880432129</v>
+        <v>57.8675842285156</v>
       </c>
       <c r="H1232" t="n">
         <v>2813</v>
@@ -36155,7 +36155,7 @@
         <v>62.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1234" t="n">
         <v>3018</v>
@@ -36213,7 +36213,7 @@
         <v>64</v>
       </c>
       <c r="G1236" t="n">
-        <v>59.9275932312012</v>
+        <v>59.9275970458984</v>
       </c>
       <c r="H1236" t="n">
         <v>3476</v>
@@ -36271,7 +36271,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1238" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1238" t="n">
         <v>8167</v>
@@ -36387,7 +36387,7 @@
         <v>62.5</v>
       </c>
       <c r="G1242" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1242" t="n">
         <v>2340</v>
@@ -36416,7 +36416,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1243" t="n">
-        <v>58.803955078125</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1243" t="n">
         <v>927</v>
@@ -36445,7 +36445,7 @@
         <v>61.5</v>
       </c>
       <c r="G1244" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1244" t="n">
         <v>3144</v>
@@ -36474,7 +36474,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>58.803955078125</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1245" t="n">
         <v>4530</v>
@@ -36561,7 +36561,7 @@
         <v>62</v>
       </c>
       <c r="G1248" t="n">
-        <v>58.0548629760742</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1248" t="n">
         <v>9034</v>
@@ -36677,7 +36677,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1252" t="n">
-        <v>55.9012107849121</v>
+        <v>55.9012145996094</v>
       </c>
       <c r="H1252" t="n">
         <v>2532</v>
@@ -36735,7 +36735,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1254" t="n">
-        <v>56.5566749572754</v>
+        <v>56.5566711425781</v>
       </c>
       <c r="H1254" t="n">
         <v>2202</v>
@@ -36764,7 +36764,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>57.3057670593262</v>
+        <v>57.3057632446289</v>
       </c>
       <c r="H1255" t="n">
         <v>1840</v>
@@ -37025,7 +37025,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1264" t="n">
-        <v>60.6766967773438</v>
+        <v>60.6766929626465</v>
       </c>
       <c r="H1264" t="n">
         <v>17158</v>
@@ -37054,7 +37054,7 @@
         <v>67</v>
       </c>
       <c r="G1265" t="n">
-        <v>62.7366981506348</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1265" t="n">
         <v>20893</v>
@@ -37083,7 +37083,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1266" t="n">
-        <v>61.6130599975586</v>
+        <v>61.6130638122559</v>
       </c>
       <c r="H1266" t="n">
         <v>8319</v>
@@ -37170,7 +37170,7 @@
         <v>63</v>
       </c>
       <c r="G1269" t="n">
-        <v>58.9912261962891</v>
+        <v>58.9912338256836</v>
       </c>
       <c r="H1269" t="n">
         <v>5348</v>
@@ -37199,7 +37199,7 @@
         <v>64.5</v>
       </c>
       <c r="G1270" t="n">
-        <v>60.3957824707031</v>
+        <v>60.3957786560059</v>
       </c>
       <c r="H1270" t="n">
         <v>4689</v>
@@ -37286,7 +37286,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>59.7403221130371</v>
+        <v>59.7403259277344</v>
       </c>
       <c r="H1273" t="n">
         <v>3377</v>
@@ -37373,7 +37373,7 @@
         <v>64.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>60.3957824707031</v>
+        <v>60.3957786560059</v>
       </c>
       <c r="H1276" t="n">
         <v>1278</v>
@@ -37402,7 +37402,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1277" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1277" t="n">
         <v>3313</v>
@@ -37431,7 +37431,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1278" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1278" t="n">
         <v>7535</v>
@@ -37576,7 +37576,7 @@
         <v>68</v>
       </c>
       <c r="G1283" t="n">
-        <v>63.6730728149414</v>
+        <v>63.6730690002441</v>
       </c>
       <c r="H1283" t="n">
         <v>3127</v>
@@ -37634,7 +37634,7 @@
         <v>67</v>
       </c>
       <c r="G1285" t="n">
-        <v>62.7366981506348</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1285" t="n">
         <v>3334</v>
@@ -37663,7 +37663,7 @@
         <v>68</v>
       </c>
       <c r="G1286" t="n">
-        <v>63.6730728149414</v>
+        <v>63.6730690002441</v>
       </c>
       <c r="H1286" t="n">
         <v>4639</v>
@@ -37721,7 +37721,7 @@
         <v>69</v>
       </c>
       <c r="G1288" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1288" t="n">
         <v>4841</v>
@@ -37808,7 +37808,7 @@
         <v>68.1999969482422</v>
       </c>
       <c r="G1291" t="n">
-        <v>63.8603439331055</v>
+        <v>63.8603363037109</v>
       </c>
       <c r="H1291" t="n">
         <v>716</v>
@@ -37837,7 +37837,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>63.7667007446289</v>
+        <v>63.7667083740234</v>
       </c>
       <c r="H1292" t="n">
         <v>2952</v>
@@ -37866,7 +37866,7 @@
         <v>67.5999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>63.2985191345215</v>
+        <v>63.2985229492188</v>
       </c>
       <c r="H1293" t="n">
         <v>6297</v>
@@ -37895,7 +37895,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1294" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1294" t="n">
         <v>1691</v>
@@ -37924,7 +37924,7 @@
         <v>67</v>
       </c>
       <c r="G1295" t="n">
-        <v>62.7366981506348</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1295" t="n">
         <v>3848</v>
@@ -38011,7 +38011,7 @@
         <v>69</v>
       </c>
       <c r="G1298" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1298" t="n">
         <v>3290</v>
@@ -38040,7 +38040,7 @@
         <v>69</v>
       </c>
       <c r="G1299" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1299" t="n">
         <v>4702</v>
@@ -38127,7 +38127,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G1302" t="n">
-        <v>63.3921546936035</v>
+        <v>63.3921508789062</v>
       </c>
       <c r="H1302" t="n">
         <v>6182</v>
@@ -38156,7 +38156,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1303" t="n">
-        <v>63.5794410705566</v>
+        <v>63.5794334411621</v>
       </c>
       <c r="H1303" t="n">
         <v>7397</v>
@@ -38214,7 +38214,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G1305" t="n">
-        <v>64.8903579711914</v>
+        <v>64.8903503417969</v>
       </c>
       <c r="H1305" t="n">
         <v>9202</v>
@@ -38330,7 +38330,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1309" t="n">
-        <v>65.3585433959961</v>
+        <v>65.358528137207</v>
       </c>
       <c r="H1309" t="n">
         <v>5793</v>
@@ -38417,7 +38417,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1312" t="n">
-        <v>66.2949066162109</v>
+        <v>66.2949142456055</v>
       </c>
       <c r="H1312" t="n">
         <v>3551</v>
@@ -38475,7 +38475,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G1314" t="n">
-        <v>66.8567276000977</v>
+        <v>66.8567199707031</v>
       </c>
       <c r="H1314" t="n">
         <v>11466</v>
@@ -38504,7 +38504,7 @@
         <v>70.3000030517578</v>
       </c>
       <c r="G1315" t="n">
-        <v>65.8267211914062</v>
+        <v>65.8267135620117</v>
       </c>
       <c r="H1315" t="n">
         <v>8792</v>
@@ -38533,7 +38533,7 @@
         <v>68</v>
       </c>
       <c r="G1316" t="n">
-        <v>63.6730728149414</v>
+        <v>63.6730690002441</v>
       </c>
       <c r="H1316" t="n">
         <v>16446</v>
@@ -38591,7 +38591,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1318" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1318" t="n">
         <v>6967</v>
@@ -38620,7 +38620,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1319" t="n">
-        <v>59.7403221130371</v>
+        <v>59.7403259277344</v>
       </c>
       <c r="H1319" t="n">
         <v>9758</v>
@@ -38707,7 +38707,7 @@
         <v>64</v>
       </c>
       <c r="G1322" t="n">
-        <v>59.9275932312012</v>
+        <v>59.9275970458984</v>
       </c>
       <c r="H1322" t="n">
         <v>13481</v>
@@ -38765,7 +38765,7 @@
         <v>66.3000030517578</v>
       </c>
       <c r="G1324" t="n">
-        <v>62.0812492370605</v>
+        <v>62.0812454223633</v>
       </c>
       <c r="H1324" t="n">
         <v>7316</v>
@@ -38794,7 +38794,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1325" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1325" t="n">
         <v>5034</v>
@@ -38910,7 +38910,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1329" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1329" t="n">
         <v>4284</v>
@@ -38997,7 +38997,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1332" t="n">
-        <v>59.5530471801758</v>
+        <v>59.5530433654785</v>
       </c>
       <c r="H1332" t="n">
         <v>3100</v>
@@ -39113,7 +39113,7 @@
         <v>64</v>
       </c>
       <c r="G1336" t="n">
-        <v>59.9275932312012</v>
+        <v>59.9275970458984</v>
       </c>
       <c r="H1336" t="n">
         <v>3411</v>
@@ -39142,7 +39142,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1337" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1337" t="n">
         <v>889</v>
@@ -39229,7 +39229,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1340" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1340" t="n">
         <v>2138</v>
@@ -39345,7 +39345,7 @@
         <v>68</v>
       </c>
       <c r="G1344" t="n">
-        <v>63.6730728149414</v>
+        <v>63.6730690002441</v>
       </c>
       <c r="H1344" t="n">
         <v>1117</v>
@@ -39403,7 +39403,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G1346" t="n">
-        <v>63.3921546936035</v>
+        <v>63.3921508789062</v>
       </c>
       <c r="H1346" t="n">
         <v>1676</v>
@@ -39461,7 +39461,7 @@
         <v>66.9000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>62.6430702209473</v>
+        <v>62.6430740356445</v>
       </c>
       <c r="H1348" t="n">
         <v>1938</v>
@@ -39519,7 +39519,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1350" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1350" t="n">
         <v>899</v>
@@ -39606,7 +39606,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1353" t="n">
-        <v>63.5794410705566</v>
+        <v>63.5794334411621</v>
       </c>
       <c r="H1353" t="n">
         <v>2513</v>
@@ -39635,7 +39635,7 @@
         <v>67</v>
       </c>
       <c r="G1354" t="n">
-        <v>62.7366981506348</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1354" t="n">
         <v>1811</v>
@@ -39664,7 +39664,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1355" t="n">
-        <v>62.549430847168</v>
+        <v>62.5494346618652</v>
       </c>
       <c r="H1355" t="n">
         <v>1776</v>
@@ -39693,7 +39693,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1356" t="n">
-        <v>61.42578125</v>
+        <v>61.4257850646973</v>
       </c>
       <c r="H1356" t="n">
         <v>5483</v>
@@ -39751,7 +39751,7 @@
         <v>64.5</v>
       </c>
       <c r="G1358" t="n">
-        <v>60.3957824707031</v>
+        <v>60.3957786560059</v>
       </c>
       <c r="H1358" t="n">
         <v>560</v>
@@ -39780,7 +39780,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1359" t="n">
-        <v>60.6766967773438</v>
+        <v>60.6766929626465</v>
       </c>
       <c r="H1359" t="n">
         <v>1409</v>
@@ -39809,7 +39809,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1360" t="n">
-        <v>60.5830497741699</v>
+        <v>60.5830535888672</v>
       </c>
       <c r="H1360" t="n">
         <v>366</v>
@@ -39925,7 +39925,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>59.2721366882324</v>
+        <v>59.2721405029297</v>
       </c>
       <c r="H1364" t="n">
         <v>5559</v>
@@ -39983,7 +39983,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1366" t="n">
-        <v>59.5530471801758</v>
+        <v>59.5530433654785</v>
       </c>
       <c r="H1366" t="n">
         <v>9059</v>
@@ -40070,7 +40070,7 @@
         <v>62</v>
       </c>
       <c r="G1369" t="n">
-        <v>58.0548629760742</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1369" t="n">
         <v>2182</v>
@@ -40099,7 +40099,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1370" t="n">
-        <v>58.8975944519043</v>
+        <v>58.897590637207</v>
       </c>
       <c r="H1370" t="n">
         <v>2370</v>
@@ -40157,7 +40157,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>57.6803092956543</v>
+        <v>57.6803131103516</v>
       </c>
       <c r="H1372" t="n">
         <v>6771</v>
@@ -40215,7 +40215,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1374" t="n">
-        <v>59.2721366882324</v>
+        <v>59.2721405029297</v>
       </c>
       <c r="H1374" t="n">
         <v>4750</v>
@@ -40244,7 +40244,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1375" t="n">
-        <v>58.6166801452637</v>
+        <v>58.6166763305664</v>
       </c>
       <c r="H1375" t="n">
         <v>2697</v>
@@ -40273,7 +40273,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1376" t="n">
-        <v>59.5530471801758</v>
+        <v>59.5530433654785</v>
       </c>
       <c r="H1376" t="n">
         <v>7123</v>
@@ -40302,7 +40302,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1377" t="n">
-        <v>59.5530471801758</v>
+        <v>59.5530433654785</v>
       </c>
       <c r="H1377" t="n">
         <v>4730</v>
@@ -40331,7 +40331,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G1378" t="n">
-        <v>59.0848655700684</v>
+        <v>59.0848617553711</v>
       </c>
       <c r="H1378" t="n">
         <v>1712</v>
@@ -40360,7 +40360,7 @@
         <v>62</v>
       </c>
       <c r="G1379" t="n">
-        <v>58.0548629760742</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1379" t="n">
         <v>4144</v>
@@ -40389,7 +40389,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1380" t="n">
-        <v>58.710319519043</v>
+        <v>58.7103157043457</v>
       </c>
       <c r="H1380" t="n">
         <v>796</v>
@@ -40418,7 +40418,7 @@
         <v>63</v>
       </c>
       <c r="G1381" t="n">
-        <v>58.9912261962891</v>
+        <v>58.9912338256836</v>
       </c>
       <c r="H1381" t="n">
         <v>876</v>
@@ -40447,7 +40447,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1382" t="n">
-        <v>58.8975944519043</v>
+        <v>58.897590637207</v>
       </c>
       <c r="H1382" t="n">
         <v>1175</v>
@@ -40476,7 +40476,7 @@
         <v>62.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1383" t="n">
         <v>4236</v>
@@ -40505,7 +40505,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1384" t="n">
-        <v>58.710319519043</v>
+        <v>58.7103157043457</v>
       </c>
       <c r="H1384" t="n">
         <v>1033</v>
@@ -40534,7 +40534,7 @@
         <v>62.5</v>
       </c>
       <c r="G1385" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1385" t="n">
         <v>1012</v>
@@ -40563,7 +40563,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>58.803955078125</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1386" t="n">
         <v>617</v>
@@ -40592,7 +40592,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1387" t="n">
-        <v>58.6166801452637</v>
+        <v>58.6166763305664</v>
       </c>
       <c r="H1387" t="n">
         <v>878</v>
@@ -40650,7 +40650,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>58.803955078125</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1389" t="n">
         <v>649</v>
@@ -40679,7 +40679,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1390" t="n">
-        <v>58.710319519043</v>
+        <v>58.7103157043457</v>
       </c>
       <c r="H1390" t="n">
         <v>5705</v>
@@ -40737,7 +40737,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G1392" t="n">
-        <v>59.8339653015137</v>
+        <v>59.8339614868164</v>
       </c>
       <c r="H1392" t="n">
         <v>1331</v>
@@ -40766,7 +40766,7 @@
         <v>64</v>
       </c>
       <c r="G1393" t="n">
-        <v>59.9275932312012</v>
+        <v>59.9275970458984</v>
       </c>
       <c r="H1393" t="n">
         <v>402</v>
@@ -40795,7 +40795,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>59.5530471801758</v>
+        <v>59.5530433654785</v>
       </c>
       <c r="H1394" t="n">
         <v>6905</v>
@@ -40853,7 +40853,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1396" t="n">
-        <v>58.8975944519043</v>
+        <v>58.897590637207</v>
       </c>
       <c r="H1396" t="n">
         <v>1658</v>
@@ -40911,7 +40911,7 @@
         <v>63</v>
       </c>
       <c r="G1398" t="n">
-        <v>58.9912261962891</v>
+        <v>58.9912338256836</v>
       </c>
       <c r="H1398" t="n">
         <v>4856</v>
@@ -40940,7 +40940,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>58.803955078125</v>
+        <v>58.8039512634277</v>
       </c>
       <c r="H1399" t="n">
         <v>963</v>
@@ -40969,7 +40969,7 @@
         <v>62.5</v>
       </c>
       <c r="G1400" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1400" t="n">
         <v>2659</v>
@@ -40998,7 +40998,7 @@
         <v>62</v>
       </c>
       <c r="G1401" t="n">
-        <v>58.0548629760742</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1401" t="n">
         <v>7100</v>
@@ -41027,7 +41027,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>57.3057670593262</v>
+        <v>57.3057632446289</v>
       </c>
       <c r="H1402" t="n">
         <v>5152</v>
@@ -41056,7 +41056,7 @@
         <v>61.5</v>
       </c>
       <c r="G1403" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1403" t="n">
         <v>2847</v>
@@ -41085,7 +41085,7 @@
         <v>61.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1404" t="n">
         <v>2465</v>
@@ -41346,7 +41346,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1413" t="n">
-        <v>55.3393859863281</v>
+        <v>55.3393898010254</v>
       </c>
       <c r="H1413" t="n">
         <v>7530</v>
@@ -41404,7 +41404,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1415" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1415" t="n">
         <v>1544</v>
@@ -41491,7 +41491,7 @@
         <v>62</v>
       </c>
       <c r="G1418" t="n">
-        <v>58.0548629760742</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1418" t="n">
         <v>18668</v>
@@ -41549,7 +41549,7 @@
         <v>61.5</v>
       </c>
       <c r="G1420" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1420" t="n">
         <v>2387</v>
@@ -41665,7 +41665,7 @@
         <v>62</v>
       </c>
       <c r="G1424" t="n">
-        <v>58.0548629760742</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1424" t="n">
         <v>15816</v>
@@ -41723,7 +41723,7 @@
         <v>62</v>
       </c>
       <c r="G1426" t="n">
-        <v>58.0548629760742</v>
+        <v>58.0548553466797</v>
       </c>
       <c r="H1426" t="n">
         <v>11491</v>
@@ -41752,7 +41752,7 @@
         <v>61.5</v>
       </c>
       <c r="G1427" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1427" t="n">
         <v>6174</v>
@@ -41810,7 +41810,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1429" t="n">
-        <v>56.5566749572754</v>
+        <v>56.5566711425781</v>
       </c>
       <c r="H1429" t="n">
         <v>3742</v>
@@ -41868,7 +41868,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1431" t="n">
-        <v>56.2757568359375</v>
+        <v>56.2757530212402</v>
       </c>
       <c r="H1431" t="n">
         <v>5393</v>
@@ -41955,7 +41955,7 @@
         <v>60.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>56.6503028869629</v>
+        <v>56.6503067016602</v>
       </c>
       <c r="H1434" t="n">
         <v>2448</v>
@@ -42042,7 +42042,7 @@
         <v>57.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>53.8411979675293</v>
+        <v>53.8412017822266</v>
       </c>
       <c r="H1437" t="n">
         <v>9231</v>
@@ -42071,7 +42071,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1438" t="n">
-        <v>53.4666519165039</v>
+        <v>53.4666481018066</v>
       </c>
       <c r="H1438" t="n">
         <v>4813</v>
@@ -42100,7 +42100,7 @@
         <v>56</v>
       </c>
       <c r="G1439" t="n">
-        <v>52.4366493225098</v>
+        <v>52.4366455078125</v>
       </c>
       <c r="H1439" t="n">
         <v>8320</v>
@@ -42129,7 +42129,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>52.7175598144531</v>
+        <v>52.7175559997559</v>
       </c>
       <c r="H1440" t="n">
         <v>1414</v>
@@ -42158,7 +42158,7 @@
         <v>56</v>
       </c>
       <c r="G1441" t="n">
-        <v>52.4366493225098</v>
+        <v>52.4366455078125</v>
       </c>
       <c r="H1441" t="n">
         <v>6199</v>
@@ -42187,7 +42187,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1442" t="n">
-        <v>53.6539268493652</v>
+        <v>53.6539306640625</v>
       </c>
       <c r="H1442" t="n">
         <v>5909</v>
@@ -42274,7 +42274,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>53.4666519165039</v>
+        <v>53.4666481018066</v>
       </c>
       <c r="H1445" t="n">
         <v>5885</v>
@@ -42303,7 +42303,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1446" t="n">
-        <v>53.2793769836426</v>
+        <v>53.2793807983398</v>
       </c>
       <c r="H1446" t="n">
         <v>4740</v>
@@ -42361,7 +42361,7 @@
         <v>56</v>
       </c>
       <c r="G1448" t="n">
-        <v>52.4366493225098</v>
+        <v>52.4366455078125</v>
       </c>
       <c r="H1448" t="n">
         <v>8104</v>
@@ -42419,7 +42419,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1450" t="n">
-        <v>52.3430099487305</v>
+        <v>52.3430137634277</v>
       </c>
       <c r="H1450" t="n">
         <v>2535</v>
@@ -42448,7 +42448,7 @@
         <v>56</v>
       </c>
       <c r="G1451" t="n">
-        <v>52.4366493225098</v>
+        <v>52.4366455078125</v>
       </c>
       <c r="H1451" t="n">
         <v>5276</v>
@@ -42477,7 +42477,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>52.0620956420898</v>
+        <v>52.0621032714844</v>
       </c>
       <c r="H1452" t="n">
         <v>1922</v>
@@ -42506,7 +42506,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1453" t="n">
-        <v>52.0620956420898</v>
+        <v>52.0621032714844</v>
       </c>
       <c r="H1453" t="n">
         <v>1637</v>
@@ -42535,7 +42535,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>52.1557388305664</v>
+        <v>52.1557350158691</v>
       </c>
       <c r="H1454" t="n">
         <v>1438</v>
@@ -42564,7 +42564,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1455" t="n">
-        <v>51.4066390991211</v>
+        <v>51.4066429138184</v>
       </c>
       <c r="H1455" t="n">
         <v>3335</v>
@@ -42622,7 +42622,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1457" t="n">
-        <v>51.5939140319824</v>
+        <v>51.5939178466797</v>
       </c>
       <c r="H1457" t="n">
         <v>1898</v>
@@ -42651,7 +42651,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1458" t="n">
-        <v>51.4066390991211</v>
+        <v>51.4066429138184</v>
       </c>
       <c r="H1458" t="n">
         <v>4585</v>
@@ -42709,7 +42709,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>51.219367980957</v>
+        <v>51.2193717956543</v>
       </c>
       <c r="H1460" t="n">
         <v>3848</v>
@@ -42738,7 +42738,7 @@
         <v>54</v>
       </c>
       <c r="G1461" t="n">
-        <v>50.563907623291</v>
+        <v>50.5639114379883</v>
       </c>
       <c r="H1461" t="n">
         <v>10162</v>
@@ -42796,7 +42796,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1463" t="n">
-        <v>50.376636505127</v>
+        <v>50.3766326904297</v>
       </c>
       <c r="H1463" t="n">
         <v>5407</v>
@@ -42825,7 +42825,7 @@
         <v>53</v>
       </c>
       <c r="G1464" t="n">
-        <v>49.6275367736816</v>
+        <v>49.6275405883789</v>
       </c>
       <c r="H1464" t="n">
         <v>6098</v>
@@ -42883,7 +42883,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1466" t="n">
-        <v>50.0020904541016</v>
+        <v>50.0020942687988</v>
       </c>
       <c r="H1466" t="n">
         <v>9739</v>
@@ -42912,7 +42912,7 @@
         <v>53.5999984741211</v>
       </c>
       <c r="G1467" t="n">
-        <v>50.1893615722656</v>
+        <v>50.1893577575684</v>
       </c>
       <c r="H1467" t="n">
         <v>3607</v>
@@ -42941,7 +42941,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1468" t="n">
-        <v>48.8784484863281</v>
+        <v>48.8784446716309</v>
       </c>
       <c r="H1468" t="n">
         <v>3171</v>
@@ -42970,7 +42970,7 @@
         <v>50</v>
       </c>
       <c r="G1469" t="n">
-        <v>46.8184356689453</v>
+        <v>46.818431854248</v>
       </c>
       <c r="H1469" t="n">
         <v>23042</v>
@@ -42999,7 +42999,7 @@
         <v>51</v>
       </c>
       <c r="G1470" t="n">
-        <v>47.7548027038574</v>
+        <v>47.7548065185547</v>
       </c>
       <c r="H1470" t="n">
         <v>7368</v>
@@ -43028,7 +43028,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>47.192985534668</v>
+        <v>47.1929817199707</v>
       </c>
       <c r="H1471" t="n">
         <v>4172</v>
@@ -43086,7 +43086,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1473" t="n">
-        <v>48.5975379943848</v>
+        <v>48.5975341796875</v>
       </c>
       <c r="H1473" t="n">
         <v>5452</v>
@@ -43144,7 +43144,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1475" t="n">
-        <v>48.5975379943848</v>
+        <v>48.5975341796875</v>
       </c>
       <c r="H1475" t="n">
         <v>3380</v>
@@ -43260,7 +43260,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1479" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1479" t="n">
         <v>8380</v>
@@ -43318,7 +43318,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1481" t="n">
-        <v>54.1134948730469</v>
+        <v>54.1134986877441</v>
       </c>
       <c r="H1481" t="n">
         <v>8061</v>
@@ -43376,7 +43376,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G1483" t="n">
-        <v>54.3988037109375</v>
+        <v>54.3988075256348</v>
       </c>
       <c r="H1483" t="n">
         <v>11670</v>
@@ -43492,7 +43492,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G1487" t="n">
-        <v>55.444938659668</v>
+        <v>55.4449348449707</v>
       </c>
       <c r="H1487" t="n">
         <v>6014</v>
@@ -43550,7 +43550,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1489" t="n">
-        <v>55.2547264099121</v>
+        <v>55.2547302246094</v>
       </c>
       <c r="H1489" t="n">
         <v>4867</v>
@@ -43579,7 +43579,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1490" t="n">
-        <v>55.8253479003906</v>
+        <v>55.8253440856934</v>
       </c>
       <c r="H1490" t="n">
         <v>5008</v>
@@ -43608,7 +43608,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1491" t="n">
-        <v>56.205753326416</v>
+        <v>56.2057571411133</v>
       </c>
       <c r="H1491" t="n">
         <v>2633</v>
@@ -43666,7 +43666,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>55.8253479003906</v>
+        <v>55.8253440856934</v>
       </c>
       <c r="H1493" t="n">
         <v>20583</v>
@@ -43724,7 +43724,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1495" t="n">
-        <v>56.205753326416</v>
+        <v>56.2057571411133</v>
       </c>
       <c r="H1495" t="n">
         <v>3100</v>
@@ -43753,7 +43753,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>56.3008613586426</v>
+        <v>56.3008651733398</v>
       </c>
       <c r="H1496" t="n">
         <v>2040</v>
@@ -43898,7 +43898,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1501" t="n">
-        <v>57.4420967102051</v>
+        <v>57.4420928955078</v>
       </c>
       <c r="H1501" t="n">
         <v>6459</v>
@@ -43956,7 +43956,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1503" t="n">
         <v>3852</v>
@@ -44188,7 +44188,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1511" t="n">
-        <v>57.4420967102051</v>
+        <v>57.4420928955078</v>
       </c>
       <c r="H1511" t="n">
         <v>20507</v>
@@ -44217,7 +44217,7 @@
         <v>59.5</v>
       </c>
       <c r="G1512" t="n">
-        <v>56.5861701965332</v>
+        <v>56.5861663818359</v>
       </c>
       <c r="H1512" t="n">
         <v>5412</v>
@@ -44246,7 +44246,7 @@
         <v>59.5</v>
       </c>
       <c r="G1513" t="n">
-        <v>56.5861701965332</v>
+        <v>56.5861663818359</v>
       </c>
       <c r="H1513" t="n">
         <v>3757</v>
@@ -44420,7 +44420,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1519" t="n">
-        <v>56.205753326416</v>
+        <v>56.2057571411133</v>
       </c>
       <c r="H1519" t="n">
         <v>2015</v>
@@ -44449,7 +44449,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1520" t="n">
-        <v>55.8253479003906</v>
+        <v>55.8253440856934</v>
       </c>
       <c r="H1520" t="n">
         <v>1640</v>
@@ -44565,7 +44565,7 @@
         <v>58.5</v>
       </c>
       <c r="G1524" t="n">
-        <v>55.6351432800293</v>
+        <v>55.635139465332</v>
       </c>
       <c r="H1524" t="n">
         <v>4981</v>
@@ -44652,7 +44652,7 @@
         <v>58.5</v>
       </c>
       <c r="G1527" t="n">
-        <v>55.6351432800293</v>
+        <v>55.635139465332</v>
       </c>
       <c r="H1527" t="n">
         <v>1406</v>
@@ -44681,7 +44681,7 @@
         <v>58.5</v>
       </c>
       <c r="G1528" t="n">
-        <v>55.6351432800293</v>
+        <v>55.635139465332</v>
       </c>
       <c r="H1528" t="n">
         <v>4081</v>
@@ -44768,7 +44768,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1531" t="n">
-        <v>55.2547264099121</v>
+        <v>55.2547302246094</v>
       </c>
       <c r="H1531" t="n">
         <v>2078</v>
@@ -44826,7 +44826,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1533" t="n">
-        <v>54.7792167663574</v>
+        <v>54.7792129516602</v>
       </c>
       <c r="H1533" t="n">
         <v>6649</v>
@@ -44855,7 +44855,7 @@
         <v>57.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>54.6841125488281</v>
+        <v>54.6841163635254</v>
       </c>
       <c r="H1534" t="n">
         <v>1379</v>
@@ -44884,7 +44884,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1535" t="n">
-        <v>55.2547264099121</v>
+        <v>55.2547302246094</v>
       </c>
       <c r="H1535" t="n">
         <v>2556</v>
@@ -44913,7 +44913,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1536" t="n">
-        <v>55.2547264099121</v>
+        <v>55.2547302246094</v>
       </c>
       <c r="H1536" t="n">
         <v>2855</v>
@@ -44971,7 +44971,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1538" t="n">
-        <v>54.1134948730469</v>
+        <v>54.1134986877441</v>
       </c>
       <c r="H1538" t="n">
         <v>2006</v>
@@ -45087,7 +45087,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>53.0673637390137</v>
+        <v>53.0673675537109</v>
       </c>
       <c r="H1542" t="n">
         <v>3001</v>
@@ -45145,7 +45145,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1544" t="n">
-        <v>53.162467956543</v>
+        <v>53.1624717712402</v>
       </c>
       <c r="H1544" t="n">
         <v>2282</v>
@@ -45232,7 +45232,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1547" t="n">
-        <v>53.5428810119629</v>
+        <v>53.5428771972656</v>
       </c>
       <c r="H1547" t="n">
         <v>704</v>
@@ -45261,7 +45261,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1548" t="n">
-        <v>52.8771553039551</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1548" t="n">
         <v>1297</v>
@@ -45464,7 +45464,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1555" t="n">
-        <v>52.8771553039551</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1555" t="n">
         <v>362</v>
@@ -45493,7 +45493,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G1556" t="n">
-        <v>52.5918464660645</v>
+        <v>52.5918502807617</v>
       </c>
       <c r="H1556" t="n">
         <v>2970</v>
@@ -45638,7 +45638,7 @@
         <v>54.5</v>
       </c>
       <c r="G1561" t="n">
-        <v>51.8310317993164</v>
+        <v>51.8310279846191</v>
       </c>
       <c r="H1561" t="n">
         <v>8729</v>
@@ -45667,7 +45667,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1562" t="n">
-        <v>51.2604141235352</v>
+        <v>51.2604179382324</v>
       </c>
       <c r="H1562" t="n">
         <v>2719</v>
@@ -45870,7 +45870,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1569" t="n">
-        <v>51.2604141235352</v>
+        <v>51.2604179382324</v>
       </c>
       <c r="H1569" t="n">
         <v>2926</v>
@@ -45928,7 +45928,7 @@
         <v>53</v>
       </c>
       <c r="G1571" t="n">
-        <v>50.4044876098633</v>
+        <v>50.404483795166</v>
       </c>
       <c r="H1571" t="n">
         <v>1778</v>
@@ -45986,7 +45986,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>49.643669128418</v>
+        <v>49.6436653137207</v>
       </c>
       <c r="H1573" t="n">
         <v>4057</v>
@@ -46015,7 +46015,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1574" t="n">
-        <v>48.8828430175781</v>
+        <v>48.8828468322754</v>
       </c>
       <c r="H1574" t="n">
         <v>4069</v>
@@ -46160,7 +46160,7 @@
         <v>49</v>
       </c>
       <c r="G1579" t="n">
-        <v>46.6003723144531</v>
+        <v>46.6003761291504</v>
       </c>
       <c r="H1579" t="n">
         <v>3563</v>
@@ -46276,7 +46276,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G1583" t="n">
-        <v>45.2213859558105</v>
+        <v>45.2213821411133</v>
       </c>
       <c r="H1583" t="n">
         <v>6805</v>
@@ -46334,7 +46334,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1585" t="n">
-        <v>43.1766777038574</v>
+        <v>43.1766738891602</v>
       </c>
       <c r="H1585" t="n">
         <v>16444</v>
@@ -46363,7 +46363,7 @@
         <v>46.5</v>
       </c>
       <c r="G1586" t="n">
-        <v>44.2228012084961</v>
+        <v>44.2228050231934</v>
       </c>
       <c r="H1586" t="n">
         <v>14423</v>
@@ -46450,7 +46450,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G1589" t="n">
-        <v>45.5542488098145</v>
+        <v>45.5542449951172</v>
       </c>
       <c r="H1589" t="n">
         <v>2191</v>
@@ -46479,7 +46479,7 @@
         <v>48.9500007629395</v>
       </c>
       <c r="G1590" t="n">
-        <v>46.5528221130371</v>
+        <v>46.5528259277344</v>
       </c>
       <c r="H1590" t="n">
         <v>8441</v>
@@ -46508,7 +46508,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1591" t="n">
-        <v>48.7877388000488</v>
+        <v>48.7877349853516</v>
       </c>
       <c r="H1591" t="n">
         <v>16510</v>
@@ -46595,7 +46595,7 @@
         <v>49.25</v>
       </c>
       <c r="G1594" t="n">
-        <v>46.8381309509277</v>
+        <v>46.838134765625</v>
       </c>
       <c r="H1594" t="n">
         <v>3122</v>
@@ -46653,7 +46653,7 @@
         <v>49.2999992370605</v>
       </c>
       <c r="G1596" t="n">
-        <v>46.8856811523438</v>
+        <v>46.885684967041</v>
       </c>
       <c r="H1596" t="n">
         <v>3011</v>
@@ -46682,7 +46682,7 @@
         <v>49</v>
       </c>
       <c r="G1597" t="n">
-        <v>46.6003723144531</v>
+        <v>46.6003761291504</v>
       </c>
       <c r="H1597" t="n">
         <v>2928</v>
@@ -46769,7 +46769,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G1600" t="n">
-        <v>46.1724128723145</v>
+        <v>46.1724090576172</v>
       </c>
       <c r="H1600" t="n">
         <v>565</v>
@@ -46798,7 +46798,7 @@
         <v>48.25</v>
       </c>
       <c r="G1601" t="n">
-        <v>45.8871040344238</v>
+        <v>45.8871078491211</v>
       </c>
       <c r="H1601" t="n">
         <v>13370</v>
@@ -46856,7 +46856,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1603" t="n">
-        <v>48.7877388000488</v>
+        <v>48.7877349853516</v>
       </c>
       <c r="H1603" t="n">
         <v>4600</v>
@@ -46972,7 +46972,7 @@
         <v>48.9000015258789</v>
       </c>
       <c r="G1607" t="n">
-        <v>46.5052757263184</v>
+        <v>46.5052719116211</v>
       </c>
       <c r="H1607" t="n">
         <v>4933</v>
@@ -47001,7 +47001,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>46.9807891845703</v>
+        <v>46.980785369873</v>
       </c>
       <c r="H1608" t="n">
         <v>2685</v>
@@ -47030,7 +47030,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G1609" t="n">
-        <v>47.4087448120117</v>
+        <v>47.408748626709</v>
       </c>
       <c r="H1609" t="n">
         <v>1214</v>
@@ -47059,7 +47059,7 @@
         <v>49.4500007629395</v>
       </c>
       <c r="G1610" t="n">
-        <v>47.0283393859863</v>
+        <v>47.0283355712891</v>
       </c>
       <c r="H1610" t="n">
         <v>2132</v>
@@ -47175,7 +47175,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1614" t="n">
-        <v>49.8338737487793</v>
+        <v>49.833869934082</v>
       </c>
       <c r="H1614" t="n">
         <v>2347</v>
@@ -47349,7 +47349,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G1620" t="n">
-        <v>47.4563026428223</v>
+        <v>47.4563064575195</v>
       </c>
       <c r="H1620" t="n">
         <v>3176</v>
@@ -47378,7 +47378,7 @@
         <v>51.5</v>
       </c>
       <c r="G1621" t="n">
-        <v>48.9779434204102</v>
+        <v>48.9779472351074</v>
       </c>
       <c r="H1621" t="n">
         <v>2986</v>
@@ -47407,7 +47407,7 @@
         <v>51.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>48.9779434204102</v>
+        <v>48.9779472351074</v>
       </c>
       <c r="H1622" t="n">
         <v>1263</v>
@@ -47436,7 +47436,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G1623" t="n">
-        <v>48.5975341796875</v>
+        <v>48.5975303649902</v>
       </c>
       <c r="H1623" t="n">
         <v>4309</v>
@@ -47465,7 +47465,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1624" t="n">
-        <v>48.8828430175781</v>
+        <v>48.8828468322754</v>
       </c>
       <c r="H1624" t="n">
         <v>1935</v>
@@ -47523,7 +47523,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1626" t="n">
-        <v>51.2604141235352</v>
+        <v>51.2604179382324</v>
       </c>
       <c r="H1626" t="n">
         <v>11914</v>
@@ -47552,7 +47552,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1627" t="n">
-        <v>52.8771553039551</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1627" t="n">
         <v>11544</v>
@@ -47610,7 +47610,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1629" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1629" t="n">
         <v>6837</v>
@@ -47668,7 +47668,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1631" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1631" t="n">
         <v>1580</v>
@@ -47697,7 +47697,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1632" t="n">
-        <v>52.8771553039551</v>
+        <v>52.8771629333496</v>
       </c>
       <c r="H1632" t="n">
         <v>4324</v>
@@ -47784,7 +47784,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1635" t="n">
-        <v>54.1134948730469</v>
+        <v>54.1134986877441</v>
       </c>
       <c r="H1635" t="n">
         <v>7941</v>
@@ -47813,7 +47813,7 @@
         <v>56</v>
       </c>
       <c r="G1636" t="n">
-        <v>53.2575759887695</v>
+        <v>53.2575721740723</v>
       </c>
       <c r="H1636" t="n">
         <v>8522</v>
@@ -47842,7 +47842,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G1637" t="n">
-        <v>53.0673637390137</v>
+        <v>53.0673675537109</v>
       </c>
       <c r="H1637" t="n">
         <v>6582</v>
@@ -47900,7 +47900,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1639" t="n">
-        <v>52.6869583129883</v>
+        <v>52.686954498291</v>
       </c>
       <c r="H1639" t="n">
         <v>1545</v>
@@ -48045,7 +48045,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1644" t="n">
-        <v>53.5428810119629</v>
+        <v>53.5428771972656</v>
       </c>
       <c r="H1644" t="n">
         <v>3063</v>
@@ -48103,7 +48103,7 @@
         <v>56</v>
       </c>
       <c r="G1646" t="n">
-        <v>53.2575759887695</v>
+        <v>53.2575721740723</v>
       </c>
       <c r="H1646" t="n">
         <v>2964</v>
@@ -48132,7 +48132,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1647" t="n">
-        <v>53.162467956543</v>
+        <v>53.1624717712402</v>
       </c>
       <c r="H1647" t="n">
         <v>1754</v>
@@ -48161,7 +48161,7 @@
         <v>57</v>
       </c>
       <c r="G1648" t="n">
-        <v>54.2086029052734</v>
+        <v>54.2085990905762</v>
       </c>
       <c r="H1648" t="n">
         <v>5732</v>
@@ -48277,7 +48277,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>56.7763748168945</v>
+        <v>56.7763786315918</v>
       </c>
       <c r="H1652" t="n">
         <v>10689</v>
@@ -48306,7 +48306,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1653" t="n">
-        <v>56.205753326416</v>
+        <v>56.2057571411133</v>
       </c>
       <c r="H1653" t="n">
         <v>5326</v>
@@ -48364,7 +48364,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1655" t="n">
-        <v>54.7792167663574</v>
+        <v>54.7792129516602</v>
       </c>
       <c r="H1655" t="n">
         <v>4992</v>
@@ -48393,7 +48393,7 @@
         <v>59.5</v>
       </c>
       <c r="G1656" t="n">
-        <v>56.5861701965332</v>
+        <v>56.5861663818359</v>
       </c>
       <c r="H1656" t="n">
         <v>55446</v>
@@ -48451,7 +48451,7 @@
         <v>60.5</v>
       </c>
       <c r="G1658" t="n">
-        <v>57.5371971130371</v>
+        <v>57.5372009277344</v>
       </c>
       <c r="H1658" t="n">
         <v>8090</v>
@@ -48480,7 +48480,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1659" t="n">
-        <v>57.2518920898438</v>
+        <v>57.2518882751465</v>
       </c>
       <c r="H1659" t="n">
         <v>4972</v>
@@ -48596,7 +48596,7 @@
         <v>62</v>
       </c>
       <c r="G1663" t="n">
-        <v>58.9637413024902</v>
+        <v>58.963737487793</v>
       </c>
       <c r="H1663" t="n">
         <v>2529</v>
@@ -48625,7 +48625,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>59.1539459228516</v>
+        <v>59.1539497375488</v>
       </c>
       <c r="H1664" t="n">
         <v>7902</v>
@@ -48654,7 +48654,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1665" t="n">
         <v>6024</v>
@@ -48683,7 +48683,7 @@
         <v>62</v>
       </c>
       <c r="G1666" t="n">
-        <v>58.9637413024902</v>
+        <v>58.963737487793</v>
       </c>
       <c r="H1666" t="n">
         <v>4789</v>
@@ -48712,7 +48712,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1667" t="n">
-        <v>57.4420967102051</v>
+        <v>57.4420928955078</v>
       </c>
       <c r="H1667" t="n">
         <v>6641</v>
@@ -48741,7 +48741,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1668" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1668" t="n">
         <v>4693</v>
@@ -48770,7 +48770,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1669" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1669" t="n">
         <v>3555</v>
@@ -48799,7 +48799,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1670" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1670" t="n">
         <v>4025</v>
@@ -48828,7 +48828,7 @@
         <v>60.5</v>
       </c>
       <c r="G1671" t="n">
-        <v>57.5371971130371</v>
+        <v>57.5372009277344</v>
       </c>
       <c r="H1671" t="n">
         <v>2631</v>
@@ -48886,7 +48886,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1673" t="n">
-        <v>59.7245635986328</v>
+        <v>59.7245597839355</v>
       </c>
       <c r="H1673" t="n">
         <v>9087</v>
@@ -48915,7 +48915,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G1674" t="n">
-        <v>60.0098724365234</v>
+        <v>60.0098686218262</v>
       </c>
       <c r="H1674" t="n">
         <v>10808</v>
@@ -48944,7 +48944,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1675" t="n">
-        <v>59.5343589782715</v>
+        <v>59.5343551635742</v>
       </c>
       <c r="H1675" t="n">
         <v>9876</v>
@@ -49002,7 +49002,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1677" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1677" t="n">
         <v>2547</v>
@@ -49031,7 +49031,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1678" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1678" t="n">
         <v>4489</v>
@@ -49060,7 +49060,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1679" t="n">
-        <v>58.2029190063477</v>
+        <v>58.2029151916504</v>
       </c>
       <c r="H1679" t="n">
         <v>3557</v>
@@ -49176,7 +49176,7 @@
         <v>60.5</v>
       </c>
       <c r="G1683" t="n">
-        <v>57.5371971130371</v>
+        <v>57.5372009277344</v>
       </c>
       <c r="H1683" t="n">
         <v>2906</v>
@@ -49205,7 +49205,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1684" t="n">
-        <v>56.7763748168945</v>
+        <v>56.7763786315918</v>
       </c>
       <c r="H1684" t="n">
         <v>5568</v>
@@ -49263,7 +49263,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>56.3008613586426</v>
+        <v>56.3008651733398</v>
       </c>
       <c r="H1686" t="n">
         <v>3846</v>
@@ -49292,7 +49292,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1687" t="n">
-        <v>57.2518920898438</v>
+        <v>57.2518882751465</v>
       </c>
       <c r="H1687" t="n">
         <v>6610</v>
@@ -49321,7 +49321,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G1688" t="n">
-        <v>56.3008613586426</v>
+        <v>56.3008651733398</v>
       </c>
       <c r="H1688" t="n">
         <v>3383</v>
@@ -49495,7 +49495,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1694" t="n">
-        <v>56.7763748168945</v>
+        <v>56.7763786315918</v>
       </c>
       <c r="H1694" t="n">
         <v>2571</v>
@@ -49524,7 +49524,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G1695" t="n">
-        <v>56.3959655761719</v>
+        <v>56.3959617614746</v>
       </c>
       <c r="H1695" t="n">
         <v>2243</v>
@@ -49553,7 +49553,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G1696" t="n">
-        <v>56.3008613586426</v>
+        <v>56.3008651733398</v>
       </c>
       <c r="H1696" t="n">
         <v>4574</v>
@@ -49698,7 +49698,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1701" t="n">
-        <v>55.2547264099121</v>
+        <v>55.2547302246094</v>
       </c>
       <c r="H1701" t="n">
         <v>5255</v>
@@ -49756,7 +49756,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1703" t="n">
-        <v>54.7792167663574</v>
+        <v>54.7792129516602</v>
       </c>
       <c r="H1703" t="n">
         <v>3738</v>
@@ -49814,7 +49814,7 @@
         <v>57</v>
       </c>
       <c r="G1705" t="n">
-        <v>54.2086029052734</v>
+        <v>54.2085990905762</v>
       </c>
       <c r="H1705" t="n">
         <v>6565</v>
@@ -49901,7 +49901,7 @@
         <v>56</v>
       </c>
       <c r="G1708" t="n">
-        <v>53.2575759887695</v>
+        <v>53.2575721740723</v>
       </c>
       <c r="H1708" t="n">
         <v>2250</v>
@@ -49988,7 +49988,7 @@
         <v>54.7999992370605</v>
       </c>
       <c r="G1711" t="n">
-        <v>52.1163368225098</v>
+        <v>52.116340637207</v>
       </c>
       <c r="H1711" t="n">
         <v>4411</v>
@@ -50017,7 +50017,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1712" t="n">
-        <v>51.2604141235352</v>
+        <v>51.2604179382324</v>
       </c>
       <c r="H1712" t="n">
         <v>6885</v>
@@ -50133,7 +50133,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1716" t="n">
-        <v>51.1653099060059</v>
+        <v>51.1653060913086</v>
       </c>
       <c r="H1716" t="n">
         <v>5423</v>
@@ -50162,7 +50162,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1717" t="n">
-        <v>51.1653099060059</v>
+        <v>51.1653060913086</v>
       </c>
       <c r="H1717" t="n">
         <v>2501</v>
@@ -50191,7 +50191,7 @@
         <v>53</v>
       </c>
       <c r="G1718" t="n">
-        <v>50.4044876098633</v>
+        <v>50.404483795166</v>
       </c>
       <c r="H1718" t="n">
         <v>3597</v>
@@ -50220,7 +50220,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1719" t="n">
-        <v>49.2632522583008</v>
+        <v>49.263256072998</v>
       </c>
       <c r="H1719" t="n">
         <v>12468</v>
@@ -50278,7 +50278,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1721" t="n">
-        <v>51.2604141235352</v>
+        <v>51.2604179382324</v>
       </c>
       <c r="H1721" t="n">
         <v>3934</v>
@@ -50307,7 +50307,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1722" t="n">
-        <v>50.4995880126953</v>
+        <v>50.4995918273926</v>
       </c>
       <c r="H1722" t="n">
         <v>3955</v>
@@ -50365,7 +50365,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G1724" t="n">
-        <v>50.6897926330566</v>
+        <v>50.6897964477539</v>
       </c>
       <c r="H1724" t="n">
         <v>2797</v>
@@ -50394,7 +50394,7 @@
         <v>54</v>
       </c>
       <c r="G1725" t="n">
-        <v>51.3555145263672</v>
+        <v>51.3555183410645</v>
       </c>
       <c r="H1725" t="n">
         <v>6074</v>
@@ -50452,7 +50452,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1727" t="n">
-        <v>49.3583602905273</v>
+        <v>49.3583564758301</v>
       </c>
       <c r="H1727" t="n">
         <v>14723</v>
@@ -50655,7 +50655,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G1734" t="n">
-        <v>49.0168228149414</v>
+        <v>49.0168266296387</v>
       </c>
       <c r="H1734" t="n">
         <v>4123</v>
@@ -50742,7 +50742,7 @@
         <v>48.25</v>
       </c>
       <c r="G1737" t="n">
-        <v>46.6481590270996</v>
+        <v>46.6481628417969</v>
       </c>
       <c r="H1737" t="n">
         <v>12798</v>
@@ -50771,7 +50771,7 @@
         <v>48</v>
       </c>
       <c r="G1738" t="n">
-        <v>46.4064598083496</v>
+        <v>46.4064559936523</v>
       </c>
       <c r="H1738" t="n">
         <v>8909</v>
@@ -50800,7 +50800,7 @@
         <v>48.25</v>
       </c>
       <c r="G1739" t="n">
-        <v>46.6481590270996</v>
+        <v>46.6481628417969</v>
       </c>
       <c r="H1739" t="n">
         <v>7440</v>
@@ -50829,7 +50829,7 @@
         <v>48.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>46.6481590270996</v>
+        <v>46.6481628417969</v>
       </c>
       <c r="H1740" t="n">
         <v>4589</v>
@@ -50974,7 +50974,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>47.4699401855469</v>
+        <v>47.4699363708496</v>
       </c>
       <c r="H1745" t="n">
         <v>5196</v>
@@ -51032,7 +51032,7 @@
         <v>48.4500007629395</v>
       </c>
       <c r="G1747" t="n">
-        <v>46.8415184020996</v>
+        <v>46.8415222167969</v>
       </c>
       <c r="H1747" t="n">
         <v>6424</v>
@@ -51061,7 +51061,7 @@
         <v>49.25</v>
       </c>
       <c r="G1748" t="n">
-        <v>47.6149635314941</v>
+        <v>47.6149597167969</v>
       </c>
       <c r="H1748" t="n">
         <v>13987</v>
@@ -51177,7 +51177,7 @@
         <v>48</v>
       </c>
       <c r="G1752" t="n">
-        <v>46.4064598083496</v>
+        <v>46.4064559936523</v>
       </c>
       <c r="H1752" t="n">
         <v>7366</v>
@@ -51351,7 +51351,7 @@
         <v>46.0499992370605</v>
       </c>
       <c r="G1758" t="n">
-        <v>44.5211944580078</v>
+        <v>44.5211982727051</v>
       </c>
       <c r="H1758" t="n">
         <v>22829</v>
@@ -51467,7 +51467,7 @@
         <v>47.4500007629395</v>
       </c>
       <c r="G1762" t="n">
-        <v>45.8747177124023</v>
+        <v>45.8747215270996</v>
       </c>
       <c r="H1762" t="n">
         <v>16906</v>
@@ -51525,7 +51525,7 @@
         <v>47.5</v>
       </c>
       <c r="G1764" t="n">
-        <v>45.9230613708496</v>
+        <v>45.9230575561523</v>
       </c>
       <c r="H1764" t="n">
         <v>3409</v>
@@ -51844,7 +51844,7 @@
         <v>48</v>
       </c>
       <c r="G1775" t="n">
-        <v>46.4064598083496</v>
+        <v>46.4064559936523</v>
       </c>
       <c r="H1775" t="n">
         <v>2868</v>
@@ -51931,7 +51931,7 @@
         <v>48.25</v>
       </c>
       <c r="G1778" t="n">
-        <v>46.6481590270996</v>
+        <v>46.6481628417969</v>
       </c>
       <c r="H1778" t="n">
         <v>2304</v>
@@ -52018,7 +52018,7 @@
         <v>48.2000007629395</v>
       </c>
       <c r="G1781" t="n">
-        <v>46.5998191833496</v>
+        <v>46.5998229980469</v>
       </c>
       <c r="H1781" t="n">
         <v>2415</v>
@@ -52134,7 +52134,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G1785" t="n">
-        <v>45.5846786499023</v>
+        <v>45.5846824645996</v>
       </c>
       <c r="H1785" t="n">
         <v>2631</v>
@@ -52163,7 +52163,7 @@
         <v>47.75</v>
       </c>
       <c r="G1786" t="n">
-        <v>46.1647605895996</v>
+        <v>46.1647567749023</v>
       </c>
       <c r="H1786" t="n">
         <v>1985</v>
@@ -52279,7 +52279,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G1790" t="n">
-        <v>46.2614402770996</v>
+        <v>46.2614364624023</v>
       </c>
       <c r="H1790" t="n">
         <v>1116</v>
@@ -52453,7 +52453,7 @@
         <v>47.4500007629395</v>
       </c>
       <c r="G1796" t="n">
-        <v>45.8747177124023</v>
+        <v>45.8747215270996</v>
       </c>
       <c r="H1796" t="n">
         <v>1134</v>
@@ -52656,7 +52656,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G1803" t="n">
-        <v>47.7116394042969</v>
+        <v>47.7116432189941</v>
       </c>
       <c r="H1803" t="n">
         <v>1192</v>
@@ -52859,7 +52859,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1810" t="n">
-        <v>49.5969047546387</v>
+        <v>49.5969009399414</v>
       </c>
       <c r="H1810" t="n">
         <v>4232</v>
@@ -53381,7 +53381,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1828" t="n">
-        <v>55.4943962097168</v>
+        <v>55.4943923950195</v>
       </c>
       <c r="H1828" t="n">
         <v>1941</v>
@@ -53410,7 +53410,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1829" t="n">
-        <v>56.1711502075195</v>
+        <v>56.1711540222168</v>
       </c>
       <c r="H1829" t="n">
         <v>2077</v>
@@ -53555,7 +53555,7 @@
         <v>57</v>
       </c>
       <c r="G1834" t="n">
-        <v>55.1076698303223</v>
+        <v>55.1076736450195</v>
       </c>
       <c r="H1834" t="n">
         <v>4201</v>
@@ -53613,7 +53613,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1836" t="n">
-        <v>53.2707443237305</v>
+        <v>53.2707481384277</v>
       </c>
       <c r="H1836" t="n">
         <v>3803</v>
@@ -53642,7 +53642,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1837" t="n">
-        <v>53.077392578125</v>
+        <v>53.0773887634277</v>
       </c>
       <c r="H1837" t="n">
         <v>5249</v>
@@ -53729,7 +53729,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1840" t="n">
-        <v>53.560791015625</v>
+        <v>53.5607872009277</v>
       </c>
       <c r="H1840" t="n">
         <v>11120</v>
@@ -53816,7 +53816,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1843" t="n">
-        <v>55.4943962097168</v>
+        <v>55.4943923950195</v>
       </c>
       <c r="H1843" t="n">
         <v>3819</v>
@@ -53903,7 +53903,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1846" t="n">
-        <v>56.1711502075195</v>
+        <v>56.1711540222168</v>
       </c>
       <c r="H1846" t="n">
         <v>6678</v>
@@ -54048,7 +54048,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1851" t="n">
-        <v>53.7541465759277</v>
+        <v>53.754150390625</v>
       </c>
       <c r="H1851" t="n">
         <v>1761</v>
@@ -54106,7 +54106,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1853" t="n">
-        <v>55.4943962097168</v>
+        <v>55.4943923950195</v>
       </c>
       <c r="H1853" t="n">
         <v>1538</v>
@@ -54135,7 +54135,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1854" t="n">
-        <v>54.9143104553223</v>
+        <v>54.914306640625</v>
       </c>
       <c r="H1854" t="n">
         <v>2669</v>
@@ -54164,7 +54164,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1855" t="n">
-        <v>53.7541465759277</v>
+        <v>53.754150390625</v>
       </c>
       <c r="H1855" t="n">
         <v>2839</v>
@@ -54280,7 +54280,7 @@
         <v>53</v>
       </c>
       <c r="G1859" t="n">
-        <v>51.2404670715332</v>
+        <v>51.2404632568359</v>
       </c>
       <c r="H1859" t="n">
         <v>17183</v>
@@ -54309,7 +54309,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1860" t="n">
-        <v>50.8537406921387</v>
+        <v>50.8537445068359</v>
       </c>
       <c r="H1860" t="n">
         <v>9585</v>
@@ -54454,7 +54454,7 @@
         <v>57</v>
       </c>
       <c r="G1865" t="n">
-        <v>55.1076698303223</v>
+        <v>55.1076736450195</v>
       </c>
       <c r="H1865" t="n">
         <v>5904</v>
@@ -54686,7 +54686,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1873" t="n">
-        <v>53.077392578125</v>
+        <v>53.0773887634277</v>
       </c>
       <c r="H1873" t="n">
         <v>3146</v>
@@ -54744,7 +54744,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1875" t="n">
-        <v>53.560791015625</v>
+        <v>53.5607872009277</v>
       </c>
       <c r="H1875" t="n">
         <v>1086</v>
@@ -54889,7 +54889,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1880" t="n">
-        <v>53.077392578125</v>
+        <v>53.0773887634277</v>
       </c>
       <c r="H1880" t="n">
         <v>2906</v>
@@ -54918,7 +54918,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1881" t="n">
-        <v>53.2707443237305</v>
+        <v>53.2707481384277</v>
       </c>
       <c r="H1881" t="n">
         <v>1253</v>
@@ -55092,7 +55092,7 @@
         <v>54.5</v>
       </c>
       <c r="G1887" t="n">
-        <v>52.6906661987305</v>
+        <v>52.6906700134277</v>
       </c>
       <c r="H1887" t="n">
         <v>28310</v>
@@ -55150,7 +55150,7 @@
         <v>54</v>
       </c>
       <c r="G1889" t="n">
-        <v>52.2072639465332</v>
+        <v>52.2072677612305</v>
       </c>
       <c r="H1889" t="n">
         <v>2997</v>
@@ -55266,7 +55266,7 @@
         <v>54</v>
       </c>
       <c r="G1893" t="n">
-        <v>52.2072639465332</v>
+        <v>52.2072677612305</v>
       </c>
       <c r="H1893" t="n">
         <v>870</v>
@@ -55440,7 +55440,7 @@
         <v>53</v>
       </c>
       <c r="G1899" t="n">
-        <v>51.2404670715332</v>
+        <v>51.2404632568359</v>
       </c>
       <c r="H1899" t="n">
         <v>4188</v>
@@ -55498,7 +55498,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1901" t="n">
-        <v>50.8537406921387</v>
+        <v>50.8537445068359</v>
       </c>
       <c r="H1901" t="n">
         <v>5689</v>
@@ -55614,7 +55614,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1905" t="n">
-        <v>50.6603889465332</v>
+        <v>50.6603851318359</v>
       </c>
       <c r="H1905" t="n">
         <v>2333</v>
@@ -55730,7 +55730,7 @@
         <v>52.5</v>
       </c>
       <c r="G1909" t="n">
-        <v>50.7570686340332</v>
+        <v>50.7570648193359</v>
       </c>
       <c r="H1909" t="n">
         <v>2398</v>
@@ -55759,7 +55759,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1910" t="n">
-        <v>50.6603889465332</v>
+        <v>50.6603851318359</v>
       </c>
       <c r="H1910" t="n">
         <v>2425</v>
@@ -55875,7 +55875,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G1914" t="n">
-        <v>49.0168228149414</v>
+        <v>49.0168266296387</v>
       </c>
       <c r="H1914" t="n">
         <v>8427</v>
@@ -55904,7 +55904,7 @@
         <v>50.5</v>
       </c>
       <c r="G1915" t="n">
-        <v>48.8234634399414</v>
+        <v>48.8234596252441</v>
       </c>
       <c r="H1915" t="n">
         <v>4977</v>
@@ -56020,7 +56020,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1919" t="n">
-        <v>50.6603889465332</v>
+        <v>50.6603851318359</v>
       </c>
       <c r="H1919" t="n">
         <v>3266</v>
@@ -56078,7 +56078,7 @@
         <v>52.5</v>
       </c>
       <c r="G1921" t="n">
-        <v>50.7570686340332</v>
+        <v>50.7570648193359</v>
       </c>
       <c r="H1921" t="n">
         <v>3895</v>
@@ -56339,7 +56339,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1930" t="n">
-        <v>52.4973068237305</v>
+        <v>52.4973030090332</v>
       </c>
       <c r="H1930" t="n">
         <v>7946</v>
@@ -56368,7 +56368,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1931" t="n">
-        <v>53.2707443237305</v>
+        <v>53.2707481384277</v>
       </c>
       <c r="H1931" t="n">
         <v>7341</v>
@@ -56774,7 +56774,7 @@
         <v>54</v>
       </c>
       <c r="G1945" t="n">
-        <v>52.2072639465332</v>
+        <v>52.2072677612305</v>
       </c>
       <c r="H1945" t="n">
         <v>14594</v>
@@ -56977,7 +56977,7 @@
         <v>49.25</v>
       </c>
       <c r="G1952" t="n">
-        <v>47.6149635314941</v>
+        <v>47.6149597167969</v>
       </c>
       <c r="H1952" t="n">
         <v>24970</v>
@@ -57064,7 +57064,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1955" t="n">
-        <v>47.2282409667969</v>
+        <v>47.2282371520996</v>
       </c>
       <c r="H1955" t="n">
         <v>7459</v>
@@ -57122,7 +57122,7 @@
         <v>49.25</v>
       </c>
       <c r="G1957" t="n">
-        <v>47.6149635314941</v>
+        <v>47.6149597167969</v>
       </c>
       <c r="H1957" t="n">
         <v>4605</v>
@@ -57267,7 +57267,7 @@
         <v>48.25</v>
       </c>
       <c r="G1962" t="n">
-        <v>46.6481590270996</v>
+        <v>46.6481628417969</v>
       </c>
       <c r="H1962" t="n">
         <v>12015</v>
@@ -57296,7 +57296,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G1963" t="n">
-        <v>45.5846786499023</v>
+        <v>45.5846824645996</v>
       </c>
       <c r="H1963" t="n">
         <v>10367</v>
@@ -57499,7 +57499,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1970" t="n">
-        <v>49.5969047546387</v>
+        <v>49.5969009399414</v>
       </c>
       <c r="H1970" t="n">
         <v>6798</v>
@@ -57557,7 +57557,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G1972" t="n">
-        <v>49.0168228149414</v>
+        <v>49.0168266296387</v>
       </c>
       <c r="H1972" t="n">
         <v>3589</v>
@@ -57586,7 +57586,7 @@
         <v>50.5</v>
       </c>
       <c r="G1973" t="n">
-        <v>48.8234634399414</v>
+        <v>48.8234596252441</v>
       </c>
       <c r="H1973" t="n">
         <v>2070</v>
@@ -57615,7 +57615,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1974" t="n">
-        <v>49.5969047546387</v>
+        <v>49.5969009399414</v>
       </c>
       <c r="H1974" t="n">
         <v>3776</v>
@@ -68609,9 +68609,38 @@
         <v>71.6999969482422</v>
       </c>
       <c r="H2353" t="n">
-        <v>8955</v>
+        <v>8962</v>
       </c>
       <c r="I2353" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2354" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2354" t="n">
+        <v>72.0999984741211</v>
+      </c>
+      <c r="D2354" t="n">
+        <v>72.0999984741211</v>
+      </c>
+      <c r="E2354" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="F2354" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="G2354" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="H2354" t="n">
+        <v>26338</v>
+      </c>
+      <c r="I2354" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>11.8307571411133</v>
+        <v>11.8307590484619</v>
       </c>
       <c r="H2" t="n">
         <v>167700</v>
@@ -485,7 +485,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G4" t="n">
-        <v>11.1796007156372</v>
+        <v>11.1795997619629</v>
       </c>
       <c r="H4" t="n">
         <v>83600</v>
@@ -601,7 +601,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G8" t="n">
-        <v>10.9005355834961</v>
+        <v>10.9005336761475</v>
       </c>
       <c r="H8" t="n">
         <v>13200</v>
@@ -659,7 +659,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1711454391479</v>
+        <v>11.1711444854736</v>
       </c>
       <c r="H10" t="n">
         <v>5500</v>
@@ -688,7 +688,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G11" t="n">
-        <v>11.2726240158081</v>
+        <v>11.2726230621338</v>
       </c>
       <c r="H11" t="n">
         <v>2400</v>
@@ -717,7 +717,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G12" t="n">
-        <v>11.1880569458008</v>
+        <v>11.1880578994751</v>
       </c>
       <c r="H12" t="n">
         <v>2200</v>
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H13" t="n">
         <v>7400</v>
@@ -804,7 +804,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G15" t="n">
-        <v>11.0781230926514</v>
+        <v>11.0781221389771</v>
       </c>
       <c r="H15" t="n">
         <v>2900</v>
@@ -862,7 +862,7 @@
         <v>13.3299999237061</v>
       </c>
       <c r="G17" t="n">
-        <v>11.2726240158081</v>
+        <v>11.2726230621338</v>
       </c>
       <c r="H17" t="n">
         <v>2700</v>
@@ -891,7 +891,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G18" t="n">
-        <v>11.1034917831421</v>
+        <v>11.1034927368164</v>
       </c>
       <c r="H18" t="n">
         <v>3600</v>
@@ -920,7 +920,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>11.0358381271362</v>
+        <v>11.0358400344849</v>
       </c>
       <c r="H19" t="n">
         <v>1100</v>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H20" t="n">
         <v>2800</v>
@@ -978,7 +978,7 @@
         <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H21" t="n">
         <v>6300</v>
@@ -1007,7 +1007,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895364761353</v>
       </c>
       <c r="H22" t="n">
         <v>6300</v>
@@ -1065,7 +1065,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G24" t="n">
-        <v>10.9174470901489</v>
+        <v>10.9174461364746</v>
       </c>
       <c r="H24" t="n">
         <v>4500</v>
@@ -1094,7 +1094,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G25" t="n">
-        <v>11.1034917831421</v>
+        <v>11.1034927368164</v>
       </c>
       <c r="H25" t="n">
         <v>200</v>
@@ -1123,7 +1123,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>11.0781230926514</v>
+        <v>11.0781221389771</v>
       </c>
       <c r="H26" t="n">
         <v>2000</v>
@@ -1210,7 +1210,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>10.9850988388062</v>
+        <v>10.9850997924805</v>
       </c>
       <c r="H29" t="n">
         <v>3800</v>
@@ -1268,7 +1268,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H31" t="n">
         <v>4100</v>
@@ -1326,7 +1326,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H33" t="n">
         <v>4700</v>
@@ -1355,7 +1355,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7652282714844</v>
+        <v>10.7652292251587</v>
       </c>
       <c r="H34" t="n">
         <v>4500</v>
@@ -1384,7 +1384,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G35" t="n">
-        <v>10.6468353271484</v>
+        <v>10.6468362808228</v>
       </c>
       <c r="H35" t="n">
         <v>10800</v>
@@ -1442,7 +1442,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>10.942816734314</v>
+        <v>10.9428157806396</v>
       </c>
       <c r="H37" t="n">
         <v>2100</v>
@@ -1471,7 +1471,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G38" t="n">
-        <v>10.9343585968018</v>
+        <v>10.9343595504761</v>
       </c>
       <c r="H38" t="n">
         <v>1700</v>
@@ -1558,7 +1558,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0781230926514</v>
+        <v>11.0781221389771</v>
       </c>
       <c r="H41" t="n">
         <v>3100</v>
@@ -1587,7 +1587,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G42" t="n">
-        <v>11.2387981414795</v>
+        <v>11.2387971878052</v>
       </c>
       <c r="H42" t="n">
         <v>13400</v>
@@ -1616,7 +1616,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>11.6700820922852</v>
+        <v>11.6700830459595</v>
       </c>
       <c r="H43" t="n">
         <v>18500</v>
@@ -1645,7 +1645,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G44" t="n">
-        <v>11.6700820922852</v>
+        <v>11.6700830459595</v>
       </c>
       <c r="H44" t="n">
         <v>27300</v>
@@ -1674,7 +1674,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G45" t="n">
-        <v>11.8223009109497</v>
+        <v>11.8222999572754</v>
       </c>
       <c r="H45" t="n">
         <v>38700</v>
@@ -1703,7 +1703,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.6447143554688</v>
+        <v>11.6447124481201</v>
       </c>
       <c r="H46" t="n">
         <v>24300</v>
@@ -1732,7 +1732,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6447143554688</v>
+        <v>11.6447124481201</v>
       </c>
       <c r="H47" t="n">
         <v>9700</v>
@@ -1848,7 +1848,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G51" t="n">
-        <v>11.4671239852905</v>
+        <v>11.4671258926392</v>
       </c>
       <c r="H51" t="n">
         <v>500</v>
@@ -1877,7 +1877,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.458667755127</v>
+        <v>11.4586687088013</v>
       </c>
       <c r="H52" t="n">
         <v>1500</v>
@@ -1935,7 +1935,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895364761353</v>
       </c>
       <c r="H54" t="n">
         <v>1300</v>
@@ -1964,7 +1964,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>11.3318195343018</v>
+        <v>11.3318176269531</v>
       </c>
       <c r="H55" t="n">
         <v>34600</v>
@@ -1993,7 +1993,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>11.281081199646</v>
+        <v>11.2810792922974</v>
       </c>
       <c r="H56" t="n">
         <v>7600</v>
@@ -2022,7 +2022,7 @@
         <v>13.25</v>
       </c>
       <c r="G57" t="n">
-        <v>11.2049694061279</v>
+        <v>11.2049703598022</v>
       </c>
       <c r="H57" t="n">
         <v>2500</v>
@@ -2080,7 +2080,7 @@
         <v>13</v>
       </c>
       <c r="G59" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H59" t="n">
         <v>9700</v>
@@ -2196,7 +2196,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G63" t="n">
-        <v>11.0527515411377</v>
+        <v>11.052752494812</v>
       </c>
       <c r="H63" t="n">
         <v>13700</v>
@@ -2225,7 +2225,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G64" t="n">
-        <v>11.1542301177979</v>
+        <v>11.1542310714722</v>
       </c>
       <c r="H64" t="n">
         <v>1500</v>
@@ -2254,7 +2254,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>10.942816734314</v>
+        <v>10.9428157806396</v>
       </c>
       <c r="H65" t="n">
         <v>1100</v>
@@ -2283,7 +2283,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>11.0020141601562</v>
+        <v>11.0020122528076</v>
       </c>
       <c r="H66" t="n">
         <v>3400</v>
@@ -2399,7 +2399,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G70" t="n">
-        <v>10.8328800201416</v>
+        <v>10.8328809738159</v>
       </c>
       <c r="H70" t="n">
         <v>3300</v>
@@ -2428,7 +2428,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G71" t="n">
-        <v>10.8328800201416</v>
+        <v>10.8328809738159</v>
       </c>
       <c r="H71" t="n">
         <v>900</v>
@@ -2573,7 +2573,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8328800201416</v>
+        <v>10.8328809738159</v>
       </c>
       <c r="H76" t="n">
         <v>1600</v>
@@ -2689,7 +2689,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>10.9005355834961</v>
+        <v>10.9005336761475</v>
       </c>
       <c r="H80" t="n">
         <v>1200</v>
@@ -2718,7 +2718,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>10.9259033203125</v>
+        <v>10.9259042739868</v>
       </c>
       <c r="H81" t="n">
         <v>1600</v>
@@ -2776,7 +2776,7 @@
         <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H83" t="n">
         <v>6800</v>
@@ -2863,7 +2863,7 @@
         <v>12.5</v>
       </c>
       <c r="G86" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H86" t="n">
         <v>1600</v>
@@ -2892,7 +2892,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G87" t="n">
-        <v>10.6806631088257</v>
+        <v>10.6806640625</v>
       </c>
       <c r="H87" t="n">
         <v>800</v>
@@ -2921,7 +2921,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G88" t="n">
-        <v>10.6637477874756</v>
+        <v>10.6637487411499</v>
       </c>
       <c r="H88" t="n">
         <v>20600</v>
@@ -2950,7 +2950,7 @@
         <v>13</v>
       </c>
       <c r="G89" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H89" t="n">
         <v>43500</v>
@@ -2979,7 +2979,7 @@
         <v>13</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H90" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G91" t="n">
-        <v>10.9850988388062</v>
+        <v>10.9850997924805</v>
       </c>
       <c r="H91" t="n">
         <v>3900</v>
@@ -3066,7 +3066,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.6383790969849</v>
+        <v>10.6383781433105</v>
       </c>
       <c r="H93" t="n">
         <v>3300</v>
@@ -3095,7 +3095,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G94" t="n">
-        <v>10.6383790969849</v>
+        <v>10.6383781433105</v>
       </c>
       <c r="H94" t="n">
         <v>200</v>
@@ -3124,7 +3124,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H95" t="n">
         <v>1700</v>
@@ -3153,7 +3153,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>12.75</v>
       </c>
       <c r="G101" t="n">
-        <v>10.7821426391602</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H101" t="n">
         <v>7700</v>
@@ -3385,7 +3385,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G104" t="n">
-        <v>10.7144889831543</v>
+        <v>10.7144899368286</v>
       </c>
       <c r="H104" t="n">
         <v>300</v>
@@ -3414,7 +3414,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G105" t="n">
-        <v>10.6806631088257</v>
+        <v>10.6806640625</v>
       </c>
       <c r="H105" t="n">
         <v>100</v>
@@ -3443,7 +3443,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G106" t="n">
-        <v>10.8497934341431</v>
+        <v>10.8497943878174</v>
       </c>
       <c r="H106" t="n">
         <v>500</v>
@@ -3501,7 +3501,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G108" t="n">
-        <v>10.8328800201416</v>
+        <v>10.8328809738159</v>
       </c>
       <c r="H108" t="n">
         <v>5200</v>
@@ -3530,7 +3530,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G109" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H109" t="n">
         <v>600</v>
@@ -3559,7 +3559,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>10.7990560531616</v>
+        <v>10.7990550994873</v>
       </c>
       <c r="H110" t="n">
         <v>700</v>
@@ -3588,7 +3588,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.7060327529907</v>
+        <v>10.706033706665</v>
       </c>
       <c r="H111" t="n">
         <v>7100</v>
@@ -3617,7 +3617,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G112" t="n">
-        <v>10.7060327529907</v>
+        <v>10.706033706665</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G113" t="n">
-        <v>10.7060327529907</v>
+        <v>10.706033706665</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G114" t="n">
-        <v>10.7060327529907</v>
+        <v>10.706033706665</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H115" t="n">
         <v>600</v>
@@ -3733,7 +3733,7 @@
         <v>12.75</v>
       </c>
       <c r="G116" t="n">
-        <v>10.7821426391602</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H116" t="n">
         <v>1500</v>
@@ -3762,7 +3762,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H117" t="n">
         <v>3300</v>
@@ -3791,7 +3791,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H118" t="n">
         <v>1000</v>
@@ -3820,7 +3820,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.4861631393433</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H119" t="n">
         <v>1200</v>
@@ -3849,7 +3849,7 @@
         <v>12.5</v>
       </c>
       <c r="G120" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H120" t="n">
         <v>1800</v>
@@ -3965,7 +3965,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H124" t="n">
         <v>1000</v>
@@ -3994,7 +3994,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H125" t="n">
         <v>1300</v>
@@ -4023,7 +4023,7 @@
         <v>12.5</v>
       </c>
       <c r="G126" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H126" t="n">
         <v>1100</v>
@@ -4052,7 +4052,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H127" t="n">
         <v>200</v>
@@ -4081,7 +4081,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H128" t="n">
         <v>800</v>
@@ -4110,7 +4110,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H131" t="n">
         <v>1200</v>
@@ -4197,7 +4197,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>10.4861631393433</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H136" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>10.4015951156616</v>
+        <v>10.4015970230103</v>
       </c>
       <c r="H138" t="n">
         <v>6500</v>
@@ -4400,7 +4400,7 @@
         <v>12.25</v>
       </c>
       <c r="G139" t="n">
-        <v>10.3593139648438</v>
+        <v>10.3593120574951</v>
       </c>
       <c r="H139" t="n">
         <v>18900</v>
@@ -4429,7 +4429,7 @@
         <v>12.75</v>
       </c>
       <c r="G140" t="n">
-        <v>10.7821426391602</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H140" t="n">
         <v>21700</v>
@@ -4458,7 +4458,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>10.6975765228271</v>
+        <v>10.6975755691528</v>
       </c>
       <c r="H141" t="n">
         <v>3500</v>
@@ -4487,7 +4487,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>10.5284452438354</v>
+        <v>10.5284442901611</v>
       </c>
       <c r="H142" t="n">
         <v>800</v>
@@ -4516,7 +4516,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>10.5284452438354</v>
+        <v>10.5284442901611</v>
       </c>
       <c r="H143" t="n">
         <v>1800</v>
@@ -4574,7 +4574,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>10.4861631393433</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H145" t="n">
         <v>8600</v>
@@ -4632,7 +4632,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>10.4861631393433</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H147" t="n">
         <v>500</v>
@@ -4661,7 +4661,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>10.4861631393433</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H148" t="n">
         <v>4000</v>
@@ -4690,7 +4690,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>10.1901807785034</v>
+        <v>10.1901817321777</v>
       </c>
       <c r="H149" t="n">
         <v>10500</v>
@@ -4719,7 +4719,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>10.4861631393433</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H150" t="n">
         <v>2300</v>
@@ -4748,7 +4748,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>10.4861631393433</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H151" t="n">
         <v>1600</v>
@@ -4777,7 +4777,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>10.4861631393433</v>
+        <v>10.4861612319946</v>
       </c>
       <c r="H152" t="n">
         <v>800</v>
@@ -4806,7 +4806,7 @@
         <v>13</v>
       </c>
       <c r="G153" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H153" t="n">
         <v>6700</v>
@@ -5038,7 +5038,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H161" t="n">
         <v>2200</v>
@@ -5067,7 +5067,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G163" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G165" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>12.5</v>
       </c>
       <c r="G167" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H167" t="n">
         <v>3800</v>
@@ -5241,7 +5241,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>10.7398595809937</v>
+        <v>10.7398586273193</v>
       </c>
       <c r="H168" t="n">
         <v>12000</v>
@@ -5270,7 +5270,7 @@
         <v>12.5</v>
       </c>
       <c r="G169" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H169" t="n">
         <v>500</v>
@@ -5299,7 +5299,7 @@
         <v>12.75</v>
       </c>
       <c r="G170" t="n">
-        <v>10.7821426391602</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H170" t="n">
         <v>8800</v>
@@ -5328,7 +5328,7 @@
         <v>12.75</v>
       </c>
       <c r="G171" t="n">
-        <v>10.7821426391602</v>
+        <v>10.7821407318115</v>
       </c>
       <c r="H171" t="n">
         <v>400</v>
@@ -5357,7 +5357,7 @@
         <v>12.5</v>
       </c>
       <c r="G172" t="n">
-        <v>10.5707263946533</v>
+        <v>10.5707273483276</v>
       </c>
       <c r="H172" t="n">
         <v>800</v>
@@ -5386,7 +5386,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>10.5284452438354</v>
+        <v>10.5284442901611</v>
       </c>
       <c r="H173" t="n">
         <v>4300</v>
@@ -5415,7 +5415,7 @@
         <v>13</v>
       </c>
       <c r="G174" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H174" t="n">
         <v>41300</v>
@@ -5618,7 +5618,7 @@
         <v>13</v>
       </c>
       <c r="G181" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H181" t="n">
         <v>900</v>
@@ -5647,7 +5647,7 @@
         <v>13</v>
       </c>
       <c r="G182" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H182" t="n">
         <v>1300</v>
@@ -5676,7 +5676,7 @@
         <v>13</v>
       </c>
       <c r="G183" t="n">
-        <v>10.9935550689697</v>
+        <v>10.993556022644</v>
       </c>
       <c r="H183" t="n">
         <v>4000</v>
@@ -5763,7 +5763,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895364761353</v>
       </c>
       <c r="H186" t="n">
         <v>11400</v>
@@ -5792,7 +5792,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>11.3318195343018</v>
+        <v>11.3318176269531</v>
       </c>
       <c r="H187" t="n">
         <v>10200</v>
@@ -5821,7 +5821,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895364761353</v>
       </c>
       <c r="H188" t="n">
         <v>2000</v>
@@ -5850,7 +5850,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>11.2472515106201</v>
+        <v>11.2472534179688</v>
       </c>
       <c r="H189" t="n">
         <v>100</v>
@@ -5879,7 +5879,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>11.0358381271362</v>
+        <v>11.0358400344849</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5908,7 +5908,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>11.2895374298096</v>
+        <v>11.2895364761353</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -5937,7 +5937,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>11.3318195343018</v>
+        <v>11.3318176269531</v>
       </c>
       <c r="H192" t="n">
         <v>900</v>
@@ -5966,7 +5966,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G193" t="n">
-        <v>11.2472515106201</v>
+        <v>11.2472534179688</v>
       </c>
       <c r="H193" t="n">
         <v>1600</v>
@@ -5995,7 +5995,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>11.3318195343018</v>
+        <v>11.3318176269531</v>
       </c>
       <c r="H194" t="n">
         <v>25800</v>
@@ -6024,7 +6024,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>11.3741016387939</v>
+        <v>11.3741025924683</v>
       </c>
       <c r="H195" t="n">
         <v>2100</v>
@@ -6053,7 +6053,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>11.458667755127</v>
+        <v>11.4586687088013</v>
       </c>
       <c r="H196" t="n">
         <v>2000</v>
@@ -6082,7 +6082,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>11.458667755127</v>
+        <v>11.4586687088013</v>
       </c>
       <c r="H197" t="n">
         <v>400</v>
@@ -6111,7 +6111,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.3318195343018</v>
+        <v>11.3318176269531</v>
       </c>
       <c r="H198" t="n">
         <v>8700</v>
@@ -6372,7 +6372,7 @@
         <v>13.25</v>
       </c>
       <c r="G207" t="n">
-        <v>11.4836158752441</v>
+        <v>11.4836168289185</v>
       </c>
       <c r="H207" t="n">
         <v>7400</v>
@@ -6401,7 +6401,7 @@
         <v>13.25</v>
       </c>
       <c r="G208" t="n">
-        <v>11.4836158752441</v>
+        <v>11.4836168289185</v>
       </c>
       <c r="H208" t="n">
         <v>400</v>
@@ -6459,7 +6459,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>11.6136207580566</v>
+        <v>11.613618850708</v>
       </c>
       <c r="H210" t="n">
         <v>3600</v>
@@ -6517,7 +6517,7 @@
         <v>13.75</v>
       </c>
       <c r="G212" t="n">
-        <v>11.9169607162476</v>
+        <v>11.9169597625732</v>
       </c>
       <c r="H212" t="n">
         <v>5600</v>
@@ -6546,7 +6546,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>11.6569538116455</v>
+        <v>11.6569557189941</v>
       </c>
       <c r="H213" t="n">
         <v>4500</v>
@@ -6604,7 +6604,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436246871948</v>
       </c>
       <c r="H215" t="n">
         <v>700</v>
@@ -6633,7 +6633,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436246871948</v>
       </c>
       <c r="H216" t="n">
         <v>1800</v>
@@ -6662,7 +6662,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G217" t="n">
-        <v>11.8736276626587</v>
+        <v>11.8736267089844</v>
       </c>
       <c r="H217" t="n">
         <v>2900</v>
@@ -6691,7 +6691,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436246871948</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>11.5269508361816</v>
+        <v>11.526951789856</v>
       </c>
       <c r="H219" t="n">
         <v>3200</v>
@@ -6778,7 +6778,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436246871948</v>
       </c>
       <c r="H221" t="n">
         <v>1500</v>
@@ -6807,7 +6807,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.6569538116455</v>
+        <v>11.6569557189941</v>
       </c>
       <c r="H222" t="n">
         <v>1900</v>
@@ -6836,7 +6836,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436246871948</v>
       </c>
       <c r="H223" t="n">
         <v>41700</v>
@@ -6923,7 +6923,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>11.8736276626587</v>
+        <v>11.8736267089844</v>
       </c>
       <c r="H226" t="n">
         <v>3400</v>
@@ -6952,7 +6952,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>11.9602956771851</v>
+        <v>11.9602966308594</v>
       </c>
       <c r="H227" t="n">
         <v>5400</v>
@@ -6981,7 +6981,7 @@
         <v>13.75</v>
       </c>
       <c r="G228" t="n">
-        <v>11.9169607162476</v>
+        <v>11.9169597625732</v>
       </c>
       <c r="H228" t="n">
         <v>2700</v>
@@ -7039,7 +7039,7 @@
         <v>13.75</v>
       </c>
       <c r="G230" t="n">
-        <v>11.9169607162476</v>
+        <v>11.9169597625732</v>
       </c>
       <c r="H230" t="n">
         <v>2100</v>
@@ -7126,7 +7126,7 @@
         <v>13.75</v>
       </c>
       <c r="G233" t="n">
-        <v>11.9169607162476</v>
+        <v>11.9169597625732</v>
       </c>
       <c r="H233" t="n">
         <v>2200</v>
@@ -7184,7 +7184,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>11.7436237335205</v>
+        <v>11.7436246871948</v>
       </c>
       <c r="H235" t="n">
         <v>2900</v>
@@ -7387,7 +7387,7 @@
         <v>14.5</v>
       </c>
       <c r="G242" t="n">
-        <v>12.5669775009155</v>
+        <v>12.5669765472412</v>
       </c>
       <c r="H242" t="n">
         <v>25500</v>
@@ -7445,7 +7445,7 @@
         <v>14.5</v>
       </c>
       <c r="G244" t="n">
-        <v>12.5669775009155</v>
+        <v>12.5669765472412</v>
       </c>
       <c r="H244" t="n">
         <v>5900</v>
@@ -7503,7 +7503,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>12.6969804763794</v>
+        <v>12.6969795227051</v>
       </c>
       <c r="H246" t="n">
         <v>4900</v>
@@ -7561,7 +7561,7 @@
         <v>15</v>
       </c>
       <c r="G248" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H248" t="n">
         <v>2600</v>
@@ -7648,7 +7648,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H251" t="n">
         <v>12100</v>
@@ -7677,7 +7677,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H252" t="n">
         <v>2300</v>
@@ -7706,7 +7706,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H253" t="n">
         <v>4100</v>
@@ -7735,7 +7735,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8703184127808</v>
+        <v>12.8703174591064</v>
       </c>
       <c r="H254" t="n">
         <v>1600</v>
@@ -7764,7 +7764,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>13.0436563491821</v>
+        <v>13.0436544418335</v>
       </c>
       <c r="H255" t="n">
         <v>12700</v>
@@ -7851,7 +7851,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>12.9569864273071</v>
+        <v>12.9569873809814</v>
       </c>
       <c r="H258" t="n">
         <v>100</v>
@@ -7880,7 +7880,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>12.8269834518433</v>
+        <v>12.8269853591919</v>
       </c>
       <c r="H259" t="n">
         <v>1300</v>
@@ -7938,7 +7938,7 @@
         <v>15</v>
       </c>
       <c r="G261" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H261" t="n">
         <v>1800</v>
@@ -7967,7 +7967,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H262" t="n">
         <v>5400</v>
@@ -8025,7 +8025,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H264" t="n">
         <v>2000</v>
@@ -8054,7 +8054,7 @@
         <v>15.25</v>
       </c>
       <c r="G265" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H265" t="n">
         <v>4200</v>
@@ -8083,7 +8083,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G266" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H266" t="n">
         <v>4600</v>
@@ -8141,7 +8141,7 @@
         <v>15</v>
       </c>
       <c r="G268" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H268" t="n">
         <v>3000</v>
@@ -8257,7 +8257,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H272" t="n">
         <v>400</v>
@@ -8344,7 +8344,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H275" t="n">
         <v>1600</v>
@@ -8373,7 +8373,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H276" t="n">
         <v>800</v>
@@ -8402,7 +8402,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H277" t="n">
         <v>300</v>
@@ -8547,7 +8547,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8605,7 +8605,7 @@
         <v>15.25</v>
       </c>
       <c r="G284" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H284" t="n">
         <v>100</v>
@@ -8634,7 +8634,7 @@
         <v>15.25</v>
       </c>
       <c r="G285" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H285" t="n">
         <v>800</v>
@@ -8663,7 +8663,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H286" t="n">
         <v>25700</v>
@@ -8692,7 +8692,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H287" t="n">
         <v>400</v>
@@ -8721,7 +8721,7 @@
         <v>15.25</v>
       </c>
       <c r="G288" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H288" t="n">
         <v>1900</v>
@@ -8779,7 +8779,7 @@
         <v>15.25</v>
       </c>
       <c r="G290" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H290" t="n">
         <v>700</v>
@@ -8808,7 +8808,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H291" t="n">
         <v>2500</v>
@@ -8866,7 +8866,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H293" t="n">
         <v>800</v>
@@ -8953,7 +8953,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H296" t="n">
         <v>25700</v>
@@ -8982,7 +8982,7 @@
         <v>15.5</v>
       </c>
       <c r="G297" t="n">
-        <v>13.4336652755737</v>
+        <v>13.433666229248</v>
       </c>
       <c r="H297" t="n">
         <v>13600</v>
@@ -9098,7 +9098,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H301" t="n">
         <v>2000</v>
@@ -9156,7 +9156,7 @@
         <v>15.25</v>
       </c>
       <c r="G303" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H303" t="n">
         <v>600</v>
@@ -9185,7 +9185,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G304" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H304" t="n">
         <v>900</v>
@@ -9214,7 +9214,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H305" t="n">
         <v>12300</v>
@@ -9243,7 +9243,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H306" t="n">
         <v>1200</v>
@@ -9272,7 +9272,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H307" t="n">
         <v>6600</v>
@@ -9301,7 +9301,7 @@
         <v>15.75</v>
       </c>
       <c r="G308" t="n">
-        <v>13.6503381729126</v>
+        <v>13.6503372192383</v>
       </c>
       <c r="H308" t="n">
         <v>15600</v>
@@ -9330,7 +9330,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H309" t="n">
         <v>2700</v>
@@ -9417,7 +9417,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H312" t="n">
         <v>11300</v>
@@ -9446,7 +9446,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H313" t="n">
         <v>9400</v>
@@ -9475,7 +9475,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H314" t="n">
         <v>3300</v>
@@ -9562,7 +9562,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H317" t="n">
         <v>1900</v>
@@ -9591,7 +9591,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H318" t="n">
         <v>1500</v>
@@ -9649,7 +9649,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H320" t="n">
         <v>1400</v>
@@ -9678,7 +9678,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H321" t="n">
         <v>2200</v>
@@ -9736,7 +9736,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H323" t="n">
         <v>1900</v>
@@ -9765,7 +9765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H324" t="n">
         <v>2600</v>
@@ -9794,7 +9794,7 @@
         <v>15.25</v>
       </c>
       <c r="G325" t="n">
-        <v>13.2169923782349</v>
+        <v>13.2169933319092</v>
       </c>
       <c r="H325" t="n">
         <v>2200</v>
@@ -9823,7 +9823,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H326" t="n">
         <v>2300</v>
@@ -9852,7 +9852,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H327" t="n">
         <v>1900</v>
@@ -9881,7 +9881,7 @@
         <v>15</v>
       </c>
       <c r="G328" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H328" t="n">
         <v>11200</v>
@@ -9910,7 +9910,7 @@
         <v>15</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0003213882446</v>
+        <v>13.0003223419189</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>15.5</v>
       </c>
       <c r="G330" t="n">
-        <v>13.4336652755737</v>
+        <v>13.433666229248</v>
       </c>
       <c r="H330" t="n">
         <v>800</v>
@@ -9968,7 +9968,7 @@
         <v>15.5</v>
       </c>
       <c r="G331" t="n">
-        <v>13.4336652755737</v>
+        <v>13.433666229248</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H332" t="n">
         <v>30500</v>
@@ -10026,7 +10026,7 @@
         <v>15.75</v>
       </c>
       <c r="G333" t="n">
-        <v>13.6503381729126</v>
+        <v>13.6503372192383</v>
       </c>
       <c r="H333" t="n">
         <v>1000</v>
@@ -10055,7 +10055,7 @@
         <v>15.5</v>
       </c>
       <c r="G334" t="n">
-        <v>13.4336652755737</v>
+        <v>13.433666229248</v>
       </c>
       <c r="H334" t="n">
         <v>7500</v>
@@ -10084,7 +10084,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H338" t="n">
         <v>1000</v>
@@ -10200,7 +10200,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H339" t="n">
         <v>1000</v>
@@ -10229,7 +10229,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H341" t="n">
         <v>200</v>
@@ -10316,7 +10316,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G343" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H343" t="n">
         <v>500</v>
@@ -10345,7 +10345,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H344" t="n">
         <v>5200</v>
@@ -10374,7 +10374,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H345" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H346" t="n">
         <v>1200</v>
@@ -10432,7 +10432,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>13.2603273391724</v>
+        <v>13.2603282928467</v>
       </c>
       <c r="H347" t="n">
         <v>600</v>
@@ -10461,7 +10461,7 @@
         <v>15.75</v>
       </c>
       <c r="G348" t="n">
-        <v>13.6503381729126</v>
+        <v>13.6503372192383</v>
       </c>
       <c r="H348" t="n">
         <v>1900</v>
@@ -10490,7 +10490,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H349" t="n">
         <v>3400</v>
@@ -10519,7 +10519,7 @@
         <v>15.75</v>
       </c>
       <c r="G350" t="n">
-        <v>13.6503381729126</v>
+        <v>13.6503372192383</v>
       </c>
       <c r="H350" t="n">
         <v>500</v>
@@ -10548,7 +10548,7 @@
         <v>15.5</v>
       </c>
       <c r="G351" t="n">
-        <v>13.4336652755737</v>
+        <v>13.433666229248</v>
       </c>
       <c r="H351" t="n">
         <v>1400</v>
@@ -10577,7 +10577,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H352" t="n">
         <v>4000</v>
@@ -10635,7 +10635,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>13.5203351974487</v>
+        <v>13.5203342437744</v>
       </c>
       <c r="H354" t="n">
         <v>3600</v>
@@ -10722,7 +10722,7 @@
         <v>15.75</v>
       </c>
       <c r="G357" t="n">
-        <v>13.6503381729126</v>
+        <v>13.6503372192383</v>
       </c>
       <c r="H357" t="n">
         <v>4100</v>
@@ -10780,7 +10780,7 @@
         <v>15.5</v>
       </c>
       <c r="G359" t="n">
-        <v>13.4336652755737</v>
+        <v>13.433666229248</v>
       </c>
       <c r="H359" t="n">
         <v>200</v>
@@ -10838,7 +10838,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H361" t="n">
         <v>900</v>
@@ -10867,7 +10867,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G365" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H365" t="n">
         <v>1300</v>
@@ -11012,7 +11012,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H368" t="n">
         <v>1200</v>
@@ -11070,7 +11070,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>13.086989402771</v>
+        <v>13.0869903564453</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H370" t="n">
         <v>1000</v>
@@ -11128,7 +11128,7 @@
         <v>15.5</v>
       </c>
       <c r="G371" t="n">
-        <v>13.4336652755737</v>
+        <v>13.433666229248</v>
       </c>
       <c r="H371" t="n">
         <v>400</v>
@@ -11157,7 +11157,7 @@
         <v>15.5</v>
       </c>
       <c r="G372" t="n">
-        <v>13.4336652755737</v>
+        <v>13.433666229248</v>
       </c>
       <c r="H372" t="n">
         <v>1000</v>
@@ -11244,7 +11244,7 @@
         <v>15.5</v>
       </c>
       <c r="G375" t="n">
-        <v>13.4336652755737</v>
+        <v>13.433666229248</v>
       </c>
       <c r="H375" t="n">
         <v>1000</v>
@@ -11273,7 +11273,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>13.5636682510376</v>
+        <v>13.5636692047119</v>
       </c>
       <c r="H376" t="n">
         <v>2300</v>
@@ -11360,7 +11360,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H379" t="n">
         <v>6400</v>
@@ -11418,7 +11418,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H381" t="n">
         <v>800</v>
@@ -11447,7 +11447,7 @@
         <v>15.5</v>
       </c>
       <c r="G382" t="n">
-        <v>13.4336652755737</v>
+        <v>13.433666229248</v>
       </c>
       <c r="H382" t="n">
         <v>300</v>
@@ -11505,7 +11505,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>13.3469972610474</v>
+        <v>13.3469953536987</v>
       </c>
       <c r="H384" t="n">
         <v>300</v>
@@ -11534,7 +11534,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>13.4770002365112</v>
+        <v>13.4769992828369</v>
       </c>
       <c r="H385" t="n">
         <v>200</v>
@@ -11563,7 +11563,7 @@
         <v>15.75</v>
       </c>
       <c r="G386" t="n">
-        <v>13.6503381729126</v>
+        <v>13.6503372192383</v>
       </c>
       <c r="H386" t="n">
         <v>8100</v>
@@ -11592,7 +11592,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1270160675049</v>
+        <v>14.1270141601562</v>
       </c>
       <c r="H387" t="n">
         <v>5300</v>
@@ -11621,7 +11621,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>14.2136840820312</v>
+        <v>14.2136850357056</v>
       </c>
       <c r="H388" t="n">
         <v>3100</v>
@@ -11650,7 +11650,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G389" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H389" t="n">
         <v>3500</v>
@@ -11679,7 +11679,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>14.6470289230347</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H390" t="n">
         <v>10000</v>
@@ -11708,7 +11708,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.6470289230347</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H391" t="n">
         <v>7500</v>
@@ -11737,7 +11737,7 @@
         <v>17.25</v>
       </c>
       <c r="G392" t="n">
-        <v>14.9503698348999</v>
+        <v>14.9503679275513</v>
       </c>
       <c r="H392" t="n">
         <v>5500</v>
@@ -11766,7 +11766,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070358276367</v>
       </c>
       <c r="H393" t="n">
         <v>3100</v>
@@ -11795,7 +11795,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>14.6903629302979</v>
+        <v>14.6903667449951</v>
       </c>
       <c r="H394" t="n">
         <v>3700</v>
@@ -11824,7 +11824,7 @@
         <v>17</v>
       </c>
       <c r="G395" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H395" t="n">
         <v>3200</v>
@@ -11853,7 +11853,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H396" t="n">
         <v>2400</v>
@@ -11882,7 +11882,7 @@
         <v>16.75</v>
       </c>
       <c r="G397" t="n">
-        <v>14.5170278549194</v>
+        <v>14.5170249938965</v>
       </c>
       <c r="H397" t="n">
         <v>4600</v>
@@ -11911,7 +11911,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>14.5603580474854</v>
+        <v>14.5603609085083</v>
       </c>
       <c r="H398" t="n">
         <v>300</v>
@@ -11940,7 +11940,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>14.6470289230347</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H399" t="n">
         <v>1200</v>
@@ -11969,7 +11969,7 @@
         <v>17</v>
       </c>
       <c r="G400" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H400" t="n">
         <v>3000</v>
@@ -11998,7 +11998,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036958694458</v>
       </c>
       <c r="H401" t="n">
         <v>500</v>
@@ -12027,7 +12027,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>14.3870229721069</v>
+        <v>14.3870210647583</v>
       </c>
       <c r="H402" t="n">
         <v>1500</v>
@@ -12056,7 +12056,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G403" t="n">
-        <v>14.6470289230347</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H403" t="n">
         <v>900</v>
@@ -12085,7 +12085,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>14.5603580474854</v>
+        <v>14.5603609085083</v>
       </c>
       <c r="H404" t="n">
         <v>2900</v>
@@ -12114,7 +12114,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>14.5603580474854</v>
+        <v>14.5603609085083</v>
       </c>
       <c r="H405" t="n">
         <v>2000</v>
@@ -12143,7 +12143,7 @@
         <v>17</v>
       </c>
       <c r="G406" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H406" t="n">
         <v>3400</v>
@@ -12172,7 +12172,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>14.6470289230347</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H407" t="n">
         <v>5600</v>
@@ -12201,7 +12201,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>14.6903629302979</v>
+        <v>14.6903667449951</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>14.6903629302979</v>
+        <v>14.6903667449951</v>
       </c>
       <c r="H409" t="n">
         <v>2600</v>
@@ -12259,7 +12259,7 @@
         <v>17</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H410" t="n">
         <v>6700</v>
@@ -12288,7 +12288,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G411" t="n">
-        <v>14.6903629302979</v>
+        <v>14.6903667449951</v>
       </c>
       <c r="H411" t="n">
         <v>9500</v>
@@ -12317,7 +12317,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G412" t="n">
-        <v>14.6903629302979</v>
+        <v>14.6903667449951</v>
       </c>
       <c r="H412" t="n">
         <v>3600</v>
@@ -12346,7 +12346,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6903629302979</v>
+        <v>14.6903667449951</v>
       </c>
       <c r="H413" t="n">
         <v>2000</v>
@@ -12375,7 +12375,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G414" t="n">
-        <v>14.7770299911499</v>
+        <v>14.7770309448242</v>
       </c>
       <c r="H414" t="n">
         <v>900</v>
@@ -12404,7 +12404,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036958694458</v>
       </c>
       <c r="H415" t="n">
         <v>1700</v>
@@ -12433,7 +12433,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>14.6470289230347</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H416" t="n">
         <v>2000</v>
@@ -12462,7 +12462,7 @@
         <v>16.75</v>
       </c>
       <c r="G417" t="n">
-        <v>14.5170278549194</v>
+        <v>14.5170249938965</v>
       </c>
       <c r="H417" t="n">
         <v>15600</v>
@@ -12491,7 +12491,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H418" t="n">
         <v>15800</v>
@@ -12520,7 +12520,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H419" t="n">
         <v>1300</v>
@@ -12549,7 +12549,7 @@
         <v>16.5</v>
       </c>
       <c r="G420" t="n">
-        <v>14.3003530502319</v>
+        <v>14.3003540039062</v>
       </c>
       <c r="H420" t="n">
         <v>25000</v>
@@ -12578,7 +12578,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>14.4303560256958</v>
+        <v>14.4303550720215</v>
       </c>
       <c r="H421" t="n">
         <v>4300</v>
@@ -12607,7 +12607,7 @@
         <v>16.5</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3003530502319</v>
+        <v>14.3003540039062</v>
       </c>
       <c r="H422" t="n">
         <v>4000</v>
@@ -12665,7 +12665,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>14.2570209503174</v>
+        <v>14.2570199966431</v>
       </c>
       <c r="H424" t="n">
         <v>3100</v>
@@ -12694,7 +12694,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>14.3870229721069</v>
+        <v>14.3870210647583</v>
       </c>
       <c r="H425" t="n">
         <v>4300</v>
@@ -12723,7 +12723,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036958694458</v>
       </c>
       <c r="H426" t="n">
         <v>4900</v>
@@ -12752,7 +12752,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>14.3870229721069</v>
+        <v>14.3870210647583</v>
       </c>
       <c r="H427" t="n">
         <v>600</v>
@@ -12781,7 +12781,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>14.2570209503174</v>
+        <v>14.2570199966431</v>
       </c>
       <c r="H428" t="n">
         <v>9500</v>
@@ -12810,7 +12810,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>14.6470289230347</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H429" t="n">
         <v>11700</v>
@@ -12839,7 +12839,7 @@
         <v>17</v>
       </c>
       <c r="G430" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H430" t="n">
         <v>8300</v>
@@ -12868,7 +12868,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>14.4736919403076</v>
+        <v>14.4736909866333</v>
       </c>
       <c r="H431" t="n">
         <v>3900</v>
@@ -12897,7 +12897,7 @@
         <v>17</v>
       </c>
       <c r="G432" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H432" t="n">
         <v>4100</v>
@@ -12926,7 +12926,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036958694458</v>
       </c>
       <c r="H433" t="n">
         <v>3000</v>
@@ -12955,7 +12955,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>14.6470289230347</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H434" t="n">
         <v>700</v>
@@ -12984,7 +12984,7 @@
         <v>17</v>
       </c>
       <c r="G435" t="n">
-        <v>14.7336978912354</v>
+        <v>14.733696937561</v>
       </c>
       <c r="H435" t="n">
         <v>3600</v>
@@ -13013,7 +13013,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>14.6903629302979</v>
+        <v>14.6903667449951</v>
       </c>
       <c r="H436" t="n">
         <v>2900</v>
@@ -13042,7 +13042,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>14.6470289230347</v>
+        <v>14.6470279693604</v>
       </c>
       <c r="H437" t="n">
         <v>2300</v>
@@ -13071,7 +13071,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>14.6903629302979</v>
+        <v>14.6903667449951</v>
       </c>
       <c r="H438" t="n">
         <v>3800</v>
@@ -13100,7 +13100,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>14.8203678131104</v>
+        <v>14.8203649520874</v>
       </c>
       <c r="H439" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>14.8203678131104</v>
+        <v>14.8203649520874</v>
       </c>
       <c r="H440" t="n">
         <v>3000</v>
@@ -13158,7 +13158,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>14.8203678131104</v>
+        <v>14.8203649520874</v>
       </c>
       <c r="H441" t="n">
         <v>600</v>
@@ -13187,7 +13187,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>14.8203678131104</v>
+        <v>14.8203649520874</v>
       </c>
       <c r="H442" t="n">
         <v>3700</v>
@@ -13216,7 +13216,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G443" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070358276367</v>
       </c>
       <c r="H443" t="n">
         <v>14843</v>
@@ -13245,7 +13245,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G444" t="n">
-        <v>14.6036949157715</v>
+        <v>14.6036958694458</v>
       </c>
       <c r="H444" t="n">
         <v>3486</v>
@@ -13303,7 +13303,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G446" t="n">
-        <v>14.907036781311</v>
+        <v>14.9070358276367</v>
       </c>
       <c r="H446" t="n">
         <v>3301</v>
@@ -13332,7 +13332,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>14.8203678131104</v>
+        <v>14.8203649520874</v>
       </c>
       <c r="H447" t="n">
         <v>37419</v>
@@ -13361,7 +13361,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G448" t="n">
-        <v>14.7770299911499</v>
+        <v>14.7770309448242</v>
       </c>
       <c r="H448" t="n">
         <v>885</v>
@@ -13390,7 +13390,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>15.0370388031006</v>
+        <v>15.0370378494263</v>
       </c>
       <c r="H449" t="n">
         <v>3162</v>
@@ -13535,7 +13535,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>15.526535987854</v>
+        <v>15.5265378952026</v>
       </c>
       <c r="H454" t="n">
         <v>4000</v>
@@ -13564,7 +13564,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>15.526535987854</v>
+        <v>15.5265378952026</v>
       </c>
       <c r="H455" t="n">
         <v>10462</v>
@@ -13593,7 +13593,7 @@
         <v>17.25</v>
       </c>
       <c r="G456" t="n">
-        <v>15.3926877975464</v>
+        <v>15.3926868438721</v>
       </c>
       <c r="H456" t="n">
         <v>5156</v>
@@ -13622,7 +13622,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>15.526535987854</v>
+        <v>15.5265378952026</v>
       </c>
       <c r="H457" t="n">
         <v>880</v>
@@ -13651,7 +13651,7 @@
         <v>17.25</v>
       </c>
       <c r="G458" t="n">
-        <v>15.3926877975464</v>
+        <v>15.3926868438721</v>
       </c>
       <c r="H458" t="n">
         <v>6310</v>
@@ -13680,7 +13680,7 @@
         <v>17</v>
       </c>
       <c r="G459" t="n">
-        <v>15.1696062088013</v>
+        <v>15.169605255127</v>
       </c>
       <c r="H459" t="n">
         <v>20546</v>
@@ -13709,7 +13709,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>15.0803728103638</v>
+        <v>15.0803718566895</v>
       </c>
       <c r="H460" t="n">
         <v>2407</v>
@@ -13738,7 +13738,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>15.2142210006714</v>
+        <v>15.21422290802</v>
       </c>
       <c r="H461" t="n">
         <v>4400</v>
@@ -13767,7 +13767,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>14.991138458252</v>
+        <v>14.9911403656006</v>
       </c>
       <c r="H462" t="n">
         <v>599</v>
@@ -13796,7 +13796,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G463" t="n">
-        <v>15.1249895095825</v>
+        <v>15.1249923706055</v>
       </c>
       <c r="H463" t="n">
         <v>771</v>
@@ -13825,7 +13825,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>15.4373054504395</v>
+        <v>15.4373035430908</v>
       </c>
       <c r="H464" t="n">
         <v>1237</v>
@@ -13854,7 +13854,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>15.3480730056763</v>
+        <v>15.348072052002</v>
       </c>
       <c r="H465" t="n">
         <v>9270</v>
@@ -13883,7 +13883,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>15.3480730056763</v>
+        <v>15.348072052002</v>
       </c>
       <c r="H466" t="n">
         <v>3452</v>
@@ -13912,7 +13912,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>15.3480730056763</v>
+        <v>15.348072052002</v>
       </c>
       <c r="H467" t="n">
         <v>30811</v>
@@ -13941,7 +13941,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>15.4373054504395</v>
+        <v>15.4373035430908</v>
       </c>
       <c r="H468" t="n">
         <v>1311</v>
@@ -13999,7 +13999,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>15.8834686279297</v>
+        <v>15.883469581604</v>
       </c>
       <c r="H470" t="n">
         <v>9513</v>
@@ -14028,7 +14028,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>15.8834686279297</v>
+        <v>15.883469581604</v>
       </c>
       <c r="H471" t="n">
         <v>3677</v>
@@ -14057,7 +14057,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G472" t="n">
-        <v>16.7758007049561</v>
+        <v>16.7757987976074</v>
       </c>
       <c r="H472" t="n">
         <v>10770</v>
@@ -14086,7 +14086,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G473" t="n">
-        <v>17.5788974761963</v>
+        <v>17.5788955688477</v>
       </c>
       <c r="H473" t="n">
         <v>51869</v>
@@ -14202,7 +14202,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G477" t="n">
-        <v>17.1327342987061</v>
+        <v>17.1327323913574</v>
       </c>
       <c r="H477" t="n">
         <v>16785</v>
@@ -14231,7 +14231,7 @@
         <v>19.5</v>
       </c>
       <c r="G478" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H478" t="n">
         <v>16646</v>
@@ -14289,7 +14289,7 @@
         <v>19.5</v>
       </c>
       <c r="G480" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H480" t="n">
         <v>6935</v>
@@ -14318,7 +14318,7 @@
         <v>19.5</v>
       </c>
       <c r="G481" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H481" t="n">
         <v>8270</v>
@@ -14347,7 +14347,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>17.2219638824463</v>
+        <v>17.2219619750977</v>
       </c>
       <c r="H482" t="n">
         <v>2971</v>
@@ -14376,7 +14376,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>17.4450454711914</v>
+        <v>17.4450435638428</v>
       </c>
       <c r="H483" t="n">
         <v>4149</v>
@@ -14405,7 +14405,7 @@
         <v>19.25</v>
       </c>
       <c r="G484" t="n">
-        <v>17.1773490905762</v>
+        <v>17.1773471832275</v>
       </c>
       <c r="H484" t="n">
         <v>531</v>
@@ -14434,7 +14434,7 @@
         <v>19.25</v>
       </c>
       <c r="G485" t="n">
-        <v>17.1773490905762</v>
+        <v>17.1773471832275</v>
       </c>
       <c r="H485" t="n">
         <v>662</v>
@@ -14463,7 +14463,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G486" t="n">
-        <v>17.3111953735352</v>
+        <v>17.3111972808838</v>
       </c>
       <c r="H486" t="n">
         <v>305</v>
@@ -14492,7 +14492,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H487" t="n">
         <v>5816</v>
@@ -14521,7 +14521,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>17.4450454711914</v>
+        <v>17.4450435638428</v>
       </c>
       <c r="H488" t="n">
         <v>2521</v>
@@ -14550,7 +14550,7 @@
         <v>19.5</v>
       </c>
       <c r="G489" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H489" t="n">
         <v>2164</v>
@@ -14695,7 +14695,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>18.5604610443115</v>
+        <v>18.5604572296143</v>
       </c>
       <c r="H494" t="n">
         <v>3493</v>
@@ -14753,7 +14753,7 @@
         <v>21</v>
       </c>
       <c r="G496" t="n">
-        <v>18.7389240264893</v>
+        <v>18.7389259338379</v>
       </c>
       <c r="H496" t="n">
         <v>12906</v>
@@ -14840,7 +14840,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>18.5604610443115</v>
+        <v>18.5604572296143</v>
       </c>
       <c r="H499" t="n">
         <v>5362</v>
@@ -14869,7 +14869,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>18.5604610443115</v>
+        <v>18.5604572296143</v>
       </c>
       <c r="H500" t="n">
         <v>4065</v>
@@ -14898,7 +14898,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G501" t="n">
-        <v>18.4712238311768</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H501" t="n">
         <v>3610</v>
@@ -14956,7 +14956,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>18.3819923400879</v>
+        <v>18.3819942474365</v>
       </c>
       <c r="H503" t="n">
         <v>4027</v>
@@ -15014,7 +15014,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G505" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H505" t="n">
         <v>2052</v>
@@ -15043,7 +15043,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H506" t="n">
         <v>8048</v>
@@ -15188,7 +15188,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H511" t="n">
         <v>2701</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H512" t="n">
         <v>3189</v>
@@ -15246,7 +15246,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>17.4450454711914</v>
+        <v>17.4450435638428</v>
       </c>
       <c r="H513" t="n">
         <v>3700</v>
@@ -15275,7 +15275,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>17.4450454711914</v>
+        <v>17.4450435638428</v>
       </c>
       <c r="H514" t="n">
         <v>5110</v>
@@ -15362,7 +15362,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G517" t="n">
-        <v>17.5788974761963</v>
+        <v>17.5788955688477</v>
       </c>
       <c r="H517" t="n">
         <v>9741</v>
@@ -15420,7 +15420,7 @@
         <v>19.75</v>
       </c>
       <c r="G519" t="n">
-        <v>17.6235103607178</v>
+        <v>17.6235122680664</v>
       </c>
       <c r="H519" t="n">
         <v>3789</v>
@@ -15449,7 +15449,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>17.2219638824463</v>
+        <v>17.2219619750977</v>
       </c>
       <c r="H520" t="n">
         <v>1635</v>
@@ -15478,7 +15478,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>17.3111953735352</v>
+        <v>17.3111972808838</v>
       </c>
       <c r="H521" t="n">
         <v>2284</v>
@@ -15507,7 +15507,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>17.2665786743164</v>
+        <v>17.2665824890137</v>
       </c>
       <c r="H522" t="n">
         <v>1999</v>
@@ -15536,7 +15536,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>17.2665786743164</v>
+        <v>17.2665824890137</v>
       </c>
       <c r="H523" t="n">
         <v>5001</v>
@@ -15565,7 +15565,7 @@
         <v>19.5</v>
       </c>
       <c r="G524" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H524" t="n">
         <v>2311</v>
@@ -15594,7 +15594,7 @@
         <v>19.5</v>
       </c>
       <c r="G525" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H525" t="n">
         <v>4044</v>
@@ -15623,7 +15623,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>17.3111953735352</v>
+        <v>17.3111972808838</v>
       </c>
       <c r="H526" t="n">
         <v>7865</v>
@@ -15652,7 +15652,7 @@
         <v>19.5</v>
       </c>
       <c r="G527" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H527" t="n">
         <v>1461</v>
@@ -15681,7 +15681,7 @@
         <v>19.5</v>
       </c>
       <c r="G528" t="n">
-        <v>17.4004287719727</v>
+        <v>17.4004306793213</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>17.4896659851074</v>
+        <v>17.4896621704102</v>
       </c>
       <c r="H529" t="n">
         <v>1050</v>
@@ -15739,7 +15739,7 @@
         <v>19.25</v>
       </c>
       <c r="G530" t="n">
-        <v>17.1773490905762</v>
+        <v>17.1773471832275</v>
       </c>
       <c r="H530" t="n">
         <v>851</v>
@@ -15768,7 +15768,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>17.4450454711914</v>
+        <v>17.4450435638428</v>
       </c>
       <c r="H531" t="n">
         <v>1036</v>
@@ -15797,7 +15797,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G532" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H532" t="n">
         <v>1402</v>
@@ -15826,7 +15826,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>17.7573585510254</v>
+        <v>17.757360458374</v>
       </c>
       <c r="H533" t="n">
         <v>1112</v>
@@ -15855,7 +15855,7 @@
         <v>20</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H534" t="n">
         <v>2224</v>
@@ -15884,7 +15884,7 @@
         <v>20</v>
       </c>
       <c r="G535" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H535" t="n">
         <v>4616</v>
@@ -15942,7 +15942,7 @@
         <v>20</v>
       </c>
       <c r="G537" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H537" t="n">
         <v>2250</v>
@@ -15971,7 +15971,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H538" t="n">
         <v>10406</v>
@@ -16000,7 +16000,7 @@
         <v>20</v>
       </c>
       <c r="G539" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H539" t="n">
         <v>1256</v>
@@ -16029,7 +16029,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H540" t="n">
         <v>5116</v>
@@ -16058,7 +16058,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G541" t="n">
-        <v>18.3819923400879</v>
+        <v>18.3819942474365</v>
       </c>
       <c r="H541" t="n">
         <v>2182</v>
@@ -16116,7 +16116,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>18.4712238311768</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H543" t="n">
         <v>2090</v>
@@ -16145,7 +16145,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>18.4712238311768</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H544" t="n">
         <v>2060</v>
@@ -16174,7 +16174,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>18.4712238311768</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H545" t="n">
         <v>2697</v>
@@ -16203,7 +16203,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H546" t="n">
         <v>720</v>
@@ -16232,7 +16232,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>18.4712238311768</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H547" t="n">
         <v>603</v>
@@ -16261,7 +16261,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H548" t="n">
         <v>4408</v>
@@ -16319,7 +16319,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G550" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H550" t="n">
         <v>9268</v>
@@ -16377,7 +16377,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G552" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H552" t="n">
         <v>5016</v>
@@ -16406,7 +16406,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G553" t="n">
-        <v>18.3819923400879</v>
+        <v>18.3819942474365</v>
       </c>
       <c r="H553" t="n">
         <v>3343</v>
@@ -16464,7 +16464,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G555" t="n">
-        <v>18.5604610443115</v>
+        <v>18.5604572296143</v>
       </c>
       <c r="H555" t="n">
         <v>7200</v>
@@ -16493,7 +16493,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H556" t="n">
         <v>4973</v>
@@ -16522,7 +16522,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H557" t="n">
         <v>1111</v>
@@ -16580,7 +16580,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>17.7127475738525</v>
+        <v>17.7127456665039</v>
       </c>
       <c r="H559" t="n">
         <v>1400</v>
@@ -16609,7 +16609,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H560" t="n">
         <v>12249</v>
@@ -16638,7 +16638,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>17.7127475738525</v>
+        <v>17.7127456665039</v>
       </c>
       <c r="H561" t="n">
         <v>5664</v>
@@ -16696,7 +16696,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H563" t="n">
         <v>2101</v>
@@ -16754,7 +16754,7 @@
         <v>20</v>
       </c>
       <c r="G565" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H565" t="n">
         <v>2880</v>
@@ -16783,7 +16783,7 @@
         <v>20</v>
       </c>
       <c r="G566" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H566" t="n">
         <v>2491</v>
@@ -16812,7 +16812,7 @@
         <v>20</v>
       </c>
       <c r="G567" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H567" t="n">
         <v>2423</v>
@@ -16841,7 +16841,7 @@
         <v>20</v>
       </c>
       <c r="G568" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H568" t="n">
         <v>5106</v>
@@ -16899,7 +16899,7 @@
         <v>20</v>
       </c>
       <c r="G570" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H570" t="n">
         <v>534</v>
@@ -16928,7 +16928,7 @@
         <v>20</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H571" t="n">
         <v>1494</v>
@@ -16957,7 +16957,7 @@
         <v>20</v>
       </c>
       <c r="G572" t="n">
-        <v>17.8465976715088</v>
+        <v>17.8465957641602</v>
       </c>
       <c r="H572" t="n">
         <v>126</v>
@@ -16986,7 +16986,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H573" t="n">
         <v>1276</v>
@@ -17015,7 +17015,7 @@
         <v>19.75</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6235103607178</v>
+        <v>17.6235122680664</v>
       </c>
       <c r="H574" t="n">
         <v>1476</v>
@@ -17044,7 +17044,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H575" t="n">
         <v>12920</v>
@@ -17073,7 +17073,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H576" t="n">
         <v>6126</v>
@@ -17102,7 +17102,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H577" t="n">
         <v>3426</v>
@@ -17189,7 +17189,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H580" t="n">
         <v>11118</v>
@@ -17218,7 +17218,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>18.1142921447754</v>
+        <v>18.114294052124</v>
       </c>
       <c r="H581" t="n">
         <v>1397</v>
@@ -17247,7 +17247,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H582" t="n">
         <v>3500</v>
@@ -17276,7 +17276,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H583" t="n">
         <v>26</v>
@@ -17305,7 +17305,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>18.2035274505615</v>
+        <v>18.2035293579102</v>
       </c>
       <c r="H584" t="n">
         <v>1966</v>
@@ -17334,7 +17334,7 @@
         <v>21</v>
       </c>
       <c r="G585" t="n">
-        <v>18.7389240264893</v>
+        <v>18.7389259338379</v>
       </c>
       <c r="H585" t="n">
         <v>62155</v>
@@ -17421,7 +17421,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>19.0066242218018</v>
+        <v>19.0066223144531</v>
       </c>
       <c r="H588" t="n">
         <v>3033</v>
@@ -17450,7 +17450,7 @@
         <v>21.5</v>
       </c>
       <c r="G589" t="n">
-        <v>19.1850910186768</v>
+        <v>19.1850891113281</v>
       </c>
       <c r="H589" t="n">
         <v>3910</v>
@@ -17479,7 +17479,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>19.4527893066406</v>
+        <v>19.4527854919434</v>
       </c>
       <c r="H590" t="n">
         <v>27442</v>
@@ -17508,7 +17508,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>19.4527893066406</v>
+        <v>19.4527854919434</v>
       </c>
       <c r="H591" t="n">
         <v>2820</v>
@@ -17537,7 +17537,7 @@
         <v>21.5</v>
       </c>
       <c r="G592" t="n">
-        <v>19.1850910186768</v>
+        <v>19.1850891113281</v>
       </c>
       <c r="H592" t="n">
         <v>14908</v>
@@ -17624,7 +17624,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>19.4527893066406</v>
+        <v>19.4527854919434</v>
       </c>
       <c r="H595" t="n">
         <v>7478</v>
@@ -17682,7 +17682,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>19.8097229003906</v>
+        <v>19.809720993042</v>
       </c>
       <c r="H597" t="n">
         <v>6848</v>
@@ -17798,7 +17798,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H601" t="n">
         <v>2527</v>
@@ -17885,7 +17885,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>19.8097229003906</v>
+        <v>19.809720993042</v>
       </c>
       <c r="H604" t="n">
         <v>6581</v>
@@ -17943,7 +17943,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H606" t="n">
         <v>2280</v>
@@ -17972,7 +17972,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H607" t="n">
         <v>3152</v>
@@ -18001,7 +18001,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G608" t="n">
-        <v>19.4527893066406</v>
+        <v>19.4527854919434</v>
       </c>
       <c r="H608" t="n">
         <v>8174</v>
@@ -18175,7 +18175,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H614" t="n">
         <v>2737</v>
@@ -18204,7 +18204,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>19.8097229003906</v>
+        <v>19.809720993042</v>
       </c>
       <c r="H615" t="n">
         <v>420</v>
@@ -18291,7 +18291,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G618" t="n">
-        <v>20.7020492553711</v>
+        <v>20.7020511627197</v>
       </c>
       <c r="H618" t="n">
         <v>17175</v>
@@ -18320,7 +18320,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>20.7020492553711</v>
+        <v>20.7020511627197</v>
       </c>
       <c r="H619" t="n">
         <v>10967</v>
@@ -18349,7 +18349,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>21.1482181549072</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H620" t="n">
         <v>3563</v>
@@ -18378,7 +18378,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>20.8805160522461</v>
+        <v>20.8805141448975</v>
       </c>
       <c r="H621" t="n">
         <v>2225</v>
@@ -18436,7 +18436,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G623" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H623" t="n">
         <v>4899</v>
@@ -18465,7 +18465,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>21.1482181549072</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H624" t="n">
         <v>4403</v>
@@ -18494,7 +18494,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>20.8805160522461</v>
+        <v>20.8805141448975</v>
       </c>
       <c r="H625" t="n">
         <v>3148</v>
@@ -18552,7 +18552,7 @@
         <v>24.5</v>
       </c>
       <c r="G627" t="n">
-        <v>21.86208152771</v>
+        <v>21.8620758056641</v>
       </c>
       <c r="H627" t="n">
         <v>11972</v>
@@ -18581,7 +18581,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>21.7728424072266</v>
+        <v>21.7728462219238</v>
       </c>
       <c r="H628" t="n">
         <v>3942</v>
@@ -18610,7 +18610,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G629" t="n">
-        <v>21.9513111114502</v>
+        <v>21.9513130187988</v>
       </c>
       <c r="H629" t="n">
         <v>6820</v>
@@ -18668,7 +18668,7 @@
         <v>24</v>
       </c>
       <c r="G631" t="n">
-        <v>21.4159107208252</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H631" t="n">
         <v>16893</v>
@@ -18842,7 +18842,7 @@
         <v>24</v>
       </c>
       <c r="G637" t="n">
-        <v>21.4159107208252</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H637" t="n">
         <v>11025</v>
@@ -18900,7 +18900,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>21.0589809417725</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H639" t="n">
         <v>5914</v>
@@ -18929,7 +18929,7 @@
         <v>23.5</v>
       </c>
       <c r="G640" t="n">
-        <v>20.9697494506836</v>
+        <v>20.9697513580322</v>
       </c>
       <c r="H640" t="n">
         <v>4685</v>
@@ -18958,7 +18958,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>21.1482181549072</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H641" t="n">
         <v>1401</v>
@@ -18987,7 +18987,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>21.0589809417725</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H642" t="n">
         <v>2409</v>
@@ -19074,7 +19074,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G645" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H645" t="n">
         <v>5975</v>
@@ -19103,7 +19103,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H646" t="n">
         <v>1770</v>
@@ -19132,7 +19132,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>21.1482181549072</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H647" t="n">
         <v>2283</v>
@@ -19161,7 +19161,7 @@
         <v>24</v>
       </c>
       <c r="G648" t="n">
-        <v>21.4159107208252</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H648" t="n">
         <v>6636</v>
@@ -19190,7 +19190,7 @@
         <v>24</v>
       </c>
       <c r="G649" t="n">
-        <v>21.4159107208252</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H649" t="n">
         <v>10221</v>
@@ -19219,7 +19219,7 @@
         <v>24</v>
       </c>
       <c r="G650" t="n">
-        <v>21.4159107208252</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H650" t="n">
         <v>3081</v>
@@ -19248,7 +19248,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H651" t="n">
         <v>3427</v>
@@ -19277,7 +19277,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>21.1482181549072</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H652" t="n">
         <v>1361</v>
@@ -19306,7 +19306,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H653" t="n">
         <v>746</v>
@@ -19335,7 +19335,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G654" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H654" t="n">
         <v>675</v>
@@ -19364,7 +19364,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G655" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H655" t="n">
         <v>11198</v>
@@ -19393,7 +19393,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>21.1482181549072</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H656" t="n">
         <v>4430</v>
@@ -19480,7 +19480,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G659" t="n">
-        <v>20.2558841705322</v>
+        <v>20.2558860778809</v>
       </c>
       <c r="H659" t="n">
         <v>9014</v>
@@ -19509,7 +19509,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>20.7020492553711</v>
+        <v>20.7020511627197</v>
       </c>
       <c r="H660" t="n">
         <v>2179</v>
@@ -19538,7 +19538,7 @@
         <v>23.5</v>
       </c>
       <c r="G661" t="n">
-        <v>20.9697494506836</v>
+        <v>20.9697513580322</v>
       </c>
       <c r="H661" t="n">
         <v>6201</v>
@@ -19654,7 +19654,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H665" t="n">
         <v>8640</v>
@@ -19712,7 +19712,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.5420207977295</v>
+        <v>19.5420227050781</v>
       </c>
       <c r="H667" t="n">
         <v>10615</v>
@@ -19741,7 +19741,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>19.0066242218018</v>
+        <v>19.0066223144531</v>
       </c>
       <c r="H668" t="n">
         <v>4049</v>
@@ -19828,7 +19828,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G671" t="n">
-        <v>17.5342788696289</v>
+        <v>17.5342769622803</v>
       </c>
       <c r="H671" t="n">
         <v>4618</v>
@@ -19886,7 +19886,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>17.4896659851074</v>
+        <v>17.4896621704102</v>
       </c>
       <c r="H673" t="n">
         <v>2591</v>
@@ -19915,7 +19915,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>16.1957855224609</v>
+        <v>16.1957836151123</v>
       </c>
       <c r="H674" t="n">
         <v>4844</v>
@@ -19973,7 +19973,7 @@
         <v>17.5</v>
       </c>
       <c r="G676" t="n">
-        <v>15.6157732009888</v>
+        <v>15.6157703399658</v>
       </c>
       <c r="H676" t="n">
         <v>12149</v>
@@ -20002,7 +20002,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>14.9019088745117</v>
+        <v>14.9019069671631</v>
       </c>
       <c r="H677" t="n">
         <v>5955</v>
@@ -20031,7 +20031,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>15.035756111145</v>
+        <v>15.0357580184937</v>
       </c>
       <c r="H678" t="n">
         <v>6939</v>
@@ -20118,7 +20118,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>18.4712238311768</v>
+        <v>18.4712257385254</v>
       </c>
       <c r="H681" t="n">
         <v>24241</v>
@@ -20147,7 +20147,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>18.5604610443115</v>
+        <v>18.5604572296143</v>
       </c>
       <c r="H682" t="n">
         <v>3394</v>
@@ -20205,7 +20205,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>19.0066242218018</v>
+        <v>19.0066223144531</v>
       </c>
       <c r="H684" t="n">
         <v>1114</v>
@@ -20263,7 +20263,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>20.2558841705322</v>
+        <v>20.2558860778809</v>
       </c>
       <c r="H686" t="n">
         <v>17625</v>
@@ -20350,7 +20350,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G689" t="n">
-        <v>21.1482181549072</v>
+        <v>21.1482162475586</v>
       </c>
       <c r="H689" t="n">
         <v>5460</v>
@@ -20408,7 +20408,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>20.8805160522461</v>
+        <v>20.8805141448975</v>
       </c>
       <c r="H691" t="n">
         <v>1329</v>
@@ -20437,7 +20437,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>20.8805160522461</v>
+        <v>20.8805141448975</v>
       </c>
       <c r="H692" t="n">
         <v>2028</v>
@@ -20466,7 +20466,7 @@
         <v>23.5</v>
       </c>
       <c r="G693" t="n">
-        <v>20.9697494506836</v>
+        <v>20.9697513580322</v>
       </c>
       <c r="H693" t="n">
         <v>3825</v>
@@ -20553,7 +20553,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G696" t="n">
-        <v>21.0589809417725</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H696" t="n">
         <v>6358</v>
@@ -20611,7 +20611,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H698" t="n">
         <v>3647</v>
@@ -20640,7 +20640,7 @@
         <v>24</v>
       </c>
       <c r="G699" t="n">
-        <v>21.4159107208252</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H699" t="n">
         <v>4272</v>
@@ -20669,7 +20669,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>21.0589809417725</v>
+        <v>21.0589828491211</v>
       </c>
       <c r="H700" t="n">
         <v>3057</v>
@@ -20698,7 +20698,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H701" t="n">
         <v>2334</v>
@@ -20727,7 +20727,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H702" t="n">
         <v>3693</v>
@@ -20756,7 +20756,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>21.326681137085</v>
+        <v>21.3266792297363</v>
       </c>
       <c r="H703" t="n">
         <v>4301</v>
@@ -20785,7 +20785,7 @@
         <v>24</v>
       </c>
       <c r="G704" t="n">
-        <v>21.4159107208252</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H704" t="n">
         <v>20313</v>
@@ -20843,7 +20843,7 @@
         <v>24</v>
       </c>
       <c r="G706" t="n">
-        <v>21.4159107208252</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H706" t="n">
         <v>2368</v>
@@ -20872,7 +20872,7 @@
         <v>24</v>
       </c>
       <c r="G707" t="n">
-        <v>21.4159107208252</v>
+        <v>21.4159126281738</v>
       </c>
       <c r="H707" t="n">
         <v>10495</v>
@@ -20959,7 +20959,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>22.0405426025391</v>
+        <v>22.0405464172363</v>
       </c>
       <c r="H710" t="n">
         <v>9060</v>
@@ -20988,7 +20988,7 @@
         <v>25</v>
       </c>
       <c r="G711" t="n">
-        <v>22.7315826416016</v>
+        <v>22.7315845489502</v>
       </c>
       <c r="H711" t="n">
         <v>5201</v>
@@ -21017,7 +21017,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>22.6406593322754</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H712" t="n">
         <v>5833</v>
@@ -21075,7 +21075,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H714" t="n">
         <v>3575</v>
@@ -21104,7 +21104,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H715" t="n">
         <v>1991</v>
@@ -21133,7 +21133,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H716" t="n">
         <v>3812</v>
@@ -21162,7 +21162,7 @@
         <v>24.5</v>
       </c>
       <c r="G717" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769508361816</v>
       </c>
       <c r="H717" t="n">
         <v>2681</v>
@@ -21191,7 +21191,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H718" t="n">
         <v>1554</v>
@@ -21220,7 +21220,7 @@
         <v>24.5</v>
       </c>
       <c r="G719" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769508361816</v>
       </c>
       <c r="H719" t="n">
         <v>565</v>
@@ -21278,7 +21278,7 @@
         <v>24.5</v>
       </c>
       <c r="G721" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769508361816</v>
       </c>
       <c r="H721" t="n">
         <v>484</v>
@@ -21307,7 +21307,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>22.6406593322754</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H722" t="n">
         <v>17150</v>
@@ -21365,7 +21365,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>22.6406593322754</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H724" t="n">
         <v>722</v>
@@ -21394,7 +21394,7 @@
         <v>24.5</v>
       </c>
       <c r="G725" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769508361816</v>
       </c>
       <c r="H725" t="n">
         <v>1685</v>
@@ -21423,7 +21423,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>22.549732208252</v>
+        <v>22.5497283935547</v>
       </c>
       <c r="H726" t="n">
         <v>1103</v>
@@ -21452,7 +21452,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>22.6406593322754</v>
+        <v>22.6406574249268</v>
       </c>
       <c r="H727" t="n">
         <v>412</v>
@@ -21481,7 +21481,7 @@
         <v>24.5</v>
       </c>
       <c r="G728" t="n">
-        <v>22.2769527435303</v>
+        <v>22.2769508361816</v>
       </c>
       <c r="H728" t="n">
         <v>11066</v>
@@ -21568,7 +21568,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>21.7313919067383</v>
+        <v>21.7313938140869</v>
       </c>
       <c r="H731" t="n">
         <v>1834</v>
@@ -21597,7 +21597,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G732" t="n">
-        <v>21.7313919067383</v>
+        <v>21.7313938140869</v>
       </c>
       <c r="H732" t="n">
         <v>4585</v>
@@ -21626,7 +21626,7 @@
         <v>24</v>
       </c>
       <c r="G733" t="n">
-        <v>21.8223190307617</v>
+        <v>21.8223209381104</v>
       </c>
       <c r="H733" t="n">
         <v>698</v>
@@ -21655,7 +21655,7 @@
         <v>23.5</v>
       </c>
       <c r="G734" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H734" t="n">
         <v>416</v>
@@ -21684,7 +21684,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H735" t="n">
         <v>5515</v>
@@ -21713,7 +21713,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H736" t="n">
         <v>1631</v>
@@ -21800,7 +21800,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H739" t="n">
         <v>7641</v>
@@ -21829,7 +21829,7 @@
         <v>23.5</v>
       </c>
       <c r="G740" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H740" t="n">
         <v>3450</v>
@@ -21858,7 +21858,7 @@
         <v>23.5</v>
       </c>
       <c r="G741" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H741" t="n">
         <v>767</v>
@@ -21887,7 +21887,7 @@
         <v>23.5</v>
       </c>
       <c r="G742" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H742" t="n">
         <v>1047</v>
@@ -21945,7 +21945,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H744" t="n">
         <v>1375</v>
@@ -22003,7 +22003,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H746" t="n">
         <v>1755</v>
@@ -22032,7 +22032,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H747" t="n">
         <v>103</v>
@@ -22061,7 +22061,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H748" t="n">
         <v>1173</v>
@@ -22090,7 +22090,7 @@
         <v>23.5</v>
       </c>
       <c r="G749" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H749" t="n">
         <v>979</v>
@@ -22119,7 +22119,7 @@
         <v>23.5</v>
       </c>
       <c r="G750" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H750" t="n">
         <v>3667</v>
@@ -22148,7 +22148,7 @@
         <v>24</v>
       </c>
       <c r="G751" t="n">
-        <v>21.8223190307617</v>
+        <v>21.8223209381104</v>
       </c>
       <c r="H751" t="n">
         <v>3728</v>
@@ -22177,7 +22177,7 @@
         <v>24</v>
       </c>
       <c r="G752" t="n">
-        <v>21.8223190307617</v>
+        <v>21.8223209381104</v>
       </c>
       <c r="H752" t="n">
         <v>3094</v>
@@ -22235,7 +22235,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G754" t="n">
-        <v>21.7313919067383</v>
+        <v>21.7313938140869</v>
       </c>
       <c r="H754" t="n">
         <v>1943</v>
@@ -22264,7 +22264,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>21.7313919067383</v>
+        <v>21.7313938140869</v>
       </c>
       <c r="H755" t="n">
         <v>912</v>
@@ -22293,7 +22293,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H756" t="n">
         <v>2089</v>
@@ -22322,7 +22322,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H757" t="n">
         <v>722</v>
@@ -22351,7 +22351,7 @@
         <v>23.5</v>
       </c>
       <c r="G758" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H758" t="n">
         <v>6240</v>
@@ -22380,7 +22380,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H759" t="n">
         <v>1830</v>
@@ -22438,7 +22438,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G761" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H761" t="n">
         <v>2011</v>
@@ -22467,7 +22467,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H762" t="n">
         <v>383</v>
@@ -22496,7 +22496,7 @@
         <v>23.5</v>
       </c>
       <c r="G763" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H763" t="n">
         <v>728</v>
@@ -22525,7 +22525,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H764" t="n">
         <v>3151</v>
@@ -22554,7 +22554,7 @@
         <v>23.5</v>
       </c>
       <c r="G765" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H765" t="n">
         <v>1731</v>
@@ -22612,7 +22612,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H767" t="n">
         <v>305</v>
@@ -22670,7 +22670,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G769" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H769" t="n">
         <v>3953</v>
@@ -22699,7 +22699,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>21.0949096679688</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H770" t="n">
         <v>305</v>
@@ -22728,7 +22728,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H771" t="n">
         <v>779</v>
@@ -22786,7 +22786,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>21.0949096679688</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H773" t="n">
         <v>688</v>
@@ -22815,7 +22815,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>21.0949096679688</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H774" t="n">
         <v>881</v>
@@ -22931,7 +22931,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H778" t="n">
         <v>340</v>
@@ -22960,7 +22960,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>21.5495452880859</v>
+        <v>21.5495433807373</v>
       </c>
       <c r="H779" t="n">
         <v>4210</v>
@@ -22989,7 +22989,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H780" t="n">
         <v>300</v>
@@ -23018,7 +23018,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H781" t="n">
         <v>278</v>
@@ -23047,7 +23047,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>21.0949096679688</v>
+        <v>21.0949115753174</v>
       </c>
       <c r="H782" t="n">
         <v>424</v>
@@ -23134,7 +23134,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>20.7312030792236</v>
+        <v>20.7312088012695</v>
       </c>
       <c r="H785" t="n">
         <v>294</v>
@@ -23163,7 +23163,7 @@
         <v>23.5</v>
       </c>
       <c r="G786" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H786" t="n">
         <v>19431</v>
@@ -23192,7 +23192,7 @@
         <v>23.5</v>
       </c>
       <c r="G787" t="n">
-        <v>21.3676891326904</v>
+        <v>21.3676910400391</v>
       </c>
       <c r="H787" t="n">
         <v>8270</v>
@@ -23221,7 +23221,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G788" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H788" t="n">
         <v>30</v>
@@ -23250,7 +23250,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>21.1858367919922</v>
+        <v>21.1858386993408</v>
       </c>
       <c r="H789" t="n">
         <v>8927</v>
@@ -23598,7 +23598,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>21.0039844512939</v>
+        <v>21.0039863586426</v>
       </c>
       <c r="H801" t="n">
         <v>1969</v>
@@ -23656,7 +23656,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>22.1860256195068</v>
+        <v>22.1860275268555</v>
       </c>
       <c r="H803" t="n">
         <v>3814</v>
@@ -23714,7 +23714,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>23.5499248504639</v>
+        <v>23.5499210357666</v>
       </c>
       <c r="H805" t="n">
         <v>15078</v>
@@ -23772,7 +23772,7 @@
         <v>27</v>
       </c>
       <c r="G807" t="n">
-        <v>24.5501136779785</v>
+        <v>24.5501098632812</v>
       </c>
       <c r="H807" t="n">
         <v>16372</v>
@@ -23830,7 +23830,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>23.0952911376953</v>
+        <v>23.0952892303467</v>
       </c>
       <c r="H809" t="n">
         <v>248720</v>
@@ -23859,7 +23859,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>23.3680686950684</v>
+        <v>23.368070602417</v>
       </c>
       <c r="H810" t="n">
         <v>2600</v>
@@ -23917,7 +23917,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>24.4591827392578</v>
+        <v>24.4591865539551</v>
       </c>
       <c r="H812" t="n">
         <v>2196</v>
@@ -23946,7 +23946,7 @@
         <v>26.5</v>
       </c>
       <c r="G813" t="n">
-        <v>24.0954780578613</v>
+        <v>24.09547996521</v>
       </c>
       <c r="H813" t="n">
         <v>742</v>
@@ -23975,7 +23975,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>24.2773342132568</v>
+        <v>24.2773323059082</v>
       </c>
       <c r="H814" t="n">
         <v>1094</v>
@@ -24004,7 +24004,7 @@
         <v>26.5</v>
       </c>
       <c r="G815" t="n">
-        <v>24.0954780578613</v>
+        <v>24.09547996521</v>
       </c>
       <c r="H815" t="n">
         <v>1378</v>
@@ -24033,7 +24033,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7319641113281</v>
+        <v>24.7319660186768</v>
       </c>
       <c r="H816" t="n">
         <v>19373</v>
@@ -24062,7 +24062,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G817" t="n">
-        <v>24.913818359375</v>
+        <v>24.9138164520264</v>
       </c>
       <c r="H817" t="n">
         <v>5600</v>
@@ -24091,7 +24091,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>24.913818359375</v>
+        <v>24.9138164520264</v>
       </c>
       <c r="H818" t="n">
         <v>1123</v>
@@ -24120,7 +24120,7 @@
         <v>27.5</v>
       </c>
       <c r="G819" t="n">
-        <v>25.0047435760498</v>
+        <v>25.0047416687012</v>
       </c>
       <c r="H819" t="n">
         <v>12457</v>
@@ -24149,7 +24149,7 @@
         <v>28</v>
       </c>
       <c r="G820" t="n">
-        <v>25.4593734741211</v>
+        <v>25.4593753814697</v>
       </c>
       <c r="H820" t="n">
         <v>21274</v>
@@ -24178,7 +24178,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>26.0049324035645</v>
+        <v>26.0049343109131</v>
       </c>
       <c r="H821" t="n">
         <v>17472</v>
@@ -24207,7 +24207,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>26.0958595275879</v>
+        <v>26.0958614349365</v>
       </c>
       <c r="H822" t="n">
         <v>12698</v>
@@ -24236,7 +24236,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>26.0958595275879</v>
+        <v>26.0958614349365</v>
       </c>
       <c r="H823" t="n">
         <v>9499</v>
@@ -24265,7 +24265,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>25.2775230407715</v>
+        <v>25.2775211334229</v>
       </c>
       <c r="H824" t="n">
         <v>9201</v>
@@ -24294,7 +24294,7 @@
         <v>27.5</v>
       </c>
       <c r="G825" t="n">
-        <v>25.0047435760498</v>
+        <v>25.0047416687012</v>
       </c>
       <c r="H825" t="n">
         <v>7361</v>
@@ -24410,7 +24410,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G829" t="n">
-        <v>24.913818359375</v>
+        <v>24.9138164520264</v>
       </c>
       <c r="H829" t="n">
         <v>1504</v>
@@ -24439,7 +24439,7 @@
         <v>27.5</v>
       </c>
       <c r="G830" t="n">
-        <v>25.0047435760498</v>
+        <v>25.0047416687012</v>
       </c>
       <c r="H830" t="n">
         <v>3462</v>
@@ -24497,7 +24497,7 @@
         <v>27</v>
       </c>
       <c r="G832" t="n">
-        <v>24.5501136779785</v>
+        <v>24.5501098632812</v>
       </c>
       <c r="H832" t="n">
         <v>462</v>
@@ -24555,7 +24555,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G834" t="n">
-        <v>24.1864070892334</v>
+        <v>24.1864051818848</v>
       </c>
       <c r="H834" t="n">
         <v>2244</v>
@@ -24584,7 +24584,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>24.2773342132568</v>
+        <v>24.2773323059082</v>
       </c>
       <c r="H835" t="n">
         <v>942</v>
@@ -24613,7 +24613,7 @@
         <v>27.5</v>
       </c>
       <c r="G836" t="n">
-        <v>25.0047435760498</v>
+        <v>25.0047416687012</v>
       </c>
       <c r="H836" t="n">
         <v>3180</v>
@@ -24671,7 +24671,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G838" t="n">
-        <v>26.0049324035645</v>
+        <v>26.0049343109131</v>
       </c>
       <c r="H838" t="n">
         <v>8817</v>
@@ -24729,7 +24729,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>25.5503005981445</v>
+        <v>25.5503044128418</v>
       </c>
       <c r="H840" t="n">
         <v>1023</v>
@@ -24787,7 +24787,7 @@
         <v>28</v>
       </c>
       <c r="G842" t="n">
-        <v>25.4593734741211</v>
+        <v>25.4593753814697</v>
       </c>
       <c r="H842" t="n">
         <v>1789</v>
@@ -24816,7 +24816,7 @@
         <v>28</v>
       </c>
       <c r="G843" t="n">
-        <v>25.4593734741211</v>
+        <v>25.4593753814697</v>
       </c>
       <c r="H843" t="n">
         <v>5435</v>
@@ -24845,7 +24845,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>26.1867828369141</v>
+        <v>26.1867847442627</v>
       </c>
       <c r="H844" t="n">
         <v>4971</v>
@@ -24874,7 +24874,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>26.2777137756348</v>
+        <v>26.2777118682861</v>
       </c>
       <c r="H845" t="n">
         <v>4924</v>
@@ -24903,7 +24903,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>26.2777137756348</v>
+        <v>26.2777118682861</v>
       </c>
       <c r="H846" t="n">
         <v>2260</v>
@@ -24932,7 +24932,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G847" t="n">
-        <v>26.0958595275879</v>
+        <v>26.0958614349365</v>
       </c>
       <c r="H847" t="n">
         <v>1305</v>
@@ -25019,7 +25019,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>25.5503005981445</v>
+        <v>25.5503044128418</v>
       </c>
       <c r="H850" t="n">
         <v>4390</v>
@@ -25048,7 +25048,7 @@
         <v>28</v>
       </c>
       <c r="G851" t="n">
-        <v>25.4593734741211</v>
+        <v>25.4593753814697</v>
       </c>
       <c r="H851" t="n">
         <v>3647</v>
@@ -25077,7 +25077,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>25.5503005981445</v>
+        <v>25.5503044128418</v>
       </c>
       <c r="H852" t="n">
         <v>2971</v>
@@ -25106,7 +25106,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>26.1867828369141</v>
+        <v>26.1867847442627</v>
       </c>
       <c r="H853" t="n">
         <v>2676</v>
@@ -25164,7 +25164,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>26.0049324035645</v>
+        <v>26.0049343109131</v>
       </c>
       <c r="H855" t="n">
         <v>2338</v>
@@ -25396,7 +25396,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>29.6419849395752</v>
+        <v>29.6419830322266</v>
       </c>
       <c r="H863" t="n">
         <v>5110</v>
@@ -25425,7 +25425,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G864" t="n">
-        <v>29.9147682189941</v>
+        <v>29.9147663116455</v>
       </c>
       <c r="H864" t="n">
         <v>1831</v>
@@ -25454,7 +25454,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>30.6421775817871</v>
+        <v>30.6421794891357</v>
       </c>
       <c r="H865" t="n">
         <v>13129</v>
@@ -25483,7 +25483,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G866" t="n">
-        <v>31.7332878112793</v>
+        <v>31.7332954406738</v>
       </c>
       <c r="H866" t="n">
         <v>25815</v>
@@ -25512,7 +25512,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>31.1877403259277</v>
+        <v>31.1877307891846</v>
       </c>
       <c r="H867" t="n">
         <v>9130</v>
@@ -25541,7 +25541,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>31.7332878112793</v>
+        <v>31.7332954406738</v>
       </c>
       <c r="H868" t="n">
         <v>10584</v>
@@ -25570,7 +25570,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>32.0060691833496</v>
+        <v>32.0060768127441</v>
       </c>
       <c r="H869" t="n">
         <v>47310</v>
@@ -25599,7 +25599,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H870" t="n">
         <v>18083</v>
@@ -25628,7 +25628,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>34.2792320251465</v>
+        <v>34.2792358398438</v>
       </c>
       <c r="H871" t="n">
         <v>19913</v>
@@ -25657,7 +25657,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>35.6431312561035</v>
+        <v>35.643123626709</v>
       </c>
       <c r="H872" t="n">
         <v>23146</v>
@@ -25686,7 +25686,7 @@
         <v>40</v>
       </c>
       <c r="G873" t="n">
-        <v>36.3705406188965</v>
+        <v>36.3705368041992</v>
       </c>
       <c r="H873" t="n">
         <v>15350</v>
@@ -25715,7 +25715,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G874" t="n">
-        <v>36.0068244934082</v>
+        <v>36.0068283081055</v>
       </c>
       <c r="H874" t="n">
         <v>13085</v>
@@ -25744,7 +25744,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>35.5521965026855</v>
+        <v>35.5521926879883</v>
       </c>
       <c r="H875" t="n">
         <v>8378</v>
@@ -25860,7 +25860,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>35.1884918212891</v>
+        <v>35.1884956359863</v>
       </c>
       <c r="H879" t="n">
         <v>1363</v>
@@ -25889,7 +25889,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>34.7338638305664</v>
+        <v>34.7338600158691</v>
       </c>
       <c r="H880" t="n">
         <v>5049</v>
@@ -26005,7 +26005,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>34.8247909545898</v>
+        <v>34.8247833251953</v>
       </c>
       <c r="H884" t="n">
         <v>7646</v>
@@ -26034,7 +26034,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G885" t="n">
-        <v>34.7338638305664</v>
+        <v>34.7338600158691</v>
       </c>
       <c r="H885" t="n">
         <v>3396</v>
@@ -26150,7 +26150,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>34.8247909545898</v>
+        <v>34.8247833251953</v>
       </c>
       <c r="H889" t="n">
         <v>3085</v>
@@ -26353,7 +26353,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G896" t="n">
-        <v>34.2792320251465</v>
+        <v>34.2792358398438</v>
       </c>
       <c r="H896" t="n">
         <v>2791</v>
@@ -26440,7 +26440,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>33.3699684143066</v>
+        <v>33.3699645996094</v>
       </c>
       <c r="H899" t="n">
         <v>5283</v>
@@ -26469,7 +26469,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G900" t="n">
-        <v>33.0971832275391</v>
+        <v>33.0971870422363</v>
       </c>
       <c r="H900" t="n">
         <v>10732</v>
@@ -26614,7 +26614,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H905" t="n">
         <v>8882</v>
@@ -26643,7 +26643,7 @@
         <v>38.5</v>
       </c>
       <c r="G906" t="n">
-        <v>35.0066413879395</v>
+        <v>35.0066375732422</v>
       </c>
       <c r="H906" t="n">
         <v>14610</v>
@@ -26701,7 +26701,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>34.8247909545898</v>
+        <v>34.8247833251953</v>
       </c>
       <c r="H908" t="n">
         <v>5104</v>
@@ -26933,7 +26933,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>32.9153327941895</v>
+        <v>32.9153366088867</v>
       </c>
       <c r="H916" t="n">
         <v>5400</v>
@@ -27020,7 +27020,7 @@
         <v>36.5</v>
       </c>
       <c r="G919" t="n">
-        <v>33.1881141662598</v>
+        <v>33.188117980957</v>
       </c>
       <c r="H919" t="n">
         <v>1912</v>
@@ -27049,7 +27049,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G920" t="n">
-        <v>33.0062561035156</v>
+        <v>33.0062599182129</v>
       </c>
       <c r="H920" t="n">
         <v>1008</v>
@@ -27078,7 +27078,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G921" t="n">
-        <v>32.9153327941895</v>
+        <v>32.9153366088867</v>
       </c>
       <c r="H921" t="n">
         <v>160</v>
@@ -27136,7 +27136,7 @@
         <v>36.5</v>
       </c>
       <c r="G923" t="n">
-        <v>33.1881141662598</v>
+        <v>33.188117980957</v>
       </c>
       <c r="H923" t="n">
         <v>1171</v>
@@ -27165,7 +27165,7 @@
         <v>36.5</v>
       </c>
       <c r="G924" t="n">
-        <v>33.1881141662598</v>
+        <v>33.188117980957</v>
       </c>
       <c r="H924" t="n">
         <v>233</v>
@@ -27223,7 +27223,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>33.0062561035156</v>
+        <v>33.0062599182129</v>
       </c>
       <c r="H926" t="n">
         <v>3948</v>
@@ -27252,7 +27252,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>32.1879272460938</v>
+        <v>32.1879234313965</v>
       </c>
       <c r="H927" t="n">
         <v>8883</v>
@@ -27281,7 +27281,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.6425590515137</v>
+        <v>32.6425628662109</v>
       </c>
       <c r="H928" t="n">
         <v>5913</v>
@@ -27397,7 +27397,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>35.2794151306152</v>
+        <v>35.2794189453125</v>
       </c>
       <c r="H932" t="n">
         <v>8467</v>
@@ -27455,7 +27455,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H934" t="n">
         <v>5593</v>
@@ -27687,7 +27687,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H942" t="n">
         <v>7615</v>
@@ -27716,7 +27716,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G943" t="n">
-        <v>34.0064468383789</v>
+        <v>34.0064544677734</v>
       </c>
       <c r="H943" t="n">
         <v>5713</v>
@@ -27803,7 +27803,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H946" t="n">
         <v>1543</v>
@@ -27861,7 +27861,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G948" t="n">
-        <v>33.9155235290527</v>
+        <v>33.9155197143555</v>
       </c>
       <c r="H948" t="n">
         <v>1091</v>
@@ -27890,7 +27890,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G949" t="n">
-        <v>33.3699684143066</v>
+        <v>33.3699645996094</v>
       </c>
       <c r="H949" t="n">
         <v>4083</v>
@@ -27919,7 +27919,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G950" t="n">
-        <v>33.3699684143066</v>
+        <v>33.3699645996094</v>
       </c>
       <c r="H950" t="n">
         <v>2437</v>
@@ -28035,7 +28035,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>33.4608955383301</v>
+        <v>33.4608917236328</v>
       </c>
       <c r="H954" t="n">
         <v>3675</v>
@@ -28180,7 +28180,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>33.4608955383301</v>
+        <v>33.4608917236328</v>
       </c>
       <c r="H959" t="n">
         <v>2602</v>
@@ -28325,7 +28325,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G964" t="n">
-        <v>34.6370697021484</v>
+        <v>34.6370735168457</v>
       </c>
       <c r="H964" t="n">
         <v>18984</v>
@@ -28383,7 +28383,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G966" t="n">
-        <v>34.1740112304688</v>
+        <v>34.174015045166</v>
       </c>
       <c r="H966" t="n">
         <v>4232</v>
@@ -28412,7 +28412,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>34.1740112304688</v>
+        <v>34.174015045166</v>
       </c>
       <c r="H967" t="n">
         <v>5406</v>
@@ -28499,7 +28499,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G970" t="n">
-        <v>33.9887886047363</v>
+        <v>33.9887847900391</v>
       </c>
       <c r="H970" t="n">
         <v>2687</v>
@@ -28528,7 +28528,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G971" t="n">
-        <v>34.1740112304688</v>
+        <v>34.174015045166</v>
       </c>
       <c r="H971" t="n">
         <v>1501</v>
@@ -28557,7 +28557,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G972" t="n">
-        <v>33.9887886047363</v>
+        <v>33.9887847900391</v>
       </c>
       <c r="H972" t="n">
         <v>778</v>
@@ -28702,7 +28702,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G977" t="n">
-        <v>33.4331092834473</v>
+        <v>33.43310546875</v>
       </c>
       <c r="H977" t="n">
         <v>374</v>
@@ -28789,7 +28789,7 @@
         <v>36</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3404960632324</v>
+        <v>33.3404998779297</v>
       </c>
       <c r="H980" t="n">
         <v>3550</v>
@@ -28818,7 +28818,7 @@
         <v>36</v>
       </c>
       <c r="G981" t="n">
-        <v>33.3404960632324</v>
+        <v>33.3404998779297</v>
       </c>
       <c r="H981" t="n">
         <v>8066</v>
@@ -28847,7 +28847,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G982" t="n">
-        <v>33.4331092834473</v>
+        <v>33.43310546875</v>
       </c>
       <c r="H982" t="n">
         <v>32523</v>
@@ -28963,7 +28963,7 @@
         <v>39</v>
       </c>
       <c r="G986" t="n">
-        <v>36.1188697814941</v>
+        <v>36.1188735961914</v>
       </c>
       <c r="H986" t="n">
         <v>41483</v>
@@ -29108,7 +29108,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>42.2312927246094</v>
+        <v>42.2312965393066</v>
       </c>
       <c r="H991" t="n">
         <v>8761</v>
@@ -29137,7 +29137,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G992" t="n">
-        <v>41.5830154418945</v>
+        <v>41.5830078125</v>
       </c>
       <c r="H992" t="n">
         <v>7185</v>
@@ -29166,7 +29166,7 @@
         <v>45.2999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>41.9534568786621</v>
+        <v>41.9534606933594</v>
       </c>
       <c r="H993" t="n">
         <v>15219</v>
@@ -29195,7 +29195,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G994" t="n">
-        <v>42.4165229797363</v>
+        <v>42.4165191650391</v>
       </c>
       <c r="H994" t="n">
         <v>28173</v>
@@ -29224,7 +29224,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>44.361385345459</v>
+        <v>44.3613815307617</v>
       </c>
       <c r="H995" t="n">
         <v>45209</v>
@@ -29253,7 +29253,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>45.9357948303223</v>
+        <v>45.935791015625</v>
       </c>
       <c r="H996" t="n">
         <v>42057</v>
@@ -29282,7 +29282,7 @@
         <v>48.9000015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>45.2875022888184</v>
+        <v>45.2875099182129</v>
       </c>
       <c r="H997" t="n">
         <v>23201</v>
@@ -29340,7 +29340,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>45.4727363586426</v>
+        <v>45.4727325439453</v>
       </c>
       <c r="H999" t="n">
         <v>2553</v>
@@ -29398,7 +29398,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1001" t="n">
-        <v>46.1210250854492</v>
+        <v>46.121021270752</v>
       </c>
       <c r="H1001" t="n">
         <v>19411</v>
@@ -29427,7 +29427,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>45.5653495788574</v>
+        <v>45.5653457641602</v>
       </c>
       <c r="H1002" t="n">
         <v>31698</v>
@@ -29485,7 +29485,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G1004" t="n">
-        <v>45.1948928833008</v>
+        <v>45.194896697998</v>
       </c>
       <c r="H1004" t="n">
         <v>7319</v>
@@ -29514,7 +29514,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>46.1210250854492</v>
+        <v>46.121021270752</v>
       </c>
       <c r="H1005" t="n">
         <v>7713</v>
@@ -29543,7 +29543,7 @@
         <v>51</v>
       </c>
       <c r="G1006" t="n">
-        <v>47.2323684692383</v>
+        <v>47.2323722839355</v>
       </c>
       <c r="H1006" t="n">
         <v>15076</v>
@@ -29572,7 +29572,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>47.0471420288086</v>
+        <v>47.0471458435059</v>
       </c>
       <c r="H1007" t="n">
         <v>4716</v>
@@ -29630,7 +29630,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1009" t="n">
-        <v>47.0471420288086</v>
+        <v>47.0471458435059</v>
       </c>
       <c r="H1009" t="n">
         <v>7743</v>
@@ -29717,7 +29717,7 @@
         <v>49</v>
       </c>
       <c r="G1012" t="n">
-        <v>45.3801231384277</v>
+        <v>45.3801193237305</v>
       </c>
       <c r="H1012" t="n">
         <v>9197</v>
@@ -29746,7 +29746,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1013" t="n">
-        <v>47.0471420288086</v>
+        <v>47.0471458435059</v>
       </c>
       <c r="H1013" t="n">
         <v>26393</v>
@@ -29775,7 +29775,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>46.1210250854492</v>
+        <v>46.121021270752</v>
       </c>
       <c r="H1014" t="n">
         <v>2874</v>
@@ -29833,7 +29833,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1016" t="n">
-        <v>47.6028251647949</v>
+        <v>47.6028289794922</v>
       </c>
       <c r="H1016" t="n">
         <v>10783</v>
@@ -29891,7 +29891,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>47.0471420288086</v>
+        <v>47.0471458435059</v>
       </c>
       <c r="H1018" t="n">
         <v>4979</v>
@@ -30036,7 +30036,7 @@
         <v>54</v>
       </c>
       <c r="G1023" t="n">
-        <v>50.0107460021973</v>
+        <v>50.0107421875</v>
       </c>
       <c r="H1023" t="n">
         <v>11513</v>
@@ -30065,7 +30065,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>48.8993949890137</v>
+        <v>48.8993911743164</v>
       </c>
       <c r="H1024" t="n">
         <v>7243</v>
@@ -30123,7 +30123,7 @@
         <v>56</v>
       </c>
       <c r="G1026" t="n">
-        <v>51.8629951477051</v>
+        <v>51.8629989624023</v>
       </c>
       <c r="H1026" t="n">
         <v>16498</v>
@@ -30268,7 +30268,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>58.16064453125</v>
+        <v>58.1606407165527</v>
       </c>
       <c r="H1031" t="n">
         <v>5992</v>
@@ -30297,7 +30297,7 @@
         <v>62</v>
       </c>
       <c r="G1032" t="n">
-        <v>57.4197425842285</v>
+        <v>57.419750213623</v>
       </c>
       <c r="H1032" t="n">
         <v>5899</v>
@@ -30326,7 +30326,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>57.0492973327637</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1033" t="n">
         <v>6666</v>
@@ -30355,7 +30355,7 @@
         <v>62</v>
       </c>
       <c r="G1034" t="n">
-        <v>57.4197425842285</v>
+        <v>57.419750213623</v>
       </c>
       <c r="H1034" t="n">
         <v>2445</v>
@@ -30413,7 +30413,7 @@
         <v>61</v>
       </c>
       <c r="G1036" t="n">
-        <v>56.4936180114746</v>
+        <v>56.4936218261719</v>
       </c>
       <c r="H1036" t="n">
         <v>5963</v>
@@ -30471,7 +30471,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1038" t="n">
-        <v>57.0492973327637</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1038" t="n">
         <v>7252</v>
@@ -30500,7 +30500,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>55.0118217468262</v>
+        <v>55.0118179321289</v>
       </c>
       <c r="H1039" t="n">
         <v>13841</v>
@@ -30587,7 +30587,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>59.642448425293</v>
+        <v>59.6424446105957</v>
       </c>
       <c r="H1042" t="n">
         <v>52827</v>
@@ -30616,7 +30616,7 @@
         <v>65</v>
       </c>
       <c r="G1043" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1043" t="n">
         <v>9419</v>
@@ -30645,7 +30645,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1044" t="n">
-        <v>60.0128974914551</v>
+        <v>60.0129013061523</v>
       </c>
       <c r="H1044" t="n">
         <v>8170</v>
@@ -30703,7 +30703,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1046" t="n">
-        <v>60.7537956237793</v>
+        <v>60.753791809082</v>
       </c>
       <c r="H1046" t="n">
         <v>21992</v>
@@ -30732,7 +30732,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1047" t="n">
-        <v>62.7912712097168</v>
+        <v>62.7912788391113</v>
       </c>
       <c r="H1047" t="n">
         <v>20312</v>
@@ -30761,7 +30761,7 @@
         <v>71</v>
       </c>
       <c r="G1048" t="n">
-        <v>65.7548675537109</v>
+        <v>65.7548751831055</v>
       </c>
       <c r="H1048" t="n">
         <v>33718</v>
@@ -30790,7 +30790,7 @@
         <v>71</v>
       </c>
       <c r="G1049" t="n">
-        <v>65.7548675537109</v>
+        <v>65.7548751831055</v>
       </c>
       <c r="H1049" t="n">
         <v>27056</v>
@@ -30819,7 +30819,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>65.1991882324219</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1050" t="n">
         <v>20635</v>
@@ -30848,7 +30848,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1051" t="n">
-        <v>65.1991882324219</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1051" t="n">
         <v>16230</v>
@@ -30906,7 +30906,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1053" t="n">
-        <v>65.1991882324219</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1053" t="n">
         <v>9328</v>
@@ -30964,7 +30964,7 @@
         <v>68.5999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>63.5321769714355</v>
+        <v>63.5321617126465</v>
       </c>
       <c r="H1055" t="n">
         <v>12535</v>
@@ -30993,7 +30993,7 @@
         <v>66</v>
       </c>
       <c r="G1056" t="n">
-        <v>61.1242408752441</v>
+        <v>61.1242485046387</v>
       </c>
       <c r="H1056" t="n">
         <v>24459</v>
@@ -31022,7 +31022,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>61.6799201965332</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1057" t="n">
         <v>8167</v>
@@ -31051,7 +31051,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>61.6799201965332</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1058" t="n">
         <v>7589</v>
@@ -31080,7 +31080,7 @@
         <v>69</v>
       </c>
       <c r="G1059" t="n">
-        <v>63.9026222229004</v>
+        <v>63.9026145935059</v>
       </c>
       <c r="H1059" t="n">
         <v>24805</v>
@@ -31109,7 +31109,7 @@
         <v>67</v>
       </c>
       <c r="G1060" t="n">
-        <v>62.0503730773926</v>
+        <v>62.050365447998</v>
       </c>
       <c r="H1060" t="n">
         <v>10940</v>
@@ -31138,7 +31138,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1061" t="n">
-        <v>62.235595703125</v>
+        <v>62.2355918884277</v>
       </c>
       <c r="H1061" t="n">
         <v>6033</v>
@@ -31167,7 +31167,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1062" t="n">
-        <v>62.420825958252</v>
+        <v>62.4208221435547</v>
       </c>
       <c r="H1062" t="n">
         <v>4435</v>
@@ -31196,7 +31196,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>61.4946937561035</v>
+        <v>61.4946899414062</v>
       </c>
       <c r="H1063" t="n">
         <v>4540</v>
@@ -31225,7 +31225,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1064" t="n">
-        <v>61.6799201965332</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1064" t="n">
         <v>7255</v>
@@ -31254,7 +31254,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>60.5685691833496</v>
+        <v>60.5685729980469</v>
       </c>
       <c r="H1065" t="n">
         <v>10994</v>
@@ -31283,7 +31283,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1066" t="n">
-        <v>58.16064453125</v>
+        <v>58.1606407165527</v>
       </c>
       <c r="H1066" t="n">
         <v>16555</v>
@@ -31312,7 +31312,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5310935974121</v>
       </c>
       <c r="H1067" t="n">
         <v>5930</v>
@@ -31370,7 +31370,7 @@
         <v>61</v>
       </c>
       <c r="G1069" t="n">
-        <v>56.4936180114746</v>
+        <v>56.4936218261719</v>
       </c>
       <c r="H1069" t="n">
         <v>6987</v>
@@ -31399,7 +31399,7 @@
         <v>63</v>
       </c>
       <c r="G1070" t="n">
-        <v>58.345874786377</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1070" t="n">
         <v>25088</v>
@@ -31428,7 +31428,7 @@
         <v>64</v>
       </c>
       <c r="G1071" t="n">
-        <v>59.2719917297363</v>
+        <v>59.2719955444336</v>
       </c>
       <c r="H1071" t="n">
         <v>19842</v>
@@ -31457,7 +31457,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1072" t="n">
-        <v>57.975414276123</v>
+        <v>57.9754180908203</v>
       </c>
       <c r="H1072" t="n">
         <v>11411</v>
@@ -31486,7 +31486,7 @@
         <v>62</v>
       </c>
       <c r="G1073" t="n">
-        <v>57.4197425842285</v>
+        <v>57.419750213623</v>
       </c>
       <c r="H1073" t="n">
         <v>5082</v>
@@ -31515,7 +31515,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>57.6049728393555</v>
+        <v>57.6049690246582</v>
       </c>
       <c r="H1074" t="n">
         <v>9173</v>
@@ -31602,7 +31602,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5310935974121</v>
       </c>
       <c r="H1077" t="n">
         <v>16965</v>
@@ -31631,7 +31631,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1078" t="n">
-        <v>63.3469505310059</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1078" t="n">
         <v>26812</v>
@@ -31689,7 +31689,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1080" t="n">
-        <v>63.3469505310059</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1080" t="n">
         <v>15561</v>
@@ -31718,7 +31718,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1081" t="n">
-        <v>63.3469505310059</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1081" t="n">
         <v>12734</v>
@@ -31747,7 +31747,7 @@
         <v>69</v>
       </c>
       <c r="G1082" t="n">
-        <v>63.9026222229004</v>
+        <v>63.9026145935059</v>
       </c>
       <c r="H1082" t="n">
         <v>5155</v>
@@ -31805,7 +31805,7 @@
         <v>67</v>
       </c>
       <c r="G1084" t="n">
-        <v>62.0503730773926</v>
+        <v>62.050365447998</v>
       </c>
       <c r="H1084" t="n">
         <v>14476</v>
@@ -31834,7 +31834,7 @@
         <v>67</v>
       </c>
       <c r="G1085" t="n">
-        <v>62.0503730773926</v>
+        <v>62.050365447998</v>
       </c>
       <c r="H1085" t="n">
         <v>9085</v>
@@ -31863,7 +31863,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>62.7912712097168</v>
+        <v>62.7912788391113</v>
       </c>
       <c r="H1086" t="n">
         <v>23354</v>
@@ -31921,7 +31921,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1088" t="n">
-        <v>63.3469505310059</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1088" t="n">
         <v>8142</v>
@@ -31979,7 +31979,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1090" t="n">
-        <v>66.310546875</v>
+        <v>66.3105392456055</v>
       </c>
       <c r="H1090" t="n">
         <v>11957</v>
@@ -32008,7 +32008,7 @@
         <v>72</v>
       </c>
       <c r="G1091" t="n">
-        <v>66.6809921264648</v>
+        <v>66.6809997558594</v>
       </c>
       <c r="H1091" t="n">
         <v>20242</v>
@@ -32037,7 +32037,7 @@
         <v>71</v>
       </c>
       <c r="G1092" t="n">
-        <v>65.7548675537109</v>
+        <v>65.7548751831055</v>
       </c>
       <c r="H1092" t="n">
         <v>9074</v>
@@ -32066,7 +32066,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1093" t="n">
-        <v>66.310546875</v>
+        <v>66.3105392456055</v>
       </c>
       <c r="H1093" t="n">
         <v>6325</v>
@@ -32124,7 +32124,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1095" t="n">
-        <v>65.5696563720703</v>
+        <v>65.5696487426758</v>
       </c>
       <c r="H1095" t="n">
         <v>9719</v>
@@ -32153,7 +32153,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1096" t="n">
-        <v>66.310546875</v>
+        <v>66.3105392456055</v>
       </c>
       <c r="H1096" t="n">
         <v>25041</v>
@@ -32211,7 +32211,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1098" t="n">
-        <v>65.1991882324219</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1098" t="n">
         <v>5246</v>
@@ -32240,7 +32240,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1099" t="n">
-        <v>65.5696563720703</v>
+        <v>65.5696487426758</v>
       </c>
       <c r="H1099" t="n">
         <v>22010</v>
@@ -32385,7 +32385,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1104" t="n">
-        <v>64.0878448486328</v>
+        <v>64.0878372192383</v>
       </c>
       <c r="H1104" t="n">
         <v>8003</v>
@@ -32472,7 +32472,7 @@
         <v>74</v>
       </c>
       <c r="G1107" t="n">
-        <v>68.5332489013672</v>
+        <v>68.5332412719727</v>
       </c>
       <c r="H1107" t="n">
         <v>25256</v>
@@ -32501,7 +32501,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1108" t="n">
-        <v>70.2002716064453</v>
+        <v>70.2002792358398</v>
       </c>
       <c r="H1108" t="n">
         <v>15408</v>
@@ -32530,7 +32530,7 @@
         <v>74</v>
       </c>
       <c r="G1109" t="n">
-        <v>68.5332489013672</v>
+        <v>68.5332412719727</v>
       </c>
       <c r="H1109" t="n">
         <v>24390</v>
@@ -32588,7 +32588,7 @@
         <v>71</v>
       </c>
       <c r="G1111" t="n">
-        <v>65.7548675537109</v>
+        <v>65.7548751831055</v>
       </c>
       <c r="H1111" t="n">
         <v>110589</v>
@@ -32646,7 +32646,7 @@
         <v>74</v>
       </c>
       <c r="G1113" t="n">
-        <v>68.5332489013672</v>
+        <v>68.5332412719727</v>
       </c>
       <c r="H1113" t="n">
         <v>10107</v>
@@ -32849,7 +32849,7 @@
         <v>73.4000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>67.9775772094727</v>
+        <v>67.9775695800781</v>
       </c>
       <c r="H1120" t="n">
         <v>5221</v>
@@ -32907,7 +32907,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G1122" t="n">
-        <v>66.8662185668945</v>
+        <v>66.8662109375</v>
       </c>
       <c r="H1122" t="n">
         <v>7373</v>
@@ -32936,7 +32936,7 @@
         <v>72</v>
       </c>
       <c r="G1123" t="n">
-        <v>66.6809921264648</v>
+        <v>66.6809997558594</v>
       </c>
       <c r="H1123" t="n">
         <v>3823</v>
@@ -32965,7 +32965,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1124" t="n">
-        <v>66.310546875</v>
+        <v>66.3105392456055</v>
       </c>
       <c r="H1124" t="n">
         <v>19893</v>
@@ -32994,7 +32994,7 @@
         <v>74</v>
       </c>
       <c r="G1125" t="n">
-        <v>68.5332489013672</v>
+        <v>68.5332412719727</v>
       </c>
       <c r="H1125" t="n">
         <v>8495</v>
@@ -33081,7 +33081,7 @@
         <v>73.4000015258789</v>
       </c>
       <c r="G1128" t="n">
-        <v>67.9775772094727</v>
+        <v>67.9775695800781</v>
       </c>
       <c r="H1128" t="n">
         <v>1694</v>
@@ -33255,7 +33255,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1134" t="n">
-        <v>70.2002716064453</v>
+        <v>70.2002792358398</v>
       </c>
       <c r="H1134" t="n">
         <v>7874</v>
@@ -33284,7 +33284,7 @@
         <v>79</v>
       </c>
       <c r="G1135" t="n">
-        <v>73.1638717651367</v>
+        <v>73.1638641357422</v>
       </c>
       <c r="H1135" t="n">
         <v>27794</v>
@@ -33313,7 +33313,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G1136" t="n">
-        <v>71.8672866821289</v>
+        <v>71.8672943115234</v>
       </c>
       <c r="H1136" t="n">
         <v>9339</v>
@@ -33342,7 +33342,7 @@
         <v>78</v>
       </c>
       <c r="G1137" t="n">
-        <v>72.2377395629883</v>
+        <v>72.2377471923828</v>
       </c>
       <c r="H1137" t="n">
         <v>8145</v>
@@ -33371,7 +33371,7 @@
         <v>73.8000030517578</v>
       </c>
       <c r="G1138" t="n">
-        <v>68.3480224609375</v>
+        <v>68.348030090332</v>
       </c>
       <c r="H1138" t="n">
         <v>13068</v>
@@ -33400,7 +33400,7 @@
         <v>74</v>
       </c>
       <c r="G1139" t="n">
-        <v>68.5332489013672</v>
+        <v>68.5332412719727</v>
       </c>
       <c r="H1139" t="n">
         <v>10084</v>
@@ -33458,7 +33458,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G1141" t="n">
-        <v>66.8662185668945</v>
+        <v>66.8662109375</v>
       </c>
       <c r="H1141" t="n">
         <v>8312</v>
@@ -33487,7 +33487,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1142" t="n">
-        <v>66.310546875</v>
+        <v>66.3105392456055</v>
       </c>
       <c r="H1142" t="n">
         <v>6667</v>
@@ -33545,7 +33545,7 @@
         <v>68.4000015258789</v>
       </c>
       <c r="G1144" t="n">
-        <v>63.3469505310059</v>
+        <v>63.3469429016113</v>
       </c>
       <c r="H1144" t="n">
         <v>8038</v>
@@ -33574,7 +33574,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1145" t="n">
-        <v>64.6435165405273</v>
+        <v>64.6435241699219</v>
       </c>
       <c r="H1145" t="n">
         <v>10235</v>
@@ -33603,7 +33603,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G1146" t="n">
-        <v>65.1991882324219</v>
+        <v>65.1991958618164</v>
       </c>
       <c r="H1146" t="n">
         <v>9298</v>
@@ -33632,7 +33632,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1147" t="n">
-        <v>62.420825958252</v>
+        <v>62.4208221435547</v>
       </c>
       <c r="H1147" t="n">
         <v>9458</v>
@@ -33661,7 +33661,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1148" t="n">
-        <v>60.7537956237793</v>
+        <v>60.753791809082</v>
       </c>
       <c r="H1148" t="n">
         <v>15342</v>
@@ -33690,7 +33690,7 @@
         <v>67</v>
       </c>
       <c r="G1149" t="n">
-        <v>62.0503730773926</v>
+        <v>62.050365447998</v>
       </c>
       <c r="H1149" t="n">
         <v>9187</v>
@@ -33719,7 +33719,7 @@
         <v>66</v>
       </c>
       <c r="G1150" t="n">
-        <v>61.1242408752441</v>
+        <v>61.1242485046387</v>
       </c>
       <c r="H1150" t="n">
         <v>10090</v>
@@ -33748,7 +33748,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1151" t="n">
-        <v>61.6799201965332</v>
+        <v>61.6799163818359</v>
       </c>
       <c r="H1151" t="n">
         <v>3890</v>
@@ -33806,7 +33806,7 @@
         <v>66</v>
       </c>
       <c r="G1153" t="n">
-        <v>61.1242408752441</v>
+        <v>61.1242485046387</v>
       </c>
       <c r="H1153" t="n">
         <v>7908</v>
@@ -33835,7 +33835,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1154" t="n">
-        <v>60.7537956237793</v>
+        <v>60.753791809082</v>
       </c>
       <c r="H1154" t="n">
         <v>13511</v>
@@ -33893,7 +33893,7 @@
         <v>66</v>
       </c>
       <c r="G1156" t="n">
-        <v>61.1242408752441</v>
+        <v>61.1242485046387</v>
       </c>
       <c r="H1156" t="n">
         <v>6716</v>
@@ -33951,7 +33951,7 @@
         <v>65</v>
       </c>
       <c r="G1158" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1158" t="n">
         <v>10093</v>
@@ -34096,7 +34096,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1163" t="n">
-        <v>57.975414276123</v>
+        <v>57.9754180908203</v>
       </c>
       <c r="H1163" t="n">
         <v>9156</v>
@@ -34154,7 +34154,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5310935974121</v>
       </c>
       <c r="H1165" t="n">
         <v>6544</v>
@@ -34183,7 +34183,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1166" t="n">
-        <v>57.975414276123</v>
+        <v>57.9754180908203</v>
       </c>
       <c r="H1166" t="n">
         <v>11260</v>
@@ -34241,7 +34241,7 @@
         <v>63</v>
       </c>
       <c r="G1168" t="n">
-        <v>58.345874786377</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1168" t="n">
         <v>7543</v>
@@ -34270,7 +34270,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>57.0492973327637</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1169" t="n">
         <v>12328</v>
@@ -34386,7 +34386,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>58.16064453125</v>
+        <v>58.1606407165527</v>
       </c>
       <c r="H1173" t="n">
         <v>12736</v>
@@ -34415,7 +34415,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1174" t="n">
-        <v>57.0492973327637</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1174" t="n">
         <v>8061</v>
@@ -34473,7 +34473,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1176" t="n">
-        <v>55.1970405578613</v>
+        <v>55.1970443725586</v>
       </c>
       <c r="H1176" t="n">
         <v>12029</v>
@@ -34531,7 +34531,7 @@
         <v>56</v>
       </c>
       <c r="G1178" t="n">
-        <v>51.8629951477051</v>
+        <v>51.8629989624023</v>
       </c>
       <c r="H1178" t="n">
         <v>17018</v>
@@ -34560,7 +34560,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1179" t="n">
-        <v>51.307315826416</v>
+        <v>51.3073234558105</v>
       </c>
       <c r="H1179" t="n">
         <v>7235</v>
@@ -34618,7 +34618,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>52.2334480285645</v>
+        <v>52.2334442138672</v>
       </c>
       <c r="H1181" t="n">
         <v>3643</v>
@@ -34647,7 +34647,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1182" t="n">
-        <v>55.1970405578613</v>
+        <v>55.1970443725586</v>
       </c>
       <c r="H1182" t="n">
         <v>3171</v>
@@ -34676,7 +34676,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>57.0492973327637</v>
+        <v>57.0492897033691</v>
       </c>
       <c r="H1183" t="n">
         <v>4645</v>
@@ -34705,7 +34705,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1184" t="n">
-        <v>55.382266998291</v>
+        <v>55.3822708129883</v>
       </c>
       <c r="H1184" t="n">
         <v>5635</v>
@@ -34734,7 +34734,7 @@
         <v>61</v>
       </c>
       <c r="G1185" t="n">
-        <v>56.4936180114746</v>
+        <v>56.4936218261719</v>
       </c>
       <c r="H1185" t="n">
         <v>8219</v>
@@ -34763,7 +34763,7 @@
         <v>61</v>
       </c>
       <c r="G1186" t="n">
-        <v>56.4936180114746</v>
+        <v>56.4936218261719</v>
       </c>
       <c r="H1186" t="n">
         <v>3492</v>
@@ -34821,7 +34821,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>60.5685691833496</v>
+        <v>60.5685729980469</v>
       </c>
       <c r="H1188" t="n">
         <v>18854</v>
@@ -34908,7 +34908,7 @@
         <v>65</v>
       </c>
       <c r="G1191" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1191" t="n">
         <v>8658</v>
@@ -35053,7 +35053,7 @@
         <v>63</v>
       </c>
       <c r="G1196" t="n">
-        <v>58.345874786377</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1196" t="n">
         <v>5314</v>
@@ -35111,7 +35111,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1198" t="n">
-        <v>58.5310974121094</v>
+        <v>58.5310935974121</v>
       </c>
       <c r="H1198" t="n">
         <v>4906</v>
@@ -35140,7 +35140,7 @@
         <v>65</v>
       </c>
       <c r="G1199" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1199" t="n">
         <v>32409</v>
@@ -35198,7 +35198,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1201" t="n">
-        <v>60.0128974914551</v>
+        <v>60.0129013061523</v>
       </c>
       <c r="H1201" t="n">
         <v>8130</v>
@@ -35227,7 +35227,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1202" t="n">
-        <v>61.8651504516602</v>
+        <v>61.8651466369629</v>
       </c>
       <c r="H1202" t="n">
         <v>7305</v>
@@ -35256,7 +35256,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>61.4946937561035</v>
+        <v>61.4946899414062</v>
       </c>
       <c r="H1203" t="n">
         <v>5708</v>
@@ -35343,7 +35343,7 @@
         <v>67</v>
       </c>
       <c r="G1206" t="n">
-        <v>62.0503730773926</v>
+        <v>62.050365447998</v>
       </c>
       <c r="H1206" t="n">
         <v>7404</v>
@@ -35372,7 +35372,7 @@
         <v>65</v>
       </c>
       <c r="G1207" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1207" t="n">
         <v>3155</v>
@@ -35401,7 +35401,7 @@
         <v>65</v>
       </c>
       <c r="G1208" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1208" t="n">
         <v>4312</v>
@@ -35430,7 +35430,7 @@
         <v>65</v>
       </c>
       <c r="G1209" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1209" t="n">
         <v>3029</v>
@@ -35459,7 +35459,7 @@
         <v>65</v>
       </c>
       <c r="G1210" t="n">
-        <v>60.1981201171875</v>
+        <v>60.1981163024902</v>
       </c>
       <c r="H1210" t="n">
         <v>3326</v>
@@ -35488,7 +35488,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1211" t="n">
-        <v>59.9202766418457</v>
+        <v>59.920280456543</v>
       </c>
       <c r="H1211" t="n">
         <v>3950</v>
@@ -35517,7 +35517,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>58.623706817627</v>
+        <v>58.6237106323242</v>
       </c>
       <c r="H1212" t="n">
         <v>5794</v>
@@ -35546,7 +35546,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>58.16064453125</v>
+        <v>58.1606407165527</v>
       </c>
       <c r="H1213" t="n">
         <v>4220</v>
@@ -35575,7 +35575,7 @@
         <v>63</v>
       </c>
       <c r="G1214" t="n">
-        <v>58.345874786377</v>
+        <v>58.3458709716797</v>
       </c>
       <c r="H1214" t="n">
         <v>4413</v>
@@ -35604,7 +35604,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1215" t="n">
-        <v>60.1055107116699</v>
+        <v>60.1055068969727</v>
       </c>
       <c r="H1215" t="n">
         <v>3849</v>
@@ -35633,7 +35633,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1216" t="n">
-        <v>60.6766929626465</v>
+        <v>60.6766967773438</v>
       </c>
       <c r="H1216" t="n">
         <v>4647</v>
@@ -35720,7 +35720,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>54.4966621398926</v>
+        <v>54.4966583251953</v>
       </c>
       <c r="H1219" t="n">
         <v>6610</v>
@@ -35749,7 +35749,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1220" t="n">
-        <v>51.5939178466797</v>
+        <v>51.5939140319824</v>
       </c>
       <c r="H1220" t="n">
         <v>9662</v>
@@ -35778,7 +35778,7 @@
         <v>56.5</v>
       </c>
       <c r="G1221" t="n">
-        <v>52.9048271179199</v>
+        <v>52.9048309326172</v>
       </c>
       <c r="H1221" t="n">
         <v>5122</v>
@@ -35836,7 +35836,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>56.2757530212402</v>
+        <v>56.2757568359375</v>
       </c>
       <c r="H1223" t="n">
         <v>8299</v>
@@ -35981,7 +35981,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1228" t="n">
-        <v>56.0884895324707</v>
+        <v>56.0884857177734</v>
       </c>
       <c r="H1228" t="n">
         <v>2058</v>
@@ -36068,7 +36068,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1231" t="n">
-        <v>58.8039512634277</v>
+        <v>58.803955078125</v>
       </c>
       <c r="H1231" t="n">
         <v>3054</v>
@@ -36097,7 +36097,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>57.8675842285156</v>
+        <v>57.8675880432129</v>
       </c>
       <c r="H1232" t="n">
         <v>2813</v>
@@ -36126,7 +36126,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1233" t="n">
-        <v>59.3657760620117</v>
+        <v>59.3657722473145</v>
       </c>
       <c r="H1233" t="n">
         <v>4469</v>
@@ -36155,7 +36155,7 @@
         <v>62.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>58.5230407714844</v>
+        <v>58.5230445861816</v>
       </c>
       <c r="H1234" t="n">
         <v>3018</v>
@@ -36242,7 +36242,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G1237" t="n">
-        <v>61.8939666748047</v>
+        <v>61.893970489502</v>
       </c>
       <c r="H1237" t="n">
         <v>15476</v>
@@ -36271,7 +36271,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1238" t="n">
-        <v>61.0512390136719</v>
+        <v>61.0512313842773</v>
       </c>
       <c r="H1238" t="n">
         <v>8167</v>
@@ -36300,7 +36300,7 @@
         <v>66</v>
       </c>
       <c r="G1239" t="n">
-        <v>61.8003311157227</v>
+        <v>61.8003349304199</v>
       </c>
       <c r="H1239" t="n">
         <v>2567</v>
@@ -36387,7 +36387,7 @@
         <v>62.5</v>
       </c>
       <c r="G1242" t="n">
-        <v>58.5230407714844</v>
+        <v>58.5230445861816</v>
       </c>
       <c r="H1242" t="n">
         <v>2340</v>
@@ -36416,7 +36416,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1243" t="n">
-        <v>58.8039512634277</v>
+        <v>58.803955078125</v>
       </c>
       <c r="H1243" t="n">
         <v>927</v>
@@ -36445,7 +36445,7 @@
         <v>61.5</v>
       </c>
       <c r="G1244" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1244" t="n">
         <v>3144</v>
@@ -36474,7 +36474,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>58.8039512634277</v>
+        <v>58.803955078125</v>
       </c>
       <c r="H1245" t="n">
         <v>4530</v>
@@ -36503,7 +36503,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>56.7439422607422</v>
+        <v>56.7439384460449</v>
       </c>
       <c r="H1246" t="n">
         <v>7288</v>
@@ -36532,7 +36532,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>55.9948463439941</v>
+        <v>55.9948501586914</v>
       </c>
       <c r="H1247" t="n">
         <v>5448</v>
@@ -36561,7 +36561,7 @@
         <v>62</v>
       </c>
       <c r="G1248" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1248" t="n">
         <v>9034</v>
@@ -36677,7 +36677,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1252" t="n">
-        <v>55.9012145996094</v>
+        <v>55.9012107849121</v>
       </c>
       <c r="H1252" t="n">
         <v>2532</v>
@@ -36764,7 +36764,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>57.3057632446289</v>
+        <v>57.3057670593262</v>
       </c>
       <c r="H1255" t="n">
         <v>1840</v>
@@ -37025,7 +37025,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1264" t="n">
-        <v>60.6766929626465</v>
+        <v>60.6766967773438</v>
       </c>
       <c r="H1264" t="n">
         <v>17158</v>
@@ -37054,7 +37054,7 @@
         <v>67</v>
       </c>
       <c r="G1265" t="n">
-        <v>62.7367057800293</v>
+        <v>62.7366981506348</v>
       </c>
       <c r="H1265" t="n">
         <v>20893</v>
@@ -37083,7 +37083,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1266" t="n">
-        <v>61.6130638122559</v>
+        <v>61.6130599975586</v>
       </c>
       <c r="H1266" t="n">
         <v>8319</v>
@@ -37170,7 +37170,7 @@
         <v>63</v>
       </c>
       <c r="G1269" t="n">
-        <v>58.9912338256836</v>
+        <v>58.9912261962891</v>
       </c>
       <c r="H1269" t="n">
         <v>5348</v>
@@ -37199,7 +37199,7 @@
         <v>64.5</v>
       </c>
       <c r="G1270" t="n">
-        <v>60.3957786560059</v>
+        <v>60.3957824707031</v>
       </c>
       <c r="H1270" t="n">
         <v>4689</v>
@@ -37286,7 +37286,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>59.7403259277344</v>
+        <v>59.7403221130371</v>
       </c>
       <c r="H1273" t="n">
         <v>3377</v>
@@ -37373,7 +37373,7 @@
         <v>64.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>60.3957786560059</v>
+        <v>60.3957824707031</v>
       </c>
       <c r="H1276" t="n">
         <v>1278</v>
@@ -37431,7 +37431,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1278" t="n">
-        <v>62.5494346618652</v>
+        <v>62.549430847168</v>
       </c>
       <c r="H1278" t="n">
         <v>7535</v>
@@ -37460,7 +37460,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1279" t="n">
-        <v>62.4557914733887</v>
+        <v>62.4557876586914</v>
       </c>
       <c r="H1279" t="n">
         <v>3239</v>
@@ -37547,7 +37547,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G1282" t="n">
-        <v>64.3285217285156</v>
+        <v>64.3285293579102</v>
       </c>
       <c r="H1282" t="n">
         <v>2456</v>
@@ -37576,7 +37576,7 @@
         <v>68</v>
       </c>
       <c r="G1283" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1283" t="n">
         <v>3127</v>
@@ -37634,7 +37634,7 @@
         <v>67</v>
       </c>
       <c r="G1285" t="n">
-        <v>62.7367057800293</v>
+        <v>62.7366981506348</v>
       </c>
       <c r="H1285" t="n">
         <v>3334</v>
@@ -37663,7 +37663,7 @@
         <v>68</v>
       </c>
       <c r="G1286" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1286" t="n">
         <v>4639</v>
@@ -37721,7 +37721,7 @@
         <v>69</v>
       </c>
       <c r="G1288" t="n">
-        <v>64.6094436645508</v>
+        <v>64.6094360351562</v>
       </c>
       <c r="H1288" t="n">
         <v>4841</v>
@@ -37808,7 +37808,7 @@
         <v>68.1999969482422</v>
       </c>
       <c r="G1291" t="n">
-        <v>63.8603363037109</v>
+        <v>63.8603401184082</v>
       </c>
       <c r="H1291" t="n">
         <v>716</v>
@@ -37837,7 +37837,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>63.7667083740234</v>
+        <v>63.7667045593262</v>
       </c>
       <c r="H1292" t="n">
         <v>2952</v>
@@ -37866,7 +37866,7 @@
         <v>67.5999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>63.2985229492188</v>
+        <v>63.2985153198242</v>
       </c>
       <c r="H1293" t="n">
         <v>6297</v>
@@ -37895,7 +37895,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1294" t="n">
-        <v>62.5494346618652</v>
+        <v>62.549430847168</v>
       </c>
       <c r="H1294" t="n">
         <v>1691</v>
@@ -37924,7 +37924,7 @@
         <v>67</v>
       </c>
       <c r="G1295" t="n">
-        <v>62.7367057800293</v>
+        <v>62.7366981506348</v>
       </c>
       <c r="H1295" t="n">
         <v>3848</v>
@@ -38011,7 +38011,7 @@
         <v>69</v>
       </c>
       <c r="G1298" t="n">
-        <v>64.6094436645508</v>
+        <v>64.6094360351562</v>
       </c>
       <c r="H1298" t="n">
         <v>3290</v>
@@ -38040,7 +38040,7 @@
         <v>69</v>
       </c>
       <c r="G1299" t="n">
-        <v>64.6094436645508</v>
+        <v>64.6094360351562</v>
       </c>
       <c r="H1299" t="n">
         <v>4702</v>
@@ -38127,7 +38127,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G1302" t="n">
-        <v>63.3921508789062</v>
+        <v>63.3921585083008</v>
       </c>
       <c r="H1302" t="n">
         <v>6182</v>
@@ -38214,7 +38214,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G1305" t="n">
-        <v>64.8903503417969</v>
+        <v>64.8903579711914</v>
       </c>
       <c r="H1305" t="n">
         <v>9202</v>
@@ -38330,7 +38330,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1309" t="n">
-        <v>65.358528137207</v>
+        <v>65.3585433959961</v>
       </c>
       <c r="H1309" t="n">
         <v>5793</v>
@@ -38417,7 +38417,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G1312" t="n">
-        <v>66.2949142456055</v>
+        <v>66.2949066162109</v>
       </c>
       <c r="H1312" t="n">
         <v>3551</v>
@@ -38475,7 +38475,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G1314" t="n">
-        <v>66.8567199707031</v>
+        <v>66.8567276000977</v>
       </c>
       <c r="H1314" t="n">
         <v>11466</v>
@@ -38504,7 +38504,7 @@
         <v>70.3000030517578</v>
       </c>
       <c r="G1315" t="n">
-        <v>65.8267135620117</v>
+        <v>65.8267211914062</v>
       </c>
       <c r="H1315" t="n">
         <v>8792</v>
@@ -38533,7 +38533,7 @@
         <v>68</v>
       </c>
       <c r="G1316" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1316" t="n">
         <v>16446</v>
@@ -38591,7 +38591,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1318" t="n">
-        <v>61.0512390136719</v>
+        <v>61.0512313842773</v>
       </c>
       <c r="H1318" t="n">
         <v>6967</v>
@@ -38620,7 +38620,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G1319" t="n">
-        <v>59.7403259277344</v>
+        <v>59.7403221130371</v>
       </c>
       <c r="H1319" t="n">
         <v>9758</v>
@@ -38765,7 +38765,7 @@
         <v>66.3000030517578</v>
       </c>
       <c r="G1324" t="n">
-        <v>62.0812454223633</v>
+        <v>62.0812492370605</v>
       </c>
       <c r="H1324" t="n">
         <v>7316</v>
@@ -38823,7 +38823,7 @@
         <v>66</v>
       </c>
       <c r="G1326" t="n">
-        <v>61.8003311157227</v>
+        <v>61.8003349304199</v>
       </c>
       <c r="H1326" t="n">
         <v>4243</v>
@@ -38852,7 +38852,7 @@
         <v>66</v>
       </c>
       <c r="G1327" t="n">
-        <v>61.8003311157227</v>
+        <v>61.8003349304199</v>
       </c>
       <c r="H1327" t="n">
         <v>2465</v>
@@ -38997,7 +38997,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1332" t="n">
-        <v>59.5530433654785</v>
+        <v>59.553050994873</v>
       </c>
       <c r="H1332" t="n">
         <v>3100</v>
@@ -39142,7 +39142,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1337" t="n">
-        <v>61.0512390136719</v>
+        <v>61.0512313842773</v>
       </c>
       <c r="H1337" t="n">
         <v>889</v>
@@ -39229,7 +39229,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1340" t="n">
-        <v>61.0512390136719</v>
+        <v>61.0512313842773</v>
       </c>
       <c r="H1340" t="n">
         <v>2138</v>
@@ -39258,7 +39258,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1341" t="n">
-        <v>61.987606048584</v>
+        <v>61.9876022338867</v>
       </c>
       <c r="H1341" t="n">
         <v>1813</v>
@@ -39287,7 +39287,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1342" t="n">
-        <v>61.987606048584</v>
+        <v>61.9876022338867</v>
       </c>
       <c r="H1342" t="n">
         <v>1533</v>
@@ -39316,7 +39316,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1343" t="n">
-        <v>61.987606048584</v>
+        <v>61.9876022338867</v>
       </c>
       <c r="H1343" t="n">
         <v>2190</v>
@@ -39345,7 +39345,7 @@
         <v>68</v>
       </c>
       <c r="G1344" t="n">
-        <v>63.6730690002441</v>
+        <v>63.6730766296387</v>
       </c>
       <c r="H1344" t="n">
         <v>1117</v>
@@ -39374,7 +39374,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1345" t="n">
-        <v>63.4857978820801</v>
+        <v>63.4858016967773</v>
       </c>
       <c r="H1345" t="n">
         <v>2489</v>
@@ -39403,7 +39403,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G1346" t="n">
-        <v>63.3921508789062</v>
+        <v>63.3921585083008</v>
       </c>
       <c r="H1346" t="n">
         <v>1676</v>
@@ -39432,7 +39432,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G1347" t="n">
-        <v>63.0176162719727</v>
+        <v>63.0176124572754</v>
       </c>
       <c r="H1347" t="n">
         <v>1993</v>
@@ -39461,7 +39461,7 @@
         <v>66.9000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>62.6430740356445</v>
+        <v>62.6430702209473</v>
       </c>
       <c r="H1348" t="n">
         <v>1938</v>
@@ -39519,7 +39519,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1350" t="n">
-        <v>62.5494346618652</v>
+        <v>62.549430847168</v>
       </c>
       <c r="H1350" t="n">
         <v>899</v>
@@ -39548,7 +39548,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1351" t="n">
-        <v>62.4557914733887</v>
+        <v>62.4557876586914</v>
       </c>
       <c r="H1351" t="n">
         <v>2889</v>
@@ -39577,7 +39577,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1352" t="n">
-        <v>62.4557914733887</v>
+        <v>62.4557876586914</v>
       </c>
       <c r="H1352" t="n">
         <v>2821</v>
@@ -39635,7 +39635,7 @@
         <v>67</v>
       </c>
       <c r="G1354" t="n">
-        <v>62.7367057800293</v>
+        <v>62.7366981506348</v>
       </c>
       <c r="H1354" t="n">
         <v>1811</v>
@@ -39664,7 +39664,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1355" t="n">
-        <v>62.5494346618652</v>
+        <v>62.549430847168</v>
       </c>
       <c r="H1355" t="n">
         <v>1776</v>
@@ -39751,7 +39751,7 @@
         <v>64.5</v>
       </c>
       <c r="G1358" t="n">
-        <v>60.3957786560059</v>
+        <v>60.3957824707031</v>
       </c>
       <c r="H1358" t="n">
         <v>560</v>
@@ -39780,7 +39780,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1359" t="n">
-        <v>60.6766929626465</v>
+        <v>60.6766967773438</v>
       </c>
       <c r="H1359" t="n">
         <v>1409</v>
@@ -39809,7 +39809,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1360" t="n">
-        <v>60.5830535888672</v>
+        <v>60.5830497741699</v>
       </c>
       <c r="H1360" t="n">
         <v>366</v>
@@ -39983,7 +39983,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1366" t="n">
-        <v>59.5530433654785</v>
+        <v>59.553050994873</v>
       </c>
       <c r="H1366" t="n">
         <v>9059</v>
@@ -40041,7 +40041,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>58.4294090270996</v>
+        <v>58.4294052124023</v>
       </c>
       <c r="H1368" t="n">
         <v>3876</v>
@@ -40070,7 +40070,7 @@
         <v>62</v>
       </c>
       <c r="G1369" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1369" t="n">
         <v>2182</v>
@@ -40099,7 +40099,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1370" t="n">
-        <v>58.897590637207</v>
+        <v>58.8975944519043</v>
       </c>
       <c r="H1370" t="n">
         <v>2370</v>
@@ -40157,7 +40157,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>57.6803131103516</v>
+        <v>57.6803092956543</v>
       </c>
       <c r="H1372" t="n">
         <v>6771</v>
@@ -40244,7 +40244,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1375" t="n">
-        <v>58.6166763305664</v>
+        <v>58.6166839599609</v>
       </c>
       <c r="H1375" t="n">
         <v>2697</v>
@@ -40273,7 +40273,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1376" t="n">
-        <v>59.5530433654785</v>
+        <v>59.553050994873</v>
       </c>
       <c r="H1376" t="n">
         <v>7123</v>
@@ -40302,7 +40302,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1377" t="n">
-        <v>59.5530433654785</v>
+        <v>59.553050994873</v>
       </c>
       <c r="H1377" t="n">
         <v>4730</v>
@@ -40331,7 +40331,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G1378" t="n">
-        <v>59.0848617553711</v>
+        <v>59.0848655700684</v>
       </c>
       <c r="H1378" t="n">
         <v>1712</v>
@@ -40360,7 +40360,7 @@
         <v>62</v>
       </c>
       <c r="G1379" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1379" t="n">
         <v>4144</v>
@@ -40418,7 +40418,7 @@
         <v>63</v>
       </c>
       <c r="G1381" t="n">
-        <v>58.9912338256836</v>
+        <v>58.9912261962891</v>
       </c>
       <c r="H1381" t="n">
         <v>876</v>
@@ -40447,7 +40447,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1382" t="n">
-        <v>58.897590637207</v>
+        <v>58.8975944519043</v>
       </c>
       <c r="H1382" t="n">
         <v>1175</v>
@@ -40476,7 +40476,7 @@
         <v>62.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>58.5230407714844</v>
+        <v>58.5230445861816</v>
       </c>
       <c r="H1383" t="n">
         <v>4236</v>
@@ -40534,7 +40534,7 @@
         <v>62.5</v>
       </c>
       <c r="G1385" t="n">
-        <v>58.5230407714844</v>
+        <v>58.5230445861816</v>
       </c>
       <c r="H1385" t="n">
         <v>1012</v>
@@ -40563,7 +40563,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>58.8039512634277</v>
+        <v>58.803955078125</v>
       </c>
       <c r="H1386" t="n">
         <v>617</v>
@@ -40592,7 +40592,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1387" t="n">
-        <v>58.6166763305664</v>
+        <v>58.6166839599609</v>
       </c>
       <c r="H1387" t="n">
         <v>878</v>
@@ -40650,7 +40650,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>58.8039512634277</v>
+        <v>58.803955078125</v>
       </c>
       <c r="H1389" t="n">
         <v>649</v>
@@ -40795,7 +40795,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1394" t="n">
-        <v>59.5530433654785</v>
+        <v>59.553050994873</v>
       </c>
       <c r="H1394" t="n">
         <v>6905</v>
@@ -40824,7 +40824,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1395" t="n">
-        <v>59.3657760620117</v>
+        <v>59.3657722473145</v>
       </c>
       <c r="H1395" t="n">
         <v>9729</v>
@@ -40853,7 +40853,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1396" t="n">
-        <v>58.897590637207</v>
+        <v>58.8975944519043</v>
       </c>
       <c r="H1396" t="n">
         <v>1658</v>
@@ -40911,7 +40911,7 @@
         <v>63</v>
       </c>
       <c r="G1398" t="n">
-        <v>58.9912338256836</v>
+        <v>58.9912261962891</v>
       </c>
       <c r="H1398" t="n">
         <v>4856</v>
@@ -40940,7 +40940,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>58.8039512634277</v>
+        <v>58.803955078125</v>
       </c>
       <c r="H1399" t="n">
         <v>963</v>
@@ -40969,7 +40969,7 @@
         <v>62.5</v>
       </c>
       <c r="G1400" t="n">
-        <v>58.5230407714844</v>
+        <v>58.5230445861816</v>
       </c>
       <c r="H1400" t="n">
         <v>2659</v>
@@ -40998,7 +40998,7 @@
         <v>62</v>
       </c>
       <c r="G1401" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1401" t="n">
         <v>7100</v>
@@ -41027,7 +41027,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>57.3057632446289</v>
+        <v>57.3057670593262</v>
       </c>
       <c r="H1402" t="n">
         <v>5152</v>
@@ -41056,7 +41056,7 @@
         <v>61.5</v>
       </c>
       <c r="G1403" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1403" t="n">
         <v>2847</v>
@@ -41085,7 +41085,7 @@
         <v>61.5</v>
       </c>
       <c r="G1404" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1404" t="n">
         <v>2465</v>
@@ -41172,7 +41172,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1407" t="n">
-        <v>55.9948463439941</v>
+        <v>55.9948501586914</v>
       </c>
       <c r="H1407" t="n">
         <v>4172</v>
@@ -41317,7 +41317,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G1412" t="n">
-        <v>55.5266609191895</v>
+        <v>55.5266647338867</v>
       </c>
       <c r="H1412" t="n">
         <v>4335</v>
@@ -41346,7 +41346,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1413" t="n">
-        <v>55.3393898010254</v>
+        <v>55.3393859863281</v>
       </c>
       <c r="H1413" t="n">
         <v>7530</v>
@@ -41404,7 +41404,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1415" t="n">
-        <v>56.2757530212402</v>
+        <v>56.2757568359375</v>
       </c>
       <c r="H1415" t="n">
         <v>1544</v>
@@ -41433,7 +41433,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1416" t="n">
-        <v>56.0884895324707</v>
+        <v>56.0884857177734</v>
       </c>
       <c r="H1416" t="n">
         <v>13800</v>
@@ -41491,7 +41491,7 @@
         <v>62</v>
       </c>
       <c r="G1418" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1418" t="n">
         <v>18668</v>
@@ -41549,7 +41549,7 @@
         <v>61.5</v>
       </c>
       <c r="G1420" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1420" t="n">
         <v>2387</v>
@@ -41636,7 +41636,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G1423" t="n">
-        <v>56.0884895324707</v>
+        <v>56.0884857177734</v>
       </c>
       <c r="H1423" t="n">
         <v>9382</v>
@@ -41665,7 +41665,7 @@
         <v>62</v>
       </c>
       <c r="G1424" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1424" t="n">
         <v>15816</v>
@@ -41723,7 +41723,7 @@
         <v>62</v>
       </c>
       <c r="G1426" t="n">
-        <v>58.0548553466797</v>
+        <v>58.054859161377</v>
       </c>
       <c r="H1426" t="n">
         <v>11491</v>
@@ -41752,7 +41752,7 @@
         <v>61.5</v>
       </c>
       <c r="G1427" t="n">
-        <v>57.5866737365723</v>
+        <v>57.5866775512695</v>
       </c>
       <c r="H1427" t="n">
         <v>6174</v>
@@ -41868,7 +41868,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1431" t="n">
-        <v>56.2757530212402</v>
+        <v>56.2757568359375</v>
       </c>
       <c r="H1431" t="n">
         <v>5393</v>
@@ -41984,7 +41984,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1435" t="n">
-        <v>56.7439422607422</v>
+        <v>56.7439384460449</v>
       </c>
       <c r="H1435" t="n">
         <v>5610</v>
@@ -42042,7 +42042,7 @@
         <v>57.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>53.8412017822266</v>
+        <v>53.8411979675293</v>
       </c>
       <c r="H1437" t="n">
         <v>9231</v>
@@ -42100,7 +42100,7 @@
         <v>56</v>
       </c>
       <c r="G1439" t="n">
-        <v>52.4366455078125</v>
+        <v>52.4366493225098</v>
       </c>
       <c r="H1439" t="n">
         <v>8320</v>
@@ -42129,7 +42129,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1440" t="n">
-        <v>52.7175559997559</v>
+        <v>52.7175598144531</v>
       </c>
       <c r="H1440" t="n">
         <v>1414</v>
@@ -42158,7 +42158,7 @@
         <v>56</v>
       </c>
       <c r="G1441" t="n">
-        <v>52.4366455078125</v>
+        <v>52.4366493225098</v>
       </c>
       <c r="H1441" t="n">
         <v>6199</v>
@@ -42303,7 +42303,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1446" t="n">
-        <v>53.2793807983398</v>
+        <v>53.2793769836426</v>
       </c>
       <c r="H1446" t="n">
         <v>4740</v>
@@ -42361,7 +42361,7 @@
         <v>56</v>
       </c>
       <c r="G1448" t="n">
-        <v>52.4366455078125</v>
+        <v>52.4366493225098</v>
       </c>
       <c r="H1448" t="n">
         <v>8104</v>
@@ -42419,7 +42419,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1450" t="n">
-        <v>52.3430137634277</v>
+        <v>52.3430099487305</v>
       </c>
       <c r="H1450" t="n">
         <v>2535</v>
@@ -42448,7 +42448,7 @@
         <v>56</v>
       </c>
       <c r="G1451" t="n">
-        <v>52.4366455078125</v>
+        <v>52.4366493225098</v>
       </c>
       <c r="H1451" t="n">
         <v>5276</v>
@@ -42477,7 +42477,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>52.0621032714844</v>
+        <v>52.0620956420898</v>
       </c>
       <c r="H1452" t="n">
         <v>1922</v>
@@ -42506,7 +42506,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1453" t="n">
-        <v>52.0621032714844</v>
+        <v>52.0620956420898</v>
       </c>
       <c r="H1453" t="n">
         <v>1637</v>
@@ -42535,7 +42535,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>52.1557350158691</v>
+        <v>52.1557388305664</v>
       </c>
       <c r="H1454" t="n">
         <v>1438</v>
@@ -42622,7 +42622,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1457" t="n">
-        <v>51.5939178466797</v>
+        <v>51.5939140319824</v>
       </c>
       <c r="H1457" t="n">
         <v>1898</v>
@@ -42680,7 +42680,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>50.8448181152344</v>
+        <v>50.8448143005371</v>
       </c>
       <c r="H1459" t="n">
         <v>2130</v>
@@ -42709,7 +42709,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>51.2193717956543</v>
+        <v>51.219367980957</v>
       </c>
       <c r="H1460" t="n">
         <v>3848</v>
@@ -42738,7 +42738,7 @@
         <v>54</v>
       </c>
       <c r="G1461" t="n">
-        <v>50.5639114379883</v>
+        <v>50.563907623291</v>
       </c>
       <c r="H1461" t="n">
         <v>10162</v>
@@ -42796,7 +42796,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1463" t="n">
-        <v>50.3766326904297</v>
+        <v>50.376636505127</v>
       </c>
       <c r="H1463" t="n">
         <v>5407</v>
@@ -42883,7 +42883,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1466" t="n">
-        <v>50.0020942687988</v>
+        <v>50.0020904541016</v>
       </c>
       <c r="H1466" t="n">
         <v>9739</v>
@@ -42941,7 +42941,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1468" t="n">
-        <v>48.8784446716309</v>
+        <v>48.8784484863281</v>
       </c>
       <c r="H1468" t="n">
         <v>3171</v>
@@ -42970,7 +42970,7 @@
         <v>50</v>
       </c>
       <c r="G1469" t="n">
-        <v>46.818431854248</v>
+        <v>46.8184356689453</v>
       </c>
       <c r="H1469" t="n">
         <v>23042</v>
@@ -42999,7 +42999,7 @@
         <v>51</v>
       </c>
       <c r="G1470" t="n">
-        <v>47.7548065185547</v>
+        <v>47.7548027038574</v>
       </c>
       <c r="H1470" t="n">
         <v>7368</v>
@@ -43028,7 +43028,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1471" t="n">
-        <v>47.1929817199707</v>
+        <v>47.192985534668</v>
       </c>
       <c r="H1471" t="n">
         <v>4172</v>
@@ -43057,7 +43057,7 @@
         <v>52</v>
       </c>
       <c r="G1472" t="n">
-        <v>48.6911735534668</v>
+        <v>48.6911697387695</v>
       </c>
       <c r="H1472" t="n">
         <v>5403</v>
@@ -43086,7 +43086,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1473" t="n">
-        <v>48.5975341796875</v>
+        <v>48.5975379943848</v>
       </c>
       <c r="H1473" t="n">
         <v>5452</v>
@@ -43115,7 +43115,7 @@
         <v>52</v>
       </c>
       <c r="G1474" t="n">
-        <v>48.6911735534668</v>
+        <v>48.6911697387695</v>
       </c>
       <c r="H1474" t="n">
         <v>3246</v>
@@ -43144,7 +43144,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1475" t="n">
-        <v>48.5975341796875</v>
+        <v>48.5975379943848</v>
       </c>
       <c r="H1475" t="n">
         <v>3380</v>
@@ -43260,7 +43260,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1479" t="n">
-        <v>52.686954498291</v>
+        <v>52.6869583129883</v>
       </c>
       <c r="H1479" t="n">
         <v>8380</v>
@@ -43318,7 +43318,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1481" t="n">
-        <v>54.1134986877441</v>
+        <v>54.1134948730469</v>
       </c>
       <c r="H1481" t="n">
         <v>8061</v>
@@ -43376,7 +43376,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G1483" t="n">
-        <v>54.3988075256348</v>
+        <v>54.3988037109375</v>
       </c>
       <c r="H1483" t="n">
         <v>11670</v>
@@ -43492,7 +43492,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G1487" t="n">
-        <v>55.4449348449707</v>
+        <v>55.444938659668</v>
       </c>
       <c r="H1487" t="n">
         <v>6014</v>
@@ -43550,7 +43550,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1489" t="n">
-        <v>55.2547302246094</v>
+        <v>55.2547264099121</v>
       </c>
       <c r="H1489" t="n">
         <v>4867</v>
@@ -43579,7 +43579,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1490" t="n">
-        <v>55.8253440856934</v>
+        <v>55.8253479003906</v>
       </c>
       <c r="H1490" t="n">
         <v>5008</v>
@@ -43608,7 +43608,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1491" t="n">
-        <v>56.2057571411133</v>
+        <v>56.205753326416</v>
       </c>
       <c r="H1491" t="n">
         <v>2633</v>
@@ -43666,7 +43666,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>55.8253440856934</v>
+        <v>55.8253479003906</v>
       </c>
       <c r="H1493" t="n">
         <v>20583</v>
@@ -43724,7 +43724,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1495" t="n">
-        <v>56.2057571411133</v>
+        <v>56.205753326416</v>
       </c>
       <c r="H1495" t="n">
         <v>3100</v>
@@ -43753,7 +43753,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>56.3008651733398</v>
+        <v>56.3008613586426</v>
       </c>
       <c r="H1496" t="n">
         <v>2040</v>
@@ -43898,7 +43898,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1501" t="n">
-        <v>57.4420928955078</v>
+        <v>57.4420967102051</v>
       </c>
       <c r="H1501" t="n">
         <v>6459</v>
@@ -43956,7 +43956,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1503" t="n">
         <v>3852</v>
@@ -44188,7 +44188,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1511" t="n">
-        <v>57.4420928955078</v>
+        <v>57.4420967102051</v>
       </c>
       <c r="H1511" t="n">
         <v>20507</v>
@@ -44217,7 +44217,7 @@
         <v>59.5</v>
       </c>
       <c r="G1512" t="n">
-        <v>56.5861663818359</v>
+        <v>56.5861701965332</v>
       </c>
       <c r="H1512" t="n">
         <v>5412</v>
@@ -44246,7 +44246,7 @@
         <v>59.5</v>
       </c>
       <c r="G1513" t="n">
-        <v>56.5861663818359</v>
+        <v>56.5861701965332</v>
       </c>
       <c r="H1513" t="n">
         <v>3757</v>
@@ -44420,7 +44420,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1519" t="n">
-        <v>56.2057571411133</v>
+        <v>56.205753326416</v>
       </c>
       <c r="H1519" t="n">
         <v>2015</v>
@@ -44449,7 +44449,7 @@
         <v>58.7000007629395</v>
       </c>
       <c r="G1520" t="n">
-        <v>55.8253440856934</v>
+        <v>55.8253479003906</v>
       </c>
       <c r="H1520" t="n">
         <v>1640</v>
@@ -44565,7 +44565,7 @@
         <v>58.5</v>
       </c>
       <c r="G1524" t="n">
-        <v>55.635139465332</v>
+        <v>55.6351432800293</v>
       </c>
       <c r="H1524" t="n">
         <v>4981</v>
@@ -44652,7 +44652,7 @@
         <v>58.5</v>
       </c>
       <c r="G1527" t="n">
-        <v>55.635139465332</v>
+        <v>55.6351432800293</v>
       </c>
       <c r="H1527" t="n">
         <v>1406</v>
@@ -44681,7 +44681,7 @@
         <v>58.5</v>
       </c>
       <c r="G1528" t="n">
-        <v>55.635139465332</v>
+        <v>55.6351432800293</v>
       </c>
       <c r="H1528" t="n">
         <v>4081</v>
@@ -44768,7 +44768,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1531" t="n">
-        <v>55.2547302246094</v>
+        <v>55.2547264099121</v>
       </c>
       <c r="H1531" t="n">
         <v>2078</v>
@@ -44826,7 +44826,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1533" t="n">
-        <v>54.7792129516602</v>
+        <v>54.7792167663574</v>
       </c>
       <c r="H1533" t="n">
         <v>6649</v>
@@ -44855,7 +44855,7 @@
         <v>57.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>54.6841163635254</v>
+        <v>54.6841125488281</v>
       </c>
       <c r="H1534" t="n">
         <v>1379</v>
@@ -44884,7 +44884,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1535" t="n">
-        <v>55.2547302246094</v>
+        <v>55.2547264099121</v>
       </c>
       <c r="H1535" t="n">
         <v>2556</v>
@@ -44913,7 +44913,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1536" t="n">
-        <v>55.2547302246094</v>
+        <v>55.2547264099121</v>
       </c>
       <c r="H1536" t="n">
         <v>2855</v>
@@ -44971,7 +44971,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1538" t="n">
-        <v>54.1134986877441</v>
+        <v>54.1134948730469</v>
       </c>
       <c r="H1538" t="n">
         <v>2006</v>
@@ -45087,7 +45087,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>53.0673675537109</v>
+        <v>53.0673637390137</v>
       </c>
       <c r="H1542" t="n">
         <v>3001</v>
@@ -45145,7 +45145,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1544" t="n">
-        <v>53.1624717712402</v>
+        <v>53.162467956543</v>
       </c>
       <c r="H1544" t="n">
         <v>2282</v>
@@ -45232,7 +45232,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1547" t="n">
-        <v>53.5428771972656</v>
+        <v>53.5428810119629</v>
       </c>
       <c r="H1547" t="n">
         <v>704</v>
@@ -45261,7 +45261,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1548" t="n">
-        <v>52.8771629333496</v>
+        <v>52.8771553039551</v>
       </c>
       <c r="H1548" t="n">
         <v>1297</v>
@@ -45464,7 +45464,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1555" t="n">
-        <v>52.8771629333496</v>
+        <v>52.8771553039551</v>
       </c>
       <c r="H1555" t="n">
         <v>362</v>
@@ -45493,7 +45493,7 @@
         <v>55.2999992370605</v>
       </c>
       <c r="G1556" t="n">
-        <v>52.5918502807617</v>
+        <v>52.5918464660645</v>
       </c>
       <c r="H1556" t="n">
         <v>2970</v>
@@ -45638,7 +45638,7 @@
         <v>54.5</v>
       </c>
       <c r="G1561" t="n">
-        <v>51.8310279846191</v>
+        <v>51.8310317993164</v>
       </c>
       <c r="H1561" t="n">
         <v>8729</v>
@@ -45667,7 +45667,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1562" t="n">
-        <v>51.2604179382324</v>
+        <v>51.2604141235352</v>
       </c>
       <c r="H1562" t="n">
         <v>2719</v>
@@ -45870,7 +45870,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1569" t="n">
-        <v>51.2604179382324</v>
+        <v>51.2604141235352</v>
       </c>
       <c r="H1569" t="n">
         <v>2926</v>
@@ -45928,7 +45928,7 @@
         <v>53</v>
       </c>
       <c r="G1571" t="n">
-        <v>50.404483795166</v>
+        <v>50.4044876098633</v>
       </c>
       <c r="H1571" t="n">
         <v>1778</v>
@@ -45986,7 +45986,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>49.6436653137207</v>
+        <v>49.643669128418</v>
       </c>
       <c r="H1573" t="n">
         <v>4057</v>
@@ -46015,7 +46015,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1574" t="n">
-        <v>48.8828468322754</v>
+        <v>48.8828430175781</v>
       </c>
       <c r="H1574" t="n">
         <v>4069</v>
@@ -46160,7 +46160,7 @@
         <v>49</v>
       </c>
       <c r="G1579" t="n">
-        <v>46.6003761291504</v>
+        <v>46.6003723144531</v>
       </c>
       <c r="H1579" t="n">
         <v>3563</v>
@@ -46276,7 +46276,7 @@
         <v>47.5499992370605</v>
       </c>
       <c r="G1583" t="n">
-        <v>45.2213821411133</v>
+        <v>45.2213859558105</v>
       </c>
       <c r="H1583" t="n">
         <v>6805</v>
@@ -46334,7 +46334,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1585" t="n">
-        <v>43.1766738891602</v>
+        <v>43.1766777038574</v>
       </c>
       <c r="H1585" t="n">
         <v>16444</v>
@@ -46363,7 +46363,7 @@
         <v>46.5</v>
       </c>
       <c r="G1586" t="n">
-        <v>44.2228050231934</v>
+        <v>44.2228012084961</v>
       </c>
       <c r="H1586" t="n">
         <v>14423</v>
@@ -46450,7 +46450,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G1589" t="n">
-        <v>45.5542449951172</v>
+        <v>45.5542488098145</v>
       </c>
       <c r="H1589" t="n">
         <v>2191</v>
@@ -46479,7 +46479,7 @@
         <v>48.9500007629395</v>
       </c>
       <c r="G1590" t="n">
-        <v>46.5528259277344</v>
+        <v>46.5528221130371</v>
       </c>
       <c r="H1590" t="n">
         <v>8441</v>
@@ -46508,7 +46508,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1591" t="n">
-        <v>48.7877349853516</v>
+        <v>48.7877388000488</v>
       </c>
       <c r="H1591" t="n">
         <v>16510</v>
@@ -46595,7 +46595,7 @@
         <v>49.25</v>
       </c>
       <c r="G1594" t="n">
-        <v>46.838134765625</v>
+        <v>46.8381309509277</v>
       </c>
       <c r="H1594" t="n">
         <v>3122</v>
@@ -46653,7 +46653,7 @@
         <v>49.2999992370605</v>
       </c>
       <c r="G1596" t="n">
-        <v>46.885684967041</v>
+        <v>46.8856811523438</v>
       </c>
       <c r="H1596" t="n">
         <v>3011</v>
@@ -46682,7 +46682,7 @@
         <v>49</v>
       </c>
       <c r="G1597" t="n">
-        <v>46.6003761291504</v>
+        <v>46.6003723144531</v>
       </c>
       <c r="H1597" t="n">
         <v>2928</v>
@@ -46769,7 +46769,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G1600" t="n">
-        <v>46.1724090576172</v>
+        <v>46.1724128723145</v>
       </c>
       <c r="H1600" t="n">
         <v>565</v>
@@ -46798,7 +46798,7 @@
         <v>48.25</v>
       </c>
       <c r="G1601" t="n">
-        <v>45.8871078491211</v>
+        <v>45.8871040344238</v>
       </c>
       <c r="H1601" t="n">
         <v>13370</v>
@@ -46856,7 +46856,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1603" t="n">
-        <v>48.7877349853516</v>
+        <v>48.7877388000488</v>
       </c>
       <c r="H1603" t="n">
         <v>4600</v>
@@ -46972,7 +46972,7 @@
         <v>48.9000015258789</v>
       </c>
       <c r="G1607" t="n">
-        <v>46.5052719116211</v>
+        <v>46.5052757263184</v>
       </c>
       <c r="H1607" t="n">
         <v>4933</v>
@@ -47001,7 +47001,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>46.980785369873</v>
+        <v>46.9807891845703</v>
       </c>
       <c r="H1608" t="n">
         <v>2685</v>
@@ -47030,7 +47030,7 @@
         <v>49.8499984741211</v>
       </c>
       <c r="G1609" t="n">
-        <v>47.408748626709</v>
+        <v>47.4087448120117</v>
       </c>
       <c r="H1609" t="n">
         <v>1214</v>
@@ -47059,7 +47059,7 @@
         <v>49.4500007629395</v>
       </c>
       <c r="G1610" t="n">
-        <v>47.0283355712891</v>
+        <v>47.0283393859863</v>
       </c>
       <c r="H1610" t="n">
         <v>2132</v>
@@ -47175,7 +47175,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1614" t="n">
-        <v>49.833869934082</v>
+        <v>49.8338737487793</v>
       </c>
       <c r="H1614" t="n">
         <v>2347</v>
@@ -47349,7 +47349,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G1620" t="n">
-        <v>47.4563064575195</v>
+        <v>47.4563026428223</v>
       </c>
       <c r="H1620" t="n">
         <v>3176</v>
@@ -47378,7 +47378,7 @@
         <v>51.5</v>
       </c>
       <c r="G1621" t="n">
-        <v>48.9779472351074</v>
+        <v>48.9779434204102</v>
       </c>
       <c r="H1621" t="n">
         <v>2986</v>
@@ -47407,7 +47407,7 @@
         <v>51.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>48.9779472351074</v>
+        <v>48.9779434204102</v>
       </c>
       <c r="H1622" t="n">
         <v>1263</v>
@@ -47436,7 +47436,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G1623" t="n">
-        <v>48.5975303649902</v>
+        <v>48.5975341796875</v>
       </c>
       <c r="H1623" t="n">
         <v>4309</v>
@@ -47465,7 +47465,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1624" t="n">
-        <v>48.8828468322754</v>
+        <v>48.8828430175781</v>
       </c>
       <c r="H1624" t="n">
         <v>1935</v>
@@ -47523,7 +47523,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1626" t="n">
-        <v>51.2604179382324</v>
+        <v>51.2604141235352</v>
       </c>
       <c r="H1626" t="n">
         <v>11914</v>
@@ -47552,7 +47552,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1627" t="n">
-        <v>52.8771629333496</v>
+        <v>52.8771553039551</v>
       </c>
       <c r="H1627" t="n">
         <v>11544</v>
@@ -47610,7 +47610,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1629" t="n">
-        <v>52.686954498291</v>
+        <v>52.6869583129883</v>
       </c>
       <c r="H1629" t="n">
         <v>6837</v>
@@ -47668,7 +47668,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1631" t="n">
-        <v>52.686954498291</v>
+        <v>52.6869583129883</v>
       </c>
       <c r="H1631" t="n">
         <v>1580</v>
@@ -47697,7 +47697,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1632" t="n">
-        <v>52.8771629333496</v>
+        <v>52.8771553039551</v>
       </c>
       <c r="H1632" t="n">
         <v>4324</v>
@@ -47784,7 +47784,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1635" t="n">
-        <v>54.1134986877441</v>
+        <v>54.1134948730469</v>
       </c>
       <c r="H1635" t="n">
         <v>7941</v>
@@ -47813,7 +47813,7 @@
         <v>56</v>
       </c>
       <c r="G1636" t="n">
-        <v>53.2575721740723</v>
+        <v>53.2575759887695</v>
       </c>
       <c r="H1636" t="n">
         <v>8522</v>
@@ -47842,7 +47842,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G1637" t="n">
-        <v>53.0673675537109</v>
+        <v>53.0673637390137</v>
       </c>
       <c r="H1637" t="n">
         <v>6582</v>
@@ -47900,7 +47900,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1639" t="n">
-        <v>52.686954498291</v>
+        <v>52.6869583129883</v>
       </c>
       <c r="H1639" t="n">
         <v>1545</v>
@@ -48045,7 +48045,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G1644" t="n">
-        <v>53.5428771972656</v>
+        <v>53.5428810119629</v>
       </c>
       <c r="H1644" t="n">
         <v>3063</v>
@@ -48103,7 +48103,7 @@
         <v>56</v>
       </c>
       <c r="G1646" t="n">
-        <v>53.2575721740723</v>
+        <v>53.2575759887695</v>
       </c>
       <c r="H1646" t="n">
         <v>2964</v>
@@ -48132,7 +48132,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1647" t="n">
-        <v>53.1624717712402</v>
+        <v>53.162467956543</v>
       </c>
       <c r="H1647" t="n">
         <v>1754</v>
@@ -48161,7 +48161,7 @@
         <v>57</v>
       </c>
       <c r="G1648" t="n">
-        <v>54.2085990905762</v>
+        <v>54.2086029052734</v>
       </c>
       <c r="H1648" t="n">
         <v>5732</v>
@@ -48277,7 +48277,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>56.7763786315918</v>
+        <v>56.7763748168945</v>
       </c>
       <c r="H1652" t="n">
         <v>10689</v>
@@ -48306,7 +48306,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G1653" t="n">
-        <v>56.2057571411133</v>
+        <v>56.205753326416</v>
       </c>
       <c r="H1653" t="n">
         <v>5326</v>
@@ -48364,7 +48364,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1655" t="n">
-        <v>54.7792129516602</v>
+        <v>54.7792167663574</v>
       </c>
       <c r="H1655" t="n">
         <v>4992</v>
@@ -48393,7 +48393,7 @@
         <v>59.5</v>
       </c>
       <c r="G1656" t="n">
-        <v>56.5861663818359</v>
+        <v>56.5861701965332</v>
       </c>
       <c r="H1656" t="n">
         <v>55446</v>
@@ -48451,7 +48451,7 @@
         <v>60.5</v>
       </c>
       <c r="G1658" t="n">
-        <v>57.5372009277344</v>
+        <v>57.5371971130371</v>
       </c>
       <c r="H1658" t="n">
         <v>8090</v>
@@ -48480,7 +48480,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1659" t="n">
-        <v>57.2518882751465</v>
+        <v>57.2518920898438</v>
       </c>
       <c r="H1659" t="n">
         <v>4972</v>
@@ -48596,7 +48596,7 @@
         <v>62</v>
       </c>
       <c r="G1663" t="n">
-        <v>58.963737487793</v>
+        <v>58.9637413024902</v>
       </c>
       <c r="H1663" t="n">
         <v>2529</v>
@@ -48625,7 +48625,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>59.1539497375488</v>
+        <v>59.1539459228516</v>
       </c>
       <c r="H1664" t="n">
         <v>7902</v>
@@ -48654,7 +48654,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1665" t="n">
         <v>6024</v>
@@ -48683,7 +48683,7 @@
         <v>62</v>
       </c>
       <c r="G1666" t="n">
-        <v>58.963737487793</v>
+        <v>58.9637413024902</v>
       </c>
       <c r="H1666" t="n">
         <v>4789</v>
@@ -48712,7 +48712,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1667" t="n">
-        <v>57.4420928955078</v>
+        <v>57.4420967102051</v>
       </c>
       <c r="H1667" t="n">
         <v>6641</v>
@@ -48741,7 +48741,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1668" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1668" t="n">
         <v>4693</v>
@@ -48770,7 +48770,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1669" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1669" t="n">
         <v>3555</v>
@@ -48799,7 +48799,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1670" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1670" t="n">
         <v>4025</v>
@@ -48828,7 +48828,7 @@
         <v>60.5</v>
       </c>
       <c r="G1671" t="n">
-        <v>57.5372009277344</v>
+        <v>57.5371971130371</v>
       </c>
       <c r="H1671" t="n">
         <v>2631</v>
@@ -48886,7 +48886,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1673" t="n">
-        <v>59.7245597839355</v>
+        <v>59.7245635986328</v>
       </c>
       <c r="H1673" t="n">
         <v>9087</v>
@@ -48915,7 +48915,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G1674" t="n">
-        <v>60.0098686218262</v>
+        <v>60.0098724365234</v>
       </c>
       <c r="H1674" t="n">
         <v>10808</v>
@@ -48944,7 +48944,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1675" t="n">
-        <v>59.5343551635742</v>
+        <v>59.5343589782715</v>
       </c>
       <c r="H1675" t="n">
         <v>9876</v>
@@ -49002,7 +49002,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1677" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1677" t="n">
         <v>2547</v>
@@ -49031,7 +49031,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1678" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1678" t="n">
         <v>4489</v>
@@ -49060,7 +49060,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G1679" t="n">
-        <v>58.2029151916504</v>
+        <v>58.2029190063477</v>
       </c>
       <c r="H1679" t="n">
         <v>3557</v>
@@ -49176,7 +49176,7 @@
         <v>60.5</v>
       </c>
       <c r="G1683" t="n">
-        <v>57.5372009277344</v>
+        <v>57.5371971130371</v>
       </c>
       <c r="H1683" t="n">
         <v>2906</v>
@@ -49205,7 +49205,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1684" t="n">
-        <v>56.7763786315918</v>
+        <v>56.7763748168945</v>
       </c>
       <c r="H1684" t="n">
         <v>5568</v>
@@ -49263,7 +49263,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>56.3008651733398</v>
+        <v>56.3008613586426</v>
       </c>
       <c r="H1686" t="n">
         <v>3846</v>
@@ -49292,7 +49292,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1687" t="n">
-        <v>57.2518882751465</v>
+        <v>57.2518920898438</v>
       </c>
       <c r="H1687" t="n">
         <v>6610</v>
@@ -49321,7 +49321,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G1688" t="n">
-        <v>56.3008651733398</v>
+        <v>56.3008613586426</v>
       </c>
       <c r="H1688" t="n">
         <v>3383</v>
@@ -49495,7 +49495,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G1694" t="n">
-        <v>56.7763786315918</v>
+        <v>56.7763748168945</v>
       </c>
       <c r="H1694" t="n">
         <v>2571</v>
@@ -49524,7 +49524,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G1695" t="n">
-        <v>56.3959617614746</v>
+        <v>56.3959655761719</v>
       </c>
       <c r="H1695" t="n">
         <v>2243</v>
@@ -49553,7 +49553,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G1696" t="n">
-        <v>56.3008651733398</v>
+        <v>56.3008613586426</v>
       </c>
       <c r="H1696" t="n">
         <v>4574</v>
@@ -49698,7 +49698,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1701" t="n">
-        <v>55.2547302246094</v>
+        <v>55.2547264099121</v>
       </c>
       <c r="H1701" t="n">
         <v>5255</v>
@@ -49756,7 +49756,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1703" t="n">
-        <v>54.7792129516602</v>
+        <v>54.7792167663574</v>
       </c>
       <c r="H1703" t="n">
         <v>3738</v>
@@ -49814,7 +49814,7 @@
         <v>57</v>
       </c>
       <c r="G1705" t="n">
-        <v>54.2085990905762</v>
+        <v>54.2086029052734</v>
       </c>
       <c r="H1705" t="n">
         <v>6565</v>
@@ -49901,7 +49901,7 @@
         <v>56</v>
       </c>
       <c r="G1708" t="n">
-        <v>53.2575721740723</v>
+        <v>53.2575759887695</v>
       </c>
       <c r="H1708" t="n">
         <v>2250</v>
@@ -49988,7 +49988,7 @@
         <v>54.7999992370605</v>
       </c>
       <c r="G1711" t="n">
-        <v>52.116340637207</v>
+        <v>52.1163368225098</v>
       </c>
       <c r="H1711" t="n">
         <v>4411</v>
@@ -50017,7 +50017,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1712" t="n">
-        <v>51.2604179382324</v>
+        <v>51.2604141235352</v>
       </c>
       <c r="H1712" t="n">
         <v>6885</v>
@@ -50133,7 +50133,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1716" t="n">
-        <v>51.1653060913086</v>
+        <v>51.1653099060059</v>
       </c>
       <c r="H1716" t="n">
         <v>5423</v>
@@ -50162,7 +50162,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G1717" t="n">
-        <v>51.1653060913086</v>
+        <v>51.1653099060059</v>
       </c>
       <c r="H1717" t="n">
         <v>2501</v>
@@ -50191,7 +50191,7 @@
         <v>53</v>
       </c>
       <c r="G1718" t="n">
-        <v>50.404483795166</v>
+        <v>50.4044876098633</v>
       </c>
       <c r="H1718" t="n">
         <v>3597</v>
@@ -50220,7 +50220,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1719" t="n">
-        <v>49.263256072998</v>
+        <v>49.2632522583008</v>
       </c>
       <c r="H1719" t="n">
         <v>12468</v>
@@ -50278,7 +50278,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1721" t="n">
-        <v>51.2604179382324</v>
+        <v>51.2604141235352</v>
       </c>
       <c r="H1721" t="n">
         <v>3934</v>
@@ -50307,7 +50307,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1722" t="n">
-        <v>50.4995918273926</v>
+        <v>50.4995880126953</v>
       </c>
       <c r="H1722" t="n">
         <v>3955</v>
@@ -50365,7 +50365,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G1724" t="n">
-        <v>50.6897964477539</v>
+        <v>50.6897926330566</v>
       </c>
       <c r="H1724" t="n">
         <v>2797</v>
@@ -50394,7 +50394,7 @@
         <v>54</v>
       </c>
       <c r="G1725" t="n">
-        <v>51.3555183410645</v>
+        <v>51.3555145263672</v>
       </c>
       <c r="H1725" t="n">
         <v>6074</v>
@@ -50452,7 +50452,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1727" t="n">
-        <v>49.3583564758301</v>
+        <v>49.3583602905273</v>
       </c>
       <c r="H1727" t="n">
         <v>14723</v>
@@ -50655,7 +50655,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G1734" t="n">
-        <v>49.0168266296387</v>
+        <v>49.0168228149414</v>
       </c>
       <c r="H1734" t="n">
         <v>4123</v>
@@ -50742,7 +50742,7 @@
         <v>48.25</v>
       </c>
       <c r="G1737" t="n">
-        <v>46.6481628417969</v>
+        <v>46.6481590270996</v>
       </c>
       <c r="H1737" t="n">
         <v>12798</v>
@@ -50771,7 +50771,7 @@
         <v>48</v>
       </c>
       <c r="G1738" t="n">
-        <v>46.4064559936523</v>
+        <v>46.4064598083496</v>
       </c>
       <c r="H1738" t="n">
         <v>8909</v>
@@ -50800,7 +50800,7 @@
         <v>48.25</v>
       </c>
       <c r="G1739" t="n">
-        <v>46.6481628417969</v>
+        <v>46.6481590270996</v>
       </c>
       <c r="H1739" t="n">
         <v>7440</v>
@@ -50829,7 +50829,7 @@
         <v>48.25</v>
       </c>
       <c r="G1740" t="n">
-        <v>46.6481628417969</v>
+        <v>46.6481590270996</v>
       </c>
       <c r="H1740" t="n">
         <v>4589</v>
@@ -50974,7 +50974,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>47.4699363708496</v>
+        <v>47.4699401855469</v>
       </c>
       <c r="H1745" t="n">
         <v>5196</v>
@@ -51032,7 +51032,7 @@
         <v>48.4500007629395</v>
       </c>
       <c r="G1747" t="n">
-        <v>46.8415222167969</v>
+        <v>46.8415184020996</v>
       </c>
       <c r="H1747" t="n">
         <v>6424</v>
@@ -51061,7 +51061,7 @@
         <v>49.25</v>
       </c>
       <c r="G1748" t="n">
-        <v>47.6149597167969</v>
+        <v>47.6149635314941</v>
       </c>
       <c r="H1748" t="n">
         <v>13987</v>
@@ -51177,7 +51177,7 @@
         <v>48</v>
       </c>
       <c r="G1752" t="n">
-        <v>46.4064559936523</v>
+        <v>46.4064598083496</v>
       </c>
       <c r="H1752" t="n">
         <v>7366</v>
@@ -51351,7 +51351,7 @@
         <v>46.0499992370605</v>
       </c>
       <c r="G1758" t="n">
-        <v>44.5211982727051</v>
+        <v>44.5211944580078</v>
       </c>
       <c r="H1758" t="n">
         <v>22829</v>
@@ -51467,7 +51467,7 @@
         <v>47.4500007629395</v>
       </c>
       <c r="G1762" t="n">
-        <v>45.8747215270996</v>
+        <v>45.8747177124023</v>
       </c>
       <c r="H1762" t="n">
         <v>16906</v>
@@ -51525,7 +51525,7 @@
         <v>47.5</v>
       </c>
       <c r="G1764" t="n">
-        <v>45.9230575561523</v>
+        <v>45.9230613708496</v>
       </c>
       <c r="H1764" t="n">
         <v>3409</v>
@@ -51844,7 +51844,7 @@
         <v>48</v>
       </c>
       <c r="G1775" t="n">
-        <v>46.4064559936523</v>
+        <v>46.4064598083496</v>
       </c>
       <c r="H1775" t="n">
         <v>2868</v>
@@ -51931,7 +51931,7 @@
         <v>48.25</v>
       </c>
       <c r="G1778" t="n">
-        <v>46.6481628417969</v>
+        <v>46.6481590270996</v>
       </c>
       <c r="H1778" t="n">
         <v>2304</v>
@@ -52018,7 +52018,7 @@
         <v>48.2000007629395</v>
       </c>
       <c r="G1781" t="n">
-        <v>46.5998229980469</v>
+        <v>46.5998191833496</v>
       </c>
       <c r="H1781" t="n">
         <v>2415</v>
@@ -52134,7 +52134,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G1785" t="n">
-        <v>45.5846824645996</v>
+        <v>45.5846786499023</v>
       </c>
       <c r="H1785" t="n">
         <v>2631</v>
@@ -52163,7 +52163,7 @@
         <v>47.75</v>
       </c>
       <c r="G1786" t="n">
-        <v>46.1647567749023</v>
+        <v>46.1647605895996</v>
       </c>
       <c r="H1786" t="n">
         <v>1985</v>
@@ -52279,7 +52279,7 @@
         <v>47.8499984741211</v>
       </c>
       <c r="G1790" t="n">
-        <v>46.2614364624023</v>
+        <v>46.2614402770996</v>
       </c>
       <c r="H1790" t="n">
         <v>1116</v>
@@ -52453,7 +52453,7 @@
         <v>47.4500007629395</v>
       </c>
       <c r="G1796" t="n">
-        <v>45.8747215270996</v>
+        <v>45.8747177124023</v>
       </c>
       <c r="H1796" t="n">
         <v>1134</v>
@@ -52656,7 +52656,7 @@
         <v>49.3499984741211</v>
       </c>
       <c r="G1803" t="n">
-        <v>47.7116432189941</v>
+        <v>47.7116394042969</v>
       </c>
       <c r="H1803" t="n">
         <v>1192</v>
@@ -52859,7 +52859,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1810" t="n">
-        <v>49.5969009399414</v>
+        <v>49.5969047546387</v>
       </c>
       <c r="H1810" t="n">
         <v>4232</v>
@@ -53381,7 +53381,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1828" t="n">
-        <v>55.4943923950195</v>
+        <v>55.4943962097168</v>
       </c>
       <c r="H1828" t="n">
         <v>1941</v>
@@ -53410,7 +53410,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1829" t="n">
-        <v>56.1711540222168</v>
+        <v>56.1711502075195</v>
       </c>
       <c r="H1829" t="n">
         <v>2077</v>
@@ -53555,7 +53555,7 @@
         <v>57</v>
       </c>
       <c r="G1834" t="n">
-        <v>55.1076736450195</v>
+        <v>55.1076698303223</v>
       </c>
       <c r="H1834" t="n">
         <v>4201</v>
@@ -53613,7 +53613,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1836" t="n">
-        <v>53.2707481384277</v>
+        <v>53.2707443237305</v>
       </c>
       <c r="H1836" t="n">
         <v>3803</v>
@@ -53642,7 +53642,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1837" t="n">
-        <v>53.0773887634277</v>
+        <v>53.077392578125</v>
       </c>
       <c r="H1837" t="n">
         <v>5249</v>
@@ -53729,7 +53729,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1840" t="n">
-        <v>53.5607872009277</v>
+        <v>53.560791015625</v>
       </c>
       <c r="H1840" t="n">
         <v>11120</v>
@@ -53816,7 +53816,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1843" t="n">
-        <v>55.4943923950195</v>
+        <v>55.4943962097168</v>
       </c>
       <c r="H1843" t="n">
         <v>3819</v>
@@ -53903,7 +53903,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G1846" t="n">
-        <v>56.1711540222168</v>
+        <v>56.1711502075195</v>
       </c>
       <c r="H1846" t="n">
         <v>6678</v>
@@ -54048,7 +54048,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1851" t="n">
-        <v>53.754150390625</v>
+        <v>53.7541465759277</v>
       </c>
       <c r="H1851" t="n">
         <v>1761</v>
@@ -54106,7 +54106,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G1853" t="n">
-        <v>55.4943923950195</v>
+        <v>55.4943962097168</v>
       </c>
       <c r="H1853" t="n">
         <v>1538</v>
@@ -54135,7 +54135,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1854" t="n">
-        <v>54.914306640625</v>
+        <v>54.9143104553223</v>
       </c>
       <c r="H1854" t="n">
         <v>2669</v>
@@ -54164,7 +54164,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1855" t="n">
-        <v>53.754150390625</v>
+        <v>53.7541465759277</v>
       </c>
       <c r="H1855" t="n">
         <v>2839</v>
@@ -54280,7 +54280,7 @@
         <v>53</v>
       </c>
       <c r="G1859" t="n">
-        <v>51.2404632568359</v>
+        <v>51.2404670715332</v>
       </c>
       <c r="H1859" t="n">
         <v>17183</v>
@@ -54309,7 +54309,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1860" t="n">
-        <v>50.8537445068359</v>
+        <v>50.8537406921387</v>
       </c>
       <c r="H1860" t="n">
         <v>9585</v>
@@ -54454,7 +54454,7 @@
         <v>57</v>
       </c>
       <c r="G1865" t="n">
-        <v>55.1076736450195</v>
+        <v>55.1076698303223</v>
       </c>
       <c r="H1865" t="n">
         <v>5904</v>
@@ -54686,7 +54686,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1873" t="n">
-        <v>53.0773887634277</v>
+        <v>53.077392578125</v>
       </c>
       <c r="H1873" t="n">
         <v>3146</v>
@@ -54744,7 +54744,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1875" t="n">
-        <v>53.5607872009277</v>
+        <v>53.560791015625</v>
       </c>
       <c r="H1875" t="n">
         <v>1086</v>
@@ -54889,7 +54889,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1880" t="n">
-        <v>53.0773887634277</v>
+        <v>53.077392578125</v>
       </c>
       <c r="H1880" t="n">
         <v>2906</v>
@@ -54918,7 +54918,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1881" t="n">
-        <v>53.2707481384277</v>
+        <v>53.2707443237305</v>
       </c>
       <c r="H1881" t="n">
         <v>1253</v>
@@ -55092,7 +55092,7 @@
         <v>54.5</v>
       </c>
       <c r="G1887" t="n">
-        <v>52.6906700134277</v>
+        <v>52.6906661987305</v>
       </c>
       <c r="H1887" t="n">
         <v>28310</v>
@@ -55150,7 +55150,7 @@
         <v>54</v>
       </c>
       <c r="G1889" t="n">
-        <v>52.2072677612305</v>
+        <v>52.2072639465332</v>
       </c>
       <c r="H1889" t="n">
         <v>2997</v>
@@ -55266,7 +55266,7 @@
         <v>54</v>
       </c>
       <c r="G1893" t="n">
-        <v>52.2072677612305</v>
+        <v>52.2072639465332</v>
       </c>
       <c r="H1893" t="n">
         <v>870</v>
@@ -55440,7 +55440,7 @@
         <v>53</v>
       </c>
       <c r="G1899" t="n">
-        <v>51.2404632568359</v>
+        <v>51.2404670715332</v>
       </c>
       <c r="H1899" t="n">
         <v>4188</v>
@@ -55498,7 +55498,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1901" t="n">
-        <v>50.8537445068359</v>
+        <v>50.8537406921387</v>
       </c>
       <c r="H1901" t="n">
         <v>5689</v>
@@ -55614,7 +55614,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1905" t="n">
-        <v>50.6603851318359</v>
+        <v>50.6603889465332</v>
       </c>
       <c r="H1905" t="n">
         <v>2333</v>
@@ -55730,7 +55730,7 @@
         <v>52.5</v>
       </c>
       <c r="G1909" t="n">
-        <v>50.7570648193359</v>
+        <v>50.7570686340332</v>
       </c>
       <c r="H1909" t="n">
         <v>2398</v>
@@ -55759,7 +55759,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1910" t="n">
-        <v>50.6603851318359</v>
+        <v>50.6603889465332</v>
       </c>
       <c r="H1910" t="n">
         <v>2425</v>
@@ -55875,7 +55875,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G1914" t="n">
-        <v>49.0168266296387</v>
+        <v>49.0168228149414</v>
       </c>
       <c r="H1914" t="n">
         <v>8427</v>
@@ -55904,7 +55904,7 @@
         <v>50.5</v>
       </c>
       <c r="G1915" t="n">
-        <v>48.8234596252441</v>
+        <v>48.8234634399414</v>
       </c>
       <c r="H1915" t="n">
         <v>4977</v>
@@ -56020,7 +56020,7 @@
         <v>52.4000015258789</v>
       </c>
       <c r="G1919" t="n">
-        <v>50.6603851318359</v>
+        <v>50.6603889465332</v>
       </c>
       <c r="H1919" t="n">
         <v>3266</v>
@@ -56078,7 +56078,7 @@
         <v>52.5</v>
       </c>
       <c r="G1921" t="n">
-        <v>50.7570648193359</v>
+        <v>50.7570686340332</v>
       </c>
       <c r="H1921" t="n">
         <v>3895</v>
@@ -56339,7 +56339,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G1930" t="n">
-        <v>52.4973030090332</v>
+        <v>52.4973068237305</v>
       </c>
       <c r="H1930" t="n">
         <v>7946</v>
@@ -56368,7 +56368,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G1931" t="n">
-        <v>53.2707481384277</v>
+        <v>53.2707443237305</v>
       </c>
       <c r="H1931" t="n">
         <v>7341</v>
@@ -56774,7 +56774,7 @@
         <v>54</v>
       </c>
       <c r="G1945" t="n">
-        <v>52.2072677612305</v>
+        <v>52.2072639465332</v>
       </c>
       <c r="H1945" t="n">
         <v>14594</v>
@@ -56977,7 +56977,7 @@
         <v>49.25</v>
       </c>
       <c r="G1952" t="n">
-        <v>47.6149597167969</v>
+        <v>47.6149635314941</v>
       </c>
       <c r="H1952" t="n">
         <v>24970</v>
@@ -57064,7 +57064,7 @@
         <v>48.8499984741211</v>
       </c>
       <c r="G1955" t="n">
-        <v>47.2282371520996</v>
+        <v>47.2282409667969</v>
       </c>
       <c r="H1955" t="n">
         <v>7459</v>
@@ -57122,7 +57122,7 @@
         <v>49.25</v>
       </c>
       <c r="G1957" t="n">
-        <v>47.6149597167969</v>
+        <v>47.6149635314941</v>
       </c>
       <c r="H1957" t="n">
         <v>4605</v>
@@ -57267,7 +57267,7 @@
         <v>48.25</v>
       </c>
       <c r="G1962" t="n">
-        <v>46.6481628417969</v>
+        <v>46.6481590270996</v>
       </c>
       <c r="H1962" t="n">
         <v>12015</v>
@@ -57296,7 +57296,7 @@
         <v>47.1500015258789</v>
       </c>
       <c r="G1963" t="n">
-        <v>45.5846824645996</v>
+        <v>45.5846786499023</v>
       </c>
       <c r="H1963" t="n">
         <v>10367</v>
@@ -57499,7 +57499,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1970" t="n">
-        <v>49.5969009399414</v>
+        <v>49.5969047546387</v>
       </c>
       <c r="H1970" t="n">
         <v>6798</v>
@@ -57557,7 +57557,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G1972" t="n">
-        <v>49.0168266296387</v>
+        <v>49.0168228149414</v>
       </c>
       <c r="H1972" t="n">
         <v>3589</v>
@@ -57586,7 +57586,7 @@
         <v>50.5</v>
       </c>
       <c r="G1973" t="n">
-        <v>48.8234596252441</v>
+        <v>48.8234634399414</v>
       </c>
       <c r="H1973" t="n">
         <v>2070</v>
@@ -57615,7 +57615,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1974" t="n">
-        <v>49.5969009399414</v>
+        <v>49.5969047546387</v>
       </c>
       <c r="H1974" t="n">
         <v>3776</v>
@@ -68641,6 +68641,35 @@
         <v>26338</v>
       </c>
       <c r="I2354" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2355" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2355" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="D2355" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E2355" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="F2355" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="G2355" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="H2355" t="n">
+        <v>7198</v>
+      </c>
+      <c r="I2355" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PHN.MI.xlsx
+++ b/data/PHN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>11.8307590484619</v>
+        <v>11.8307580947876</v>
       </c>
       <c r="H2" t="n">
         <v>167700</v>
@@ -456,7 +456,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>11.7123651504517</v>
+        <v>11.712366104126</v>
       </c>
       <c r="H3" t="n">
         <v>99700</v>
@@ -485,7 +485,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G4" t="n">
-        <v>11.1795997619629</v>
+        <v>11.1796016693115</v>
       </c>
       <c r="H4" t="n">
         <v>83600</v>
@@ -514,7 +514,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G5" t="n">
-        <v>11.027382850647</v>
+        <v>11.0273809432983</v>
       </c>
       <c r="H5" t="n">
         <v>5500</v>
@@ -572,7 +572,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H7" t="n">
         <v>5100</v>
@@ -630,7 +630,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>11.1457757949829</v>
+        <v>11.1457738876343</v>
       </c>
       <c r="H9" t="n">
         <v>12000</v>
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H13" t="n">
         <v>7400</v>
@@ -775,7 +775,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G14" t="n">
-        <v>11.027382850647</v>
+        <v>11.0273809432983</v>
       </c>
       <c r="H14" t="n">
         <v>1700</v>
@@ -804,7 +804,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G15" t="n">
-        <v>11.0781221389771</v>
+        <v>11.0781230926514</v>
       </c>
       <c r="H15" t="n">
         <v>2900</v>
@@ -833,7 +833,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G16" t="n">
-        <v>11.0189266204834</v>
+        <v>11.0189275741577</v>
       </c>
       <c r="H16" t="n">
         <v>3800</v>
@@ -891,7 +891,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G18" t="n">
-        <v>11.1034927368164</v>
+        <v>11.1034917831421</v>
       </c>
       <c r="H18" t="n">
         <v>3600</v>
@@ -920,7 +920,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>11.0358400344849</v>
+        <v>11.0358390808105</v>
       </c>
       <c r="H19" t="n">
         <v>1100</v>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H20" t="n">
         <v>2800</v>
@@ -978,7 +978,7 @@
         <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H21" t="n">
         <v>6300</v>
@@ -1036,7 +1036,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>11.1204042434692</v>
+        <v>11.1204051971436</v>
       </c>
       <c r="H23" t="n">
         <v>1700</v>
@@ -1094,7 +1094,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G25" t="n">
-        <v>11.1034927368164</v>
+        <v>11.1034917831421</v>
       </c>
       <c r="H25" t="n">
         <v>200</v>
@@ -1123,7 +1123,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>11.0781221389771</v>
+        <v>11.0781230926514</v>
       </c>
       <c r="H26" t="n">
         <v>2000</v>
@@ -1152,7 +1152,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512739181519</v>
       </c>
       <c r="H27" t="n">
         <v>1300</v>
@@ -1210,7 +1210,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>10.9850997924805</v>
+        <v>10.9850988388062</v>
       </c>
       <c r="H29" t="n">
         <v>3800</v>
@@ -1268,7 +1268,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H31" t="n">
         <v>4100</v>
@@ -1326,7 +1326,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H33" t="n">
         <v>4700</v>
@@ -1355,7 +1355,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7652292251587</v>
+        <v>10.7652282714844</v>
       </c>
       <c r="H34" t="n">
         <v>4500</v>
@@ -1413,7 +1413,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G36" t="n">
-        <v>11.0696659088135</v>
+        <v>11.0696649551392</v>
       </c>
       <c r="H36" t="n">
         <v>11400</v>
@@ -1442,7 +1442,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>10.9428157806396</v>
+        <v>10.942816734314</v>
       </c>
       <c r="H37" t="n">
         <v>2100</v>
@@ -1471,7 +1471,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G38" t="n">
-        <v>10.9343595504761</v>
+        <v>10.9343605041504</v>
       </c>
       <c r="H38" t="n">
         <v>1700</v>
@@ -1500,7 +1500,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G39" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512739181519</v>
       </c>
       <c r="H39" t="n">
         <v>3800</v>
@@ -1558,7 +1558,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0781221389771</v>
+        <v>11.0781230926514</v>
       </c>
       <c r="H41" t="n">
         <v>3100</v>
@@ -1587,7 +1587,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G42" t="n">
-        <v>11.2387971878052</v>
+        <v>11.2387962341309</v>
       </c>
       <c r="H42" t="n">
         <v>13400</v>
@@ -1761,7 +1761,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H48" t="n">
         <v>5200</v>
@@ -1790,7 +1790,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H49" t="n">
         <v>1800</v>
@@ -1848,7 +1848,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G51" t="n">
-        <v>11.4671258926392</v>
+        <v>11.4671249389648</v>
       </c>
       <c r="H51" t="n">
         <v>500</v>
@@ -1877,7 +1877,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>11.4586687088013</v>
+        <v>11.458667755127</v>
       </c>
       <c r="H52" t="n">
         <v>1500</v>
@@ -1906,7 +1906,7 @@
         <v>13.5</v>
       </c>
       <c r="G53" t="n">
-        <v>11.4163866043091</v>
+        <v>11.4163846969604</v>
       </c>
       <c r="H53" t="n">
         <v>1200</v>
@@ -1964,7 +1964,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G55" t="n">
-        <v>11.3318176269531</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H55" t="n">
         <v>34600</v>
@@ -1993,7 +1993,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>11.2810792922974</v>
+        <v>11.2810802459717</v>
       </c>
       <c r="H56" t="n">
         <v>7600</v>
@@ -2051,7 +2051,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G58" t="n">
-        <v>11.1288614273071</v>
+        <v>11.1288623809814</v>
       </c>
       <c r="H58" t="n">
         <v>1500</v>
@@ -2080,7 +2080,7 @@
         <v>13</v>
       </c>
       <c r="G59" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H59" t="n">
         <v>9700</v>
@@ -2109,7 +2109,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G60" t="n">
-        <v>11.1457757949829</v>
+        <v>11.1457738876343</v>
       </c>
       <c r="H60" t="n">
         <v>1200</v>
@@ -2138,7 +2138,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>11.1204042434692</v>
+        <v>11.1204051971436</v>
       </c>
       <c r="H61" t="n">
         <v>6300</v>
@@ -2167,7 +2167,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G62" t="n">
-        <v>11.1457757949829</v>
+        <v>11.1457738876343</v>
       </c>
       <c r="H62" t="n">
         <v>2100</v>
@@ -2196,7 +2196,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G63" t="n">
-        <v>11.052752494812</v>
+        <v>11.0527505874634</v>
       </c>
       <c r="H63" t="n">
         <v>13700</v>
@@ -2225,7 +2225,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G64" t="n">
-        <v>11.1542310714722</v>
+        <v>11.1542301177979</v>
       </c>
       <c r="H64" t="n">
         <v>1500</v>
@@ -2254,7 +2254,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>10.9428157806396</v>
+        <v>10.942816734314</v>
       </c>
       <c r="H65" t="n">
         <v>1100</v>
@@ -2283,7 +2283,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>11.0020122528076</v>
+        <v>11.0020132064819</v>
       </c>
       <c r="H66" t="n">
         <v>3400</v>
@@ -2341,7 +2341,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H68" t="n">
         <v>1800</v>
@@ -2370,7 +2370,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G69" t="n">
-        <v>10.858250617981</v>
+        <v>10.8582496643066</v>
       </c>
       <c r="H69" t="n">
         <v>3700</v>
@@ -2399,7 +2399,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G70" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328819274902</v>
       </c>
       <c r="H70" t="n">
         <v>3300</v>
@@ -2428,7 +2428,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G71" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328819274902</v>
       </c>
       <c r="H71" t="n">
         <v>900</v>
@@ -2573,7 +2573,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G76" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328819274902</v>
       </c>
       <c r="H76" t="n">
         <v>1600</v>
@@ -2718,7 +2718,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>10.9259042739868</v>
+        <v>10.9259033203125</v>
       </c>
       <c r="H81" t="n">
         <v>1600</v>
@@ -2776,7 +2776,7 @@
         <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H83" t="n">
         <v>6800</v>
@@ -2834,7 +2834,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H85" t="n">
         <v>9800</v>
@@ -2950,7 +2950,7 @@
         <v>13</v>
       </c>
       <c r="G89" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H89" t="n">
         <v>43500</v>
@@ -2979,7 +2979,7 @@
         <v>13</v>
       </c>
       <c r="G90" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H90" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G91" t="n">
-        <v>10.9850997924805</v>
+        <v>10.9850988388062</v>
       </c>
       <c r="H91" t="n">
         <v>3900</v>
@@ -3037,7 +3037,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H92" t="n">
         <v>900</v>
@@ -3066,7 +3066,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.6383781433105</v>
+        <v>10.6383800506592</v>
       </c>
       <c r="H93" t="n">
         <v>3300</v>
@@ -3095,7 +3095,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G94" t="n">
-        <v>10.6383781433105</v>
+        <v>10.6383800506592</v>
       </c>
       <c r="H94" t="n">
         <v>200</v>
@@ -3124,7 +3124,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H95" t="n">
         <v>1700</v>
@@ -3153,7 +3153,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>10.6130094528198</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H98" t="n">
         <v>3200</v>
@@ -3240,7 +3240,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H99" t="n">
         <v>1500</v>
@@ -3298,7 +3298,7 @@
         <v>12.75</v>
       </c>
       <c r="G101" t="n">
-        <v>10.7821407318115</v>
+        <v>10.7821416854858</v>
       </c>
       <c r="H101" t="n">
         <v>7700</v>
@@ -3385,7 +3385,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G104" t="n">
-        <v>10.7144899368286</v>
+        <v>10.7144889831543</v>
       </c>
       <c r="H104" t="n">
         <v>300</v>
@@ -3443,7 +3443,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G106" t="n">
-        <v>10.8497943878174</v>
+        <v>10.8497953414917</v>
       </c>
       <c r="H106" t="n">
         <v>500</v>
@@ -3472,7 +3472,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H107" t="n">
         <v>1900</v>
@@ -3501,7 +3501,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G108" t="n">
-        <v>10.8328809738159</v>
+        <v>10.8328819274902</v>
       </c>
       <c r="H108" t="n">
         <v>5200</v>
@@ -3530,7 +3530,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G109" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H109" t="n">
         <v>600</v>
@@ -3588,7 +3588,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.706033706665</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H111" t="n">
         <v>7100</v>
@@ -3617,7 +3617,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G112" t="n">
-        <v>10.706033706665</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G113" t="n">
-        <v>10.706033706665</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G114" t="n">
-        <v>10.706033706665</v>
+        <v>10.7060317993164</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H115" t="n">
         <v>600</v>
@@ -3733,7 +3733,7 @@
         <v>12.75</v>
       </c>
       <c r="G116" t="n">
-        <v>10.7821407318115</v>
+        <v>10.7821416854858</v>
       </c>
       <c r="H116" t="n">
         <v>1500</v>
@@ -3762,7 +3762,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H117" t="n">
         <v>3300</v>
@@ -3791,7 +3791,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H118" t="n">
         <v>1000</v>
@@ -3878,7 +3878,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>10.6130094528198</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H121" t="n">
         <v>1300</v>
@@ -3907,7 +3907,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>10.6130094528198</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655294418335</v>
       </c>
       <c r="H123" t="n">
         <v>1800</v>
@@ -3965,7 +3965,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H124" t="n">
         <v>1000</v>
@@ -3994,7 +3994,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G125" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H125" t="n">
         <v>1300</v>
@@ -4052,7 +4052,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H127" t="n">
         <v>200</v>
@@ -4081,7 +4081,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H128" t="n">
         <v>800</v>
@@ -4110,7 +4110,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H131" t="n">
         <v>1200</v>
@@ -4197,7 +4197,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655294418335</v>
       </c>
       <c r="H133" t="n">
         <v>2100</v>
@@ -4255,7 +4255,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655294418335</v>
       </c>
       <c r="H134" t="n">
         <v>500</v>
@@ -4284,7 +4284,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655294418335</v>
       </c>
       <c r="H135" t="n">
         <v>900</v>
@@ -4342,7 +4342,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>10.4438781738281</v>
+        <v>10.4438791275024</v>
       </c>
       <c r="H137" t="n">
         <v>4600</v>
@@ -4371,7 +4371,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>10.4015970230103</v>
+        <v>10.4015960693359</v>
       </c>
       <c r="H138" t="n">
         <v>6500</v>
@@ -4400,7 +4400,7 @@
         <v>12.25</v>
       </c>
       <c r="G139" t="n">
-        <v>10.3593120574951</v>
+        <v>10.3593111038208</v>
       </c>
       <c r="H139" t="n">
         <v>18900</v>
@@ -4429,7 +4429,7 @@
         <v>12.75</v>
       </c>
       <c r="G140" t="n">
-        <v>10.7821407318115</v>
+        <v>10.7821416854858</v>
       </c>
       <c r="H140" t="n">
         <v>21700</v>
@@ -4458,7 +4458,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>10.6975755691528</v>
+        <v>10.6975746154785</v>
       </c>
       <c r="H141" t="n">
         <v>3500</v>
@@ -4487,7 +4487,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H142" t="n">
         <v>800</v>
@@ -4516,7 +4516,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H143" t="n">
         <v>1800</v>
@@ -4545,7 +4545,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>10.4438781738281</v>
+        <v>10.4438791275024</v>
       </c>
       <c r="H144" t="n">
         <v>400</v>
@@ -4603,7 +4603,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G146" t="n">
-        <v>10.2324638366699</v>
+        <v>10.2324647903442</v>
       </c>
       <c r="H146" t="n">
         <v>600</v>
@@ -4690,7 +4690,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>10.1901817321777</v>
+        <v>10.1901798248291</v>
       </c>
       <c r="H149" t="n">
         <v>10500</v>
@@ -4806,7 +4806,7 @@
         <v>13</v>
       </c>
       <c r="G153" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H153" t="n">
         <v>6700</v>
@@ -4835,7 +4835,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512739181519</v>
       </c>
       <c r="H154" t="n">
         <v>13200</v>
@@ -4864,7 +4864,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G155" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512739181519</v>
       </c>
       <c r="H155" t="n">
         <v>3400</v>
@@ -4893,7 +4893,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H156" t="n">
         <v>2800</v>
@@ -4951,7 +4951,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>10.6552934646606</v>
+        <v>10.655294418335</v>
       </c>
       <c r="H158" t="n">
         <v>300</v>
@@ -5038,7 +5038,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G161" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H161" t="n">
         <v>2200</v>
@@ -5067,7 +5067,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G162" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G163" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G164" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G165" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.6130094528198</v>
+        <v>10.6130104064941</v>
       </c>
       <c r="H166" t="n">
         <v>2600</v>
@@ -5241,7 +5241,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>10.7398586273193</v>
+        <v>10.739857673645</v>
       </c>
       <c r="H168" t="n">
         <v>12000</v>
@@ -5299,7 +5299,7 @@
         <v>12.75</v>
       </c>
       <c r="G170" t="n">
-        <v>10.7821407318115</v>
+        <v>10.7821416854858</v>
       </c>
       <c r="H170" t="n">
         <v>8800</v>
@@ -5328,7 +5328,7 @@
         <v>12.75</v>
       </c>
       <c r="G171" t="n">
-        <v>10.7821407318115</v>
+        <v>10.7821416854858</v>
       </c>
       <c r="H171" t="n">
         <v>400</v>
@@ -5386,7 +5386,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>10.5284442901611</v>
+        <v>10.5284433364868</v>
       </c>
       <c r="H173" t="n">
         <v>4300</v>
@@ -5415,7 +5415,7 @@
         <v>13</v>
       </c>
       <c r="G174" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H174" t="n">
         <v>41300</v>
@@ -5473,7 +5473,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512739181519</v>
       </c>
       <c r="H176" t="n">
         <v>2600</v>
@@ -5502,7 +5502,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G177" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512739181519</v>
       </c>
       <c r="H177" t="n">
         <v>400</v>
@@ -5531,7 +5531,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>10.8244247436523</v>
+        <v>10.8244256973267</v>
       </c>
       <c r="H178" t="n">
         <v>700</v>
@@ -5589,7 +5589,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>11.1626873016357</v>
+        <v>11.1626882553101</v>
       </c>
       <c r="H180" t="n">
         <v>1400</v>
@@ -5618,7 +5618,7 @@
         <v>13</v>
       </c>
       <c r="G181" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H181" t="n">
         <v>900</v>
@@ -5647,7 +5647,7 @@
         <v>13</v>
       </c>
       <c r="G182" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H182" t="n">
         <v>1300</v>
@@ -5676,7 +5676,7 @@
         <v>13</v>
       </c>
       <c r="G183" t="n">
-        <v>10.993556022644</v>
+        <v>10.9935569763184</v>
       </c>
       <c r="H183" t="n">
         <v>4000</v>
@@ -5705,7 +5705,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>10.9512729644775</v>
+        <v>10.9512739181519</v>
       </c>
       <c r="H184" t="n">
         <v>9200</v>
@@ -5734,7 +5734,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G185" t="n">
-        <v>11.1626873016357</v>
+        <v>11.1626882553101</v>
       </c>
       <c r="H185" t="n">
         <v>10300</v>
@@ -5792,7 +5792,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>11.3318176269531</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H187" t="n">
         <v>10200</v>
@@ -5879,7 +5879,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>11.0358400344849</v>
+        <v>11.0358390808105</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5937,7 +5937,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>11.3318176269531</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H192" t="n">
         <v>900</v>
@@ -5995,7 +5995,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>11.3318176269531</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H194" t="n">
         <v>25800</v>
@@ -6024,7 +6024,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>11.3741025924683</v>
+        <v>11.3741016387939</v>
       </c>
       <c r="H195" t="n">
         <v>2100</v>
@@ -6053,7 +6053,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>11.4586687088013</v>
+        <v>11.458667755127</v>
       </c>
       <c r="H196" t="n">
         <v>2000</v>
@@ -6082,7 +6082,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>11.4586687088013</v>
+        <v>11.458667755127</v>
       </c>
       <c r="H197" t="n">
         <v>400</v>
@@ -6111,7 +6111,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>11.3318176269531</v>
+        <v>11.3318195343018</v>
       </c>
       <c r="H198" t="n">
         <v>8700</v>
@@ -6169,7 +6169,7 @@
         <v>13.5</v>
       </c>
       <c r="G200" t="n">
-        <v>11.4163866043091</v>
+        <v>11.4163846969604</v>
       </c>
       <c r="H200" t="n">
         <v>2800</v>
@@ -6198,7 +6198,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>11.5432329177856</v>
+        <v>11.54323387146</v>
       </c>
       <c r="H201" t="n">
         <v>7000</v>
@@ -6227,7 +6227,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>11.5432329177856</v>
+        <v>11.54323387146</v>
       </c>
       <c r="H202" t="n">
         <v>4600</v>
@@ -6256,7 +6256,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>11.5009517669678</v>
+        <v>11.5009508132935</v>
       </c>
       <c r="H203" t="n">
         <v>5800</v>
@@ -6285,7 +6285,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>11.786958694458</v>
+        <v>11.7869596481323</v>
       </c>
       <c r="H204" t="n">
         <v>8400</v>
@@ -6314,7 +6314,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>11.5702857971191</v>
+        <v>11.5702867507935</v>
       </c>
       <c r="H205" t="n">
         <v>12700</v>
@@ -6343,7 +6343,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>11.440281867981</v>
+        <v>11.4402828216553</v>
       </c>
       <c r="H206" t="n">
         <v>6500</v>
@@ -6430,7 +6430,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>11.5702857971191</v>
+        <v>11.5702867507935</v>
       </c>
       <c r="H209" t="n">
         <v>2800</v>
@@ -6459,7 +6459,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>11.613618850708</v>
+        <v>11.6136198043823</v>
       </c>
       <c r="H210" t="n">
         <v>3600</v>
@@ -6488,7 +6488,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>11.440281867981</v>
+        <v>11.4402828216553</v>
       </c>
       <c r="H211" t="n">
         <v>2300</v>
@@ -6517,7 +6517,7 @@
         <v>13.75</v>
       </c>
       <c r="G212" t="n">
-        <v>11.9169597625732</v>
+        <v>11.9169626235962</v>
       </c>
       <c r="H212" t="n">
         <v>5600</v>
@@ -6546,7 +6546,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>11.6569557189941</v>
+        <v>11.6569547653198</v>
       </c>
       <c r="H213" t="n">
         <v>4500</v>
@@ -6575,7 +6575,7 @@
         <v>13.5</v>
       </c>
       <c r="G214" t="n">
-        <v>11.7002897262573</v>
+        <v>11.700288772583</v>
       </c>
       <c r="H214" t="n">
         <v>1700</v>
@@ -6604,7 +6604,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G215" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H215" t="n">
         <v>700</v>
@@ -6633,7 +6633,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H216" t="n">
         <v>1800</v>
@@ -6662,7 +6662,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G217" t="n">
-        <v>11.8736267089844</v>
+        <v>11.8736276626587</v>
       </c>
       <c r="H217" t="n">
         <v>2900</v>
@@ -6691,7 +6691,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>11.526951789856</v>
+        <v>11.5269508361816</v>
       </c>
       <c r="H219" t="n">
         <v>3200</v>
@@ -6749,7 +6749,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>11.5702857971191</v>
+        <v>11.5702867507935</v>
       </c>
       <c r="H220" t="n">
         <v>1500</v>
@@ -6778,7 +6778,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H221" t="n">
         <v>1500</v>
@@ -6807,7 +6807,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G222" t="n">
-        <v>11.6569557189941</v>
+        <v>11.6569547653198</v>
       </c>
       <c r="H222" t="n">
         <v>1900</v>
@@ -6836,7 +6836,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H223" t="n">
         <v>41700</v>
@@ -6865,7 +6865,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>11.8302907943726</v>
+        <v>11.8302927017212</v>
       </c>
       <c r="H224" t="n">
         <v>4800</v>
@@ -6894,7 +6894,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>11.8302907943726</v>
+        <v>11.8302927017212</v>
       </c>
       <c r="H225" t="n">
         <v>40300</v>
@@ -6923,7 +6923,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>11.8736267089844</v>
+        <v>11.8736276626587</v>
       </c>
       <c r="H226" t="n">
         <v>3400</v>
@@ -6952,7 +6952,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>11.9602966308594</v>
+        <v>11.9602956771851</v>
       </c>
       <c r="H227" t="n">
         <v>5400</v>
@@ -6981,7 +6981,7 @@
         <v>13.75</v>
       </c>
       <c r="G228" t="n">
-        <v>11.9169597625732</v>
+        <v>11.9169626235962</v>
       </c>
       <c r="H228" t="n">
         <v>2700</v>
@@ -7010,7 +7010,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902996063232</v>
       </c>
       <c r="H229" t="n">
         <v>1300</v>
@@ -7039,7 +7039,7 @@
         <v>13.75</v>
       </c>
       <c r="G230" t="n">
-        <v>11.9169597625732</v>
+        <v>11.9169626235962</v>
       </c>
       <c r="H230" t="n">
         <v>2100</v>
@@ -7068,7 +7068,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G231" t="n">
-        <v>11.8302907943726</v>
+        <v>11.8302927017212</v>
       </c>
       <c r="H231" t="n">
         <v>1500</v>
@@ -7097,7 +7097,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>12.0469646453857</v>
+        <v>12.0469636917114</v>
       </c>
       <c r="H232" t="n">
         <v>2700</v>
@@ -7126,7 +7126,7 @@
         <v>13.75</v>
       </c>
       <c r="G233" t="n">
-        <v>11.9169597625732</v>
+        <v>11.9169626235962</v>
       </c>
       <c r="H233" t="n">
         <v>2200</v>
@@ -7155,7 +7155,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>11.786958694458</v>
+        <v>11.7869596481323</v>
       </c>
       <c r="H234" t="n">
         <v>700</v>
@@ -7184,7 +7184,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G235" t="n">
-        <v>11.7436246871948</v>
+        <v>11.7436227798462</v>
       </c>
       <c r="H235" t="n">
         <v>2900</v>
@@ -7213,7 +7213,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G236" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902996063232</v>
       </c>
       <c r="H236" t="n">
         <v>2000</v>
@@ -7242,7 +7242,7 @@
         <v>13.5</v>
       </c>
       <c r="G237" t="n">
-        <v>11.7002897262573</v>
+        <v>11.700288772583</v>
       </c>
       <c r="H237" t="n">
         <v>1100</v>
@@ -7271,7 +7271,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>12.0469646453857</v>
+        <v>12.0469636917114</v>
       </c>
       <c r="H238" t="n">
         <v>4000</v>
@@ -7300,7 +7300,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>12.0036296844482</v>
+        <v>12.0036306381226</v>
       </c>
       <c r="H239" t="n">
         <v>1900</v>
@@ -7329,7 +7329,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>12.0902986526489</v>
+        <v>12.0902996063232</v>
       </c>
       <c r="H240" t="n">
         <v>900</v>
@@ -7358,7 +7358,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>12.0469646453857</v>
+        <v>12.0469636917114</v>
       </c>
       <c r="H241" t="n">
         <v>5700</v>
@@ -7387,7 +7387,7 @@
         <v>14.5</v>
       </c>
       <c r="G242" t="n">
-        <v>12.5669765472412</v>
+        <v>12.5669784545898</v>
       </c>
       <c r="H242" t="n">
         <v>25500</v>
@@ -7416,7 +7416,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>12.4803085327148</v>
+        <v>12.4803075790405</v>
       </c>
       <c r="H243" t="n">
         <v>3700</v>
@@ -7445,7 +7445,7 @@
         <v>14.5</v>
       </c>
       <c r="G244" t="n">
-        <v>12.5669765472412</v>
+        <v>12.5669784545898</v>
       </c>
       <c r="H244" t="n">
         <v>5900</v>
@@ -7474,7 +7474,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>12.7403144836426</v>
+        <v>12.7403154373169</v>
       </c>
       <c r="H245" t="n">
         <v>10400</v>
@@ -7532,7 +7532,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G247" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H247" t="n">
         <v>10900</v>
@@ -7561,7 +7561,7 @@
         <v>15</v>
       </c>
       <c r="G248" t="n">
-        <v>13.0003223419189</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H248" t="n">
         <v>2600</v>
@@ -7590,7 +7590,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H249" t="n">
         <v>8300</v>
@@ -7648,7 +7648,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H251" t="n">
         <v>12100</v>
@@ -7677,7 +7677,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H252" t="n">
         <v>2300</v>
@@ -7706,7 +7706,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H253" t="n">
         <v>4100</v>
@@ -7735,7 +7735,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>12.8703174591064</v>
+        <v>12.8703184127808</v>
       </c>
       <c r="H254" t="n">
         <v>1600</v>
@@ -7764,7 +7764,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G255" t="n">
-        <v>13.0436544418335</v>
+        <v>13.0436553955078</v>
       </c>
       <c r="H255" t="n">
         <v>12700</v>
@@ -7793,7 +7793,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G256" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H256" t="n">
         <v>600</v>
@@ -7822,7 +7822,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H257" t="n">
         <v>900</v>
@@ -7851,7 +7851,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>12.9569873809814</v>
+        <v>12.9569883346558</v>
       </c>
       <c r="H258" t="n">
         <v>100</v>
@@ -7880,7 +7880,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>12.8269853591919</v>
+        <v>12.8269834518433</v>
       </c>
       <c r="H259" t="n">
         <v>1300</v>
@@ -7909,7 +7909,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>12.9136524200439</v>
+        <v>12.9136514663696</v>
       </c>
       <c r="H260" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
         <v>15</v>
       </c>
       <c r="G261" t="n">
-        <v>13.0003223419189</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H261" t="n">
         <v>1800</v>
@@ -7967,7 +7967,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H262" t="n">
         <v>5400</v>
@@ -7996,7 +7996,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H263" t="n">
         <v>2900</v>
@@ -8025,7 +8025,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H264" t="n">
         <v>2000</v>
@@ -8083,7 +8083,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G266" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H266" t="n">
         <v>4600</v>
@@ -8112,7 +8112,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H267" t="n">
         <v>2500</v>
@@ -8141,7 +8141,7 @@
         <v>15</v>
       </c>
       <c r="G268" t="n">
-        <v>13.0003223419189</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H268" t="n">
         <v>3000</v>
@@ -8170,7 +8170,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H269" t="n">
         <v>2200</v>
@@ -8199,7 +8199,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H270" t="n">
         <v>300</v>
@@ -8257,7 +8257,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H272" t="n">
         <v>400</v>
@@ -8286,7 +8286,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H273" t="n">
         <v>1600</v>
@@ -8315,7 +8315,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H274" t="n">
         <v>1100</v>
@@ -8344,7 +8344,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H275" t="n">
         <v>1600</v>
@@ -8373,7 +8373,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H276" t="n">
         <v>800</v>
@@ -8402,7 +8402,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H277" t="n">
         <v>300</v>
@@ -8431,7 +8431,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H278" t="n">
         <v>1700</v>
@@ -8460,7 +8460,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G279" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G280" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H280" t="n">
         <v>200</v>
@@ -8518,7 +8518,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H281" t="n">
         <v>1000</v>
@@ -8576,7 +8576,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H283" t="n">
         <v>4000</v>
@@ -8663,7 +8663,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H286" t="n">
         <v>25700</v>
@@ -8692,7 +8692,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H287" t="n">
         <v>400</v>
@@ -8750,7 +8750,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H289" t="n">
         <v>2500</v>
@@ -8808,7 +8808,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H291" t="n">
         <v>2500</v>
@@ -8837,7 +8837,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H292" t="n">
         <v>1100</v>
@@ -8866,7 +8866,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H293" t="n">
         <v>800</v>
@@ -8895,7 +8895,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H294" t="n">
         <v>1800</v>
@@ -8924,7 +8924,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H295" t="n">
         <v>800</v>
@@ -8953,7 +8953,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H296" t="n">
         <v>25700</v>
@@ -8982,7 +8982,7 @@
         <v>15.5</v>
       </c>
       <c r="G297" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H297" t="n">
         <v>13600</v>
@@ -9011,7 +9011,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H298" t="n">
         <v>6800</v>
@@ -9069,7 +9069,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H300" t="n">
         <v>3000</v>
@@ -9098,7 +9098,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H301" t="n">
         <v>2000</v>
@@ -9127,7 +9127,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H302" t="n">
         <v>1200</v>
@@ -9185,7 +9185,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G304" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H304" t="n">
         <v>900</v>
@@ -9272,7 +9272,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H307" t="n">
         <v>6600</v>
@@ -9330,7 +9330,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H309" t="n">
         <v>2700</v>
@@ -9359,7 +9359,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>13.737006187439</v>
+        <v>13.7370071411133</v>
       </c>
       <c r="H310" t="n">
         <v>2000</v>
@@ -9388,7 +9388,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>13.737006187439</v>
+        <v>13.7370071411133</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H312" t="n">
         <v>11300</v>
@@ -9446,7 +9446,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H313" t="n">
         <v>9400</v>
@@ -9533,7 +9533,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>13.7803401947021</v>
+        <v>13.7803392410278</v>
       </c>
       <c r="H316" t="n">
         <v>3200</v>
@@ -9649,7 +9649,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H320" t="n">
         <v>1400</v>
@@ -9678,7 +9678,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H321" t="n">
         <v>2200</v>
@@ -9736,7 +9736,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H323" t="n">
         <v>1900</v>
@@ -9765,7 +9765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H324" t="n">
         <v>2600</v>
@@ -9823,7 +9823,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H326" t="n">
         <v>2300</v>
@@ -9852,7 +9852,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H327" t="n">
         <v>1900</v>
@@ -9881,7 +9881,7 @@
         <v>15</v>
       </c>
       <c r="G328" t="n">
-        <v>13.0003223419189</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H328" t="n">
         <v>11200</v>
@@ -9910,7 +9910,7 @@
         <v>15</v>
       </c>
       <c r="G329" t="n">
-        <v>13.0003223419189</v>
+        <v>13.0003204345703</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>15.5</v>
       </c>
       <c r="G330" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H330" t="n">
         <v>800</v>
@@ -9968,7 +9968,7 @@
         <v>15.5</v>
       </c>
       <c r="G331" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H332" t="n">
         <v>30500</v>
@@ -10055,7 +10055,7 @@
         <v>15.5</v>
       </c>
       <c r="G334" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H334" t="n">
         <v>7500</v>
@@ -10084,7 +10084,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>13.737006187439</v>
+        <v>13.7370071411133</v>
       </c>
       <c r="H337" t="n">
         <v>3100</v>
@@ -10171,7 +10171,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H338" t="n">
         <v>1000</v>
@@ -10200,7 +10200,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H339" t="n">
         <v>1000</v>
@@ -10229,7 +10229,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H341" t="n">
         <v>200</v>
@@ -10287,7 +10287,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H342" t="n">
         <v>1100</v>
@@ -10316,7 +10316,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G343" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H343" t="n">
         <v>500</v>
@@ -10345,7 +10345,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H344" t="n">
         <v>5200</v>
@@ -10374,7 +10374,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H345" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H346" t="n">
         <v>1200</v>
@@ -10432,7 +10432,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>13.2603282928467</v>
+        <v>13.2603273391724</v>
       </c>
       <c r="H347" t="n">
         <v>600</v>
@@ -10548,7 +10548,7 @@
         <v>15.5</v>
       </c>
       <c r="G351" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H351" t="n">
         <v>1400</v>
@@ -10577,7 +10577,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H352" t="n">
         <v>4000</v>
@@ -10780,7 +10780,7 @@
         <v>15.5</v>
       </c>
       <c r="G359" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H359" t="n">
         <v>200</v>
@@ -10838,7 +10838,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H361" t="n">
         <v>900</v>
@@ -10867,7 +10867,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H363" t="n">
         <v>1300</v>
@@ -10925,7 +10925,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G364" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H364" t="n">
         <v>200</v>
@@ -10954,7 +10954,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G365" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H365" t="n">
         <v>1300</v>
@@ -11012,7 +11012,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H367" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H368" t="n">
         <v>1200</v>
@@ -11070,7 +11070,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>13.0869903564453</v>
+        <v>13.086989402771</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H370" t="n">
         <v>1000</v>
@@ -11128,7 +11128,7 @@
         <v>15.5</v>
       </c>
       <c r="G371" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H371" t="n">
         <v>400</v>
@@ -11157,7 +11157,7 @@
         <v>15.5</v>
       </c>
       <c r="G372" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H372" t="n">
         <v>1000</v>
@@ -11215,7 +11215,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>13.1736583709717</v>
+        <v>13.173659324646</v>
       </c>
       <c r="H374" t="n">
         <v>100</v>
@@ -11244,7 +11244,7 @@
         <v>15.5</v>
       </c>
       <c r="G375" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H375" t="n">
         <v>1000</v>
@@ -11273,7 +11273,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>13.5636692047119</v>
+        <v>13.5636682510376</v>
       </c>
       <c r="H376" t="n">
         <v>2300</v>
@@ -11302,7 +11302,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H377" t="n">
         <v>900</v>
@@ -11331,7 +11331,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>13.3036623001099</v>
+        <v>13.3036632537842</v>
       </c>
       <c r="H378" t="n">
         <v>100</v>
@@ -11360,7 +11360,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H379" t="n">
         <v>6400</v>
@@ -11418,7 +11418,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H381" t="n">
         <v>800</v>
@@ -11447,7 +11447,7 @@
         <v>15.5</v>
       </c>
       <c r="G382" t="n">
-        <v>13.433666229248</v>
+        <v>13.4336643218994</v>
       </c>
       <c r="H382" t="n">
         <v>300</v>
@@ -11505,7 +11505,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>13.3469953536987</v>
+        <v>13.3469972610474</v>
       </c>
       <c r="H384" t="n">
         <v>300</v>
@@ -11534,7 +11534,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G385" t="n">
-        <v>13.4769992828369</v>
+        <v>13.4770002365112</v>
       </c>
       <c r="H385" t="n">
         <v>200</v>
@@ -11592,7 +11592,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1270141601562</v>
+        <v>14.1270160675049</v>
       </c>
       <c r="H387" t="n">
         <v>5300</v>
@@ -11621,7 +11621,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>14.2136850357056</v>
+        <v>14.2136831283569</v>
       </c>
       <c r="H388" t="n">
         <v>3100</v>
@@ -11679,7 +11679,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H390" t="n">
         <v>10000</v>
@@ -11708,7 +11708,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H391" t="n">
         <v>7500</v>
@@ -11737,7 +11737,7 @@
         <v>17.25</v>
       </c>
       <c r="G392" t="n">
-        <v>14.9503679275513</v>
+        <v>14.9503688812256</v>
       </c>
       <c r="H392" t="n">
         <v>5500</v>
@@ -11795,7 +11795,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>14.6903667449951</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H394" t="n">
         <v>3700</v>
@@ -11882,7 +11882,7 @@
         <v>16.75</v>
       </c>
       <c r="G397" t="n">
-        <v>14.5170249938965</v>
+        <v>14.5170259475708</v>
       </c>
       <c r="H397" t="n">
         <v>4600</v>
@@ -11911,7 +11911,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>14.5603609085083</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H398" t="n">
         <v>300</v>
@@ -11940,7 +11940,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G399" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H399" t="n">
         <v>1200</v>
@@ -12027,7 +12027,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>14.3870210647583</v>
+        <v>14.3870229721069</v>
       </c>
       <c r="H402" t="n">
         <v>1500</v>
@@ -12056,7 +12056,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G403" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H403" t="n">
         <v>900</v>
@@ -12085,7 +12085,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>14.5603609085083</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H404" t="n">
         <v>2900</v>
@@ -12114,7 +12114,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>14.5603609085083</v>
+        <v>14.5603590011597</v>
       </c>
       <c r="H405" t="n">
         <v>2000</v>
@@ -12172,7 +12172,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H407" t="n">
         <v>5600</v>
@@ -12201,7 +12201,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>14.6903667449951</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>14.6903667449951</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H409" t="n">
         <v>2600</v>
@@ -12288,7 +12288,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G411" t="n">
-        <v>14.6903667449951</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H411" t="n">
         <v>9500</v>
@@ -12317,7 +12317,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G412" t="n">
-        <v>14.6903667449951</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H412" t="n">
         <v>3600</v>
@@ -12346,7 +12346,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6903667449951</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H413" t="n">
         <v>2000</v>
@@ -12433,7 +12433,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G416" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H416" t="n">
         <v>2000</v>
@@ -12462,7 +12462,7 @@
         <v>16.75</v>
       </c>
       <c r="G417" t="n">
-        <v>14.5170249938965</v>
+        <v>14.5170259475708</v>
       </c>
       <c r="H417" t="n">
         <v>15600</v>
@@ -12549,7 +12549,7 @@
         <v>16.5</v>
       </c>
       <c r="G420" t="n">
-        <v>14.3003540039062</v>
+        <v>14.3003530502319</v>
       </c>
       <c r="H420" t="n">
         <v>25000</v>
@@ -12578,7 +12578,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>14.4303550720215</v>
+        <v>14.4303560256958</v>
       </c>
       <c r="H421" t="n">
         <v>4300</v>
@@ -12607,7 +12607,7 @@
         <v>16.5</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3003540039062</v>
+        <v>14.3003530502319</v>
       </c>
       <c r="H422" t="n">
         <v>4000</v>
@@ -12694,7 +12694,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>14.3870210647583</v>
+        <v>14.3870229721069</v>
       </c>
       <c r="H425" t="n">
         <v>4300</v>
@@ -12752,7 +12752,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>14.3870210647583</v>
+        <v>14.3870229721069</v>
       </c>
       <c r="H427" t="n">
         <v>600</v>
@@ -12810,7 +12810,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H429" t="n">
         <v>11700</v>
@@ -12955,7 +12955,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H434" t="n">
         <v>700</v>
@@ -13013,7 +13013,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>14.6903667449951</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H436" t="n">
         <v>2900</v>
@@ -13042,7 +13042,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>14.6470279693604</v>
+        <v>14.6470260620117</v>
       </c>
       <c r="H437" t="n">
         <v>2300</v>
@@ -13071,7 +13071,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>14.6903667449951</v>
+        <v>14.6903629302979</v>
       </c>
       <c r="H438" t="n">
         <v>3800</v>
@@ -13100,7 +13100,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>14.8203649520874</v>
+        <v>14.820366859436</v>
       </c>
       <c r="H439" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>14.8203649520874</v>
+        <v>14.820366859436</v>
       </c>
       <c r="H440" t="n">
         <v>3000</v>
@@ -13158,7 +13158,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>14.8203649520874</v>
+        <v>14.820366859436</v>
       </c>
       <c r="H441" t="n">
         <v>600</v>
@@ -13187,7 +13187,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>14.8203649520874</v>
+        <v>14.820366859436</v>
       </c>
       <c r="H442" t="n">
         <v>3700</v>
@@ -13274,7 +13274,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>14.9937038421631</v>
+        <v>14.9937028884888</v>
       </c>
       <c r="H445" t="n">
         <v>4294</v>
@@ -13332,7 +13332,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G447" t="n">
-        <v>14.8203649520874</v>
+        <v>14.820366859436</v>
       </c>
       <c r="H447" t="n">
         <v>37419</v>
@@ -13390,7 +13390,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>15.0370378494263</v>
+        <v>15.0370407104492</v>
       </c>
       <c r="H449" t="n">
         <v>3162</v>
@@ -13419,7 +13419,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G450" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803709030151</v>
       </c>
       <c r="H450" t="n">
         <v>6177</v>
@@ -13448,7 +13448,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803709030151</v>
       </c>
       <c r="H451" t="n">
         <v>14450</v>
@@ -13477,7 +13477,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>14.9937038421631</v>
+        <v>14.9937028884888</v>
       </c>
       <c r="H452" t="n">
         <v>4325</v>
@@ -13506,7 +13506,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803709030151</v>
       </c>
       <c r="H453" t="n">
         <v>24934</v>
@@ -13535,7 +13535,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>15.5265378952026</v>
+        <v>15.526535987854</v>
       </c>
       <c r="H454" t="n">
         <v>4000</v>
@@ -13564,7 +13564,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>15.5265378952026</v>
+        <v>15.526535987854</v>
       </c>
       <c r="H455" t="n">
         <v>10462</v>
@@ -13622,7 +13622,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>15.5265378952026</v>
+        <v>15.526535987854</v>
       </c>
       <c r="H457" t="n">
         <v>880</v>
@@ -13680,7 +13680,7 @@
         <v>17</v>
       </c>
       <c r="G459" t="n">
-        <v>15.169605255127</v>
+        <v>15.1696062088013</v>
       </c>
       <c r="H459" t="n">
         <v>20546</v>
@@ -13709,7 +13709,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>15.0803718566895</v>
+        <v>15.0803709030151</v>
       </c>
       <c r="H460" t="n">
         <v>2407</v>
@@ -13738,7 +13738,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>15.21422290802</v>
+        <v>15.2142219543457</v>
       </c>
       <c r="H461" t="n">
         <v>4400</v>
@@ -13767,7 +13767,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>14.9911403656006</v>
+        <v>14.9911394119263</v>
       </c>
       <c r="H462" t="n">
         <v>599</v>
@@ -13796,7 +13796,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G463" t="n">
-        <v>15.1249923706055</v>
+        <v>15.1249895095825</v>
       </c>
       <c r="H463" t="n">
         <v>771</v>
@@ -13825,7 +13825,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>15.4373035430908</v>
+        <v>15.4373044967651</v>
       </c>
       <c r="H464" t="n">
         <v>1237</v>
@@ -13941,7 +13941,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>15.4373035430908</v>
+        <v>15.4373044967651</v>
       </c>
       <c r="H468" t="n">
         <v>1311</v>
@@ -14115,7 +14115,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G474" t="n">
-        <v>17.0434970855713</v>
+        <v>17.0434989929199</v>
       </c>
       <c r="H474" t="n">
         <v>23112</v>
@@ -14144,7 +14144,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G475" t="n">
-        <v>17.0434970855713</v>
+        <v>17.0434989929199</v>
       </c>
       <c r="H475" t="n">
         <v>20082</v>
@@ -14231,7 +14231,7 @@
         <v>19.5</v>
       </c>
       <c r="G478" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H478" t="n">
         <v>16646</v>
@@ -14260,7 +14260,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G479" t="n">
-        <v>17.0434970855713</v>
+        <v>17.0434989929199</v>
       </c>
       <c r="H479" t="n">
         <v>8480</v>
@@ -14289,7 +14289,7 @@
         <v>19.5</v>
       </c>
       <c r="G480" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H480" t="n">
         <v>6935</v>
@@ -14318,7 +14318,7 @@
         <v>19.5</v>
       </c>
       <c r="G481" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H481" t="n">
         <v>8270</v>
@@ -14376,7 +14376,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G483" t="n">
-        <v>17.4450435638428</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H483" t="n">
         <v>4149</v>
@@ -14492,7 +14492,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H487" t="n">
         <v>5816</v>
@@ -14521,7 +14521,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>17.4450435638428</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H488" t="n">
         <v>2521</v>
@@ -14550,7 +14550,7 @@
         <v>19.5</v>
       </c>
       <c r="G489" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H489" t="n">
         <v>2164</v>
@@ -14579,7 +14579,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G490" t="n">
-        <v>18.649694442749</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H490" t="n">
         <v>46374</v>
@@ -14608,7 +14608,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>18.649694442749</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H491" t="n">
         <v>14670</v>
@@ -14637,7 +14637,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>18.649694442749</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H492" t="n">
         <v>6388</v>
@@ -14666,7 +14666,7 @@
         <v>20.5</v>
       </c>
       <c r="G493" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H493" t="n">
         <v>2753</v>
@@ -14695,7 +14695,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604610443115</v>
       </c>
       <c r="H494" t="n">
         <v>3493</v>
@@ -14724,7 +14724,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>18.649694442749</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H495" t="n">
         <v>6097</v>
@@ -14753,7 +14753,7 @@
         <v>21</v>
       </c>
       <c r="G496" t="n">
-        <v>18.7389259338379</v>
+        <v>18.7389221191406</v>
       </c>
       <c r="H496" t="n">
         <v>12906</v>
@@ -14782,7 +14782,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G497" t="n">
-        <v>18.649694442749</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H497" t="n">
         <v>6035</v>
@@ -14811,7 +14811,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G498" t="n">
-        <v>18.649694442749</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H498" t="n">
         <v>7892</v>
@@ -14840,7 +14840,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604610443115</v>
       </c>
       <c r="H499" t="n">
         <v>5362</v>
@@ -14869,7 +14869,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604610443115</v>
       </c>
       <c r="H500" t="n">
         <v>4065</v>
@@ -14898,7 +14898,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G501" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H501" t="n">
         <v>3610</v>
@@ -14927,7 +14927,7 @@
         <v>20.5</v>
       </c>
       <c r="G502" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H502" t="n">
         <v>6475</v>
@@ -15014,7 +15014,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G505" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H505" t="n">
         <v>2052</v>
@@ -15043,7 +15043,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H506" t="n">
         <v>8048</v>
@@ -15072,7 +15072,7 @@
         <v>20.5</v>
       </c>
       <c r="G507" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H507" t="n">
         <v>3880</v>
@@ -15130,7 +15130,7 @@
         <v>20.5</v>
       </c>
       <c r="G509" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H509" t="n">
         <v>3508</v>
@@ -15159,7 +15159,7 @@
         <v>20.5</v>
       </c>
       <c r="G510" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H510" t="n">
         <v>1314</v>
@@ -15188,7 +15188,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H511" t="n">
         <v>2701</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H512" t="n">
         <v>3189</v>
@@ -15246,7 +15246,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>17.4450435638428</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H513" t="n">
         <v>3700</v>
@@ -15275,7 +15275,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>17.4450435638428</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H514" t="n">
         <v>5110</v>
@@ -15420,7 +15420,7 @@
         <v>19.75</v>
       </c>
       <c r="G519" t="n">
-        <v>17.6235122680664</v>
+        <v>17.623514175415</v>
       </c>
       <c r="H519" t="n">
         <v>3789</v>
@@ -15507,7 +15507,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>17.2665824890137</v>
+        <v>17.266580581665</v>
       </c>
       <c r="H522" t="n">
         <v>1999</v>
@@ -15536,7 +15536,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G523" t="n">
-        <v>17.2665824890137</v>
+        <v>17.266580581665</v>
       </c>
       <c r="H523" t="n">
         <v>5001</v>
@@ -15565,7 +15565,7 @@
         <v>19.5</v>
       </c>
       <c r="G524" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H524" t="n">
         <v>2311</v>
@@ -15594,7 +15594,7 @@
         <v>19.5</v>
       </c>
       <c r="G525" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H525" t="n">
         <v>4044</v>
@@ -15652,7 +15652,7 @@
         <v>19.5</v>
       </c>
       <c r="G527" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H527" t="n">
         <v>1461</v>
@@ -15681,7 +15681,7 @@
         <v>19.5</v>
       </c>
       <c r="G528" t="n">
-        <v>17.4004306793213</v>
+        <v>17.4004287719727</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>17.4896621704102</v>
+        <v>17.4896640777588</v>
       </c>
       <c r="H529" t="n">
         <v>1050</v>
@@ -15768,7 +15768,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>17.4450435638428</v>
+        <v>17.44504737854</v>
       </c>
       <c r="H531" t="n">
         <v>1036</v>
@@ -15797,7 +15797,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G532" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H532" t="n">
         <v>1402</v>
@@ -15826,7 +15826,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G533" t="n">
-        <v>17.757360458374</v>
+        <v>17.7573623657227</v>
       </c>
       <c r="H533" t="n">
         <v>1112</v>
@@ -15855,7 +15855,7 @@
         <v>20</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H534" t="n">
         <v>2224</v>
@@ -15884,7 +15884,7 @@
         <v>20</v>
       </c>
       <c r="G535" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H535" t="n">
         <v>4616</v>
@@ -15942,7 +15942,7 @@
         <v>20</v>
       </c>
       <c r="G537" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H537" t="n">
         <v>2250</v>
@@ -15971,7 +15971,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H538" t="n">
         <v>10406</v>
@@ -16000,7 +16000,7 @@
         <v>20</v>
       </c>
       <c r="G539" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H539" t="n">
         <v>1256</v>
@@ -16029,7 +16029,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H540" t="n">
         <v>5116</v>
@@ -16087,7 +16087,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>18.649694442749</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H542" t="n">
         <v>7090</v>
@@ -16116,7 +16116,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H543" t="n">
         <v>2090</v>
@@ -16145,7 +16145,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H544" t="n">
         <v>2060</v>
@@ -16174,7 +16174,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H545" t="n">
         <v>2697</v>
@@ -16203,7 +16203,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H546" t="n">
         <v>720</v>
@@ -16232,7 +16232,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H547" t="n">
         <v>603</v>
@@ -16261,7 +16261,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H548" t="n">
         <v>4408</v>
@@ -16290,7 +16290,7 @@
         <v>20.5</v>
       </c>
       <c r="G549" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H549" t="n">
         <v>7326</v>
@@ -16319,7 +16319,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G550" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H550" t="n">
         <v>9268</v>
@@ -16377,7 +16377,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G552" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H552" t="n">
         <v>5016</v>
@@ -16435,7 +16435,7 @@
         <v>20.5</v>
       </c>
       <c r="G554" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H554" t="n">
         <v>1796</v>
@@ -16464,7 +16464,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G555" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604610443115</v>
       </c>
       <c r="H555" t="n">
         <v>7200</v>
@@ -16493,7 +16493,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H556" t="n">
         <v>4973</v>
@@ -16522,7 +16522,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H557" t="n">
         <v>1111</v>
@@ -16609,7 +16609,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H560" t="n">
         <v>12249</v>
@@ -16696,7 +16696,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H563" t="n">
         <v>2101</v>
@@ -16725,7 +16725,7 @@
         <v>20.5</v>
       </c>
       <c r="G564" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H564" t="n">
         <v>3218</v>
@@ -16754,7 +16754,7 @@
         <v>20</v>
       </c>
       <c r="G565" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H565" t="n">
         <v>2880</v>
@@ -16783,7 +16783,7 @@
         <v>20</v>
       </c>
       <c r="G566" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H566" t="n">
         <v>2491</v>
@@ -16812,7 +16812,7 @@
         <v>20</v>
       </c>
       <c r="G567" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H567" t="n">
         <v>2423</v>
@@ -16841,7 +16841,7 @@
         <v>20</v>
       </c>
       <c r="G568" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H568" t="n">
         <v>5106</v>
@@ -16899,7 +16899,7 @@
         <v>20</v>
       </c>
       <c r="G570" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H570" t="n">
         <v>534</v>
@@ -16928,7 +16928,7 @@
         <v>20</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H571" t="n">
         <v>1494</v>
@@ -16957,7 +16957,7 @@
         <v>20</v>
       </c>
       <c r="G572" t="n">
-        <v>17.8465957641602</v>
+        <v>17.8465938568115</v>
       </c>
       <c r="H572" t="n">
         <v>126</v>
@@ -16986,7 +16986,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H573" t="n">
         <v>1276</v>
@@ -17015,7 +17015,7 @@
         <v>19.75</v>
       </c>
       <c r="G574" t="n">
-        <v>17.6235122680664</v>
+        <v>17.623514175415</v>
       </c>
       <c r="H574" t="n">
         <v>1476</v>
@@ -17044,7 +17044,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H575" t="n">
         <v>12920</v>
@@ -17073,7 +17073,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H576" t="n">
         <v>6126</v>
@@ -17102,7 +17102,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H577" t="n">
         <v>3426</v>
@@ -17160,7 +17160,7 @@
         <v>20.5</v>
       </c>
       <c r="G579" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H579" t="n">
         <v>6769</v>
@@ -17189,7 +17189,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H580" t="n">
         <v>11118</v>
@@ -17218,7 +17218,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>18.114294052124</v>
+        <v>18.1142959594727</v>
       </c>
       <c r="H581" t="n">
         <v>1397</v>
@@ -17247,7 +17247,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H582" t="n">
         <v>3500</v>
@@ -17276,7 +17276,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H583" t="n">
         <v>26</v>
@@ -17305,7 +17305,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>18.2035293579102</v>
+        <v>18.2035255432129</v>
       </c>
       <c r="H584" t="n">
         <v>1966</v>
@@ -17334,7 +17334,7 @@
         <v>21</v>
       </c>
       <c r="G585" t="n">
-        <v>18.7389259338379</v>
+        <v>18.7389221191406</v>
       </c>
       <c r="H585" t="n">
         <v>62155</v>
@@ -17421,7 +17421,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>19.0066223144531</v>
+        <v>19.0066204071045</v>
       </c>
       <c r="H588" t="n">
         <v>3033</v>
@@ -17450,7 +17450,7 @@
         <v>21.5</v>
       </c>
       <c r="G589" t="n">
-        <v>19.1850891113281</v>
+        <v>19.1850910186768</v>
       </c>
       <c r="H589" t="n">
         <v>3910</v>
@@ -17479,7 +17479,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>19.4527854919434</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H590" t="n">
         <v>27442</v>
@@ -17508,7 +17508,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>19.4527854919434</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H591" t="n">
         <v>2820</v>
@@ -17537,7 +17537,7 @@
         <v>21.5</v>
       </c>
       <c r="G592" t="n">
-        <v>19.1850891113281</v>
+        <v>19.1850910186768</v>
       </c>
       <c r="H592" t="n">
         <v>14908</v>
@@ -17566,7 +17566,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>19.3635559082031</v>
+        <v>19.3635578155518</v>
       </c>
       <c r="H593" t="n">
         <v>5818</v>
@@ -17624,7 +17624,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>19.4527854919434</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H595" t="n">
         <v>7478</v>
@@ -17740,7 +17740,7 @@
         <v>22</v>
       </c>
       <c r="G599" t="n">
-        <v>19.631254196167</v>
+        <v>19.6312561035156</v>
       </c>
       <c r="H599" t="n">
         <v>6801</v>
@@ -17798,7 +17798,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G601" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H601" t="n">
         <v>2527</v>
@@ -17914,7 +17914,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>19.3635559082031</v>
+        <v>19.3635578155518</v>
       </c>
       <c r="H605" t="n">
         <v>5376</v>
@@ -17943,7 +17943,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H606" t="n">
         <v>2280</v>
@@ -17972,7 +17972,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H607" t="n">
         <v>3152</v>
@@ -18001,7 +18001,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G608" t="n">
-        <v>19.4527854919434</v>
+        <v>19.452787399292</v>
       </c>
       <c r="H608" t="n">
         <v>8174</v>
@@ -18088,7 +18088,7 @@
         <v>22</v>
       </c>
       <c r="G611" t="n">
-        <v>19.631254196167</v>
+        <v>19.6312561035156</v>
       </c>
       <c r="H611" t="n">
         <v>2653</v>
@@ -18146,7 +18146,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>19.8989505767822</v>
+        <v>19.8989524841309</v>
       </c>
       <c r="H613" t="n">
         <v>3145</v>
@@ -18175,7 +18175,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H614" t="n">
         <v>2737</v>
@@ -18233,7 +18233,7 @@
         <v>22</v>
       </c>
       <c r="G616" t="n">
-        <v>19.631254196167</v>
+        <v>19.6312561035156</v>
       </c>
       <c r="H616" t="n">
         <v>6076</v>
@@ -18262,7 +18262,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>20.7912845611572</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H617" t="n">
         <v>12485</v>
@@ -18349,7 +18349,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>21.1482162475586</v>
+        <v>21.1482200622559</v>
       </c>
       <c r="H620" t="n">
         <v>3563</v>
@@ -18378,7 +18378,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>20.8805141448975</v>
+        <v>20.8805160522461</v>
       </c>
       <c r="H621" t="n">
         <v>2225</v>
@@ -18436,7 +18436,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G623" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H623" t="n">
         <v>4899</v>
@@ -18465,7 +18465,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>21.1482162475586</v>
+        <v>21.1482200622559</v>
       </c>
       <c r="H624" t="n">
         <v>4403</v>
@@ -18494,7 +18494,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>20.8805141448975</v>
+        <v>20.8805160522461</v>
       </c>
       <c r="H625" t="n">
         <v>3148</v>
@@ -18581,7 +18581,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>21.7728462219238</v>
+        <v>21.7728443145752</v>
       </c>
       <c r="H628" t="n">
         <v>3942</v>
@@ -18668,7 +18668,7 @@
         <v>24</v>
       </c>
       <c r="G631" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H631" t="n">
         <v>16893</v>
@@ -18842,7 +18842,7 @@
         <v>24</v>
       </c>
       <c r="G637" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H637" t="n">
         <v>11025</v>
@@ -18900,7 +18900,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H639" t="n">
         <v>5914</v>
@@ -18958,7 +18958,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G641" t="n">
-        <v>21.1482162475586</v>
+        <v>21.1482200622559</v>
       </c>
       <c r="H641" t="n">
         <v>1401</v>
@@ -18987,7 +18987,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H642" t="n">
         <v>2409</v>
@@ -19016,7 +19016,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>20.7912845611572</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H643" t="n">
         <v>2095</v>
@@ -19074,7 +19074,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G645" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H645" t="n">
         <v>5975</v>
@@ -19103,7 +19103,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H646" t="n">
         <v>1770</v>
@@ -19132,7 +19132,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>21.1482162475586</v>
+        <v>21.1482200622559</v>
       </c>
       <c r="H647" t="n">
         <v>2283</v>
@@ -19161,7 +19161,7 @@
         <v>24</v>
       </c>
       <c r="G648" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H648" t="n">
         <v>6636</v>
@@ -19190,7 +19190,7 @@
         <v>24</v>
       </c>
       <c r="G649" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H649" t="n">
         <v>10221</v>
@@ -19219,7 +19219,7 @@
         <v>24</v>
       </c>
       <c r="G650" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H650" t="n">
         <v>3081</v>
@@ -19248,7 +19248,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H651" t="n">
         <v>3427</v>
@@ -19277,7 +19277,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>21.1482162475586</v>
+        <v>21.1482200622559</v>
       </c>
       <c r="H652" t="n">
         <v>1361</v>
@@ -19306,7 +19306,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G653" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H653" t="n">
         <v>746</v>
@@ -19335,7 +19335,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G654" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H654" t="n">
         <v>675</v>
@@ -19364,7 +19364,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G655" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H655" t="n">
         <v>11198</v>
@@ -19393,7 +19393,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>21.1482162475586</v>
+        <v>21.1482200622559</v>
       </c>
       <c r="H656" t="n">
         <v>4430</v>
@@ -19480,7 +19480,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G659" t="n">
-        <v>20.2558860778809</v>
+        <v>20.2558841705322</v>
       </c>
       <c r="H659" t="n">
         <v>9014</v>
@@ -19567,7 +19567,7 @@
         <v>23</v>
       </c>
       <c r="G662" t="n">
-        <v>20.5235862731934</v>
+        <v>20.5235843658447</v>
       </c>
       <c r="H662" t="n">
         <v>3585</v>
@@ -19625,7 +19625,7 @@
         <v>22.5</v>
       </c>
       <c r="G664" t="n">
-        <v>20.0774192810059</v>
+        <v>20.0774230957031</v>
       </c>
       <c r="H664" t="n">
         <v>8734</v>
@@ -19654,7 +19654,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H665" t="n">
         <v>8640</v>
@@ -19683,7 +19683,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>19.3635559082031</v>
+        <v>19.3635578155518</v>
       </c>
       <c r="H666" t="n">
         <v>4583</v>
@@ -19712,7 +19712,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.5420227050781</v>
+        <v>19.5420207977295</v>
       </c>
       <c r="H667" t="n">
         <v>10615</v>
@@ -19741,7 +19741,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>19.0066223144531</v>
+        <v>19.0066204071045</v>
       </c>
       <c r="H668" t="n">
         <v>4049</v>
@@ -19770,7 +19770,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G669" t="n">
-        <v>18.649694442749</v>
+        <v>18.6496906280518</v>
       </c>
       <c r="H669" t="n">
         <v>8327</v>
@@ -19799,7 +19799,7 @@
         <v>20.5</v>
       </c>
       <c r="G670" t="n">
-        <v>18.2927589416504</v>
+        <v>18.292760848999</v>
       </c>
       <c r="H670" t="n">
         <v>9957</v>
@@ -19828,7 +19828,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G671" t="n">
-        <v>17.5342769622803</v>
+        <v>17.5342788696289</v>
       </c>
       <c r="H671" t="n">
         <v>4618</v>
@@ -19886,7 +19886,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>17.4896621704102</v>
+        <v>17.4896640777588</v>
       </c>
       <c r="H673" t="n">
         <v>2591</v>
@@ -19944,7 +19944,7 @@
         <v>18</v>
       </c>
       <c r="G675" t="n">
-        <v>16.0619354248047</v>
+        <v>16.0619335174561</v>
       </c>
       <c r="H675" t="n">
         <v>22529</v>
@@ -19973,7 +19973,7 @@
         <v>17.5</v>
       </c>
       <c r="G676" t="n">
-        <v>15.6157703399658</v>
+        <v>15.6157712936401</v>
       </c>
       <c r="H676" t="n">
         <v>12149</v>
@@ -20118,7 +20118,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>18.4712257385254</v>
+        <v>18.471227645874</v>
       </c>
       <c r="H681" t="n">
         <v>24241</v>
@@ -20147,7 +20147,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>18.5604572296143</v>
+        <v>18.5604610443115</v>
       </c>
       <c r="H682" t="n">
         <v>3394</v>
@@ -20205,7 +20205,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>19.0066223144531</v>
+        <v>19.0066204071045</v>
       </c>
       <c r="H684" t="n">
         <v>1114</v>
@@ -20234,7 +20234,7 @@
         <v>22</v>
       </c>
       <c r="G685" t="n">
-        <v>19.631254196167</v>
+        <v>19.6312561035156</v>
       </c>
       <c r="H685" t="n">
         <v>14359</v>
@@ -20263,7 +20263,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>20.2558860778809</v>
+        <v>20.2558841705322</v>
       </c>
       <c r="H686" t="n">
         <v>17625</v>
@@ -20292,7 +20292,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>20.7912845611572</v>
+        <v>20.79128074646</v>
       </c>
       <c r="H687" t="n">
         <v>33277</v>
@@ -20350,7 +20350,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G689" t="n">
-        <v>21.1482162475586</v>
+        <v>21.1482200622559</v>
       </c>
       <c r="H689" t="n">
         <v>5460</v>
@@ -20379,7 +20379,7 @@
         <v>23</v>
       </c>
       <c r="G690" t="n">
-        <v>20.5235862731934</v>
+        <v>20.5235843658447</v>
       </c>
       <c r="H690" t="n">
         <v>13295</v>
@@ -20408,7 +20408,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>20.8805141448975</v>
+        <v>20.8805160522461</v>
       </c>
       <c r="H691" t="n">
         <v>1329</v>
@@ -20437,7 +20437,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>20.8805141448975</v>
+        <v>20.8805160522461</v>
       </c>
       <c r="H692" t="n">
         <v>2028</v>
@@ -20553,7 +20553,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G696" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H696" t="n">
         <v>6358</v>
@@ -20611,7 +20611,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H698" t="n">
         <v>3647</v>
@@ -20640,7 +20640,7 @@
         <v>24</v>
       </c>
       <c r="G699" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H699" t="n">
         <v>4272</v>
@@ -20669,7 +20669,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>21.0589828491211</v>
+        <v>21.0589809417725</v>
       </c>
       <c r="H700" t="n">
         <v>3057</v>
@@ -20698,7 +20698,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H701" t="n">
         <v>2334</v>
@@ -20727,7 +20727,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H702" t="n">
         <v>3693</v>
@@ -20756,7 +20756,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>21.3266792297363</v>
+        <v>21.326681137085</v>
       </c>
       <c r="H703" t="n">
         <v>4301</v>
@@ -20785,7 +20785,7 @@
         <v>24</v>
       </c>
       <c r="G704" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H704" t="n">
         <v>20313</v>
@@ -20843,7 +20843,7 @@
         <v>24</v>
       </c>
       <c r="G706" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H706" t="n">
         <v>2368</v>
@@ -20872,7 +20872,7 @@
         <v>24</v>
       </c>
       <c r="G707" t="n">
-        <v>21.4159126281738</v>
+        <v>21.4159145355225</v>
       </c>
       <c r="H707" t="n">
         <v>10495</v>
@@ -20988,7 +20988,7 @@
         <v>25</v>
       </c>
       <c r="G711" t="n">
-        <v>22.7315845489502</v>
+        <v>22.7315826416016</v>
       </c>
       <c r="H711" t="n">
         <v>5201</v>
@@ -21017,7 +21017,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>22.6406574249268</v>
+        <v>22.6406593322754</v>
       </c>
       <c r="H712" t="n">
         <v>5833</v>
@@ -21046,7 +21046,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678779602051</v>
       </c>
       <c r="H713" t="n">
         <v>4418</v>
@@ -21075,7 +21075,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>22.1860275268555</v>
+        <v>22.1860294342041</v>
       </c>
       <c r="H714" t="n">
         <v>3575</v>
@@ -21104,7 +21104,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>22.1860275268555</v>
+        <v>22.1860294342041</v>
       </c>
       <c r="H715" t="n">
         <v>1991</v>
@@ -21133,7 +21133,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>22.1860275268555</v>
+        <v>22.1860294342041</v>
       </c>
       <c r="H716" t="n">
         <v>3812</v>
@@ -21162,7 +21162,7 @@
         <v>24.5</v>
       </c>
       <c r="G717" t="n">
-        <v>22.2769508361816</v>
+        <v>22.2769527435303</v>
       </c>
       <c r="H717" t="n">
         <v>2681</v>
@@ -21191,7 +21191,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>22.1860275268555</v>
+        <v>22.1860294342041</v>
       </c>
       <c r="H718" t="n">
         <v>1554</v>
@@ -21220,7 +21220,7 @@
         <v>24.5</v>
       </c>
       <c r="G719" t="n">
-        <v>22.2769508361816</v>
+        <v>22.2769527435303</v>
       </c>
       <c r="H719" t="n">
         <v>565</v>
@@ -21278,7 +21278,7 @@
         <v>24.5</v>
       </c>
       <c r="G721" t="n">
-        <v>22.2769508361816</v>
+        <v>22.2769527435303</v>
       </c>
       <c r="H721" t="n">
         <v>484</v>
@@ -21307,7 +21307,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>22.6406574249268</v>
+        <v>22.6406593322754</v>
       </c>
       <c r="H722" t="n">
         <v>17150</v>
@@ -21336,7 +21336,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678779602051</v>
       </c>
       <c r="H723" t="n">
         <v>6214</v>
@@ -21365,7 +21365,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G724" t="n">
-        <v>22.6406574249268</v>
+        <v>22.6406593322754</v>
       </c>
       <c r="H724" t="n">
         <v>722</v>
@@ -21394,7 +21394,7 @@
         <v>24.5</v>
       </c>
       <c r="G725" t="n">
-        <v>22.2769508361816</v>
+        <v>22.2769527435303</v>
       </c>
       <c r="H725" t="n">
         <v>1685</v>
@@ -21423,7 +21423,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G726" t="n">
-        <v>22.5497283935547</v>
+        <v>22.549732208252</v>
       </c>
       <c r="H726" t="n">
         <v>1103</v>
@@ -21452,7 +21452,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>22.6406574249268</v>
+        <v>22.6406593322754</v>
       </c>
       <c r="H727" t="n">
         <v>412</v>
@@ -21481,7 +21481,7 @@
         <v>24.5</v>
       </c>
       <c r="G728" t="n">
-        <v>22.2769508361816</v>
+        <v>22.2769527435303</v>
       </c>
       <c r="H728" t="n">
         <v>11066</v>
@@ -21539,7 +21539,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G730" t="n">
-        <v>22.0950984954834</v>
+        <v>22.095100402832</v>
       </c>
       <c r="H730" t="n">
         <v>2200</v>
@@ -21655,7 +21655,7 @@
         <v>23.5</v>
       </c>
       <c r="G734" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H734" t="n">
         <v>416</v>
@@ -21829,7 +21829,7 @@
         <v>23.5</v>
       </c>
       <c r="G740" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H740" t="n">
         <v>3450</v>
@@ -21858,7 +21858,7 @@
         <v>23.5</v>
       </c>
       <c r="G741" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H741" t="n">
         <v>767</v>
@@ -21887,7 +21887,7 @@
         <v>23.5</v>
       </c>
       <c r="G742" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H742" t="n">
         <v>1047</v>
@@ -21916,7 +21916,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>20.549352645874</v>
+        <v>20.5493507385254</v>
       </c>
       <c r="H743" t="n">
         <v>3875</v>
@@ -21974,7 +21974,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767658233643</v>
       </c>
       <c r="H745" t="n">
         <v>1335</v>
@@ -22061,7 +22061,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H748" t="n">
         <v>1173</v>
@@ -22090,7 +22090,7 @@
         <v>23.5</v>
       </c>
       <c r="G749" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H749" t="n">
         <v>979</v>
@@ -22119,7 +22119,7 @@
         <v>23.5</v>
       </c>
       <c r="G750" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H750" t="n">
         <v>3667</v>
@@ -22322,7 +22322,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H757" t="n">
         <v>722</v>
@@ -22351,7 +22351,7 @@
         <v>23.5</v>
       </c>
       <c r="G758" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H758" t="n">
         <v>6240</v>
@@ -22409,7 +22409,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767658233643</v>
       </c>
       <c r="H760" t="n">
         <v>2070</v>
@@ -22496,7 +22496,7 @@
         <v>23.5</v>
       </c>
       <c r="G763" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H763" t="n">
         <v>728</v>
@@ -22554,7 +22554,7 @@
         <v>23.5</v>
       </c>
       <c r="G765" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H765" t="n">
         <v>1731</v>
@@ -22583,7 +22583,7 @@
         <v>23</v>
       </c>
       <c r="G766" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H766" t="n">
         <v>1718</v>
@@ -22612,7 +22612,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H767" t="n">
         <v>305</v>
@@ -22728,7 +22728,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H771" t="n">
         <v>779</v>
@@ -22757,7 +22757,7 @@
         <v>23</v>
       </c>
       <c r="G772" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H772" t="n">
         <v>843</v>
@@ -22873,7 +22873,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G776" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767658233643</v>
       </c>
       <c r="H776" t="n">
         <v>3</v>
@@ -22902,7 +22902,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767658233643</v>
       </c>
       <c r="H777" t="n">
         <v>3189</v>
@@ -23018,7 +23018,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H781" t="n">
         <v>278</v>
@@ -23076,7 +23076,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>21.276762008667</v>
+        <v>21.2767658233643</v>
       </c>
       <c r="H783" t="n">
         <v>505</v>
@@ -23105,7 +23105,7 @@
         <v>23</v>
       </c>
       <c r="G784" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H784" t="n">
         <v>1187</v>
@@ -23134,7 +23134,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>20.7312088012695</v>
+        <v>20.7312049865723</v>
       </c>
       <c r="H785" t="n">
         <v>294</v>
@@ -23163,7 +23163,7 @@
         <v>23.5</v>
       </c>
       <c r="G786" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H786" t="n">
         <v>19431</v>
@@ -23192,7 +23192,7 @@
         <v>23.5</v>
       </c>
       <c r="G787" t="n">
-        <v>21.3676910400391</v>
+        <v>21.3676872253418</v>
       </c>
       <c r="H787" t="n">
         <v>8270</v>
@@ -23279,7 +23279,7 @@
         <v>23</v>
       </c>
       <c r="G790" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H790" t="n">
         <v>1960</v>
@@ -23308,7 +23308,7 @@
         <v>23</v>
       </c>
       <c r="G791" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H791" t="n">
         <v>417</v>
@@ -23337,7 +23337,7 @@
         <v>23</v>
       </c>
       <c r="G792" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H792" t="n">
         <v>14773</v>
@@ -23424,7 +23424,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>20.549352645874</v>
+        <v>20.5493507385254</v>
       </c>
       <c r="H795" t="n">
         <v>869</v>
@@ -23482,7 +23482,7 @@
         <v>23</v>
       </c>
       <c r="G797" t="n">
-        <v>20.9130592346191</v>
+        <v>20.9130573272705</v>
       </c>
       <c r="H797" t="n">
         <v>710</v>
@@ -23569,7 +23569,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G800" t="n">
-        <v>20.549352645874</v>
+        <v>20.5493507385254</v>
       </c>
       <c r="H800" t="n">
         <v>7793</v>
@@ -23598,7 +23598,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>21.0039863586426</v>
+        <v>21.0039844512939</v>
       </c>
       <c r="H801" t="n">
         <v>1969</v>
@@ -23656,7 +23656,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>22.1860275268555</v>
+        <v>22.1860294342041</v>
       </c>
       <c r="H803" t="n">
         <v>3814</v>
@@ -23685,7 +23685,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G804" t="n">
-        <v>22.3678798675537</v>
+        <v>22.3678779602051</v>
       </c>
       <c r="H804" t="n">
         <v>9325</v>
@@ -23743,7 +23743,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>22.9134387969971</v>
+        <v>22.9134368896484</v>
       </c>
       <c r="H806" t="n">
         <v>5503</v>
@@ -23801,7 +23801,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G808" t="n">
-        <v>24.0045528411865</v>
+        <v>24.0045547485352</v>
       </c>
       <c r="H808" t="n">
         <v>10233</v>
@@ -23830,7 +23830,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G809" t="n">
-        <v>23.0952892303467</v>
+        <v>23.0952911376953</v>
       </c>
       <c r="H809" t="n">
         <v>248720</v>
@@ -23859,7 +23859,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G810" t="n">
-        <v>23.368070602417</v>
+        <v>23.3680686950684</v>
       </c>
       <c r="H810" t="n">
         <v>2600</v>
@@ -23888,7 +23888,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>24.0045528411865</v>
+        <v>24.0045547485352</v>
       </c>
       <c r="H811" t="n">
         <v>3875</v>
@@ -23946,7 +23946,7 @@
         <v>26.5</v>
       </c>
       <c r="G813" t="n">
-        <v>24.09547996521</v>
+        <v>24.0954780578613</v>
       </c>
       <c r="H813" t="n">
         <v>742</v>
@@ -23975,7 +23975,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>24.2773323059082</v>
+        <v>24.2773342132568</v>
       </c>
       <c r="H814" t="n">
         <v>1094</v>
@@ -24004,7 +24004,7 @@
         <v>26.5</v>
       </c>
       <c r="G815" t="n">
-        <v>24.09547996521</v>
+        <v>24.0954780578613</v>
       </c>
       <c r="H815" t="n">
         <v>1378</v>
@@ -24033,7 +24033,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>24.7319660186768</v>
+        <v>24.7319622039795</v>
       </c>
       <c r="H816" t="n">
         <v>19373</v>
@@ -24120,7 +24120,7 @@
         <v>27.5</v>
       </c>
       <c r="G819" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H819" t="n">
         <v>12457</v>
@@ -24265,7 +24265,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>25.2775211334229</v>
+        <v>25.2775230407715</v>
       </c>
       <c r="H824" t="n">
         <v>9201</v>
@@ -24294,7 +24294,7 @@
         <v>27.5</v>
       </c>
       <c r="G825" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H825" t="n">
         <v>7361</v>
@@ -24323,7 +24323,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G826" t="n">
-        <v>24.8228874206543</v>
+        <v>24.8228912353516</v>
       </c>
       <c r="H826" t="n">
         <v>3821</v>
@@ -24352,7 +24352,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>24.8228874206543</v>
+        <v>24.8228912353516</v>
       </c>
       <c r="H827" t="n">
         <v>2515</v>
@@ -24381,7 +24381,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>24.8228874206543</v>
+        <v>24.8228912353516</v>
       </c>
       <c r="H828" t="n">
         <v>2875</v>
@@ -24439,7 +24439,7 @@
         <v>27.5</v>
       </c>
       <c r="G830" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H830" t="n">
         <v>3462</v>
@@ -24468,7 +24468,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>25.186595916748</v>
+        <v>25.1865978240967</v>
       </c>
       <c r="H831" t="n">
         <v>800</v>
@@ -24526,7 +24526,7 @@
         <v>26</v>
       </c>
       <c r="G833" t="n">
-        <v>23.64084815979</v>
+        <v>23.6408500671387</v>
       </c>
       <c r="H833" t="n">
         <v>7174</v>
@@ -24555,7 +24555,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G834" t="n">
-        <v>24.1864051818848</v>
+        <v>24.186408996582</v>
       </c>
       <c r="H834" t="n">
         <v>2244</v>
@@ -24584,7 +24584,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>24.2773323059082</v>
+        <v>24.2773342132568</v>
       </c>
       <c r="H835" t="n">
         <v>942</v>
@@ -24613,7 +24613,7 @@
         <v>27.5</v>
       </c>
       <c r="G836" t="n">
-        <v>25.0047416687012</v>
+        <v>25.0047435760498</v>
       </c>
       <c r="H836" t="n">
         <v>3180</v>
@@ -24642,7 +24642,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>25.7321548461914</v>
+        <v>25.7321529388428</v>
       </c>
       <c r="H837" t="n">
         <v>6802</v>
@@ -24700,7 +24700,7 @@
         <v>28.5</v>
       </c>
       <c r="G839" t="n">
-        <v>25.9140071868896</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H839" t="n">
         <v>1912</v>
@@ -24729,7 +24729,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>25.5503044128418</v>
+        <v>25.5503005981445</v>
       </c>
       <c r="H840" t="n">
         <v>1023</v>
@@ -24845,7 +24845,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>26.1867847442627</v>
+        <v>26.1867866516113</v>
       </c>
       <c r="H844" t="n">
         <v>4971</v>
@@ -24961,7 +24961,7 @@
         <v>28.5</v>
       </c>
       <c r="G848" t="n">
-        <v>25.9140071868896</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H848" t="n">
         <v>4337</v>
@@ -24990,7 +24990,7 @@
         <v>28.5</v>
       </c>
       <c r="G849" t="n">
-        <v>25.9140071868896</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H849" t="n">
         <v>1560</v>
@@ -25019,7 +25019,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>25.5503044128418</v>
+        <v>25.5503005981445</v>
       </c>
       <c r="H850" t="n">
         <v>4390</v>
@@ -25077,7 +25077,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>25.5503044128418</v>
+        <v>25.5503005981445</v>
       </c>
       <c r="H852" t="n">
         <v>2971</v>
@@ -25106,7 +25106,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>26.1867847442627</v>
+        <v>26.1867866516113</v>
       </c>
       <c r="H853" t="n">
         <v>2676</v>
@@ -25193,7 +25193,7 @@
         <v>28.5</v>
       </c>
       <c r="G856" t="n">
-        <v>25.9140071868896</v>
+        <v>25.914005279541</v>
       </c>
       <c r="H856" t="n">
         <v>2177</v>
@@ -25251,7 +25251,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>28.0053119659424</v>
+        <v>28.005313873291</v>
       </c>
       <c r="H858" t="n">
         <v>16337</v>
@@ -25280,7 +25280,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>29.0055027008057</v>
+        <v>29.0055046081543</v>
       </c>
       <c r="H859" t="n">
         <v>9815</v>
@@ -25367,7 +25367,7 @@
         <v>32.5</v>
       </c>
       <c r="G862" t="n">
-        <v>29.5510578155518</v>
+        <v>29.5510597229004</v>
       </c>
       <c r="H862" t="n">
         <v>8073</v>
@@ -25396,7 +25396,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>29.6419830322266</v>
+        <v>29.6419868469238</v>
       </c>
       <c r="H863" t="n">
         <v>5110</v>
@@ -25454,7 +25454,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>30.6421794891357</v>
+        <v>30.6421775817871</v>
       </c>
       <c r="H865" t="n">
         <v>13129</v>
@@ -25483,7 +25483,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G866" t="n">
-        <v>31.7332954406738</v>
+        <v>31.7332916259766</v>
       </c>
       <c r="H866" t="n">
         <v>25815</v>
@@ -25512,7 +25512,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>31.1877307891846</v>
+        <v>31.1877346038818</v>
       </c>
       <c r="H867" t="n">
         <v>9130</v>
@@ -25541,7 +25541,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G868" t="n">
-        <v>31.7332954406738</v>
+        <v>31.7332916259766</v>
       </c>
       <c r="H868" t="n">
         <v>10584</v>
@@ -25570,7 +25570,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>32.0060768127441</v>
+        <v>32.0060729980469</v>
       </c>
       <c r="H869" t="n">
         <v>47310</v>
@@ -25628,7 +25628,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>34.2792358398438</v>
+        <v>34.2792282104492</v>
       </c>
       <c r="H871" t="n">
         <v>19913</v>
@@ -25715,7 +25715,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G874" t="n">
-        <v>36.0068283081055</v>
+        <v>36.0068321228027</v>
       </c>
       <c r="H874" t="n">
         <v>13085</v>
@@ -25744,7 +25744,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>35.5521926879883</v>
+        <v>35.5521965026855</v>
       </c>
       <c r="H875" t="n">
         <v>8378</v>
@@ -25773,7 +25773,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>34.1883010864258</v>
+        <v>34.188304901123</v>
       </c>
       <c r="H876" t="n">
         <v>14351</v>
@@ -25802,7 +25802,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G877" t="n">
-        <v>34.9157180786133</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H877" t="n">
         <v>17056</v>
@@ -25831,7 +25831,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G878" t="n">
-        <v>34.9157180786133</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H878" t="n">
         <v>9962</v>
@@ -25889,7 +25889,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>34.7338600158691</v>
+        <v>34.7338638305664</v>
       </c>
       <c r="H880" t="n">
         <v>5049</v>
@@ -25918,7 +25918,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H881" t="n">
         <v>3852</v>
@@ -25947,7 +25947,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G882" t="n">
-        <v>34.1883010864258</v>
+        <v>34.188304901123</v>
       </c>
       <c r="H882" t="n">
         <v>2774</v>
@@ -25976,7 +25976,7 @@
         <v>37.5</v>
       </c>
       <c r="G883" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H883" t="n">
         <v>3077</v>
@@ -26005,7 +26005,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>34.8247833251953</v>
+        <v>34.8247871398926</v>
       </c>
       <c r="H884" t="n">
         <v>7646</v>
@@ -26034,7 +26034,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G885" t="n">
-        <v>34.7338600158691</v>
+        <v>34.7338638305664</v>
       </c>
       <c r="H885" t="n">
         <v>3396</v>
@@ -26092,7 +26092,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>34.1883010864258</v>
+        <v>34.188304901123</v>
       </c>
       <c r="H887" t="n">
         <v>3978</v>
@@ -26121,7 +26121,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G888" t="n">
-        <v>34.6429328918457</v>
+        <v>34.642936706543</v>
       </c>
       <c r="H888" t="n">
         <v>3065</v>
@@ -26150,7 +26150,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>34.8247833251953</v>
+        <v>34.8247871398926</v>
       </c>
       <c r="H889" t="n">
         <v>3085</v>
@@ -26179,7 +26179,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>34.6429328918457</v>
+        <v>34.642936706543</v>
       </c>
       <c r="H890" t="n">
         <v>4527</v>
@@ -26208,7 +26208,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>34.9157180786133</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H891" t="n">
         <v>8405</v>
@@ -26266,7 +26266,7 @@
         <v>37.5</v>
       </c>
       <c r="G893" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H893" t="n">
         <v>3082</v>
@@ -26295,7 +26295,7 @@
         <v>37</v>
       </c>
       <c r="G894" t="n">
-        <v>33.642749786377</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H894" t="n">
         <v>6046</v>
@@ -26353,7 +26353,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G896" t="n">
-        <v>34.2792358398438</v>
+        <v>34.2792282104492</v>
       </c>
       <c r="H896" t="n">
         <v>2791</v>
@@ -26382,7 +26382,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H897" t="n">
         <v>2274</v>
@@ -26411,7 +26411,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G898" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H898" t="n">
         <v>5138</v>
@@ -26469,7 +26469,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G900" t="n">
-        <v>33.0971870422363</v>
+        <v>33.0971908569336</v>
       </c>
       <c r="H900" t="n">
         <v>10732</v>
@@ -26498,7 +26498,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G901" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244094848633</v>
       </c>
       <c r="H901" t="n">
         <v>8762</v>
@@ -26527,7 +26527,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H902" t="n">
         <v>30124</v>
@@ -26585,7 +26585,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H904" t="n">
         <v>11103</v>
@@ -26643,7 +26643,7 @@
         <v>38.5</v>
       </c>
       <c r="G906" t="n">
-        <v>35.0066375732422</v>
+        <v>35.0066413879395</v>
       </c>
       <c r="H906" t="n">
         <v>14610</v>
@@ -26672,7 +26672,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G907" t="n">
-        <v>34.9157180786133</v>
+        <v>34.915714263916</v>
       </c>
       <c r="H907" t="n">
         <v>10279</v>
@@ -26701,7 +26701,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>34.8247833251953</v>
+        <v>34.8247871398926</v>
       </c>
       <c r="H908" t="n">
         <v>5104</v>
@@ -26730,7 +26730,7 @@
         <v>37.5</v>
       </c>
       <c r="G909" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H909" t="n">
         <v>1722</v>
@@ -26759,7 +26759,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G910" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H910" t="n">
         <v>2409</v>
@@ -26788,7 +26788,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G911" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H911" t="n">
         <v>2922</v>
@@ -26817,7 +26817,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G912" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H912" t="n">
         <v>13822</v>
@@ -26875,7 +26875,7 @@
         <v>37</v>
       </c>
       <c r="G914" t="n">
-        <v>33.642749786377</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H914" t="n">
         <v>4087</v>
@@ -26904,7 +26904,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G915" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244094848633</v>
       </c>
       <c r="H915" t="n">
         <v>5242</v>
@@ -26962,7 +26962,7 @@
         <v>37</v>
       </c>
       <c r="G917" t="n">
-        <v>33.642749786377</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H917" t="n">
         <v>3855</v>
@@ -27020,7 +27020,7 @@
         <v>36.5</v>
       </c>
       <c r="G919" t="n">
-        <v>33.188117980957</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H919" t="n">
         <v>1912</v>
@@ -27136,7 +27136,7 @@
         <v>36.5</v>
       </c>
       <c r="G923" t="n">
-        <v>33.188117980957</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H923" t="n">
         <v>1171</v>
@@ -27165,7 +27165,7 @@
         <v>36.5</v>
       </c>
       <c r="G924" t="n">
-        <v>33.188117980957</v>
+        <v>33.1881141662598</v>
       </c>
       <c r="H924" t="n">
         <v>233</v>
@@ -27252,7 +27252,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G927" t="n">
-        <v>32.1879234313965</v>
+        <v>32.1879272460938</v>
       </c>
       <c r="H927" t="n">
         <v>8883</v>
@@ -27281,7 +27281,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.6425628662109</v>
+        <v>32.6425590515137</v>
       </c>
       <c r="H928" t="n">
         <v>5913</v>
@@ -27368,7 +27368,7 @@
         <v>39.5</v>
       </c>
       <c r="G931" t="n">
-        <v>35.9159049987793</v>
+        <v>35.915901184082</v>
       </c>
       <c r="H931" t="n">
         <v>14219</v>
@@ -27426,7 +27426,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.1883010864258</v>
+        <v>34.188304901123</v>
       </c>
       <c r="H933" t="n">
         <v>13379</v>
@@ -27484,7 +27484,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H935" t="n">
         <v>3269</v>
@@ -27513,7 +27513,7 @@
         <v>37.5</v>
       </c>
       <c r="G936" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H936" t="n">
         <v>3891</v>
@@ -27542,7 +27542,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G937" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H937" t="n">
         <v>43211</v>
@@ -27571,7 +27571,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H938" t="n">
         <v>1429</v>
@@ -27600,7 +27600,7 @@
         <v>37.5</v>
       </c>
       <c r="G939" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H939" t="n">
         <v>1372</v>
@@ -27629,7 +27629,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G940" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H940" t="n">
         <v>3638</v>
@@ -27658,7 +27658,7 @@
         <v>37</v>
       </c>
       <c r="G941" t="n">
-        <v>33.642749786377</v>
+        <v>33.6427421569824</v>
       </c>
       <c r="H941" t="n">
         <v>2299</v>
@@ -27716,7 +27716,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G943" t="n">
-        <v>34.0064544677734</v>
+        <v>34.0064506530762</v>
       </c>
       <c r="H943" t="n">
         <v>5713</v>
@@ -27745,7 +27745,7 @@
         <v>37.5</v>
       </c>
       <c r="G944" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H944" t="n">
         <v>3069</v>
@@ -27774,7 +27774,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G945" t="n">
-        <v>34.3701553344727</v>
+        <v>34.3701591491699</v>
       </c>
       <c r="H945" t="n">
         <v>3459</v>
@@ -27832,7 +27832,7 @@
         <v>37.5</v>
       </c>
       <c r="G947" t="n">
-        <v>34.0973777770996</v>
+        <v>34.0973739624023</v>
       </c>
       <c r="H947" t="n">
         <v>2150</v>
@@ -27948,7 +27948,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G951" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244094848633</v>
       </c>
       <c r="H951" t="n">
         <v>6258</v>
@@ -27977,7 +27977,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>32.824405670166</v>
+        <v>32.8244094848633</v>
       </c>
       <c r="H952" t="n">
         <v>2522</v>
@@ -28006,7 +28006,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G953" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H953" t="n">
         <v>3746</v>
@@ -28035,7 +28035,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G954" t="n">
-        <v>33.4608917236328</v>
+        <v>33.4608879089355</v>
       </c>
       <c r="H954" t="n">
         <v>3675</v>
@@ -28064,7 +28064,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G955" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H955" t="n">
         <v>782</v>
@@ -28093,7 +28093,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7336692810059</v>
+        <v>33.7336730957031</v>
       </c>
       <c r="H956" t="n">
         <v>2318</v>
@@ -28122,7 +28122,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H957" t="n">
         <v>3272</v>
@@ -28151,7 +28151,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G958" t="n">
-        <v>33.8246002197266</v>
+        <v>33.8245964050293</v>
       </c>
       <c r="H958" t="n">
         <v>2088</v>
@@ -28180,7 +28180,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>33.4608917236328</v>
+        <v>33.4608879089355</v>
       </c>
       <c r="H959" t="n">
         <v>2602</v>
@@ -28238,7 +28238,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>34.5444564819336</v>
+        <v>34.5444602966309</v>
       </c>
       <c r="H961" t="n">
         <v>2709</v>
@@ -28267,7 +28267,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>34.451847076416</v>
+        <v>34.4518432617188</v>
       </c>
       <c r="H962" t="n">
         <v>3059</v>
@@ -28296,7 +28296,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>34.451847076416</v>
+        <v>34.4518432617188</v>
       </c>
       <c r="H963" t="n">
         <v>6242</v>
@@ -28325,7 +28325,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G964" t="n">
-        <v>34.6370735168457</v>
+        <v>34.6370697021484</v>
       </c>
       <c r="H964" t="n">
         <v>18984</v>
@@ -28354,7 +28354,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G965" t="n">
-        <v>34.5444564819336</v>
+        <v>34.5444602966309</v>
       </c>
       <c r="H965" t="n">
         <v>6827</v>
@@ -28383,7 +28383,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G966" t="n">
-        <v>34.174015045166</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H966" t="n">
         <v>4232</v>
@@ -28412,7 +28412,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G967" t="n">
-        <v>34.174015045166</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H967" t="n">
         <v>5406</v>
@@ -28528,7 +28528,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G971" t="n">
-        <v>34.174015045166</v>
+        <v>34.1740112304688</v>
       </c>
       <c r="H971" t="n">
         <v>1501</v>
@@ -28789,7 +28789,7 @@
         <v>36</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3404998779297</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H980" t="n">
         <v>3550</v>
@@ -28818,7 +28818,7 @@
         <v>36</v>
       </c>
       <c r="G981" t="n">
-        <v>33.3404998779297</v>
+        <v>33.3404960632324</v>
       </c>
       <c r="H981" t="n">
         <v>8066</v>
@@ -28934,7 +28934,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.7109451293945</v>
+        <v>33.7109527587891</v>
       </c>
       <c r="H985" t="n">
         <v>35290</v>
@@ -29021,7 +29021,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G988" t="n">
-        <v>39.1750831604004</v>
+        <v>39.1750869750977</v>
       </c>
       <c r="H988" t="n">
         <v>28013</v>
@@ -29224,7 +29224,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>44.3613815307617</v>
+        <v>44.361385345459</v>
       </c>
       <c r="H995" t="n">
         <v>45209</v>
@@ -29253,7 +29253,7 @@
         <v>49.5999984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>45.935791015625</v>
+        <v>45.9357948303223</v>
       </c>
       <c r="H996" t="n">
         <v>42057</v>
@@ -29369,7 +29369,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>45.1022796630859</v>
+        <v>45.1022834777832</v>
       </c>
       <c r="H1000" t="n">
         <v>7355</v>
@@ -29427,7 +29427,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>45.5653457641602</v>
+        <v>45.5653495788574</v>
       </c>
       <c r="H1002" t="n">
         <v>31698</v>
@@ -29485,7 +29485,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G1004" t="n">
-        <v>45.194896697998</v>
+        <v>45.1948928833008</v>
       </c>
       <c r="H1004" t="n">
         <v>7319</v>
@@ -29601,7 +29601,7 @@
         <v>50</v>
       </c>
       <c r="G1008" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1008" t="n">
         <v>9494</v>
@@ -29659,7 +29659,7 @@
         <v>50</v>
       </c>
       <c r="G1010" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1010" t="n">
         <v>4334</v>
@@ -29688,7 +29688,7 @@
         <v>50</v>
       </c>
       <c r="G1011" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1011" t="n">
         <v>9263</v>
@@ -29804,7 +29804,7 @@
         <v>48.7000007629395</v>
       </c>
       <c r="G1015" t="n">
-        <v>45.1022796630859</v>
+        <v>45.1022834777832</v>
       </c>
       <c r="H1015" t="n">
         <v>9897</v>
@@ -29833,7 +29833,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1016" t="n">
-        <v>47.6028289794922</v>
+        <v>47.6028251647949</v>
       </c>
       <c r="H1016" t="n">
         <v>10783</v>
@@ -29949,7 +29949,7 @@
         <v>50</v>
       </c>
       <c r="G1020" t="n">
-        <v>46.3062477111816</v>
+        <v>46.3062438964844</v>
       </c>
       <c r="H1020" t="n">
         <v>4229</v>
@@ -30036,7 +30036,7 @@
         <v>54</v>
       </c>
       <c r="G1023" t="n">
-        <v>50.0107421875</v>
+        <v>50.0107460021973</v>
       </c>
       <c r="H1023" t="n">
         <v>11513</v>
@@ -30123,7 +30123,7 @@
         <v>56</v>
       </c>
       <c r="G1026" t="n">
-        <v>51.8629989624023</v>
+        <v>51.8629951477051</v>
       </c>
       <c r="H1026" t="n">
         <v>16498</v>
@@ -30152,7 +30152,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>53.5300178527832</v>
+        <v>53.5300216674805</v>
       </c>
       <c r="H1027" t="n">
         <v>19723</v>
@@ -30268,7 +30268,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>58.1606407165527</v>
+        <v>58.16064453125</v>
       </c>
       <c r="H1031" t="n">
         <v>5992</v>
@@ -30297,7 +30297,7 @@
         <v>62</v>
       </c>
       <c r="G1032" t="n">
-        <v>57.419750213623</v>
+        <v>57.4197463989258</v>
       </c>
       <c r="H1032" t="n">
         <v>5899</v>
@@ -30326,7 +30326,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1033" t="n">
         <v>6666</v>
@@ -30355,7 +30355,7 @@
         <v>62</v>
       </c>
       <c r="G1034" t="n">
-        <v>57.419750213623</v>
+        <v>57.4197463989258</v>
       </c>
       <c r="H1034" t="n">
         <v>2445</v>
@@ -30413,7 +30413,7 @@
         <v>61</v>
       </c>
       <c r="G1036" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1036" t="n">
         <v>5963</v>
@@ -30471,7 +30471,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1038" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1038" t="n">
         <v>7252</v>
@@ -30500,7 +30500,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>55.0118179321289</v>
+        <v>55.0118217468262</v>
       </c>
       <c r="H1039" t="n">
         <v>13841</v>
@@ -30529,7 +30529,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>56.3083953857422</v>
+        <v>56.3083915710449</v>
       </c>
       <c r="H1040" t="n">
         <v>5631</v>
@@ -30587,7 +30587,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>59.6424446105957</v>
+        <v>59.642448425293</v>
       </c>
       <c r="H1042" t="n">
         <v>52827</v>
@@ -30645,7 +30645,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1044" t="n">
-        <v>60.0129013061523</v>
+        <v>60.0128936767578</v>
       </c>
       <c r="H1044" t="n">
         <v>8170</v>
@@ -30674,7 +30674,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276672363281</v>
       </c>
       <c r="H1045" t="n">
         <v>7081</v>
@@ -30732,7 +30732,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1047" t="n">
-        <v>62.7912788391113</v>
+        <v>62.7912712097168</v>
       </c>
       <c r="H1047" t="n">
         <v>20312</v>
@@ -30761,7 +30761,7 @@
         <v>71</v>
       </c>
       <c r="G1048" t="n">
-        <v>65.7548751831055</v>
+        <v>65.7548599243164</v>
       </c>
       <c r="H1048" t="n">
         <v>33718</v>
@@ -30790,7 +30790,7 @@
         <v>71</v>
       </c>
       <c r="G1049" t="n">
-        <v>65.7548751831055</v>
+        <v>65.7548599243164</v>
       </c>
       <c r="H1049" t="n">
         <v>27056</v>
@@ -30877,7 +30877,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>65.3844146728516</v>
+        <v>65.3844223022461</v>
       </c>
       <c r="H1052" t="n">
         <v>17181</v>
@@ -30964,7 +30964,7 @@
         <v>68.5999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>63.5321617126465</v>
+        <v>63.532169342041</v>
       </c>
       <c r="H1055" t="n">
         <v>12535</v>
@@ -30993,7 +30993,7 @@
         <v>66</v>
       </c>
       <c r="G1056" t="n">
-        <v>61.1242485046387</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1056" t="n">
         <v>24459</v>
@@ -31022,7 +31022,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1057" t="n">
         <v>8167</v>
@@ -31051,7 +31051,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1058" t="n">
         <v>7589</v>
@@ -31080,7 +31080,7 @@
         <v>69</v>
       </c>
       <c r="G1059" t="n">
-        <v>63.9026145935059</v>
+        <v>63.9026260375977</v>
       </c>
       <c r="H1059" t="n">
         <v>24805</v>
@@ -31109,7 +31109,7 @@
         <v>67</v>
       </c>
       <c r="G1060" t="n">
-        <v>62.050365447998</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1060" t="n">
         <v>10940</v>
@@ -31138,7 +31138,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1061" t="n">
-        <v>62.2355918884277</v>
+        <v>62.235595703125</v>
       </c>
       <c r="H1061" t="n">
         <v>6033</v>
@@ -31167,7 +31167,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1062" t="n">
-        <v>62.4208221435547</v>
+        <v>62.4208297729492</v>
       </c>
       <c r="H1062" t="n">
         <v>4435</v>
@@ -31196,7 +31196,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>61.4946899414062</v>
+        <v>61.4946975708008</v>
       </c>
       <c r="H1063" t="n">
         <v>4540</v>
@@ -31225,7 +31225,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1064" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1064" t="n">
         <v>7255</v>
@@ -31254,7 +31254,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>60.5685729980469</v>
+        <v>60.5685653686523</v>
       </c>
       <c r="H1065" t="n">
         <v>10994</v>
@@ -31283,7 +31283,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1066" t="n">
-        <v>58.1606407165527</v>
+        <v>58.16064453125</v>
       </c>
       <c r="H1066" t="n">
         <v>16555</v>
@@ -31312,7 +31312,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1067" t="n">
         <v>5930</v>
@@ -31370,7 +31370,7 @@
         <v>61</v>
       </c>
       <c r="G1069" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1069" t="n">
         <v>6987</v>
@@ -31399,7 +31399,7 @@
         <v>63</v>
       </c>
       <c r="G1070" t="n">
-        <v>58.3458709716797</v>
+        <v>58.345874786377</v>
       </c>
       <c r="H1070" t="n">
         <v>25088</v>
@@ -31428,7 +31428,7 @@
         <v>64</v>
       </c>
       <c r="G1071" t="n">
-        <v>59.2719955444336</v>
+        <v>59.2719917297363</v>
       </c>
       <c r="H1071" t="n">
         <v>19842</v>
@@ -31486,7 +31486,7 @@
         <v>62</v>
       </c>
       <c r="G1073" t="n">
-        <v>57.419750213623</v>
+        <v>57.4197463989258</v>
       </c>
       <c r="H1073" t="n">
         <v>5082</v>
@@ -31515,7 +31515,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>57.6049690246582</v>
+        <v>57.6049728393555</v>
       </c>
       <c r="H1074" t="n">
         <v>9173</v>
@@ -31602,7 +31602,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1077" t="n">
         <v>16965</v>
@@ -31660,7 +31660,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1079" t="n">
-        <v>61.3094673156738</v>
+        <v>61.3094635009766</v>
       </c>
       <c r="H1079" t="n">
         <v>18499</v>
@@ -31747,7 +31747,7 @@
         <v>69</v>
       </c>
       <c r="G1082" t="n">
-        <v>63.9026145935059</v>
+        <v>63.9026260375977</v>
       </c>
       <c r="H1082" t="n">
         <v>5155</v>
@@ -31776,7 +31776,7 @@
         <v>68</v>
       </c>
       <c r="G1083" t="n">
-        <v>62.9764938354492</v>
+        <v>62.976490020752</v>
       </c>
       <c r="H1083" t="n">
         <v>14757</v>
@@ -31805,7 +31805,7 @@
         <v>67</v>
       </c>
       <c r="G1084" t="n">
-        <v>62.050365447998</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1084" t="n">
         <v>14476</v>
@@ -31834,7 +31834,7 @@
         <v>67</v>
       </c>
       <c r="G1085" t="n">
-        <v>62.050365447998</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1085" t="n">
         <v>9085</v>
@@ -31863,7 +31863,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>62.7912788391113</v>
+        <v>62.7912712097168</v>
       </c>
       <c r="H1086" t="n">
         <v>23354</v>
@@ -31892,7 +31892,7 @@
         <v>68</v>
       </c>
       <c r="G1087" t="n">
-        <v>62.9764938354492</v>
+        <v>62.976490020752</v>
       </c>
       <c r="H1087" t="n">
         <v>9103</v>
@@ -31950,7 +31950,7 @@
         <v>68</v>
       </c>
       <c r="G1089" t="n">
-        <v>62.9764938354492</v>
+        <v>62.976490020752</v>
       </c>
       <c r="H1089" t="n">
         <v>7549</v>
@@ -31979,7 +31979,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1090" t="n">
-        <v>66.3105392456055</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1090" t="n">
         <v>11957</v>
@@ -32008,7 +32008,7 @@
         <v>72</v>
       </c>
       <c r="G1091" t="n">
-        <v>66.6809997558594</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1091" t="n">
         <v>20242</v>
@@ -32037,7 +32037,7 @@
         <v>71</v>
       </c>
       <c r="G1092" t="n">
-        <v>65.7548751831055</v>
+        <v>65.7548599243164</v>
       </c>
       <c r="H1092" t="n">
         <v>9074</v>
@@ -32066,7 +32066,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1093" t="n">
-        <v>66.3105392456055</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1093" t="n">
         <v>6325</v>
@@ -32095,7 +32095,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G1094" t="n">
-        <v>65.0139694213867</v>
+        <v>65.0139617919922</v>
       </c>
       <c r="H1094" t="n">
         <v>10097</v>
@@ -32153,7 +32153,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1096" t="n">
-        <v>66.3105392456055</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1096" t="n">
         <v>25041</v>
@@ -32269,7 +32269,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1100" t="n">
-        <v>65.3844146728516</v>
+        <v>65.3844223022461</v>
       </c>
       <c r="H1100" t="n">
         <v>17521</v>
@@ -32298,7 +32298,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1101" t="n">
-        <v>65.3844146728516</v>
+        <v>65.3844223022461</v>
       </c>
       <c r="H1101" t="n">
         <v>9924</v>
@@ -32327,7 +32327,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1102" t="n">
-        <v>65.3844146728516</v>
+        <v>65.3844223022461</v>
       </c>
       <c r="H1102" t="n">
         <v>10321</v>
@@ -32356,7 +32356,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G1103" t="n">
-        <v>65.0139694213867</v>
+        <v>65.0139617919922</v>
       </c>
       <c r="H1103" t="n">
         <v>9902</v>
@@ -32385,7 +32385,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1104" t="n">
-        <v>64.0878372192383</v>
+        <v>64.0878448486328</v>
       </c>
       <c r="H1104" t="n">
         <v>8003</v>
@@ -32443,7 +32443,7 @@
         <v>74.4000015258789</v>
       </c>
       <c r="G1106" t="n">
-        <v>68.903694152832</v>
+        <v>68.9036865234375</v>
       </c>
       <c r="H1106" t="n">
         <v>33245</v>
@@ -32588,7 +32588,7 @@
         <v>71</v>
       </c>
       <c r="G1111" t="n">
-        <v>65.7548751831055</v>
+        <v>65.7548599243164</v>
       </c>
       <c r="H1111" t="n">
         <v>110589</v>
@@ -32675,7 +32675,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1114" t="n">
-        <v>67.4218902587891</v>
+        <v>67.4219055175781</v>
       </c>
       <c r="H1114" t="n">
         <v>10376</v>
@@ -32704,7 +32704,7 @@
         <v>74.4000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>68.903694152832</v>
+        <v>68.9036865234375</v>
       </c>
       <c r="H1115" t="n">
         <v>11706</v>
@@ -32733,7 +32733,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>69.0889129638672</v>
+        <v>69.0889205932617</v>
       </c>
       <c r="H1116" t="n">
         <v>7602</v>
@@ -32936,7 +32936,7 @@
         <v>72</v>
       </c>
       <c r="G1123" t="n">
-        <v>66.6809997558594</v>
+        <v>66.6809921264648</v>
       </c>
       <c r="H1123" t="n">
         <v>3823</v>
@@ -32965,7 +32965,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1124" t="n">
-        <v>66.3105392456055</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1124" t="n">
         <v>19893</v>
@@ -33052,7 +33052,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1127" t="n">
-        <v>67.4218902587891</v>
+        <v>67.4219055175781</v>
       </c>
       <c r="H1127" t="n">
         <v>3719</v>
@@ -33168,7 +33168,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1131" t="n">
-        <v>69.0889129638672</v>
+        <v>69.0889205932617</v>
       </c>
       <c r="H1131" t="n">
         <v>6699</v>
@@ -33226,7 +33226,7 @@
         <v>75</v>
       </c>
       <c r="G1133" t="n">
-        <v>69.4593734741211</v>
+        <v>69.4593658447266</v>
       </c>
       <c r="H1133" t="n">
         <v>3252</v>
@@ -33371,7 +33371,7 @@
         <v>73.8000030517578</v>
       </c>
       <c r="G1138" t="n">
-        <v>68.348030090332</v>
+        <v>68.3480224609375</v>
       </c>
       <c r="H1138" t="n">
         <v>13068</v>
@@ -33429,7 +33429,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1140" t="n">
-        <v>67.4218902587891</v>
+        <v>67.4219055175781</v>
       </c>
       <c r="H1140" t="n">
         <v>4244</v>
@@ -33487,7 +33487,7 @@
         <v>71.5999984741211</v>
       </c>
       <c r="G1142" t="n">
-        <v>66.3105392456055</v>
+        <v>66.310546875</v>
       </c>
       <c r="H1142" t="n">
         <v>6667</v>
@@ -33574,7 +33574,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1145" t="n">
-        <v>64.6435241699219</v>
+        <v>64.6435165405273</v>
       </c>
       <c r="H1145" t="n">
         <v>10235</v>
@@ -33632,7 +33632,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G1147" t="n">
-        <v>62.4208221435547</v>
+        <v>62.4208297729492</v>
       </c>
       <c r="H1147" t="n">
         <v>9458</v>
@@ -33690,7 +33690,7 @@
         <v>67</v>
       </c>
       <c r="G1149" t="n">
-        <v>62.050365447998</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1149" t="n">
         <v>9187</v>
@@ -33719,7 +33719,7 @@
         <v>66</v>
       </c>
       <c r="G1150" t="n">
-        <v>61.1242485046387</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1150" t="n">
         <v>10090</v>
@@ -33748,7 +33748,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G1151" t="n">
-        <v>61.6799163818359</v>
+        <v>61.6799201965332</v>
       </c>
       <c r="H1151" t="n">
         <v>3890</v>
@@ -33777,7 +33777,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1152" t="n">
-        <v>61.3094673156738</v>
+        <v>61.3094635009766</v>
       </c>
       <c r="H1152" t="n">
         <v>5804</v>
@@ -33806,7 +33806,7 @@
         <v>66</v>
       </c>
       <c r="G1153" t="n">
-        <v>61.1242485046387</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1153" t="n">
         <v>7908</v>
@@ -33864,7 +33864,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>60.9390258789062</v>
+        <v>60.939022064209</v>
       </c>
       <c r="H1155" t="n">
         <v>10916</v>
@@ -33893,7 +33893,7 @@
         <v>66</v>
       </c>
       <c r="G1156" t="n">
-        <v>61.1242485046387</v>
+        <v>61.1242408752441</v>
       </c>
       <c r="H1156" t="n">
         <v>6716</v>
@@ -34009,7 +34009,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1160" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276672363281</v>
       </c>
       <c r="H1160" t="n">
         <v>5490</v>
@@ -34067,7 +34067,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1162" t="n">
-        <v>59.457218170166</v>
+        <v>59.4572143554688</v>
       </c>
       <c r="H1162" t="n">
         <v>7471</v>
@@ -34154,7 +34154,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1165" t="n">
         <v>6544</v>
@@ -34241,7 +34241,7 @@
         <v>63</v>
       </c>
       <c r="G1168" t="n">
-        <v>58.3458709716797</v>
+        <v>58.345874786377</v>
       </c>
       <c r="H1168" t="n">
         <v>7543</v>
@@ -34270,7 +34270,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1169" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1169" t="n">
         <v>12328</v>
@@ -34299,7 +34299,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1170" t="n">
-        <v>56.3083953857422</v>
+        <v>56.3083915710449</v>
       </c>
       <c r="H1170" t="n">
         <v>7643</v>
@@ -34386,7 +34386,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>58.1606407165527</v>
+        <v>58.16064453125</v>
       </c>
       <c r="H1173" t="n">
         <v>12736</v>
@@ -34415,7 +34415,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1174" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1174" t="n">
         <v>8061</v>
@@ -34473,7 +34473,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1176" t="n">
-        <v>55.1970443725586</v>
+        <v>55.1970405578613</v>
       </c>
       <c r="H1176" t="n">
         <v>12029</v>
@@ -34502,7 +34502,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>53.5300178527832</v>
+        <v>53.5300216674805</v>
       </c>
       <c r="H1177" t="n">
         <v>10454</v>
@@ -34531,7 +34531,7 @@
         <v>56</v>
       </c>
       <c r="G1178" t="n">
-        <v>51.8629989624023</v>
+        <v>51.8629951477051</v>
       </c>
       <c r="H1178" t="n">
         <v>17018</v>
@@ -34560,7 +34560,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G1179" t="n">
-        <v>51.3073234558105</v>
+        <v>51.3073196411133</v>
       </c>
       <c r="H1179" t="n">
         <v>7235</v>
@@ -34589,7 +34589,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1180" t="n">
-        <v>53.3447914123535</v>
+        <v>53.3447952270508</v>
       </c>
       <c r="H1180" t="n">
         <v>8463</v>
@@ -34618,7 +34618,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>52.2334442138672</v>
+        <v>52.2334480285645</v>
       </c>
       <c r="H1181" t="n">
         <v>3643</v>
@@ -34647,7 +34647,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1182" t="n">
-        <v>55.1970443725586</v>
+        <v>55.1970405578613</v>
       </c>
       <c r="H1182" t="n">
         <v>3171</v>
@@ -34676,7 +34676,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>57.0492897033691</v>
+        <v>57.0492935180664</v>
       </c>
       <c r="H1183" t="n">
         <v>4645</v>
@@ -34734,7 +34734,7 @@
         <v>61</v>
       </c>
       <c r="G1185" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1185" t="n">
         <v>8219</v>
@@ -34763,7 +34763,7 @@
         <v>61</v>
       </c>
       <c r="G1186" t="n">
-        <v>56.4936218261719</v>
+        <v>56.4936180114746</v>
       </c>
       <c r="H1186" t="n">
         <v>3492</v>
@@ -34821,7 +34821,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1188" t="n">
-        <v>60.5685729980469</v>
+        <v>60.5685653686523</v>
       </c>
       <c r="H1188" t="n">
         <v>18854</v>
@@ -34850,7 +34850,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1189" t="n">
-        <v>61.3094673156738</v>
+        <v>61.3094635009766</v>
       </c>
       <c r="H1189" t="n">
         <v>10432</v>
@@ -34879,7 +34879,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1190" t="n">
-        <v>60.9390258789062</v>
+        <v>60.939022064209</v>
       </c>
       <c r="H1190" t="n">
         <v>5931</v>
@@ -34937,7 +34937,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1192" t="n">
-        <v>59.457218170166</v>
+        <v>59.4572143554688</v>
       </c>
       <c r="H1192" t="n">
         <v>4435</v>
@@ -34966,7 +34966,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1193" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276672363281</v>
       </c>
       <c r="H1193" t="n">
         <v>2596</v>
@@ -34995,7 +34995,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1194" t="n">
-        <v>59.8276710510254</v>
+        <v>59.8276672363281</v>
       </c>
       <c r="H1194" t="n">
         <v>7145</v>
@@ -35053,7 +35053,7 @@
         <v>63</v>
       </c>
       <c r="G1196" t="n">
-        <v>58.3458709716797</v>
+        <v>58.345874786377</v>
       </c>
       <c r="H1196" t="n">
         <v>5314</v>
@@ -35111,7 +35111,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G1198" t="n">
-        <v>58.5310935974121</v>
+        <v>58.5310974121094</v>
       </c>
       <c r="H1198" t="n">
         <v>4906</v>
@@ -35169,7 +35169,7 @@
         <v>63.5</v>
       </c>
       <c r="G1200" t="n">
-        <v>58.8089332580566</v>
+        <v>58.8089294433594</v>
       </c>
       <c r="H1200" t="n">
         <v>4442</v>
@@ -35198,7 +35198,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1201" t="n">
-        <v>60.0129013061523</v>
+        <v>60.0128936767578</v>
       </c>
       <c r="H1201" t="n">
         <v>8130</v>
@@ -35227,7 +35227,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1202" t="n">
-        <v>61.8651466369629</v>
+        <v>61.8651504516602</v>
       </c>
       <c r="H1202" t="n">
         <v>7305</v>
@@ -35256,7 +35256,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1203" t="n">
-        <v>61.4946899414062</v>
+        <v>61.4946975708008</v>
       </c>
       <c r="H1203" t="n">
         <v>5708</v>
@@ -35343,7 +35343,7 @@
         <v>67</v>
       </c>
       <c r="G1206" t="n">
-        <v>62.050365447998</v>
+        <v>62.0503730773926</v>
       </c>
       <c r="H1206" t="n">
         <v>7404</v>
@@ -35546,7 +35546,7 @@
         <v>62.7999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>58.1606407165527</v>
+        <v>58.16064453125</v>
       </c>
       <c r="H1213" t="n">
         <v>4220</v>
@@ -35575,7 +35575,7 @@
         <v>63</v>
       </c>
       <c r="G1214" t="n">
-        <v>58.3458709716797</v>
+        <v>58.345874786377</v>
       </c>
       <c r="H1214" t="n">
         <v>4413</v>
@@ -35633,7 +35633,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1216" t="n">
-        <v>60.6766967773438</v>
+        <v>60.6766891479492</v>
       </c>
       <c r="H1216" t="n">
         <v>4647</v>
@@ -35720,7 +35720,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>54.4966583251953</v>
+        <v>54.496654510498</v>
       </c>
       <c r="H1219" t="n">
         <v>6610</v>
@@ -35807,7 +35807,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1222" t="n">
-        <v>54.1221084594727</v>
+        <v>54.1221122741699</v>
       </c>
       <c r="H1222" t="n">
         <v>5048</v>
@@ -35865,7 +35865,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1224" t="n">
-        <v>53.6539306640625</v>
+        <v>53.653923034668</v>
       </c>
       <c r="H1224" t="n">
         <v>2530</v>
@@ -35894,7 +35894,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G1225" t="n">
-        <v>56.8375816345215</v>
+        <v>56.8375778198242</v>
       </c>
       <c r="H1225" t="n">
         <v>3546</v>
@@ -36097,7 +36097,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>57.8675880432129</v>
+        <v>57.8675842285156</v>
       </c>
       <c r="H1232" t="n">
         <v>2813</v>
@@ -36126,7 +36126,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G1233" t="n">
-        <v>59.3657722473145</v>
+        <v>59.3657760620117</v>
       </c>
       <c r="H1233" t="n">
         <v>4469</v>
@@ -36155,7 +36155,7 @@
         <v>62.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1234" t="n">
         <v>3018</v>
@@ -36184,7 +36184,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G1235" t="n">
-        <v>57.9612236022949</v>
+        <v>57.9612274169922</v>
       </c>
       <c r="H1235" t="n">
         <v>3550</v>
@@ -36213,7 +36213,7 @@
         <v>64</v>
       </c>
       <c r="G1236" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1236" t="n">
         <v>3476</v>
@@ -36271,7 +36271,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1238" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1238" t="n">
         <v>8167</v>
@@ -36300,7 +36300,7 @@
         <v>66</v>
       </c>
       <c r="G1239" t="n">
-        <v>61.8003349304199</v>
+        <v>61.8003273010254</v>
       </c>
       <c r="H1239" t="n">
         <v>2567</v>
@@ -36329,7 +36329,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1240" t="n">
         <v>1183</v>
@@ -36387,7 +36387,7 @@
         <v>62.5</v>
       </c>
       <c r="G1242" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
       <c r="H1242" t="n">
         <v>2340</v>
@@ -36445,7 +36445,7 @@
         <v>61.5</v>
       </c>
       <c r="G1244" t="n">
-        <v>57.5866775512695</v>
+        <v>57.5866737365723</v>
       </c>
       <c r="H1244" t="n">
         <v>3144</v>
@@ -36503,7 +36503,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>56.7439384460449</v>
+        <v>56.7439422607422</v>
       </c>
       <c r="H1246" t="n">
         <v>7288</v>
@@ -36532,7 +36532,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>55.9948501586914</v>
+        <v>55.9948463439941</v>
       </c>
       <c r="H1247" t="n">
         <v>5448</v>
@@ -36561,7 +36561,7 @@
         <v>62</v>
       </c>
       <c r="G1248" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548629760742</v>
       </c>
       <c r="H1248" t="n">
         <v>9034</v>
@@ -36909,7 +36909,7 @@
         <v>60</v>
       </c>
       <c r="G1260" t="n">
-        <v>56.1821212768555</v>
+        <v>56.1821250915527</v>
       </c>
       <c r="H1260" t="n">
         <v>873</v>
@@ -37025,7 +37025,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1264" t="n">
-        <v>60.6766967773438</v>
+        <v>60.6766891479492</v>
       </c>
       <c r="H1264" t="n">
         <v>17158</v>
@@ -37054,7 +37054,7 @@
         <v>67</v>
       </c>
       <c r="G1265" t="n">
-        <v>62.7366981506348</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1265" t="n">
         <v>20893</v>
@@ -37083,7 +37083,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G1266" t="n">
-        <v>61.6130599975586</v>
+        <v>61.6130638122559</v>
       </c>
       <c r="H1266" t="n">
         <v>8319</v>
@@ -37141,7 +37141,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1268" t="n">
-        <v>60.7703285217285</v>
+        <v>60.7703247070312</v>
       </c>
       <c r="H1268" t="n">
         <v>6160</v>
@@ -37170,7 +37170,7 @@
         <v>63</v>
       </c>
       <c r="G1269" t="n">
-        <v>58.9912261962891</v>
+        <v>58.9912300109863</v>
       </c>
       <c r="H1269" t="n">
         <v>5348</v>
@@ -37257,7 +37257,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1272" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1272" t="n">
         <v>836</v>
@@ -37402,7 +37402,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1277" t="n">
-        <v>61.4257850646973</v>
+        <v>61.42578125</v>
       </c>
       <c r="H1277" t="n">
         <v>3313</v>
@@ -37547,7 +37547,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G1282" t="n">
-        <v>64.3285293579102</v>
+        <v>64.3285217285156</v>
       </c>
       <c r="H1282" t="n">
         <v>2456</v>
@@ -37576,7 +37576,7 @@
         <v>68</v>
       </c>
       <c r="G1283" t="n">
-        <v>63.6730766296387</v>
+        <v>63.6730651855469</v>
       </c>
       <c r="H1283" t="n">
         <v>3127</v>
@@ -37634,7 +37634,7 @@
         <v>67</v>
       </c>
       <c r="G1285" t="n">
-        <v>62.7366981506348</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1285" t="n">
         <v>3334</v>
@@ -37663,7 +37663,7 @@
         <v>68</v>
       </c>
       <c r="G1286" t="n">
-        <v>63.6730766296387</v>
+        <v>63.6730651855469</v>
       </c>
       <c r="H1286" t="n">
         <v>4639</v>
@@ -37721,7 +37721,7 @@
         <v>69</v>
       </c>
       <c r="G1288" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1288" t="n">
         <v>4841</v>
@@ -37808,7 +37808,7 @@
         <v>68.1999969482422</v>
       </c>
       <c r="G1291" t="n">
-        <v>63.8603401184082</v>
+        <v>63.8603363037109</v>
       </c>
       <c r="H1291" t="n">
         <v>716</v>
@@ -37837,7 +37837,7 @@
         <v>68.0999984741211</v>
       </c>
       <c r="G1292" t="n">
-        <v>63.7667045593262</v>
+        <v>63.7667083740234</v>
       </c>
       <c r="H1292" t="n">
         <v>2952</v>
@@ -37866,7 +37866,7 @@
         <v>67.5999984741211</v>
       </c>
       <c r="G1293" t="n">
-        <v>63.2985153198242</v>
+        <v>63.2985191345215</v>
       </c>
       <c r="H1293" t="n">
         <v>6297</v>
@@ -37924,7 +37924,7 @@
         <v>67</v>
       </c>
       <c r="G1295" t="n">
-        <v>62.7366981506348</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1295" t="n">
         <v>3848</v>
@@ -38011,7 +38011,7 @@
         <v>69</v>
       </c>
       <c r="G1298" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1298" t="n">
         <v>3290</v>
@@ -38040,7 +38040,7 @@
         <v>69</v>
       </c>
       <c r="G1299" t="n">
-        <v>64.6094360351562</v>
+        <v>64.6094436645508</v>
       </c>
       <c r="H1299" t="n">
         <v>4702</v>
@@ -38127,7 +38127,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G1302" t="n">
-        <v>63.3921585083008</v>
+        <v>63.392162322998</v>
       </c>
       <c r="H1302" t="n">
         <v>6182</v>
@@ -38156,7 +38156,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1303" t="n">
-        <v>63.5794334411621</v>
+        <v>63.5794410705566</v>
       </c>
       <c r="H1303" t="n">
         <v>7397</v>
@@ -38185,7 +38185,7 @@
         <v>70</v>
       </c>
       <c r="G1304" t="n">
-        <v>65.5458145141602</v>
+        <v>65.5458068847656</v>
       </c>
       <c r="H1304" t="n">
         <v>9973</v>
@@ -38243,7 +38243,7 @@
         <v>71</v>
       </c>
       <c r="G1306" t="n">
-        <v>66.482177734375</v>
+        <v>66.4821701049805</v>
       </c>
       <c r="H1306" t="n">
         <v>11441</v>
@@ -38272,7 +38272,7 @@
         <v>71</v>
       </c>
       <c r="G1307" t="n">
-        <v>66.482177734375</v>
+        <v>66.4821701049805</v>
       </c>
       <c r="H1307" t="n">
         <v>11320</v>
@@ -38301,7 +38301,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1308" t="n">
-        <v>66.1076278686523</v>
+        <v>66.1076354980469</v>
       </c>
       <c r="H1308" t="n">
         <v>13536</v>
@@ -38330,7 +38330,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1309" t="n">
-        <v>65.3585433959961</v>
+        <v>65.3585357666016</v>
       </c>
       <c r="H1309" t="n">
         <v>5793</v>
@@ -38359,7 +38359,7 @@
         <v>71.0999984741211</v>
       </c>
       <c r="G1310" t="n">
-        <v>66.575813293457</v>
+        <v>66.5758056640625</v>
       </c>
       <c r="H1310" t="n">
         <v>23508</v>
@@ -38388,7 +38388,7 @@
         <v>70.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>66.0139923095703</v>
+        <v>66.0139999389648</v>
       </c>
       <c r="H1311" t="n">
         <v>9821</v>
@@ -38446,7 +38446,7 @@
         <v>70</v>
       </c>
       <c r="G1313" t="n">
-        <v>65.5458145141602</v>
+        <v>65.5458068847656</v>
       </c>
       <c r="H1313" t="n">
         <v>6557</v>
@@ -38533,7 +38533,7 @@
         <v>68</v>
       </c>
       <c r="G1316" t="n">
-        <v>63.6730766296387</v>
+        <v>63.6730651855469</v>
       </c>
       <c r="H1316" t="n">
         <v>16446</v>
@@ -38591,7 +38591,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1318" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1318" t="n">
         <v>6967</v>
@@ -38707,7 +38707,7 @@
         <v>64</v>
       </c>
       <c r="G1322" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1322" t="n">
         <v>13481</v>
@@ -38765,7 +38765,7 @@
         <v>66.3000030517578</v>
       </c>
       <c r="G1324" t="n">
-        <v>62.0812492370605</v>
+        <v>62.0812530517578</v>
       </c>
       <c r="H1324" t="n">
         <v>7316</v>
@@ -38794,7 +38794,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1325" t="n">
-        <v>61.4257850646973</v>
+        <v>61.42578125</v>
       </c>
       <c r="H1325" t="n">
         <v>5034</v>
@@ -38823,7 +38823,7 @@
         <v>66</v>
       </c>
       <c r="G1326" t="n">
-        <v>61.8003349304199</v>
+        <v>61.8003273010254</v>
       </c>
       <c r="H1326" t="n">
         <v>4243</v>
@@ -38852,7 +38852,7 @@
         <v>66</v>
       </c>
       <c r="G1327" t="n">
-        <v>61.8003349304199</v>
+        <v>61.8003273010254</v>
       </c>
       <c r="H1327" t="n">
         <v>2465</v>
@@ -38881,7 +38881,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1328" t="n">
-        <v>60.7703285217285</v>
+        <v>60.7703247070312</v>
       </c>
       <c r="H1328" t="n">
         <v>5636</v>
@@ -38910,7 +38910,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1329" t="n">
-        <v>61.4257850646973</v>
+        <v>61.42578125</v>
       </c>
       <c r="H1329" t="n">
         <v>4284</v>
@@ -38939,7 +38939,7 @@
         <v>64.9000015258789</v>
       </c>
       <c r="G1330" t="n">
-        <v>60.7703285217285</v>
+        <v>60.7703247070312</v>
       </c>
       <c r="H1330" t="n">
         <v>3373</v>
@@ -38968,7 +38968,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1331" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1331" t="n">
         <v>1785</v>
@@ -38997,7 +38997,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1332" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1332" t="n">
         <v>3100</v>
@@ -39084,7 +39084,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G1335" t="n">
-        <v>60.9575996398926</v>
+        <v>60.9576034545898</v>
       </c>
       <c r="H1335" t="n">
         <v>1813</v>
@@ -39113,7 +39113,7 @@
         <v>64</v>
       </c>
       <c r="G1336" t="n">
-        <v>59.9275970458984</v>
+        <v>59.9275932312012</v>
       </c>
       <c r="H1336" t="n">
         <v>3411</v>
@@ -39142,7 +39142,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1337" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1337" t="n">
         <v>889</v>
@@ -39171,7 +39171,7 @@
         <v>65.0999984741211</v>
       </c>
       <c r="G1338" t="n">
-        <v>60.9575996398926</v>
+        <v>60.9576034545898</v>
       </c>
       <c r="H1338" t="n">
         <v>1104</v>
@@ -39229,7 +39229,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G1340" t="n">
-        <v>61.0512313842773</v>
+        <v>61.0512390136719</v>
       </c>
       <c r="H1340" t="n">
         <v>2138</v>
@@ -39345,7 +39345,7 @@
         <v>68</v>
       </c>
       <c r="G1344" t="n">
-        <v>63.6730766296387</v>
+        <v>63.6730651855469</v>
       </c>
       <c r="H1344" t="n">
         <v>1117</v>
@@ -39374,7 +39374,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1345" t="n">
-        <v>63.4858016967773</v>
+        <v>63.4857978820801</v>
       </c>
       <c r="H1345" t="n">
         <v>2489</v>
@@ -39403,7 +39403,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G1346" t="n">
-        <v>63.3921585083008</v>
+        <v>63.392162322998</v>
       </c>
       <c r="H1346" t="n">
         <v>1676</v>
@@ -39432,7 +39432,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G1347" t="n">
-        <v>63.0176124572754</v>
+        <v>63.0176162719727</v>
       </c>
       <c r="H1347" t="n">
         <v>1993</v>
@@ -39461,7 +39461,7 @@
         <v>66.9000015258789</v>
       </c>
       <c r="G1348" t="n">
-        <v>62.6430702209473</v>
+        <v>62.64306640625</v>
       </c>
       <c r="H1348" t="n">
         <v>1938</v>
@@ -39606,7 +39606,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1353" t="n">
-        <v>63.5794334411621</v>
+        <v>63.5794410705566</v>
       </c>
       <c r="H1353" t="n">
         <v>2513</v>
@@ -39635,7 +39635,7 @@
         <v>67</v>
       </c>
       <c r="G1354" t="n">
-        <v>62.7366981506348</v>
+        <v>62.7367057800293</v>
       </c>
       <c r="H1354" t="n">
         <v>1811</v>
@@ -39693,7 +39693,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1356" t="n">
-        <v>61.4257850646973</v>
+        <v>61.42578125</v>
       </c>
       <c r="H1356" t="n">
         <v>5483</v>
@@ -39780,7 +39780,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1359" t="n">
-        <v>60.6766967773438</v>
+        <v>60.6766891479492</v>
       </c>
       <c r="H1359" t="n">
         <v>1409</v>
@@ -39809,7 +39809,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1360" t="n">
-        <v>60.5830497741699</v>
+        <v>60.5830535888672</v>
       </c>
       <c r="H1360" t="n">
         <v>366</v>
@@ -39896,7 +39896,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>60.3021430969238</v>
+        <v>60.3021469116211</v>
       </c>
       <c r="H1363" t="n">
         <v>5150</v>
@@ -39954,7 +39954,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G1365" t="n">
-        <v>57.9612236022949</v>
+        <v>57.9612274169922</v>
       </c>
       <c r="H1365" t="n">
         <v>5916</v>
@@ -39983,7 +39983,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1366" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1366" t="n">
         <v>9059</v>
@@ -40041,7 +40041,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G1368" t="n">
-        <v>58.4294052124023</v>
+        <v>58.4294090270996</v>
       </c>
       <c r="H1368" t="n">
         <v>3876</v>
@@ -40070,7 +40070,7 @@
         <v>62</v>
       </c>
       <c r="G1369" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548629760742</v>
       </c>
       <c r="H1369" t="n">
         <v>2182</v>
@@ -40099,7 +40099,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1370" t="n">
-        <v>58.8975944519043</v>
+        <v>58.897590637207</v>
       </c>
       <c r="H1370" t="n">
         <v>2370</v>
@@ -40157,7 +40157,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1372" t="n">
-        <v>57.6803092956543</v>
+        <v>57.6803131103516</v>
       </c>
       <c r="H1372" t="n">
         <v>6771</v>
@@ -40244,7 +40244,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1375" t="n">
-        <v>58.6166839599609</v>
+        <v>58.6166763305664</v>
       </c>
       <c r="H1375" t="n">
         <v>2697</v>
@@ -40273,7 +40273,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1376" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1376" t="n">
         <v>7123</v>
@@ -40302,7 +40302,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1377" t="n">
-        <v>59.553050994873</v>
+        <v>59.5530471801758</v>
       </c>
       <c r="H1377" t="n">
         <v>4730</v>
@@ -40360,7 +40360,7 @@
         <v>62</v>
       </c>
       <c r="G1379" t="n">
-        <v>58.054859161377</v>
+        <v>58.0548629760742</v>
       </c>
       <c r="H1379" t="n">
         <v>4144</v>
@@ -40389,7 +40389,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1380" t="n">
-        <v>58.7103157043457</v>
+        <v>58.710319519043</v>
       </c>
       <c r="H1380" t="n">
         <v>796</v>
@@ -40418,7 +40418,7 @@
         <v>63</v>
       </c>
       <c r="G1381" t="n">
-        <v>58.9912261962891</v>
+        <v>58.9912300109863</v>
       </c>
       <c r="H1381" t="n">
         <v>876</v>
@@ -40447,7 +40447,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1382" t="n">
-        <v>58.8975944519043</v>
+        <v>58.897590637207</v>
       </c>
       <c r="H1382" t="n">
         <v>1175</v>
@@ -40476,7 +40476,7 @@
         <v>62.5</v>
       </c>
       <c r="G1383" t="n">
-        <v>58.5230445861816</v>
+        <v>58.5230407714844</v>
       </c>
